--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3159" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3165" uniqueCount="489">
   <si>
     <t>trade_time</t>
   </si>
@@ -1111,7 +1111,10 @@
     <t>2021-05-10</t>
   </si>
   <si>
-    <t>2021-07-20</t>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1473,6 +1476,12 @@
   <si>
     <t>2021-07-09</t>
   </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>2021-07-15</t>
+  </si>
 </sst>
 </file>
 
@@ -1829,7 +1838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1049"/>
+  <dimension ref="A1:P1051"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1926,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1976,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2026,7 +2035,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2076,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2126,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2176,7 +2185,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2226,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2276,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2326,7 +2335,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2376,7 +2385,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2426,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2476,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2526,7 +2535,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2576,7 +2585,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2626,7 +2635,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2676,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2726,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2776,7 +2785,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2826,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2876,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2926,7 +2935,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2976,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3026,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3076,7 +3085,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3126,7 +3135,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3176,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3226,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3276,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3326,7 +3335,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3376,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3426,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3476,7 +3485,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3776,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3826,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3876,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3926,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3976,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4026,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4076,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4126,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4176,7 +4185,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4226,7 +4235,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4276,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4326,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4376,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4426,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4476,7 +4485,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4526,7 +4535,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4576,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4626,7 +4635,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4676,7 +4685,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4726,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4776,7 +4785,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4826,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4876,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4926,7 +4935,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4976,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5026,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5076,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5126,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5176,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5226,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5276,7 +5285,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5326,7 +5335,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5376,7 +5385,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5426,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5476,7 +5485,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5526,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5576,7 +5585,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5626,7 +5635,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5676,7 +5685,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5726,7 +5735,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5976,7 +5985,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6026,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6076,7 +6085,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6126,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6776,7 +6785,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6826,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6876,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6926,7 +6935,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6976,7 +6985,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7026,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7076,7 +7085,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7126,7 +7135,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7176,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7226,7 +7235,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7276,7 +7285,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7326,7 +7335,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7576,7 +7585,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7626,7 +7635,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7676,7 +7685,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7726,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8026,7 +8035,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8076,7 +8085,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8126,7 +8135,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8176,7 +8185,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8226,7 +8235,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8276,7 +8285,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8326,7 +8335,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8776,7 +8785,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8826,7 +8835,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8876,7 +8885,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8926,7 +8935,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8976,7 +8985,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9026,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9076,7 +9085,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9126,7 +9135,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9176,7 +9185,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9226,7 +9235,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9276,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9326,7 +9335,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9376,7 +9385,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9426,7 +9435,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9476,7 +9485,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9526,7 +9535,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9576,7 +9585,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9626,7 +9635,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9676,7 +9685,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9726,7 +9735,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9776,7 +9785,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9826,7 +9835,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9876,7 +9885,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9926,7 +9935,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9976,7 +9985,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10026,7 +10035,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10076,7 +10085,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10126,7 +10135,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10176,7 +10185,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10226,7 +10235,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10276,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10326,7 +10335,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10376,7 +10385,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10426,7 +10435,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10476,7 +10485,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10526,7 +10535,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10576,7 +10585,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10626,7 +10635,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10676,7 +10685,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10726,7 +10735,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10776,7 +10785,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10826,7 +10835,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10876,7 +10885,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10926,7 +10935,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11276,7 +11285,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11326,7 +11335,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11376,7 +11385,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11426,7 +11435,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11476,7 +11485,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11526,7 +11535,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11576,7 +11585,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11976,7 +11985,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12026,7 +12035,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12076,7 +12085,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12126,7 +12135,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12176,7 +12185,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12226,7 +12235,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12276,7 +12285,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12326,7 +12335,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12376,7 +12385,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12426,7 +12435,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12476,7 +12485,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12526,7 +12535,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12576,7 +12585,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12626,7 +12635,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12676,7 +12685,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12726,7 +12735,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12776,7 +12785,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12826,7 +12835,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12876,7 +12885,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12926,7 +12935,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12976,7 +12985,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -13926,7 +13935,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13976,7 +13985,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14026,7 +14035,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14076,7 +14085,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14126,7 +14135,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14176,7 +14185,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14226,7 +14235,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14276,7 +14285,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14326,7 +14335,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14376,7 +14385,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14426,7 +14435,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14476,7 +14485,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14526,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14576,7 +14585,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14626,7 +14635,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14676,7 +14685,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14726,7 +14735,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14776,7 +14785,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14826,7 +14835,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14876,7 +14885,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14926,7 +14935,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14976,7 +14985,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15026,7 +15035,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15076,7 +15085,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15126,7 +15135,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15176,7 +15185,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15226,7 +15235,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15276,7 +15285,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15326,7 +15335,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15376,7 +15385,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15426,7 +15435,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15476,7 +15485,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15526,7 +15535,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15576,7 +15585,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15626,7 +15635,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15676,7 +15685,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15726,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15776,7 +15785,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15826,7 +15835,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15876,7 +15885,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15926,7 +15935,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15976,7 +15985,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -16026,7 +16035,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16076,7 +16085,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16126,7 +16135,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16176,7 +16185,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16226,7 +16235,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16276,7 +16285,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16326,7 +16335,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16376,7 +16385,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16426,7 +16435,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16476,7 +16485,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16526,7 +16535,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16576,7 +16585,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16626,7 +16635,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16676,7 +16685,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16726,7 +16735,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16776,7 +16785,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16826,7 +16835,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16876,7 +16885,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16926,7 +16935,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16976,7 +16985,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17026,7 +17035,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17076,7 +17085,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17126,7 +17135,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17176,7 +17185,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17226,7 +17235,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17276,7 +17285,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17326,7 +17335,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17376,7 +17385,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17426,7 +17435,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17476,7 +17485,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17526,7 +17535,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17576,7 +17585,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17626,7 +17635,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17676,7 +17685,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17726,7 +17735,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17776,7 +17785,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17826,7 +17835,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17876,7 +17885,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17926,7 +17935,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17976,7 +17985,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -18026,7 +18035,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18526,7 +18535,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18576,7 +18585,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18626,7 +18635,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18676,7 +18685,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18726,7 +18735,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18776,7 +18785,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18826,7 +18835,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18876,7 +18885,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18926,7 +18935,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18976,7 +18985,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19026,7 +19035,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19076,7 +19085,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19126,7 +19135,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19176,7 +19185,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19226,7 +19235,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19276,7 +19285,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19326,7 +19335,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19376,7 +19385,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19426,7 +19435,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19476,7 +19485,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19526,7 +19535,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19576,7 +19585,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19626,7 +19635,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19676,7 +19685,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19726,7 +19735,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19776,7 +19785,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19826,7 +19835,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19876,7 +19885,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19926,7 +19935,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19976,7 +19985,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20026,7 +20035,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20076,7 +20085,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20126,7 +20135,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20176,7 +20185,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20226,7 +20235,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20276,7 +20285,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20326,7 +20335,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20376,7 +20385,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20426,7 +20435,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20476,7 +20485,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20526,7 +20535,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20576,7 +20585,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20626,7 +20635,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20676,7 +20685,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20726,7 +20735,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20776,7 +20785,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20826,7 +20835,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20876,7 +20885,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20926,7 +20935,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20976,7 +20985,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21026,7 +21035,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21076,7 +21085,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21126,7 +21135,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21176,7 +21185,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21226,7 +21235,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21276,7 +21285,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21326,7 +21335,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21376,7 +21385,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21426,7 +21435,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21476,7 +21485,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21526,7 +21535,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21576,7 +21585,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21626,7 +21635,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21676,7 +21685,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21726,7 +21735,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21776,7 +21785,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21826,7 +21835,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21876,7 +21885,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21926,7 +21935,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21976,7 +21985,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22026,7 +22035,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22076,7 +22085,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22126,7 +22135,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22176,7 +22185,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22226,7 +22235,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22276,7 +22285,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22326,7 +22335,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22376,7 +22385,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22426,7 +22435,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22476,7 +22485,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22526,7 +22535,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22576,7 +22585,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22626,7 +22635,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22676,7 +22685,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22726,7 +22735,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22776,7 +22785,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22826,7 +22835,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22876,7 +22885,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22926,7 +22935,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22976,7 +22985,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23026,7 +23035,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23076,7 +23085,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23126,7 +23135,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23176,7 +23185,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23226,7 +23235,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23276,7 +23285,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23326,7 +23335,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23376,7 +23385,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23426,7 +23435,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23476,7 +23485,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23526,7 +23535,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23576,7 +23585,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23626,7 +23635,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23676,7 +23685,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23726,7 +23735,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23776,7 +23785,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23826,7 +23835,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23876,7 +23885,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23926,7 +23935,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23976,7 +23985,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24026,7 +24035,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24076,7 +24085,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24126,7 +24135,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24176,7 +24185,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24226,7 +24235,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24276,7 +24285,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24326,7 +24335,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24376,7 +24385,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24426,7 +24435,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24476,7 +24485,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24526,7 +24535,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24576,7 +24585,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24626,7 +24635,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24676,7 +24685,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24726,7 +24735,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24776,7 +24785,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24826,7 +24835,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24876,7 +24885,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24926,7 +24935,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25276,7 +25285,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25326,7 +25335,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25376,7 +25385,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25426,7 +25435,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25476,7 +25485,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25526,7 +25535,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25576,7 +25585,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25626,7 +25635,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25676,7 +25685,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25726,7 +25735,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25776,7 +25785,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25826,7 +25835,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25876,7 +25885,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25926,7 +25935,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25976,7 +25985,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26026,7 +26035,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26076,7 +26085,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26126,7 +26135,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26176,7 +26185,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26226,7 +26235,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26876,7 +26885,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26926,7 +26935,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26976,7 +26985,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27026,7 +27035,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27076,7 +27085,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27126,7 +27135,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27176,7 +27185,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27226,7 +27235,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27276,7 +27285,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27326,7 +27335,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27376,7 +27385,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27426,7 +27435,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27476,7 +27485,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28126,7 +28135,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28176,7 +28185,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28226,7 +28235,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28276,7 +28285,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28326,7 +28335,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28376,7 +28385,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28426,7 +28435,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28476,7 +28485,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28526,7 +28535,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28576,7 +28585,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28626,7 +28635,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28676,7 +28685,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -32226,7 +32235,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32276,7 +32285,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32326,7 +32335,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32376,7 +32385,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32426,7 +32435,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32476,7 +32485,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32526,7 +32535,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32576,7 +32585,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32626,7 +32635,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33476,7 +33485,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33526,7 +33535,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33576,7 +33585,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33626,7 +33635,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33676,7 +33685,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33726,7 +33735,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33776,7 +33785,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33826,7 +33835,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33876,7 +33885,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33926,7 +33935,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33976,7 +33985,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34026,7 +34035,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34076,7 +34085,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34126,7 +34135,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34176,7 +34185,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34226,7 +34235,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -35076,7 +35085,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35126,7 +35135,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35176,7 +35185,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35226,7 +35235,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35276,7 +35285,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35326,7 +35335,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35376,7 +35385,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35426,7 +35435,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35476,7 +35485,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35526,7 +35535,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35576,7 +35585,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35626,7 +35635,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35676,7 +35685,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35726,7 +35735,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35776,7 +35785,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36176,7 +36185,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36226,7 +36235,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36276,7 +36285,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36326,7 +36335,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36376,7 +36385,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36426,7 +36435,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36476,7 +36485,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37226,7 +37235,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37276,7 +37285,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37326,7 +37335,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37376,7 +37385,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37426,7 +37435,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37476,7 +37485,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37526,7 +37535,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37576,7 +37585,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37626,7 +37635,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37676,7 +37685,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37726,7 +37735,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37776,7 +37785,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37826,7 +37835,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37876,7 +37885,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37926,7 +37935,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37976,7 +37985,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38026,7 +38035,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38076,7 +38085,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38126,7 +38135,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38176,7 +38185,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38626,7 +38635,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38676,7 +38685,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38726,7 +38735,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38776,7 +38785,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38826,7 +38835,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38876,7 +38885,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38926,7 +38935,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39276,7 +39285,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39326,7 +39335,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39376,7 +39385,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39426,7 +39435,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39476,7 +39485,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39526,7 +39535,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39576,7 +39585,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39626,7 +39635,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39676,7 +39685,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39726,7 +39735,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39776,7 +39785,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -41876,7 +41885,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41926,7 +41935,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41976,7 +41985,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42026,7 +42035,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42076,7 +42085,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42126,7 +42135,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42176,7 +42185,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42226,7 +42235,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42276,7 +42285,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42326,7 +42335,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42376,7 +42385,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42426,7 +42435,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42476,7 +42485,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42526,7 +42535,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42576,7 +42585,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42626,7 +42635,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42676,7 +42685,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42726,7 +42735,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -42776,7 +42785,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -42826,7 +42835,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -42876,7 +42885,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42926,7 +42935,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42976,7 +42985,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -44626,7 +44635,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44676,7 +44685,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44726,7 +44735,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44776,7 +44785,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44826,7 +44835,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44876,7 +44885,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44926,7 +44935,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44976,7 +44985,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45026,7 +45035,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45076,7 +45085,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45126,7 +45135,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45176,7 +45185,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45426,7 +45435,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45476,7 +45485,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45526,7 +45535,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45576,7 +45585,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45626,7 +45635,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45676,7 +45685,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45726,7 +45735,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -45776,7 +45785,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -45826,7 +45835,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -45876,7 +45885,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -45926,7 +45935,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -45976,7 +45985,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46026,7 +46035,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46076,7 +46085,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46476,7 +46485,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46526,7 +46535,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46576,7 +46585,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -48726,7 +48735,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -48776,7 +48785,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -48826,7 +48835,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -48876,7 +48885,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -48926,7 +48935,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -48976,7 +48985,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49026,7 +49035,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49076,7 +49085,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49126,7 +49135,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49176,7 +49185,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49226,7 +49235,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49276,7 +49285,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49326,7 +49335,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49376,7 +49385,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49426,7 +49435,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49476,7 +49485,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49526,7 +49535,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49576,7 +49585,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49626,7 +49635,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49676,7 +49685,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -49726,7 +49735,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -49776,7 +49785,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -49826,7 +49835,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -49876,7 +49885,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -49926,7 +49935,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -49976,7 +49985,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50026,7 +50035,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50076,7 +50085,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50126,7 +50135,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50176,7 +50185,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50226,7 +50235,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -50276,7 +50285,7 @@
         <v>1</v>
       </c>
       <c r="P969" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="970" spans="1:16">
@@ -50326,7 +50335,7 @@
         <v>1</v>
       </c>
       <c r="P970" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="971" spans="1:16">
@@ -50376,7 +50385,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -50426,7 +50435,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -50476,7 +50485,7 @@
         <v>1</v>
       </c>
       <c r="P973" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="974" spans="1:16">
@@ -50526,7 +50535,7 @@
         <v>1</v>
       </c>
       <c r="P974" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="975" spans="1:16">
@@ -50576,7 +50585,7 @@
         <v>1</v>
       </c>
       <c r="P975" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="976" spans="1:16">
@@ -50626,7 +50635,7 @@
         <v>1</v>
       </c>
       <c r="P976" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="977" spans="1:16">
@@ -50676,7 +50685,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50726,7 +50735,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50776,7 +50785,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50826,7 +50835,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50876,7 +50885,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50926,7 +50935,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50976,7 +50985,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51026,7 +51035,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51076,7 +51085,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51126,7 +51135,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51176,7 +51185,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51226,7 +51235,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51276,7 +51285,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51326,7 +51335,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51376,7 +51385,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51426,7 +51435,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51476,7 +51485,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51526,7 +51535,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51576,7 +51585,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51626,7 +51635,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51676,7 +51685,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51726,7 +51735,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51776,7 +51785,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51826,7 +51835,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51876,7 +51885,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -52076,7 +52085,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52126,7 +52135,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52176,7 +52185,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52226,7 +52235,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52476,7 +52485,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52526,7 +52535,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -52576,7 +52585,7 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -52626,7 +52635,7 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -52676,7 +52685,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52726,7 +52735,7 @@
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
@@ -52776,7 +52785,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52826,7 +52835,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52876,7 +52885,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52926,7 +52935,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -52976,7 +52985,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -53026,7 +53035,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53076,7 +53085,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53126,7 +53135,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53176,7 +53185,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53226,7 +53235,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53276,7 +53285,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53326,7 +53335,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53376,7 +53385,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53426,7 +53435,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53476,7 +53485,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53493,7 +53502,7 @@
         <v>365</v>
       </c>
       <c r="E1034">
-        <v>1.712250857986236</v>
+        <v>1.786386262736427</v>
       </c>
       <c r="F1034">
         <v>1</v>
@@ -53502,10 +53511,10 @@
         <v>0.006789674113414224</v>
       </c>
       <c r="H1034">
-        <v>0.006627749142013764</v>
+        <v>0.006633613737263573</v>
       </c>
       <c r="I1034">
-        <v>0.001924971400458997</v>
+        <v>0.0760603761506502</v>
       </c>
       <c r="J1034">
         <v>0.6827080950038233</v>
@@ -53517,16 +53526,16 @@
         <v>4.25</v>
       </c>
       <c r="M1034">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N1034">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="O1034">
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53534,49 +53543,49 @@
         <v>0</v>
       </c>
       <c r="B1035" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1035">
+        <v>1.815102844953163</v>
+      </c>
+      <c r="D1035" t="s">
         <v>220</v>
       </c>
-      <c r="C1035">
+      <c r="E1035">
         <v>1.683711088313052</v>
       </c>
-      <c r="D1035" t="s">
-        <v>365</v>
-      </c>
-      <c r="E1035">
-        <v>1.686494601593276</v>
-      </c>
       <c r="F1035">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1035">
+        <v>0.006864897155046836</v>
+      </c>
+      <c r="H1035">
         <v>0.006816288911686948</v>
       </c>
-      <c r="H1035">
-        <v>0.006653505398406724</v>
-      </c>
       <c r="I1035">
-        <v>0.002783513280224081</v>
+        <v>0.1313917566401117</v>
       </c>
       <c r="J1035">
         <v>0.6898626106685345</v>
       </c>
       <c r="K1035">
+        <v>3.66</v>
+      </c>
+      <c r="L1035">
+        <v>4.34</v>
+      </c>
+      <c r="M1035">
         <v>3.72</v>
       </c>
-      <c r="L1035">
+      <c r="N1035">
         <v>4.25</v>
       </c>
-      <c r="M1035">
-        <v>3.6</v>
-      </c>
-      <c r="N1035">
-        <v>4.17</v>
-      </c>
       <c r="O1035">
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -53626,168 +53635,168 @@
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
       <c r="A1037" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1037" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1037">
-        <v>1.611570514679623</v>
+        <v>1.745068418380975</v>
       </c>
       <c r="D1037" t="s">
-        <v>365</v>
+        <v>220</v>
       </c>
       <c r="E1037">
-        <v>1.646707694092438</v>
+        <v>1.612528556387221</v>
       </c>
       <c r="F1037">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1037">
-        <v>0.006868429485320376</v>
+        <v>0.006934931581619024</v>
       </c>
       <c r="H1037">
-        <v>0.006693292305907562</v>
+        <v>0.006887471443612779</v>
       </c>
       <c r="I1037">
-        <v>0.03513717941281458</v>
+        <v>0.1325398619937541</v>
       </c>
       <c r="J1037">
-        <v>0.7009145294187672</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1037">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="L1037">
-        <v>4.24</v>
+        <v>4.34</v>
       </c>
       <c r="M1037">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N1037">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="O1037">
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
       <c r="A1038" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1038" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1038">
-        <v>1.745068418380975</v>
+        <v>1.581258625390344</v>
       </c>
       <c r="D1038" t="s">
-        <v>220</v>
+        <v>365</v>
       </c>
       <c r="E1038">
-        <v>1.612528556387221</v>
+        <v>1.693058165369526</v>
       </c>
       <c r="F1038">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1038">
-        <v>0.006934931581619024</v>
+        <v>0.006898741374609657</v>
       </c>
       <c r="H1038">
-        <v>0.006887471443612779</v>
+        <v>0.006726941834630474</v>
       </c>
       <c r="I1038">
-        <v>0.1325398619937541</v>
+        <v>0.1117995399791814</v>
       </c>
       <c r="J1038">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1038">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="L1038">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="M1038">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="N1038">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="O1038">
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
       <c r="A1039" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1039" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1039">
-        <v>1.581258625390344</v>
+        <v>1.699617198359457</v>
       </c>
       <c r="D1039" t="s">
-        <v>365</v>
+        <v>220</v>
       </c>
       <c r="E1039">
-        <v>1.61760828037473</v>
+        <v>1.592473309406249</v>
       </c>
       <c r="F1039">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1039">
-        <v>0.006898741374609657</v>
+        <v>0.007000382801640542</v>
       </c>
       <c r="H1039">
-        <v>0.006722391719625269</v>
+        <v>0.006907526690593752</v>
       </c>
       <c r="I1039">
-        <v>0.0363496549843858</v>
+        <v>0.1071438889532086</v>
       </c>
       <c r="J1039">
-        <v>0.7089976998959082</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1039">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="L1039">
-        <v>4.24</v>
+        <v>4.35</v>
       </c>
       <c r="M1039">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N1039">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="O1039">
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1040" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C1040">
-        <v>1.699617198359457</v>
+        <v>1.725336643125503</v>
       </c>
       <c r="D1040" t="s">
         <v>220</v>
@@ -53799,22 +53808,22 @@
         <v>-1</v>
       </c>
       <c r="G1040">
-        <v>0.007000382801640542</v>
+        <v>0.006954663356874498</v>
       </c>
       <c r="H1040">
         <v>0.006907526690593752</v>
       </c>
       <c r="I1040">
-        <v>0.1071438889532086</v>
+        <v>0.132863333719254</v>
       </c>
       <c r="J1040">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1040">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="L1040">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="M1040">
         <v>3.72</v>
@@ -53826,118 +53835,118 @@
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1041" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1041">
-        <v>1.725336643125503</v>
+        <v>1.561041642546622</v>
       </c>
       <c r="D1041" t="s">
-        <v>220</v>
+        <v>365</v>
       </c>
       <c r="E1041">
-        <v>1.592473309406249</v>
+        <v>1.673919421610802</v>
       </c>
       <c r="F1041">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1041">
-        <v>0.006954663356874498</v>
+        <v>0.006918958357453379</v>
       </c>
       <c r="H1041">
-        <v>0.006907526690593752</v>
+        <v>0.006746080578389198</v>
       </c>
       <c r="I1041">
-        <v>0.132863333719254</v>
+        <v>0.11287777906418</v>
       </c>
       <c r="J1041">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1041">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="L1041">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="M1041">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="N1041">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="O1041">
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1042" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1042">
-        <v>1.561041642546622</v>
+        <v>1.680740288937959</v>
       </c>
       <c r="D1042" t="s">
-        <v>365</v>
+        <v>220</v>
       </c>
       <c r="E1042">
-        <v>1.598199976844757</v>
+        <v>1.57354551882728</v>
       </c>
       <c r="F1042">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1042">
-        <v>0.006918958357453379</v>
+        <v>0.007019259711062041</v>
       </c>
       <c r="H1042">
-        <v>0.006741800023155243</v>
+        <v>0.00692645448117272</v>
       </c>
       <c r="I1042">
-        <v>0.03715833429813475</v>
+        <v>0.107194770110679</v>
       </c>
       <c r="J1042">
-        <v>0.7143888953209009</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1042">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="L1042">
-        <v>4.24</v>
+        <v>4.35</v>
       </c>
       <c r="M1042">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N1042">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="O1042">
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1043" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C1043">
-        <v>1.680740288937959</v>
+        <v>1.706714139491356</v>
       </c>
       <c r="D1043" t="s">
         <v>220</v>
@@ -53949,22 +53958,22 @@
         <v>-1</v>
       </c>
       <c r="G1043">
-        <v>0.007019259711062041</v>
+        <v>0.006973285860508644</v>
       </c>
       <c r="H1043">
         <v>0.00692645448117272</v>
       </c>
       <c r="I1043">
-        <v>0.107194770110679</v>
+        <v>0.1331686206640756</v>
       </c>
       <c r="J1043">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1043">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="L1043">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="M1043">
         <v>3.72</v>
@@ -53976,151 +53985,151 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1044" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1044">
-        <v>1.706714139491356</v>
+        <v>1.541961208495242</v>
       </c>
       <c r="D1044" t="s">
-        <v>220</v>
+        <v>366</v>
       </c>
       <c r="E1044">
-        <v>1.57354551882728</v>
+        <v>1.625856610708829</v>
       </c>
       <c r="F1044">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1044">
-        <v>0.006973285860508644</v>
+        <v>0.006938038791504758</v>
       </c>
       <c r="H1044">
-        <v>0.00692645448117272</v>
+        <v>0.00673414338929117</v>
       </c>
       <c r="I1044">
-        <v>0.1331686206640756</v>
+        <v>0.08389540221358693</v>
       </c>
       <c r="J1044">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1044">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="L1044">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="M1044">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="N1044">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="O1044">
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1045" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1045">
-        <v>1.541961208495242</v>
+        <v>1.687585123258323</v>
       </c>
       <c r="D1045" t="s">
-        <v>365</v>
+        <v>220</v>
       </c>
       <c r="E1045">
-        <v>1.579882760155432</v>
+        <v>1.554102912164197</v>
       </c>
       <c r="F1045">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1045">
-        <v>0.006938038791504758</v>
+        <v>0.006992414876741677</v>
       </c>
       <c r="H1045">
-        <v>0.006760117239844568</v>
+        <v>0.006945897087835803</v>
       </c>
       <c r="I1045">
-        <v>0.03792155166018985</v>
+        <v>0.1334822110941256</v>
       </c>
       <c r="J1045">
-        <v>0.7194770110679355</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1045">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="L1045">
-        <v>4.24</v>
+        <v>4.34</v>
       </c>
       <c r="M1045">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N1045">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="O1045">
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>484</v>
+        <v>223</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1046" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1046">
-        <v>1.687585123258323</v>
+        <v>1.522361806617135</v>
       </c>
       <c r="D1046" t="s">
-        <v>220</v>
+        <v>366</v>
       </c>
       <c r="E1046">
-        <v>1.554102912164197</v>
+        <v>1.60730251026422</v>
       </c>
       <c r="F1046">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1046">
-        <v>0.006992414876741677</v>
+        <v>0.006957638193382866</v>
       </c>
       <c r="H1046">
-        <v>0.006945897087835803</v>
+        <v>0.006752697489735779</v>
       </c>
       <c r="I1046">
-        <v>0.1334822110941256</v>
+        <v>0.0849407036470855</v>
       </c>
       <c r="J1046">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1046">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="L1046">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="M1046">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="N1046">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="O1046">
         <v>1</v>
@@ -54131,34 +54140,34 @@
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1047" t="s">
         <v>222</v>
       </c>
       <c r="C1047">
-        <v>1.522361806617135</v>
+        <v>1.508515390817059</v>
       </c>
       <c r="D1047" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E1047">
-        <v>1.561067334352449</v>
+        <v>1.594194569973482</v>
       </c>
       <c r="F1047">
         <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.006957638193382866</v>
+        <v>0.006971484609182942</v>
       </c>
       <c r="H1047">
-        <v>0.006778932665647551</v>
+        <v>0.006765805430026518</v>
       </c>
       <c r="I1047">
-        <v>0.03870552773531433</v>
+        <v>0.08567917915642331</v>
       </c>
       <c r="J1047">
-        <v>0.7247035182354308</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1047">
         <v>3.75</v>
@@ -54167,16 +54176,16 @@
         <v>4.24</v>
       </c>
       <c r="M1047">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N1047">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>223</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54187,28 +54196,28 @@
         <v>222</v>
       </c>
       <c r="C1048">
-        <v>1.508515390817059</v>
+        <v>1.493174878743735</v>
       </c>
       <c r="D1048" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E1048">
-        <v>1.547774775184376</v>
+        <v>1.579672218544069</v>
       </c>
       <c r="F1048">
         <v>1</v>
       </c>
       <c r="G1048">
-        <v>0.006971484609182942</v>
+        <v>0.006986825121256265</v>
       </c>
       <c r="H1048">
-        <v>0.006792225224815624</v>
+        <v>0.006780327781455931</v>
       </c>
       <c r="I1048">
-        <v>0.03925938436731746</v>
+        <v>0.08649733980033369</v>
       </c>
       <c r="J1048">
-        <v>0.7283958957821177</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1048">
         <v>3.75</v>
@@ -54217,16 +54226,16 @@
         <v>4.24</v>
       </c>
       <c r="M1048">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N1048">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="O1048">
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>485</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
@@ -54237,28 +54246,28 @@
         <v>222</v>
       </c>
       <c r="C1049">
-        <v>1.493174878743735</v>
+        <v>1.483278292917471</v>
       </c>
       <c r="D1049" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E1049">
-        <v>1.533047883593986</v>
+        <v>1.570303450628539</v>
       </c>
       <c r="F1049">
         <v>1</v>
       </c>
       <c r="G1049">
-        <v>0.006986825121256265</v>
+        <v>0.00699672170708253</v>
       </c>
       <c r="H1049">
-        <v>0.006806952116406015</v>
+        <v>0.00678969654937146</v>
       </c>
       <c r="I1049">
-        <v>0.03987300485025047</v>
+        <v>0.08702515771106789</v>
       </c>
       <c r="J1049">
-        <v>0.7324866990016706</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1049">
         <v>3.75</v>
@@ -54267,16 +54276,116 @@
         <v>4.24</v>
       </c>
       <c r="M1049">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N1049">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="O1049">
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>221</v>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:16">
+      <c r="A1050" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1050">
+        <v>1.471153106994671</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>366</v>
+      </c>
+      <c r="E1050">
+        <v>1.558824941288288</v>
+      </c>
+      <c r="F1050">
+        <v>1</v>
+      </c>
+      <c r="G1050">
+        <v>0.007008846893005329</v>
+      </c>
+      <c r="H1050">
+        <v>0.006801175058711712</v>
+      </c>
+      <c r="I1050">
+        <v>0.08767183429361713</v>
+      </c>
+      <c r="J1050">
+        <v>0.7383591714680878</v>
+      </c>
+      <c r="K1050">
+        <v>3.75</v>
+      </c>
+      <c r="L1050">
+        <v>4.24</v>
+      </c>
+      <c r="M1050">
+        <v>3.55</v>
+      </c>
+      <c r="N1050">
+        <v>4.18</v>
+      </c>
+      <c r="O1050">
+        <v>1</v>
+      </c>
+      <c r="P1050" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:16">
+      <c r="A1051" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1051">
+        <v>1.450207109606322</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>366</v>
+      </c>
+      <c r="E1051">
+        <v>1.538996063760651</v>
+      </c>
+      <c r="F1051">
+        <v>1</v>
+      </c>
+      <c r="G1051">
+        <v>0.007029792890393678</v>
+      </c>
+      <c r="H1051">
+        <v>0.006821003936239348</v>
+      </c>
+      <c r="I1051">
+        <v>0.08878895415432897</v>
+      </c>
+      <c r="J1051">
+        <v>0.7439447707716474</v>
+      </c>
+      <c r="K1051">
+        <v>3.75</v>
+      </c>
+      <c r="L1051">
+        <v>4.24</v>
+      </c>
+      <c r="M1051">
+        <v>3.55</v>
+      </c>
+      <c r="N1051">
+        <v>4.18</v>
+      </c>
+      <c r="O1051">
+        <v>1</v>
+      </c>
+      <c r="P1051" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3174" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="492">
   <si>
     <t>trade_time</t>
   </si>
@@ -682,13 +682,13 @@
     <t>2021-07-12</t>
   </si>
   <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
     <t>2021-07-16</t>
   </si>
   <si>
-    <t>2021-07-08</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
+    <t>2021-07-26</t>
   </si>
   <si>
     <t>2016-07-22</t>
@@ -1114,13 +1114,16 @@
     <t>2021-05-10</t>
   </si>
   <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
     <t>2021-07-23</t>
   </si>
   <si>
     <t>2021-07-13</t>
   </si>
   <si>
-    <t>2021-07-21</t>
+    <t>2021-07-22</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1478,6 +1481,9 @@
   </si>
   <si>
     <t>2021-07-07</t>
+  </si>
+  <si>
+    <t>2021-07-08</t>
   </si>
   <si>
     <t>2021-07-09</t>
@@ -1841,7 +1847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1054"/>
+  <dimension ref="A1:P1059"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1938,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1988,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2038,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2088,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2138,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2188,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2238,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2288,7 +2294,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2338,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2388,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2438,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2488,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2538,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2588,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2638,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2688,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2738,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2788,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2838,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2888,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2938,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2988,7 +2994,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3038,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3088,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3138,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3188,7 +3194,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3238,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3288,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3338,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3388,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3438,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3488,7 +3494,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3788,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3838,7 +3844,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3888,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3938,7 +3944,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3988,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4038,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4088,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4138,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4188,7 +4194,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4238,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4288,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4338,7 +4344,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4388,7 +4394,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4438,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4488,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4538,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4588,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4638,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4688,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4738,7 +4744,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4788,7 +4794,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4838,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4888,7 +4894,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4938,7 +4944,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4988,7 +4994,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5038,7 +5044,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5088,7 +5094,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5138,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5188,7 +5194,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5238,7 +5244,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5288,7 +5294,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5338,7 +5344,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5388,7 +5394,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5438,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5488,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5538,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5588,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5638,7 +5644,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5688,7 +5694,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5738,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5988,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6038,7 +6044,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6088,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6138,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6788,7 +6794,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6838,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6888,7 +6894,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6938,7 +6944,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6988,7 +6994,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7038,7 +7044,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7088,7 +7094,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7138,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7188,7 +7194,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7238,7 +7244,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7288,7 +7294,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7338,7 +7344,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7588,7 +7594,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7638,7 +7644,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7688,7 +7694,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7738,7 +7744,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8038,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8088,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8138,7 +8144,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8188,7 +8194,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8238,7 +8244,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8288,7 +8294,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8338,7 +8344,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8788,7 +8794,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8838,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8888,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8938,7 +8944,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8988,7 +8994,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9038,7 +9044,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9088,7 +9094,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9138,7 +9144,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9188,7 +9194,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9238,7 +9244,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9288,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9338,7 +9344,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9388,7 +9394,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9438,7 +9444,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9488,7 +9494,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9538,7 +9544,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9588,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9638,7 +9644,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9688,7 +9694,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9738,7 +9744,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9788,7 +9794,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9838,7 +9844,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9888,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9938,7 +9944,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9988,7 +9994,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10038,7 +10044,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10088,7 +10094,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10138,7 +10144,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10188,7 +10194,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10238,7 +10244,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10288,7 +10294,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10338,7 +10344,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10388,7 +10394,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10438,7 +10444,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10488,7 +10494,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10538,7 +10544,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10588,7 +10594,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10638,7 +10644,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10688,7 +10694,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10738,7 +10744,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10788,7 +10794,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10838,7 +10844,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10888,7 +10894,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10938,7 +10944,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11288,7 +11294,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11338,7 +11344,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11388,7 +11394,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11438,7 +11444,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11488,7 +11494,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11538,7 +11544,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11588,7 +11594,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11988,7 +11994,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12038,7 +12044,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12088,7 +12094,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12138,7 +12144,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12188,7 +12194,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12238,7 +12244,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12288,7 +12294,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12338,7 +12344,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12388,7 +12394,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12438,7 +12444,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12488,7 +12494,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12538,7 +12544,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12588,7 +12594,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12638,7 +12644,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12688,7 +12694,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12738,7 +12744,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12788,7 +12794,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12838,7 +12844,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12888,7 +12894,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12938,7 +12944,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12988,7 +12994,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -13938,7 +13944,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13988,7 +13994,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14038,7 +14044,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14088,7 +14094,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14138,7 +14144,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14188,7 +14194,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14238,7 +14244,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14288,7 +14294,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14338,7 +14344,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14388,7 +14394,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14438,7 +14444,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14488,7 +14494,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14538,7 +14544,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14588,7 +14594,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14638,7 +14644,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14688,7 +14694,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14738,7 +14744,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14788,7 +14794,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14838,7 +14844,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14888,7 +14894,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14938,7 +14944,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14988,7 +14994,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15038,7 +15044,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15088,7 +15094,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15138,7 +15144,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15188,7 +15194,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15238,7 +15244,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15288,7 +15294,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15338,7 +15344,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15388,7 +15394,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15438,7 +15444,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15488,7 +15494,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15538,7 +15544,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15588,7 +15594,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15638,7 +15644,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15688,7 +15694,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15738,7 +15744,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15788,7 +15794,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15838,7 +15844,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15888,7 +15894,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15938,7 +15944,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15988,7 +15994,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -16038,7 +16044,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16088,7 +16094,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16138,7 +16144,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16188,7 +16194,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16238,7 +16244,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16288,7 +16294,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16338,7 +16344,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16388,7 +16394,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16438,7 +16444,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16488,7 +16494,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16538,7 +16544,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16588,7 +16594,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16638,7 +16644,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16688,7 +16694,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16738,7 +16744,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16788,7 +16794,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16838,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16888,7 +16894,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16938,7 +16944,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16988,7 +16994,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17038,7 +17044,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17088,7 +17094,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17138,7 +17144,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17188,7 +17194,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17238,7 +17244,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17288,7 +17294,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17338,7 +17344,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17388,7 +17394,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17438,7 +17444,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17488,7 +17494,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17538,7 +17544,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17588,7 +17594,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17638,7 +17644,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17688,7 +17694,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17738,7 +17744,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17788,7 +17794,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17838,7 +17844,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17888,7 +17894,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17938,7 +17944,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17988,7 +17994,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -18038,7 +18044,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18538,7 +18544,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18588,7 +18594,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18638,7 +18644,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18688,7 +18694,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18738,7 +18744,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18788,7 +18794,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18838,7 +18844,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18888,7 +18894,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18938,7 +18944,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18988,7 +18994,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19038,7 +19044,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19088,7 +19094,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19138,7 +19144,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19188,7 +19194,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19238,7 +19244,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19288,7 +19294,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19338,7 +19344,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19388,7 +19394,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19438,7 +19444,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19488,7 +19494,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19538,7 +19544,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19588,7 +19594,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19638,7 +19644,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19688,7 +19694,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19738,7 +19744,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19788,7 +19794,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19838,7 +19844,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19888,7 +19894,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19938,7 +19944,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19988,7 +19994,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20038,7 +20044,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20088,7 +20094,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20138,7 +20144,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20188,7 +20194,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20238,7 +20244,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20288,7 +20294,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20338,7 +20344,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20388,7 +20394,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20438,7 +20444,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20488,7 +20494,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20538,7 +20544,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20588,7 +20594,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20638,7 +20644,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20688,7 +20694,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20738,7 +20744,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20788,7 +20794,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20838,7 +20844,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20888,7 +20894,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20938,7 +20944,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20988,7 +20994,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21038,7 +21044,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21088,7 +21094,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21138,7 +21144,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21188,7 +21194,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21238,7 +21244,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21288,7 +21294,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21338,7 +21344,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21388,7 +21394,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21438,7 +21444,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21488,7 +21494,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21538,7 +21544,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21588,7 +21594,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21638,7 +21644,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21688,7 +21694,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21738,7 +21744,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21788,7 +21794,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21838,7 +21844,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21888,7 +21894,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21938,7 +21944,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21988,7 +21994,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22038,7 +22044,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22088,7 +22094,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22138,7 +22144,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22188,7 +22194,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22238,7 +22244,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22288,7 +22294,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22338,7 +22344,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22388,7 +22394,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22438,7 +22444,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22488,7 +22494,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22538,7 +22544,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22588,7 +22594,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22638,7 +22644,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22688,7 +22694,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22738,7 +22744,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22788,7 +22794,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22838,7 +22844,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22888,7 +22894,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22938,7 +22944,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22988,7 +22994,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23038,7 +23044,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23088,7 +23094,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23138,7 +23144,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23188,7 +23194,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23238,7 +23244,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23288,7 +23294,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23338,7 +23344,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23388,7 +23394,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23438,7 +23444,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23488,7 +23494,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23538,7 +23544,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23588,7 +23594,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23638,7 +23644,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23688,7 +23694,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23738,7 +23744,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23788,7 +23794,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23838,7 +23844,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23888,7 +23894,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23938,7 +23944,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23988,7 +23994,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24038,7 +24044,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24088,7 +24094,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24138,7 +24144,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24188,7 +24194,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24238,7 +24244,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24288,7 +24294,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24338,7 +24344,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24388,7 +24394,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24438,7 +24444,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24488,7 +24494,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24538,7 +24544,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24588,7 +24594,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24638,7 +24644,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24688,7 +24694,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24738,7 +24744,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24788,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24838,7 +24844,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24888,7 +24894,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24938,7 +24944,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25288,7 +25294,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25338,7 +25344,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25388,7 +25394,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25438,7 +25444,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25488,7 +25494,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25538,7 +25544,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25588,7 +25594,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25638,7 +25644,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25688,7 +25694,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25738,7 +25744,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25788,7 +25794,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25838,7 +25844,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25888,7 +25894,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25938,7 +25944,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25988,7 +25994,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26038,7 +26044,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26088,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26138,7 +26144,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26188,7 +26194,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26238,7 +26244,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26888,7 +26894,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26938,7 +26944,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26988,7 +26994,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27038,7 +27044,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27088,7 +27094,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27138,7 +27144,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27188,7 +27194,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27238,7 +27244,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27288,7 +27294,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27338,7 +27344,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27388,7 +27394,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27438,7 +27444,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27488,7 +27494,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28138,7 +28144,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28188,7 +28194,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28238,7 +28244,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28288,7 +28294,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28338,7 +28344,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28388,7 +28394,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28438,7 +28444,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28488,7 +28494,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28538,7 +28544,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28588,7 +28594,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28638,7 +28644,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28688,7 +28694,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -32238,7 +32244,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32288,7 +32294,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32338,7 +32344,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32388,7 +32394,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32438,7 +32444,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32488,7 +32494,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32538,7 +32544,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32588,7 +32594,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32638,7 +32644,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33488,7 +33494,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33538,7 +33544,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33588,7 +33594,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33638,7 +33644,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33688,7 +33694,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33738,7 +33744,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33788,7 +33794,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33838,7 +33844,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33888,7 +33894,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33938,7 +33944,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33988,7 +33994,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34038,7 +34044,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34088,7 +34094,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34138,7 +34144,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34188,7 +34194,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34238,7 +34244,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -35088,7 +35094,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35138,7 +35144,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35188,7 +35194,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35238,7 +35244,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35288,7 +35294,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35338,7 +35344,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35388,7 +35394,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35438,7 +35444,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35488,7 +35494,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35538,7 +35544,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35588,7 +35594,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35638,7 +35644,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35688,7 +35694,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35738,7 +35744,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35788,7 +35794,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36188,7 +36194,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36238,7 +36244,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36288,7 +36294,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36338,7 +36344,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36388,7 +36394,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36438,7 +36444,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36488,7 +36494,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37238,7 +37244,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37288,7 +37294,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37338,7 +37344,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37388,7 +37394,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37438,7 +37444,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37488,7 +37494,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37538,7 +37544,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37588,7 +37594,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37638,7 +37644,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37688,7 +37694,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37738,7 +37744,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37788,7 +37794,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37838,7 +37844,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37888,7 +37894,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37938,7 +37944,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37988,7 +37994,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38038,7 +38044,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38088,7 +38094,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38138,7 +38144,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38188,7 +38194,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38638,7 +38644,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38688,7 +38694,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38738,7 +38744,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38788,7 +38794,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38838,7 +38844,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38888,7 +38894,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38938,7 +38944,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39288,7 +39294,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39338,7 +39344,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39388,7 +39394,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39438,7 +39444,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39488,7 +39494,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39538,7 +39544,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39588,7 +39594,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39638,7 +39644,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39688,7 +39694,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39738,7 +39744,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39788,7 +39794,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -41888,7 +41894,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41938,7 +41944,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41988,7 +41994,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42038,7 +42044,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42088,7 +42094,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42138,7 +42144,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42188,7 +42194,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42238,7 +42244,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42288,7 +42294,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42338,7 +42344,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42388,7 +42394,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42438,7 +42444,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42488,7 +42494,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42538,7 +42544,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42588,7 +42594,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42638,7 +42644,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42688,7 +42694,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42738,7 +42744,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -42788,7 +42794,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -42838,7 +42844,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -42888,7 +42894,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42938,7 +42944,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42988,7 +42994,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -44638,7 +44644,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44688,7 +44694,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44738,7 +44744,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44788,7 +44794,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44838,7 +44844,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44888,7 +44894,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44938,7 +44944,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44988,7 +44994,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45038,7 +45044,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45088,7 +45094,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45138,7 +45144,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45188,7 +45194,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45438,7 +45444,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45488,7 +45494,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45538,7 +45544,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45588,7 +45594,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45638,7 +45644,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45688,7 +45694,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45738,7 +45744,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -45788,7 +45794,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -45838,7 +45844,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -45888,7 +45894,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -45938,7 +45944,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -45988,7 +45994,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46038,7 +46044,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46088,7 +46094,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46488,7 +46494,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46538,7 +46544,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46588,7 +46594,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -48738,7 +48744,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -48788,7 +48794,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -48838,7 +48844,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -48888,7 +48894,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -48938,7 +48944,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -48988,7 +48994,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49038,7 +49044,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49088,7 +49094,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49138,7 +49144,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49188,7 +49194,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49238,7 +49244,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49288,7 +49294,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49338,7 +49344,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49388,7 +49394,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49438,7 +49444,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49488,7 +49494,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49538,7 +49544,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49588,7 +49594,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49638,7 +49644,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49688,7 +49694,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -49738,7 +49744,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -49788,7 +49794,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -49838,7 +49844,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -49888,7 +49894,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -49938,7 +49944,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -49988,7 +49994,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50038,7 +50044,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50088,7 +50094,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50138,7 +50144,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50188,7 +50194,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50238,7 +50244,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -50288,7 +50294,7 @@
         <v>1</v>
       </c>
       <c r="P969" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="970" spans="1:16">
@@ -50338,7 +50344,7 @@
         <v>1</v>
       </c>
       <c r="P970" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="971" spans="1:16">
@@ -50388,7 +50394,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -50438,7 +50444,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -50488,7 +50494,7 @@
         <v>1</v>
       </c>
       <c r="P973" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="974" spans="1:16">
@@ -50538,7 +50544,7 @@
         <v>1</v>
       </c>
       <c r="P974" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="975" spans="1:16">
@@ -50588,7 +50594,7 @@
         <v>1</v>
       </c>
       <c r="P975" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="976" spans="1:16">
@@ -50638,7 +50644,7 @@
         <v>1</v>
       </c>
       <c r="P976" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="977" spans="1:16">
@@ -50688,7 +50694,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50738,7 +50744,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50788,7 +50794,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50838,7 +50844,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50888,7 +50894,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50938,7 +50944,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50988,7 +50994,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51038,7 +51044,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51088,7 +51094,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51138,7 +51144,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51188,7 +51194,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51238,7 +51244,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51288,7 +51294,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51338,7 +51344,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51388,7 +51394,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51438,7 +51444,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51488,7 +51494,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51538,7 +51544,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51588,7 +51594,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51638,7 +51644,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51688,7 +51694,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51738,7 +51744,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51788,7 +51794,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51838,7 +51844,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51888,7 +51894,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -52088,7 +52094,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52138,7 +52144,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52188,7 +52194,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52238,7 +52244,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52488,7 +52494,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52538,7 +52544,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -52588,7 +52594,7 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -52638,7 +52644,7 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -52688,7 +52694,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52738,7 +52744,7 @@
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
@@ -52788,7 +52794,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52838,7 +52844,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52888,7 +52894,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52938,7 +52944,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -52988,7 +52994,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -53038,7 +53044,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53088,7 +53094,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53138,7 +53144,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53188,7 +53194,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53238,7 +53244,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53288,7 +53294,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53338,7 +53344,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53388,7 +53394,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53438,7 +53444,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53488,7 +53494,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53505,7 +53511,7 @@
         <v>366</v>
       </c>
       <c r="E1034">
-        <v>1.80369458653658</v>
+        <v>1.818507015037727</v>
       </c>
       <c r="F1034">
         <v>1</v>
@@ -53514,10 +53520,10 @@
         <v>0.006789674113414224</v>
       </c>
       <c r="H1034">
-        <v>0.00659630541346342</v>
+        <v>0.006201492984962273</v>
       </c>
       <c r="I1034">
-        <v>0.09336869995080344</v>
+        <v>0.10818112845195</v>
       </c>
       <c r="J1034">
         <v>0.6827080950038233</v>
@@ -53529,16 +53535,16 @@
         <v>4.25</v>
       </c>
       <c r="M1034">
-        <v>3.51</v>
+        <v>3.21</v>
       </c>
       <c r="N1034">
-        <v>4.2</v>
+        <v>4.01</v>
       </c>
       <c r="O1034">
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53546,149 +53552,149 @@
         <v>0</v>
       </c>
       <c r="B1035" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1035">
-        <v>1.815102844953163</v>
+        <v>1.683711088313052</v>
       </c>
       <c r="D1035" t="s">
         <v>367</v>
       </c>
       <c r="E1035">
-        <v>1.753015209992995</v>
+        <v>1.778582236553444</v>
       </c>
       <c r="F1035">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1035">
-        <v>0.006864897155046836</v>
+        <v>0.006816288911686948</v>
       </c>
       <c r="H1035">
-        <v>0.006926984790007005</v>
+        <v>0.006621417763446557</v>
       </c>
       <c r="I1035">
-        <v>0.062087634960168</v>
+        <v>0.09487114824039233</v>
       </c>
       <c r="J1035">
         <v>0.6898626106685345</v>
       </c>
       <c r="K1035">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1035">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1035">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="N1035">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="O1035">
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
       <c r="A1036" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1036" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1036">
-        <v>1.683711088313052</v>
+        <v>1.774652822327312</v>
       </c>
       <c r="D1036" t="s">
-        <v>224</v>
+        <v>368</v>
       </c>
       <c r="E1036">
-        <v>1.760987732126702</v>
+        <v>1.711570514679623</v>
       </c>
       <c r="F1036">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1036">
-        <v>0.006816288911686948</v>
+        <v>0.006905347177672688</v>
       </c>
       <c r="H1036">
-        <v>0.006659012267873298</v>
+        <v>0.006968429485320377</v>
       </c>
       <c r="I1036">
-        <v>0.07727664381365074</v>
+        <v>0.06308230764768874</v>
       </c>
       <c r="J1036">
-        <v>0.6898626106685345</v>
+        <v>0.7009145294187672</v>
       </c>
       <c r="K1036">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="L1036">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="M1036">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N1036">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="O1036">
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
       <c r="A1037" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1037" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1037">
-        <v>1.774652822327312</v>
+        <v>1.642597950562186</v>
       </c>
       <c r="D1037" t="s">
-        <v>220</v>
+        <v>369</v>
       </c>
       <c r="E1037">
-        <v>1.642597950562186</v>
+        <v>1.721753420563377</v>
       </c>
       <c r="F1037">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1037">
-        <v>0.006905347177672688</v>
+        <v>0.006857402049437814</v>
       </c>
       <c r="H1037">
-        <v>0.006857402049437814</v>
+        <v>0.006698246579436623</v>
       </c>
       <c r="I1037">
-        <v>0.132054871765126</v>
+        <v>0.07915547000119094</v>
       </c>
       <c r="J1037">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1037">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1037">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1037">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="N1037">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="O1037">
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
@@ -53702,10 +53708,10 @@
         <v>1.745068418380975</v>
       </c>
       <c r="D1038" t="s">
-        <v>220</v>
+        <v>368</v>
       </c>
       <c r="E1038">
-        <v>1.612528556387221</v>
+        <v>1.681258625390344</v>
       </c>
       <c r="F1038">
         <v>-1</v>
@@ -53714,10 +53720,10 @@
         <v>0.006934931581619024</v>
       </c>
       <c r="H1038">
-        <v>0.006887471443612779</v>
+        <v>0.006998741374609656</v>
       </c>
       <c r="I1038">
-        <v>0.1325398619937541</v>
+        <v>0.06380979299063139</v>
       </c>
       <c r="J1038">
         <v>0.7089976998959082</v>
@@ -53729,60 +53735,60 @@
         <v>4.34</v>
       </c>
       <c r="M1038">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="N1038">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="O1038">
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
       <c r="A1039" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1039" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1039">
-        <v>1.725336643125503</v>
+        <v>1.612528556387221</v>
       </c>
       <c r="D1039" t="s">
-        <v>220</v>
+        <v>369</v>
       </c>
       <c r="E1039">
-        <v>1.592473309406249</v>
+        <v>1.693058165369526</v>
       </c>
       <c r="F1039">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1039">
-        <v>0.006954663356874498</v>
+        <v>0.006887471443612779</v>
       </c>
       <c r="H1039">
-        <v>0.006907526690593752</v>
+        <v>0.006726941834630474</v>
       </c>
       <c r="I1039">
-        <v>0.132863333719254</v>
+        <v>0.08052960898230443</v>
       </c>
       <c r="J1039">
-        <v>0.7143888953209009</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1039">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1039">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1039">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="N1039">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="O1039">
         <v>1</v>
@@ -53793,46 +53799,46 @@
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1040" t="s">
         <v>222</v>
       </c>
       <c r="C1040">
-        <v>1.561041642546622</v>
+        <v>1.738667498339339</v>
       </c>
       <c r="D1040" t="s">
-        <v>224</v>
+        <v>366</v>
       </c>
       <c r="E1040">
-        <v>1.673919421610802</v>
+        <v>1.734117383334135</v>
       </c>
       <c r="F1040">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1040">
-        <v>0.006918958357453379</v>
+        <v>0.006361332501660661</v>
       </c>
       <c r="H1040">
-        <v>0.006746080578389198</v>
+        <v>0.006285882616665866</v>
       </c>
       <c r="I1040">
-        <v>0.11287777906418</v>
+        <v>0.004550115005204525</v>
       </c>
       <c r="J1040">
-        <v>0.7143888953209009</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1040">
-        <v>3.75</v>
+        <v>3.26</v>
       </c>
       <c r="L1040">
-        <v>4.24</v>
+        <v>4.05</v>
       </c>
       <c r="M1040">
-        <v>3.55</v>
+        <v>3.21</v>
       </c>
       <c r="N1040">
-        <v>4.21</v>
+        <v>4.01</v>
       </c>
       <c r="O1040">
         <v>1</v>
@@ -53846,43 +53852,43 @@
         <v>0</v>
       </c>
       <c r="B1041" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C1041">
-        <v>1.680740288937959</v>
+        <v>1.725336643125503</v>
       </c>
       <c r="D1041" t="s">
-        <v>220</v>
+        <v>368</v>
       </c>
       <c r="E1041">
-        <v>1.57354551882728</v>
+        <v>1.661041642546622</v>
       </c>
       <c r="F1041">
         <v>-1</v>
       </c>
       <c r="G1041">
-        <v>0.007019259711062041</v>
+        <v>0.006954663356874498</v>
       </c>
       <c r="H1041">
-        <v>0.00692645448117272</v>
+        <v>0.007018958357453379</v>
       </c>
       <c r="I1041">
-        <v>0.107194770110679</v>
+        <v>0.06429500057888093</v>
       </c>
       <c r="J1041">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1041">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="L1041">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="M1041">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="N1041">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="O1041">
         <v>1</v>
@@ -53896,43 +53902,43 @@
         <v>1</v>
       </c>
       <c r="B1042" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1042">
-        <v>1.706714139491356</v>
+        <v>1.592473309406249</v>
       </c>
       <c r="D1042" t="s">
-        <v>220</v>
+        <v>369</v>
       </c>
       <c r="E1042">
-        <v>1.57354551882728</v>
+        <v>1.673919421610802</v>
       </c>
       <c r="F1042">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1042">
-        <v>0.006973285860508644</v>
+        <v>0.006907526690593752</v>
       </c>
       <c r="H1042">
-        <v>0.00692645448117272</v>
+        <v>0.006746080578389198</v>
       </c>
       <c r="I1042">
-        <v>0.1331686206640756</v>
+        <v>0.08144611220455333</v>
       </c>
       <c r="J1042">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1042">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1042">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1042">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="N1042">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="O1042">
         <v>1</v>
@@ -53949,40 +53955,40 @@
         <v>222</v>
       </c>
       <c r="C1043">
-        <v>1.541961208495242</v>
+        <v>1.721092201253863</v>
       </c>
       <c r="D1043" t="s">
-        <v>224</v>
+        <v>366</v>
       </c>
       <c r="E1043">
-        <v>1.655856610708829</v>
+        <v>1.716811646019908</v>
       </c>
       <c r="F1043">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1043">
-        <v>0.006938038791504758</v>
+        <v>0.006378907798746137</v>
       </c>
       <c r="H1043">
-        <v>0.006764143389291171</v>
+        <v>0.006303188353980092</v>
       </c>
       <c r="I1043">
-        <v>0.1138954022135872</v>
+        <v>0.004280555233954875</v>
       </c>
       <c r="J1043">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1043">
-        <v>3.75</v>
+        <v>3.26</v>
       </c>
       <c r="L1043">
-        <v>4.24</v>
+        <v>4.05</v>
       </c>
       <c r="M1043">
-        <v>3.55</v>
+        <v>3.21</v>
       </c>
       <c r="N1043">
-        <v>4.21</v>
+        <v>4.01</v>
       </c>
       <c r="O1043">
         <v>1</v>
@@ -53999,28 +54005,28 @@
         <v>221</v>
       </c>
       <c r="C1044">
-        <v>1.687585123258323</v>
+        <v>1.706714139491356</v>
       </c>
       <c r="D1044" t="s">
-        <v>220</v>
+        <v>368</v>
       </c>
       <c r="E1044">
-        <v>1.554102912164197</v>
+        <v>1.641961208495242</v>
       </c>
       <c r="F1044">
         <v>-1</v>
       </c>
       <c r="G1044">
-        <v>0.006992414876741677</v>
+        <v>0.006973285860508644</v>
       </c>
       <c r="H1044">
-        <v>0.006945897087835803</v>
+        <v>0.007038038791504758</v>
       </c>
       <c r="I1044">
-        <v>0.1334822110941256</v>
+        <v>0.0647529309961139</v>
       </c>
       <c r="J1044">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1044">
         <v>3.66</v>
@@ -54029,16 +54035,16 @@
         <v>4.34</v>
       </c>
       <c r="M1044">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="N1044">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="O1044">
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>223</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
@@ -54046,93 +54052,93 @@
         <v>1</v>
       </c>
       <c r="B1045" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1045">
-        <v>1.522361806617135</v>
+        <v>1.57354551882728</v>
       </c>
       <c r="D1045" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E1045">
-        <v>1.60730251026422</v>
+        <v>1.655856610708829</v>
       </c>
       <c r="F1045">
         <v>1</v>
       </c>
       <c r="G1045">
-        <v>0.006957638193382866</v>
+        <v>0.00692645448117272</v>
       </c>
       <c r="H1045">
-        <v>0.006752697489735779</v>
+        <v>0.006764143389291171</v>
       </c>
       <c r="I1045">
-        <v>0.0849407036470855</v>
+        <v>0.08231109188154928</v>
       </c>
       <c r="J1045">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1045">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="L1045">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="M1045">
         <v>3.55</v>
       </c>
       <c r="N1045">
-        <v>4.18</v>
+        <v>4.21</v>
       </c>
       <c r="O1045">
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>223</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1046" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1046">
-        <v>1.674071021437449</v>
+        <v>1.70450494391853</v>
       </c>
       <c r="D1046" t="s">
-        <v>220</v>
+        <v>366</v>
       </c>
       <c r="E1046">
-        <v>1.540367267690522</v>
+        <v>1.700478794471927</v>
       </c>
       <c r="F1046">
         <v>-1</v>
       </c>
       <c r="G1046">
-        <v>0.007005928978562551</v>
+        <v>0.006395495056081469</v>
       </c>
       <c r="H1046">
-        <v>0.006959632732309478</v>
+        <v>0.006319521205528073</v>
       </c>
       <c r="I1046">
-        <v>0.1337037537469268</v>
+        <v>0.004026149446603622</v>
       </c>
       <c r="J1046">
-        <v>0.7283958957821177</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1046">
-        <v>3.66</v>
+        <v>3.26</v>
       </c>
       <c r="L1046">
-        <v>4.34</v>
+        <v>4.05</v>
       </c>
       <c r="M1046">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="N1046">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="O1046">
         <v>1</v>
@@ -54143,302 +54149,302 @@
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1047" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1047">
-        <v>1.508515390817059</v>
+        <v>1.687585123258323</v>
       </c>
       <c r="D1047" t="s">
         <v>368</v>
       </c>
       <c r="E1047">
-        <v>1.594194569973482</v>
+        <v>1.622361806617135</v>
       </c>
       <c r="F1047">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1047">
-        <v>0.006971484609182942</v>
+        <v>0.006992414876741677</v>
       </c>
       <c r="H1047">
-        <v>0.006765805430026518</v>
+        <v>0.007057638193382865</v>
       </c>
       <c r="I1047">
-        <v>0.08567917915642331</v>
+        <v>0.06522331664118841</v>
       </c>
       <c r="J1047">
-        <v>0.7283958957821177</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1047">
+        <v>3.66</v>
+      </c>
+      <c r="L1047">
+        <v>4.34</v>
+      </c>
+      <c r="M1047">
         <v>3.75</v>
       </c>
-      <c r="L1047">
-        <v>4.24</v>
-      </c>
-      <c r="M1047">
-        <v>3.55</v>
-      </c>
       <c r="N1047">
-        <v>4.18</v>
+        <v>4.34</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1048" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1048">
-        <v>1.493174878743735</v>
+        <v>1.554102912164197</v>
       </c>
       <c r="D1048" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E1048">
-        <v>1.579672218544069</v>
+        <v>1.637302510264221</v>
       </c>
       <c r="F1048">
         <v>1</v>
       </c>
       <c r="G1048">
-        <v>0.006986825121256265</v>
+        <v>0.006945897087835803</v>
       </c>
       <c r="H1048">
-        <v>0.006780327781455931</v>
+        <v>0.00678269748973578</v>
       </c>
       <c r="I1048">
-        <v>0.08649733980033369</v>
+        <v>0.08319959810002331</v>
       </c>
       <c r="J1048">
-        <v>0.7324866990016706</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1048">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="L1048">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="M1048">
         <v>3.55</v>
       </c>
       <c r="N1048">
-        <v>4.18</v>
+        <v>4.21</v>
       </c>
       <c r="O1048">
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>221</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1049" t="s">
         <v>222</v>
       </c>
       <c r="C1049">
-        <v>1.483278292917471</v>
+        <v>1.687466530552496</v>
       </c>
       <c r="D1049" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E1049">
-        <v>1.570303450628539</v>
+        <v>1.683701706464267</v>
       </c>
       <c r="F1049">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.00699672170708253</v>
+        <v>0.006412533469447504</v>
       </c>
       <c r="H1049">
-        <v>0.00678969654937146</v>
+        <v>0.006336298293535732</v>
       </c>
       <c r="I1049">
-        <v>0.08702515771106789</v>
+        <v>0.003764824088228647</v>
       </c>
       <c r="J1049">
-        <v>0.7351257885553412</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1049">
-        <v>3.75</v>
+        <v>3.26</v>
       </c>
       <c r="L1049">
-        <v>4.24</v>
+        <v>4.05</v>
       </c>
       <c r="M1049">
-        <v>3.55</v>
+        <v>3.21</v>
       </c>
       <c r="N1049">
-        <v>4.18</v>
+        <v>4.01</v>
       </c>
       <c r="O1049">
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>367</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1050" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C1050">
-        <v>1.600303450628539</v>
+        <v>1.674071021437449</v>
       </c>
       <c r="D1050" t="s">
-        <v>366</v>
+        <v>220</v>
       </c>
       <c r="E1050">
-        <v>1.619708482170753</v>
+        <v>1.540367267690522</v>
       </c>
       <c r="F1050">
         <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.006819696549371461</v>
+        <v>0.007005928978562551</v>
       </c>
       <c r="H1050">
-        <v>0.006780291517829248</v>
+        <v>0.006959632732309478</v>
       </c>
       <c r="I1050">
-        <v>-0.01940503154221362</v>
+        <v>0.1337037537469268</v>
       </c>
       <c r="J1050">
-        <v>0.7351257885553412</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1050">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="L1050">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="M1050">
-        <v>3.51</v>
+        <v>3.72</v>
       </c>
       <c r="N1050">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="O1050">
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>367</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1051" t="s">
         <v>222</v>
       </c>
       <c r="C1051">
-        <v>1.471153106994671</v>
+        <v>1.675429379750296</v>
       </c>
       <c r="D1051" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E1051">
-        <v>1.558824941288288</v>
+        <v>1.671849174539402</v>
       </c>
       <c r="F1051">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1051">
-        <v>0.007008846893005329</v>
+        <v>0.006424570620249703</v>
       </c>
       <c r="H1051">
-        <v>0.006801175058711712</v>
+        <v>0.006348150825460598</v>
       </c>
       <c r="I1051">
-        <v>0.08767183429361713</v>
+        <v>0.003580205210894416</v>
       </c>
       <c r="J1051">
-        <v>0.7383591714680878</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1051">
-        <v>3.75</v>
+        <v>3.26</v>
       </c>
       <c r="L1051">
-        <v>4.24</v>
+        <v>4.05</v>
       </c>
       <c r="M1051">
-        <v>3.55</v>
+        <v>3.21</v>
       </c>
       <c r="N1051">
-        <v>4.18</v>
+        <v>4.01</v>
       </c>
       <c r="O1051">
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>220</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1052" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1052">
-        <v>1.588824941288288</v>
+        <v>1.662093361254554</v>
       </c>
       <c r="D1052" t="s">
         <v>366</v>
       </c>
       <c r="E1052">
-        <v>1.608359308147012</v>
+        <v>1.658717696204637</v>
       </c>
       <c r="F1052">
         <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.006831175058711711</v>
+        <v>0.006437906638745446</v>
       </c>
       <c r="H1052">
-        <v>0.006791640691852989</v>
+        <v>0.006361282303795362</v>
       </c>
       <c r="I1052">
-        <v>-0.01953436685872356</v>
+        <v>0.003375665049916599</v>
       </c>
       <c r="J1052">
-        <v>0.7383591714680878</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1052">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="L1052">
-        <v>4.21</v>
+        <v>4.05</v>
       </c>
       <c r="M1052">
-        <v>3.51</v>
+        <v>3.21</v>
       </c>
       <c r="N1052">
-        <v>4.2</v>
+        <v>4.01</v>
       </c>
       <c r="O1052">
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -54446,31 +54452,31 @@
         <v>0</v>
       </c>
       <c r="B1053" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1053">
-        <v>1.450207109606322</v>
+        <v>1.483278292917471</v>
       </c>
       <c r="D1053" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E1053">
-        <v>1.538996063760651</v>
+        <v>1.600303450628539</v>
       </c>
       <c r="F1053">
         <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.007029792890393678</v>
+        <v>0.00699672170708253</v>
       </c>
       <c r="H1053">
-        <v>0.006821003936239348</v>
+        <v>0.006819696549371461</v>
       </c>
       <c r="I1053">
-        <v>0.08878895415432897</v>
+        <v>0.1170251577110681</v>
       </c>
       <c r="J1053">
-        <v>0.7439447707716474</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1053">
         <v>3.75</v>
@@ -54482,13 +54488,13 @@
         <v>3.55</v>
       </c>
       <c r="N1053">
-        <v>4.18</v>
+        <v>4.21</v>
       </c>
       <c r="O1053">
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>489</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -54499,46 +54505,296 @@
         <v>224</v>
       </c>
       <c r="C1054">
-        <v>1.568996063760652</v>
+        <v>1.6426260925685</v>
       </c>
       <c r="D1054" t="s">
         <v>366</v>
       </c>
       <c r="E1054">
-        <v>1.588753854591518</v>
+        <v>1.650246218737355</v>
       </c>
       <c r="F1054">
         <v>-1</v>
       </c>
       <c r="G1054">
+        <v>0.0065973739074315</v>
+      </c>
+      <c r="H1054">
+        <v>0.006369753781262645</v>
+      </c>
+      <c r="I1054">
+        <v>-0.007620126168854213</v>
+      </c>
+      <c r="J1054">
+        <v>0.7351257885553412</v>
+      </c>
+      <c r="K1054">
+        <v>3.37</v>
+      </c>
+      <c r="L1054">
+        <v>4.12</v>
+      </c>
+      <c r="M1054">
+        <v>3.21</v>
+      </c>
+      <c r="N1054">
+        <v>4.01</v>
+      </c>
+      <c r="O1054">
+        <v>1</v>
+      </c>
+      <c r="P1054" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:16">
+      <c r="A1055" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1055">
+        <v>1.471153106994671</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>369</v>
+      </c>
+      <c r="E1055">
+        <v>1.588824941288288</v>
+      </c>
+      <c r="F1055">
+        <v>1</v>
+      </c>
+      <c r="G1055">
+        <v>0.007008846893005329</v>
+      </c>
+      <c r="H1055">
+        <v>0.006831175058711711</v>
+      </c>
+      <c r="I1055">
+        <v>0.1176718342936174</v>
+      </c>
+      <c r="J1055">
+        <v>0.7383591714680878</v>
+      </c>
+      <c r="K1055">
+        <v>3.75</v>
+      </c>
+      <c r="L1055">
+        <v>4.24</v>
+      </c>
+      <c r="M1055">
+        <v>3.55</v>
+      </c>
+      <c r="N1055">
+        <v>4.21</v>
+      </c>
+      <c r="O1055">
+        <v>1</v>
+      </c>
+      <c r="P1055" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:16">
+      <c r="A1056" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1056">
+        <v>1.631729592152544</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>366</v>
+      </c>
+      <c r="E1056">
+        <v>1.639867059587438</v>
+      </c>
+      <c r="F1056">
+        <v>-1</v>
+      </c>
+      <c r="G1056">
+        <v>0.006608270407847457</v>
+      </c>
+      <c r="H1056">
+        <v>0.006380132940412562</v>
+      </c>
+      <c r="I1056">
+        <v>-0.008137467434893964</v>
+      </c>
+      <c r="J1056">
+        <v>0.7383591714680878</v>
+      </c>
+      <c r="K1056">
+        <v>3.37</v>
+      </c>
+      <c r="L1056">
+        <v>4.12</v>
+      </c>
+      <c r="M1056">
+        <v>3.21</v>
+      </c>
+      <c r="N1056">
+        <v>4.01</v>
+      </c>
+      <c r="O1056">
+        <v>1</v>
+      </c>
+      <c r="P1056" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:16">
+      <c r="A1057" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1057">
+        <v>1.450207109606322</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>369</v>
+      </c>
+      <c r="E1057">
+        <v>1.568996063760652</v>
+      </c>
+      <c r="F1057">
+        <v>1</v>
+      </c>
+      <c r="G1057">
+        <v>0.007029792890393678</v>
+      </c>
+      <c r="H1057">
         <v>0.006851003936239348</v>
       </c>
-      <c r="H1054">
-        <v>0.006811246145408482</v>
-      </c>
-      <c r="I1054">
-        <v>-0.01975779083086593</v>
-      </c>
-      <c r="J1054">
+      <c r="I1057">
+        <v>0.1187889541543292</v>
+      </c>
+      <c r="J1057">
         <v>0.7439447707716474</v>
       </c>
-      <c r="K1054">
+      <c r="K1057">
+        <v>3.75</v>
+      </c>
+      <c r="L1057">
+        <v>4.24</v>
+      </c>
+      <c r="M1057">
         <v>3.55</v>
       </c>
-      <c r="L1054">
+      <c r="N1057">
         <v>4.21</v>
       </c>
-      <c r="M1054">
-        <v>3.51</v>
-      </c>
-      <c r="N1054">
-        <v>4.2</v>
-      </c>
-      <c r="O1054">
-        <v>1</v>
-      </c>
-      <c r="P1054" t="s">
-        <v>489</v>
+      <c r="O1057">
+        <v>1</v>
+      </c>
+      <c r="P1057" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:16">
+      <c r="A1058" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1058">
+        <v>1.624740047284429</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>366</v>
+      </c>
+      <c r="E1058">
+        <v>1.621937285823011</v>
+      </c>
+      <c r="F1058">
+        <v>-1</v>
+      </c>
+      <c r="G1058">
+        <v>0.00647525995271557</v>
+      </c>
+      <c r="H1058">
+        <v>0.006398062714176988</v>
+      </c>
+      <c r="I1058">
+        <v>0.002802761461417891</v>
+      </c>
+      <c r="J1058">
+        <v>0.7439447707716474</v>
+      </c>
+      <c r="K1058">
+        <v>3.26</v>
+      </c>
+      <c r="L1058">
+        <v>4.05</v>
+      </c>
+      <c r="M1058">
+        <v>3.21</v>
+      </c>
+      <c r="N1058">
+        <v>4.01</v>
+      </c>
+      <c r="O1058">
+        <v>1</v>
+      </c>
+      <c r="P1058" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:16">
+      <c r="A1059" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1059">
+        <v>1.61016227805581</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>366</v>
+      </c>
+      <c r="E1059">
+        <v>1.607583102012009</v>
+      </c>
+      <c r="F1059">
+        <v>-1</v>
+      </c>
+      <c r="G1059">
+        <v>0.006489837721944189</v>
+      </c>
+      <c r="H1059">
+        <v>0.00641241689798799</v>
+      </c>
+      <c r="I1059">
+        <v>0.002579176043800757</v>
+      </c>
+      <c r="J1059">
+        <v>0.7484164791239846</v>
+      </c>
+      <c r="K1059">
+        <v>3.26</v>
+      </c>
+      <c r="L1059">
+        <v>4.05</v>
+      </c>
+      <c r="M1059">
+        <v>3.21</v>
+      </c>
+      <c r="N1059">
+        <v>4.01</v>
+      </c>
+      <c r="O1059">
+        <v>1</v>
+      </c>
+      <c r="P1059" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3195" uniqueCount="492">
   <si>
     <t>trade_time</t>
   </si>
@@ -685,10 +685,10 @@
     <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-07-16</t>
+    <t>2021-07-29</t>
   </si>
   <si>
-    <t>2021-07-26</t>
+    <t>2021-07-16</t>
   </si>
   <si>
     <t>2016-07-22</t>
@@ -1114,7 +1114,7 @@
     <t>2021-05-10</t>
   </si>
   <si>
-    <t>2021-07-29</t>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2021-07-23</t>
@@ -1847,7 +1847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1059"/>
+  <dimension ref="A1:P1061"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -53511,7 +53511,7 @@
         <v>366</v>
       </c>
       <c r="E1034">
-        <v>1.818507015037727</v>
+        <v>1.822642419787918</v>
       </c>
       <c r="F1034">
         <v>1</v>
@@ -53520,10 +53520,10 @@
         <v>0.006789674113414224</v>
       </c>
       <c r="H1034">
-        <v>0.006201492984962273</v>
+        <v>0.006137357580212082</v>
       </c>
       <c r="I1034">
-        <v>0.10818112845195</v>
+        <v>0.1123165332021414</v>
       </c>
       <c r="J1034">
         <v>0.6827080950038233</v>
@@ -53535,10 +53535,10 @@
         <v>4.25</v>
       </c>
       <c r="M1034">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="N1034">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1034">
         <v>1</v>
@@ -53799,96 +53799,96 @@
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1040" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1040">
-        <v>1.738667498339339</v>
+        <v>1.725336643125503</v>
       </c>
       <c r="D1040" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E1040">
-        <v>1.734117383334135</v>
+        <v>1.661041642546622</v>
       </c>
       <c r="F1040">
         <v>-1</v>
       </c>
       <c r="G1040">
-        <v>0.006361332501660661</v>
+        <v>0.006954663356874498</v>
       </c>
       <c r="H1040">
-        <v>0.006285882616665866</v>
+        <v>0.007018958357453379</v>
       </c>
       <c r="I1040">
-        <v>0.004550115005204525</v>
+        <v>0.06429500057888093</v>
       </c>
       <c r="J1040">
-        <v>0.7089976998959082</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1040">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="L1040">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="M1040">
-        <v>3.21</v>
+        <v>3.75</v>
       </c>
       <c r="N1040">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="O1040">
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1041" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1041">
-        <v>1.725336643125503</v>
+        <v>1.592473309406249</v>
       </c>
       <c r="D1041" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E1041">
-        <v>1.661041642546622</v>
+        <v>1.673919421610802</v>
       </c>
       <c r="F1041">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1041">
-        <v>0.006954663356874498</v>
+        <v>0.006907526690593752</v>
       </c>
       <c r="H1041">
-        <v>0.007018958357453379</v>
+        <v>0.006746080578389198</v>
       </c>
       <c r="I1041">
-        <v>0.06429500057888093</v>
+        <v>0.08144611220455333</v>
       </c>
       <c r="J1041">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1041">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1041">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1041">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N1041">
-        <v>4.34</v>
+        <v>4.21</v>
       </c>
       <c r="O1041">
         <v>1</v>
@@ -53899,46 +53899,46 @@
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1042" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C1042">
-        <v>1.592473309406249</v>
+        <v>1.721092201253863</v>
       </c>
       <c r="D1042" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1042">
-        <v>1.673919421610802</v>
+        <v>1.722531090785953</v>
       </c>
       <c r="F1042">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1042">
-        <v>0.006907526690593752</v>
+        <v>0.006378907798746137</v>
       </c>
       <c r="H1042">
-        <v>0.006746080578389198</v>
+        <v>0.006237468909214047</v>
       </c>
       <c r="I1042">
-        <v>0.08144611220455333</v>
+        <v>-0.001438889532090037</v>
       </c>
       <c r="J1042">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1042">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1042">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1042">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="N1042">
-        <v>4.21</v>
+        <v>3.98</v>
       </c>
       <c r="O1042">
         <v>1</v>
@@ -53949,96 +53949,96 @@
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1043" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1043">
-        <v>1.721092201253863</v>
+        <v>1.706714139491356</v>
       </c>
       <c r="D1043" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E1043">
-        <v>1.716811646019908</v>
+        <v>1.641961208495242</v>
       </c>
       <c r="F1043">
         <v>-1</v>
       </c>
       <c r="G1043">
-        <v>0.006378907798746137</v>
+        <v>0.006973285860508644</v>
       </c>
       <c r="H1043">
-        <v>0.006303188353980092</v>
+        <v>0.007038038791504758</v>
       </c>
       <c r="I1043">
-        <v>0.004280555233954875</v>
+        <v>0.0647529309961139</v>
       </c>
       <c r="J1043">
-        <v>0.7143888953209009</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1043">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="L1043">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="M1043">
-        <v>3.21</v>
+        <v>3.75</v>
       </c>
       <c r="N1043">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="O1043">
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1044" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1044">
-        <v>1.706714139491356</v>
+        <v>1.57354551882728</v>
       </c>
       <c r="D1044" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E1044">
-        <v>1.641961208495242</v>
+        <v>1.655856610708829</v>
       </c>
       <c r="F1044">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1044">
-        <v>0.006973285860508644</v>
+        <v>0.00692645448117272</v>
       </c>
       <c r="H1044">
-        <v>0.007038038791504758</v>
+        <v>0.006764143389291171</v>
       </c>
       <c r="I1044">
-        <v>0.0647529309961139</v>
+        <v>0.08231109188154928</v>
       </c>
       <c r="J1044">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1044">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1044">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1044">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N1044">
-        <v>4.34</v>
+        <v>4.21</v>
       </c>
       <c r="O1044">
         <v>1</v>
@@ -54049,46 +54049,46 @@
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1045" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C1045">
-        <v>1.57354551882728</v>
+        <v>1.70450494391853</v>
       </c>
       <c r="D1045" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1045">
-        <v>1.655856610708829</v>
+        <v>1.706452645025324</v>
       </c>
       <c r="F1045">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1045">
-        <v>0.00692645448117272</v>
+        <v>0.006395495056081469</v>
       </c>
       <c r="H1045">
-        <v>0.006764143389291171</v>
+        <v>0.006253547354974676</v>
       </c>
       <c r="I1045">
-        <v>0.08231109188154928</v>
+        <v>-0.001947701106793431</v>
       </c>
       <c r="J1045">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1045">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1045">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1045">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="N1045">
-        <v>4.21</v>
+        <v>3.98</v>
       </c>
       <c r="O1045">
         <v>1</v>
@@ -54099,96 +54099,96 @@
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1046" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1046">
-        <v>1.70450494391853</v>
+        <v>1.687585123258323</v>
       </c>
       <c r="D1046" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E1046">
-        <v>1.700478794471927</v>
+        <v>1.622361806617135</v>
       </c>
       <c r="F1046">
         <v>-1</v>
       </c>
       <c r="G1046">
-        <v>0.006395495056081469</v>
+        <v>0.006992414876741677</v>
       </c>
       <c r="H1046">
-        <v>0.006319521205528073</v>
+        <v>0.007057638193382865</v>
       </c>
       <c r="I1046">
-        <v>0.004026149446603622</v>
+        <v>0.06522331664118841</v>
       </c>
       <c r="J1046">
-        <v>0.7194770110679355</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1046">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="L1046">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="M1046">
-        <v>3.21</v>
+        <v>3.75</v>
       </c>
       <c r="N1046">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="O1046">
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1047" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1047">
-        <v>1.687585123258323</v>
+        <v>1.554102912164197</v>
       </c>
       <c r="D1047" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E1047">
-        <v>1.622361806617135</v>
+        <v>1.637302510264221</v>
       </c>
       <c r="F1047">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.006992414876741677</v>
+        <v>0.006945897087835803</v>
       </c>
       <c r="H1047">
-        <v>0.007057638193382865</v>
+        <v>0.00678269748973578</v>
       </c>
       <c r="I1047">
-        <v>0.06522331664118841</v>
+        <v>0.08319959810002331</v>
       </c>
       <c r="J1047">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1047">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1047">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1047">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N1047">
-        <v>4.34</v>
+        <v>4.21</v>
       </c>
       <c r="O1047">
         <v>1</v>
@@ -54199,46 +54199,46 @@
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1048" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C1048">
-        <v>1.554102912164197</v>
+        <v>1.687466530552496</v>
       </c>
       <c r="D1048" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1048">
-        <v>1.637302510264221</v>
+        <v>1.689936882376039</v>
       </c>
       <c r="F1048">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.006945897087835803</v>
+        <v>0.006412533469447504</v>
       </c>
       <c r="H1048">
-        <v>0.00678269748973578</v>
+        <v>0.006270063117623961</v>
       </c>
       <c r="I1048">
-        <v>0.08319959810002331</v>
+        <v>-0.002470351823542938</v>
       </c>
       <c r="J1048">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1048">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1048">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1048">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="N1048">
-        <v>4.21</v>
+        <v>3.98</v>
       </c>
       <c r="O1048">
         <v>1</v>
@@ -54249,96 +54249,96 @@
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1049" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1049">
-        <v>1.687466530552496</v>
+        <v>1.674071021437449</v>
       </c>
       <c r="D1049" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E1049">
-        <v>1.683701706464267</v>
+        <v>1.608515390817058</v>
       </c>
       <c r="F1049">
         <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.006412533469447504</v>
+        <v>0.007005928978562551</v>
       </c>
       <c r="H1049">
-        <v>0.006336298293535732</v>
+        <v>0.007071484609182941</v>
       </c>
       <c r="I1049">
-        <v>0.003764824088228647</v>
+        <v>0.06555563062039038</v>
       </c>
       <c r="J1049">
-        <v>0.7247035182354308</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1049">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="L1049">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="M1049">
-        <v>3.21</v>
+        <v>3.75</v>
       </c>
       <c r="N1049">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="O1049">
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1050" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1050">
-        <v>1.674071021437449</v>
+        <v>1.540367267690522</v>
       </c>
       <c r="D1050" t="s">
-        <v>220</v>
+        <v>369</v>
       </c>
       <c r="E1050">
-        <v>1.540367267690522</v>
+        <v>1.624194569973482</v>
       </c>
       <c r="F1050">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1050">
-        <v>0.007005928978562551</v>
+        <v>0.006959632732309478</v>
       </c>
       <c r="H1050">
-        <v>0.006959632732309478</v>
+        <v>0.006795805430026517</v>
       </c>
       <c r="I1050">
-        <v>0.1337037537469268</v>
+        <v>0.08382730228296031</v>
       </c>
       <c r="J1050">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1050">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1050">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1050">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="N1050">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="O1050">
         <v>1</v>
@@ -54349,7 +54349,7 @@
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1051" t="s">
         <v>222</v>
@@ -54361,7 +54361,7 @@
         <v>366</v>
       </c>
       <c r="E1051">
-        <v>1.671849174539402</v>
+        <v>1.678268969328508</v>
       </c>
       <c r="F1051">
         <v>-1</v>
@@ -54370,10 +54370,10 @@
         <v>0.006424570620249703</v>
       </c>
       <c r="H1051">
-        <v>0.006348150825460598</v>
+        <v>0.006281731030671493</v>
       </c>
       <c r="I1051">
-        <v>0.003580205210894416</v>
+        <v>-0.002839589578211399</v>
       </c>
       <c r="J1051">
         <v>0.7283958957821177</v>
@@ -54385,10 +54385,10 @@
         <v>4.05</v>
       </c>
       <c r="M1051">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="N1051">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1051">
         <v>1</v>
@@ -54399,52 +54399,52 @@
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1052" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1052">
-        <v>1.662093361254554</v>
+        <v>1.671849174539402</v>
       </c>
       <c r="D1052" t="s">
         <v>366</v>
       </c>
       <c r="E1052">
-        <v>1.658717696204637</v>
+        <v>1.678268969328508</v>
       </c>
       <c r="F1052">
         <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.006437906638745446</v>
+        <v>0.006348150825460598</v>
       </c>
       <c r="H1052">
-        <v>0.006361282303795362</v>
+        <v>0.006281731030671493</v>
       </c>
       <c r="I1052">
-        <v>0.003375665049916599</v>
+        <v>-0.006419794789105815</v>
       </c>
       <c r="J1052">
-        <v>0.7324866990016706</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1052">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1052">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1052">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="N1052">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1052">
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>221</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -54452,37 +54452,37 @@
         <v>0</v>
       </c>
       <c r="B1053" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C1053">
-        <v>1.483278292917471</v>
+        <v>1.525149479713785</v>
       </c>
       <c r="D1053" t="s">
         <v>369</v>
       </c>
       <c r="E1053">
-        <v>1.600303450628539</v>
+        <v>1.609672218544069</v>
       </c>
       <c r="F1053">
         <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.00699672170708253</v>
+        <v>0.006974850520286215</v>
       </c>
       <c r="H1053">
-        <v>0.006819696549371461</v>
+        <v>0.00681032778145593</v>
       </c>
       <c r="I1053">
-        <v>0.1170251577110681</v>
+        <v>0.08452273883028427</v>
       </c>
       <c r="J1053">
-        <v>0.7351257885553412</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1053">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="L1053">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="M1053">
         <v>3.55</v>
@@ -54494,7 +54494,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>368</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -54502,281 +54502,281 @@
         <v>1</v>
       </c>
       <c r="B1054" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1054">
-        <v>1.6426260925685</v>
+        <v>1.662093361254554</v>
       </c>
       <c r="D1054" t="s">
         <v>366</v>
       </c>
       <c r="E1054">
-        <v>1.650246218737355</v>
+        <v>1.665342031154721</v>
       </c>
       <c r="F1054">
         <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.0065973739074315</v>
+        <v>0.006437906638745446</v>
       </c>
       <c r="H1054">
-        <v>0.006369753781262645</v>
+        <v>0.006294657968845279</v>
       </c>
       <c r="I1054">
-        <v>-0.007620126168854213</v>
+        <v>-0.003248669900167034</v>
       </c>
       <c r="J1054">
-        <v>0.7351257885553412</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1054">
-        <v>3.37</v>
+        <v>3.26</v>
       </c>
       <c r="L1054">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="M1054">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="N1054">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1054">
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>368</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1055" t="s">
         <v>223</v>
       </c>
       <c r="C1055">
-        <v>1.471153106994671</v>
+        <v>1.658717696204637</v>
       </c>
       <c r="D1055" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1055">
-        <v>1.588824941288288</v>
+        <v>1.665342031154721</v>
       </c>
       <c r="F1055">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.007008846893005329</v>
+        <v>0.006361282303795362</v>
       </c>
       <c r="H1055">
-        <v>0.006831175058711711</v>
+        <v>0.006294657968845279</v>
       </c>
       <c r="I1055">
-        <v>0.1176718342936174</v>
+        <v>-0.006624334950083632</v>
       </c>
       <c r="J1055">
-        <v>0.7383591714680878</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1055">
-        <v>3.75</v>
+        <v>3.21</v>
       </c>
       <c r="L1055">
-        <v>4.24</v>
+        <v>4.01</v>
       </c>
       <c r="M1055">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="N1055">
-        <v>4.21</v>
+        <v>3.98</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1056" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1056">
-        <v>1.631729592152544</v>
+        <v>1.653489929309588</v>
       </c>
       <c r="D1056" t="s">
         <v>366</v>
       </c>
       <c r="E1056">
-        <v>1.639867059587438</v>
+        <v>1.657002508165122</v>
       </c>
       <c r="F1056">
         <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.006608270407847457</v>
+        <v>0.006446510070690412</v>
       </c>
       <c r="H1056">
-        <v>0.006380132940412562</v>
+        <v>0.006302997491834879</v>
       </c>
       <c r="I1056">
-        <v>-0.008137467434893964</v>
+        <v>-0.00351257885553391</v>
       </c>
       <c r="J1056">
-        <v>0.7383591714680878</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1056">
-        <v>3.37</v>
+        <v>3.26</v>
       </c>
       <c r="L1056">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="M1056">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="N1056">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1056">
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>220</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1057" t="s">
         <v>223</v>
       </c>
       <c r="C1057">
-        <v>1.450207109606322</v>
+        <v>1.650246218737355</v>
       </c>
       <c r="D1057" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1057">
-        <v>1.568996063760652</v>
+        <v>1.657002508165122</v>
       </c>
       <c r="F1057">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.007029792890393678</v>
+        <v>0.006369753781262645</v>
       </c>
       <c r="H1057">
-        <v>0.006851003936239348</v>
+        <v>0.006302997491834879</v>
       </c>
       <c r="I1057">
-        <v>0.1187889541543292</v>
+        <v>-0.006756289427767292</v>
       </c>
       <c r="J1057">
-        <v>0.7439447707716474</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1057">
-        <v>3.75</v>
+        <v>3.21</v>
       </c>
       <c r="L1057">
-        <v>4.24</v>
+        <v>4.01</v>
       </c>
       <c r="M1057">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="N1057">
-        <v>4.21</v>
+        <v>3.98</v>
       </c>
       <c r="O1057">
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>491</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1058" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C1058">
-        <v>1.624740047284429</v>
+        <v>1.471153106994671</v>
       </c>
       <c r="D1058" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1058">
-        <v>1.621937285823011</v>
+        <v>1.588824941288288</v>
       </c>
       <c r="F1058">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.00647525995271557</v>
+        <v>0.007008846893005329</v>
       </c>
       <c r="H1058">
-        <v>0.006398062714176988</v>
+        <v>0.006831175058711711</v>
       </c>
       <c r="I1058">
-        <v>0.002802761461417891</v>
+        <v>0.1176718342936174</v>
       </c>
       <c r="J1058">
-        <v>0.7439447707716474</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1058">
-        <v>3.26</v>
+        <v>3.75</v>
       </c>
       <c r="L1058">
-        <v>4.05</v>
+        <v>4.24</v>
       </c>
       <c r="M1058">
-        <v>3.21</v>
+        <v>3.55</v>
       </c>
       <c r="N1058">
-        <v>4.01</v>
+        <v>4.21</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>491</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1059" t="s">
         <v>222</v>
       </c>
       <c r="C1059">
-        <v>1.61016227805581</v>
+        <v>1.642949101014034</v>
       </c>
       <c r="D1059" t="s">
         <v>366</v>
       </c>
       <c r="E1059">
-        <v>1.607583102012009</v>
+        <v>1.646785018160843</v>
       </c>
       <c r="F1059">
         <v>-1</v>
       </c>
       <c r="G1059">
-        <v>0.006489837721944189</v>
+        <v>0.006457050898985965</v>
       </c>
       <c r="H1059">
-        <v>0.00641241689798799</v>
+        <v>0.006313214981839158</v>
       </c>
       <c r="I1059">
-        <v>0.002579176043800757</v>
+        <v>-0.003835917146808754</v>
       </c>
       <c r="J1059">
-        <v>0.7484164791239846</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1059">
         <v>3.26</v>
@@ -54785,16 +54785,116 @@
         <v>4.05</v>
       </c>
       <c r="M1059">
+        <v>3.16</v>
+      </c>
+      <c r="N1059">
+        <v>3.98</v>
+      </c>
+      <c r="O1059">
+        <v>1</v>
+      </c>
+      <c r="P1059" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:16">
+      <c r="A1060" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1060">
+        <v>1.639867059587438</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>366</v>
+      </c>
+      <c r="E1060">
+        <v>1.646785018160843</v>
+      </c>
+      <c r="F1060">
+        <v>-1</v>
+      </c>
+      <c r="G1060">
+        <v>0.006380132940412562</v>
+      </c>
+      <c r="H1060">
+        <v>0.006313214981839158</v>
+      </c>
+      <c r="I1060">
+        <v>-0.006917958573404714</v>
+      </c>
+      <c r="J1060">
+        <v>0.7383591714680878</v>
+      </c>
+      <c r="K1060">
         <v>3.21</v>
       </c>
-      <c r="N1059">
+      <c r="L1060">
         <v>4.01</v>
       </c>
-      <c r="O1059">
-        <v>1</v>
-      </c>
-      <c r="P1059" t="s">
-        <v>223</v>
+      <c r="M1060">
+        <v>3.16</v>
+      </c>
+      <c r="N1060">
+        <v>3.98</v>
+      </c>
+      <c r="O1060">
+        <v>1</v>
+      </c>
+      <c r="P1060" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:16">
+      <c r="A1061" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1061">
+        <v>1.624740047284429</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>366</v>
+      </c>
+      <c r="E1061">
+        <v>1.629134524361594</v>
+      </c>
+      <c r="F1061">
+        <v>-1</v>
+      </c>
+      <c r="G1061">
+        <v>0.00647525995271557</v>
+      </c>
+      <c r="H1061">
+        <v>0.006330865475638406</v>
+      </c>
+      <c r="I1061">
+        <v>-0.004394477077164449</v>
+      </c>
+      <c r="J1061">
+        <v>0.7439447707716474</v>
+      </c>
+      <c r="K1061">
+        <v>3.26</v>
+      </c>
+      <c r="L1061">
+        <v>4.05</v>
+      </c>
+      <c r="M1061">
+        <v>3.16</v>
+      </c>
+      <c r="N1061">
+        <v>3.98</v>
+      </c>
+      <c r="O1061">
+        <v>1</v>
+      </c>
+      <c r="P1061" t="s">
+        <v>491</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3255" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3270" uniqueCount="500">
   <si>
     <t>trade_time</t>
   </si>
@@ -682,16 +682,16 @@
     <t>2021-07-12</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-07-27</t>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2021-07-29</t>
   </si>
   <si>
-    <t>2021-08-03</t>
+    <t>2021-08-04</t>
   </si>
   <si>
     <t>2016-07-22</t>
@@ -1117,7 +1117,7 @@
     <t>2021-05-10</t>
   </si>
   <si>
-    <t>2021-08-04</t>
+    <t>2021-08-05</t>
   </si>
   <si>
     <t>2021-07-13</t>
@@ -1127,6 +1127,9 @@
   </si>
   <si>
     <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-08-03</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -1868,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1081"/>
+  <dimension ref="A1:P1086"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1965,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2015,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2065,7 +2068,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2115,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2165,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2215,7 +2218,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2265,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2315,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2365,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2415,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2465,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2515,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2565,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2615,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2665,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2715,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2765,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2815,7 +2818,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2865,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2915,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2965,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3015,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3065,7 +3068,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3115,7 +3118,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3165,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3215,7 +3218,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3265,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3315,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3365,7 +3368,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3415,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3465,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3515,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3815,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3865,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3915,7 +3918,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3965,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4015,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4065,7 +4068,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4115,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4165,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4215,7 +4218,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4265,7 +4268,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4315,7 +4318,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4365,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4415,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4465,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4515,7 +4518,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4565,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4615,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4665,7 +4668,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4715,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4765,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4815,7 +4818,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4865,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4915,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4965,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5015,7 +5018,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5065,7 +5068,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5115,7 +5118,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5165,7 +5168,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5215,7 +5218,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5265,7 +5268,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5315,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5365,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5415,7 +5418,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5465,7 +5468,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5515,7 +5518,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5565,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5615,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5665,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5715,7 +5718,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5765,7 +5768,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6015,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6065,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6115,7 +6118,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6165,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6815,7 +6818,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6865,7 +6868,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6915,7 +6918,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6965,7 +6968,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7015,7 +7018,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7065,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7115,7 +7118,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7165,7 +7168,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7215,7 +7218,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7265,7 +7268,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7315,7 +7318,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7365,7 +7368,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7615,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7665,7 +7668,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7715,7 +7718,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7765,7 +7768,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8065,7 +8068,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8115,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8165,7 +8168,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8215,7 +8218,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8265,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8315,7 +8318,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8365,7 +8368,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8815,7 +8818,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8865,7 +8868,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8915,7 +8918,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8965,7 +8968,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9015,7 +9018,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9065,7 +9068,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9115,7 +9118,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9165,7 +9168,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9215,7 +9218,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9265,7 +9268,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9315,7 +9318,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9365,7 +9368,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9415,7 +9418,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9465,7 +9468,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9515,7 +9518,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9565,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9615,7 +9618,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9665,7 +9668,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9715,7 +9718,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9765,7 +9768,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9815,7 +9818,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9865,7 +9868,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9915,7 +9918,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9965,7 +9968,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10015,7 +10018,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10065,7 +10068,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10115,7 +10118,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10165,7 +10168,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10215,7 +10218,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10265,7 +10268,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10315,7 +10318,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10365,7 +10368,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10415,7 +10418,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10465,7 +10468,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10515,7 +10518,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10565,7 +10568,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10615,7 +10618,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10665,7 +10668,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10715,7 +10718,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10765,7 +10768,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10815,7 +10818,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10865,7 +10868,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10915,7 +10918,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10965,7 +10968,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11315,7 +11318,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11365,7 +11368,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11415,7 +11418,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11465,7 +11468,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11515,7 +11518,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11565,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11615,7 +11618,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -12015,7 +12018,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12065,7 +12068,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12115,7 +12118,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12165,7 +12168,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12215,7 +12218,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12265,7 +12268,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12315,7 +12318,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12365,7 +12368,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12415,7 +12418,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12465,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12515,7 +12518,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12565,7 +12568,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12615,7 +12618,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12665,7 +12668,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12715,7 +12718,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12765,7 +12768,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12815,7 +12818,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12865,7 +12868,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12915,7 +12918,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12965,7 +12968,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -13015,7 +13018,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -13965,7 +13968,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14015,7 +14018,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14065,7 +14068,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14115,7 +14118,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14165,7 +14168,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14215,7 +14218,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14265,7 +14268,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14315,7 +14318,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14365,7 +14368,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14415,7 +14418,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14465,7 +14468,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14515,7 +14518,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14565,7 +14568,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14615,7 +14618,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14665,7 +14668,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14715,7 +14718,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14765,7 +14768,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14815,7 +14818,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14865,7 +14868,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14915,7 +14918,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14965,7 +14968,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15015,7 +15018,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15065,7 +15068,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15115,7 +15118,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15165,7 +15168,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15215,7 +15218,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15265,7 +15268,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15315,7 +15318,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15365,7 +15368,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15415,7 +15418,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15465,7 +15468,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15515,7 +15518,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15565,7 +15568,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15615,7 +15618,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15665,7 +15668,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15715,7 +15718,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15765,7 +15768,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15815,7 +15818,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15865,7 +15868,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15915,7 +15918,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15965,7 +15968,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -16015,7 +16018,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -16065,7 +16068,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16115,7 +16118,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16165,7 +16168,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16215,7 +16218,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16265,7 +16268,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16315,7 +16318,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16365,7 +16368,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16415,7 +16418,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16465,7 +16468,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16515,7 +16518,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16565,7 +16568,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16615,7 +16618,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16665,7 +16668,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16715,7 +16718,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16765,7 +16768,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16815,7 +16818,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16865,7 +16868,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16915,7 +16918,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16965,7 +16968,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17015,7 +17018,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17065,7 +17068,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17115,7 +17118,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17165,7 +17168,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17215,7 +17218,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17265,7 +17268,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17315,7 +17318,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17365,7 +17368,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17415,7 +17418,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17465,7 +17468,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17515,7 +17518,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17565,7 +17568,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17615,7 +17618,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17665,7 +17668,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17715,7 +17718,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17765,7 +17768,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17815,7 +17818,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17865,7 +17868,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17915,7 +17918,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17965,7 +17968,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18015,7 +18018,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -18065,7 +18068,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18565,7 +18568,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18615,7 +18618,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18665,7 +18668,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18715,7 +18718,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18765,7 +18768,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18815,7 +18818,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18865,7 +18868,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18915,7 +18918,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18965,7 +18968,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19015,7 +19018,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19065,7 +19068,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19115,7 +19118,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19165,7 +19168,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19215,7 +19218,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19265,7 +19268,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19315,7 +19318,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19365,7 +19368,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19415,7 +19418,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19465,7 +19468,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19515,7 +19518,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19565,7 +19568,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19615,7 +19618,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19665,7 +19668,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19715,7 +19718,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19765,7 +19768,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19815,7 +19818,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19865,7 +19868,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19915,7 +19918,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19965,7 +19968,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20015,7 +20018,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20065,7 +20068,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20115,7 +20118,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20165,7 +20168,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20215,7 +20218,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20265,7 +20268,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20315,7 +20318,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20365,7 +20368,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20415,7 +20418,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20465,7 +20468,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20515,7 +20518,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20565,7 +20568,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20615,7 +20618,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20665,7 +20668,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20715,7 +20718,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20765,7 +20768,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20815,7 +20818,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20865,7 +20868,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20915,7 +20918,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20965,7 +20968,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21015,7 +21018,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21065,7 +21068,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21115,7 +21118,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21165,7 +21168,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21215,7 +21218,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21265,7 +21268,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21315,7 +21318,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21365,7 +21368,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21415,7 +21418,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21465,7 +21468,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21515,7 +21518,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21565,7 +21568,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21615,7 +21618,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21665,7 +21668,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21715,7 +21718,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21765,7 +21768,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21815,7 +21818,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21865,7 +21868,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21915,7 +21918,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21965,7 +21968,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22015,7 +22018,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22065,7 +22068,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22115,7 +22118,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22165,7 +22168,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22215,7 +22218,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22265,7 +22268,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22315,7 +22318,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22365,7 +22368,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22415,7 +22418,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22465,7 +22468,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22515,7 +22518,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22565,7 +22568,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22615,7 +22618,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22665,7 +22668,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22715,7 +22718,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22765,7 +22768,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22815,7 +22818,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22865,7 +22868,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22915,7 +22918,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22965,7 +22968,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23015,7 +23018,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23065,7 +23068,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23115,7 +23118,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23165,7 +23168,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23215,7 +23218,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23265,7 +23268,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23315,7 +23318,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23365,7 +23368,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23415,7 +23418,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23465,7 +23468,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23515,7 +23518,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23565,7 +23568,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23615,7 +23618,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23665,7 +23668,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23715,7 +23718,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23765,7 +23768,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23815,7 +23818,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23865,7 +23868,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23915,7 +23918,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23965,7 +23968,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24015,7 +24018,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24065,7 +24068,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24115,7 +24118,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24165,7 +24168,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24215,7 +24218,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24265,7 +24268,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24315,7 +24318,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24365,7 +24368,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24415,7 +24418,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24465,7 +24468,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24515,7 +24518,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24565,7 +24568,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24615,7 +24618,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24665,7 +24668,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24715,7 +24718,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24765,7 +24768,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24815,7 +24818,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24865,7 +24868,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24915,7 +24918,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24965,7 +24968,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25315,7 +25318,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25365,7 +25368,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25415,7 +25418,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25465,7 +25468,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25515,7 +25518,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25565,7 +25568,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25615,7 +25618,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25665,7 +25668,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25715,7 +25718,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25765,7 +25768,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25815,7 +25818,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25865,7 +25868,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25915,7 +25918,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25965,7 +25968,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26015,7 +26018,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26065,7 +26068,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26115,7 +26118,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26165,7 +26168,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26215,7 +26218,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26265,7 +26268,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26915,7 +26918,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26965,7 +26968,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27015,7 +27018,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27065,7 +27068,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27115,7 +27118,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27165,7 +27168,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27215,7 +27218,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27265,7 +27268,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27315,7 +27318,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27365,7 +27368,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27415,7 +27418,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27465,7 +27468,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27515,7 +27518,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28165,7 +28168,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28215,7 +28218,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28265,7 +28268,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28315,7 +28318,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28365,7 +28368,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28415,7 +28418,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28465,7 +28468,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28515,7 +28518,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28565,7 +28568,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28615,7 +28618,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28665,7 +28668,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28715,7 +28718,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -32265,7 +32268,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32315,7 +32318,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32365,7 +32368,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32415,7 +32418,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32465,7 +32468,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32515,7 +32518,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32565,7 +32568,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32615,7 +32618,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32665,7 +32668,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33515,7 +33518,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33565,7 +33568,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33615,7 +33618,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33665,7 +33668,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33715,7 +33718,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33765,7 +33768,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33815,7 +33818,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33865,7 +33868,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33915,7 +33918,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33965,7 +33968,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34015,7 +34018,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34065,7 +34068,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34115,7 +34118,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34165,7 +34168,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34215,7 +34218,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34265,7 +34268,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -35115,7 +35118,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35165,7 +35168,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35215,7 +35218,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35265,7 +35268,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35315,7 +35318,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35365,7 +35368,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35415,7 +35418,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35465,7 +35468,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35515,7 +35518,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35565,7 +35568,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35615,7 +35618,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35665,7 +35668,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35715,7 +35718,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35765,7 +35768,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35815,7 +35818,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36215,7 +36218,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36265,7 +36268,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36315,7 +36318,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36365,7 +36368,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36415,7 +36418,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36465,7 +36468,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36515,7 +36518,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37265,7 +37268,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37315,7 +37318,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37365,7 +37368,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37415,7 +37418,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37465,7 +37468,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37515,7 +37518,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37565,7 +37568,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37615,7 +37618,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37665,7 +37668,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37715,7 +37718,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37765,7 +37768,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37815,7 +37818,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37865,7 +37868,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37915,7 +37918,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37965,7 +37968,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38015,7 +38018,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38065,7 +38068,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38115,7 +38118,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38165,7 +38168,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38215,7 +38218,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38665,7 +38668,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38715,7 +38718,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38765,7 +38768,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38815,7 +38818,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38865,7 +38868,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38915,7 +38918,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38965,7 +38968,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39315,7 +39318,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39365,7 +39368,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39415,7 +39418,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39465,7 +39468,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39515,7 +39518,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39565,7 +39568,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39615,7 +39618,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39665,7 +39668,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39715,7 +39718,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39765,7 +39768,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39815,7 +39818,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -41915,7 +41918,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41965,7 +41968,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42015,7 +42018,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42065,7 +42068,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42115,7 +42118,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42165,7 +42168,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42215,7 +42218,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42265,7 +42268,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42315,7 +42318,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42365,7 +42368,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42415,7 +42418,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42465,7 +42468,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42515,7 +42518,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42565,7 +42568,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42615,7 +42618,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42665,7 +42668,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42715,7 +42718,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42765,7 +42768,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -42815,7 +42818,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -42865,7 +42868,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -42915,7 +42918,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42965,7 +42968,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -43015,7 +43018,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -44665,7 +44668,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44715,7 +44718,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44765,7 +44768,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44815,7 +44818,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44865,7 +44868,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44915,7 +44918,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44965,7 +44968,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45015,7 +45018,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45065,7 +45068,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45115,7 +45118,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45165,7 +45168,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45215,7 +45218,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45465,7 +45468,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45515,7 +45518,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45565,7 +45568,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45615,7 +45618,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45665,7 +45668,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45715,7 +45718,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45765,7 +45768,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -45815,7 +45818,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -45865,7 +45868,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -45915,7 +45918,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -45965,7 +45968,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46015,7 +46018,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46065,7 +46068,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46115,7 +46118,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46515,7 +46518,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46565,7 +46568,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46615,7 +46618,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -48765,7 +48768,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -48815,7 +48818,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -48865,7 +48868,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -48915,7 +48918,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -48965,7 +48968,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49015,7 +49018,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49065,7 +49068,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49115,7 +49118,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49165,7 +49168,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49215,7 +49218,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49265,7 +49268,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49315,7 +49318,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49365,7 +49368,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49415,7 +49418,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49465,7 +49468,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49515,7 +49518,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49565,7 +49568,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49615,7 +49618,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49665,7 +49668,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49715,7 +49718,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -49765,7 +49768,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -49815,7 +49818,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -49865,7 +49868,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -49915,7 +49918,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -49965,7 +49968,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -50015,7 +50018,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50065,7 +50068,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50115,7 +50118,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50165,7 +50168,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50215,7 +50218,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50265,7 +50268,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -50315,7 +50318,7 @@
         <v>1</v>
       </c>
       <c r="P969" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="970" spans="1:16">
@@ -50365,7 +50368,7 @@
         <v>1</v>
       </c>
       <c r="P970" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="971" spans="1:16">
@@ -50415,7 +50418,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -50465,7 +50468,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -50515,7 +50518,7 @@
         <v>1</v>
       </c>
       <c r="P973" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="974" spans="1:16">
@@ -50565,7 +50568,7 @@
         <v>1</v>
       </c>
       <c r="P974" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="975" spans="1:16">
@@ -50615,7 +50618,7 @@
         <v>1</v>
       </c>
       <c r="P975" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="976" spans="1:16">
@@ -50665,7 +50668,7 @@
         <v>1</v>
       </c>
       <c r="P976" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="977" spans="1:16">
@@ -50715,7 +50718,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50765,7 +50768,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50815,7 +50818,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50865,7 +50868,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50915,7 +50918,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50965,7 +50968,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51015,7 +51018,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51065,7 +51068,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51115,7 +51118,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51165,7 +51168,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51215,7 +51218,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51265,7 +51268,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51315,7 +51318,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51365,7 +51368,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51415,7 +51418,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51465,7 +51468,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51515,7 +51518,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51565,7 +51568,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51615,7 +51618,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51665,7 +51668,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51715,7 +51718,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51765,7 +51768,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51815,7 +51818,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51865,7 +51868,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51915,7 +51918,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -52115,7 +52118,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52165,7 +52168,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52215,7 +52218,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52265,7 +52268,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52515,7 +52518,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52565,7 +52568,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -52615,7 +52618,7 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -52665,7 +52668,7 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -52715,7 +52718,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52765,7 +52768,7 @@
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
@@ -52815,7 +52818,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52865,7 +52868,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52915,7 +52918,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52965,7 +52968,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -53015,7 +53018,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -53065,7 +53068,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53115,7 +53118,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53165,7 +53168,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53215,7 +53218,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53265,7 +53268,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53315,7 +53318,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53365,7 +53368,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53415,7 +53418,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53465,7 +53468,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53515,7 +53518,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53532,7 +53535,7 @@
         <v>367</v>
       </c>
       <c r="E1034">
-        <v>1.77485285313765</v>
+        <v>1.781679934087689</v>
       </c>
       <c r="F1034">
         <v>1</v>
@@ -53541,10 +53544,10 @@
         <v>0.006789674113414224</v>
       </c>
       <c r="H1034">
-        <v>0.00618514714686235</v>
+        <v>0.006178320065912311</v>
       </c>
       <c r="I1034">
-        <v>0.06452696655187351</v>
+        <v>0.07135404750191165</v>
       </c>
       <c r="J1034">
         <v>0.6827080950038233</v>
@@ -53556,7 +53559,7 @@
         <v>4.25</v>
       </c>
       <c r="M1034">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1034">
         <v>3.98</v>
@@ -53565,7 +53568,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53615,7 +53618,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -53665,7 +53668,7 @@
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
@@ -53715,7 +53718,7 @@
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
@@ -53765,7 +53768,7 @@
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
@@ -53815,7 +53818,7 @@
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
@@ -53865,7 +53868,7 @@
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
@@ -53876,10 +53879,10 @@
         <v>222</v>
       </c>
       <c r="C1041">
-        <v>1.73956726832893</v>
+        <v>1.738667498339339</v>
       </c>
       <c r="D1041" t="s">
-        <v>367</v>
+        <v>225</v>
       </c>
       <c r="E1041">
         <v>1.689937429336216</v>
@@ -53888,22 +53891,22 @@
         <v>-1</v>
       </c>
       <c r="G1041">
-        <v>0.006220432731671071</v>
+        <v>0.006361332501660661</v>
       </c>
       <c r="H1041">
         <v>0.006270062570663784</v>
       </c>
       <c r="I1041">
-        <v>0.04962983899271345</v>
+        <v>0.04873006900312271</v>
       </c>
       <c r="J1041">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1041">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1041">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1041">
         <v>3.23</v>
@@ -53915,51 +53918,51 @@
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1042" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1042">
-        <v>1.725336643125503</v>
+        <v>1.73956726832893</v>
       </c>
       <c r="D1042" t="s">
-        <v>368</v>
+        <v>225</v>
       </c>
       <c r="E1042">
-        <v>1.661041642546622</v>
+        <v>1.689937429336216</v>
       </c>
       <c r="F1042">
         <v>-1</v>
       </c>
       <c r="G1042">
-        <v>0.006954663356874498</v>
+        <v>0.006220432731671071</v>
       </c>
       <c r="H1042">
-        <v>0.007018958357453379</v>
+        <v>0.006270062570663784</v>
       </c>
       <c r="I1042">
-        <v>0.06429500057888093</v>
+        <v>0.04962983899271345</v>
       </c>
       <c r="J1042">
-        <v>0.7143888953209009</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1042">
-        <v>3.66</v>
+        <v>3.16</v>
       </c>
       <c r="L1042">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="M1042">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N1042">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="O1042">
         <v>1</v>
@@ -53970,143 +53973,143 @@
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1043" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1043">
-        <v>1.592473309406249</v>
+        <v>1.725336643125503</v>
       </c>
       <c r="D1043" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E1043">
-        <v>1.673919421610802</v>
+        <v>1.661041642546622</v>
       </c>
       <c r="F1043">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1043">
-        <v>0.006907526690593752</v>
+        <v>0.006954663356874498</v>
       </c>
       <c r="H1043">
-        <v>0.006746080578389198</v>
+        <v>0.007018958357453379</v>
       </c>
       <c r="I1043">
-        <v>0.08144611220455333</v>
+        <v>0.06429500057888093</v>
       </c>
       <c r="J1043">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1043">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="L1043">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="M1043">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N1043">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="O1043">
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1044" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C1044">
-        <v>1.721092201253863</v>
+        <v>1.592473309406249</v>
       </c>
       <c r="D1044" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E1044">
-        <v>1.67252386811349</v>
+        <v>1.673919421610802</v>
       </c>
       <c r="F1044">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1044">
-        <v>0.006378907798746137</v>
+        <v>0.006907526690593752</v>
       </c>
       <c r="H1044">
-        <v>0.006287476131886511</v>
+        <v>0.006746080578389198</v>
       </c>
       <c r="I1044">
-        <v>0.04856833314037301</v>
+        <v>0.08144611220455333</v>
       </c>
       <c r="J1044">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1044">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="L1044">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M1044">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N1044">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1044">
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1045" t="s">
         <v>222</v>
       </c>
       <c r="C1045">
-        <v>1.722531090785953</v>
+        <v>1.721092201253863</v>
       </c>
       <c r="D1045" t="s">
         <v>367</v>
       </c>
       <c r="E1045">
-        <v>1.67252386811349</v>
+        <v>1.679667757066699</v>
       </c>
       <c r="F1045">
         <v>-1</v>
       </c>
       <c r="G1045">
-        <v>0.006237468909214047</v>
+        <v>0.006378907798746137</v>
       </c>
       <c r="H1045">
-        <v>0.006287476131886511</v>
+        <v>0.006280332242933302</v>
       </c>
       <c r="I1045">
-        <v>0.05000722267246305</v>
+        <v>0.04142444418716407</v>
       </c>
       <c r="J1045">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1045">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1045">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1045">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1045">
         <v>3.98</v>
@@ -54115,51 +54118,51 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1046" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1046">
-        <v>1.706714139491356</v>
+        <v>1.722531090785953</v>
       </c>
       <c r="D1046" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E1046">
-        <v>1.641961208495242</v>
+        <v>1.679667757066699</v>
       </c>
       <c r="F1046">
         <v>-1</v>
       </c>
       <c r="G1046">
-        <v>0.006973285860508644</v>
+        <v>0.006237468909214047</v>
       </c>
       <c r="H1046">
-        <v>0.007038038791504758</v>
+        <v>0.006280332242933302</v>
       </c>
       <c r="I1046">
-        <v>0.0647529309961139</v>
+        <v>0.0428633337192541</v>
       </c>
       <c r="J1046">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1046">
-        <v>3.66</v>
+        <v>3.16</v>
       </c>
       <c r="L1046">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="M1046">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="N1046">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="O1046">
         <v>1</v>
@@ -54170,143 +54173,143 @@
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1047" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1047">
-        <v>1.57354551882728</v>
+        <v>1.706714139491356</v>
       </c>
       <c r="D1047" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E1047">
-        <v>1.655856610708829</v>
+        <v>1.641961208495242</v>
       </c>
       <c r="F1047">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1047">
-        <v>0.00692645448117272</v>
+        <v>0.006973285860508644</v>
       </c>
       <c r="H1047">
-        <v>0.006764143389291171</v>
+        <v>0.007038038791504758</v>
       </c>
       <c r="I1047">
-        <v>0.08231109188154928</v>
+        <v>0.0647529309961139</v>
       </c>
       <c r="J1047">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1047">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="L1047">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="M1047">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N1047">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1048" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C1048">
-        <v>1.70450494391853</v>
+        <v>1.57354551882728</v>
       </c>
       <c r="D1048" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E1048">
-        <v>1.656089254250568</v>
+        <v>1.655856610708829</v>
       </c>
       <c r="F1048">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1048">
-        <v>0.006395495056081469</v>
+        <v>0.00692645448117272</v>
       </c>
       <c r="H1048">
-        <v>0.006303910745749432</v>
+        <v>0.006764143389291171</v>
       </c>
       <c r="I1048">
-        <v>0.04841568966796217</v>
+        <v>0.08231109188154928</v>
       </c>
       <c r="J1048">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1048">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="L1048">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M1048">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N1048">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1048">
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1049" t="s">
         <v>222</v>
       </c>
       <c r="C1049">
-        <v>1.706452645025324</v>
+        <v>1.70450494391853</v>
       </c>
       <c r="D1049" t="s">
         <v>367</v>
       </c>
       <c r="E1049">
-        <v>1.656089254250568</v>
+        <v>1.663284024361248</v>
       </c>
       <c r="F1049">
         <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.006253547354974676</v>
+        <v>0.006395495056081469</v>
       </c>
       <c r="H1049">
-        <v>0.006303910745749432</v>
+        <v>0.006296715975638753</v>
       </c>
       <c r="I1049">
-        <v>0.0503633907747556</v>
+        <v>0.0412209195572828</v>
       </c>
       <c r="J1049">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1049">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1049">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1049">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1049">
         <v>3.98</v>
@@ -54315,51 +54318,51 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1050" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1050">
-        <v>1.687585123258323</v>
+        <v>1.706452645025324</v>
       </c>
       <c r="D1050" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E1050">
-        <v>1.622361806617135</v>
+        <v>1.663284024361248</v>
       </c>
       <c r="F1050">
         <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.006992414876741677</v>
+        <v>0.006253547354974676</v>
       </c>
       <c r="H1050">
-        <v>0.007057638193382865</v>
+        <v>0.006296715975638753</v>
       </c>
       <c r="I1050">
-        <v>0.06522331664118841</v>
+        <v>0.04316862066407623</v>
       </c>
       <c r="J1050">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1050">
-        <v>3.66</v>
+        <v>3.16</v>
       </c>
       <c r="L1050">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="M1050">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="N1050">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="O1050">
         <v>1</v>
@@ -54370,143 +54373,143 @@
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1051" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1051">
-        <v>1.554102912164197</v>
+        <v>1.687585123258323</v>
       </c>
       <c r="D1051" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E1051">
-        <v>1.637302510264221</v>
+        <v>1.622361806617135</v>
       </c>
       <c r="F1051">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1051">
-        <v>0.006945897087835803</v>
+        <v>0.006992414876741677</v>
       </c>
       <c r="H1051">
-        <v>0.00678269748973578</v>
+        <v>0.007057638193382865</v>
       </c>
       <c r="I1051">
-        <v>0.08319959810002331</v>
+        <v>0.06522331664118841</v>
       </c>
       <c r="J1051">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1051">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="L1051">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="M1051">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N1051">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="O1051">
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1052" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C1052">
-        <v>1.687466530552496</v>
+        <v>1.554102912164197</v>
       </c>
       <c r="D1052" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E1052">
-        <v>1.639207636099559</v>
+        <v>1.637302510264221</v>
       </c>
       <c r="F1052">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1052">
-        <v>0.006412533469447504</v>
+        <v>0.006945897087835803</v>
       </c>
       <c r="H1052">
-        <v>0.006320792363900441</v>
+        <v>0.00678269748973578</v>
       </c>
       <c r="I1052">
-        <v>0.04825889445293718</v>
+        <v>0.08319959810002331</v>
       </c>
       <c r="J1052">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1052">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="L1052">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M1052">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N1052">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1052">
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1053" t="s">
         <v>222</v>
       </c>
       <c r="C1053">
-        <v>1.689936882376039</v>
+        <v>1.687466530552496</v>
       </c>
       <c r="D1053" t="s">
         <v>367</v>
       </c>
       <c r="E1053">
-        <v>1.639207636099559</v>
+        <v>1.646454671281913</v>
       </c>
       <c r="F1053">
         <v>-1</v>
       </c>
       <c r="G1053">
-        <v>0.006270063117623961</v>
+        <v>0.006412533469447504</v>
       </c>
       <c r="H1053">
-        <v>0.006320792363900441</v>
+        <v>0.006313545328718087</v>
       </c>
       <c r="I1053">
-        <v>0.05072924627648012</v>
+        <v>0.04101185927058326</v>
       </c>
       <c r="J1053">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1053">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1053">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1053">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1053">
         <v>3.98</v>
@@ -54515,51 +54518,51 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1054" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1054">
-        <v>1.674071021437449</v>
+        <v>1.689936882376039</v>
       </c>
       <c r="D1054" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E1054">
-        <v>1.608515390817058</v>
+        <v>1.646454671281913</v>
       </c>
       <c r="F1054">
         <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.007005928978562551</v>
+        <v>0.006270063117623961</v>
       </c>
       <c r="H1054">
-        <v>0.007071484609182941</v>
+        <v>0.006313545328718087</v>
       </c>
       <c r="I1054">
-        <v>0.06555563062039038</v>
+        <v>0.0434822110941262</v>
       </c>
       <c r="J1054">
-        <v>0.7283958957821177</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1054">
-        <v>3.66</v>
+        <v>3.16</v>
       </c>
       <c r="L1054">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="M1054">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="N1054">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -54570,143 +54573,143 @@
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1055" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1055">
-        <v>1.540367267690522</v>
+        <v>1.674071021437449</v>
       </c>
       <c r="D1055" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E1055">
-        <v>1.624194569973482</v>
+        <v>1.608515390817058</v>
       </c>
       <c r="F1055">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.006959632732309478</v>
+        <v>0.007005928978562551</v>
       </c>
       <c r="H1055">
-        <v>0.006795805430026517</v>
+        <v>0.007071484609182941</v>
       </c>
       <c r="I1055">
-        <v>0.08382730228296031</v>
+        <v>0.06555563062039038</v>
       </c>
       <c r="J1055">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1055">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="L1055">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="M1055">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N1055">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1056" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C1056">
-        <v>1.675429379750296</v>
+        <v>1.540367267690522</v>
       </c>
       <c r="D1056" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E1056">
-        <v>1.62728125662376</v>
+        <v>1.624194569973482</v>
       </c>
       <c r="F1056">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1056">
-        <v>0.006424570620249703</v>
+        <v>0.006959632732309478</v>
       </c>
       <c r="H1056">
-        <v>0.006332718743376241</v>
+        <v>0.006795805430026517</v>
       </c>
       <c r="I1056">
-        <v>0.04814812312653682</v>
+        <v>0.08382730228296031</v>
       </c>
       <c r="J1056">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1056">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="L1056">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M1056">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N1056">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1056">
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1057" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1057">
-        <v>1.671849174539402</v>
+        <v>1.675429379750296</v>
       </c>
       <c r="D1057" t="s">
         <v>367</v>
       </c>
       <c r="E1057">
-        <v>1.62728125662376</v>
+        <v>1.634565215581581</v>
       </c>
       <c r="F1057">
         <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.006348150825460598</v>
+        <v>0.006424570620249703</v>
       </c>
       <c r="H1057">
-        <v>0.006332718743376241</v>
+        <v>0.00632543478441842</v>
       </c>
       <c r="I1057">
-        <v>0.04456791791564241</v>
+        <v>0.04086416416871552</v>
       </c>
       <c r="J1057">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1057">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="L1057">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M1057">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1057">
         <v>3.98</v>
@@ -54715,101 +54718,101 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1058" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C1058">
-        <v>1.525149479713785</v>
+        <v>1.671849174539402</v>
       </c>
       <c r="D1058" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E1058">
-        <v>1.609672218544069</v>
+        <v>1.634565215581581</v>
       </c>
       <c r="F1058">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1058">
-        <v>0.006974850520286215</v>
+        <v>0.006348150825460598</v>
       </c>
       <c r="H1058">
-        <v>0.00681032778145593</v>
+        <v>0.00632543478441842</v>
       </c>
       <c r="I1058">
-        <v>0.08452273883028427</v>
+        <v>0.03728395895782111</v>
       </c>
       <c r="J1058">
-        <v>0.7324866990016706</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1058">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="L1058">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="M1058">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="N1058">
-        <v>4.21</v>
+        <v>3.98</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>221</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1059" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C1059">
-        <v>1.662093361254554</v>
+        <v>1.525149479713785</v>
       </c>
       <c r="D1059" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E1059">
-        <v>1.614067962224604</v>
+        <v>1.609672218544069</v>
       </c>
       <c r="F1059">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1059">
-        <v>0.006437906638745446</v>
+        <v>0.006974850520286215</v>
       </c>
       <c r="H1059">
-        <v>0.006345932037775397</v>
+        <v>0.00681032778145593</v>
       </c>
       <c r="I1059">
-        <v>0.04802539902994996</v>
+        <v>0.08452273883028427</v>
       </c>
       <c r="J1059">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1059">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="L1059">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M1059">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N1059">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1059">
         <v>1</v>
@@ -54820,43 +54823,43 @@
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1060" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1060">
-        <v>1.658717696204637</v>
+        <v>1.662093361254554</v>
       </c>
       <c r="D1060" t="s">
         <v>367</v>
       </c>
       <c r="E1060">
-        <v>1.614067962224604</v>
+        <v>1.62139282921462</v>
       </c>
       <c r="F1060">
         <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.006361282303795362</v>
+        <v>0.006437906638745446</v>
       </c>
       <c r="H1060">
-        <v>0.006345932037775397</v>
+        <v>0.00633860717078538</v>
       </c>
       <c r="I1060">
-        <v>0.04464973398003336</v>
+        <v>0.04070053203993362</v>
       </c>
       <c r="J1060">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1060">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="L1060">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M1060">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1060">
         <v>3.98</v>
@@ -54870,96 +54873,96 @@
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1061" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C1061">
-        <v>1.515332066574131</v>
+        <v>1.658717696204637</v>
       </c>
       <c r="D1061" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E1061">
-        <v>1.600303450628539</v>
+        <v>1.62139282921462</v>
       </c>
       <c r="F1061">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.00698466793342587</v>
+        <v>0.006361282303795362</v>
       </c>
       <c r="H1061">
-        <v>0.006819696549371461</v>
+        <v>0.00633860717078538</v>
       </c>
       <c r="I1061">
-        <v>0.08497138405440863</v>
+        <v>0.03732486699001702</v>
       </c>
       <c r="J1061">
-        <v>0.7351257885553412</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1061">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="L1061">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="M1061">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="N1061">
-        <v>4.21</v>
+        <v>3.98</v>
       </c>
       <c r="O1061">
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>368</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1062" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C1062">
-        <v>1.653489929309588</v>
+        <v>1.515332066574131</v>
       </c>
       <c r="D1062" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E1062">
-        <v>1.605543702966248</v>
+        <v>1.600303450628539</v>
       </c>
       <c r="F1062">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.006446510070690412</v>
+        <v>0.00698466793342587</v>
       </c>
       <c r="H1062">
-        <v>0.006354456297033752</v>
+        <v>0.006819696549371461</v>
       </c>
       <c r="I1062">
-        <v>0.04794622634334011</v>
+        <v>0.08497138405440863</v>
       </c>
       <c r="J1062">
         <v>0.7351257885553412</v>
       </c>
       <c r="K1062">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="L1062">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M1062">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N1062">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1062">
         <v>1</v>
@@ -54970,43 +54973,43 @@
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1063" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1063">
-        <v>1.650246218737355</v>
+        <v>1.653489929309588</v>
       </c>
       <c r="D1063" t="s">
         <v>367</v>
       </c>
       <c r="E1063">
-        <v>1.605543702966248</v>
+        <v>1.612894960851802</v>
       </c>
       <c r="F1063">
         <v>-1</v>
       </c>
       <c r="G1063">
-        <v>0.006369753781262645</v>
+        <v>0.006446510070690412</v>
       </c>
       <c r="H1063">
-        <v>0.006354456297033752</v>
+        <v>0.006347105039148198</v>
       </c>
       <c r="I1063">
-        <v>0.04470251577110673</v>
+        <v>0.04059496845778643</v>
       </c>
       <c r="J1063">
         <v>0.7351257885553412</v>
       </c>
       <c r="K1063">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="L1063">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M1063">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1063">
         <v>3.98</v>
@@ -55020,43 +55023,43 @@
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1064" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C1064">
-        <v>1.642949101014034</v>
+        <v>1.650246218737355</v>
       </c>
       <c r="D1064" t="s">
         <v>367</v>
       </c>
       <c r="E1064">
-        <v>1.595099876158076</v>
+        <v>1.612894960851802</v>
       </c>
       <c r="F1064">
         <v>-1</v>
       </c>
       <c r="G1064">
-        <v>0.006457050898985965</v>
+        <v>0.006369753781262645</v>
       </c>
       <c r="H1064">
-        <v>0.006364900123841924</v>
+        <v>0.006347105039148198</v>
       </c>
       <c r="I1064">
-        <v>0.04784922485595766</v>
+        <v>0.03735125788555305</v>
       </c>
       <c r="J1064">
-        <v>0.7383591714680878</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1064">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1064">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1064">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1064">
         <v>3.98</v>
@@ -55065,48 +55068,48 @@
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>220</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1065" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1065">
-        <v>1.639867059587438</v>
+        <v>1.642949101014034</v>
       </c>
       <c r="D1065" t="s">
         <v>367</v>
       </c>
       <c r="E1065">
-        <v>1.595099876158076</v>
+        <v>1.602483467872757</v>
       </c>
       <c r="F1065">
         <v>-1</v>
       </c>
       <c r="G1065">
-        <v>0.006380132940412562</v>
+        <v>0.006457050898985965</v>
       </c>
       <c r="H1065">
-        <v>0.006364900123841924</v>
+        <v>0.006357516532127243</v>
       </c>
       <c r="I1065">
-        <v>0.0447671834293617</v>
+        <v>0.04046563314127694</v>
       </c>
       <c r="J1065">
         <v>0.7383591714680878</v>
       </c>
       <c r="K1065">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="L1065">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M1065">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1065">
         <v>3.98</v>
@@ -55120,43 +55123,43 @@
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1066" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C1066">
-        <v>1.624740047284429</v>
+        <v>1.639867059587438</v>
       </c>
       <c r="D1066" t="s">
         <v>367</v>
       </c>
       <c r="E1066">
-        <v>1.577058390407579</v>
+        <v>1.602483467872757</v>
       </c>
       <c r="F1066">
         <v>-1</v>
       </c>
       <c r="G1066">
-        <v>0.00647525995271557</v>
+        <v>0.006380132940412562</v>
       </c>
       <c r="H1066">
-        <v>0.006382941609592422</v>
+        <v>0.006357516532127243</v>
       </c>
       <c r="I1066">
-        <v>0.04768165687685055</v>
+        <v>0.03738359171468097</v>
       </c>
       <c r="J1066">
-        <v>0.7439447707716474</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1066">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1066">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1066">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1066">
         <v>3.98</v>
@@ -55165,48 +55168,48 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>493</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1067" t="s">
         <v>222</v>
       </c>
       <c r="C1067">
-        <v>1.629134524361594</v>
+        <v>1.624740047284429</v>
       </c>
       <c r="D1067" t="s">
         <v>367</v>
       </c>
       <c r="E1067">
-        <v>1.577058390407579</v>
+        <v>1.584497838115295</v>
       </c>
       <c r="F1067">
         <v>-1</v>
       </c>
       <c r="G1067">
-        <v>0.006330865475638406</v>
+        <v>0.00647525995271557</v>
       </c>
       <c r="H1067">
-        <v>0.006382941609592422</v>
+        <v>0.006375502161884705</v>
       </c>
       <c r="I1067">
-        <v>0.052076133954015</v>
+        <v>0.04024220916913412</v>
       </c>
       <c r="J1067">
         <v>0.7439447707716474</v>
       </c>
       <c r="K1067">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1067">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1067">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1067">
         <v>3.98</v>
@@ -55215,39 +55218,39 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1068" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1068">
-        <v>1.615003925968209</v>
+        <v>1.629134524361594</v>
       </c>
       <c r="D1068" t="s">
         <v>367</v>
       </c>
       <c r="E1068">
-        <v>1.56261477242953</v>
+        <v>1.584497838115295</v>
       </c>
       <c r="F1068">
         <v>-1</v>
       </c>
       <c r="G1068">
-        <v>0.006344996074031791</v>
+        <v>0.006330865475638406</v>
       </c>
       <c r="H1068">
-        <v>0.006397385227570471</v>
+        <v>0.006375502161884705</v>
       </c>
       <c r="I1068">
-        <v>0.0523891535386789</v>
+        <v>0.04463668624629857</v>
       </c>
       <c r="J1068">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1068">
         <v>3.16</v>
@@ -55256,7 +55259,7 @@
         <v>3.98</v>
       </c>
       <c r="M1068">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1068">
         <v>3.98</v>
@@ -55273,31 +55276,31 @@
         <v>0</v>
       </c>
       <c r="B1069" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1069">
-        <v>1.581010547255576</v>
+        <v>1.615003925968209</v>
       </c>
       <c r="D1069" t="s">
         <v>367</v>
       </c>
       <c r="E1069">
-        <v>1.527868375834023</v>
+        <v>1.57009893722077</v>
       </c>
       <c r="F1069">
         <v>-1</v>
       </c>
       <c r="G1069">
-        <v>0.006378989452744424</v>
+        <v>0.006344996074031791</v>
       </c>
       <c r="H1069">
-        <v>0.006432131624165977</v>
+        <v>0.006389901062779231</v>
       </c>
       <c r="I1069">
-        <v>0.05314217142155364</v>
+        <v>0.04490498874743887</v>
       </c>
       <c r="J1069">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1069">
         <v>3.16</v>
@@ -55306,7 +55309,7 @@
         <v>3.98</v>
       </c>
       <c r="M1069">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N1069">
         <v>3.98</v>
@@ -55326,40 +55329,40 @@
         <v>223</v>
       </c>
       <c r="C1070">
-        <v>1.560901809388644</v>
+        <v>1.581010547255576</v>
       </c>
       <c r="D1070" t="s">
         <v>225</v>
       </c>
       <c r="E1070">
-        <v>1.523807620958687</v>
+        <v>1.527868375834023</v>
       </c>
       <c r="F1070">
         <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.006539098190611355</v>
+        <v>0.006378989452744424</v>
       </c>
       <c r="H1070">
-        <v>0.006456192379041313</v>
+        <v>0.006432131624165977</v>
       </c>
       <c r="I1070">
-        <v>0.03709418842995671</v>
+        <v>0.05314217142155364</v>
       </c>
       <c r="J1070">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1070">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="L1070">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1070">
         <v>3.23</v>
       </c>
       <c r="N1070">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="O1070">
         <v>1</v>
@@ -55370,16 +55373,16 @@
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1071" t="s">
         <v>222</v>
       </c>
       <c r="C1071">
-        <v>1.567254514622121</v>
+        <v>1.560901809388644</v>
       </c>
       <c r="D1071" t="s">
-        <v>225</v>
+        <v>371</v>
       </c>
       <c r="E1071">
         <v>1.523807620958687</v>
@@ -55388,22 +55391,22 @@
         <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.006392745485377879</v>
+        <v>0.006539098190611355</v>
       </c>
       <c r="H1071">
         <v>0.006456192379041313</v>
       </c>
       <c r="I1071">
-        <v>0.04344689366343379</v>
+        <v>0.03709418842995671</v>
       </c>
       <c r="J1071">
         <v>0.7635270523347718</v>
       </c>
       <c r="K1071">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1071">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1071">
         <v>3.23</v>
@@ -55415,101 +55418,101 @@
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1072" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C1072">
-        <v>1.553174199563495</v>
+        <v>1.559078162005382</v>
       </c>
       <c r="D1072" t="s">
         <v>371</v>
       </c>
       <c r="E1072">
-        <v>1.528492149259424</v>
+        <v>1.523807620958687</v>
       </c>
       <c r="F1072">
         <v>-1</v>
       </c>
       <c r="G1072">
-        <v>0.006546825800436505</v>
+        <v>0.006460921837994617</v>
       </c>
       <c r="H1072">
-        <v>0.006491507850740576</v>
+        <v>0.006456192379041313</v>
       </c>
       <c r="I1072">
-        <v>0.024682050304071</v>
+        <v>0.03527054104669514</v>
       </c>
       <c r="J1072">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1072">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1072">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1072">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="N1072">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="O1072">
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>370</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1073" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1073">
-        <v>1.551469073803319</v>
+        <v>1.553174199563495</v>
       </c>
       <c r="D1073" t="s">
         <v>371</v>
       </c>
       <c r="E1073">
-        <v>1.528492149259424</v>
+        <v>1.51615112410739</v>
       </c>
       <c r="F1073">
         <v>-1</v>
       </c>
       <c r="G1073">
-        <v>0.006468530926196681</v>
+        <v>0.006546825800436505</v>
       </c>
       <c r="H1073">
-        <v>0.006491507850740576</v>
+        <v>0.006463848875892611</v>
       </c>
       <c r="I1073">
-        <v>0.02297692454389466</v>
+        <v>0.03702307545610539</v>
       </c>
       <c r="J1073">
         <v>0.7658974847964738</v>
       </c>
       <c r="K1073">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="L1073">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M1073">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="N1073">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="O1073">
         <v>1</v>
@@ -55520,102 +55523,102 @@
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1074" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C1074">
-        <v>1.54817973372066</v>
+        <v>1.551469073803319</v>
       </c>
       <c r="D1074" t="s">
         <v>371</v>
       </c>
       <c r="E1074">
-        <v>1.52352832431133</v>
+        <v>1.51615112410739</v>
       </c>
       <c r="F1074">
         <v>-1</v>
       </c>
       <c r="G1074">
-        <v>0.00655182026627934</v>
+        <v>0.006468530926196681</v>
       </c>
       <c r="H1074">
-        <v>0.006496471675688669</v>
+        <v>0.006463848875892611</v>
       </c>
       <c r="I1074">
-        <v>0.02465140940932953</v>
+        <v>0.03531794969592905</v>
       </c>
       <c r="J1074">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1074">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1074">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1074">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="N1074">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="O1074">
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
       <c r="A1075" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1075" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C1075">
-        <v>1.554922686674014</v>
+        <v>1.50615112410739</v>
       </c>
       <c r="D1075" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E1075">
-        <v>1.52352832431133</v>
+        <v>1.513810098955354</v>
       </c>
       <c r="F1075">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1075">
-        <v>0.006405077313325986</v>
+        <v>0.006453848875892611</v>
       </c>
       <c r="H1075">
-        <v>0.006496471675688669</v>
+        <v>0.006446189901044646</v>
       </c>
       <c r="I1075">
-        <v>0.03139436236268356</v>
+        <v>0.007658974847964295</v>
       </c>
       <c r="J1075">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1075">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="L1075">
         <v>3.98</v>
       </c>
       <c r="M1075">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="N1075">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1075">
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55626,34 +55629,34 @@
         <v>222</v>
       </c>
       <c r="C1076">
-        <v>1.551006173140757</v>
+        <v>1.54817973372066</v>
       </c>
       <c r="D1076" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E1076">
-        <v>1.519512658536726</v>
+        <v>1.52352832431133</v>
       </c>
       <c r="F1076">
         <v>-1</v>
       </c>
       <c r="G1076">
-        <v>0.006408993826859243</v>
+        <v>0.00655182026627934</v>
       </c>
       <c r="H1076">
-        <v>0.006500487341463274</v>
+        <v>0.006496471675688669</v>
       </c>
       <c r="I1076">
-        <v>0.0314935146040316</v>
+        <v>0.02465140940932953</v>
       </c>
       <c r="J1076">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1076">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1076">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1076">
         <v>3.24</v>
@@ -55665,7 +55668,7 @@
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>497</v>
+        <v>369</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
@@ -55673,181 +55676,181 @@
         <v>1</v>
       </c>
       <c r="B1077" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C1077">
-        <v>1.507199347862231</v>
+        <v>1.546551210197337</v>
       </c>
       <c r="D1077" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E1077">
-        <v>1.49719934786223</v>
+        <v>1.52352832431133</v>
       </c>
       <c r="F1077">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1077">
-        <v>0.00647280065213777</v>
+        <v>0.006473448789802663</v>
       </c>
       <c r="H1077">
-        <v>0.006462800652137769</v>
+        <v>0.006496471675688669</v>
       </c>
       <c r="I1077">
-        <v>-0.01000000000000023</v>
+        <v>0.02302288588600643</v>
       </c>
       <c r="J1077">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1077">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="L1077">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="M1077">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="N1077">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="O1077">
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>497</v>
+        <v>369</v>
       </c>
     </row>
     <row r="1078" spans="1:16">
       <c r="A1078" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1078" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C1078">
-        <v>1.551334098382603</v>
+        <v>1.501202619606667</v>
       </c>
       <c r="D1078" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E1078">
-        <v>1.519848885683428</v>
+        <v>1.508876914902002</v>
       </c>
       <c r="F1078">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1078">
-        <v>0.006408665901617397</v>
+        <v>0.006458797380393334</v>
       </c>
       <c r="H1078">
-        <v>0.006500151114316571</v>
+        <v>0.006451123085097999</v>
       </c>
       <c r="I1078">
-        <v>0.03148521269917515</v>
+        <v>0.007674295295335032</v>
       </c>
       <c r="J1078">
-        <v>0.7685651587396826</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1078">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="L1078">
         <v>3.98</v>
       </c>
       <c r="M1078">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="N1078">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1078">
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>223</v>
+        <v>369</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
       <c r="A1079" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1079" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C1079">
-        <v>1.507534537270826</v>
+        <v>1.544139279885719</v>
       </c>
       <c r="D1079" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E1079">
-        <v>1.497534537270826</v>
+        <v>1.519512658536726</v>
       </c>
       <c r="F1079">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1079">
-        <v>0.006472465462729175</v>
+        <v>0.006555860720114281</v>
       </c>
       <c r="H1079">
-        <v>0.006462465462729174</v>
+        <v>0.006500487341463274</v>
       </c>
       <c r="I1079">
-        <v>-0.01000000000000023</v>
+        <v>0.02462662134899274</v>
       </c>
       <c r="J1079">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1079">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="L1079">
-        <v>3.99</v>
+        <v>4.05</v>
       </c>
       <c r="M1079">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="N1079">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="O1079">
         <v>1</v>
       </c>
       <c r="P1079" t="s">
-        <v>223</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1080" spans="1:16">
       <c r="A1080" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1080" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1080">
-        <v>1.554703628836944</v>
+        <v>1.551006173140757</v>
       </c>
       <c r="D1080" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E1080">
-        <v>1.523303720706234</v>
+        <v>1.519512658536726</v>
       </c>
       <c r="F1080">
         <v>-1</v>
       </c>
       <c r="G1080">
-        <v>0.006405296371163056</v>
+        <v>0.006408993826859243</v>
       </c>
       <c r="H1080">
-        <v>0.006496696279293766</v>
+        <v>0.006500487341463274</v>
       </c>
       <c r="I1080">
-        <v>0.03139990813071059</v>
+        <v>0.0314935146040316</v>
       </c>
       <c r="J1080">
-        <v>0.7674988516338783</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1080">
         <v>3.16</v>
@@ -55870,51 +55873,301 @@
     </row>
     <row r="1081" spans="1:16">
       <c r="A1081" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1081" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C1081">
-        <v>1.549132021580153</v>
+        <v>1.49719934786223</v>
       </c>
       <c r="D1081" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E1081">
-        <v>1.517591060101169</v>
+        <v>1.504886037187734</v>
       </c>
       <c r="F1081">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1081">
-        <v>0.006410867978419848</v>
+        <v>0.006462800652137769</v>
       </c>
       <c r="H1081">
-        <v>0.00650240893989883</v>
+        <v>0.006455113962812267</v>
       </c>
       <c r="I1081">
-        <v>0.03154096147898366</v>
+        <v>0.007686689325503426</v>
       </c>
       <c r="J1081">
-        <v>0.7692620184872934</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1081">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="L1081">
         <v>3.98</v>
       </c>
       <c r="M1081">
+        <v>3.22</v>
+      </c>
+      <c r="N1081">
+        <v>3.98</v>
+      </c>
+      <c r="O1081">
+        <v>1</v>
+      </c>
+      <c r="P1081" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:16">
+      <c r="A1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1082">
+        <v>1.551334098382603</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1082">
+        <v>1.519848885683428</v>
+      </c>
+      <c r="F1082">
+        <v>-1</v>
+      </c>
+      <c r="G1082">
+        <v>0.006408665901617397</v>
+      </c>
+      <c r="H1082">
+        <v>0.006500151114316571</v>
+      </c>
+      <c r="I1082">
+        <v>0.03148521269917515</v>
+      </c>
+      <c r="J1082">
+        <v>0.7685651587396826</v>
+      </c>
+      <c r="K1082">
+        <v>3.16</v>
+      </c>
+      <c r="L1082">
+        <v>3.98</v>
+      </c>
+      <c r="M1082">
         <v>3.24</v>
       </c>
-      <c r="N1081">
+      <c r="N1082">
         <v>4.01</v>
       </c>
-      <c r="O1081">
-        <v>1</v>
-      </c>
-      <c r="P1081" t="s">
+      <c r="O1082">
+        <v>1</v>
+      </c>
+      <c r="P1082" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:16">
+      <c r="A1083" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1083">
+        <v>1.497534537270826</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>367</v>
+      </c>
+      <c r="E1083">
+        <v>1.505220188858222</v>
+      </c>
+      <c r="F1083">
+        <v>1</v>
+      </c>
+      <c r="G1083">
+        <v>0.006462465462729174</v>
+      </c>
+      <c r="H1083">
+        <v>0.006454779811141778</v>
+      </c>
+      <c r="I1083">
+        <v>0.007685651587396425</v>
+      </c>
+      <c r="J1083">
+        <v>0.7685651587396826</v>
+      </c>
+      <c r="K1083">
+        <v>3.23</v>
+      </c>
+      <c r="L1083">
+        <v>3.98</v>
+      </c>
+      <c r="M1083">
+        <v>3.22</v>
+      </c>
+      <c r="N1083">
+        <v>3.98</v>
+      </c>
+      <c r="O1083">
+        <v>1</v>
+      </c>
+      <c r="P1083" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:16">
+      <c r="A1084" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1084">
+        <v>1.54632868625525</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1084">
+        <v>1.523303720706234</v>
+      </c>
+      <c r="F1084">
+        <v>-1</v>
+      </c>
+      <c r="G1084">
+        <v>0.006473671313744749</v>
+      </c>
+      <c r="H1084">
+        <v>0.006496696279293766</v>
+      </c>
+      <c r="I1084">
+        <v>0.02302496554901667</v>
+      </c>
+      <c r="J1084">
+        <v>0.7674988516338783</v>
+      </c>
+      <c r="K1084">
+        <v>3.21</v>
+      </c>
+      <c r="L1084">
+        <v>4.01</v>
+      </c>
+      <c r="M1084">
+        <v>3.24</v>
+      </c>
+      <c r="N1084">
+        <v>4.01</v>
+      </c>
+      <c r="O1084">
+        <v>1</v>
+      </c>
+      <c r="P1084" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:16">
+      <c r="A1085" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1085">
+        <v>1.500978709222573</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>367</v>
+      </c>
+      <c r="E1085">
+        <v>1.508653697738912</v>
+      </c>
+      <c r="F1085">
+        <v>1</v>
+      </c>
+      <c r="G1085">
+        <v>0.006459021290777427</v>
+      </c>
+      <c r="H1085">
+        <v>0.006451346302261089</v>
+      </c>
+      <c r="I1085">
+        <v>0.007674988516338743</v>
+      </c>
+      <c r="J1085">
+        <v>0.7674988516338783</v>
+      </c>
+      <c r="K1085">
+        <v>3.23</v>
+      </c>
+      <c r="L1085">
+        <v>3.98</v>
+      </c>
+      <c r="M1085">
+        <v>3.22</v>
+      </c>
+      <c r="N1085">
+        <v>3.98</v>
+      </c>
+      <c r="O1085">
+        <v>1</v>
+      </c>
+      <c r="P1085" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:16">
+      <c r="A1086" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1086">
+        <v>1.495283680286042</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>367</v>
+      </c>
+      <c r="E1086">
+        <v>1.502976300470915</v>
+      </c>
+      <c r="F1086">
+        <v>1</v>
+      </c>
+      <c r="G1086">
+        <v>0.006464716319713958</v>
+      </c>
+      <c r="H1086">
+        <v>0.006457023699529085</v>
+      </c>
+      <c r="I1086">
+        <v>0.007692620184872823</v>
+      </c>
+      <c r="J1086">
+        <v>0.7692620184872934</v>
+      </c>
+      <c r="K1086">
+        <v>3.23</v>
+      </c>
+      <c r="L1086">
+        <v>3.98</v>
+      </c>
+      <c r="M1086">
+        <v>3.22</v>
+      </c>
+      <c r="N1086">
+        <v>3.98</v>
+      </c>
+      <c r="O1086">
+        <v>1</v>
+      </c>
+      <c r="P1086" t="s">
         <v>224</v>
       </c>
     </row>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3270" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3231" uniqueCount="500">
   <si>
     <t>trade_time</t>
   </si>
@@ -682,16 +682,16 @@
     <t>2021-07-12</t>
   </si>
   <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
     <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-08-04</t>
   </si>
   <si>
-    <t>2021-07-29</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
+    <t>2021-08-03</t>
   </si>
   <si>
     <t>2016-07-22</t>
@@ -1117,7 +1117,7 @@
     <t>2021-05-10</t>
   </si>
   <si>
-    <t>2021-08-05</t>
+    <t>2021-08-09</t>
   </si>
   <si>
     <t>2021-07-13</t>
@@ -1129,10 +1129,10 @@
     <t>2021-07-22</t>
   </si>
   <si>
-    <t>2021-08-03</t>
+    <t>2021-08-02</t>
   </si>
   <si>
-    <t>2021-08-02</t>
+    <t>2021-08-06</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1501,9 +1501,6 @@
     <t>2021-07-15</t>
   </si>
   <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
     <t>2021-07-20</t>
   </si>
   <si>
@@ -1514,6 +1511,9 @@
   </si>
   <si>
     <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
   </si>
 </sst>
 </file>
@@ -1871,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1086"/>
+  <dimension ref="A1:P1073"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -53535,7 +53535,7 @@
         <v>367</v>
       </c>
       <c r="E1034">
-        <v>1.781679934087689</v>
+        <v>1.818025772187613</v>
       </c>
       <c r="F1034">
         <v>1</v>
@@ -53544,10 +53544,10 @@
         <v>0.006789674113414224</v>
       </c>
       <c r="H1034">
-        <v>0.006178320065912311</v>
+        <v>0.006241974227812389</v>
       </c>
       <c r="I1034">
-        <v>0.07135404750191165</v>
+        <v>0.1076998856018356</v>
       </c>
       <c r="J1034">
         <v>0.6827080950038233</v>
@@ -53559,10 +53559,10 @@
         <v>4.25</v>
       </c>
       <c r="M1034">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="N1034">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="O1034">
         <v>1</v>
@@ -53732,10 +53732,10 @@
         <v>1.642597950562186</v>
       </c>
       <c r="D1038" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E1038">
-        <v>1.721753420563377</v>
+        <v>1.739790001740127</v>
       </c>
       <c r="F1038">
         <v>1</v>
@@ -53744,10 +53744,10 @@
         <v>0.006857402049437814</v>
       </c>
       <c r="H1038">
-        <v>0.006698246579436623</v>
+        <v>0.006660209998259873</v>
       </c>
       <c r="I1038">
-        <v>0.07915547000119094</v>
+        <v>0.09719205117794161</v>
       </c>
       <c r="J1038">
         <v>0.7009145294187672</v>
@@ -53759,10 +53759,10 @@
         <v>4.25</v>
       </c>
       <c r="M1038">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="N1038">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="O1038">
         <v>1</v>
@@ -53832,10 +53832,10 @@
         <v>1.612528556387221</v>
       </c>
       <c r="D1040" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E1040">
-        <v>1.693058165369526</v>
+        <v>1.711418073365362</v>
       </c>
       <c r="F1040">
         <v>1</v>
@@ -53844,10 +53844,10 @@
         <v>0.006887471443612779</v>
       </c>
       <c r="H1040">
-        <v>0.006726941834630474</v>
+        <v>0.006688581926634639</v>
       </c>
       <c r="I1040">
-        <v>0.08052960898230443</v>
+        <v>0.09888951697814097</v>
       </c>
       <c r="J1040">
         <v>0.7089976998959082</v>
@@ -53859,10 +53859,10 @@
         <v>4.25</v>
       </c>
       <c r="M1040">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="N1040">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="O1040">
         <v>1</v>
@@ -53873,146 +53873,146 @@
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1041" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1041">
-        <v>1.738667498339339</v>
+        <v>1.725336643125503</v>
       </c>
       <c r="D1041" t="s">
-        <v>225</v>
+        <v>368</v>
       </c>
       <c r="E1041">
-        <v>1.689937429336216</v>
+        <v>1.661041642546622</v>
       </c>
       <c r="F1041">
         <v>-1</v>
       </c>
       <c r="G1041">
-        <v>0.006361332501660661</v>
+        <v>0.006954663356874498</v>
       </c>
       <c r="H1041">
-        <v>0.006270062570663784</v>
+        <v>0.007018958357453379</v>
       </c>
       <c r="I1041">
-        <v>0.04873006900312271</v>
+        <v>0.06429500057888093</v>
       </c>
       <c r="J1041">
-        <v>0.7089976998959082</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1041">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="L1041">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="M1041">
-        <v>3.23</v>
+        <v>3.75</v>
       </c>
       <c r="N1041">
-        <v>3.98</v>
+        <v>4.34</v>
       </c>
       <c r="O1041">
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1042" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C1042">
-        <v>1.73956726832893</v>
+        <v>1.592473309406249</v>
       </c>
       <c r="D1042" t="s">
-        <v>225</v>
+        <v>370</v>
       </c>
       <c r="E1042">
-        <v>1.689937429336216</v>
+        <v>1.673919421610802</v>
       </c>
       <c r="F1042">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1042">
-        <v>0.006220432731671071</v>
+        <v>0.006907526690593752</v>
       </c>
       <c r="H1042">
-        <v>0.006270062570663784</v>
+        <v>0.006746080578389198</v>
       </c>
       <c r="I1042">
-        <v>0.04962983899271345</v>
+        <v>0.08144611220455333</v>
       </c>
       <c r="J1042">
-        <v>0.7089976998959082</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1042">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="L1042">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1042">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N1042">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1042">
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1043" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1043">
-        <v>1.725336643125503</v>
+        <v>1.722531090785953</v>
       </c>
       <c r="D1043" t="s">
-        <v>368</v>
+        <v>224</v>
       </c>
       <c r="E1043">
-        <v>1.661041642546622</v>
+        <v>1.67252386811349</v>
       </c>
       <c r="F1043">
         <v>-1</v>
       </c>
       <c r="G1043">
-        <v>0.006954663356874498</v>
+        <v>0.006237468909214047</v>
       </c>
       <c r="H1043">
-        <v>0.007018958357453379</v>
+        <v>0.006287476131886511</v>
       </c>
       <c r="I1043">
-        <v>0.06429500057888093</v>
+        <v>0.05000722267246305</v>
       </c>
       <c r="J1043">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1043">
-        <v>3.66</v>
+        <v>3.16</v>
       </c>
       <c r="L1043">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="M1043">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N1043">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="O1043">
         <v>1</v>
@@ -54023,134 +54023,134 @@
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1044" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1044">
-        <v>1.592473309406249</v>
+        <v>1.706714139491356</v>
       </c>
       <c r="D1044" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E1044">
-        <v>1.673919421610802</v>
+        <v>1.641961208495242</v>
       </c>
       <c r="F1044">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1044">
-        <v>0.006907526690593752</v>
+        <v>0.006973285860508644</v>
       </c>
       <c r="H1044">
-        <v>0.006746080578389198</v>
+        <v>0.007038038791504758</v>
       </c>
       <c r="I1044">
-        <v>0.08144611220455333</v>
+        <v>0.0647529309961139</v>
       </c>
       <c r="J1044">
-        <v>0.7143888953209009</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1044">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="L1044">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="M1044">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N1044">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="O1044">
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1045" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1045">
-        <v>1.721092201253863</v>
+        <v>1.57354551882728</v>
       </c>
       <c r="D1045" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E1045">
-        <v>1.679667757066699</v>
+        <v>1.655856610708829</v>
       </c>
       <c r="F1045">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1045">
-        <v>0.006378907798746137</v>
+        <v>0.00692645448117272</v>
       </c>
       <c r="H1045">
-        <v>0.006280332242933302</v>
+        <v>0.006764143389291171</v>
       </c>
       <c r="I1045">
-        <v>0.04142444418716407</v>
+        <v>0.08231109188154928</v>
       </c>
       <c r="J1045">
-        <v>0.7143888953209009</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1045">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="L1045">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M1045">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="N1045">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1045">
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1046" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C1046">
-        <v>1.722531090785953</v>
+        <v>1.706452645025324</v>
       </c>
       <c r="D1046" t="s">
         <v>367</v>
       </c>
       <c r="E1046">
-        <v>1.679667757066699</v>
+        <v>1.698894484139889</v>
       </c>
       <c r="F1046">
         <v>-1</v>
       </c>
       <c r="G1046">
-        <v>0.006237468909214047</v>
+        <v>0.006253547354974676</v>
       </c>
       <c r="H1046">
-        <v>0.006280332242933302</v>
+        <v>0.006361105515860111</v>
       </c>
       <c r="I1046">
-        <v>0.0428633337192541</v>
+        <v>0.007558160885434706</v>
       </c>
       <c r="J1046">
-        <v>0.7143888953209009</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1046">
         <v>3.16</v>
@@ -54159,16 +54159,16 @@
         <v>3.98</v>
       </c>
       <c r="M1046">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="N1046">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="O1046">
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54176,49 +54176,49 @@
         <v>0</v>
       </c>
       <c r="B1047" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1047">
-        <v>1.706714139491356</v>
+        <v>1.554102912164197</v>
       </c>
       <c r="D1047" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E1047">
-        <v>1.641961208495242</v>
+        <v>1.637302510264221</v>
       </c>
       <c r="F1047">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.006973285860508644</v>
+        <v>0.006945897087835803</v>
       </c>
       <c r="H1047">
-        <v>0.007038038791504758</v>
+        <v>0.00678269748973578</v>
       </c>
       <c r="I1047">
-        <v>0.0647529309961139</v>
+        <v>0.08319959810002331</v>
       </c>
       <c r="J1047">
-        <v>0.7194770110679355</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1047">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1047">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1047">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N1047">
-        <v>4.34</v>
+        <v>4.21</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54226,131 +54226,131 @@
         <v>1</v>
       </c>
       <c r="B1048" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C1048">
-        <v>1.57354551882728</v>
+        <v>1.689936882376039</v>
       </c>
       <c r="D1048" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E1048">
-        <v>1.655856610708829</v>
+        <v>1.681960600917205</v>
       </c>
       <c r="F1048">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.00692645448117272</v>
+        <v>0.006270063117623961</v>
       </c>
       <c r="H1048">
-        <v>0.006764143389291171</v>
+        <v>0.006378039399082797</v>
       </c>
       <c r="I1048">
-        <v>0.08231109188154928</v>
+        <v>0.007976281458834222</v>
       </c>
       <c r="J1048">
-        <v>0.7194770110679355</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1048">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="L1048">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1048">
-        <v>3.55</v>
+        <v>3.24</v>
       </c>
       <c r="N1048">
-        <v>4.21</v>
+        <v>4.03</v>
       </c>
       <c r="O1048">
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1049" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1049">
-        <v>1.70450494391853</v>
+        <v>1.540367267690522</v>
       </c>
       <c r="D1049" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E1049">
-        <v>1.663284024361248</v>
+        <v>1.624194569973482</v>
       </c>
       <c r="F1049">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1049">
-        <v>0.006395495056081469</v>
+        <v>0.006959632732309478</v>
       </c>
       <c r="H1049">
-        <v>0.006296715975638753</v>
+        <v>0.006795805430026517</v>
       </c>
       <c r="I1049">
-        <v>0.0412209195572828</v>
+        <v>0.08382730228296031</v>
       </c>
       <c r="J1049">
-        <v>0.7194770110679355</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1049">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="L1049">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M1049">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="N1049">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1049">
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1050" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C1050">
-        <v>1.706452645025324</v>
+        <v>1.678268969328508</v>
       </c>
       <c r="D1050" t="s">
         <v>367</v>
       </c>
       <c r="E1050">
-        <v>1.663284024361248</v>
+        <v>1.669997297665939</v>
       </c>
       <c r="F1050">
         <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.006253547354974676</v>
+        <v>0.006281731030671493</v>
       </c>
       <c r="H1050">
-        <v>0.006296715975638753</v>
+        <v>0.006390002702334062</v>
       </c>
       <c r="I1050">
-        <v>0.04316862066407623</v>
+        <v>0.008271671662569258</v>
       </c>
       <c r="J1050">
-        <v>0.7194770110679355</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1050">
         <v>3.16</v>
@@ -54359,16 +54359,16 @@
         <v>3.98</v>
       </c>
       <c r="M1050">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="N1050">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="O1050">
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
@@ -54376,49 +54376,49 @@
         <v>0</v>
       </c>
       <c r="B1051" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1051">
+        <v>1.525149479713785</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1051">
+        <v>1.609672218544069</v>
+      </c>
+      <c r="F1051">
+        <v>1</v>
+      </c>
+      <c r="G1051">
+        <v>0.006974850520286215</v>
+      </c>
+      <c r="H1051">
+        <v>0.00681032778145593</v>
+      </c>
+      <c r="I1051">
+        <v>0.08452273883028427</v>
+      </c>
+      <c r="J1051">
+        <v>0.7324866990016706</v>
+      </c>
+      <c r="K1051">
+        <v>3.72</v>
+      </c>
+      <c r="L1051">
+        <v>4.25</v>
+      </c>
+      <c r="M1051">
+        <v>3.55</v>
+      </c>
+      <c r="N1051">
+        <v>4.21</v>
+      </c>
+      <c r="O1051">
+        <v>1</v>
+      </c>
+      <c r="P1051" t="s">
         <v>221</v>
-      </c>
-      <c r="C1051">
-        <v>1.687585123258323</v>
-      </c>
-      <c r="D1051" t="s">
-        <v>368</v>
-      </c>
-      <c r="E1051">
-        <v>1.622361806617135</v>
-      </c>
-      <c r="F1051">
-        <v>-1</v>
-      </c>
-      <c r="G1051">
-        <v>0.006992414876741677</v>
-      </c>
-      <c r="H1051">
-        <v>0.007057638193382865</v>
-      </c>
-      <c r="I1051">
-        <v>0.06522331664118841</v>
-      </c>
-      <c r="J1051">
-        <v>0.7247035182354308</v>
-      </c>
-      <c r="K1051">
-        <v>3.66</v>
-      </c>
-      <c r="L1051">
-        <v>4.34</v>
-      </c>
-      <c r="M1051">
-        <v>3.75</v>
-      </c>
-      <c r="N1051">
-        <v>4.34</v>
-      </c>
-      <c r="O1051">
-        <v>1</v>
-      </c>
-      <c r="P1051" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -54426,349 +54426,349 @@
         <v>1</v>
       </c>
       <c r="B1052" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C1052">
-        <v>1.554102912164197</v>
+        <v>1.665342031154721</v>
       </c>
       <c r="D1052" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E1052">
-        <v>1.637302510264221</v>
+        <v>1.656743095234587</v>
       </c>
       <c r="F1052">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.006945897087835803</v>
+        <v>0.006294657968845279</v>
       </c>
       <c r="H1052">
-        <v>0.00678269748973578</v>
+        <v>0.006403256904765414</v>
       </c>
       <c r="I1052">
-        <v>0.08319959810002331</v>
+        <v>0.008598935920133499</v>
       </c>
       <c r="J1052">
-        <v>0.7247035182354308</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1052">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="L1052">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1052">
-        <v>3.55</v>
+        <v>3.24</v>
       </c>
       <c r="N1052">
-        <v>4.21</v>
+        <v>4.03</v>
       </c>
       <c r="O1052">
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>492</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1053" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1053">
-        <v>1.687466530552496</v>
+        <v>1.515332066574131</v>
       </c>
       <c r="D1053" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E1053">
-        <v>1.646454671281913</v>
+        <v>1.600303450628539</v>
       </c>
       <c r="F1053">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.006412533469447504</v>
+        <v>0.00698466793342587</v>
       </c>
       <c r="H1053">
-        <v>0.006313545328718087</v>
+        <v>0.006819696549371461</v>
       </c>
       <c r="I1053">
-        <v>0.04101185927058326</v>
+        <v>0.08497138405440863</v>
       </c>
       <c r="J1053">
-        <v>0.7247035182354308</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1053">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="L1053">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M1053">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="N1053">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1053">
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>492</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1054" t="s">
         <v>223</v>
       </c>
       <c r="C1054">
-        <v>1.689936882376039</v>
+        <v>1.653489929309588</v>
       </c>
       <c r="D1054" t="s">
         <v>367</v>
       </c>
       <c r="E1054">
-        <v>1.646454671281913</v>
+        <v>1.648192445080695</v>
       </c>
       <c r="F1054">
         <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.006270063117623961</v>
+        <v>0.006446510070690412</v>
       </c>
       <c r="H1054">
-        <v>0.006313545328718087</v>
+        <v>0.006411807554919306</v>
       </c>
       <c r="I1054">
-        <v>0.0434822110941262</v>
+        <v>0.00529748422889309</v>
       </c>
       <c r="J1054">
-        <v>0.7247035182354308</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1054">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1054">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1054">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="N1054">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="O1054">
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>492</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1055" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1055">
-        <v>1.674071021437449</v>
+        <v>1.657002508165122</v>
       </c>
       <c r="D1055" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E1055">
-        <v>1.608515390817058</v>
+        <v>1.648192445080695</v>
       </c>
       <c r="F1055">
         <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.007005928978562551</v>
+        <v>0.006302997491834879</v>
       </c>
       <c r="H1055">
-        <v>0.007071484609182941</v>
+        <v>0.006411807554919306</v>
       </c>
       <c r="I1055">
-        <v>0.06555563062039038</v>
+        <v>0.008810063084427</v>
       </c>
       <c r="J1055">
-        <v>0.7283958957821177</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1055">
-        <v>3.66</v>
+        <v>3.16</v>
       </c>
       <c r="L1055">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="M1055">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="N1055">
-        <v>4.34</v>
+        <v>4.03</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>493</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1056" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1056">
+        <v>1.646785018160843</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>367</v>
+      </c>
+      <c r="E1056">
+        <v>1.637716284443396</v>
+      </c>
+      <c r="F1056">
+        <v>-1</v>
+      </c>
+      <c r="G1056">
+        <v>0.006313214981839158</v>
+      </c>
+      <c r="H1056">
+        <v>0.006422283715556604</v>
+      </c>
+      <c r="I1056">
+        <v>0.009068733717446875</v>
+      </c>
+      <c r="J1056">
+        <v>0.7383591714680878</v>
+      </c>
+      <c r="K1056">
+        <v>3.16</v>
+      </c>
+      <c r="L1056">
+        <v>3.98</v>
+      </c>
+      <c r="M1056">
+        <v>3.24</v>
+      </c>
+      <c r="N1056">
+        <v>4.03</v>
+      </c>
+      <c r="O1056">
+        <v>1</v>
+      </c>
+      <c r="P1056" t="s">
         <v>220</v>
-      </c>
-      <c r="C1056">
-        <v>1.540367267690522</v>
-      </c>
-      <c r="D1056" t="s">
-        <v>370</v>
-      </c>
-      <c r="E1056">
-        <v>1.624194569973482</v>
-      </c>
-      <c r="F1056">
-        <v>1</v>
-      </c>
-      <c r="G1056">
-        <v>0.006959632732309478</v>
-      </c>
-      <c r="H1056">
-        <v>0.006795805430026517</v>
-      </c>
-      <c r="I1056">
-        <v>0.08382730228296031</v>
-      </c>
-      <c r="J1056">
-        <v>0.7283958957821177</v>
-      </c>
-      <c r="K1056">
-        <v>3.72</v>
-      </c>
-      <c r="L1056">
-        <v>4.25</v>
-      </c>
-      <c r="M1056">
-        <v>3.55</v>
-      </c>
-      <c r="N1056">
-        <v>4.21</v>
-      </c>
-      <c r="O1056">
-        <v>1</v>
-      </c>
-      <c r="P1056" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1057" t="s">
         <v>222</v>
       </c>
       <c r="C1057">
-        <v>1.675429379750296</v>
+        <v>1.629134524361594</v>
       </c>
       <c r="D1057" t="s">
         <v>367</v>
       </c>
       <c r="E1057">
-        <v>1.634565215581581</v>
+        <v>1.619618942699862</v>
       </c>
       <c r="F1057">
         <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.006424570620249703</v>
+        <v>0.006330865475638406</v>
       </c>
       <c r="H1057">
-        <v>0.00632543478441842</v>
+        <v>0.006440381057300139</v>
       </c>
       <c r="I1057">
-        <v>0.04086416416871552</v>
+        <v>0.009515581661731609</v>
       </c>
       <c r="J1057">
-        <v>0.7283958957821177</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1057">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="L1057">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1057">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="N1057">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="O1057">
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1058" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1058">
-        <v>1.671849174539402</v>
+        <v>1.581010547255576</v>
       </c>
       <c r="D1058" t="s">
-        <v>367</v>
+        <v>225</v>
       </c>
       <c r="E1058">
-        <v>1.634565215581581</v>
+        <v>1.537868375834023</v>
       </c>
       <c r="F1058">
         <v>-1</v>
       </c>
       <c r="G1058">
-        <v>0.006348150825460598</v>
+        <v>0.006378989452744424</v>
       </c>
       <c r="H1058">
-        <v>0.00632543478441842</v>
+        <v>0.006442131624165978</v>
       </c>
       <c r="I1058">
-        <v>0.03728395895782111</v>
+        <v>0.04314217142155341</v>
       </c>
       <c r="J1058">
-        <v>0.7283958957821177</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1058">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="L1058">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1058">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="N1058">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -54776,81 +54776,81 @@
         <v>0</v>
       </c>
       <c r="B1059" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C1059">
-        <v>1.525149479713785</v>
+        <v>1.567254514622121</v>
       </c>
       <c r="D1059" t="s">
-        <v>370</v>
+        <v>225</v>
       </c>
       <c r="E1059">
-        <v>1.609672218544069</v>
+        <v>1.523807620958687</v>
       </c>
       <c r="F1059">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1059">
-        <v>0.006974850520286215</v>
+        <v>0.006392745485377879</v>
       </c>
       <c r="H1059">
-        <v>0.00681032778145593</v>
+        <v>0.006456192379041313</v>
       </c>
       <c r="I1059">
-        <v>0.08452273883028427</v>
+        <v>0.04344689366343379</v>
       </c>
       <c r="J1059">
-        <v>0.7324866990016706</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1059">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="L1059">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1059">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="N1059">
-        <v>4.21</v>
+        <v>3.99</v>
       </c>
       <c r="O1059">
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>221</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1060" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1060">
-        <v>1.662093361254554</v>
+        <v>1.553174199563495</v>
       </c>
       <c r="D1060" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E1060">
-        <v>1.62139282921462</v>
+        <v>1.528492149259424</v>
       </c>
       <c r="F1060">
         <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.006437906638745446</v>
+        <v>0.006546825800436505</v>
       </c>
       <c r="H1060">
-        <v>0.00633860717078538</v>
+        <v>0.006491507850740576</v>
       </c>
       <c r="I1060">
-        <v>0.04070053203993362</v>
+        <v>0.024682050304071</v>
       </c>
       <c r="J1060">
-        <v>0.7324866990016706</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1060">
         <v>3.26</v>
@@ -54859,207 +54859,207 @@
         <v>4.05</v>
       </c>
       <c r="M1060">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="N1060">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="O1060">
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>221</v>
+        <v>370</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1061" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1061">
-        <v>1.658717696204637</v>
+        <v>1.559763948043143</v>
       </c>
       <c r="D1061" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E1061">
-        <v>1.62139282921462</v>
+        <v>1.528492149259424</v>
       </c>
       <c r="F1061">
         <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.006361282303795362</v>
+        <v>0.006400236051956857</v>
       </c>
       <c r="H1061">
-        <v>0.00633860717078538</v>
+        <v>0.006491507850740576</v>
       </c>
       <c r="I1061">
-        <v>0.03732486699001702</v>
+        <v>0.03127179878371855</v>
       </c>
       <c r="J1061">
-        <v>0.7324866990016706</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1061">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="L1061">
+        <v>3.98</v>
+      </c>
+      <c r="M1061">
+        <v>3.24</v>
+      </c>
+      <c r="N1061">
         <v>4.01</v>
       </c>
-      <c r="M1061">
-        <v>3.22</v>
-      </c>
-      <c r="N1061">
-        <v>3.98</v>
-      </c>
       <c r="O1061">
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>221</v>
+        <v>370</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1062" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C1062">
-        <v>1.515332066574131</v>
+        <v>1.50615112410739</v>
       </c>
       <c r="D1062" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1062">
+        <v>1.552104973195178</v>
+      </c>
+      <c r="F1062">
+        <v>1</v>
+      </c>
+      <c r="G1062">
+        <v>0.006453848875892611</v>
+      </c>
+      <c r="H1062">
+        <v>0.006407895026804822</v>
+      </c>
+      <c r="I1062">
+        <v>0.04595384908778843</v>
+      </c>
+      <c r="J1062">
+        <v>0.7658974847964738</v>
+      </c>
+      <c r="K1062">
+        <v>3.23</v>
+      </c>
+      <c r="L1062">
+        <v>3.98</v>
+      </c>
+      <c r="M1062">
+        <v>3.17</v>
+      </c>
+      <c r="N1062">
+        <v>3.98</v>
+      </c>
+      <c r="O1062">
+        <v>1</v>
+      </c>
+      <c r="P1062" t="s">
         <v>370</v>
-      </c>
-      <c r="E1062">
-        <v>1.600303450628539</v>
-      </c>
-      <c r="F1062">
-        <v>1</v>
-      </c>
-      <c r="G1062">
-        <v>0.00698466793342587</v>
-      </c>
-      <c r="H1062">
-        <v>0.006819696549371461</v>
-      </c>
-      <c r="I1062">
-        <v>0.08497138405440863</v>
-      </c>
-      <c r="J1062">
-        <v>0.7351257885553412</v>
-      </c>
-      <c r="K1062">
-        <v>3.72</v>
-      </c>
-      <c r="L1062">
-        <v>4.25</v>
-      </c>
-      <c r="M1062">
-        <v>3.55</v>
-      </c>
-      <c r="N1062">
-        <v>4.21</v>
-      </c>
-      <c r="O1062">
-        <v>1</v>
-      </c>
-      <c r="P1062" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1063" t="s">
         <v>222</v>
       </c>
       <c r="C1063">
-        <v>1.653489929309588</v>
+        <v>1.554922686674014</v>
       </c>
       <c r="D1063" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E1063">
-        <v>1.612894960851802</v>
+        <v>1.52352832431133</v>
       </c>
       <c r="F1063">
         <v>-1</v>
       </c>
       <c r="G1063">
-        <v>0.006446510070690412</v>
+        <v>0.006405077313325986</v>
       </c>
       <c r="H1063">
-        <v>0.006347105039148198</v>
+        <v>0.006496471675688669</v>
       </c>
       <c r="I1063">
-        <v>0.04059496845778643</v>
+        <v>0.03139436236268356</v>
       </c>
       <c r="J1063">
-        <v>0.7351257885553412</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1063">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="L1063">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1063">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="N1063">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="O1063">
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1064" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C1064">
-        <v>1.650246218737355</v>
+        <v>1.511202619606667</v>
       </c>
       <c r="D1064" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E1064">
-        <v>1.612894960851802</v>
+        <v>1.547248391378679</v>
       </c>
       <c r="F1064">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1064">
-        <v>0.006369753781262645</v>
+        <v>0.006468797380393333</v>
       </c>
       <c r="H1064">
-        <v>0.006347105039148198</v>
+        <v>0.00641275160862132</v>
       </c>
       <c r="I1064">
-        <v>0.03735125788555305</v>
+        <v>0.03604577177201218</v>
       </c>
       <c r="J1064">
-        <v>0.7351257885553412</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1064">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="L1064">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1064">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="N1064">
         <v>3.98</v>
@@ -55068,7 +55068,7 @@
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
@@ -55079,46 +55079,46 @@
         <v>222</v>
       </c>
       <c r="C1065">
-        <v>1.642949101014034</v>
+        <v>1.551006173140757</v>
       </c>
       <c r="D1065" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E1065">
-        <v>1.602483467872757</v>
+        <v>1.519512658536726</v>
       </c>
       <c r="F1065">
         <v>-1</v>
       </c>
       <c r="G1065">
-        <v>0.006457050898985965</v>
+        <v>0.006408993826859243</v>
       </c>
       <c r="H1065">
-        <v>0.006357516532127243</v>
+        <v>0.006500487341463274</v>
       </c>
       <c r="I1065">
-        <v>0.04046563314127694</v>
+        <v>0.0314935146040316</v>
       </c>
       <c r="J1065">
-        <v>0.7383591714680878</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1065">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="L1065">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1065">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="N1065">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="O1065">
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>220</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55126,40 +55126,40 @@
         <v>1</v>
       </c>
       <c r="B1066" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C1066">
-        <v>1.639867059587438</v>
+        <v>1.507199347862231</v>
       </c>
       <c r="D1066" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E1066">
-        <v>1.602483467872757</v>
+        <v>1.543319483815254</v>
       </c>
       <c r="F1066">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1066">
-        <v>0.006380132940412562</v>
+        <v>0.00647280065213777</v>
       </c>
       <c r="H1066">
-        <v>0.006357516532127243</v>
+        <v>0.006416680516184746</v>
       </c>
       <c r="I1066">
-        <v>0.03738359171468097</v>
+        <v>0.03612013595302344</v>
       </c>
       <c r="J1066">
-        <v>0.7383591714680878</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1066">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="L1066">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1066">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="N1066">
         <v>3.98</v>
@@ -55168,7 +55168,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>220</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55179,46 +55179,46 @@
         <v>222</v>
       </c>
       <c r="C1067">
-        <v>1.624740047284429</v>
+        <v>1.551334098382603</v>
       </c>
       <c r="D1067" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E1067">
-        <v>1.584497838115295</v>
+        <v>1.519848885683428</v>
       </c>
       <c r="F1067">
         <v>-1</v>
       </c>
       <c r="G1067">
-        <v>0.00647525995271557</v>
+        <v>0.006408665901617397</v>
       </c>
       <c r="H1067">
-        <v>0.006375502161884705</v>
+        <v>0.006500151114316571</v>
       </c>
       <c r="I1067">
-        <v>0.04024220916913412</v>
+        <v>0.03148521269917515</v>
       </c>
       <c r="J1067">
-        <v>0.7439447707716474</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1067">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="L1067">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1067">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="N1067">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="O1067">
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>494</v>
+        <v>223</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
@@ -55226,40 +55226,40 @@
         <v>1</v>
       </c>
       <c r="B1068" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C1068">
-        <v>1.629134524361594</v>
+        <v>1.507534537270826</v>
       </c>
       <c r="D1068" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E1068">
-        <v>1.584497838115295</v>
+        <v>1.543648446795206</v>
       </c>
       <c r="F1068">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1068">
-        <v>0.006330865475638406</v>
+        <v>0.006472465462729175</v>
       </c>
       <c r="H1068">
-        <v>0.006375502161884705</v>
+        <v>0.006416351553204793</v>
       </c>
       <c r="I1068">
-        <v>0.04463668624629857</v>
+        <v>0.03611390952438054</v>
       </c>
       <c r="J1068">
-        <v>0.7439447707716474</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1068">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="L1068">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1068">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="N1068">
         <v>3.98</v>
@@ -55268,7 +55268,7 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>494</v>
+        <v>223</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55276,31 +55276,31 @@
         <v>0</v>
       </c>
       <c r="B1069" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C1069">
-        <v>1.615003925968209</v>
+        <v>1.554703628836944</v>
       </c>
       <c r="D1069" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E1069">
-        <v>1.57009893722077</v>
+        <v>1.523303720706234</v>
       </c>
       <c r="F1069">
         <v>-1</v>
       </c>
       <c r="G1069">
-        <v>0.006344996074031791</v>
+        <v>0.006405296371163056</v>
       </c>
       <c r="H1069">
-        <v>0.006389901062779231</v>
+        <v>0.006496696279293766</v>
       </c>
       <c r="I1069">
-        <v>0.04490498874743887</v>
+        <v>0.03139990813071059</v>
       </c>
       <c r="J1069">
-        <v>0.7484164791239846</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1069">
         <v>3.16</v>
@@ -55309,57 +55309,57 @@
         <v>3.98</v>
       </c>
       <c r="M1069">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="N1069">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="O1069">
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1070" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C1070">
-        <v>1.581010547255576</v>
+        <v>1.510978709222573</v>
       </c>
       <c r="D1070" t="s">
-        <v>225</v>
+        <v>372</v>
       </c>
       <c r="E1070">
-        <v>1.527868375834023</v>
+        <v>1.547028640320606</v>
       </c>
       <c r="F1070">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1070">
-        <v>0.006378989452744424</v>
+        <v>0.006469021290777427</v>
       </c>
       <c r="H1070">
-        <v>0.006432131624165977</v>
+        <v>0.006412971359679395</v>
       </c>
       <c r="I1070">
-        <v>0.05314217142155364</v>
+        <v>0.03604993109803267</v>
       </c>
       <c r="J1070">
-        <v>0.7591738774507669</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1070">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="L1070">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1070">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="N1070">
         <v>3.98</v>
@@ -55368,7 +55368,7 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
@@ -55379,46 +55379,46 @@
         <v>222</v>
       </c>
       <c r="C1071">
-        <v>1.560901809388644</v>
+        <v>1.549132021580153</v>
       </c>
       <c r="D1071" t="s">
         <v>371</v>
       </c>
       <c r="E1071">
-        <v>1.523807620958687</v>
+        <v>1.517591060101169</v>
       </c>
       <c r="F1071">
         <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.006539098190611355</v>
+        <v>0.006410867978419848</v>
       </c>
       <c r="H1071">
-        <v>0.006456192379041313</v>
+        <v>0.00650240893989883</v>
       </c>
       <c r="I1071">
-        <v>0.03709418842995671</v>
+        <v>0.03154096147898366</v>
       </c>
       <c r="J1071">
-        <v>0.7635270523347718</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1071">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="L1071">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1071">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="N1071">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="O1071">
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -55429,46 +55429,46 @@
         <v>224</v>
       </c>
       <c r="C1072">
-        <v>1.559078162005382</v>
+        <v>1.495283680286042</v>
       </c>
       <c r="D1072" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E1072">
-        <v>1.523807620958687</v>
+        <v>1.54143940139528</v>
       </c>
       <c r="F1072">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1072">
-        <v>0.006460921837994617</v>
+        <v>0.006464716319713958</v>
       </c>
       <c r="H1072">
-        <v>0.006456192379041313</v>
+        <v>0.00641856059860472</v>
       </c>
       <c r="I1072">
-        <v>0.03527054104669514</v>
+        <v>0.04615572110923782</v>
       </c>
       <c r="J1072">
-        <v>0.7635270523347718</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1072">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="L1072">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1072">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="N1072">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="O1072">
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -55476,699 +55476,49 @@
         <v>0</v>
       </c>
       <c r="B1073" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1073">
+        <v>1.495727236198634</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1073">
+        <v>1.541874717879155</v>
+      </c>
+      <c r="F1073">
+        <v>1</v>
+      </c>
+      <c r="G1073">
+        <v>0.006464272763801366</v>
+      </c>
+      <c r="H1073">
+        <v>0.006418125282120845</v>
+      </c>
+      <c r="I1073">
+        <v>0.04614748168052074</v>
+      </c>
+      <c r="J1073">
+        <v>0.7691246946753454</v>
+      </c>
+      <c r="K1073">
+        <v>3.23</v>
+      </c>
+      <c r="L1073">
+        <v>3.98</v>
+      </c>
+      <c r="M1073">
+        <v>3.17</v>
+      </c>
+      <c r="N1073">
+        <v>3.98</v>
+      </c>
+      <c r="O1073">
+        <v>1</v>
+      </c>
+      <c r="P1073" t="s">
         <v>222</v>
-      </c>
-      <c r="C1073">
-        <v>1.553174199563495</v>
-      </c>
-      <c r="D1073" t="s">
-        <v>371</v>
-      </c>
-      <c r="E1073">
-        <v>1.51615112410739</v>
-      </c>
-      <c r="F1073">
-        <v>-1</v>
-      </c>
-      <c r="G1073">
-        <v>0.006546825800436505</v>
-      </c>
-      <c r="H1073">
-        <v>0.006463848875892611</v>
-      </c>
-      <c r="I1073">
-        <v>0.03702307545610539</v>
-      </c>
-      <c r="J1073">
-        <v>0.7658974847964738</v>
-      </c>
-      <c r="K1073">
-        <v>3.26</v>
-      </c>
-      <c r="L1073">
-        <v>4.05</v>
-      </c>
-      <c r="M1073">
-        <v>3.23</v>
-      </c>
-      <c r="N1073">
-        <v>3.99</v>
-      </c>
-      <c r="O1073">
-        <v>1</v>
-      </c>
-      <c r="P1073" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="1074" spans="1:16">
-      <c r="A1074" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1074">
-        <v>1.551469073803319</v>
-      </c>
-      <c r="D1074" t="s">
-        <v>371</v>
-      </c>
-      <c r="E1074">
-        <v>1.51615112410739</v>
-      </c>
-      <c r="F1074">
-        <v>-1</v>
-      </c>
-      <c r="G1074">
-        <v>0.006468530926196681</v>
-      </c>
-      <c r="H1074">
-        <v>0.006463848875892611</v>
-      </c>
-      <c r="I1074">
-        <v>0.03531794969592905</v>
-      </c>
-      <c r="J1074">
-        <v>0.7658974847964738</v>
-      </c>
-      <c r="K1074">
-        <v>3.21</v>
-      </c>
-      <c r="L1074">
-        <v>4.01</v>
-      </c>
-      <c r="M1074">
-        <v>3.23</v>
-      </c>
-      <c r="N1074">
-        <v>3.99</v>
-      </c>
-      <c r="O1074">
-        <v>1</v>
-      </c>
-      <c r="P1074" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="1075" spans="1:16">
-      <c r="A1075" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1075">
-        <v>1.50615112410739</v>
-      </c>
-      <c r="D1075" t="s">
-        <v>367</v>
-      </c>
-      <c r="E1075">
-        <v>1.513810098955354</v>
-      </c>
-      <c r="F1075">
-        <v>1</v>
-      </c>
-      <c r="G1075">
-        <v>0.006453848875892611</v>
-      </c>
-      <c r="H1075">
-        <v>0.006446189901044646</v>
-      </c>
-      <c r="I1075">
-        <v>0.007658974847964295</v>
-      </c>
-      <c r="J1075">
-        <v>0.7658974847964738</v>
-      </c>
-      <c r="K1075">
-        <v>3.23</v>
-      </c>
-      <c r="L1075">
-        <v>3.98</v>
-      </c>
-      <c r="M1075">
-        <v>3.22</v>
-      </c>
-      <c r="N1075">
-        <v>3.98</v>
-      </c>
-      <c r="O1075">
-        <v>1</v>
-      </c>
-      <c r="P1075" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="1076" spans="1:16">
-      <c r="A1076" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>222</v>
-      </c>
-      <c r="C1076">
-        <v>1.54817973372066</v>
-      </c>
-      <c r="D1076" t="s">
-        <v>372</v>
-      </c>
-      <c r="E1076">
-        <v>1.52352832431133</v>
-      </c>
-      <c r="F1076">
-        <v>-1</v>
-      </c>
-      <c r="G1076">
-        <v>0.00655182026627934</v>
-      </c>
-      <c r="H1076">
-        <v>0.006496471675688669</v>
-      </c>
-      <c r="I1076">
-        <v>0.02465140940932953</v>
-      </c>
-      <c r="J1076">
-        <v>0.7674295295335398</v>
-      </c>
-      <c r="K1076">
-        <v>3.26</v>
-      </c>
-      <c r="L1076">
-        <v>4.05</v>
-      </c>
-      <c r="M1076">
-        <v>3.24</v>
-      </c>
-      <c r="N1076">
-        <v>4.01</v>
-      </c>
-      <c r="O1076">
-        <v>1</v>
-      </c>
-      <c r="P1076" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="1077" spans="1:16">
-      <c r="A1077" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1077" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1077">
-        <v>1.546551210197337</v>
-      </c>
-      <c r="D1077" t="s">
-        <v>372</v>
-      </c>
-      <c r="E1077">
-        <v>1.52352832431133</v>
-      </c>
-      <c r="F1077">
-        <v>-1</v>
-      </c>
-      <c r="G1077">
-        <v>0.006473448789802663</v>
-      </c>
-      <c r="H1077">
-        <v>0.006496471675688669</v>
-      </c>
-      <c r="I1077">
-        <v>0.02302288588600643</v>
-      </c>
-      <c r="J1077">
-        <v>0.7674295295335398</v>
-      </c>
-      <c r="K1077">
-        <v>3.21</v>
-      </c>
-      <c r="L1077">
-        <v>4.01</v>
-      </c>
-      <c r="M1077">
-        <v>3.24</v>
-      </c>
-      <c r="N1077">
-        <v>4.01</v>
-      </c>
-      <c r="O1077">
-        <v>1</v>
-      </c>
-      <c r="P1077" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="1078" spans="1:16">
-      <c r="A1078" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1078">
-        <v>1.501202619606667</v>
-      </c>
-      <c r="D1078" t="s">
-        <v>367</v>
-      </c>
-      <c r="E1078">
-        <v>1.508876914902002</v>
-      </c>
-      <c r="F1078">
-        <v>1</v>
-      </c>
-      <c r="G1078">
-        <v>0.006458797380393334</v>
-      </c>
-      <c r="H1078">
-        <v>0.006451123085097999</v>
-      </c>
-      <c r="I1078">
-        <v>0.007674295295335032</v>
-      </c>
-      <c r="J1078">
-        <v>0.7674295295335398</v>
-      </c>
-      <c r="K1078">
-        <v>3.23</v>
-      </c>
-      <c r="L1078">
-        <v>3.98</v>
-      </c>
-      <c r="M1078">
-        <v>3.22</v>
-      </c>
-      <c r="N1078">
-        <v>3.98</v>
-      </c>
-      <c r="O1078">
-        <v>1</v>
-      </c>
-      <c r="P1078" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="1079" spans="1:16">
-      <c r="A1079" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1079" t="s">
-        <v>222</v>
-      </c>
-      <c r="C1079">
-        <v>1.544139279885719</v>
-      </c>
-      <c r="D1079" t="s">
-        <v>372</v>
-      </c>
-      <c r="E1079">
-        <v>1.519512658536726</v>
-      </c>
-      <c r="F1079">
-        <v>-1</v>
-      </c>
-      <c r="G1079">
-        <v>0.006555860720114281</v>
-      </c>
-      <c r="H1079">
-        <v>0.006500487341463274</v>
-      </c>
-      <c r="I1079">
-        <v>0.02462662134899274</v>
-      </c>
-      <c r="J1079">
-        <v>0.7686689325503931</v>
-      </c>
-      <c r="K1079">
-        <v>3.26</v>
-      </c>
-      <c r="L1079">
-        <v>4.05</v>
-      </c>
-      <c r="M1079">
-        <v>3.24</v>
-      </c>
-      <c r="N1079">
-        <v>4.01</v>
-      </c>
-      <c r="O1079">
-        <v>1</v>
-      </c>
-      <c r="P1079" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="1080" spans="1:16">
-      <c r="A1080" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1080" t="s">
-        <v>223</v>
-      </c>
-      <c r="C1080">
-        <v>1.551006173140757</v>
-      </c>
-      <c r="D1080" t="s">
-        <v>372</v>
-      </c>
-      <c r="E1080">
-        <v>1.519512658536726</v>
-      </c>
-      <c r="F1080">
-        <v>-1</v>
-      </c>
-      <c r="G1080">
-        <v>0.006408993826859243</v>
-      </c>
-      <c r="H1080">
-        <v>0.006500487341463274</v>
-      </c>
-      <c r="I1080">
-        <v>0.0314935146040316</v>
-      </c>
-      <c r="J1080">
-        <v>0.7686689325503931</v>
-      </c>
-      <c r="K1080">
-        <v>3.16</v>
-      </c>
-      <c r="L1080">
-        <v>3.98</v>
-      </c>
-      <c r="M1080">
-        <v>3.24</v>
-      </c>
-      <c r="N1080">
-        <v>4.01</v>
-      </c>
-      <c r="O1080">
-        <v>1</v>
-      </c>
-      <c r="P1080" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="1081" spans="1:16">
-      <c r="A1081" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1081" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1081">
-        <v>1.49719934786223</v>
-      </c>
-      <c r="D1081" t="s">
-        <v>367</v>
-      </c>
-      <c r="E1081">
-        <v>1.504886037187734</v>
-      </c>
-      <c r="F1081">
-        <v>1</v>
-      </c>
-      <c r="G1081">
-        <v>0.006462800652137769</v>
-      </c>
-      <c r="H1081">
-        <v>0.006455113962812267</v>
-      </c>
-      <c r="I1081">
-        <v>0.007686689325503426</v>
-      </c>
-      <c r="J1081">
-        <v>0.7686689325503931</v>
-      </c>
-      <c r="K1081">
-        <v>3.23</v>
-      </c>
-      <c r="L1081">
-        <v>3.98</v>
-      </c>
-      <c r="M1081">
-        <v>3.22</v>
-      </c>
-      <c r="N1081">
-        <v>3.98</v>
-      </c>
-      <c r="O1081">
-        <v>1</v>
-      </c>
-      <c r="P1081" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="1082" spans="1:16">
-      <c r="A1082" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1082" t="s">
-        <v>223</v>
-      </c>
-      <c r="C1082">
-        <v>1.551334098382603</v>
-      </c>
-      <c r="D1082" t="s">
-        <v>372</v>
-      </c>
-      <c r="E1082">
-        <v>1.519848885683428</v>
-      </c>
-      <c r="F1082">
-        <v>-1</v>
-      </c>
-      <c r="G1082">
-        <v>0.006408665901617397</v>
-      </c>
-      <c r="H1082">
-        <v>0.006500151114316571</v>
-      </c>
-      <c r="I1082">
-        <v>0.03148521269917515</v>
-      </c>
-      <c r="J1082">
-        <v>0.7685651587396826</v>
-      </c>
-      <c r="K1082">
-        <v>3.16</v>
-      </c>
-      <c r="L1082">
-        <v>3.98</v>
-      </c>
-      <c r="M1082">
-        <v>3.24</v>
-      </c>
-      <c r="N1082">
-        <v>4.01</v>
-      </c>
-      <c r="O1082">
-        <v>1</v>
-      </c>
-      <c r="P1082" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="1083" spans="1:16">
-      <c r="A1083" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1083" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1083">
-        <v>1.497534537270826</v>
-      </c>
-      <c r="D1083" t="s">
-        <v>367</v>
-      </c>
-      <c r="E1083">
-        <v>1.505220188858222</v>
-      </c>
-      <c r="F1083">
-        <v>1</v>
-      </c>
-      <c r="G1083">
-        <v>0.006462465462729174</v>
-      </c>
-      <c r="H1083">
-        <v>0.006454779811141778</v>
-      </c>
-      <c r="I1083">
-        <v>0.007685651587396425</v>
-      </c>
-      <c r="J1083">
-        <v>0.7685651587396826</v>
-      </c>
-      <c r="K1083">
-        <v>3.23</v>
-      </c>
-      <c r="L1083">
-        <v>3.98</v>
-      </c>
-      <c r="M1083">
-        <v>3.22</v>
-      </c>
-      <c r="N1083">
-        <v>3.98</v>
-      </c>
-      <c r="O1083">
-        <v>1</v>
-      </c>
-      <c r="P1083" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="1084" spans="1:16">
-      <c r="A1084" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1084" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1084">
-        <v>1.54632868625525</v>
-      </c>
-      <c r="D1084" t="s">
-        <v>372</v>
-      </c>
-      <c r="E1084">
-        <v>1.523303720706234</v>
-      </c>
-      <c r="F1084">
-        <v>-1</v>
-      </c>
-      <c r="G1084">
-        <v>0.006473671313744749</v>
-      </c>
-      <c r="H1084">
-        <v>0.006496696279293766</v>
-      </c>
-      <c r="I1084">
-        <v>0.02302496554901667</v>
-      </c>
-      <c r="J1084">
-        <v>0.7674988516338783</v>
-      </c>
-      <c r="K1084">
-        <v>3.21</v>
-      </c>
-      <c r="L1084">
-        <v>4.01</v>
-      </c>
-      <c r="M1084">
-        <v>3.24</v>
-      </c>
-      <c r="N1084">
-        <v>4.01</v>
-      </c>
-      <c r="O1084">
-        <v>1</v>
-      </c>
-      <c r="P1084" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="1085" spans="1:16">
-      <c r="A1085" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1085" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1085">
-        <v>1.500978709222573</v>
-      </c>
-      <c r="D1085" t="s">
-        <v>367</v>
-      </c>
-      <c r="E1085">
-        <v>1.508653697738912</v>
-      </c>
-      <c r="F1085">
-        <v>1</v>
-      </c>
-      <c r="G1085">
-        <v>0.006459021290777427</v>
-      </c>
-      <c r="H1085">
-        <v>0.006451346302261089</v>
-      </c>
-      <c r="I1085">
-        <v>0.007674988516338743</v>
-      </c>
-      <c r="J1085">
-        <v>0.7674988516338783</v>
-      </c>
-      <c r="K1085">
-        <v>3.23</v>
-      </c>
-      <c r="L1085">
-        <v>3.98</v>
-      </c>
-      <c r="M1085">
-        <v>3.22</v>
-      </c>
-      <c r="N1085">
-        <v>3.98</v>
-      </c>
-      <c r="O1085">
-        <v>1</v>
-      </c>
-      <c r="P1085" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="1086" spans="1:16">
-      <c r="A1086" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1086" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1086">
-        <v>1.495283680286042</v>
-      </c>
-      <c r="D1086" t="s">
-        <v>367</v>
-      </c>
-      <c r="E1086">
-        <v>1.502976300470915</v>
-      </c>
-      <c r="F1086">
-        <v>1</v>
-      </c>
-      <c r="G1086">
-        <v>0.006464716319713958</v>
-      </c>
-      <c r="H1086">
-        <v>0.006457023699529085</v>
-      </c>
-      <c r="I1086">
-        <v>0.007692620184872823</v>
-      </c>
-      <c r="J1086">
-        <v>0.7692620184872934</v>
-      </c>
-      <c r="K1086">
-        <v>3.23</v>
-      </c>
-      <c r="L1086">
-        <v>3.98</v>
-      </c>
-      <c r="M1086">
-        <v>3.22</v>
-      </c>
-      <c r="N1086">
-        <v>3.98</v>
-      </c>
-      <c r="O1086">
-        <v>1</v>
-      </c>
-      <c r="P1086" t="s">
-        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3231" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="501">
   <si>
     <t>trade_time</t>
   </si>
@@ -688,10 +688,10 @@
     <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-08-04</t>
+    <t>2021-07-29</t>
   </si>
   <si>
-    <t>2021-08-03</t>
+    <t>2021-08-04</t>
   </si>
   <si>
     <t>2016-07-22</t>
@@ -1117,7 +1117,7 @@
     <t>2021-05-10</t>
   </si>
   <si>
-    <t>2021-08-09</t>
+    <t>2021-08-11</t>
   </si>
   <si>
     <t>2021-07-13</t>
@@ -1127,6 +1127,9 @@
   </si>
   <si>
     <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-08-03</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -1501,6 +1504,9 @@
     <t>2021-07-15</t>
   </si>
   <si>
+    <t>2021-07-16</t>
+  </si>
+  <si>
     <t>2021-07-20</t>
   </si>
   <si>
@@ -1511,9 +1517,6 @@
   </si>
   <si>
     <t>2021-07-28</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
   </si>
 </sst>
 </file>
@@ -1871,7 +1874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1073"/>
+  <dimension ref="A1:P1079"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1968,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2018,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2068,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2118,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2168,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2218,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2268,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2318,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2368,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2418,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2468,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2518,7 +2521,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2568,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2618,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2668,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2718,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2768,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2818,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2868,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2918,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2968,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3018,7 +3021,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3068,7 +3071,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3118,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3168,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3218,7 +3221,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3268,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3318,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3368,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3418,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3468,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3518,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3818,7 +3821,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3868,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3918,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3968,7 +3971,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4018,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4068,7 +4071,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4118,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4168,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4218,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4268,7 +4271,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4318,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4368,7 +4371,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4418,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4468,7 +4471,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4518,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4568,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4618,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4668,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4718,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4768,7 +4771,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4818,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4868,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4918,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4968,7 +4971,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5018,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5068,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5118,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5168,7 +5171,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5218,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5268,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5318,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5368,7 +5371,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5418,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5468,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5518,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5568,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5618,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5668,7 +5671,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5718,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5768,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6018,7 +6021,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6068,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6118,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6168,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6818,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6868,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6918,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6968,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7018,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7068,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7118,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7168,7 +7171,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7218,7 +7221,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7268,7 +7271,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7318,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7368,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7618,7 +7621,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7668,7 +7671,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7718,7 +7721,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7768,7 +7771,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8068,7 +8071,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8118,7 +8121,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8168,7 +8171,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8218,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8268,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8318,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8368,7 +8371,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8818,7 +8821,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8868,7 +8871,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8918,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8968,7 +8971,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9018,7 +9021,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9068,7 +9071,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9118,7 +9121,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9168,7 +9171,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9218,7 +9221,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9268,7 +9271,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9318,7 +9321,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9368,7 +9371,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9418,7 +9421,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9468,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9518,7 +9521,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9568,7 +9571,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9618,7 +9621,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9668,7 +9671,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9718,7 +9721,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9768,7 +9771,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9818,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9868,7 +9871,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9918,7 +9921,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9968,7 +9971,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10018,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10068,7 +10071,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10118,7 +10121,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10168,7 +10171,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10218,7 +10221,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10268,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10318,7 +10321,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10368,7 +10371,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10418,7 +10421,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10468,7 +10471,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10518,7 +10521,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10568,7 +10571,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10618,7 +10621,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10668,7 +10671,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10718,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10768,7 +10771,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10818,7 +10821,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10868,7 +10871,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10918,7 +10921,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10968,7 +10971,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11318,7 +11321,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11368,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11418,7 +11421,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11468,7 +11471,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11518,7 +11521,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11568,7 +11571,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11618,7 +11621,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -12018,7 +12021,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12068,7 +12071,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12118,7 +12121,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12168,7 +12171,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12218,7 +12221,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12268,7 +12271,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12318,7 +12321,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12368,7 +12371,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12418,7 +12421,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12468,7 +12471,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12518,7 +12521,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12568,7 +12571,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12618,7 +12621,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12668,7 +12671,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12718,7 +12721,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12768,7 +12771,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12818,7 +12821,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12868,7 +12871,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12918,7 +12921,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12968,7 +12971,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -13018,7 +13021,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -13968,7 +13971,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14018,7 +14021,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14068,7 +14071,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14118,7 +14121,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14168,7 +14171,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14218,7 +14221,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14268,7 +14271,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14318,7 +14321,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14368,7 +14371,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14418,7 +14421,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14468,7 +14471,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14518,7 +14521,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14568,7 +14571,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14618,7 +14621,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14668,7 +14671,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14718,7 +14721,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14768,7 +14771,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14818,7 +14821,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14868,7 +14871,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14918,7 +14921,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14968,7 +14971,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15018,7 +15021,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15068,7 +15071,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15118,7 +15121,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15168,7 +15171,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15218,7 +15221,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15268,7 +15271,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15318,7 +15321,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15368,7 +15371,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15418,7 +15421,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15468,7 +15471,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15518,7 +15521,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15568,7 +15571,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15618,7 +15621,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15668,7 +15671,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15718,7 +15721,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15768,7 +15771,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15818,7 +15821,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15868,7 +15871,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15918,7 +15921,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15968,7 +15971,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -16018,7 +16021,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -16068,7 +16071,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16118,7 +16121,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16168,7 +16171,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16218,7 +16221,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16268,7 +16271,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16318,7 +16321,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16368,7 +16371,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16418,7 +16421,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16468,7 +16471,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16518,7 +16521,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16568,7 +16571,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16618,7 +16621,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16668,7 +16671,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16718,7 +16721,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16768,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16818,7 +16821,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16868,7 +16871,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16918,7 +16921,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16968,7 +16971,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17018,7 +17021,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17068,7 +17071,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17118,7 +17121,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17168,7 +17171,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17218,7 +17221,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17268,7 +17271,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17318,7 +17321,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17368,7 +17371,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17418,7 +17421,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17468,7 +17471,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17518,7 +17521,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17568,7 +17571,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17618,7 +17621,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17668,7 +17671,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17718,7 +17721,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17768,7 +17771,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17818,7 +17821,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17868,7 +17871,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17918,7 +17921,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17968,7 +17971,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18018,7 +18021,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -18068,7 +18071,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18568,7 +18571,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18618,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18668,7 +18671,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18718,7 +18721,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18768,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18818,7 +18821,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18868,7 +18871,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18918,7 +18921,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18968,7 +18971,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19018,7 +19021,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19068,7 +19071,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19118,7 +19121,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19168,7 +19171,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19218,7 +19221,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19268,7 +19271,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19318,7 +19321,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19368,7 +19371,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19418,7 +19421,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19468,7 +19471,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19518,7 +19521,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19568,7 +19571,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19618,7 +19621,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19668,7 +19671,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19718,7 +19721,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19768,7 +19771,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19818,7 +19821,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19868,7 +19871,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19918,7 +19921,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19968,7 +19971,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20018,7 +20021,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20068,7 +20071,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20118,7 +20121,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20168,7 +20171,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20218,7 +20221,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20268,7 +20271,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20318,7 +20321,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20368,7 +20371,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20418,7 +20421,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20468,7 +20471,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20518,7 +20521,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20568,7 +20571,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20618,7 +20621,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20668,7 +20671,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20718,7 +20721,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20768,7 +20771,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20818,7 +20821,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20868,7 +20871,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20918,7 +20921,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20968,7 +20971,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21018,7 +21021,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21068,7 +21071,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21118,7 +21121,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21168,7 +21171,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21218,7 +21221,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21268,7 +21271,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21318,7 +21321,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21368,7 +21371,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21418,7 +21421,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21468,7 +21471,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21518,7 +21521,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21568,7 +21571,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21618,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21668,7 +21671,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21718,7 +21721,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21768,7 +21771,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21818,7 +21821,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21868,7 +21871,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21918,7 +21921,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21968,7 +21971,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22018,7 +22021,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22068,7 +22071,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22118,7 +22121,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22168,7 +22171,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22218,7 +22221,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22268,7 +22271,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22318,7 +22321,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22368,7 +22371,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22418,7 +22421,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22468,7 +22471,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22518,7 +22521,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22568,7 +22571,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22618,7 +22621,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22668,7 +22671,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22718,7 +22721,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22768,7 +22771,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22818,7 +22821,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22868,7 +22871,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22918,7 +22921,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22968,7 +22971,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23018,7 +23021,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23068,7 +23071,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23118,7 +23121,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23168,7 +23171,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23218,7 +23221,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23268,7 +23271,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23318,7 +23321,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23368,7 +23371,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23418,7 +23421,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23468,7 +23471,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23518,7 +23521,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23568,7 +23571,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23618,7 +23621,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23668,7 +23671,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23718,7 +23721,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23768,7 +23771,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23818,7 +23821,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23868,7 +23871,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23918,7 +23921,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23968,7 +23971,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24018,7 +24021,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24068,7 +24071,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24118,7 +24121,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24168,7 +24171,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24218,7 +24221,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24268,7 +24271,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24318,7 +24321,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24368,7 +24371,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24418,7 +24421,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24468,7 +24471,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24518,7 +24521,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24568,7 +24571,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24618,7 +24621,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24668,7 +24671,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24718,7 +24721,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24768,7 +24771,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24818,7 +24821,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24868,7 +24871,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24918,7 +24921,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24968,7 +24971,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25318,7 +25321,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25368,7 +25371,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25418,7 +25421,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25468,7 +25471,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25518,7 +25521,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25568,7 +25571,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25618,7 +25621,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25668,7 +25671,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25718,7 +25721,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25768,7 +25771,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25818,7 +25821,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25868,7 +25871,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25918,7 +25921,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25968,7 +25971,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26018,7 +26021,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26068,7 +26071,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26118,7 +26121,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26168,7 +26171,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26218,7 +26221,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26268,7 +26271,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26918,7 +26921,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26968,7 +26971,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27018,7 +27021,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27068,7 +27071,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27118,7 +27121,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27168,7 +27171,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27218,7 +27221,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27268,7 +27271,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27318,7 +27321,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27368,7 +27371,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27418,7 +27421,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27468,7 +27471,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27518,7 +27521,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28168,7 +28171,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28218,7 +28221,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28268,7 +28271,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28318,7 +28321,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28368,7 +28371,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28418,7 +28421,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28468,7 +28471,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28518,7 +28521,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28568,7 +28571,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28618,7 +28621,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28668,7 +28671,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28718,7 +28721,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -32268,7 +32271,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32318,7 +32321,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32368,7 +32371,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32418,7 +32421,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32468,7 +32471,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32518,7 +32521,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32568,7 +32571,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32618,7 +32621,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32668,7 +32671,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33518,7 +33521,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33568,7 +33571,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33618,7 +33621,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33668,7 +33671,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33718,7 +33721,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33768,7 +33771,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33818,7 +33821,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33868,7 +33871,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33918,7 +33921,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33968,7 +33971,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34018,7 +34021,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34068,7 +34071,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34118,7 +34121,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34168,7 +34171,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34218,7 +34221,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34268,7 +34271,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -35118,7 +35121,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35168,7 +35171,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35218,7 +35221,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35268,7 +35271,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35318,7 +35321,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35368,7 +35371,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35418,7 +35421,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35468,7 +35471,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35518,7 +35521,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35568,7 +35571,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35618,7 +35621,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35668,7 +35671,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35718,7 +35721,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35768,7 +35771,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35818,7 +35821,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36218,7 +36221,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36268,7 +36271,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36318,7 +36321,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36368,7 +36371,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36418,7 +36421,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36468,7 +36471,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36518,7 +36521,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37268,7 +37271,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37318,7 +37321,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37368,7 +37371,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37418,7 +37421,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37468,7 +37471,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37518,7 +37521,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37568,7 +37571,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37618,7 +37621,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37668,7 +37671,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37718,7 +37721,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37768,7 +37771,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37818,7 +37821,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37868,7 +37871,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37918,7 +37921,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37968,7 +37971,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38018,7 +38021,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38068,7 +38071,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38118,7 +38121,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38168,7 +38171,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38218,7 +38221,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38668,7 +38671,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38718,7 +38721,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38768,7 +38771,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38818,7 +38821,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38868,7 +38871,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38918,7 +38921,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38968,7 +38971,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39318,7 +39321,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39368,7 +39371,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39418,7 +39421,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39468,7 +39471,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39518,7 +39521,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39568,7 +39571,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39618,7 +39621,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39668,7 +39671,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39718,7 +39721,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39768,7 +39771,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39818,7 +39821,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -41918,7 +41921,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41968,7 +41971,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42018,7 +42021,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42068,7 +42071,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42118,7 +42121,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42168,7 +42171,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42218,7 +42221,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42268,7 +42271,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42318,7 +42321,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42368,7 +42371,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42418,7 +42421,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42468,7 +42471,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42518,7 +42521,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42568,7 +42571,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42618,7 +42621,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42668,7 +42671,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42718,7 +42721,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42768,7 +42771,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -42818,7 +42821,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -42868,7 +42871,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -42918,7 +42921,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42968,7 +42971,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -43018,7 +43021,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -44668,7 +44671,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44718,7 +44721,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44768,7 +44771,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44818,7 +44821,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44868,7 +44871,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44918,7 +44921,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44968,7 +44971,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45018,7 +45021,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45068,7 +45071,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45118,7 +45121,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45168,7 +45171,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45218,7 +45221,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45468,7 +45471,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45518,7 +45521,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45568,7 +45571,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45618,7 +45621,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45668,7 +45671,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45718,7 +45721,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45768,7 +45771,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -45818,7 +45821,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -45868,7 +45871,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -45918,7 +45921,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -45968,7 +45971,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46018,7 +46021,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46068,7 +46071,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46118,7 +46121,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46518,7 +46521,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46568,7 +46571,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46618,7 +46621,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -48768,7 +48771,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -48818,7 +48821,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -48868,7 +48871,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -48918,7 +48921,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -48968,7 +48971,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49018,7 +49021,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49068,7 +49071,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49118,7 +49121,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49168,7 +49171,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49218,7 +49221,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49268,7 +49271,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49318,7 +49321,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49368,7 +49371,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49418,7 +49421,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49468,7 +49471,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49518,7 +49521,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49568,7 +49571,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49618,7 +49621,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49668,7 +49671,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49718,7 +49721,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -49768,7 +49771,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -49818,7 +49821,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -49868,7 +49871,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -49918,7 +49921,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -49968,7 +49971,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -50018,7 +50021,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50068,7 +50071,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50118,7 +50121,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50168,7 +50171,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50218,7 +50221,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50268,7 +50271,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -50318,7 +50321,7 @@
         <v>1</v>
       </c>
       <c r="P969" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="970" spans="1:16">
@@ -50368,7 +50371,7 @@
         <v>1</v>
       </c>
       <c r="P970" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="971" spans="1:16">
@@ -50418,7 +50421,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -50468,7 +50471,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -50518,7 +50521,7 @@
         <v>1</v>
       </c>
       <c r="P973" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="974" spans="1:16">
@@ -50568,7 +50571,7 @@
         <v>1</v>
       </c>
       <c r="P974" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="975" spans="1:16">
@@ -50618,7 +50621,7 @@
         <v>1</v>
       </c>
       <c r="P975" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="976" spans="1:16">
@@ -50668,7 +50671,7 @@
         <v>1</v>
       </c>
       <c r="P976" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="977" spans="1:16">
@@ -50718,7 +50721,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50768,7 +50771,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50818,7 +50821,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50868,7 +50871,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50918,7 +50921,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50968,7 +50971,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51018,7 +51021,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51068,7 +51071,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51118,7 +51121,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51168,7 +51171,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51218,7 +51221,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51268,7 +51271,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51318,7 +51321,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51368,7 +51371,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51418,7 +51421,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51468,7 +51471,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51518,7 +51521,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51568,7 +51571,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51618,7 +51621,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51668,7 +51671,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51718,7 +51721,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51768,7 +51771,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51818,7 +51821,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51868,7 +51871,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51918,7 +51921,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -52118,7 +52121,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52168,7 +52171,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52218,7 +52221,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52268,7 +52271,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52518,7 +52521,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52568,7 +52571,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -52618,7 +52621,7 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -52668,7 +52671,7 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -52718,7 +52721,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52768,7 +52771,7 @@
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
@@ -52818,7 +52821,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52868,7 +52871,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52918,7 +52921,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52968,7 +52971,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -53018,7 +53021,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -53068,7 +53071,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53118,7 +53121,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53168,7 +53171,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53218,7 +53221,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53268,7 +53271,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53318,7 +53321,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53368,7 +53371,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53418,7 +53421,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53468,7 +53471,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53518,7 +53521,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53535,7 +53538,7 @@
         <v>367</v>
       </c>
       <c r="E1034">
-        <v>1.818025772187613</v>
+        <v>1.752927881737192</v>
       </c>
       <c r="F1034">
         <v>1</v>
@@ -53544,10 +53547,10 @@
         <v>0.006789674113414224</v>
       </c>
       <c r="H1034">
-        <v>0.006241974227812389</v>
+        <v>0.006327072118262809</v>
       </c>
       <c r="I1034">
-        <v>0.1076998856018356</v>
+        <v>0.04260199515141494</v>
       </c>
       <c r="J1034">
         <v>0.6827080950038233</v>
@@ -53559,16 +53562,16 @@
         <v>4.25</v>
       </c>
       <c r="M1034">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N1034">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1034">
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53618,7 +53621,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -53668,7 +53671,7 @@
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
@@ -53718,7 +53721,7 @@
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
@@ -53768,7 +53771,7 @@
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
@@ -53818,7 +53821,7 @@
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
@@ -53832,10 +53835,10 @@
         <v>1.612528556387221</v>
       </c>
       <c r="D1040" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E1040">
-        <v>1.711418073365362</v>
+        <v>1.693058165369526</v>
       </c>
       <c r="F1040">
         <v>1</v>
@@ -53844,10 +53847,10 @@
         <v>0.006887471443612779</v>
       </c>
       <c r="H1040">
-        <v>0.006688581926634639</v>
+        <v>0.006726941834630474</v>
       </c>
       <c r="I1040">
-        <v>0.09888951697814097</v>
+        <v>0.08052960898230443</v>
       </c>
       <c r="J1040">
         <v>0.7089976998959082</v>
@@ -53859,60 +53862,60 @@
         <v>4.25</v>
       </c>
       <c r="M1040">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="N1040">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="O1040">
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1041" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1041">
-        <v>1.725336643125503</v>
+        <v>1.73956726832893</v>
       </c>
       <c r="D1041" t="s">
-        <v>368</v>
+        <v>225</v>
       </c>
       <c r="E1041">
-        <v>1.661041642546622</v>
+        <v>1.689937429336216</v>
       </c>
       <c r="F1041">
         <v>-1</v>
       </c>
       <c r="G1041">
-        <v>0.006954663356874498</v>
+        <v>0.006220432731671071</v>
       </c>
       <c r="H1041">
-        <v>0.007018958357453379</v>
+        <v>0.006270062570663784</v>
       </c>
       <c r="I1041">
-        <v>0.06429500057888093</v>
+        <v>0.04962983899271345</v>
       </c>
       <c r="J1041">
-        <v>0.7143888953209009</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1041">
-        <v>3.66</v>
+        <v>3.16</v>
       </c>
       <c r="L1041">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="M1041">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N1041">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="O1041">
         <v>1</v>
@@ -53923,146 +53926,146 @@
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1042" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1042">
-        <v>1.592473309406249</v>
+        <v>1.725336643125503</v>
       </c>
       <c r="D1042" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E1042">
-        <v>1.673919421610802</v>
+        <v>1.661041642546622</v>
       </c>
       <c r="F1042">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1042">
-        <v>0.006907526690593752</v>
+        <v>0.006954663356874498</v>
       </c>
       <c r="H1042">
-        <v>0.006746080578389198</v>
+        <v>0.007018958357453379</v>
       </c>
       <c r="I1042">
-        <v>0.08144611220455333</v>
+        <v>0.06429500057888093</v>
       </c>
       <c r="J1042">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1042">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="L1042">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="M1042">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N1042">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="O1042">
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1043" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1043">
-        <v>1.722531090785953</v>
+        <v>1.592473309406249</v>
       </c>
       <c r="D1043" t="s">
-        <v>224</v>
+        <v>370</v>
       </c>
       <c r="E1043">
-        <v>1.67252386811349</v>
+        <v>1.673919421610802</v>
       </c>
       <c r="F1043">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1043">
-        <v>0.006237468909214047</v>
+        <v>0.006907526690593752</v>
       </c>
       <c r="H1043">
-        <v>0.006287476131886511</v>
+        <v>0.006746080578389198</v>
       </c>
       <c r="I1043">
-        <v>0.05000722267246305</v>
+        <v>0.08144611220455333</v>
       </c>
       <c r="J1043">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1043">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="L1043">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1043">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N1043">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1043">
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1044" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1044">
-        <v>1.706714139491356</v>
+        <v>1.721092201253863</v>
       </c>
       <c r="D1044" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E1044">
-        <v>1.641961208495242</v>
+        <v>1.646797200674982</v>
       </c>
       <c r="F1044">
         <v>-1</v>
       </c>
       <c r="G1044">
-        <v>0.006973285860508644</v>
+        <v>0.006378907798746137</v>
       </c>
       <c r="H1044">
-        <v>0.007038038791504758</v>
+        <v>0.006433202799325018</v>
       </c>
       <c r="I1044">
-        <v>0.0647529309961139</v>
+        <v>0.07429500057888117</v>
       </c>
       <c r="J1044">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1044">
-        <v>3.66</v>
+        <v>3.26</v>
       </c>
       <c r="L1044">
-        <v>4.34</v>
+        <v>4.05</v>
       </c>
       <c r="M1044">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1044">
-        <v>4.34</v>
+        <v>4.04</v>
       </c>
       <c r="O1044">
         <v>1</v>
@@ -54073,46 +54076,46 @@
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1045" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C1045">
-        <v>1.57354551882728</v>
+        <v>1.722531090785953</v>
       </c>
       <c r="D1045" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E1045">
-        <v>1.655856610708829</v>
+        <v>1.646797200674982</v>
       </c>
       <c r="F1045">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1045">
-        <v>0.00692645448117272</v>
+        <v>0.006237468909214047</v>
       </c>
       <c r="H1045">
-        <v>0.006764143389291171</v>
+        <v>0.006433202799325018</v>
       </c>
       <c r="I1045">
-        <v>0.08231109188154928</v>
+        <v>0.0757338901109712</v>
       </c>
       <c r="J1045">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1045">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="L1045">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1045">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1045">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1045">
         <v>1</v>
@@ -54123,84 +54126,84 @@
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1046" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1046">
-        <v>1.706452645025324</v>
+        <v>1.706714139491356</v>
       </c>
       <c r="D1046" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E1046">
-        <v>1.698894484139889</v>
+        <v>1.641961208495242</v>
       </c>
       <c r="F1046">
         <v>-1</v>
       </c>
       <c r="G1046">
-        <v>0.006253547354974676</v>
+        <v>0.006973285860508644</v>
       </c>
       <c r="H1046">
-        <v>0.006361105515860111</v>
+        <v>0.007038038791504758</v>
       </c>
       <c r="I1046">
-        <v>0.007558160885434706</v>
+        <v>0.0647529309961139</v>
       </c>
       <c r="J1046">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1046">
-        <v>3.16</v>
+        <v>3.66</v>
       </c>
       <c r="L1046">
-        <v>3.98</v>
+        <v>4.34</v>
       </c>
       <c r="M1046">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="N1046">
-        <v>4.03</v>
+        <v>4.34</v>
       </c>
       <c r="O1046">
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1047" t="s">
         <v>220</v>
       </c>
       <c r="C1047">
-        <v>1.554102912164197</v>
+        <v>1.57354551882728</v>
       </c>
       <c r="D1047" t="s">
         <v>370</v>
       </c>
       <c r="E1047">
-        <v>1.637302510264221</v>
+        <v>1.655856610708829</v>
       </c>
       <c r="F1047">
         <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.006945897087835803</v>
+        <v>0.00692645448117272</v>
       </c>
       <c r="H1047">
-        <v>0.00678269748973578</v>
+        <v>0.006764143389291171</v>
       </c>
       <c r="I1047">
-        <v>0.08319959810002331</v>
+        <v>0.08231109188154928</v>
       </c>
       <c r="J1047">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1047">
         <v>3.72</v>
@@ -54223,46 +54226,46 @@
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1048" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1048">
-        <v>1.689936882376039</v>
+        <v>1.70450494391853</v>
       </c>
       <c r="D1048" t="s">
         <v>367</v>
       </c>
       <c r="E1048">
-        <v>1.681960600917205</v>
+        <v>1.629752012922416</v>
       </c>
       <c r="F1048">
         <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.006270063117623961</v>
+        <v>0.006395495056081469</v>
       </c>
       <c r="H1048">
-        <v>0.006378039399082797</v>
+        <v>0.006450247987077585</v>
       </c>
       <c r="I1048">
-        <v>0.007976281458834222</v>
+        <v>0.07475293099611457</v>
       </c>
       <c r="J1048">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1048">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1048">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1048">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N1048">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1048">
         <v>1</v>
@@ -54273,96 +54276,96 @@
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1049" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C1049">
-        <v>1.540367267690522</v>
+        <v>1.706452645025324</v>
       </c>
       <c r="D1049" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E1049">
-        <v>1.624194569973482</v>
+        <v>1.629752012922416</v>
       </c>
       <c r="F1049">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.006959632732309478</v>
+        <v>0.006253547354974676</v>
       </c>
       <c r="H1049">
-        <v>0.006795805430026517</v>
+        <v>0.006450247987077585</v>
       </c>
       <c r="I1049">
-        <v>0.08382730228296031</v>
+        <v>0.07670063210290801</v>
       </c>
       <c r="J1049">
-        <v>0.7283958957821177</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1049">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="L1049">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1049">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1049">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1049">
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1050" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1050">
-        <v>1.678268969328508</v>
+        <v>1.687585123258323</v>
       </c>
       <c r="D1050" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E1050">
-        <v>1.669997297665939</v>
+        <v>1.622361806617135</v>
       </c>
       <c r="F1050">
         <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.006281731030671493</v>
+        <v>0.006992414876741677</v>
       </c>
       <c r="H1050">
-        <v>0.006390002702334062</v>
+        <v>0.007057638193382865</v>
       </c>
       <c r="I1050">
-        <v>0.008271671662569258</v>
+        <v>0.06522331664118841</v>
       </c>
       <c r="J1050">
-        <v>0.7283958957821177</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1050">
-        <v>3.16</v>
+        <v>3.66</v>
       </c>
       <c r="L1050">
-        <v>3.98</v>
+        <v>4.34</v>
       </c>
       <c r="M1050">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="N1050">
-        <v>4.03</v>
+        <v>4.34</v>
       </c>
       <c r="O1050">
         <v>1</v>
@@ -54373,34 +54376,34 @@
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1051" t="s">
         <v>220</v>
       </c>
       <c r="C1051">
-        <v>1.525149479713785</v>
+        <v>1.554102912164197</v>
       </c>
       <c r="D1051" t="s">
         <v>370</v>
       </c>
       <c r="E1051">
-        <v>1.609672218544069</v>
+        <v>1.637302510264221</v>
       </c>
       <c r="F1051">
         <v>1</v>
       </c>
       <c r="G1051">
-        <v>0.006974850520286215</v>
+        <v>0.006945897087835803</v>
       </c>
       <c r="H1051">
-        <v>0.00681032778145593</v>
+        <v>0.00678269748973578</v>
       </c>
       <c r="I1051">
-        <v>0.08452273883028427</v>
+        <v>0.08319959810002331</v>
       </c>
       <c r="J1051">
-        <v>0.7324866990016706</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1051">
         <v>3.72</v>
@@ -54418,289 +54421,289 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>221</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1052" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1052">
-        <v>1.665342031154721</v>
+        <v>1.687466530552496</v>
       </c>
       <c r="D1052" t="s">
         <v>367</v>
       </c>
       <c r="E1052">
-        <v>1.656743095234587</v>
+        <v>1.612243213911307</v>
       </c>
       <c r="F1052">
         <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.006294657968845279</v>
+        <v>0.006412533469447504</v>
       </c>
       <c r="H1052">
-        <v>0.006403256904765414</v>
+        <v>0.006467756786088693</v>
       </c>
       <c r="I1052">
-        <v>0.008598935920133499</v>
+        <v>0.07522331664118909</v>
       </c>
       <c r="J1052">
-        <v>0.7324866990016706</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1052">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1052">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1052">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N1052">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1052">
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>221</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1053" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C1053">
-        <v>1.515332066574131</v>
+        <v>1.689936882376039</v>
       </c>
       <c r="D1053" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E1053">
-        <v>1.600303450628539</v>
+        <v>1.612243213911307</v>
       </c>
       <c r="F1053">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1053">
-        <v>0.00698466793342587</v>
+        <v>0.006270063117623961</v>
       </c>
       <c r="H1053">
-        <v>0.006819696549371461</v>
+        <v>0.006467756786088693</v>
       </c>
       <c r="I1053">
-        <v>0.08497138405440863</v>
+        <v>0.07769366846473202</v>
       </c>
       <c r="J1053">
-        <v>0.7351257885553412</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1053">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="L1053">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1053">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1053">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1053">
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>368</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1054" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C1054">
-        <v>1.653489929309588</v>
+        <v>1.674071021437449</v>
       </c>
       <c r="D1054" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E1054">
-        <v>1.648192445080695</v>
+        <v>1.608515390817058</v>
       </c>
       <c r="F1054">
         <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.006446510070690412</v>
+        <v>0.007005928978562551</v>
       </c>
       <c r="H1054">
-        <v>0.006411807554919306</v>
+        <v>0.007071484609182941</v>
       </c>
       <c r="I1054">
-        <v>0.00529748422889309</v>
+        <v>0.06555563062039038</v>
       </c>
       <c r="J1054">
-        <v>0.7351257885553412</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1054">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="L1054">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="M1054">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="N1054">
-        <v>4.03</v>
+        <v>4.34</v>
       </c>
       <c r="O1054">
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>368</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1055" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1055">
-        <v>1.657002508165122</v>
+        <v>1.540367267690522</v>
       </c>
       <c r="D1055" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E1055">
-        <v>1.648192445080695</v>
+        <v>1.624194569973482</v>
       </c>
       <c r="F1055">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1055">
-        <v>0.006302997491834879</v>
+        <v>0.006959632732309478</v>
       </c>
       <c r="H1055">
-        <v>0.006411807554919306</v>
+        <v>0.006795805430026517</v>
       </c>
       <c r="I1055">
-        <v>0.008810063084427</v>
+        <v>0.08382730228296031</v>
       </c>
       <c r="J1055">
-        <v>0.7351257885553412</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1055">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="L1055">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1055">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="N1055">
-        <v>4.03</v>
+        <v>4.21</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>368</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1056" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1056">
-        <v>1.646785018160843</v>
+        <v>1.675429379750296</v>
       </c>
       <c r="D1056" t="s">
         <v>367</v>
       </c>
       <c r="E1056">
-        <v>1.637716284443396</v>
+        <v>1.599873749129906</v>
       </c>
       <c r="F1056">
         <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.006313214981839158</v>
+        <v>0.006424570620249703</v>
       </c>
       <c r="H1056">
-        <v>0.006422283715556604</v>
+        <v>0.006480126250870095</v>
       </c>
       <c r="I1056">
-        <v>0.009068733717446875</v>
+        <v>0.07555563062039061</v>
       </c>
       <c r="J1056">
-        <v>0.7383591714680878</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1056">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1056">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1056">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N1056">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1056">
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>220</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1057" t="s">
         <v>222</v>
       </c>
       <c r="C1057">
-        <v>1.629134524361594</v>
+        <v>1.678268969328508</v>
       </c>
       <c r="D1057" t="s">
         <v>367</v>
       </c>
       <c r="E1057">
-        <v>1.619618942699862</v>
+        <v>1.599873749129906</v>
       </c>
       <c r="F1057">
         <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.006330865475638406</v>
+        <v>0.006281731030671493</v>
       </c>
       <c r="H1057">
-        <v>0.006440381057300139</v>
+        <v>0.006480126250870095</v>
       </c>
       <c r="I1057">
-        <v>0.009515581661731609</v>
+        <v>0.07839522019860201</v>
       </c>
       <c r="J1057">
-        <v>0.7439447707716474</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1057">
         <v>3.16</v>
@@ -54709,10 +54712,10 @@
         <v>3.98</v>
       </c>
       <c r="M1057">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N1057">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -54726,381 +54729,381 @@
         <v>0</v>
       </c>
       <c r="B1058" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1058">
-        <v>1.581010547255576</v>
+        <v>1.525149479713785</v>
       </c>
       <c r="D1058" t="s">
-        <v>225</v>
+        <v>370</v>
       </c>
       <c r="E1058">
-        <v>1.537868375834023</v>
+        <v>1.609672218544069</v>
       </c>
       <c r="F1058">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.006378989452744424</v>
+        <v>0.006974850520286215</v>
       </c>
       <c r="H1058">
-        <v>0.006442131624165978</v>
+        <v>0.00681032778145593</v>
       </c>
       <c r="I1058">
-        <v>0.04314217142155341</v>
+        <v>0.08452273883028427</v>
       </c>
       <c r="J1058">
-        <v>0.7591738774507669</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1058">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="L1058">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1058">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N1058">
-        <v>3.99</v>
+        <v>4.21</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>495</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1059" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1059">
-        <v>1.567254514622121</v>
+        <v>1.662093361254554</v>
       </c>
       <c r="D1059" t="s">
-        <v>225</v>
+        <v>367</v>
       </c>
       <c r="E1059">
-        <v>1.523807620958687</v>
+        <v>1.586169558344404</v>
       </c>
       <c r="F1059">
         <v>-1</v>
       </c>
       <c r="G1059">
-        <v>0.006392745485377879</v>
+        <v>0.006437906638745446</v>
       </c>
       <c r="H1059">
-        <v>0.006456192379041313</v>
+        <v>0.006493830441655597</v>
       </c>
       <c r="I1059">
-        <v>0.04344689366343379</v>
+        <v>0.07592380291015033</v>
       </c>
       <c r="J1059">
-        <v>0.7635270523347718</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1059">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1059">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1059">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1059">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="O1059">
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>496</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1060" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C1060">
-        <v>1.553174199563495</v>
+        <v>1.665342031154721</v>
       </c>
       <c r="D1060" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E1060">
-        <v>1.528492149259424</v>
+        <v>1.586169558344404</v>
       </c>
       <c r="F1060">
         <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.006546825800436505</v>
+        <v>0.006294657968845279</v>
       </c>
       <c r="H1060">
-        <v>0.006491507850740576</v>
+        <v>0.006493830441655597</v>
       </c>
       <c r="I1060">
-        <v>0.024682050304071</v>
+        <v>0.07917247281031736</v>
       </c>
       <c r="J1060">
-        <v>0.7658974847964738</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1060">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="L1060">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1060">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N1060">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="O1060">
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>370</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1061" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1061">
-        <v>1.559763948043143</v>
+        <v>1.515332066574131</v>
       </c>
       <c r="D1061" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E1061">
-        <v>1.528492149259424</v>
+        <v>1.600303450628539</v>
       </c>
       <c r="F1061">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1061">
-        <v>0.006400236051956857</v>
+        <v>0.00698466793342587</v>
       </c>
       <c r="H1061">
-        <v>0.006491507850740576</v>
+        <v>0.006819696549371461</v>
       </c>
       <c r="I1061">
-        <v>0.03127179878371855</v>
+        <v>0.08497138405440863</v>
       </c>
       <c r="J1061">
-        <v>0.7658974847964738</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1061">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="L1061">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1061">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="N1061">
-        <v>4.01</v>
+        <v>4.21</v>
       </c>
       <c r="O1061">
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1062" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C1062">
-        <v>1.50615112410739</v>
+        <v>1.653489929309588</v>
       </c>
       <c r="D1062" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E1062">
-        <v>1.552104973195178</v>
+        <v>1.577328608339607</v>
       </c>
       <c r="F1062">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1062">
-        <v>0.006453848875892611</v>
+        <v>0.006446510070690412</v>
       </c>
       <c r="H1062">
-        <v>0.006407895026804822</v>
+        <v>0.006502671391660392</v>
       </c>
       <c r="I1062">
-        <v>0.04595384908778843</v>
+        <v>0.07616132096998074</v>
       </c>
       <c r="J1062">
-        <v>0.7658974847964738</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1062">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="L1062">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1062">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="N1062">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1062">
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1063" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C1063">
-        <v>1.554922686674014</v>
+        <v>1.650246218737355</v>
       </c>
       <c r="D1063" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E1063">
-        <v>1.52352832431133</v>
+        <v>1.577328608339607</v>
       </c>
       <c r="F1063">
         <v>-1</v>
       </c>
       <c r="G1063">
-        <v>0.006405077313325986</v>
+        <v>0.006369753781262645</v>
       </c>
       <c r="H1063">
-        <v>0.006496471675688669</v>
+        <v>0.006502671391660392</v>
       </c>
       <c r="I1063">
-        <v>0.03139436236268356</v>
+        <v>0.07291761039774736</v>
       </c>
       <c r="J1063">
-        <v>0.7674295295335398</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1063">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="L1063">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="M1063">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N1063">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="O1063">
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1064" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C1064">
-        <v>1.511202619606667</v>
+        <v>1.642949101014034</v>
       </c>
       <c r="D1064" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E1064">
-        <v>1.547248391378679</v>
+        <v>1.566496775581906</v>
       </c>
       <c r="F1064">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1064">
-        <v>0.006468797380393333</v>
+        <v>0.006457050898985965</v>
       </c>
       <c r="H1064">
-        <v>0.00641275160862132</v>
+        <v>0.006513503224418095</v>
       </c>
       <c r="I1064">
-        <v>0.03604577177201218</v>
+        <v>0.0764523254321281</v>
       </c>
       <c r="J1064">
-        <v>0.7674295295335398</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1064">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="L1064">
-        <v>3.99</v>
+        <v>4.05</v>
       </c>
       <c r="M1064">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="N1064">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1064">
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>369</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1065" t="s">
         <v>222</v>
       </c>
       <c r="C1065">
-        <v>1.551006173140757</v>
+        <v>1.646785018160843</v>
       </c>
       <c r="D1065" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E1065">
-        <v>1.519512658536726</v>
+        <v>1.566496775581906</v>
       </c>
       <c r="F1065">
         <v>-1</v>
       </c>
       <c r="G1065">
-        <v>0.006408993826859243</v>
+        <v>0.006313214981839158</v>
       </c>
       <c r="H1065">
-        <v>0.006500487341463274</v>
+        <v>0.006513503224418095</v>
       </c>
       <c r="I1065">
-        <v>0.0314935146040316</v>
+        <v>0.08028824257893685</v>
       </c>
       <c r="J1065">
-        <v>0.7686689325503931</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1065">
         <v>3.16</v>
@@ -55109,66 +55112,66 @@
         <v>3.98</v>
       </c>
       <c r="M1065">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N1065">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="O1065">
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>497</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1066" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C1066">
-        <v>1.507199347862231</v>
+        <v>1.629134524361594</v>
       </c>
       <c r="D1066" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E1066">
-        <v>1.543319483815254</v>
+        <v>1.547785017914981</v>
       </c>
       <c r="F1066">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1066">
-        <v>0.00647280065213777</v>
+        <v>0.006330865475638406</v>
       </c>
       <c r="H1066">
-        <v>0.006416680516184746</v>
+        <v>0.00653221498208502</v>
       </c>
       <c r="I1066">
-        <v>0.03612013595302344</v>
+        <v>0.08134950644661254</v>
       </c>
       <c r="J1066">
-        <v>0.7686689325503931</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1066">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="L1066">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1066">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="N1066">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1066">
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55179,28 +55182,28 @@
         <v>222</v>
       </c>
       <c r="C1067">
-        <v>1.551334098382603</v>
+        <v>1.615003925968209</v>
       </c>
       <c r="D1067" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E1067">
-        <v>1.519848885683428</v>
+        <v>1.532804794934651</v>
       </c>
       <c r="F1067">
         <v>-1</v>
       </c>
       <c r="G1067">
-        <v>0.006408665901617397</v>
+        <v>0.006344996074031791</v>
       </c>
       <c r="H1067">
-        <v>0.006500151114316571</v>
+        <v>0.006547195205065348</v>
       </c>
       <c r="I1067">
-        <v>0.03148521269917515</v>
+        <v>0.08219913103355703</v>
       </c>
       <c r="J1067">
-        <v>0.7685651587396826</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1067">
         <v>3.16</v>
@@ -55209,66 +55212,66 @@
         <v>3.98</v>
       </c>
       <c r="M1067">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N1067">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="O1067">
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>223</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1068" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C1068">
-        <v>1.507534537270826</v>
+        <v>1.581010547255576</v>
       </c>
       <c r="D1068" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E1068">
-        <v>1.543648446795206</v>
+        <v>1.537868375834023</v>
       </c>
       <c r="F1068">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1068">
-        <v>0.006472465462729175</v>
+        <v>0.006378989452744424</v>
       </c>
       <c r="H1068">
-        <v>0.006416351553204793</v>
+        <v>0.006442131624165978</v>
       </c>
       <c r="I1068">
-        <v>0.03611390952438054</v>
+        <v>0.04314217142155341</v>
       </c>
       <c r="J1068">
-        <v>0.7685651587396826</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1068">
+        <v>3.16</v>
+      </c>
+      <c r="L1068">
+        <v>3.98</v>
+      </c>
+      <c r="M1068">
         <v>3.23</v>
       </c>
-      <c r="L1068">
+      <c r="N1068">
         <v>3.99</v>
       </c>
-      <c r="M1068">
-        <v>3.17</v>
-      </c>
-      <c r="N1068">
-        <v>3.98</v>
-      </c>
       <c r="O1068">
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>223</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55276,43 +55279,43 @@
         <v>0</v>
       </c>
       <c r="B1069" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1069">
-        <v>1.554703628836944</v>
+        <v>1.560901809388644</v>
       </c>
       <c r="D1069" t="s">
         <v>371</v>
       </c>
       <c r="E1069">
-        <v>1.523303720706234</v>
+        <v>1.523807620958687</v>
       </c>
       <c r="F1069">
         <v>-1</v>
       </c>
       <c r="G1069">
-        <v>0.006405296371163056</v>
+        <v>0.006539098190611355</v>
       </c>
       <c r="H1069">
-        <v>0.006496696279293766</v>
+        <v>0.006456192379041313</v>
       </c>
       <c r="I1069">
-        <v>0.03139990813071059</v>
+        <v>0.03709418842995671</v>
       </c>
       <c r="J1069">
-        <v>0.7674988516338783</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1069">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1069">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1069">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="N1069">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="O1069">
         <v>1</v>
@@ -55326,43 +55329,43 @@
         <v>1</v>
       </c>
       <c r="B1070" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C1070">
-        <v>1.510978709222573</v>
+        <v>1.559078162005382</v>
       </c>
       <c r="D1070" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E1070">
-        <v>1.547028640320606</v>
+        <v>1.523807620958687</v>
       </c>
       <c r="F1070">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.006469021290777427</v>
+        <v>0.006460921837994617</v>
       </c>
       <c r="H1070">
-        <v>0.006412971359679395</v>
+        <v>0.006456192379041313</v>
       </c>
       <c r="I1070">
-        <v>0.03604993109803267</v>
+        <v>0.03527054104669514</v>
       </c>
       <c r="J1070">
-        <v>0.7674988516338783</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1070">
+        <v>3.21</v>
+      </c>
+      <c r="L1070">
+        <v>4.01</v>
+      </c>
+      <c r="M1070">
         <v>3.23</v>
       </c>
-      <c r="L1070">
+      <c r="N1070">
         <v>3.99</v>
-      </c>
-      <c r="M1070">
-        <v>3.17</v>
-      </c>
-      <c r="N1070">
-        <v>3.98</v>
       </c>
       <c r="O1070">
         <v>1</v>
@@ -55376,49 +55379,49 @@
         <v>0</v>
       </c>
       <c r="B1071" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1071">
-        <v>1.549132021580153</v>
+        <v>1.553174199563495</v>
       </c>
       <c r="D1071" t="s">
         <v>371</v>
       </c>
       <c r="E1071">
-        <v>1.517591060101169</v>
+        <v>1.51615112410739</v>
       </c>
       <c r="F1071">
         <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.006410867978419848</v>
+        <v>0.006546825800436505</v>
       </c>
       <c r="H1071">
-        <v>0.00650240893989883</v>
+        <v>0.006463848875892611</v>
       </c>
       <c r="I1071">
-        <v>0.03154096147898366</v>
+        <v>0.03702307545610539</v>
       </c>
       <c r="J1071">
-        <v>0.7692620184872934</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1071">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="L1071">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1071">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="N1071">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="O1071">
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>499</v>
+        <v>370</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -55429,46 +55432,46 @@
         <v>224</v>
       </c>
       <c r="C1072">
-        <v>1.495283680286042</v>
+        <v>1.551469073803319</v>
       </c>
       <c r="D1072" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E1072">
-        <v>1.54143940139528</v>
+        <v>1.51615112410739</v>
       </c>
       <c r="F1072">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1072">
-        <v>0.006464716319713958</v>
+        <v>0.006468530926196681</v>
       </c>
       <c r="H1072">
-        <v>0.00641856059860472</v>
+        <v>0.006463848875892611</v>
       </c>
       <c r="I1072">
-        <v>0.04615572110923782</v>
+        <v>0.03531794969592905</v>
       </c>
       <c r="J1072">
-        <v>0.7692620184872934</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1072">
+        <v>3.21</v>
+      </c>
+      <c r="L1072">
+        <v>4.01</v>
+      </c>
+      <c r="M1072">
         <v>3.23</v>
       </c>
-      <c r="L1072">
-        <v>3.98</v>
-      </c>
-      <c r="M1072">
-        <v>3.17</v>
-      </c>
       <c r="N1072">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="O1072">
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>499</v>
+        <v>370</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -55476,49 +55479,349 @@
         <v>0</v>
       </c>
       <c r="B1073" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C1073">
-        <v>1.495727236198634</v>
+        <v>1.54817973372066</v>
       </c>
       <c r="D1073" t="s">
         <v>372</v>
       </c>
       <c r="E1073">
-        <v>1.541874717879155</v>
+        <v>1.52352832431133</v>
       </c>
       <c r="F1073">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1073">
-        <v>0.006464272763801366</v>
+        <v>0.00655182026627934</v>
       </c>
       <c r="H1073">
-        <v>0.006418125282120845</v>
+        <v>0.006496471675688669</v>
       </c>
       <c r="I1073">
-        <v>0.04614748168052074</v>
+        <v>0.02465140940932953</v>
       </c>
       <c r="J1073">
-        <v>0.7691246946753454</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1073">
+        <v>3.26</v>
+      </c>
+      <c r="L1073">
+        <v>4.05</v>
+      </c>
+      <c r="M1073">
+        <v>3.24</v>
+      </c>
+      <c r="N1073">
+        <v>4.01</v>
+      </c>
+      <c r="O1073">
+        <v>1</v>
+      </c>
+      <c r="P1073" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:16">
+      <c r="A1074" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1074">
+        <v>1.554922686674014</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1074">
+        <v>1.52352832431133</v>
+      </c>
+      <c r="F1074">
+        <v>-1</v>
+      </c>
+      <c r="G1074">
+        <v>0.006405077313325986</v>
+      </c>
+      <c r="H1074">
+        <v>0.006496471675688669</v>
+      </c>
+      <c r="I1074">
+        <v>0.03139436236268356</v>
+      </c>
+      <c r="J1074">
+        <v>0.7674295295335398</v>
+      </c>
+      <c r="K1074">
+        <v>3.16</v>
+      </c>
+      <c r="L1074">
+        <v>3.98</v>
+      </c>
+      <c r="M1074">
+        <v>3.24</v>
+      </c>
+      <c r="N1074">
+        <v>4.01</v>
+      </c>
+      <c r="O1074">
+        <v>1</v>
+      </c>
+      <c r="P1074" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:16">
+      <c r="A1075" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1075">
+        <v>1.551006173140757</v>
+      </c>
+      <c r="D1075" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1075">
+        <v>1.519512658536726</v>
+      </c>
+      <c r="F1075">
+        <v>-1</v>
+      </c>
+      <c r="G1075">
+        <v>0.006408993826859243</v>
+      </c>
+      <c r="H1075">
+        <v>0.006500487341463274</v>
+      </c>
+      <c r="I1075">
+        <v>0.0314935146040316</v>
+      </c>
+      <c r="J1075">
+        <v>0.7686689325503931</v>
+      </c>
+      <c r="K1075">
+        <v>3.16</v>
+      </c>
+      <c r="L1075">
+        <v>3.98</v>
+      </c>
+      <c r="M1075">
+        <v>3.24</v>
+      </c>
+      <c r="N1075">
+        <v>4.01</v>
+      </c>
+      <c r="O1075">
+        <v>1</v>
+      </c>
+      <c r="P1075" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:16">
+      <c r="A1076" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1076">
+        <v>1.49719934786223</v>
+      </c>
+      <c r="D1076" t="s">
+        <v>373</v>
+      </c>
+      <c r="E1076">
+        <v>1.543319483815254</v>
+      </c>
+      <c r="F1076">
+        <v>1</v>
+      </c>
+      <c r="G1076">
+        <v>0.006462800652137769</v>
+      </c>
+      <c r="H1076">
+        <v>0.006416680516184746</v>
+      </c>
+      <c r="I1076">
+        <v>0.04612013595302367</v>
+      </c>
+      <c r="J1076">
+        <v>0.7686689325503931</v>
+      </c>
+      <c r="K1076">
         <v>3.23</v>
       </c>
-      <c r="L1073">
+      <c r="L1076">
         <v>3.98</v>
       </c>
-      <c r="M1073">
+      <c r="M1076">
         <v>3.17</v>
       </c>
-      <c r="N1073">
+      <c r="N1076">
         <v>3.98</v>
       </c>
-      <c r="O1073">
-        <v>1</v>
-      </c>
-      <c r="P1073" t="s">
+      <c r="O1076">
+        <v>1</v>
+      </c>
+      <c r="P1076" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:16">
+      <c r="A1077" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1077" t="s">
         <v>222</v>
+      </c>
+      <c r="C1077">
+        <v>1.551334098382603</v>
+      </c>
+      <c r="D1077" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1077">
+        <v>1.519848885683428</v>
+      </c>
+      <c r="F1077">
+        <v>-1</v>
+      </c>
+      <c r="G1077">
+        <v>0.006408665901617397</v>
+      </c>
+      <c r="H1077">
+        <v>0.006500151114316571</v>
+      </c>
+      <c r="I1077">
+        <v>0.03148521269917515</v>
+      </c>
+      <c r="J1077">
+        <v>0.7685651587396826</v>
+      </c>
+      <c r="K1077">
+        <v>3.16</v>
+      </c>
+      <c r="L1077">
+        <v>3.98</v>
+      </c>
+      <c r="M1077">
+        <v>3.24</v>
+      </c>
+      <c r="N1077">
+        <v>4.01</v>
+      </c>
+      <c r="O1077">
+        <v>1</v>
+      </c>
+      <c r="P1077" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:16">
+      <c r="A1078" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1078">
+        <v>1.554703628836944</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>371</v>
+      </c>
+      <c r="E1078">
+        <v>1.510978709222573</v>
+      </c>
+      <c r="F1078">
+        <v>-1</v>
+      </c>
+      <c r="G1078">
+        <v>0.006405296371163056</v>
+      </c>
+      <c r="H1078">
+        <v>0.006469021290777427</v>
+      </c>
+      <c r="I1078">
+        <v>0.04372491961437097</v>
+      </c>
+      <c r="J1078">
+        <v>0.7674988516338783</v>
+      </c>
+      <c r="K1078">
+        <v>3.16</v>
+      </c>
+      <c r="L1078">
+        <v>3.98</v>
+      </c>
+      <c r="M1078">
+        <v>3.23</v>
+      </c>
+      <c r="N1078">
+        <v>3.99</v>
+      </c>
+      <c r="O1078">
+        <v>1</v>
+      </c>
+      <c r="P1078" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:16">
+      <c r="A1079" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1079">
+        <v>1.549132021580153</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>371</v>
+      </c>
+      <c r="E1079">
+        <v>1.505283680286043</v>
+      </c>
+      <c r="F1079">
+        <v>-1</v>
+      </c>
+      <c r="G1079">
+        <v>0.006410867978419848</v>
+      </c>
+      <c r="H1079">
+        <v>0.006474716319713958</v>
+      </c>
+      <c r="I1079">
+        <v>0.04384834129411042</v>
+      </c>
+      <c r="J1079">
+        <v>0.7692620184872934</v>
+      </c>
+      <c r="K1079">
+        <v>3.16</v>
+      </c>
+      <c r="L1079">
+        <v>3.98</v>
+      </c>
+      <c r="M1079">
+        <v>3.23</v>
+      </c>
+      <c r="N1079">
+        <v>3.99</v>
+      </c>
+      <c r="O1079">
+        <v>1</v>
+      </c>
+      <c r="P1079" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3357" uniqueCount="506">
   <si>
     <t>trade_time</t>
   </si>
@@ -1123,13 +1123,10 @@
     <t>2021-05-10</t>
   </si>
   <si>
-    <t>2021-08-16</t>
+    <t>2021-08-17</t>
   </si>
   <si>
     <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
   </si>
   <si>
     <t>2021-07-22</t>
@@ -1138,10 +1135,13 @@
     <t>2021-08-04</t>
   </si>
   <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2021-08-13</t>
+    <t>2021-08-16</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1519,6 +1519,9 @@
     <t>2021-07-21</t>
   </si>
   <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
     <t>2021-07-26</t>
   </si>
   <si>
@@ -1529,9 +1532,6 @@
   </si>
   <si>
     <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
   </si>
 </sst>
 </file>
@@ -1889,7 +1889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1110"/>
+  <dimension ref="A1:P1115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -53553,7 +53553,7 @@
         <v>369</v>
       </c>
       <c r="E1034">
-        <v>1.770236205537345</v>
+        <v>1.75071744838746</v>
       </c>
       <c r="F1034">
         <v>1</v>
@@ -53562,10 +53562,10 @@
         <v>0.006789674113414224</v>
       </c>
       <c r="H1034">
-        <v>0.006289763794462656</v>
+        <v>0.00622928255161254</v>
       </c>
       <c r="I1034">
-        <v>0.05991031895156818</v>
+        <v>0.04039156180168302</v>
       </c>
       <c r="J1034">
         <v>0.6827080950038233</v>
@@ -53577,10 +53577,10 @@
         <v>4.25</v>
       </c>
       <c r="M1034">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N1034">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="O1034">
         <v>1</v>
@@ -53653,7 +53653,7 @@
         <v>371</v>
       </c>
       <c r="E1036">
-        <v>1.778582236553444</v>
+        <v>1.760987732126702</v>
       </c>
       <c r="F1036">
         <v>1</v>
@@ -53662,10 +53662,10 @@
         <v>0.006816288911686948</v>
       </c>
       <c r="H1036">
-        <v>0.006621417763446557</v>
+        <v>0.006659012267873298</v>
       </c>
       <c r="I1036">
-        <v>0.09487114824039233</v>
+        <v>0.07727664381365074</v>
       </c>
       <c r="J1036">
         <v>0.6898626106685345</v>
@@ -53677,10 +53677,10 @@
         <v>4.25</v>
       </c>
       <c r="M1036">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="N1036">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="O1036">
         <v>1</v>
@@ -53703,7 +53703,7 @@
         <v>369</v>
       </c>
       <c r="E1037">
-        <v>1.746554758687151</v>
+        <v>1.727250637007207</v>
       </c>
       <c r="F1037">
         <v>1</v>
@@ -53712,10 +53712,10 @@
         <v>0.00633103974573959</v>
       </c>
       <c r="H1037">
-        <v>0.00631344524131285</v>
+        <v>0.006252749362992793</v>
       </c>
       <c r="I1037">
-        <v>0.03759450442674206</v>
+        <v>0.01829038274679817</v>
       </c>
       <c r="J1037">
         <v>0.6898626106685345</v>
@@ -53727,10 +53727,10 @@
         <v>4.02</v>
       </c>
       <c r="M1037">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N1037">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="O1037">
         <v>1</v>
@@ -53800,7 +53800,7 @@
         <v>1.642597950562186</v>
       </c>
       <c r="D1039" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E1039">
         <v>1.721753420563377</v>
@@ -53844,43 +53844,43 @@
         <v>2</v>
       </c>
       <c r="B1040" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1040">
-        <v>1.671936326447129</v>
+        <v>1.765018634094819</v>
       </c>
       <c r="D1040" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E1040">
-        <v>1.709972907623881</v>
+        <v>1.716046069977382</v>
       </c>
       <c r="F1040">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1040">
-        <v>0.00636806367355287</v>
+        <v>0.006334981365905181</v>
       </c>
       <c r="H1040">
-        <v>0.00635002709237612</v>
+        <v>0.006243953930022619</v>
       </c>
       <c r="I1040">
-        <v>0.03803658117675157</v>
+        <v>0.04897256411743678</v>
       </c>
       <c r="J1040">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1040">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="L1040">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="M1040">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N1040">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="O1040">
         <v>1</v>
@@ -53891,146 +53891,146 @@
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1041" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C1041">
-        <v>1.745068418380975</v>
+        <v>1.765110087036696</v>
       </c>
       <c r="D1041" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E1041">
-        <v>1.681258625390344</v>
+        <v>1.716046069977382</v>
       </c>
       <c r="F1041">
         <v>-1</v>
       </c>
       <c r="G1041">
-        <v>0.006934931581619024</v>
+        <v>0.006194889912963305</v>
       </c>
       <c r="H1041">
-        <v>0.006998741374609656</v>
+        <v>0.006243953930022619</v>
       </c>
       <c r="I1041">
-        <v>0.06380979299063139</v>
+        <v>0.04906401705931351</v>
       </c>
       <c r="J1041">
-        <v>0.7089976998959082</v>
+        <v>0.7009145294187672</v>
       </c>
       <c r="K1041">
-        <v>3.66</v>
+        <v>3.16</v>
       </c>
       <c r="L1041">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="M1041">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N1041">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="O1041">
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1042" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C1042">
-        <v>1.612528556387221</v>
+        <v>1.671936326447129</v>
       </c>
       <c r="D1042" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E1042">
-        <v>1.693058165369526</v>
+        <v>1.691000343506444</v>
       </c>
       <c r="F1042">
         <v>1</v>
       </c>
       <c r="G1042">
-        <v>0.006887471443612779</v>
+        <v>0.00636806367355287</v>
       </c>
       <c r="H1042">
-        <v>0.006726941834630474</v>
+        <v>0.006288999656493557</v>
       </c>
       <c r="I1042">
-        <v>0.08052960898230443</v>
+        <v>0.0190640170593146</v>
       </c>
       <c r="J1042">
-        <v>0.7089976998959082</v>
+        <v>0.7009145294187672</v>
       </c>
       <c r="K1042">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="L1042">
-        <v>4.25</v>
+        <v>4.02</v>
       </c>
       <c r="M1042">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="N1042">
-        <v>4.21</v>
+        <v>3.99</v>
       </c>
       <c r="O1042">
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1043" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C1043">
-        <v>1.738667498339339</v>
+        <v>1.745068418380975</v>
       </c>
       <c r="D1043" t="s">
-        <v>227</v>
+        <v>370</v>
       </c>
       <c r="E1043">
-        <v>1.664857705348707</v>
+        <v>1.681258625390344</v>
       </c>
       <c r="F1043">
         <v>-1</v>
       </c>
       <c r="G1043">
-        <v>0.006361332501660661</v>
+        <v>0.006934931581619024</v>
       </c>
       <c r="H1043">
-        <v>0.006415142294651293</v>
+        <v>0.006998741374609656</v>
       </c>
       <c r="I1043">
-        <v>0.07380979299063162</v>
+        <v>0.06380979299063139</v>
       </c>
       <c r="J1043">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1043">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="L1043">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="M1043">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1043">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="O1043">
         <v>1</v>
@@ -54041,46 +54041,46 @@
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1044" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C1044">
-        <v>1.73956726832893</v>
+        <v>1.612528556387221</v>
       </c>
       <c r="D1044" t="s">
-        <v>227</v>
+        <v>371</v>
       </c>
       <c r="E1044">
-        <v>1.664857705348707</v>
+        <v>1.693058165369526</v>
       </c>
       <c r="F1044">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1044">
-        <v>0.006220432731671071</v>
+        <v>0.006887471443612779</v>
       </c>
       <c r="H1044">
-        <v>0.006415142294651293</v>
+        <v>0.006726941834630474</v>
       </c>
       <c r="I1044">
-        <v>0.07470956298022235</v>
+        <v>0.08052960898230443</v>
       </c>
       <c r="J1044">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1044">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="L1044">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1044">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N1044">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="O1044">
         <v>1</v>
@@ -54091,146 +54091,146 @@
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1045" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1045">
-        <v>1.725336643125503</v>
+        <v>1.738667498339339</v>
       </c>
       <c r="D1045" t="s">
-        <v>370</v>
+        <v>227</v>
       </c>
       <c r="E1045">
-        <v>1.661041642546622</v>
+        <v>1.664857705348707</v>
       </c>
       <c r="F1045">
         <v>-1</v>
       </c>
       <c r="G1045">
-        <v>0.006954663356874498</v>
+        <v>0.006361332501660661</v>
       </c>
       <c r="H1045">
-        <v>0.007018958357453379</v>
+        <v>0.006415142294651293</v>
       </c>
       <c r="I1045">
-        <v>0.06429500057888093</v>
+        <v>0.07380979299063162</v>
       </c>
       <c r="J1045">
-        <v>0.7143888953209009</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1045">
-        <v>3.66</v>
+        <v>3.26</v>
       </c>
       <c r="L1045">
-        <v>4.34</v>
+        <v>4.05</v>
       </c>
       <c r="M1045">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1045">
-        <v>4.34</v>
+        <v>4.04</v>
       </c>
       <c r="O1045">
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1046" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1046">
-        <v>1.592473309406249</v>
+        <v>1.734117383334135</v>
       </c>
       <c r="D1046" t="s">
-        <v>372</v>
+        <v>227</v>
       </c>
       <c r="E1046">
-        <v>1.673919421610802</v>
+        <v>1.664857705348707</v>
       </c>
       <c r="F1046">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1046">
-        <v>0.006907526690593752</v>
+        <v>0.006285882616665866</v>
       </c>
       <c r="H1046">
-        <v>0.006746080578389198</v>
+        <v>0.006415142294651293</v>
       </c>
       <c r="I1046">
-        <v>0.08144611220455333</v>
+        <v>0.06925967798542709</v>
       </c>
       <c r="J1046">
-        <v>0.7143888953209009</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1046">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="L1046">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="M1046">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1046">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1046">
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1047" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C1047">
-        <v>1.721092201253863</v>
+        <v>1.725336643125503</v>
       </c>
       <c r="D1047" t="s">
-        <v>227</v>
+        <v>370</v>
       </c>
       <c r="E1047">
-        <v>1.646797200674982</v>
+        <v>1.661041642546622</v>
       </c>
       <c r="F1047">
         <v>-1</v>
       </c>
       <c r="G1047">
-        <v>0.006378907798746137</v>
+        <v>0.006954663356874498</v>
       </c>
       <c r="H1047">
-        <v>0.006433202799325018</v>
+        <v>0.007018958357453379</v>
       </c>
       <c r="I1047">
-        <v>0.07429500057888117</v>
+        <v>0.06429500057888093</v>
       </c>
       <c r="J1047">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1047">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="L1047">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="M1047">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1047">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="O1047">
         <v>1</v>
@@ -54241,46 +54241,46 @@
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1048" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C1048">
-        <v>1.716811646019908</v>
+        <v>1.592473309406249</v>
       </c>
       <c r="D1048" t="s">
-        <v>227</v>
+        <v>371</v>
       </c>
       <c r="E1048">
-        <v>1.646797200674982</v>
+        <v>1.673919421610802</v>
       </c>
       <c r="F1048">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1048">
-        <v>0.006303188353980092</v>
+        <v>0.006907526690593752</v>
       </c>
       <c r="H1048">
-        <v>0.006433202799325018</v>
+        <v>0.006746080578389198</v>
       </c>
       <c r="I1048">
-        <v>0.07001444534492629</v>
+        <v>0.08144611220455333</v>
       </c>
       <c r="J1048">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1048">
-        <v>3.21</v>
+        <v>3.72</v>
       </c>
       <c r="L1048">
-        <v>4.01</v>
+        <v>4.25</v>
       </c>
       <c r="M1048">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N1048">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="O1048">
         <v>1</v>
@@ -54291,140 +54291,140 @@
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1049" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1049">
-        <v>1.706714139491356</v>
+        <v>1.721092201253863</v>
       </c>
       <c r="D1049" t="s">
-        <v>370</v>
+        <v>227</v>
       </c>
       <c r="E1049">
-        <v>1.641961208495242</v>
+        <v>1.646797200674982</v>
       </c>
       <c r="F1049">
         <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.006973285860508644</v>
+        <v>0.006378907798746137</v>
       </c>
       <c r="H1049">
-        <v>0.007038038791504758</v>
+        <v>0.006433202799325018</v>
       </c>
       <c r="I1049">
-        <v>0.0647529309961139</v>
+        <v>0.07429500057888117</v>
       </c>
       <c r="J1049">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1049">
-        <v>3.66</v>
+        <v>3.26</v>
       </c>
       <c r="L1049">
-        <v>4.34</v>
+        <v>4.05</v>
       </c>
       <c r="M1049">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1049">
-        <v>4.34</v>
+        <v>4.04</v>
       </c>
       <c r="O1049">
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1050" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1050">
-        <v>1.57354551882728</v>
+        <v>1.716811646019908</v>
       </c>
       <c r="D1050" t="s">
-        <v>372</v>
+        <v>227</v>
       </c>
       <c r="E1050">
-        <v>1.655856610708829</v>
+        <v>1.646797200674982</v>
       </c>
       <c r="F1050">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.00692645448117272</v>
+        <v>0.006303188353980092</v>
       </c>
       <c r="H1050">
-        <v>0.006764143389291171</v>
+        <v>0.006433202799325018</v>
       </c>
       <c r="I1050">
-        <v>0.08231109188154928</v>
+        <v>0.07001444534492629</v>
       </c>
       <c r="J1050">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1050">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="L1050">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="M1050">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1050">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1050">
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1051" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C1051">
-        <v>1.70450494391853</v>
+        <v>1.715387201832744</v>
       </c>
       <c r="D1051" t="s">
         <v>227</v>
       </c>
       <c r="E1051">
-        <v>1.629752012922416</v>
+        <v>1.646797200674982</v>
       </c>
       <c r="F1051">
         <v>-1</v>
       </c>
       <c r="G1051">
-        <v>0.006395495056081469</v>
+        <v>0.006244612798167256</v>
       </c>
       <c r="H1051">
-        <v>0.006450247987077585</v>
+        <v>0.006433202799325018</v>
       </c>
       <c r="I1051">
-        <v>0.07475293099611457</v>
+        <v>0.06859000115776226</v>
       </c>
       <c r="J1051">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1051">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1051">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1051">
         <v>3.35</v>
@@ -54436,51 +54436,51 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1052" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C1052">
-        <v>1.700478794471927</v>
+        <v>1.706714139491356</v>
       </c>
       <c r="D1052" t="s">
-        <v>227</v>
+        <v>370</v>
       </c>
       <c r="E1052">
-        <v>1.629752012922416</v>
+        <v>1.641961208495242</v>
       </c>
       <c r="F1052">
         <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.006319521205528073</v>
+        <v>0.006973285860508644</v>
       </c>
       <c r="H1052">
-        <v>0.006450247987077585</v>
+        <v>0.007038038791504758</v>
       </c>
       <c r="I1052">
-        <v>0.07072678154951095</v>
+        <v>0.0647529309961139</v>
       </c>
       <c r="J1052">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1052">
-        <v>3.21</v>
+        <v>3.66</v>
       </c>
       <c r="L1052">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="M1052">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1052">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="O1052">
         <v>1</v>
@@ -54491,46 +54491,46 @@
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1053" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C1053">
-        <v>1.699257874914645</v>
+        <v>1.57354551882728</v>
       </c>
       <c r="D1053" t="s">
-        <v>227</v>
+        <v>371</v>
       </c>
       <c r="E1053">
-        <v>1.629752012922416</v>
+        <v>1.655856610708829</v>
       </c>
       <c r="F1053">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.006260742125085356</v>
+        <v>0.00692645448117272</v>
       </c>
       <c r="H1053">
-        <v>0.006450247987077585</v>
+        <v>0.006764143389291171</v>
       </c>
       <c r="I1053">
-        <v>0.06950586199222863</v>
+        <v>0.08231109188154928</v>
       </c>
       <c r="J1053">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1053">
-        <v>3.17</v>
+        <v>3.72</v>
       </c>
       <c r="L1053">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1053">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N1053">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="O1053">
         <v>1</v>
@@ -54541,140 +54541,140 @@
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1054" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1054">
-        <v>1.687585123258323</v>
+        <v>1.70450494391853</v>
       </c>
       <c r="D1054" t="s">
-        <v>370</v>
+        <v>227</v>
       </c>
       <c r="E1054">
-        <v>1.622361806617135</v>
+        <v>1.629752012922416</v>
       </c>
       <c r="F1054">
         <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.006992414876741677</v>
+        <v>0.006395495056081469</v>
       </c>
       <c r="H1054">
-        <v>0.007057638193382865</v>
+        <v>0.006450247987077585</v>
       </c>
       <c r="I1054">
-        <v>0.06522331664118841</v>
+        <v>0.07475293099611457</v>
       </c>
       <c r="J1054">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1054">
-        <v>3.66</v>
+        <v>3.26</v>
       </c>
       <c r="L1054">
-        <v>4.34</v>
+        <v>4.05</v>
       </c>
       <c r="M1054">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1054">
-        <v>4.34</v>
+        <v>4.04</v>
       </c>
       <c r="O1054">
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1055" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1055">
-        <v>1.554102912164197</v>
+        <v>1.700478794471927</v>
       </c>
       <c r="D1055" t="s">
-        <v>372</v>
+        <v>227</v>
       </c>
       <c r="E1055">
-        <v>1.637302510264221</v>
+        <v>1.629752012922416</v>
       </c>
       <c r="F1055">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.006945897087835803</v>
+        <v>0.006319521205528073</v>
       </c>
       <c r="H1055">
-        <v>0.00678269748973578</v>
+        <v>0.006450247987077585</v>
       </c>
       <c r="I1055">
-        <v>0.08319959810002331</v>
+        <v>0.07072678154951095</v>
       </c>
       <c r="J1055">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1055">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="L1055">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="M1055">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1055">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1056" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C1056">
-        <v>1.687466530552496</v>
+        <v>1.699257874914645</v>
       </c>
       <c r="D1056" t="s">
         <v>227</v>
       </c>
       <c r="E1056">
-        <v>1.612243213911307</v>
+        <v>1.629752012922416</v>
       </c>
       <c r="F1056">
         <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.006412533469447504</v>
+        <v>0.006260742125085356</v>
       </c>
       <c r="H1056">
-        <v>0.006467756786088693</v>
+        <v>0.006450247987077585</v>
       </c>
       <c r="I1056">
-        <v>0.07522331664118909</v>
+        <v>0.06950586199222863</v>
       </c>
       <c r="J1056">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1056">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1056">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1056">
         <v>3.35</v>
@@ -54686,51 +54686,51 @@
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1057" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C1057">
-        <v>1.683701706464267</v>
+        <v>1.687585123258323</v>
       </c>
       <c r="D1057" t="s">
-        <v>227</v>
+        <v>370</v>
       </c>
       <c r="E1057">
-        <v>1.612243213911307</v>
+        <v>1.622361806617135</v>
       </c>
       <c r="F1057">
         <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.006336298293535732</v>
+        <v>0.006992414876741677</v>
       </c>
       <c r="H1057">
-        <v>0.006467756786088693</v>
+        <v>0.007057638193382865</v>
       </c>
       <c r="I1057">
-        <v>0.07145849255296044</v>
+        <v>0.06522331664118841</v>
       </c>
       <c r="J1057">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1057">
-        <v>3.21</v>
+        <v>3.66</v>
       </c>
       <c r="L1057">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="M1057">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1057">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -54741,46 +54741,46 @@
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1058" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C1058">
-        <v>1.682689847193684</v>
+        <v>1.554102912164197</v>
       </c>
       <c r="D1058" t="s">
-        <v>227</v>
+        <v>371</v>
       </c>
       <c r="E1058">
-        <v>1.612243213911307</v>
+        <v>1.637302510264221</v>
       </c>
       <c r="F1058">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.006277310152806315</v>
+        <v>0.006945897087835803</v>
       </c>
       <c r="H1058">
-        <v>0.006467756786088693</v>
+        <v>0.00678269748973578</v>
       </c>
       <c r="I1058">
-        <v>0.07044663328237766</v>
+        <v>0.08319959810002331</v>
       </c>
       <c r="J1058">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1058">
-        <v>3.17</v>
+        <v>3.72</v>
       </c>
       <c r="L1058">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1058">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N1058">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="O1058">
         <v>1</v>
@@ -54791,140 +54791,140 @@
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1059" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1059">
-        <v>1.674071021437449</v>
+        <v>1.687466530552496</v>
       </c>
       <c r="D1059" t="s">
-        <v>370</v>
+        <v>227</v>
       </c>
       <c r="E1059">
-        <v>1.608515390817058</v>
+        <v>1.612243213911307</v>
       </c>
       <c r="F1059">
         <v>-1</v>
       </c>
       <c r="G1059">
-        <v>0.007005928978562551</v>
+        <v>0.006412533469447504</v>
       </c>
       <c r="H1059">
-        <v>0.007071484609182941</v>
+        <v>0.006467756786088693</v>
       </c>
       <c r="I1059">
-        <v>0.06555563062039038</v>
+        <v>0.07522331664118909</v>
       </c>
       <c r="J1059">
-        <v>0.7283958957821177</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1059">
-        <v>3.66</v>
+        <v>3.26</v>
       </c>
       <c r="L1059">
-        <v>4.34</v>
+        <v>4.05</v>
       </c>
       <c r="M1059">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1059">
-        <v>4.34</v>
+        <v>4.04</v>
       </c>
       <c r="O1059">
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1060" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1060">
-        <v>1.540367267690522</v>
+        <v>1.683701706464267</v>
       </c>
       <c r="D1060" t="s">
-        <v>372</v>
+        <v>227</v>
       </c>
       <c r="E1060">
-        <v>1.624194569973482</v>
+        <v>1.612243213911307</v>
       </c>
       <c r="F1060">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.006959632732309478</v>
+        <v>0.006336298293535732</v>
       </c>
       <c r="H1060">
-        <v>0.006795805430026517</v>
+        <v>0.006467756786088693</v>
       </c>
       <c r="I1060">
-        <v>0.08382730228296031</v>
+        <v>0.07145849255296044</v>
       </c>
       <c r="J1060">
-        <v>0.7283958957821177</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1060">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="L1060">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="M1060">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1060">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1060">
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1061" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C1061">
-        <v>1.675429379750296</v>
+        <v>1.682689847193684</v>
       </c>
       <c r="D1061" t="s">
         <v>227</v>
       </c>
       <c r="E1061">
-        <v>1.599873749129906</v>
+        <v>1.612243213911307</v>
       </c>
       <c r="F1061">
         <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.006424570620249703</v>
+        <v>0.006277310152806315</v>
       </c>
       <c r="H1061">
-        <v>0.006480126250870095</v>
+        <v>0.006467756786088693</v>
       </c>
       <c r="I1061">
-        <v>0.07555563062039061</v>
+        <v>0.07044663328237766</v>
       </c>
       <c r="J1061">
-        <v>0.7283958957821177</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1061">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1061">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1061">
         <v>3.35</v>
@@ -54936,51 +54936,51 @@
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1062" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C1062">
-        <v>1.671849174539402</v>
+        <v>1.674071021437449</v>
       </c>
       <c r="D1062" t="s">
-        <v>227</v>
+        <v>370</v>
       </c>
       <c r="E1062">
-        <v>1.599873749129906</v>
+        <v>1.608515390817058</v>
       </c>
       <c r="F1062">
         <v>-1</v>
       </c>
       <c r="G1062">
-        <v>0.006348150825460598</v>
+        <v>0.007005928978562551</v>
       </c>
       <c r="H1062">
-        <v>0.006480126250870095</v>
+        <v>0.007071484609182941</v>
       </c>
       <c r="I1062">
-        <v>0.0719754254094962</v>
+        <v>0.06555563062039038</v>
       </c>
       <c r="J1062">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1062">
-        <v>3.21</v>
+        <v>3.66</v>
       </c>
       <c r="L1062">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="M1062">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1062">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="O1062">
         <v>1</v>
@@ -54991,46 +54991,46 @@
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1063" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C1063">
-        <v>1.670985010370687</v>
+        <v>1.540367267690522</v>
       </c>
       <c r="D1063" t="s">
-        <v>227</v>
+        <v>371</v>
       </c>
       <c r="E1063">
-        <v>1.599873749129906</v>
+        <v>1.624194569973482</v>
       </c>
       <c r="F1063">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1063">
-        <v>0.006289014989629313</v>
+        <v>0.006959632732309478</v>
       </c>
       <c r="H1063">
-        <v>0.006480126250870095</v>
+        <v>0.006795805430026517</v>
       </c>
       <c r="I1063">
-        <v>0.07111126124078115</v>
+        <v>0.08382730228296031</v>
       </c>
       <c r="J1063">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1063">
-        <v>3.17</v>
+        <v>3.72</v>
       </c>
       <c r="L1063">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1063">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N1063">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="O1063">
         <v>1</v>
@@ -55041,90 +55041,90 @@
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1064" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C1064">
-        <v>1.525149479713785</v>
+        <v>1.675429379750296</v>
       </c>
       <c r="D1064" t="s">
-        <v>372</v>
+        <v>227</v>
       </c>
       <c r="E1064">
-        <v>1.609672218544069</v>
+        <v>1.599873749129906</v>
       </c>
       <c r="F1064">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1064">
-        <v>0.006974850520286215</v>
+        <v>0.006424570620249703</v>
       </c>
       <c r="H1064">
-        <v>0.00681032778145593</v>
+        <v>0.006480126250870095</v>
       </c>
       <c r="I1064">
-        <v>0.08452273883028427</v>
+        <v>0.07555563062039061</v>
       </c>
       <c r="J1064">
-        <v>0.7324866990016706</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1064">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1064">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1064">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1064">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1064">
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>221</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1065" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C1065">
-        <v>1.662093361254554</v>
+        <v>1.671849174539402</v>
       </c>
       <c r="D1065" t="s">
         <v>227</v>
       </c>
       <c r="E1065">
-        <v>1.586169558344404</v>
+        <v>1.599873749129906</v>
       </c>
       <c r="F1065">
         <v>-1</v>
       </c>
       <c r="G1065">
-        <v>0.006437906638745446</v>
+        <v>0.006348150825460598</v>
       </c>
       <c r="H1065">
-        <v>0.006493830441655597</v>
+        <v>0.006480126250870095</v>
       </c>
       <c r="I1065">
-        <v>0.07592380291015033</v>
+        <v>0.0719754254094962</v>
       </c>
       <c r="J1065">
-        <v>0.7324866990016706</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1065">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1065">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1065">
         <v>3.35</v>
@@ -55136,45 +55136,45 @@
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>221</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1066" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C1066">
-        <v>1.658717696204637</v>
+        <v>1.670985010370687</v>
       </c>
       <c r="D1066" t="s">
         <v>227</v>
       </c>
       <c r="E1066">
-        <v>1.586169558344404</v>
+        <v>1.599873749129906</v>
       </c>
       <c r="F1066">
         <v>-1</v>
       </c>
       <c r="G1066">
-        <v>0.006361282303795362</v>
+        <v>0.006289014989629313</v>
       </c>
       <c r="H1066">
-        <v>0.006493830441655597</v>
+        <v>0.006480126250870095</v>
       </c>
       <c r="I1066">
-        <v>0.07254813786023373</v>
+        <v>0.07111126124078115</v>
       </c>
       <c r="J1066">
-        <v>0.7324866990016706</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1066">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1066">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1066">
         <v>3.35</v>
@@ -55186,51 +55186,51 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>221</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1067" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C1067">
-        <v>1.658017164164704</v>
+        <v>1.525149479713785</v>
       </c>
       <c r="D1067" t="s">
-        <v>227</v>
+        <v>371</v>
       </c>
       <c r="E1067">
-        <v>1.586169558344404</v>
+        <v>1.609672218544069</v>
       </c>
       <c r="F1067">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1067">
-        <v>0.006301982835835296</v>
+        <v>0.006974850520286215</v>
       </c>
       <c r="H1067">
-        <v>0.006493830441655597</v>
+        <v>0.00681032778145593</v>
       </c>
       <c r="I1067">
-        <v>0.07184760582030059</v>
+        <v>0.08452273883028427</v>
       </c>
       <c r="J1067">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1067">
-        <v>3.17</v>
+        <v>3.72</v>
       </c>
       <c r="L1067">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1067">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N1067">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="O1067">
         <v>1</v>
@@ -55241,90 +55241,90 @@
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1068" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C1068">
-        <v>1.515332066574131</v>
+        <v>1.662093361254554</v>
       </c>
       <c r="D1068" t="s">
-        <v>372</v>
+        <v>227</v>
       </c>
       <c r="E1068">
-        <v>1.600303450628539</v>
+        <v>1.586169558344404</v>
       </c>
       <c r="F1068">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1068">
-        <v>0.00698466793342587</v>
+        <v>0.006437906638745446</v>
       </c>
       <c r="H1068">
-        <v>0.006819696549371461</v>
+        <v>0.006493830441655597</v>
       </c>
       <c r="I1068">
-        <v>0.08497138405440863</v>
+        <v>0.07592380291015033</v>
       </c>
       <c r="J1068">
-        <v>0.7351257885553412</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1068">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1068">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1068">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1068">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1068">
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>370</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1069" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C1069">
-        <v>1.653489929309588</v>
+        <v>1.658717696204637</v>
       </c>
       <c r="D1069" t="s">
         <v>227</v>
       </c>
       <c r="E1069">
-        <v>1.577328608339607</v>
+        <v>1.586169558344404</v>
       </c>
       <c r="F1069">
         <v>-1</v>
       </c>
       <c r="G1069">
-        <v>0.006446510070690412</v>
+        <v>0.006361282303795362</v>
       </c>
       <c r="H1069">
-        <v>0.006502671391660392</v>
+        <v>0.006493830441655597</v>
       </c>
       <c r="I1069">
-        <v>0.07616132096998074</v>
+        <v>0.07254813786023373</v>
       </c>
       <c r="J1069">
-        <v>0.7351257885553412</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1069">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1069">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1069">
         <v>3.35</v>
@@ -55336,45 +55336,45 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>370</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1070" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C1070">
-        <v>1.650246218737355</v>
+        <v>1.658017164164704</v>
       </c>
       <c r="D1070" t="s">
         <v>227</v>
       </c>
       <c r="E1070">
-        <v>1.577328608339607</v>
+        <v>1.586169558344404</v>
       </c>
       <c r="F1070">
         <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.006369753781262645</v>
+        <v>0.006301982835835296</v>
       </c>
       <c r="H1070">
-        <v>0.006502671391660392</v>
+        <v>0.006493830441655597</v>
       </c>
       <c r="I1070">
-        <v>0.07291761039774736</v>
+        <v>0.07184760582030059</v>
       </c>
       <c r="J1070">
-        <v>0.7351257885553412</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1070">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1070">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1070">
         <v>3.35</v>
@@ -55386,51 +55386,51 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>370</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1071" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C1071">
-        <v>1.649651250279569</v>
+        <v>1.515332066574131</v>
       </c>
       <c r="D1071" t="s">
-        <v>227</v>
+        <v>371</v>
       </c>
       <c r="E1071">
-        <v>1.577328608339607</v>
+        <v>1.600303450628539</v>
       </c>
       <c r="F1071">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1071">
-        <v>0.006310348749720431</v>
+        <v>0.00698466793342587</v>
       </c>
       <c r="H1071">
-        <v>0.006502671391660392</v>
+        <v>0.006819696549371461</v>
       </c>
       <c r="I1071">
-        <v>0.07232264193996141</v>
+        <v>0.08497138405440863</v>
       </c>
       <c r="J1071">
         <v>0.7351257885553412</v>
       </c>
       <c r="K1071">
-        <v>3.17</v>
+        <v>3.72</v>
       </c>
       <c r="L1071">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1071">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N1071">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="O1071">
         <v>1</v>
@@ -55441,34 +55441,34 @@
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1072" t="s">
         <v>223</v>
       </c>
       <c r="C1072">
-        <v>1.642949101014034</v>
+        <v>1.653489929309588</v>
       </c>
       <c r="D1072" t="s">
         <v>227</v>
       </c>
       <c r="E1072">
-        <v>1.566496775581906</v>
+        <v>1.577328608339607</v>
       </c>
       <c r="F1072">
         <v>-1</v>
       </c>
       <c r="G1072">
-        <v>0.006457050898985965</v>
+        <v>0.006446510070690412</v>
       </c>
       <c r="H1072">
-        <v>0.006513503224418095</v>
+        <v>0.006502671391660392</v>
       </c>
       <c r="I1072">
-        <v>0.0764523254321281</v>
+        <v>0.07616132096998074</v>
       </c>
       <c r="J1072">
-        <v>0.7383591714680878</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1072">
         <v>3.26</v>
@@ -55486,39 +55486,39 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>220</v>
+        <v>370</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1073" t="s">
         <v>225</v>
       </c>
       <c r="C1073">
-        <v>1.639867059587438</v>
+        <v>1.650246218737355</v>
       </c>
       <c r="D1073" t="s">
         <v>227</v>
       </c>
       <c r="E1073">
-        <v>1.566496775581906</v>
+        <v>1.577328608339607</v>
       </c>
       <c r="F1073">
         <v>-1</v>
       </c>
       <c r="G1073">
-        <v>0.006380132940412562</v>
+        <v>0.006369753781262645</v>
       </c>
       <c r="H1073">
-        <v>0.006513503224418095</v>
+        <v>0.006502671391660392</v>
       </c>
       <c r="I1073">
-        <v>0.07337028400553214</v>
+        <v>0.07291761039774736</v>
       </c>
       <c r="J1073">
-        <v>0.7383591714680878</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1073">
         <v>3.21</v>
@@ -55536,39 +55536,39 @@
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>220</v>
+        <v>370</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1074" t="s">
         <v>226</v>
       </c>
       <c r="C1074">
-        <v>1.639401426446162</v>
+        <v>1.649651250279569</v>
       </c>
       <c r="D1074" t="s">
         <v>227</v>
       </c>
       <c r="E1074">
-        <v>1.566496775581906</v>
+        <v>1.577328608339607</v>
       </c>
       <c r="F1074">
         <v>-1</v>
       </c>
       <c r="G1074">
-        <v>0.006320598573553837</v>
+        <v>0.006310348749720431</v>
       </c>
       <c r="H1074">
-        <v>0.006513503224418095</v>
+        <v>0.006502671391660392</v>
       </c>
       <c r="I1074">
-        <v>0.07290465086425613</v>
+        <v>0.07232264193996141</v>
       </c>
       <c r="J1074">
-        <v>0.7383591714680878</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1074">
         <v>3.17</v>
@@ -55586,7 +55586,7 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>220</v>
+        <v>370</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
@@ -55597,28 +55597,28 @@
         <v>223</v>
       </c>
       <c r="C1075">
-        <v>1.624740047284429</v>
+        <v>1.642949101014034</v>
       </c>
       <c r="D1075" t="s">
         <v>227</v>
       </c>
       <c r="E1075">
-        <v>1.547785017914981</v>
+        <v>1.566496775581906</v>
       </c>
       <c r="F1075">
         <v>-1</v>
       </c>
       <c r="G1075">
-        <v>0.00647525995271557</v>
+        <v>0.006457050898985965</v>
       </c>
       <c r="H1075">
-        <v>0.00653221498208502</v>
+        <v>0.006513503224418095</v>
       </c>
       <c r="I1075">
-        <v>0.07695502936944809</v>
+        <v>0.0764523254321281</v>
       </c>
       <c r="J1075">
-        <v>0.7439447707716474</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1075">
         <v>3.26</v>
@@ -55636,7 +55636,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>497</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55647,28 +55647,28 @@
         <v>225</v>
       </c>
       <c r="C1076">
-        <v>1.621937285823011</v>
+        <v>1.639867059587438</v>
       </c>
       <c r="D1076" t="s">
         <v>227</v>
       </c>
       <c r="E1076">
-        <v>1.547785017914981</v>
+        <v>1.566496775581906</v>
       </c>
       <c r="F1076">
         <v>-1</v>
       </c>
       <c r="G1076">
-        <v>0.006398062714176988</v>
+        <v>0.006380132940412562</v>
       </c>
       <c r="H1076">
-        <v>0.00653221498208502</v>
+        <v>0.006513503224418095</v>
       </c>
       <c r="I1076">
-        <v>0.0741522679080302</v>
+        <v>0.07337028400553214</v>
       </c>
       <c r="J1076">
-        <v>0.7439447707716474</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1076">
         <v>3.21</v>
@@ -55686,7 +55686,7 @@
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>497</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
@@ -55697,28 +55697,28 @@
         <v>226</v>
       </c>
       <c r="C1077">
-        <v>1.621695076653878</v>
+        <v>1.639401426446162</v>
       </c>
       <c r="D1077" t="s">
         <v>227</v>
       </c>
       <c r="E1077">
-        <v>1.547785017914981</v>
+        <v>1.566496775581906</v>
       </c>
       <c r="F1077">
         <v>-1</v>
       </c>
       <c r="G1077">
-        <v>0.006338304923346122</v>
+        <v>0.006320598573553837</v>
       </c>
       <c r="H1077">
-        <v>0.00653221498208502</v>
+        <v>0.006513503224418095</v>
       </c>
       <c r="I1077">
-        <v>0.07391005873889656</v>
+        <v>0.07290465086425613</v>
       </c>
       <c r="J1077">
-        <v>0.7439447707716474</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1077">
         <v>3.17</v>
@@ -55736,7 +55736,7 @@
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>497</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1078" spans="1:16">
@@ -55747,28 +55747,28 @@
         <v>223</v>
       </c>
       <c r="C1078">
-        <v>1.61016227805581</v>
+        <v>1.624740047284429</v>
       </c>
       <c r="D1078" t="s">
         <v>227</v>
       </c>
       <c r="E1078">
-        <v>1.532804794934651</v>
+        <v>1.547785017914981</v>
       </c>
       <c r="F1078">
         <v>-1</v>
       </c>
       <c r="G1078">
-        <v>0.006489837721944189</v>
+        <v>0.00647525995271557</v>
       </c>
       <c r="H1078">
-        <v>0.006547195205065348</v>
+        <v>0.00653221498208502</v>
       </c>
       <c r="I1078">
-        <v>0.07735748312115875</v>
+        <v>0.07695502936944809</v>
       </c>
       <c r="J1078">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1078">
         <v>3.26</v>
@@ -55786,7 +55786,7 @@
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
@@ -55797,28 +55797,28 @@
         <v>225</v>
       </c>
       <c r="C1079">
-        <v>1.607583102012009</v>
+        <v>1.621937285823011</v>
       </c>
       <c r="D1079" t="s">
         <v>227</v>
       </c>
       <c r="E1079">
-        <v>1.532804794934651</v>
+        <v>1.547785017914981</v>
       </c>
       <c r="F1079">
         <v>-1</v>
       </c>
       <c r="G1079">
-        <v>0.00641241689798799</v>
+        <v>0.006398062714176988</v>
       </c>
       <c r="H1079">
-        <v>0.006547195205065348</v>
+        <v>0.00653221498208502</v>
       </c>
       <c r="I1079">
-        <v>0.074778307077358</v>
+        <v>0.0741522679080302</v>
       </c>
       <c r="J1079">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1079">
         <v>3.21</v>
@@ -55836,7 +55836,7 @@
         <v>1</v>
       </c>
       <c r="P1079" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1080" spans="1:16">
@@ -55847,28 +55847,28 @@
         <v>226</v>
       </c>
       <c r="C1080">
-        <v>1.607519761176969</v>
+        <v>1.621695076653878</v>
       </c>
       <c r="D1080" t="s">
         <v>227</v>
       </c>
       <c r="E1080">
-        <v>1.532804794934651</v>
+        <v>1.547785017914981</v>
       </c>
       <c r="F1080">
         <v>-1</v>
       </c>
       <c r="G1080">
-        <v>0.006352480238823031</v>
+        <v>0.006338304923346122</v>
       </c>
       <c r="H1080">
-        <v>0.006547195205065348</v>
+        <v>0.00653221498208502</v>
       </c>
       <c r="I1080">
-        <v>0.07471496624231744</v>
+        <v>0.07391005873889656</v>
       </c>
       <c r="J1080">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1080">
         <v>3.17</v>
@@ -55886,7 +55886,7 @@
         <v>1</v>
       </c>
       <c r="P1080" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1081" spans="1:16">
@@ -55897,28 +55897,28 @@
         <v>223</v>
       </c>
       <c r="C1081">
-        <v>1.5750931595105</v>
+        <v>1.61016227805581</v>
       </c>
       <c r="D1081" t="s">
-        <v>373</v>
+        <v>227</v>
       </c>
       <c r="E1081">
-        <v>1.527868375834023</v>
+        <v>1.532804794934651</v>
       </c>
       <c r="F1081">
         <v>-1</v>
       </c>
       <c r="G1081">
-        <v>0.0065249068404895</v>
+        <v>0.006489837721944189</v>
       </c>
       <c r="H1081">
-        <v>0.006432131624165977</v>
+        <v>0.006547195205065348</v>
       </c>
       <c r="I1081">
-        <v>0.04722478367647698</v>
+        <v>0.07735748312115875</v>
       </c>
       <c r="J1081">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1081">
         <v>3.26</v>
@@ -55927,16 +55927,16 @@
         <v>4.05</v>
       </c>
       <c r="M1081">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1081">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1081">
         <v>1</v>
       </c>
       <c r="P1081" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1082" spans="1:16">
@@ -55947,28 +55947,28 @@
         <v>225</v>
       </c>
       <c r="C1082">
-        <v>1.573051853383038</v>
+        <v>1.607583102012009</v>
       </c>
       <c r="D1082" t="s">
-        <v>373</v>
+        <v>227</v>
       </c>
       <c r="E1082">
-        <v>1.527868375834023</v>
+        <v>1.532804794934651</v>
       </c>
       <c r="F1082">
         <v>-1</v>
       </c>
       <c r="G1082">
-        <v>0.006446948146616961</v>
+        <v>0.00641241689798799</v>
       </c>
       <c r="H1082">
-        <v>0.006432131624165977</v>
+        <v>0.006547195205065348</v>
       </c>
       <c r="I1082">
-        <v>0.04518347754901519</v>
+        <v>0.074778307077358</v>
       </c>
       <c r="J1082">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1082">
         <v>3.21</v>
@@ -55977,16 +55977,16 @@
         <v>4.01</v>
       </c>
       <c r="M1082">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1082">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1082">
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
@@ -55997,28 +55997,28 @@
         <v>226</v>
       </c>
       <c r="C1083">
-        <v>1.573418808481069</v>
+        <v>1.607519761176969</v>
       </c>
       <c r="D1083" t="s">
         <v>227</v>
       </c>
       <c r="E1083">
-        <v>1.496767510539931</v>
+        <v>1.532804794934651</v>
       </c>
       <c r="F1083">
         <v>-1</v>
       </c>
       <c r="G1083">
-        <v>0.006386581191518931</v>
+        <v>0.006352480238823031</v>
       </c>
       <c r="H1083">
-        <v>0.006583232489460069</v>
+        <v>0.006547195205065348</v>
       </c>
       <c r="I1083">
-        <v>0.07665129794113801</v>
+        <v>0.07471496624231744</v>
       </c>
       <c r="J1083">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1083">
         <v>3.17</v>
@@ -56036,51 +56036,51 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
       <c r="A1084" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1084" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1084">
-        <v>1.47676751053993</v>
+        <v>1.5750931595105</v>
       </c>
       <c r="D1084" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E1084">
-        <v>1.517134465637962</v>
+        <v>1.527868375834023</v>
       </c>
       <c r="F1084">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1084">
-        <v>0.006563232489460068</v>
+        <v>0.0065249068404895</v>
       </c>
       <c r="H1084">
-        <v>0.006542865534362039</v>
+        <v>0.006432131624165977</v>
       </c>
       <c r="I1084">
-        <v>0.04036695509803101</v>
+        <v>0.04722478367647698</v>
       </c>
       <c r="J1084">
         <v>0.7591738774507669</v>
       </c>
       <c r="K1084">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="L1084">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="M1084">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N1084">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="O1084">
         <v>1</v>
@@ -56091,40 +56091,40 @@
     </row>
     <row r="1085" spans="1:16">
       <c r="A1085" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1085" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C1085">
-        <v>1.560901809388644</v>
+        <v>1.573051853383038</v>
       </c>
       <c r="D1085" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E1085">
-        <v>1.513807620958687</v>
+        <v>1.527868375834023</v>
       </c>
       <c r="F1085">
         <v>-1</v>
       </c>
       <c r="G1085">
-        <v>0.006539098190611355</v>
+        <v>0.006446948146616961</v>
       </c>
       <c r="H1085">
-        <v>0.006446192379041313</v>
+        <v>0.006432131624165977</v>
       </c>
       <c r="I1085">
-        <v>0.04709418842995694</v>
+        <v>0.04518347754901519</v>
       </c>
       <c r="J1085">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1085">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1085">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1085">
         <v>3.23</v>
@@ -56136,107 +56136,107 @@
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
       <c r="A1086" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1086" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C1086">
-        <v>1.559078162005382</v>
+        <v>1.573418808481069</v>
       </c>
       <c r="D1086" t="s">
-        <v>373</v>
+        <v>227</v>
       </c>
       <c r="E1086">
-        <v>1.513807620958687</v>
+        <v>1.496767510539931</v>
       </c>
       <c r="F1086">
         <v>-1</v>
       </c>
       <c r="G1086">
-        <v>0.006460921837994617</v>
+        <v>0.006386581191518931</v>
       </c>
       <c r="H1086">
-        <v>0.006446192379041313</v>
+        <v>0.006583232489460069</v>
       </c>
       <c r="I1086">
-        <v>0.04527054104669537</v>
+        <v>0.07665129794113801</v>
       </c>
       <c r="J1086">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1086">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1086">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1086">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1086">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1086">
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
       <c r="A1087" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1087" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C1087">
-        <v>1.482184374678515</v>
+        <v>1.47676751053993</v>
       </c>
       <c r="D1087" t="s">
         <v>369</v>
       </c>
       <c r="E1087">
-        <v>1.502725456771905</v>
+        <v>1.499909681961485</v>
       </c>
       <c r="F1087">
         <v>1</v>
       </c>
       <c r="G1087">
-        <v>0.006597815625321486</v>
+        <v>0.006563232489460068</v>
       </c>
       <c r="H1087">
-        <v>0.006557274543228095</v>
+        <v>0.006480090318038516</v>
       </c>
       <c r="I1087">
-        <v>0.02054108209339089</v>
+        <v>0.02314217142155428</v>
       </c>
       <c r="J1087">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1087">
         <v>3.35</v>
       </c>
       <c r="L1087">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="M1087">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N1087">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="O1087">
         <v>1</v>
       </c>
       <c r="P1087" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1088" spans="1:16">
@@ -56247,28 +56247,28 @@
         <v>223</v>
       </c>
       <c r="C1088">
-        <v>1.553174199563495</v>
+        <v>1.560901809388644</v>
       </c>
       <c r="D1088" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E1088">
-        <v>1.51615112410739</v>
+        <v>1.513807620958687</v>
       </c>
       <c r="F1088">
         <v>-1</v>
       </c>
       <c r="G1088">
-        <v>0.006546825800436505</v>
+        <v>0.006539098190611355</v>
       </c>
       <c r="H1088">
-        <v>0.006463848875892611</v>
+        <v>0.006446192379041313</v>
       </c>
       <c r="I1088">
-        <v>0.03702307545610539</v>
+        <v>0.04709418842995694</v>
       </c>
       <c r="J1088">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1088">
         <v>3.26</v>
@@ -56280,13 +56280,13 @@
         <v>3.23</v>
       </c>
       <c r="N1088">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="O1088">
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>372</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56297,28 +56297,28 @@
         <v>225</v>
       </c>
       <c r="C1089">
-        <v>1.551469073803319</v>
+        <v>1.559078162005382</v>
       </c>
       <c r="D1089" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E1089">
-        <v>1.51615112410739</v>
+        <v>1.513807620958687</v>
       </c>
       <c r="F1089">
         <v>-1</v>
       </c>
       <c r="G1089">
-        <v>0.006468530926196681</v>
+        <v>0.006460921837994617</v>
       </c>
       <c r="H1089">
-        <v>0.006463848875892611</v>
+        <v>0.006446192379041313</v>
       </c>
       <c r="I1089">
-        <v>0.03531794969592905</v>
+        <v>0.04527054104669537</v>
       </c>
       <c r="J1089">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1089">
         <v>3.21</v>
@@ -56330,13 +56330,13 @@
         <v>3.23</v>
       </c>
       <c r="N1089">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="O1089">
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>372</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -56344,90 +56344,90 @@
         <v>2</v>
       </c>
       <c r="B1090" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C1090">
-        <v>1.474243425931813</v>
+        <v>1.559619244098773</v>
       </c>
       <c r="D1090" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E1090">
-        <v>1.494879325323672</v>
+        <v>1.520360727295253</v>
       </c>
       <c r="F1090">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1090">
-        <v>0.006605756574068187</v>
+        <v>0.006400380755901226</v>
       </c>
       <c r="H1090">
-        <v>0.006565120674676329</v>
+        <v>0.006559639272704747</v>
       </c>
       <c r="I1090">
-        <v>0.02063589939185917</v>
+        <v>0.03925851680352022</v>
       </c>
       <c r="J1090">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1090">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="L1090">
+        <v>3.98</v>
+      </c>
+      <c r="M1090">
+        <v>3.3</v>
+      </c>
+      <c r="N1090">
         <v>4.04</v>
       </c>
-      <c r="M1090">
-        <v>3.31</v>
-      </c>
-      <c r="N1090">
-        <v>4.03</v>
-      </c>
       <c r="O1090">
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>372</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
       <c r="A1091" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1091" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C1091">
-        <v>1.54817973372066</v>
+        <v>1.482184374678515</v>
       </c>
       <c r="D1091" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E1091">
-        <v>1.511202619606667</v>
+        <v>1.485631268341949</v>
       </c>
       <c r="F1091">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1091">
-        <v>0.00655182026627934</v>
+        <v>0.006597815625321486</v>
       </c>
       <c r="H1091">
-        <v>0.006468797380393333</v>
+        <v>0.006494368731658051</v>
       </c>
       <c r="I1091">
-        <v>0.03697711411399318</v>
+        <v>0.003446893663434203</v>
       </c>
       <c r="J1091">
-        <v>0.7674295295335398</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1091">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="L1091">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="M1091">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="N1091">
         <v>3.99</v>
@@ -56436,51 +56436,51 @@
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>371</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
       <c r="A1092" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1092" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C1092">
-        <v>1.546551210197337</v>
+        <v>1.553174199563495</v>
       </c>
       <c r="D1092" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E1092">
-        <v>1.511202619606667</v>
+        <v>1.50615112410739</v>
       </c>
       <c r="F1092">
         <v>-1</v>
       </c>
       <c r="G1092">
-        <v>0.006473448789802663</v>
+        <v>0.006546825800436505</v>
       </c>
       <c r="H1092">
-        <v>0.006468797380393333</v>
+        <v>0.006453848875892611</v>
       </c>
       <c r="I1092">
-        <v>0.03534859059067008</v>
+        <v>0.04702307545610562</v>
       </c>
       <c r="J1092">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1092">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="L1092">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M1092">
         <v>3.23</v>
       </c>
       <c r="N1092">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="O1092">
         <v>1</v>
@@ -56491,46 +56491,46 @@
     </row>
     <row r="1093" spans="1:16">
       <c r="A1093" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1093" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C1093">
-        <v>1.469111076062641</v>
+        <v>1.551469073803319</v>
       </c>
       <c r="D1093" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E1093">
-        <v>1.489808257243983</v>
+        <v>1.50615112410739</v>
       </c>
       <c r="F1093">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1093">
-        <v>0.006610888923937359</v>
+        <v>0.006468530926196681</v>
       </c>
       <c r="H1093">
-        <v>0.006570191742756017</v>
+        <v>0.006453848875892611</v>
       </c>
       <c r="I1093">
-        <v>0.02069718118134212</v>
+        <v>0.04531794969592928</v>
       </c>
       <c r="J1093">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1093">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="L1093">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="M1093">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N1093">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="O1093">
         <v>1</v>
@@ -56541,43 +56541,43 @@
     </row>
     <row r="1094" spans="1:16">
       <c r="A1094" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1094" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C1094">
-        <v>1.544139279885719</v>
+        <v>1.474243425931813</v>
       </c>
       <c r="D1094" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E1094">
-        <v>1.507199347862231</v>
+        <v>1.477856249867566</v>
       </c>
       <c r="F1094">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1094">
-        <v>0.006555860720114281</v>
+        <v>0.006605756574068187</v>
       </c>
       <c r="H1094">
-        <v>0.00647280065213777</v>
+        <v>0.006502143750132435</v>
       </c>
       <c r="I1094">
-        <v>0.036939932023488</v>
+        <v>0.003612823935753351</v>
       </c>
       <c r="J1094">
-        <v>0.7686689325503931</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1094">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="L1094">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="M1094">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="N1094">
         <v>3.99</v>
@@ -56586,45 +56586,45 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>501</v>
+        <v>371</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
       <c r="A1095" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1095" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C1095">
-        <v>1.542572726513238</v>
+        <v>1.54817973372066</v>
       </c>
       <c r="D1095" t="s">
         <v>374</v>
       </c>
       <c r="E1095">
-        <v>1.507199347862231</v>
+        <v>1.511202619606667</v>
       </c>
       <c r="F1095">
         <v>-1</v>
       </c>
       <c r="G1095">
-        <v>0.006477427273486762</v>
+        <v>0.00655182026627934</v>
       </c>
       <c r="H1095">
-        <v>0.00647280065213777</v>
+        <v>0.006468797380393333</v>
       </c>
       <c r="I1095">
-        <v>0.03537337865100731</v>
+        <v>0.03697711411399318</v>
       </c>
       <c r="J1095">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1095">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="L1095">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M1095">
         <v>3.23</v>
@@ -56641,46 +56641,46 @@
     </row>
     <row r="1096" spans="1:16">
       <c r="A1096" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1096" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C1096">
-        <v>1.464959075956183</v>
+        <v>1.546551210197337</v>
       </c>
       <c r="D1096" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1096">
-        <v>1.485705833258199</v>
+        <v>1.511202619606667</v>
       </c>
       <c r="F1096">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1096">
-        <v>0.006615040924043817</v>
+        <v>0.006473448789802663</v>
       </c>
       <c r="H1096">
-        <v>0.006574294166741802</v>
+        <v>0.006468797380393333</v>
       </c>
       <c r="I1096">
-        <v>0.02074675730201569</v>
+        <v>0.03534859059067008</v>
       </c>
       <c r="J1096">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1096">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="L1096">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="M1096">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N1096">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="O1096">
         <v>1</v>
@@ -56691,43 +56691,43 @@
     </row>
     <row r="1097" spans="1:16">
       <c r="A1097" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1097" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1097">
-        <v>1.542905840445619</v>
+        <v>1.469111076062641</v>
       </c>
       <c r="D1097" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E1097">
-        <v>1.507534537270826</v>
+        <v>1.47283114312999</v>
       </c>
       <c r="F1097">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1097">
-        <v>0.006477094159554382</v>
+        <v>0.006610888923937359</v>
       </c>
       <c r="H1097">
-        <v>0.006472465462729175</v>
+        <v>0.006507168856870011</v>
       </c>
       <c r="I1097">
-        <v>0.03537130317479287</v>
+        <v>0.003720067067348509</v>
       </c>
       <c r="J1097">
-        <v>0.7685651587396826</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1097">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="L1097">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="M1097">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="N1097">
         <v>3.99</v>
@@ -56736,89 +56736,89 @@
         <v>1</v>
       </c>
       <c r="P1097" t="s">
-        <v>223</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1098" spans="1:16">
       <c r="A1098" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1098" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C1098">
-        <v>1.465306718222064</v>
+        <v>1.544139279885719</v>
       </c>
       <c r="D1098" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1098">
-        <v>1.486049324571651</v>
+        <v>1.507199347862231</v>
       </c>
       <c r="F1098">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1098">
-        <v>0.006614693281777937</v>
+        <v>0.006555860720114281</v>
       </c>
       <c r="H1098">
-        <v>0.00657395067542835</v>
+        <v>0.00647280065213777</v>
       </c>
       <c r="I1098">
-        <v>0.02074260634958724</v>
+        <v>0.036939932023488</v>
       </c>
       <c r="J1098">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1098">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="L1098">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="M1098">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N1098">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="O1098">
         <v>1</v>
       </c>
       <c r="P1098" t="s">
-        <v>223</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1099" spans="1:16">
       <c r="A1099" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1099" t="s">
         <v>225</v>
       </c>
       <c r="C1099">
-        <v>1.54632868625525</v>
+        <v>1.542572726513238</v>
       </c>
       <c r="D1099" t="s">
         <v>374</v>
       </c>
       <c r="E1099">
-        <v>1.510978709222573</v>
+        <v>1.507199347862231</v>
       </c>
       <c r="F1099">
         <v>-1</v>
       </c>
       <c r="G1099">
-        <v>0.006473671313744749</v>
+        <v>0.006477427273486762</v>
       </c>
       <c r="H1099">
-        <v>0.006469021290777427</v>
+        <v>0.00647280065213777</v>
       </c>
       <c r="I1099">
-        <v>0.03534997703267706</v>
+        <v>0.03537337865100731</v>
       </c>
       <c r="J1099">
-        <v>0.7674988516338783</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1099">
         <v>3.21</v>
@@ -56841,34 +56841,34 @@
     </row>
     <row r="1100" spans="1:16">
       <c r="A1100" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1100" t="s">
         <v>227</v>
       </c>
       <c r="C1100">
-        <v>1.468878847026508</v>
+        <v>1.464959075956183</v>
       </c>
       <c r="D1100" t="s">
         <v>369</v>
       </c>
       <c r="E1100">
-        <v>1.489578801091863</v>
+        <v>1.468765901234711</v>
       </c>
       <c r="F1100">
         <v>1</v>
       </c>
       <c r="G1100">
-        <v>0.006611121152973493</v>
+        <v>0.006615040924043817</v>
       </c>
       <c r="H1100">
-        <v>0.006570421198908138</v>
+        <v>0.00651123409876529</v>
       </c>
       <c r="I1100">
-        <v>0.02069995406535519</v>
+        <v>0.003806825278527715</v>
       </c>
       <c r="J1100">
-        <v>0.7674988516338783</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1100">
         <v>3.35</v>
@@ -56877,10 +56877,10 @@
         <v>4.04</v>
       </c>
       <c r="M1100">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N1100">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="O1100">
         <v>1</v>
@@ -56894,99 +56894,99 @@
         <v>0</v>
       </c>
       <c r="B1101" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C1101">
-        <v>1.462972238067567</v>
+        <v>1.542905840445619</v>
       </c>
       <c r="D1101" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E1101">
-        <v>1.483742718807059</v>
+        <v>1.497534537270826</v>
       </c>
       <c r="F1101">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1101">
-        <v>0.006617027761932433</v>
+        <v>0.006477094159554382</v>
       </c>
       <c r="H1101">
-        <v>0.006576257281192941</v>
+        <v>0.006462465462729174</v>
       </c>
       <c r="I1101">
-        <v>0.02077048073949195</v>
+        <v>0.0453713031747931</v>
       </c>
       <c r="J1101">
-        <v>0.7692620184872934</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1101">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="L1101">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="M1101">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N1101">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="O1101">
         <v>1</v>
       </c>
       <c r="P1101" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="1102" spans="1:16">
       <c r="A1102" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1102">
-        <v>1.541874717879155</v>
+        <v>1.465306718222064</v>
       </c>
       <c r="D1102" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
       <c r="E1102">
-        <v>1.463432272837593</v>
+        <v>1.469106279333841</v>
       </c>
       <c r="F1102">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1102">
-        <v>0.006418125282120845</v>
+        <v>0.006614693281777937</v>
       </c>
       <c r="H1102">
-        <v>0.006616567727162407</v>
+        <v>0.006510893720666159</v>
       </c>
       <c r="I1102">
-        <v>0.07844244504156217</v>
+        <v>0.003799561111777816</v>
       </c>
       <c r="J1102">
-        <v>0.7691246946753454</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1102">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1102">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="M1102">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N1102">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="O1102">
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
@@ -56994,49 +56994,49 @@
         <v>0</v>
       </c>
       <c r="B1103" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C1103">
-        <v>1.531416807455531</v>
+        <v>1.54632868625525</v>
       </c>
       <c r="D1103" t="s">
-        <v>227</v>
+        <v>372</v>
       </c>
       <c r="E1103">
-        <v>1.452380537847327</v>
+        <v>1.500978709222573</v>
       </c>
       <c r="F1103">
         <v>-1</v>
       </c>
       <c r="G1103">
-        <v>0.006428583192544469</v>
+        <v>0.006473671313744749</v>
       </c>
       <c r="H1103">
-        <v>0.006627619462152673</v>
+        <v>0.006459021290777427</v>
       </c>
       <c r="I1103">
-        <v>0.07903626960820365</v>
+        <v>0.04534997703267729</v>
       </c>
       <c r="J1103">
-        <v>0.772423720045574</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1103">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="L1103">
+        <v>4.01</v>
+      </c>
+      <c r="M1103">
+        <v>3.23</v>
+      </c>
+      <c r="N1103">
         <v>3.98</v>
       </c>
-      <c r="M1103">
-        <v>3.35</v>
-      </c>
-      <c r="N1103">
-        <v>4.04</v>
-      </c>
       <c r="O1103">
         <v>1</v>
       </c>
       <c r="P1103" t="s">
-        <v>373</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1104" spans="1:16">
@@ -57044,93 +57044,93 @@
         <v>1</v>
       </c>
       <c r="B1104" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C1104">
-        <v>1.432380537847326</v>
+        <v>1.547028640320606</v>
       </c>
       <c r="D1104" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E1104">
-        <v>1.47327748664915</v>
+        <v>1.507253789608202</v>
       </c>
       <c r="F1104">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1104">
-        <v>0.006607619462152673</v>
+        <v>0.006412971359679395</v>
       </c>
       <c r="H1104">
-        <v>0.00658672251335085</v>
+        <v>0.006572746210391799</v>
       </c>
       <c r="I1104">
-        <v>0.04089694880182382</v>
+        <v>0.03977485071240405</v>
       </c>
       <c r="J1104">
-        <v>0.772423720045574</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1104">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="L1104">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1104">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N1104">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1104">
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>373</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
       <c r="A1105" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1105" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1105">
-        <v>1.530293964951826</v>
+        <v>1.468878847026508</v>
       </c>
       <c r="D1105" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
       <c r="E1105">
-        <v>1.451193937725116</v>
+        <v>1.47260376664088</v>
       </c>
       <c r="F1105">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1105">
-        <v>0.006429706035048174</v>
+        <v>0.006611121152973493</v>
       </c>
       <c r="H1105">
-        <v>0.006628806062274884</v>
+        <v>0.006507396233359121</v>
       </c>
       <c r="I1105">
-        <v>0.07910002722671017</v>
+        <v>0.003724919614371824</v>
       </c>
       <c r="J1105">
-        <v>0.7727779290372787</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1105">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1105">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="M1105">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N1105">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="O1105">
         <v>1</v>
@@ -57141,52 +57141,52 @@
     </row>
     <row r="1106" spans="1:16">
       <c r="A1106" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1106" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C1106">
-        <v>1.431193937725116</v>
+        <v>1.54143940139528</v>
       </c>
       <c r="D1106" t="s">
-        <v>369</v>
+        <v>227</v>
       </c>
       <c r="E1106">
-        <v>1.472105054886608</v>
+        <v>1.462972238067567</v>
       </c>
       <c r="F1106">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1106">
-        <v>0.006608806062274883</v>
+        <v>0.00641856059860472</v>
       </c>
       <c r="H1106">
-        <v>0.006587894945113392</v>
+        <v>0.006617027761932433</v>
       </c>
       <c r="I1106">
-        <v>0.04091111716149198</v>
+        <v>0.07846716332771297</v>
       </c>
       <c r="J1106">
-        <v>0.7727779290372787</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1106">
+        <v>3.17</v>
+      </c>
+      <c r="L1106">
+        <v>3.98</v>
+      </c>
+      <c r="M1106">
         <v>3.35</v>
       </c>
-      <c r="L1106">
-        <v>4.02</v>
-      </c>
-      <c r="M1106">
-        <v>3.31</v>
-      </c>
       <c r="N1106">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1106">
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>503</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
@@ -57194,49 +57194,49 @@
         <v>0</v>
       </c>
       <c r="B1107" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C1107">
-        <v>1.432233461226324</v>
+        <v>1.541874717879155</v>
       </c>
       <c r="D1107" t="s">
-        <v>369</v>
+        <v>227</v>
       </c>
       <c r="E1107">
-        <v>1.473132166166906</v>
+        <v>1.463432272837593</v>
       </c>
       <c r="F1107">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1107">
-        <v>0.006607766538773674</v>
+        <v>0.006418125282120845</v>
       </c>
       <c r="H1107">
-        <v>0.006586867833833095</v>
+        <v>0.006616567727162407</v>
       </c>
       <c r="I1107">
-        <v>0.04089870494058179</v>
+        <v>0.07844244504156217</v>
       </c>
       <c r="J1107">
-        <v>0.7724676235145299</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1107">
+        <v>3.17</v>
+      </c>
+      <c r="L1107">
+        <v>3.98</v>
+      </c>
+      <c r="M1107">
         <v>3.35</v>
       </c>
-      <c r="L1107">
-        <v>4.02</v>
-      </c>
-      <c r="M1107">
-        <v>3.31</v>
-      </c>
       <c r="N1107">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1107">
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
@@ -57244,81 +57244,81 @@
         <v>0</v>
       </c>
       <c r="B1108" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C1108">
-        <v>1.438192457750358</v>
+        <v>1.531416807455531</v>
       </c>
       <c r="D1108" t="s">
-        <v>369</v>
+        <v>227</v>
       </c>
       <c r="E1108">
-        <v>1.479020010493639</v>
+        <v>1.452380537847327</v>
       </c>
       <c r="F1108">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1108">
-        <v>0.00660180754224964</v>
+        <v>0.006428583192544469</v>
       </c>
       <c r="H1108">
-        <v>0.006580979989506362</v>
+        <v>0.006627619462152673</v>
       </c>
       <c r="I1108">
-        <v>0.0408275527432802</v>
+        <v>0.07903626960820365</v>
       </c>
       <c r="J1108">
-        <v>0.7706888185819823</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1108">
+        <v>3.17</v>
+      </c>
+      <c r="L1108">
+        <v>3.98</v>
+      </c>
+      <c r="M1108">
         <v>3.35</v>
       </c>
-      <c r="L1108">
-        <v>4.02</v>
-      </c>
-      <c r="M1108">
-        <v>3.31</v>
-      </c>
       <c r="N1108">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1108">
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>504</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
       <c r="A1109" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1109" t="s">
         <v>222</v>
       </c>
       <c r="C1109">
-        <v>1.442360905903367</v>
+        <v>1.432380537847326</v>
       </c>
       <c r="D1109" t="s">
         <v>369</v>
       </c>
       <c r="E1109">
-        <v>1.483138686131387</v>
+        <v>1.456450198250518</v>
       </c>
       <c r="F1109">
         <v>1</v>
       </c>
       <c r="G1109">
-        <v>0.006597639094096632</v>
+        <v>0.006607619462152673</v>
       </c>
       <c r="H1109">
-        <v>0.006576861313868614</v>
+        <v>0.006523549801749483</v>
       </c>
       <c r="I1109">
-        <v>0.04077778022801981</v>
+        <v>0.02406966040319114</v>
       </c>
       <c r="J1109">
-        <v>0.7694445057004873</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1109">
         <v>3.35</v>
@@ -57327,16 +57327,16 @@
         <v>4.02</v>
       </c>
       <c r="M1109">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N1109">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="O1109">
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>505</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
@@ -57344,48 +57344,298 @@
         <v>0</v>
       </c>
       <c r="B1110" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1110">
+        <v>1.530293964951826</v>
+      </c>
+      <c r="D1110" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1110">
+        <v>1.451193937725116</v>
+      </c>
+      <c r="F1110">
+        <v>-1</v>
+      </c>
+      <c r="G1110">
+        <v>0.006429706035048174</v>
+      </c>
+      <c r="H1110">
+        <v>0.006628806062274884</v>
+      </c>
+      <c r="I1110">
+        <v>0.07910002722671017</v>
+      </c>
+      <c r="J1110">
+        <v>0.7727779290372787</v>
+      </c>
+      <c r="K1110">
+        <v>3.17</v>
+      </c>
+      <c r="L1110">
+        <v>3.98</v>
+      </c>
+      <c r="M1110">
+        <v>3.35</v>
+      </c>
+      <c r="N1110">
+        <v>4.04</v>
+      </c>
+      <c r="O1110">
+        <v>1</v>
+      </c>
+      <c r="P1110" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:16">
+      <c r="A1111" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1111" t="s">
         <v>222</v>
       </c>
-      <c r="C1110">
+      <c r="C1111">
+        <v>1.431193937725116</v>
+      </c>
+      <c r="D1111" t="s">
+        <v>369</v>
+      </c>
+      <c r="E1111">
+        <v>1.455288392757726</v>
+      </c>
+      <c r="F1111">
+        <v>1</v>
+      </c>
+      <c r="G1111">
+        <v>0.006608806062274883</v>
+      </c>
+      <c r="H1111">
+        <v>0.006524711607242275</v>
+      </c>
+      <c r="I1111">
+        <v>0.02409445503261054</v>
+      </c>
+      <c r="J1111">
+        <v>0.7727779290372787</v>
+      </c>
+      <c r="K1111">
+        <v>3.35</v>
+      </c>
+      <c r="L1111">
+        <v>4.02</v>
+      </c>
+      <c r="M1111">
+        <v>3.28</v>
+      </c>
+      <c r="N1111">
+        <v>3.99</v>
+      </c>
+      <c r="O1111">
+        <v>1</v>
+      </c>
+      <c r="P1111" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:16">
+      <c r="A1112" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1112" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1112">
+        <v>1.432233461226324</v>
+      </c>
+      <c r="D1112" t="s">
+        <v>369</v>
+      </c>
+      <c r="E1112">
+        <v>1.456306194872342</v>
+      </c>
+      <c r="F1112">
+        <v>1</v>
+      </c>
+      <c r="G1112">
+        <v>0.006607766538773674</v>
+      </c>
+      <c r="H1112">
+        <v>0.006523693805127659</v>
+      </c>
+      <c r="I1112">
+        <v>0.02407273364601803</v>
+      </c>
+      <c r="J1112">
+        <v>0.7724676235145299</v>
+      </c>
+      <c r="K1112">
+        <v>3.35</v>
+      </c>
+      <c r="L1112">
+        <v>4.02</v>
+      </c>
+      <c r="M1112">
+        <v>3.28</v>
+      </c>
+      <c r="N1112">
+        <v>3.99</v>
+      </c>
+      <c r="O1112">
+        <v>1</v>
+      </c>
+      <c r="P1112" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:16">
+      <c r="A1113" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1113">
+        <v>1.438192457750358</v>
+      </c>
+      <c r="D1113" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1113">
+        <v>1.479020010493639</v>
+      </c>
+      <c r="F1113">
+        <v>1</v>
+      </c>
+      <c r="G1113">
+        <v>0.00660180754224964</v>
+      </c>
+      <c r="H1113">
+        <v>0.006580979989506362</v>
+      </c>
+      <c r="I1113">
+        <v>0.0408275527432802</v>
+      </c>
+      <c r="J1113">
+        <v>0.7706888185819823</v>
+      </c>
+      <c r="K1113">
+        <v>3.35</v>
+      </c>
+      <c r="L1113">
+        <v>4.02</v>
+      </c>
+      <c r="M1113">
+        <v>3.31</v>
+      </c>
+      <c r="N1113">
+        <v>4.03</v>
+      </c>
+      <c r="O1113">
+        <v>1</v>
+      </c>
+      <c r="P1113" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:16">
+      <c r="A1114" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1114">
+        <v>1.442360905903367</v>
+      </c>
+      <c r="D1114" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1114">
+        <v>1.483138686131387</v>
+      </c>
+      <c r="F1114">
+        <v>1</v>
+      </c>
+      <c r="G1114">
+        <v>0.006597639094096632</v>
+      </c>
+      <c r="H1114">
+        <v>0.006576861313868614</v>
+      </c>
+      <c r="I1114">
+        <v>0.04077778022801981</v>
+      </c>
+      <c r="J1114">
+        <v>0.7694445057004873</v>
+      </c>
+      <c r="K1114">
+        <v>3.35</v>
+      </c>
+      <c r="L1114">
+        <v>4.02</v>
+      </c>
+      <c r="M1114">
+        <v>3.31</v>
+      </c>
+      <c r="N1114">
+        <v>4.03</v>
+      </c>
+      <c r="O1114">
+        <v>1</v>
+      </c>
+      <c r="P1114" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:16">
+      <c r="A1115" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1115">
         <v>1.442612807343595</v>
       </c>
-      <c r="D1110" t="s">
+      <c r="D1115" t="s">
         <v>375</v>
       </c>
-      <c r="E1110">
-        <v>1.463387579793224</v>
-      </c>
-      <c r="F1110">
-        <v>1</v>
-      </c>
-      <c r="G1110">
+      <c r="E1115">
+        <v>1.483387579793225</v>
+      </c>
+      <c r="F1115">
+        <v>1</v>
+      </c>
+      <c r="G1115">
         <v>0.006597387192656404</v>
       </c>
-      <c r="H1110">
-        <v>0.006556612420206775</v>
-      </c>
-      <c r="I1110">
-        <v>0.020774772449629</v>
-      </c>
-      <c r="J1110">
+      <c r="H1115">
+        <v>0.006576612420206776</v>
+      </c>
+      <c r="I1115">
+        <v>0.04077477244962946</v>
+      </c>
+      <c r="J1115">
         <v>0.7693693112407177</v>
       </c>
-      <c r="K1110">
+      <c r="K1115">
         <v>3.35</v>
       </c>
-      <c r="L1110">
+      <c r="L1115">
         <v>4.02</v>
       </c>
-      <c r="M1110">
+      <c r="M1115">
         <v>3.31</v>
       </c>
-      <c r="N1110">
-        <v>4.01</v>
-      </c>
-      <c r="O1110">
-        <v>1</v>
-      </c>
-      <c r="P1110" t="s">
+      <c r="N1115">
+        <v>4.03</v>
+      </c>
+      <c r="O1115">
+        <v>1</v>
+      </c>
+      <c r="P1115" t="s">
         <v>227</v>
       </c>
     </row>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3441" uniqueCount="513">
   <si>
     <t>trade_time</t>
   </si>
@@ -682,19 +682,19 @@
     <t>2021-07-12</t>
   </si>
   <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
     <t>2021-08-12</t>
   </si>
   <si>
-    <t>2021-07-27</t>
+    <t>2021-08-25</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-07-29</t>
   </si>
   <si>
     <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
   </si>
   <si>
     <t>2021-08-06</t>
@@ -703,10 +703,10 @@
     <t>2021-08-17</t>
   </si>
   <si>
-    <t>2021-08-20</t>
+    <t>2021-08-23</t>
   </si>
   <si>
-    <t>2021-08-23</t>
+    <t>2021-08-20</t>
   </si>
   <si>
     <t>2016-07-22</t>
@@ -1132,22 +1132,22 @@
     <t>2021-05-10</t>
   </si>
   <si>
-    <t>2021-08-25</t>
-  </si>
-  <si>
     <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-22</t>
   </si>
   <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
     <t>2021-08-04</t>
   </si>
   <si>
+    <t>2021-08-26</t>
+  </si>
+  <si>
     <t>2021-08-18</t>
+  </si>
+  <si>
+    <t>2021-07-16</t>
   </si>
   <si>
     <t>2021-08-11</t>
@@ -1537,6 +1537,9 @@
     <t>2021-07-28</t>
   </si>
   <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
     <t>2021-08-05</t>
   </si>
   <si>
@@ -1547,6 +1550,9 @@
   </si>
   <si>
     <t>2021-08-13</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
   </si>
 </sst>
 </file>
@@ -1904,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1125"/>
+  <dimension ref="A1:P1143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -53565,10 +53571,10 @@
         <v>1.710325886585777</v>
       </c>
       <c r="D1034" t="s">
-        <v>372</v>
+        <v>222</v>
       </c>
       <c r="E1034">
-        <v>1.730236205537345</v>
+        <v>1.824371610287536</v>
       </c>
       <c r="F1034">
         <v>1</v>
@@ -53577,10 +53583,10 @@
         <v>0.006789674113414224</v>
       </c>
       <c r="H1034">
-        <v>0.006249763794462656</v>
+        <v>0.006275628389712465</v>
       </c>
       <c r="I1034">
-        <v>0.01991031895156814</v>
+        <v>0.1140457237017589</v>
       </c>
       <c r="J1034">
         <v>0.6827080950038233</v>
@@ -53592,10 +53598,10 @@
         <v>4.25</v>
       </c>
       <c r="M1034">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="N1034">
-        <v>3.99</v>
+        <v>4.05</v>
       </c>
       <c r="O1034">
         <v>1</v>
@@ -53615,7 +53621,7 @@
         <v>1.815102844953163</v>
       </c>
       <c r="D1035" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E1035">
         <v>1.753015209992995</v>
@@ -53665,7 +53671,7 @@
         <v>1.683711088313052</v>
       </c>
       <c r="D1036" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E1036">
         <v>1.760987732126702</v>
@@ -53712,40 +53718,40 @@
         <v>222</v>
       </c>
       <c r="C1037">
-        <v>1.708960254260409</v>
+        <v>1.801047889220578</v>
       </c>
       <c r="D1037" t="s">
-        <v>229</v>
+        <v>374</v>
       </c>
       <c r="E1037">
-        <v>1.761047889220578</v>
+        <v>1.751743767540634</v>
       </c>
       <c r="F1037">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1037">
-        <v>0.00633103974573959</v>
+        <v>0.006298952110779422</v>
       </c>
       <c r="H1037">
-        <v>0.006258952110779422</v>
+        <v>0.006208256232459367</v>
       </c>
       <c r="I1037">
-        <v>0.05208763496016866</v>
+        <v>0.04930412167994414</v>
       </c>
       <c r="J1037">
         <v>0.6898626106685345</v>
       </c>
       <c r="K1037">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="L1037">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="M1037">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="N1037">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1037">
         <v>1</v>
@@ -53756,146 +53762,146 @@
     </row>
     <row r="1038" spans="1:16">
       <c r="A1038" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1038" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1038">
-        <v>1.774652822327312</v>
+        <v>1.708960254260409</v>
       </c>
       <c r="D1038" t="s">
-        <v>373</v>
+        <v>230</v>
       </c>
       <c r="E1038">
-        <v>1.711570514679623</v>
+        <v>1.761047889220578</v>
       </c>
       <c r="F1038">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1038">
-        <v>0.006905347177672688</v>
+        <v>0.00633103974573959</v>
       </c>
       <c r="H1038">
-        <v>0.006968429485320377</v>
+        <v>0.006258952110779422</v>
       </c>
       <c r="I1038">
-        <v>0.06308230764768874</v>
+        <v>0.05208763496016866</v>
       </c>
       <c r="J1038">
-        <v>0.7009145294187672</v>
+        <v>0.6898626106685345</v>
       </c>
       <c r="K1038">
-        <v>3.66</v>
+        <v>3.35</v>
       </c>
       <c r="L1038">
-        <v>4.34</v>
+        <v>4.02</v>
       </c>
       <c r="M1038">
-        <v>3.75</v>
+        <v>3.26</v>
       </c>
       <c r="N1038">
-        <v>4.34</v>
+        <v>4.01</v>
       </c>
       <c r="O1038">
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
       <c r="A1039" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1039" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C1039">
-        <v>1.642597950562186</v>
+        <v>1.706554758687151</v>
       </c>
       <c r="D1039" t="s">
         <v>375</v>
       </c>
       <c r="E1039">
-        <v>1.611570514679623</v>
+        <v>1.717250637007207</v>
       </c>
       <c r="F1039">
         <v>1</v>
       </c>
       <c r="G1039">
-        <v>0.006857402049437814</v>
+        <v>0.00627344524131285</v>
       </c>
       <c r="H1039">
-        <v>0.006868429485320376</v>
+        <v>0.006242749362992794</v>
       </c>
       <c r="I1039">
-        <v>-0.0310274358825624</v>
+        <v>0.01069587832005592</v>
       </c>
       <c r="J1039">
-        <v>0.7009145294187672</v>
+        <v>0.6898626106685345</v>
       </c>
       <c r="K1039">
-        <v>3.72</v>
+        <v>3.31</v>
       </c>
       <c r="L1039">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="M1039">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="N1039">
-        <v>4.24</v>
+        <v>3.98</v>
       </c>
       <c r="O1039">
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1040" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C1040">
-        <v>1.765018634094819</v>
+        <v>1.774652822327312</v>
       </c>
       <c r="D1040" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E1040">
-        <v>1.716046069977382</v>
+        <v>1.711570514679623</v>
       </c>
       <c r="F1040">
         <v>-1</v>
       </c>
       <c r="G1040">
-        <v>0.006334981365905181</v>
+        <v>0.006905347177672688</v>
       </c>
       <c r="H1040">
-        <v>0.006243953930022619</v>
+        <v>0.006968429485320377</v>
       </c>
       <c r="I1040">
-        <v>0.04897256411743678</v>
+        <v>0.06308230764768874</v>
       </c>
       <c r="J1040">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1040">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="L1040">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="M1040">
-        <v>3.23</v>
+        <v>3.75</v>
       </c>
       <c r="N1040">
-        <v>3.98</v>
+        <v>4.34</v>
       </c>
       <c r="O1040">
         <v>1</v>
@@ -53906,46 +53912,46 @@
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1041" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C1041">
-        <v>1.765110087036696</v>
+        <v>1.642597950562186</v>
       </c>
       <c r="D1041" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E1041">
-        <v>1.716046069977382</v>
+        <v>1.721753420563377</v>
       </c>
       <c r="F1041">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1041">
-        <v>0.006194889912963305</v>
+        <v>0.006857402049437814</v>
       </c>
       <c r="H1041">
-        <v>0.006243953930022619</v>
+        <v>0.006698246579436623</v>
       </c>
       <c r="I1041">
-        <v>0.04906401705931351</v>
+        <v>0.07915547000119094</v>
       </c>
       <c r="J1041">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1041">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="L1041">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1041">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N1041">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="O1041">
         <v>1</v>
@@ -53956,46 +53962,46 @@
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1042" t="s">
         <v>222</v>
       </c>
       <c r="C1042">
-        <v>1.671936326447129</v>
+        <v>1.765018634094819</v>
       </c>
       <c r="D1042" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E1042">
-        <v>1.719972907623881</v>
+        <v>1.716046069977382</v>
       </c>
       <c r="F1042">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1042">
-        <v>0.00636806367355287</v>
+        <v>0.006334981365905181</v>
       </c>
       <c r="H1042">
-        <v>0.00636002709237612</v>
+        <v>0.006243953930022619</v>
       </c>
       <c r="I1042">
-        <v>0.04803658117675136</v>
+        <v>0.04897256411743678</v>
       </c>
       <c r="J1042">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1042">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="L1042">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="M1042">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N1042">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="O1042">
         <v>1</v>
@@ -54006,196 +54012,196 @@
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1043" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C1043">
-        <v>1.745068418380975</v>
+        <v>1.760064360565757</v>
       </c>
       <c r="D1043" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E1043">
-        <v>1.681258625390344</v>
+        <v>1.716046069977382</v>
       </c>
       <c r="F1043">
         <v>-1</v>
       </c>
       <c r="G1043">
-        <v>0.006934931581619024</v>
+        <v>0.006259935639434243</v>
       </c>
       <c r="H1043">
-        <v>0.006998741374609656</v>
+        <v>0.006243953930022619</v>
       </c>
       <c r="I1043">
-        <v>0.06380979299063139</v>
+        <v>0.04401829058837503</v>
       </c>
       <c r="J1043">
-        <v>0.7089976998959082</v>
+        <v>0.7009145294187672</v>
       </c>
       <c r="K1043">
-        <v>3.66</v>
+        <v>3.21</v>
       </c>
       <c r="L1043">
-        <v>4.34</v>
+        <v>4.01</v>
       </c>
       <c r="M1043">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N1043">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="O1043">
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1044" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C1044">
-        <v>1.612528556387221</v>
+        <v>1.671936326447129</v>
       </c>
       <c r="D1044" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E1044">
-        <v>1.581258625390344</v>
+        <v>1.719972907623881</v>
       </c>
       <c r="F1044">
         <v>1</v>
       </c>
       <c r="G1044">
-        <v>0.006887471443612779</v>
+        <v>0.00636806367355287</v>
       </c>
       <c r="H1044">
-        <v>0.006898741374609657</v>
+        <v>0.00636002709237612</v>
       </c>
       <c r="I1044">
-        <v>-0.03126993099687692</v>
+        <v>0.04803658117675136</v>
       </c>
       <c r="J1044">
-        <v>0.7089976998959082</v>
+        <v>0.7009145294187672</v>
       </c>
       <c r="K1044">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="L1044">
-        <v>4.25</v>
+        <v>4.02</v>
       </c>
       <c r="M1044">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="N1044">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="O1044">
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B1045" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C1045">
-        <v>1.730677751350789</v>
+        <v>1.669972907623881</v>
       </c>
       <c r="D1045" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E1045">
-        <v>1.664857705348707</v>
+        <v>1.681000343506444</v>
       </c>
       <c r="F1045">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1045">
-        <v>0.006509322248649211</v>
+        <v>0.006310027092376119</v>
       </c>
       <c r="H1045">
-        <v>0.006415142294651293</v>
+        <v>0.006278999656493556</v>
       </c>
       <c r="I1045">
-        <v>0.06582004600208169</v>
+        <v>0.01102743588256283</v>
       </c>
       <c r="J1045">
-        <v>0.7089976998959082</v>
+        <v>0.7009145294187672</v>
       </c>
       <c r="K1045">
-        <v>3.37</v>
+        <v>3.31</v>
       </c>
       <c r="L1045">
-        <v>4.12</v>
+        <v>3.99</v>
       </c>
       <c r="M1045">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N1045">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="O1045">
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1046" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C1046">
-        <v>1.734117383334135</v>
+        <v>1.745068418380975</v>
       </c>
       <c r="D1046" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E1046">
-        <v>1.664857705348707</v>
+        <v>1.681258625390344</v>
       </c>
       <c r="F1046">
         <v>-1</v>
       </c>
       <c r="G1046">
-        <v>0.006285882616665866</v>
+        <v>0.006934931581619024</v>
       </c>
       <c r="H1046">
-        <v>0.006415142294651293</v>
+        <v>0.006998741374609656</v>
       </c>
       <c r="I1046">
-        <v>0.06925967798542709</v>
+        <v>0.06380979299063139</v>
       </c>
       <c r="J1046">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1046">
-        <v>3.21</v>
+        <v>3.66</v>
       </c>
       <c r="L1046">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="M1046">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1046">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="O1046">
         <v>1</v>
@@ -54206,46 +54212,46 @@
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1047" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C1047">
-        <v>1.732477291329971</v>
+        <v>1.612528556387221</v>
       </c>
       <c r="D1047" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1047">
-        <v>1.664857705348707</v>
+        <v>1.581258625390344</v>
       </c>
       <c r="F1047">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.006227522708670029</v>
+        <v>0.006887471443612779</v>
       </c>
       <c r="H1047">
-        <v>0.006415142294651293</v>
+        <v>0.006898741374609657</v>
       </c>
       <c r="I1047">
-        <v>0.06761958598126361</v>
+        <v>-0.03126993099687692</v>
       </c>
       <c r="J1047">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1047">
-        <v>3.17</v>
+        <v>3.72</v>
       </c>
       <c r="L1047">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1047">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1047">
-        <v>4.04</v>
+        <v>4.24</v>
       </c>
       <c r="O1047">
         <v>1</v>
@@ -54256,43 +54262,43 @@
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B1048" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C1048">
-        <v>1.644857705348707</v>
+        <v>1.730677751350789</v>
       </c>
       <c r="D1048" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1048">
-        <v>1.693217613344544</v>
+        <v>1.664857705348707</v>
       </c>
       <c r="F1048">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.006395142294651292</v>
+        <v>0.006509322248649211</v>
       </c>
       <c r="H1048">
-        <v>0.006386782386655456</v>
+        <v>0.006415142294651293</v>
       </c>
       <c r="I1048">
-        <v>0.04835990799583678</v>
+        <v>0.06582004600208169</v>
       </c>
       <c r="J1048">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1048">
+        <v>3.37</v>
+      </c>
+      <c r="L1048">
+        <v>4.12</v>
+      </c>
+      <c r="M1048">
         <v>3.35</v>
-      </c>
-      <c r="L1048">
-        <v>4.02</v>
-      </c>
-      <c r="M1048">
-        <v>3.31</v>
       </c>
       <c r="N1048">
         <v>4.04</v>
@@ -54306,143 +54312,143 @@
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1049" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C1049">
-        <v>1.725336643125503</v>
+        <v>1.734117383334135</v>
       </c>
       <c r="D1049" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E1049">
-        <v>1.661041642546622</v>
+        <v>1.664857705348707</v>
       </c>
       <c r="F1049">
         <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.006954663356874498</v>
+        <v>0.006285882616665866</v>
       </c>
       <c r="H1049">
-        <v>0.007018958357453379</v>
+        <v>0.006415142294651293</v>
       </c>
       <c r="I1049">
-        <v>0.06429500057888093</v>
+        <v>0.06925967798542709</v>
       </c>
       <c r="J1049">
-        <v>0.7143888953209009</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1049">
-        <v>3.66</v>
+        <v>3.21</v>
       </c>
       <c r="L1049">
-        <v>4.34</v>
+        <v>4.01</v>
       </c>
       <c r="M1049">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1049">
-        <v>4.34</v>
+        <v>4.04</v>
       </c>
       <c r="O1049">
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1050" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C1050">
-        <v>1.592473309406249</v>
+        <v>1.732477291329971</v>
       </c>
       <c r="D1050" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E1050">
-        <v>1.561041642546622</v>
+        <v>1.664857705348707</v>
       </c>
       <c r="F1050">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.006907526690593752</v>
+        <v>0.006227522708670029</v>
       </c>
       <c r="H1050">
-        <v>0.006918958357453379</v>
+        <v>0.006415142294651293</v>
       </c>
       <c r="I1050">
-        <v>-0.03143166685962662</v>
+        <v>0.06761958598126361</v>
       </c>
       <c r="J1050">
-        <v>0.7143888953209009</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1050">
-        <v>3.72</v>
+        <v>3.17</v>
       </c>
       <c r="L1050">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1050">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1050">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="O1050">
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B1051" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C1051">
-        <v>1.712509422768564</v>
+        <v>1.644857705348707</v>
       </c>
       <c r="D1051" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E1051">
-        <v>1.646797200674982</v>
+        <v>1.693217613344544</v>
       </c>
       <c r="F1051">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1051">
-        <v>0.006527490577231437</v>
+        <v>0.006395142294651292</v>
       </c>
       <c r="H1051">
-        <v>0.006433202799325018</v>
+        <v>0.006386782386655456</v>
       </c>
       <c r="I1051">
-        <v>0.06571222209358218</v>
+        <v>0.04835990799583678</v>
       </c>
       <c r="J1051">
-        <v>0.7143888953209009</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1051">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="L1051">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
       <c r="M1051">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N1051">
         <v>4.04</v>
@@ -54451,101 +54457,101 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B1052" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C1052">
-        <v>1.716811646019908</v>
+        <v>1.643217613344544</v>
       </c>
       <c r="D1052" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E1052">
-        <v>1.646797200674982</v>
+        <v>1.654487544341421</v>
       </c>
       <c r="F1052">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1052">
-        <v>0.006303188353980092</v>
+        <v>0.006336782386655457</v>
       </c>
       <c r="H1052">
-        <v>0.006433202799325018</v>
+        <v>0.006305512455658579</v>
       </c>
       <c r="I1052">
-        <v>0.07001444534492629</v>
+        <v>0.01126993099687734</v>
       </c>
       <c r="J1052">
-        <v>0.7143888953209009</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1052">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="L1052">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1052">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N1052">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="O1052">
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1053" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C1053">
-        <v>1.715387201832744</v>
+        <v>1.725336643125503</v>
       </c>
       <c r="D1053" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E1053">
-        <v>1.646797200674982</v>
+        <v>1.661041642546622</v>
       </c>
       <c r="F1053">
         <v>-1</v>
       </c>
       <c r="G1053">
-        <v>0.006244612798167256</v>
+        <v>0.006954663356874498</v>
       </c>
       <c r="H1053">
-        <v>0.006433202799325018</v>
+        <v>0.007018958357453379</v>
       </c>
       <c r="I1053">
-        <v>0.06859000115776226</v>
+        <v>0.06429500057888093</v>
       </c>
       <c r="J1053">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1053">
-        <v>3.17</v>
+        <v>3.66</v>
       </c>
       <c r="L1053">
-        <v>3.98</v>
+        <v>4.34</v>
       </c>
       <c r="M1053">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1053">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="O1053">
         <v>1</v>
@@ -54556,140 +54562,140 @@
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1054" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1054">
-        <v>1.706714139491356</v>
+        <v>1.592473309406249</v>
       </c>
       <c r="D1054" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E1054">
-        <v>1.641961208495242</v>
+        <v>1.561041642546622</v>
       </c>
       <c r="F1054">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1054">
-        <v>0.006973285860508644</v>
+        <v>0.006907526690593752</v>
       </c>
       <c r="H1054">
-        <v>0.007038038791504758</v>
+        <v>0.006918958357453379</v>
       </c>
       <c r="I1054">
-        <v>0.0647529309961139</v>
+        <v>-0.03143166685962662</v>
       </c>
       <c r="J1054">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1054">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1054">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1054">
         <v>3.75</v>
       </c>
       <c r="N1054">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="O1054">
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1055" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C1055">
-        <v>1.57354551882728</v>
+        <v>1.712509422768564</v>
       </c>
       <c r="D1055" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E1055">
-        <v>1.541961208495242</v>
+        <v>1.646797200674982</v>
       </c>
       <c r="F1055">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.00692645448117272</v>
+        <v>0.006527490577231437</v>
       </c>
       <c r="H1055">
-        <v>0.006938038791504758</v>
+        <v>0.006433202799325018</v>
       </c>
       <c r="I1055">
-        <v>-0.0315843103320379</v>
+        <v>0.06571222209358218</v>
       </c>
       <c r="J1055">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1055">
-        <v>3.72</v>
+        <v>3.37</v>
       </c>
       <c r="L1055">
-        <v>4.25</v>
+        <v>4.12</v>
       </c>
       <c r="M1055">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1055">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1056" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1056">
-        <v>1.695362472701057</v>
+        <v>1.715387201832744</v>
       </c>
       <c r="D1056" t="s">
         <v>378</v>
       </c>
       <c r="E1056">
-        <v>1.629752012922416</v>
+        <v>1.646797200674982</v>
       </c>
       <c r="F1056">
         <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.006544637527298943</v>
+        <v>0.006244612798167256</v>
       </c>
       <c r="H1056">
-        <v>0.006450247987077585</v>
+        <v>0.006433202799325018</v>
       </c>
       <c r="I1056">
-        <v>0.06561045977864133</v>
+        <v>0.06859000115776226</v>
       </c>
       <c r="J1056">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1056">
-        <v>3.37</v>
+        <v>3.17</v>
       </c>
       <c r="L1056">
-        <v>4.12</v>
+        <v>3.98</v>
       </c>
       <c r="M1056">
         <v>3.35</v>
@@ -54701,101 +54707,101 @@
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1057" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C1057">
-        <v>1.700478794471927</v>
+        <v>1.625372756487818</v>
       </c>
       <c r="D1057" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E1057">
-        <v>1.629752012922416</v>
+        <v>1.636804423347445</v>
       </c>
       <c r="F1057">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1057">
-        <v>0.006319521205528073</v>
+        <v>0.006354627243512182</v>
       </c>
       <c r="H1057">
-        <v>0.006450247987077585</v>
+        <v>0.006323195576652555</v>
       </c>
       <c r="I1057">
-        <v>0.07072678154951095</v>
+        <v>0.01143166685962704</v>
       </c>
       <c r="J1057">
-        <v>0.7194770110679355</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1057">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="L1057">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1057">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N1057">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="O1057">
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1058" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C1058">
-        <v>1.699257874914645</v>
+        <v>1.706714139491356</v>
       </c>
       <c r="D1058" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E1058">
-        <v>1.629752012922416</v>
+        <v>1.641961208495242</v>
       </c>
       <c r="F1058">
         <v>-1</v>
       </c>
       <c r="G1058">
-        <v>0.006260742125085356</v>
+        <v>0.006973285860508644</v>
       </c>
       <c r="H1058">
-        <v>0.006450247987077585</v>
+        <v>0.007038038791504758</v>
       </c>
       <c r="I1058">
-        <v>0.06950586199222863</v>
+        <v>0.0647529309961139</v>
       </c>
       <c r="J1058">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1058">
-        <v>3.17</v>
+        <v>3.66</v>
       </c>
       <c r="L1058">
-        <v>3.98</v>
+        <v>4.34</v>
       </c>
       <c r="M1058">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1058">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="O1058">
         <v>1</v>
@@ -54806,140 +54812,140 @@
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1059" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1059">
-        <v>1.687585123258323</v>
+        <v>1.57354551882728</v>
       </c>
       <c r="D1059" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E1059">
-        <v>1.622361806617135</v>
+        <v>1.541961208495242</v>
       </c>
       <c r="F1059">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1059">
-        <v>0.006992414876741677</v>
+        <v>0.00692645448117272</v>
       </c>
       <c r="H1059">
-        <v>0.007057638193382865</v>
+        <v>0.006938038791504758</v>
       </c>
       <c r="I1059">
-        <v>0.06522331664118841</v>
+        <v>-0.0315843103320379</v>
       </c>
       <c r="J1059">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1059">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1059">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1059">
         <v>3.75</v>
       </c>
       <c r="N1059">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="O1059">
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1060" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C1060">
-        <v>1.554102912164197</v>
+        <v>1.695362472701057</v>
       </c>
       <c r="D1060" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E1060">
-        <v>1.637302510264221</v>
+        <v>1.629752012922416</v>
       </c>
       <c r="F1060">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.006945897087835803</v>
+        <v>0.006544637527298943</v>
       </c>
       <c r="H1060">
-        <v>0.00678269748973578</v>
+        <v>0.006450247987077585</v>
       </c>
       <c r="I1060">
-        <v>0.08319959810002331</v>
+        <v>0.06561045977864133</v>
       </c>
       <c r="J1060">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1060">
-        <v>3.72</v>
+        <v>3.37</v>
       </c>
       <c r="L1060">
-        <v>4.25</v>
+        <v>4.12</v>
       </c>
       <c r="M1060">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1060">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1060">
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1061" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1061">
-        <v>1.677749143546598</v>
+        <v>1.699257874914645</v>
       </c>
       <c r="D1061" t="s">
         <v>378</v>
       </c>
       <c r="E1061">
-        <v>1.612243213911307</v>
+        <v>1.629752012922416</v>
       </c>
       <c r="F1061">
         <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.006562250856453402</v>
+        <v>0.006260742125085356</v>
       </c>
       <c r="H1061">
-        <v>0.006467756786088693</v>
+        <v>0.006450247987077585</v>
       </c>
       <c r="I1061">
-        <v>0.06550592963529134</v>
+        <v>0.06950586199222863</v>
       </c>
       <c r="J1061">
-        <v>0.7247035182354308</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1061">
-        <v>3.37</v>
+        <v>3.17</v>
       </c>
       <c r="L1061">
-        <v>4.12</v>
+        <v>3.98</v>
       </c>
       <c r="M1061">
         <v>3.35</v>
@@ -54951,51 +54957,51 @@
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1062" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C1062">
-        <v>1.683701706464267</v>
+        <v>1.687585123258323</v>
       </c>
       <c r="D1062" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E1062">
-        <v>1.612243213911307</v>
+        <v>1.622361806617135</v>
       </c>
       <c r="F1062">
         <v>-1</v>
       </c>
       <c r="G1062">
-        <v>0.006336298293535732</v>
+        <v>0.006992414876741677</v>
       </c>
       <c r="H1062">
-        <v>0.006467756786088693</v>
+        <v>0.007057638193382865</v>
       </c>
       <c r="I1062">
-        <v>0.07145849255296044</v>
+        <v>0.06522331664118841</v>
       </c>
       <c r="J1062">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1062">
-        <v>3.21</v>
+        <v>3.66</v>
       </c>
       <c r="L1062">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="M1062">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1062">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="O1062">
         <v>1</v>
@@ -55006,46 +55012,46 @@
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1063" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C1063">
-        <v>1.682689847193684</v>
+        <v>1.554102912164197</v>
       </c>
       <c r="D1063" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E1063">
-        <v>1.612243213911307</v>
+        <v>1.637302510264221</v>
       </c>
       <c r="F1063">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1063">
-        <v>0.006277310152806315</v>
+        <v>0.006945897087835803</v>
       </c>
       <c r="H1063">
-        <v>0.006467756786088693</v>
+        <v>0.00678269748973578</v>
       </c>
       <c r="I1063">
-        <v>0.07044663328237766</v>
+        <v>0.08319959810002331</v>
       </c>
       <c r="J1063">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1063">
-        <v>3.17</v>
+        <v>3.72</v>
       </c>
       <c r="L1063">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M1063">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N1063">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="O1063">
         <v>1</v>
@@ -55056,146 +55062,146 @@
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1064" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C1064">
-        <v>1.674071021437449</v>
+        <v>1.677749143546598</v>
       </c>
       <c r="D1064" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E1064">
-        <v>1.608515390817058</v>
+        <v>1.612243213911307</v>
       </c>
       <c r="F1064">
         <v>-1</v>
       </c>
       <c r="G1064">
-        <v>0.007005928978562551</v>
+        <v>0.006562250856453402</v>
       </c>
       <c r="H1064">
-        <v>0.007071484609182941</v>
+        <v>0.006467756786088693</v>
       </c>
       <c r="I1064">
-        <v>0.06555563062039038</v>
+        <v>0.06550592963529134</v>
       </c>
       <c r="J1064">
-        <v>0.7283958957821177</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1064">
-        <v>3.66</v>
+        <v>3.37</v>
       </c>
       <c r="L1064">
-        <v>4.34</v>
+        <v>4.12</v>
       </c>
       <c r="M1064">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1064">
-        <v>4.34</v>
+        <v>4.04</v>
       </c>
       <c r="O1064">
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1065" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C1065">
-        <v>1.540367267690522</v>
+        <v>1.682689847193684</v>
       </c>
       <c r="D1065" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E1065">
-        <v>1.624194569973482</v>
+        <v>1.612243213911307</v>
       </c>
       <c r="F1065">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1065">
-        <v>0.006959632732309478</v>
+        <v>0.006277310152806315</v>
       </c>
       <c r="H1065">
-        <v>0.006795805430026517</v>
+        <v>0.006467756786088693</v>
       </c>
       <c r="I1065">
-        <v>0.08382730228296031</v>
+        <v>0.07044663328237766</v>
       </c>
       <c r="J1065">
-        <v>0.7283958957821177</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1065">
-        <v>3.72</v>
+        <v>3.17</v>
       </c>
       <c r="L1065">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1065">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1065">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1065">
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1066" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C1066">
-        <v>1.665305831214263</v>
+        <v>1.674071021437449</v>
       </c>
       <c r="D1066" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E1066">
-        <v>1.599873749129906</v>
+        <v>1.608515390817058</v>
       </c>
       <c r="F1066">
         <v>-1</v>
       </c>
       <c r="G1066">
-        <v>0.006574694168785737</v>
+        <v>0.007005928978562551</v>
       </c>
       <c r="H1066">
-        <v>0.006480126250870095</v>
+        <v>0.007071484609182941</v>
       </c>
       <c r="I1066">
-        <v>0.06543208208435747</v>
+        <v>0.06555563062039038</v>
       </c>
       <c r="J1066">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1066">
-        <v>3.37</v>
+        <v>3.66</v>
       </c>
       <c r="L1066">
-        <v>4.12</v>
+        <v>4.34</v>
       </c>
       <c r="M1066">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1066">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="O1066">
         <v>1</v>
@@ -55206,46 +55212,46 @@
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1067" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C1067">
-        <v>1.671849174539402</v>
+        <v>1.540367267690522</v>
       </c>
       <c r="D1067" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E1067">
-        <v>1.599873749129906</v>
+        <v>1.624194569973482</v>
       </c>
       <c r="F1067">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1067">
-        <v>0.006348150825460598</v>
+        <v>0.006959632732309478</v>
       </c>
       <c r="H1067">
-        <v>0.006480126250870095</v>
+        <v>0.006795805430026517</v>
       </c>
       <c r="I1067">
-        <v>0.0719754254094962</v>
+        <v>0.08382730228296031</v>
       </c>
       <c r="J1067">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1067">
-        <v>3.21</v>
+        <v>3.72</v>
       </c>
       <c r="L1067">
-        <v>4.01</v>
+        <v>4.25</v>
       </c>
       <c r="M1067">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N1067">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="O1067">
         <v>1</v>
@@ -55256,13 +55262,13 @@
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1068" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C1068">
-        <v>1.670985010370687</v>
+        <v>1.665305831214263</v>
       </c>
       <c r="D1068" t="s">
         <v>378</v>
@@ -55274,22 +55280,22 @@
         <v>-1</v>
       </c>
       <c r="G1068">
-        <v>0.006289014989629313</v>
+        <v>0.006574694168785737</v>
       </c>
       <c r="H1068">
         <v>0.006480126250870095</v>
       </c>
       <c r="I1068">
-        <v>0.07111126124078115</v>
+        <v>0.06543208208435747</v>
       </c>
       <c r="J1068">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1068">
-        <v>3.17</v>
+        <v>3.37</v>
       </c>
       <c r="L1068">
-        <v>3.98</v>
+        <v>4.12</v>
       </c>
       <c r="M1068">
         <v>3.35</v>
@@ -55306,96 +55312,96 @@
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1069" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C1069">
-        <v>1.525149479713785</v>
+        <v>1.670985010370687</v>
       </c>
       <c r="D1069" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E1069">
-        <v>1.609672218544069</v>
+        <v>1.599873749129906</v>
       </c>
       <c r="F1069">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1069">
-        <v>0.006974850520286215</v>
+        <v>0.006289014989629313</v>
       </c>
       <c r="H1069">
-        <v>0.00681032778145593</v>
+        <v>0.006480126250870095</v>
       </c>
       <c r="I1069">
-        <v>0.08452273883028427</v>
+        <v>0.07111126124078115</v>
       </c>
       <c r="J1069">
-        <v>0.7324866990016706</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1069">
-        <v>3.72</v>
+        <v>3.17</v>
       </c>
       <c r="L1069">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1069">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N1069">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="O1069">
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>221</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1070" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C1070">
-        <v>1.65151982436437</v>
+        <v>1.525149479713785</v>
       </c>
       <c r="D1070" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E1070">
-        <v>1.586169558344404</v>
+        <v>1.609672218544069</v>
       </c>
       <c r="F1070">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1070">
-        <v>0.00658848017563563</v>
+        <v>0.006974850520286215</v>
       </c>
       <c r="H1070">
-        <v>0.006493830441655597</v>
+        <v>0.00681032778145593</v>
       </c>
       <c r="I1070">
-        <v>0.06535026601996652</v>
+        <v>0.08452273883028427</v>
       </c>
       <c r="J1070">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1070">
-        <v>3.37</v>
+        <v>3.72</v>
       </c>
       <c r="L1070">
-        <v>4.12</v>
+        <v>4.25</v>
       </c>
       <c r="M1070">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N1070">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="O1070">
         <v>1</v>
@@ -55406,13 +55412,13 @@
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1071" t="s">
         <v>226</v>
       </c>
       <c r="C1071">
-        <v>1.658717696204637</v>
+        <v>1.65151982436437</v>
       </c>
       <c r="D1071" t="s">
         <v>378</v>
@@ -55424,22 +55430,22 @@
         <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.006361282303795362</v>
+        <v>0.00658848017563563</v>
       </c>
       <c r="H1071">
         <v>0.006493830441655597</v>
       </c>
       <c r="I1071">
-        <v>0.07254813786023373</v>
+        <v>0.06535026601996652</v>
       </c>
       <c r="J1071">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1071">
-        <v>3.21</v>
+        <v>3.37</v>
       </c>
       <c r="L1071">
-        <v>4.01</v>
+        <v>4.12</v>
       </c>
       <c r="M1071">
         <v>3.35</v>
@@ -55456,7 +55462,7 @@
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1072" t="s">
         <v>227</v>
@@ -55515,7 +55521,7 @@
         <v>1.515332066574131</v>
       </c>
       <c r="D1073" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E1073">
         <v>1.600303450628539</v>
@@ -55551,7 +55557,7 @@
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -55559,7 +55565,7 @@
         <v>1</v>
       </c>
       <c r="B1074" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C1074">
         <v>1.6426260925685</v>
@@ -55601,7 +55607,7 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
@@ -55651,7 +55657,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55659,7 +55665,7 @@
         <v>0</v>
       </c>
       <c r="B1076" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C1076">
         <v>1.631729592152544</v>
@@ -55709,10 +55715,10 @@
         <v>1</v>
       </c>
       <c r="B1077" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1077">
-        <v>1.639867059587438</v>
+        <v>1.639401426446162</v>
       </c>
       <c r="D1077" t="s">
         <v>378</v>
@@ -55724,22 +55730,22 @@
         <v>-1</v>
       </c>
       <c r="G1077">
-        <v>0.006380132940412562</v>
+        <v>0.006320598573553837</v>
       </c>
       <c r="H1077">
         <v>0.006513503224418095</v>
       </c>
       <c r="I1077">
-        <v>0.07337028400553214</v>
+        <v>0.07290465086425613</v>
       </c>
       <c r="J1077">
         <v>0.7383591714680878</v>
       </c>
       <c r="K1077">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1077">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1077">
         <v>3.35</v>
@@ -55756,40 +55762,40 @@
     </row>
     <row r="1078" spans="1:16">
       <c r="A1078" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1078" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C1078">
-        <v>1.639401426446162</v>
+        <v>1.612906122499548</v>
       </c>
       <c r="D1078" t="s">
         <v>378</v>
       </c>
       <c r="E1078">
-        <v>1.566496775581906</v>
+        <v>1.547785017914981</v>
       </c>
       <c r="F1078">
         <v>-1</v>
       </c>
       <c r="G1078">
-        <v>0.006320598573553837</v>
+        <v>0.006627093877500452</v>
       </c>
       <c r="H1078">
-        <v>0.006513503224418095</v>
+        <v>0.00653221498208502</v>
       </c>
       <c r="I1078">
-        <v>0.07290465086425613</v>
+        <v>0.06512110458456677</v>
       </c>
       <c r="J1078">
-        <v>0.7383591714680878</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1078">
-        <v>3.17</v>
+        <v>3.37</v>
       </c>
       <c r="L1078">
-        <v>3.98</v>
+        <v>4.12</v>
       </c>
       <c r="M1078">
         <v>3.35</v>
@@ -55801,18 +55807,18 @@
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>220</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
       <c r="A1079" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1079" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C1079">
-        <v>1.624740047284429</v>
+        <v>1.621937285823011</v>
       </c>
       <c r="D1079" t="s">
         <v>378</v>
@@ -55824,22 +55830,22 @@
         <v>-1</v>
       </c>
       <c r="G1079">
-        <v>0.00647525995271557</v>
+        <v>0.006398062714176988</v>
       </c>
       <c r="H1079">
         <v>0.00653221498208502</v>
       </c>
       <c r="I1079">
-        <v>0.07695502936944809</v>
+        <v>0.0741522679080302</v>
       </c>
       <c r="J1079">
         <v>0.7439447707716474</v>
       </c>
       <c r="K1079">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1079">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1079">
         <v>3.35</v>
@@ -55856,13 +55862,13 @@
     </row>
     <row r="1080" spans="1:16">
       <c r="A1080" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1080" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1080">
-        <v>1.621937285823011</v>
+        <v>1.621695076653878</v>
       </c>
       <c r="D1080" t="s">
         <v>378</v>
@@ -55874,22 +55880,22 @@
         <v>-1</v>
       </c>
       <c r="G1080">
-        <v>0.006398062714176988</v>
+        <v>0.006338304923346122</v>
       </c>
       <c r="H1080">
         <v>0.00653221498208502</v>
       </c>
       <c r="I1080">
-        <v>0.0741522679080302</v>
+        <v>0.07391005873889656</v>
       </c>
       <c r="J1080">
         <v>0.7439447707716474</v>
       </c>
       <c r="K1080">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1080">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1080">
         <v>3.35</v>
@@ -55906,40 +55912,40 @@
     </row>
     <row r="1081" spans="1:16">
       <c r="A1081" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1081" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C1081">
-        <v>1.621695076653878</v>
+        <v>1.61016227805581</v>
       </c>
       <c r="D1081" t="s">
         <v>378</v>
       </c>
       <c r="E1081">
-        <v>1.547785017914981</v>
+        <v>1.532804794934651</v>
       </c>
       <c r="F1081">
         <v>-1</v>
       </c>
       <c r="G1081">
-        <v>0.006338304923346122</v>
+        <v>0.006489837721944189</v>
       </c>
       <c r="H1081">
-        <v>0.00653221498208502</v>
+        <v>0.006547195205065348</v>
       </c>
       <c r="I1081">
-        <v>0.07391005873889656</v>
+        <v>0.07735748312115875</v>
       </c>
       <c r="J1081">
-        <v>0.7439447707716474</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1081">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L1081">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1081">
         <v>3.35</v>
@@ -55951,18 +55957,18 @@
         <v>1</v>
       </c>
       <c r="P1081" t="s">
-        <v>502</v>
+        <v>377</v>
       </c>
     </row>
     <row r="1082" spans="1:16">
       <c r="A1082" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1082" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C1082">
-        <v>1.61016227805581</v>
+        <v>1.607583102012009</v>
       </c>
       <c r="D1082" t="s">
         <v>378</v>
@@ -55974,22 +55980,22 @@
         <v>-1</v>
       </c>
       <c r="G1082">
-        <v>0.006489837721944189</v>
+        <v>0.00641241689798799</v>
       </c>
       <c r="H1082">
         <v>0.006547195205065348</v>
       </c>
       <c r="I1082">
-        <v>0.07735748312115875</v>
+        <v>0.074778307077358</v>
       </c>
       <c r="J1082">
         <v>0.7484164791239846</v>
       </c>
       <c r="K1082">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1082">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1082">
         <v>3.35</v>
@@ -56001,18 +56007,18 @@
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
       <c r="A1083" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1083" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1083">
-        <v>1.607583102012009</v>
+        <v>1.607519761176969</v>
       </c>
       <c r="D1083" t="s">
         <v>378</v>
@@ -56024,22 +56030,22 @@
         <v>-1</v>
       </c>
       <c r="G1083">
-        <v>0.00641241689798799</v>
+        <v>0.006352480238823031</v>
       </c>
       <c r="H1083">
         <v>0.006547195205065348</v>
       </c>
       <c r="I1083">
-        <v>0.074778307077358</v>
+        <v>0.07471496624231744</v>
       </c>
       <c r="J1083">
         <v>0.7484164791239846</v>
       </c>
       <c r="K1083">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1083">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1083">
         <v>3.35</v>
@@ -56051,45 +56057,45 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
       <c r="A1084" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1084" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C1084">
-        <v>1.607519761176969</v>
+        <v>1.5750931595105</v>
       </c>
       <c r="D1084" t="s">
         <v>378</v>
       </c>
       <c r="E1084">
-        <v>1.532804794934651</v>
+        <v>1.496767510539931</v>
       </c>
       <c r="F1084">
         <v>-1</v>
       </c>
       <c r="G1084">
-        <v>0.006352480238823031</v>
+        <v>0.0065249068404895</v>
       </c>
       <c r="H1084">
-        <v>0.006547195205065348</v>
+        <v>0.006583232489460069</v>
       </c>
       <c r="I1084">
-        <v>0.07471496624231744</v>
+        <v>0.07832564897056882</v>
       </c>
       <c r="J1084">
-        <v>0.7484164791239846</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1084">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L1084">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="M1084">
         <v>3.35</v>
@@ -56101,51 +56107,51 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>375</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
       <c r="A1085" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1085" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C1085">
-        <v>1.5750931595105</v>
+        <v>1.573418808481069</v>
       </c>
       <c r="D1085" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E1085">
-        <v>1.527868375834023</v>
+        <v>1.496767510539931</v>
       </c>
       <c r="F1085">
         <v>-1</v>
       </c>
       <c r="G1085">
-        <v>0.0065249068404895</v>
+        <v>0.006386581191518931</v>
       </c>
       <c r="H1085">
-        <v>0.006432131624165977</v>
+        <v>0.006583232489460069</v>
       </c>
       <c r="I1085">
-        <v>0.04722478367647698</v>
+        <v>0.07665129794113801</v>
       </c>
       <c r="J1085">
         <v>0.7591738774507669</v>
       </c>
       <c r="K1085">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1085">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1085">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1085">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1085">
         <v>1</v>
@@ -56156,46 +56162,46 @@
     </row>
     <row r="1086" spans="1:16">
       <c r="A1086" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1086" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C1086">
-        <v>1.573051853383038</v>
+        <v>1.47676751053993</v>
       </c>
       <c r="D1086" t="s">
         <v>376</v>
       </c>
       <c r="E1086">
-        <v>1.527868375834023</v>
+        <v>1.527134465637961</v>
       </c>
       <c r="F1086">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1086">
-        <v>0.006446948146616961</v>
+        <v>0.006563232489460068</v>
       </c>
       <c r="H1086">
-        <v>0.006432131624165977</v>
+        <v>0.006552865534362039</v>
       </c>
       <c r="I1086">
-        <v>0.04518347754901519</v>
+        <v>0.0503669550980308</v>
       </c>
       <c r="J1086">
         <v>0.7591738774507669</v>
       </c>
       <c r="K1086">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="L1086">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="M1086">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N1086">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1086">
         <v>1</v>
@@ -56206,46 +56212,46 @@
     </row>
     <row r="1087" spans="1:16">
       <c r="A1087" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1087" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C1087">
-        <v>1.573418808481069</v>
+        <v>1.477134465637961</v>
       </c>
       <c r="D1087" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E1087">
-        <v>1.496767510539931</v>
+        <v>1.489909681961485</v>
       </c>
       <c r="F1087">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1087">
-        <v>0.006386581191518931</v>
+        <v>0.006502865534362039</v>
       </c>
       <c r="H1087">
-        <v>0.006583232489460069</v>
+        <v>0.006470090318038515</v>
       </c>
       <c r="I1087">
-        <v>0.07665129794113801</v>
+        <v>0.01277521632352308</v>
       </c>
       <c r="J1087">
         <v>0.7591738774507669</v>
       </c>
       <c r="K1087">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1087">
+        <v>3.99</v>
+      </c>
+      <c r="M1087">
+        <v>3.28</v>
+      </c>
+      <c r="N1087">
         <v>3.98</v>
-      </c>
-      <c r="M1087">
-        <v>3.35</v>
-      </c>
-      <c r="N1087">
-        <v>4.04</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56256,96 +56262,96 @@
     </row>
     <row r="1088" spans="1:16">
       <c r="A1088" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1088" t="s">
         <v>222</v>
       </c>
       <c r="C1088">
-        <v>1.47676751053993</v>
+        <v>1.560901809388644</v>
       </c>
       <c r="D1088" t="s">
-        <v>229</v>
+        <v>374</v>
       </c>
       <c r="E1088">
-        <v>1.5350931595105</v>
+        <v>1.513807620958687</v>
       </c>
       <c r="F1088">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1088">
-        <v>0.006563232489460068</v>
+        <v>0.006539098190611355</v>
       </c>
       <c r="H1088">
-        <v>0.0064849068404895</v>
+        <v>0.006446192379041313</v>
       </c>
       <c r="I1088">
-        <v>0.05832564897056924</v>
+        <v>0.04709418842995694</v>
       </c>
       <c r="J1088">
-        <v>0.7591738774507669</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1088">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="L1088">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="M1088">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="N1088">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1088">
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
       <c r="A1089" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1089" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C1089">
-        <v>1.560901809388644</v>
+        <v>1.559619244098773</v>
       </c>
       <c r="D1089" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E1089">
-        <v>1.513807620958687</v>
+        <v>1.482184374678515</v>
       </c>
       <c r="F1089">
         <v>-1</v>
       </c>
       <c r="G1089">
-        <v>0.006539098190611355</v>
+        <v>0.006400380755901226</v>
       </c>
       <c r="H1089">
-        <v>0.006446192379041313</v>
+        <v>0.006597815625321486</v>
       </c>
       <c r="I1089">
-        <v>0.04709418842995694</v>
+        <v>0.07743486942025868</v>
       </c>
       <c r="J1089">
         <v>0.7635270523347718</v>
       </c>
       <c r="K1089">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1089">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1089">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1089">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1089">
         <v>1</v>
@@ -56356,43 +56362,43 @@
     </row>
     <row r="1090" spans="1:16">
       <c r="A1090" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1090" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C1090">
-        <v>1.559078162005382</v>
+        <v>1.462725456771905</v>
       </c>
       <c r="D1090" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E1090">
-        <v>1.513807620958687</v>
+        <v>1.475631268341949</v>
       </c>
       <c r="F1090">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1090">
-        <v>0.006460921837994617</v>
+        <v>0.006517274543228095</v>
       </c>
       <c r="H1090">
-        <v>0.006446192379041313</v>
+        <v>0.006484368731658052</v>
       </c>
       <c r="I1090">
-        <v>0.04527054104669537</v>
+        <v>0.01290581157004311</v>
       </c>
       <c r="J1090">
         <v>0.7635270523347718</v>
       </c>
       <c r="K1090">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="L1090">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1090">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="N1090">
         <v>3.98</v>
@@ -56406,316 +56412,316 @@
     </row>
     <row r="1091" spans="1:16">
       <c r="A1091" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1091" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C1091">
-        <v>1.559619244098773</v>
+        <v>1.553174199563495</v>
       </c>
       <c r="D1091" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E1091">
-        <v>1.482184374678515</v>
+        <v>1.50615112410739</v>
       </c>
       <c r="F1091">
         <v>-1</v>
       </c>
       <c r="G1091">
-        <v>0.006400380755901226</v>
+        <v>0.006546825800436505</v>
       </c>
       <c r="H1091">
-        <v>0.006597815625321486</v>
+        <v>0.006453848875892611</v>
       </c>
       <c r="I1091">
-        <v>0.07743486942025868</v>
+        <v>0.04702307545610562</v>
       </c>
       <c r="J1091">
-        <v>0.7635270523347718</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1091">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L1091">
+        <v>4.05</v>
+      </c>
+      <c r="M1091">
+        <v>3.23</v>
+      </c>
+      <c r="N1091">
         <v>3.98</v>
       </c>
-      <c r="M1091">
-        <v>3.35</v>
-      </c>
-      <c r="N1091">
-        <v>4.04</v>
-      </c>
       <c r="O1091">
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>504</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
       <c r="A1092" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1092" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C1092">
-        <v>1.485631268341949</v>
+        <v>1.551469073803319</v>
       </c>
       <c r="D1092" t="s">
-        <v>229</v>
+        <v>374</v>
       </c>
       <c r="E1092">
-        <v>1.520901809388644</v>
+        <v>1.50615112410739</v>
       </c>
       <c r="F1092">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1092">
-        <v>0.006494368731658051</v>
+        <v>0.006468530926196681</v>
       </c>
       <c r="H1092">
-        <v>0.006499098190611357</v>
+        <v>0.006453848875892611</v>
       </c>
       <c r="I1092">
-        <v>0.03527054104669514</v>
+        <v>0.04531794969592928</v>
       </c>
       <c r="J1092">
-        <v>0.7635270523347718</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1092">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="L1092">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="M1092">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="N1092">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1092">
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>504</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1093" spans="1:16">
       <c r="A1093" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1093" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C1093">
-        <v>1.553174199563495</v>
+        <v>1.552104973195178</v>
       </c>
       <c r="D1093" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E1093">
-        <v>1.50615112410739</v>
+        <v>1.474243425931813</v>
       </c>
       <c r="F1093">
         <v>-1</v>
       </c>
       <c r="G1093">
-        <v>0.006546825800436505</v>
+        <v>0.006407895026804822</v>
       </c>
       <c r="H1093">
-        <v>0.006453848875892611</v>
+        <v>0.006605756574068187</v>
       </c>
       <c r="I1093">
-        <v>0.04702307545610562</v>
+        <v>0.07786154726336525</v>
       </c>
       <c r="J1093">
         <v>0.7658974847964738</v>
       </c>
       <c r="K1093">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1093">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1093">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1093">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1093">
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
       <c r="A1094" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1094" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C1094">
-        <v>1.551469073803319</v>
+        <v>1.477856249867566</v>
       </c>
       <c r="D1094" t="s">
-        <v>376</v>
+        <v>230</v>
       </c>
       <c r="E1094">
-        <v>1.50615112410739</v>
+        <v>1.513174199563495</v>
       </c>
       <c r="F1094">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1094">
-        <v>0.006468530926196681</v>
+        <v>0.006502143750132435</v>
       </c>
       <c r="H1094">
-        <v>0.006453848875892611</v>
+        <v>0.006506825800436504</v>
       </c>
       <c r="I1094">
-        <v>0.04531794969592928</v>
+        <v>0.03531794969592905</v>
       </c>
       <c r="J1094">
         <v>0.7658974847964738</v>
       </c>
       <c r="K1094">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="L1094">
+        <v>3.99</v>
+      </c>
+      <c r="M1094">
+        <v>3.26</v>
+      </c>
+      <c r="N1094">
         <v>4.01</v>
       </c>
-      <c r="M1094">
-        <v>3.23</v>
-      </c>
-      <c r="N1094">
-        <v>3.98</v>
-      </c>
       <c r="O1094">
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
       <c r="A1095" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1095" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C1095">
-        <v>1.552104973195178</v>
+        <v>1.454879325323672</v>
       </c>
       <c r="D1095" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E1095">
-        <v>1.474243425931813</v>
+        <v>1.467856249867566</v>
       </c>
       <c r="F1095">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1095">
-        <v>0.006407895026804822</v>
+        <v>0.006525120674676328</v>
       </c>
       <c r="H1095">
-        <v>0.006605756574068187</v>
+        <v>0.006492143750132434</v>
       </c>
       <c r="I1095">
-        <v>0.07786154726336525</v>
+        <v>0.01297692454389399</v>
       </c>
       <c r="J1095">
         <v>0.7658974847964738</v>
       </c>
       <c r="K1095">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1095">
+        <v>3.99</v>
+      </c>
+      <c r="M1095">
+        <v>3.28</v>
+      </c>
+      <c r="N1095">
         <v>3.98</v>
       </c>
-      <c r="M1095">
-        <v>3.35</v>
-      </c>
-      <c r="N1095">
-        <v>4.04</v>
-      </c>
       <c r="O1095">
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
       <c r="A1096" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1096" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C1096">
-        <v>1.477856249867566</v>
+        <v>1.54817973372066</v>
       </c>
       <c r="D1096" t="s">
-        <v>229</v>
+        <v>374</v>
       </c>
       <c r="E1096">
-        <v>1.513174199563495</v>
+        <v>1.501202619606667</v>
       </c>
       <c r="F1096">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1096">
-        <v>0.006502143750132435</v>
+        <v>0.00655182026627934</v>
       </c>
       <c r="H1096">
-        <v>0.006506825800436504</v>
+        <v>0.006458797380393334</v>
       </c>
       <c r="I1096">
-        <v>0.03531794969592905</v>
+        <v>0.04697711411399341</v>
       </c>
       <c r="J1096">
-        <v>0.7658974847964738</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1096">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="L1096">
-        <v>3.99</v>
+        <v>4.05</v>
       </c>
       <c r="M1096">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="N1096">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1096">
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>374</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
       <c r="A1097" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1097" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C1097">
-        <v>1.54817973372066</v>
+        <v>1.546551210197337</v>
       </c>
       <c r="D1097" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E1097">
         <v>1.501202619606667</v>
@@ -56724,22 +56730,22 @@
         <v>-1</v>
       </c>
       <c r="G1097">
-        <v>0.00655182026627934</v>
+        <v>0.006473448789802663</v>
       </c>
       <c r="H1097">
         <v>0.006458797380393334</v>
       </c>
       <c r="I1097">
-        <v>0.04697711411399341</v>
+        <v>0.04534859059067031</v>
       </c>
       <c r="J1097">
         <v>0.7674295295335398</v>
       </c>
       <c r="K1097">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="L1097">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M1097">
         <v>3.23</v>
@@ -56756,46 +56762,46 @@
     </row>
     <row r="1098" spans="1:16">
       <c r="A1098" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1098" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1098">
-        <v>1.546551210197337</v>
+        <v>1.547248391378679</v>
       </c>
       <c r="D1098" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E1098">
-        <v>1.501202619606667</v>
+        <v>1.469111076062641</v>
       </c>
       <c r="F1098">
         <v>-1</v>
       </c>
       <c r="G1098">
-        <v>0.006473448789802663</v>
+        <v>0.00641275160862132</v>
       </c>
       <c r="H1098">
-        <v>0.006458797380393334</v>
+        <v>0.006610888923937359</v>
       </c>
       <c r="I1098">
-        <v>0.04534859059067031</v>
+        <v>0.07813731531603763</v>
       </c>
       <c r="J1098">
         <v>0.7674295295335398</v>
       </c>
       <c r="K1098">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1098">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1098">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1098">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1098">
         <v>1</v>
@@ -56806,46 +56812,46 @@
     </row>
     <row r="1099" spans="1:16">
       <c r="A1099" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1099" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C1099">
-        <v>1.547248391378679</v>
+        <v>1.47283114312999</v>
       </c>
       <c r="D1099" t="s">
-        <v>378</v>
+        <v>230</v>
       </c>
       <c r="E1099">
-        <v>1.469111076062641</v>
+        <v>1.50817973372066</v>
       </c>
       <c r="F1099">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1099">
-        <v>0.00641275160862132</v>
+        <v>0.006507168856870011</v>
       </c>
       <c r="H1099">
-        <v>0.006610888923937359</v>
+        <v>0.00651182026627934</v>
       </c>
       <c r="I1099">
-        <v>0.07813731531603763</v>
+        <v>0.03534859059067008</v>
       </c>
       <c r="J1099">
         <v>0.7674295295335398</v>
       </c>
       <c r="K1099">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="L1099">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1099">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1099">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="O1099">
         <v>1</v>
@@ -56856,46 +56862,46 @@
     </row>
     <row r="1100" spans="1:16">
       <c r="A1100" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1100" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C1100">
-        <v>1.47283114312999</v>
+        <v>1.449808257243983</v>
       </c>
       <c r="D1100" t="s">
-        <v>229</v>
+        <v>375</v>
       </c>
       <c r="E1100">
-        <v>1.50817973372066</v>
+        <v>1.46283114312999</v>
       </c>
       <c r="F1100">
         <v>1</v>
       </c>
       <c r="G1100">
-        <v>0.006507168856870011</v>
+        <v>0.006530191742756017</v>
       </c>
       <c r="H1100">
-        <v>0.00651182026627934</v>
+        <v>0.00649716885687001</v>
       </c>
       <c r="I1100">
-        <v>0.03534859059067008</v>
+        <v>0.0130228858860062</v>
       </c>
       <c r="J1100">
         <v>0.7674295295335398</v>
       </c>
       <c r="K1100">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="L1100">
         <v>3.99</v>
       </c>
       <c r="M1100">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="N1100">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1100">
         <v>1</v>
@@ -56909,13 +56915,13 @@
         <v>0</v>
       </c>
       <c r="B1101" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C1101">
         <v>1.544139279885719</v>
       </c>
       <c r="D1101" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E1101">
         <v>1.49719934786223</v>
@@ -56951,7 +56957,7 @@
         <v>1</v>
       </c>
       <c r="P1101" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1102" spans="1:16">
@@ -56959,13 +56965,13 @@
         <v>1</v>
       </c>
       <c r="B1102" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C1102">
         <v>1.542572726513238</v>
       </c>
       <c r="D1102" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E1102">
         <v>1.49719934786223</v>
@@ -57001,7 +57007,7 @@
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
@@ -57051,7 +57057,7 @@
         <v>1</v>
       </c>
       <c r="P1103" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1104" spans="1:16">
@@ -57065,7 +57071,7 @@
         <v>1.468765901234711</v>
       </c>
       <c r="D1104" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E1104">
         <v>1.504139279885718</v>
@@ -57101,48 +57107,48 @@
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
       <c r="A1105" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1105" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C1105">
-        <v>1.542905840445619</v>
+        <v>1.445705833258199</v>
       </c>
       <c r="D1105" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E1105">
-        <v>1.497534537270826</v>
+        <v>1.458765901234711</v>
       </c>
       <c r="F1105">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1105">
-        <v>0.006477094159554382</v>
+        <v>0.006534294166741802</v>
       </c>
       <c r="H1105">
-        <v>0.006462465462729174</v>
+        <v>0.006501234098765289</v>
       </c>
       <c r="I1105">
-        <v>0.0453713031747931</v>
+        <v>0.01306006797651182</v>
       </c>
       <c r="J1105">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1105">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="L1105">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1105">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="N1105">
         <v>3.98</v>
@@ -57151,201 +57157,201 @@
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
       <c r="A1106" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1106" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C1106">
-        <v>1.543648446795206</v>
+        <v>1.542905840445619</v>
       </c>
       <c r="D1106" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E1106">
-        <v>1.465306718222064</v>
+        <v>1.497534537270826</v>
       </c>
       <c r="F1106">
         <v>-1</v>
       </c>
       <c r="G1106">
-        <v>0.006416351553204793</v>
+        <v>0.006477094159554382</v>
       </c>
       <c r="H1106">
-        <v>0.006614693281777937</v>
+        <v>0.006462465462729174</v>
       </c>
       <c r="I1106">
-        <v>0.0783417285731427</v>
+        <v>0.0453713031747931</v>
       </c>
       <c r="J1106">
         <v>0.7685651587396826</v>
       </c>
       <c r="K1106">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="L1106">
+        <v>4.01</v>
+      </c>
+      <c r="M1106">
+        <v>3.23</v>
+      </c>
+      <c r="N1106">
         <v>3.98</v>
       </c>
-      <c r="M1106">
-        <v>3.35</v>
-      </c>
-      <c r="N1106">
-        <v>4.04</v>
-      </c>
       <c r="O1106">
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
       <c r="A1107" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1107" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C1107">
-        <v>1.469106279333841</v>
+        <v>1.543648446795206</v>
       </c>
       <c r="D1107" t="s">
-        <v>229</v>
+        <v>378</v>
       </c>
       <c r="E1107">
-        <v>1.504477582508635</v>
+        <v>1.465306718222064</v>
       </c>
       <c r="F1107">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1107">
-        <v>0.006510893720666159</v>
+        <v>0.006416351553204793</v>
       </c>
       <c r="H1107">
-        <v>0.006515522417491365</v>
+        <v>0.006614693281777937</v>
       </c>
       <c r="I1107">
-        <v>0.03537130317479331</v>
+        <v>0.0783417285731427</v>
       </c>
       <c r="J1107">
         <v>0.7685651587396826</v>
       </c>
       <c r="K1107">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="L1107">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1107">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1107">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="O1107">
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
       <c r="A1108" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1108" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C1108">
-        <v>1.547028640320606</v>
+        <v>1.446049324571651</v>
       </c>
       <c r="D1108" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E1108">
-        <v>1.468878847026508</v>
+        <v>1.459106279333841</v>
       </c>
       <c r="F1108">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1108">
-        <v>0.006412971359679395</v>
+        <v>0.00653395067542835</v>
       </c>
       <c r="H1108">
-        <v>0.006611121152973493</v>
+        <v>0.006500893720666159</v>
       </c>
       <c r="I1108">
-        <v>0.07814979329409821</v>
+        <v>0.01305695476219038</v>
       </c>
       <c r="J1108">
-        <v>0.7674988516338783</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1108">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1108">
+        <v>3.99</v>
+      </c>
+      <c r="M1108">
+        <v>3.28</v>
+      </c>
+      <c r="N1108">
         <v>3.98</v>
       </c>
-      <c r="M1108">
-        <v>3.35</v>
-      </c>
-      <c r="N1108">
-        <v>4.04</v>
-      </c>
       <c r="O1108">
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>506</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
       <c r="A1109" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1109" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C1109">
-        <v>1.47260376664088</v>
+        <v>1.547028640320606</v>
       </c>
       <c r="D1109" t="s">
-        <v>229</v>
+        <v>378</v>
       </c>
       <c r="E1109">
-        <v>1.507953743673557</v>
+        <v>1.468878847026508</v>
       </c>
       <c r="F1109">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1109">
-        <v>0.006507396233359121</v>
+        <v>0.006412971359679395</v>
       </c>
       <c r="H1109">
-        <v>0.006512046256326442</v>
+        <v>0.006611121152973493</v>
       </c>
       <c r="I1109">
-        <v>0.03534997703267706</v>
+        <v>0.07814979329409821</v>
       </c>
       <c r="J1109">
         <v>0.7674988516338783</v>
       </c>
       <c r="K1109">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="L1109">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1109">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1109">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="O1109">
         <v>1</v>
@@ -57356,52 +57362,52 @@
     </row>
     <row r="1110" spans="1:16">
       <c r="A1110" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1110" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C1110">
-        <v>1.54143940139528</v>
+        <v>1.449578801091863</v>
       </c>
       <c r="D1110" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E1110">
-        <v>1.462972238067567</v>
+        <v>1.462603766640879</v>
       </c>
       <c r="F1110">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1110">
-        <v>0.00641856059860472</v>
+        <v>0.006530421198908138</v>
       </c>
       <c r="H1110">
-        <v>0.006617027761932433</v>
+        <v>0.006497396233359121</v>
       </c>
       <c r="I1110">
-        <v>0.07846716332771297</v>
+        <v>0.01302496554901644</v>
       </c>
       <c r="J1110">
-        <v>0.7692620184872934</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1110">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1110">
+        <v>3.99</v>
+      </c>
+      <c r="M1110">
+        <v>3.28</v>
+      </c>
+      <c r="N1110">
         <v>3.98</v>
       </c>
-      <c r="M1110">
-        <v>3.35</v>
-      </c>
-      <c r="N1110">
-        <v>4.04</v>
-      </c>
       <c r="O1110">
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>226</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1111" spans="1:16">
@@ -57412,28 +57418,28 @@
         <v>227</v>
       </c>
       <c r="C1111">
-        <v>1.541874717879155</v>
+        <v>1.54143940139528</v>
       </c>
       <c r="D1111" t="s">
         <v>378</v>
       </c>
       <c r="E1111">
-        <v>1.463432272837593</v>
+        <v>1.462972238067567</v>
       </c>
       <c r="F1111">
         <v>-1</v>
       </c>
       <c r="G1111">
-        <v>0.006418125282120845</v>
+        <v>0.00641856059860472</v>
       </c>
       <c r="H1111">
-        <v>0.006616567727162407</v>
+        <v>0.006617027761932433</v>
       </c>
       <c r="I1111">
-        <v>0.07844244504156217</v>
+        <v>0.07846716332771297</v>
       </c>
       <c r="J1111">
-        <v>0.7691246946753454</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1111">
         <v>3.17</v>
@@ -57451,98 +57457,98 @@
         <v>1</v>
       </c>
       <c r="P1111" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1112" spans="1:16">
       <c r="A1112" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1112" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C1112">
-        <v>1.531416807455531</v>
+        <v>1.443742718807059</v>
       </c>
       <c r="D1112" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E1112">
-        <v>1.452380537847327</v>
+        <v>1.456820579361678</v>
       </c>
       <c r="F1112">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1112">
-        <v>0.006428583192544469</v>
+        <v>0.006536257281192942</v>
       </c>
       <c r="H1112">
-        <v>0.006627619462152673</v>
+        <v>0.006503179420638322</v>
       </c>
       <c r="I1112">
-        <v>0.07903626960820365</v>
+        <v>0.01307786055461868</v>
       </c>
       <c r="J1112">
-        <v>0.772423720045574</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1112">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1112">
+        <v>3.99</v>
+      </c>
+      <c r="M1112">
+        <v>3.28</v>
+      </c>
+      <c r="N1112">
         <v>3.98</v>
       </c>
-      <c r="M1112">
-        <v>3.35</v>
-      </c>
-      <c r="N1112">
-        <v>4.04</v>
-      </c>
       <c r="O1112">
         <v>1</v>
       </c>
       <c r="P1112" t="s">
-        <v>376</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1113" spans="1:16">
       <c r="A1113" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1113" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C1113">
-        <v>1.432380537847326</v>
+        <v>1.541874717879155</v>
       </c>
       <c r="D1113" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1113">
-        <v>1.48327748664915</v>
+        <v>1.463432272837593</v>
       </c>
       <c r="F1113">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1113">
-        <v>0.006607619462152673</v>
+        <v>0.006418125282120845</v>
       </c>
       <c r="H1113">
-        <v>0.00659672251335085</v>
+        <v>0.006616567727162407</v>
       </c>
       <c r="I1113">
-        <v>0.0508969488018236</v>
+        <v>0.07844244504156217</v>
       </c>
       <c r="J1113">
-        <v>0.772423720045574</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1113">
+        <v>3.17</v>
+      </c>
+      <c r="L1113">
+        <v>3.98</v>
+      </c>
+      <c r="M1113">
         <v>3.35</v>
-      </c>
-      <c r="L1113">
-        <v>4.02</v>
-      </c>
-      <c r="M1113">
-        <v>3.31</v>
       </c>
       <c r="N1113">
         <v>4.04</v>
@@ -57551,48 +57557,48 @@
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>376</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
       <c r="A1114" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1114" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C1114">
-        <v>1.530293964951826</v>
+        <v>1.443432272837593</v>
       </c>
       <c r="D1114" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E1114">
-        <v>1.451193937725116</v>
+        <v>1.494197260624607</v>
       </c>
       <c r="F1114">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1114">
-        <v>0.006429706035048174</v>
+        <v>0.006596567727162407</v>
       </c>
       <c r="H1114">
-        <v>0.006628806062274884</v>
+        <v>0.006585802739375394</v>
       </c>
       <c r="I1114">
-        <v>0.07910002722671017</v>
+        <v>0.05076498778701399</v>
       </c>
       <c r="J1114">
-        <v>0.7727779290372787</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1114">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1114">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1114">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N1114">
         <v>4.04</v>
@@ -57606,46 +57612,46 @@
     </row>
     <row r="1115" spans="1:16">
       <c r="A1115" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1115" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C1115">
-        <v>1.431193937725116</v>
+        <v>1.444197260624607</v>
       </c>
       <c r="D1115" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E1115">
-        <v>1.482105054886607</v>
+        <v>1.457271001464867</v>
       </c>
       <c r="F1115">
         <v>1</v>
       </c>
       <c r="G1115">
-        <v>0.006608806062274883</v>
+        <v>0.006535802739375394</v>
       </c>
       <c r="H1115">
-        <v>0.006597894945113392</v>
+        <v>0.006502728998535133</v>
       </c>
       <c r="I1115">
-        <v>0.05091111716149177</v>
+        <v>0.01307374084026058</v>
       </c>
       <c r="J1115">
-        <v>0.7727779290372787</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1115">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1115">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1115">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N1115">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="O1115">
         <v>1</v>
@@ -57659,40 +57665,40 @@
         <v>0</v>
       </c>
       <c r="B1116" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C1116">
-        <v>1.432233461226324</v>
+        <v>1.531416807455531</v>
       </c>
       <c r="D1116" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1116">
-        <v>1.483132166166906</v>
+        <v>1.452380537847327</v>
       </c>
       <c r="F1116">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1116">
-        <v>0.006607766538773674</v>
+        <v>0.006428583192544469</v>
       </c>
       <c r="H1116">
-        <v>0.006596867833833095</v>
+        <v>0.006627619462152673</v>
       </c>
       <c r="I1116">
-        <v>0.05089870494058157</v>
+        <v>0.07903626960820365</v>
       </c>
       <c r="J1116">
-        <v>0.7724676235145299</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1116">
+        <v>3.17</v>
+      </c>
+      <c r="L1116">
+        <v>3.98</v>
+      </c>
+      <c r="M1116">
         <v>3.35</v>
-      </c>
-      <c r="L1116">
-        <v>4.02</v>
-      </c>
-      <c r="M1116">
-        <v>3.31</v>
       </c>
       <c r="N1116">
         <v>4.04</v>
@@ -57701,39 +57707,39 @@
         <v>1</v>
       </c>
       <c r="P1116" t="s">
-        <v>227</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1117" spans="1:16">
       <c r="A1117" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1117" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1117">
-        <v>1.438192457750358</v>
+        <v>1.432380537847326</v>
       </c>
       <c r="D1117" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E1117">
-        <v>1.479020010493639</v>
+        <v>1.48327748664915</v>
       </c>
       <c r="F1117">
         <v>1</v>
       </c>
       <c r="G1117">
-        <v>0.00660180754224964</v>
+        <v>0.006607619462152673</v>
       </c>
       <c r="H1117">
-        <v>0.006580979989506362</v>
+        <v>0.00659672251335085</v>
       </c>
       <c r="I1117">
-        <v>0.0408275527432802</v>
+        <v>0.0508969488018236</v>
       </c>
       <c r="J1117">
-        <v>0.7706888185819823</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1117">
         <v>3.35</v>
@@ -57745,145 +57751,145 @@
         <v>3.31</v>
       </c>
       <c r="N1117">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1117">
         <v>1</v>
       </c>
       <c r="P1117" t="s">
-        <v>508</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1118" spans="1:16">
       <c r="A1118" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1118" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C1118">
-        <v>1.442360905903367</v>
+        <v>1.43327748664915</v>
       </c>
       <c r="D1118" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E1118">
-        <v>1.483138686131387</v>
+        <v>1.446450198250517</v>
       </c>
       <c r="F1118">
         <v>1</v>
       </c>
       <c r="G1118">
-        <v>0.006597639094096632</v>
+        <v>0.006546722513350851</v>
       </c>
       <c r="H1118">
-        <v>0.006576861313868614</v>
+        <v>0.006513549801749482</v>
       </c>
       <c r="I1118">
-        <v>0.04077778022801981</v>
+        <v>0.01317271160136713</v>
       </c>
       <c r="J1118">
-        <v>0.7694445057004873</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1118">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1118">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1118">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N1118">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="O1118">
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>509</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
       <c r="A1119" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1119" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C1119">
-        <v>1.501610911416412</v>
+        <v>1.530293964951826</v>
       </c>
       <c r="D1119" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E1119">
-        <v>1.476222021302402</v>
+        <v>1.451193937725116</v>
       </c>
       <c r="F1119">
         <v>-1</v>
       </c>
       <c r="G1119">
-        <v>0.006518389088583588</v>
+        <v>0.006429706035048174</v>
       </c>
       <c r="H1119">
-        <v>0.006523777978697598</v>
+        <v>0.006628806062274884</v>
       </c>
       <c r="I1119">
-        <v>0.02538889011400958</v>
+        <v>0.07910002722671017</v>
       </c>
       <c r="J1119">
-        <v>0.7694445057004873</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1119">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1119">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1119">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="N1119">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="O1119">
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
       <c r="A1120" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1120" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1120">
-        <v>1.442612807343595</v>
+        <v>1.431193937725116</v>
       </c>
       <c r="D1120" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E1120">
-        <v>1.483387579793225</v>
+        <v>1.482105054886607</v>
       </c>
       <c r="F1120">
         <v>1</v>
       </c>
       <c r="G1120">
-        <v>0.006597387192656404</v>
+        <v>0.006608806062274883</v>
       </c>
       <c r="H1120">
-        <v>0.006576612420206776</v>
+        <v>0.006597894945113392</v>
       </c>
       <c r="I1120">
-        <v>0.04077477244962946</v>
+        <v>0.05091111716149177</v>
       </c>
       <c r="J1120">
-        <v>0.7693693112407177</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1120">
         <v>3.35</v>
@@ -57895,63 +57901,63 @@
         <v>3.31</v>
       </c>
       <c r="N1120">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="O1120">
         <v>1</v>
       </c>
       <c r="P1120" t="s">
-        <v>378</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1121" spans="1:16">
       <c r="A1121" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1121" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C1121">
-        <v>1.50185604535526</v>
+        <v>1.432105054886608</v>
       </c>
       <c r="D1121" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E1121">
-        <v>1.443387579793225</v>
+        <v>1.445288392757726</v>
       </c>
       <c r="F1121">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1121">
-        <v>0.00651814395464474</v>
+        <v>0.006547894945113393</v>
       </c>
       <c r="H1121">
-        <v>0.006536612420206776</v>
+        <v>0.006514711607242274</v>
       </c>
       <c r="I1121">
-        <v>0.05846846556203555</v>
+        <v>0.01318333787111836</v>
       </c>
       <c r="J1121">
-        <v>0.7693693112407177</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1121">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1121">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1121">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N1121">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="O1121">
         <v>1</v>
       </c>
       <c r="P1121" t="s">
-        <v>378</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1122" spans="1:16">
@@ -57959,99 +57965,99 @@
         <v>0</v>
       </c>
       <c r="B1122" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C1122">
-        <v>1.499364642155481</v>
+        <v>1.432233461226324</v>
       </c>
       <c r="D1122" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E1122">
-        <v>1.47396197124846</v>
+        <v>1.483132166166906</v>
       </c>
       <c r="F1122">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1122">
-        <v>0.006520635357844519</v>
+        <v>0.006607766538773674</v>
       </c>
       <c r="H1122">
-        <v>0.006526038028751541</v>
+        <v>0.006596867833833095</v>
       </c>
       <c r="I1122">
-        <v>0.0254026709070212</v>
+        <v>0.05089870494058157</v>
       </c>
       <c r="J1122">
-        <v>0.7701335453510795</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1122">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="L1122">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="M1122">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="N1122">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="O1122">
         <v>1</v>
       </c>
       <c r="P1122" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="1123" spans="1:16">
       <c r="A1123" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1123" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C1123">
-        <v>1.497753215965518</v>
+        <v>1.433132166166906</v>
       </c>
       <c r="D1123" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E1123">
-        <v>1.472340659008252</v>
+        <v>1.446306194872342</v>
       </c>
       <c r="F1123">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1123">
-        <v>0.006522246784034482</v>
+        <v>0.006546867833833094</v>
       </c>
       <c r="H1123">
-        <v>0.006527659340991749</v>
+        <v>0.006513693805127658</v>
       </c>
       <c r="I1123">
-        <v>0.0254125569572663</v>
+        <v>0.01317402870543605</v>
       </c>
       <c r="J1123">
-        <v>0.770627847863338</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1123">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1123">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1123">
         <v>3.28</v>
       </c>
       <c r="N1123">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="O1123">
         <v>1</v>
       </c>
       <c r="P1123" t="s">
-        <v>510</v>
+        <v>227</v>
       </c>
     </row>
     <row r="1124" spans="1:16">
@@ -58059,81 +58065,81 @@
         <v>0</v>
       </c>
       <c r="B1124" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C1124">
-        <v>1.503784379575643</v>
+        <v>1.438192457750358</v>
       </c>
       <c r="D1124" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E1124">
-        <v>1.472966902780281</v>
+        <v>1.479020010493639</v>
       </c>
       <c r="F1124">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1124">
-        <v>0.006496215620424356</v>
+        <v>0.00660180754224964</v>
       </c>
       <c r="H1124">
-        <v>0.00652703309721972</v>
+        <v>0.006580979989506362</v>
       </c>
       <c r="I1124">
-        <v>0.03081747679536218</v>
+        <v>0.0408275527432802</v>
       </c>
       <c r="J1124">
-        <v>0.7704369198840608</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1124">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="L1124">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="M1124">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="N1124">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="O1124">
         <v>1</v>
       </c>
       <c r="P1124" t="s">
-        <v>379</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1125" spans="1:16">
       <c r="A1125" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1125" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C1125">
-        <v>1.50634775103581</v>
+        <v>1.502968227794377</v>
       </c>
       <c r="D1125" t="s">
         <v>380</v>
       </c>
       <c r="E1125">
-        <v>1.475561920801684</v>
+        <v>1.472140675051098</v>
       </c>
       <c r="F1125">
         <v>-1</v>
       </c>
       <c r="G1125">
-        <v>0.00649365224896419</v>
+        <v>0.006497031772205623</v>
       </c>
       <c r="H1125">
-        <v>0.006524438079198316</v>
+        <v>0.006527859324948902</v>
       </c>
       <c r="I1125">
-        <v>0.03078583023412573</v>
+        <v>0.03082755274327909</v>
       </c>
       <c r="J1125">
-        <v>0.7696457558531451</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1125">
         <v>3.24</v>
@@ -58151,7 +58157,907 @@
         <v>1</v>
       </c>
       <c r="P1125" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:16">
+      <c r="A1126" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1126">
+        <v>1.439020010493639</v>
+      </c>
+      <c r="D1126" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1126">
+        <v>1.452140675051098</v>
+      </c>
+      <c r="F1126">
+        <v>1</v>
+      </c>
+      <c r="G1126">
+        <v>0.006540979989506361</v>
+      </c>
+      <c r="H1126">
+        <v>0.006507859324948902</v>
+      </c>
+      <c r="I1126">
+        <v>0.01312066455745953</v>
+      </c>
+      <c r="J1126">
+        <v>0.7706888185819823</v>
+      </c>
+      <c r="K1126">
+        <v>3.31</v>
+      </c>
+      <c r="L1126">
+        <v>3.99</v>
+      </c>
+      <c r="M1126">
+        <v>3.28</v>
+      </c>
+      <c r="N1126">
+        <v>3.98</v>
+      </c>
+      <c r="O1126">
+        <v>1</v>
+      </c>
+      <c r="P1126" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:16">
+      <c r="A1127" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1127">
+        <v>1.442360905903367</v>
+      </c>
+      <c r="D1127" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1127">
+        <v>1.483138686131387</v>
+      </c>
+      <c r="F1127">
+        <v>1</v>
+      </c>
+      <c r="G1127">
+        <v>0.006597639094096632</v>
+      </c>
+      <c r="H1127">
+        <v>0.006576861313868614</v>
+      </c>
+      <c r="I1127">
+        <v>0.04077778022801981</v>
+      </c>
+      <c r="J1127">
+        <v>0.7694445057004873</v>
+      </c>
+      <c r="K1127">
+        <v>3.35</v>
+      </c>
+      <c r="L1127">
+        <v>4.02</v>
+      </c>
+      <c r="M1127">
+        <v>3.31</v>
+      </c>
+      <c r="N1127">
+        <v>4.03</v>
+      </c>
+      <c r="O1127">
+        <v>1</v>
+      </c>
+      <c r="P1127" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:16">
+      <c r="A1128" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1128">
+        <v>1.501610911416412</v>
+      </c>
+      <c r="D1128" t="s">
+        <v>224</v>
+      </c>
+      <c r="E1128">
+        <v>1.443138686131387</v>
+      </c>
+      <c r="F1128">
+        <v>-1</v>
+      </c>
+      <c r="G1128">
+        <v>0.006518389088583588</v>
+      </c>
+      <c r="H1128">
+        <v>0.006536861313868613</v>
+      </c>
+      <c r="I1128">
+        <v>0.05847222528502449</v>
+      </c>
+      <c r="J1128">
+        <v>0.7694445057004873</v>
+      </c>
+      <c r="K1128">
+        <v>3.26</v>
+      </c>
+      <c r="L1128">
+        <v>4.01</v>
+      </c>
+      <c r="M1128">
+        <v>3.31</v>
+      </c>
+      <c r="N1128">
+        <v>3.99</v>
+      </c>
+      <c r="O1128">
+        <v>1</v>
+      </c>
+      <c r="P1128" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:16">
+      <c r="A1129" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1129">
+        <v>1.442612807343595</v>
+      </c>
+      <c r="D1129" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1129">
+        <v>1.483387579793225</v>
+      </c>
+      <c r="F1129">
+        <v>1</v>
+      </c>
+      <c r="G1129">
+        <v>0.006597387192656404</v>
+      </c>
+      <c r="H1129">
+        <v>0.006576612420206776</v>
+      </c>
+      <c r="I1129">
+        <v>0.04077477244962946</v>
+      </c>
+      <c r="J1129">
+        <v>0.7693693112407177</v>
+      </c>
+      <c r="K1129">
+        <v>3.35</v>
+      </c>
+      <c r="L1129">
+        <v>4.02</v>
+      </c>
+      <c r="M1129">
+        <v>3.31</v>
+      </c>
+      <c r="N1129">
+        <v>4.03</v>
+      </c>
+      <c r="O1129">
+        <v>1</v>
+      </c>
+      <c r="P1129" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:16">
+      <c r="A1130" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1130">
+        <v>1.50185604535526</v>
+      </c>
+      <c r="D1130" t="s">
+        <v>224</v>
+      </c>
+      <c r="E1130">
+        <v>1.443387579793225</v>
+      </c>
+      <c r="F1130">
+        <v>-1</v>
+      </c>
+      <c r="G1130">
+        <v>0.00651814395464474</v>
+      </c>
+      <c r="H1130">
+        <v>0.006536612420206776</v>
+      </c>
+      <c r="I1130">
+        <v>0.05846846556203555</v>
+      </c>
+      <c r="J1130">
+        <v>0.7693693112407177</v>
+      </c>
+      <c r="K1130">
+        <v>3.26</v>
+      </c>
+      <c r="L1130">
+        <v>4.01</v>
+      </c>
+      <c r="M1130">
+        <v>3.31</v>
+      </c>
+      <c r="N1130">
+        <v>3.99</v>
+      </c>
+      <c r="O1130">
+        <v>1</v>
+      </c>
+      <c r="P1130" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:16">
+      <c r="A1131" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1131">
+        <v>1.499364642155481</v>
+      </c>
+      <c r="D1131" t="s">
+        <v>224</v>
+      </c>
+      <c r="E1131">
+        <v>1.440857964887927</v>
+      </c>
+      <c r="F1131">
+        <v>-1</v>
+      </c>
+      <c r="G1131">
+        <v>0.006520635357844519</v>
+      </c>
+      <c r="H1131">
+        <v>0.006539142035112073</v>
+      </c>
+      <c r="I1131">
+        <v>0.05850667726755354</v>
+      </c>
+      <c r="J1131">
+        <v>0.7701335453510795</v>
+      </c>
+      <c r="K1131">
+        <v>3.26</v>
+      </c>
+      <c r="L1131">
+        <v>4.01</v>
+      </c>
+      <c r="M1131">
+        <v>3.31</v>
+      </c>
+      <c r="N1131">
+        <v>3.99</v>
+      </c>
+      <c r="O1131">
+        <v>1</v>
+      </c>
+      <c r="P1131" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:16">
+      <c r="A1132" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1132">
+        <v>1.497753215965518</v>
+      </c>
+      <c r="D1132" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1132">
+        <v>1.472340659008252</v>
+      </c>
+      <c r="F1132">
+        <v>-1</v>
+      </c>
+      <c r="G1132">
+        <v>0.006522246784034482</v>
+      </c>
+      <c r="H1132">
+        <v>0.006527659340991749</v>
+      </c>
+      <c r="I1132">
+        <v>0.0254125569572663</v>
+      </c>
+      <c r="J1132">
+        <v>0.770627847863338</v>
+      </c>
+      <c r="K1132">
+        <v>3.26</v>
+      </c>
+      <c r="L1132">
+        <v>4.01</v>
+      </c>
+      <c r="M1132">
+        <v>3.28</v>
+      </c>
+      <c r="N1132">
+        <v>4</v>
+      </c>
+      <c r="O1132">
+        <v>1</v>
+      </c>
+      <c r="P1132" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:16">
+      <c r="A1133" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1133">
+        <v>1.439221823572351</v>
+      </c>
+      <c r="D1133" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1133">
+        <v>1.452340659008251</v>
+      </c>
+      <c r="F1133">
+        <v>1</v>
+      </c>
+      <c r="G1133">
+        <v>0.006540778176427649</v>
+      </c>
+      <c r="H1133">
+        <v>0.006507659340991749</v>
+      </c>
+      <c r="I1133">
+        <v>0.01311883543590042</v>
+      </c>
+      <c r="J1133">
+        <v>0.770627847863338</v>
+      </c>
+      <c r="K1133">
+        <v>3.31</v>
+      </c>
+      <c r="L1133">
+        <v>3.99</v>
+      </c>
+      <c r="M1133">
+        <v>3.28</v>
+      </c>
+      <c r="N1133">
+        <v>3.98</v>
+      </c>
+      <c r="O1133">
+        <v>1</v>
+      </c>
+      <c r="P1133" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:16">
+      <c r="A1134" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1134">
+        <v>1.498375641177962</v>
+      </c>
+      <c r="D1134" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1134">
+        <v>1.472966902780281</v>
+      </c>
+      <c r="F1134">
+        <v>-1</v>
+      </c>
+      <c r="G1134">
+        <v>0.006521624358822038</v>
+      </c>
+      <c r="H1134">
+        <v>0.00652703309721972</v>
+      </c>
+      <c r="I1134">
+        <v>0.02540873839768087</v>
+      </c>
+      <c r="J1134">
+        <v>0.7704369198840608</v>
+      </c>
+      <c r="K1134">
+        <v>3.26</v>
+      </c>
+      <c r="L1134">
+        <v>4.01</v>
+      </c>
+      <c r="M1134">
+        <v>3.28</v>
+      </c>
+      <c r="N1134">
+        <v>4</v>
+      </c>
+      <c r="O1134">
+        <v>1</v>
+      </c>
+      <c r="P1134" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:16">
+      <c r="A1135" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1135">
+        <v>1.439853795183759</v>
+      </c>
+      <c r="D1135" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1135">
+        <v>1.452966902780281</v>
+      </c>
+      <c r="F1135">
+        <v>1</v>
+      </c>
+      <c r="G1135">
+        <v>0.006540146204816242</v>
+      </c>
+      <c r="H1135">
+        <v>0.006507033097219719</v>
+      </c>
+      <c r="I1135">
+        <v>0.01311310759652207</v>
+      </c>
+      <c r="J1135">
+        <v>0.7704369198840608</v>
+      </c>
+      <c r="K1135">
+        <v>3.31</v>
+      </c>
+      <c r="L1135">
+        <v>3.99</v>
+      </c>
+      <c r="M1135">
+        <v>3.28</v>
+      </c>
+      <c r="N1135">
+        <v>3.98</v>
+      </c>
+      <c r="O1135">
+        <v>1</v>
+      </c>
+      <c r="P1135" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:16">
+      <c r="A1136" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1136" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1136">
+        <v>1.500954835918747</v>
+      </c>
+      <c r="D1136" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1136">
+        <v>1.475561920801684</v>
+      </c>
+      <c r="F1136">
+        <v>-1</v>
+      </c>
+      <c r="G1136">
+        <v>0.006519045164081253</v>
+      </c>
+      <c r="H1136">
+        <v>0.006524438079198316</v>
+      </c>
+      <c r="I1136">
+        <v>0.02539291511706265</v>
+      </c>
+      <c r="J1136">
+        <v>0.7696457558531451</v>
+      </c>
+      <c r="K1136">
+        <v>3.26</v>
+      </c>
+      <c r="L1136">
+        <v>4.01</v>
+      </c>
+      <c r="M1136">
+        <v>3.28</v>
+      </c>
+      <c r="N1136">
+        <v>4</v>
+      </c>
+      <c r="O1136">
+        <v>1</v>
+      </c>
+      <c r="P1136" t="s">
         <v>228</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:16">
+      <c r="A1137" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1137">
+        <v>1.44247254812609</v>
+      </c>
+      <c r="D1137" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1137">
+        <v>1.455561920801684</v>
+      </c>
+      <c r="F1137">
+        <v>1</v>
+      </c>
+      <c r="G1137">
+        <v>0.006537527451873911</v>
+      </c>
+      <c r="H1137">
+        <v>0.006504438079198316</v>
+      </c>
+      <c r="I1137">
+        <v>0.01308937267559429</v>
+      </c>
+      <c r="J1137">
+        <v>0.7696457558531451</v>
+      </c>
+      <c r="K1137">
+        <v>3.31</v>
+      </c>
+      <c r="L1137">
+        <v>3.99</v>
+      </c>
+      <c r="M1137">
+        <v>3.28</v>
+      </c>
+      <c r="N1137">
+        <v>3.98</v>
+      </c>
+      <c r="O1137">
+        <v>1</v>
+      </c>
+      <c r="P1137" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:16">
+      <c r="A1138" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1138">
+        <v>1.506090942130069</v>
+      </c>
+      <c r="D1138" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1138">
+        <v>1.475301941415625</v>
+      </c>
+      <c r="F1138">
+        <v>-1</v>
+      </c>
+      <c r="G1138">
+        <v>0.006493909057869932</v>
+      </c>
+      <c r="H1138">
+        <v>0.006524698058584376</v>
+      </c>
+      <c r="I1138">
+        <v>0.03078900071444357</v>
+      </c>
+      <c r="J1138">
+        <v>0.7697250178610899</v>
+      </c>
+      <c r="K1138">
+        <v>3.24</v>
+      </c>
+      <c r="L1138">
+        <v>4</v>
+      </c>
+      <c r="M1138">
+        <v>3.28</v>
+      </c>
+      <c r="N1138">
+        <v>4</v>
+      </c>
+      <c r="O1138">
+        <v>1</v>
+      </c>
+      <c r="P1138" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:16">
+      <c r="A1139" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1139">
+        <v>1.442210190879793</v>
+      </c>
+      <c r="D1139" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1139">
+        <v>1.455301941415625</v>
+      </c>
+      <c r="F1139">
+        <v>1</v>
+      </c>
+      <c r="G1139">
+        <v>0.006537789809120208</v>
+      </c>
+      <c r="H1139">
+        <v>0.006504698058584375</v>
+      </c>
+      <c r="I1139">
+        <v>0.01309175053583234</v>
+      </c>
+      <c r="J1139">
+        <v>0.7697250178610899</v>
+      </c>
+      <c r="K1139">
+        <v>3.31</v>
+      </c>
+      <c r="L1139">
+        <v>3.99</v>
+      </c>
+      <c r="M1139">
+        <v>3.28</v>
+      </c>
+      <c r="N1139">
+        <v>3.98</v>
+      </c>
+      <c r="O1139">
+        <v>1</v>
+      </c>
+      <c r="P1139" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:16">
+      <c r="A1140" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1140">
+        <v>1.503436737971889</v>
+      </c>
+      <c r="D1140" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1140">
+        <v>1.472614969304875</v>
+      </c>
+      <c r="F1140">
+        <v>-1</v>
+      </c>
+      <c r="G1140">
+        <v>0.006496563262028111</v>
+      </c>
+      <c r="H1140">
+        <v>0.006527385030695125</v>
+      </c>
+      <c r="I1140">
+        <v>0.03082176866701358</v>
+      </c>
+      <c r="J1140">
+        <v>0.770544216675343</v>
+      </c>
+      <c r="K1140">
+        <v>3.24</v>
+      </c>
+      <c r="L1140">
+        <v>4</v>
+      </c>
+      <c r="M1140">
+        <v>3.28</v>
+      </c>
+      <c r="N1140">
+        <v>4</v>
+      </c>
+      <c r="O1140">
+        <v>1</v>
+      </c>
+      <c r="P1140" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:16">
+      <c r="A1141" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1141">
+        <v>1.439498642804615</v>
+      </c>
+      <c r="D1141" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1141">
+        <v>1.452614969304875</v>
+      </c>
+      <c r="F1141">
+        <v>1</v>
+      </c>
+      <c r="G1141">
+        <v>0.006540501357195385</v>
+      </c>
+      <c r="H1141">
+        <v>0.006507385030695125</v>
+      </c>
+      <c r="I1141">
+        <v>0.01311632650026029</v>
+      </c>
+      <c r="J1141">
+        <v>0.770544216675343</v>
+      </c>
+      <c r="K1141">
+        <v>3.31</v>
+      </c>
+      <c r="L1141">
+        <v>3.99</v>
+      </c>
+      <c r="M1141">
+        <v>3.28</v>
+      </c>
+      <c r="N1141">
+        <v>3.98</v>
+      </c>
+      <c r="O1141">
+        <v>1</v>
+      </c>
+      <c r="P1141" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:16">
+      <c r="A1142" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1142">
+        <v>1.503858854335709</v>
+      </c>
+      <c r="D1142" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1142">
+        <v>1.473042296981829</v>
+      </c>
+      <c r="F1142">
+        <v>-1</v>
+      </c>
+      <c r="G1142">
+        <v>0.006496141145664291</v>
+      </c>
+      <c r="H1142">
+        <v>0.006526957703018171</v>
+      </c>
+      <c r="I1142">
+        <v>0.03081655735387967</v>
+      </c>
+      <c r="J1142">
+        <v>0.7704139338470033</v>
+      </c>
+      <c r="K1142">
+        <v>3.24</v>
+      </c>
+      <c r="L1142">
+        <v>4</v>
+      </c>
+      <c r="M1142">
+        <v>3.28</v>
+      </c>
+      <c r="N1142">
+        <v>4</v>
+      </c>
+      <c r="O1142">
+        <v>1</v>
+      </c>
+      <c r="P1142" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:16">
+      <c r="A1143" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1143">
+        <v>1.439929878966419</v>
+      </c>
+      <c r="D1143" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1143">
+        <v>1.453042296981829</v>
+      </c>
+      <c r="F1143">
+        <v>1</v>
+      </c>
+      <c r="G1143">
+        <v>0.006540070121033582</v>
+      </c>
+      <c r="H1143">
+        <v>0.00650695770301817</v>
+      </c>
+      <c r="I1143">
+        <v>0.01311241801540985</v>
+      </c>
+      <c r="J1143">
+        <v>0.7704139338470033</v>
+      </c>
+      <c r="K1143">
+        <v>3.31</v>
+      </c>
+      <c r="L1143">
+        <v>3.99</v>
+      </c>
+      <c r="M1143">
+        <v>3.28</v>
+      </c>
+      <c r="N1143">
+        <v>3.98</v>
+      </c>
+      <c r="O1143">
+        <v>1</v>
+      </c>
+      <c r="P1143" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -709,10 +709,10 @@
     <t>2021-08-23</t>
   </si>
   <si>
-    <t>2021-08-20</t>
+    <t>2021-08-19</t>
   </si>
   <si>
-    <t>2021-08-19</t>
+    <t>2021-08-20</t>
   </si>
   <si>
     <t>2016-07-22</t>
@@ -1150,7 +1150,7 @@
     <t>2021-08-18</t>
   </si>
   <si>
-    <t>2021-08-30</t>
+    <t>2021-08-31</t>
   </si>
   <si>
     <t>2021-08-11</t>
@@ -53571,10 +53571,10 @@
         <v>1.710325886585777</v>
       </c>
       <c r="D1034" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E1034">
-        <v>1.824371610287536</v>
+        <v>1.819273719837115</v>
       </c>
       <c r="F1034">
         <v>1</v>
@@ -53583,10 +53583,10 @@
         <v>0.006789674113414224</v>
       </c>
       <c r="H1034">
-        <v>0.006275628389712465</v>
+        <v>0.006420726280162885</v>
       </c>
       <c r="I1034">
-        <v>0.1140457237017589</v>
+        <v>0.1089478332513383</v>
       </c>
       <c r="J1034">
         <v>0.6827080950038233</v>
@@ -53598,10 +53598,10 @@
         <v>4.25</v>
       </c>
       <c r="M1034">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
       <c r="N1034">
-        <v>4.05</v>
+        <v>4.12</v>
       </c>
       <c r="O1034">
         <v>1</v>
@@ -53874,7 +53874,7 @@
         <v>378</v>
       </c>
       <c r="E1040">
-        <v>1.707946515327263</v>
+        <v>1.727946515327263</v>
       </c>
       <c r="F1040">
         <v>1</v>
@@ -53883,10 +53883,10 @@
         <v>0.00627344524131285</v>
       </c>
       <c r="H1040">
-        <v>0.006192053484672737</v>
+        <v>0.006212053484672737</v>
       </c>
       <c r="I1040">
-        <v>0.001391756640112263</v>
+        <v>0.02139175664011228</v>
       </c>
       <c r="J1040">
         <v>0.6898626106685345</v>
@@ -53901,7 +53901,7 @@
         <v>3.25</v>
       </c>
       <c r="N1040">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1040">
         <v>1</v>
@@ -53924,7 +53924,7 @@
         <v>378</v>
       </c>
       <c r="E1041">
-        <v>1.707946515327263</v>
+        <v>1.727946515327263</v>
       </c>
       <c r="F1041">
         <v>1</v>
@@ -53933,10 +53933,10 @@
         <v>0.00627344524131285</v>
       </c>
       <c r="H1041">
-        <v>0.006192053484672737</v>
+        <v>0.006212053484672737</v>
       </c>
       <c r="I1041">
-        <v>0.001391756640112263</v>
+        <v>0.02139175664011228</v>
       </c>
       <c r="J1041">
         <v>0.6898626106685345</v>
@@ -53951,7 +53951,7 @@
         <v>3.25</v>
       </c>
       <c r="N1041">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1041">
         <v>1</v>
@@ -54274,7 +54274,7 @@
         <v>378</v>
       </c>
       <c r="E1048">
-        <v>1.672027779389007</v>
+        <v>1.692027779389007</v>
       </c>
       <c r="F1048">
         <v>1</v>
@@ -54283,10 +54283,10 @@
         <v>0.006310027092376119</v>
       </c>
       <c r="H1048">
-        <v>0.006227972220610994</v>
+        <v>0.006247972220610993</v>
       </c>
       <c r="I1048">
-        <v>0.002054871765125643</v>
+        <v>0.02205487176512566</v>
       </c>
       <c r="J1048">
         <v>0.7009145294187672</v>
@@ -54301,7 +54301,7 @@
         <v>3.25</v>
       </c>
       <c r="N1048">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1048">
         <v>1</v>
@@ -54324,7 +54324,7 @@
         <v>378</v>
       </c>
       <c r="E1049">
-        <v>1.672027779389007</v>
+        <v>1.692027779389007</v>
       </c>
       <c r="F1049">
         <v>1</v>
@@ -54333,10 +54333,10 @@
         <v>0.006310027092376119</v>
       </c>
       <c r="H1049">
-        <v>0.006227972220610994</v>
+        <v>0.006247972220610993</v>
       </c>
       <c r="I1049">
-        <v>0.002054871765125643</v>
+        <v>0.02205487176512566</v>
       </c>
       <c r="J1049">
         <v>0.7009145294187672</v>
@@ -54351,7 +54351,7 @@
         <v>3.25</v>
       </c>
       <c r="N1049">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1049">
         <v>1</v>
@@ -54421,10 +54421,10 @@
         <v>1.612528556387221</v>
       </c>
       <c r="D1051" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1051">
-        <v>1.693058165369526</v>
+        <v>1.581258625390344</v>
       </c>
       <c r="F1051">
         <v>1</v>
@@ -54433,10 +54433,10 @@
         <v>0.006887471443612779</v>
       </c>
       <c r="H1051">
-        <v>0.006726941834630474</v>
+        <v>0.006898741374609657</v>
       </c>
       <c r="I1051">
-        <v>0.08052960898230443</v>
+        <v>-0.03126993099687692</v>
       </c>
       <c r="J1051">
         <v>0.7089976998959082</v>
@@ -54448,10 +54448,10 @@
         <v>4.25</v>
       </c>
       <c r="M1051">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N1051">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="O1051">
         <v>1</v>
@@ -54574,7 +54574,7 @@
         <v>378</v>
       </c>
       <c r="E1054">
-        <v>1.645757475338299</v>
+        <v>1.665757475338299</v>
       </c>
       <c r="F1054">
         <v>1</v>
@@ -54583,10 +54583,10 @@
         <v>0.006336782386655457</v>
       </c>
       <c r="H1054">
-        <v>0.006254242524661702</v>
+        <v>0.006274242524661702</v>
       </c>
       <c r="I1054">
-        <v>0.002539861993754666</v>
+        <v>0.02253986199375468</v>
       </c>
       <c r="J1054">
         <v>0.7089976998959082</v>
@@ -54601,7 +54601,7 @@
         <v>3.25</v>
       </c>
       <c r="N1054">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -54624,7 +54624,7 @@
         <v>378</v>
       </c>
       <c r="E1055">
-        <v>1.645757475338299</v>
+        <v>1.665757475338299</v>
       </c>
       <c r="F1055">
         <v>1</v>
@@ -54633,10 +54633,10 @@
         <v>0.006336782386655457</v>
       </c>
       <c r="H1055">
-        <v>0.006254242524661702</v>
+        <v>0.006274242524661702</v>
       </c>
       <c r="I1055">
-        <v>0.002539861993754666</v>
+        <v>0.02253986199375468</v>
       </c>
       <c r="J1055">
         <v>0.7089976998959082</v>
@@ -54651,7 +54651,7 @@
         <v>3.25</v>
       </c>
       <c r="N1055">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -54921,10 +54921,10 @@
         <v>1.57354551882728</v>
       </c>
       <c r="D1061" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1061">
-        <v>1.655856610708829</v>
+        <v>1.541961208495242</v>
       </c>
       <c r="F1061">
         <v>1</v>
@@ -54933,10 +54933,10 @@
         <v>0.00692645448117272</v>
       </c>
       <c r="H1061">
-        <v>0.006764143389291171</v>
+        <v>0.006938038791504758</v>
       </c>
       <c r="I1061">
-        <v>0.08231109188154928</v>
+        <v>-0.0315843103320379</v>
       </c>
       <c r="J1061">
         <v>0.7194770110679355</v>
@@ -54948,10 +54948,10 @@
         <v>4.25</v>
       </c>
       <c r="M1061">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N1061">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="O1061">
         <v>1</v>
@@ -56224,7 +56224,7 @@
         <v>378</v>
       </c>
       <c r="E1087">
-        <v>1.482684898285008</v>
+        <v>1.502684898285008</v>
       </c>
       <c r="F1087">
         <v>1</v>
@@ -56233,10 +56233,10 @@
         <v>0.006502865534362039</v>
       </c>
       <c r="H1087">
-        <v>0.006417315101714992</v>
+        <v>0.006437315101714993</v>
       </c>
       <c r="I1087">
-        <v>0.005550432647046133</v>
+        <v>0.02555043264704615</v>
       </c>
       <c r="J1087">
         <v>0.7591738774507669</v>
@@ -56251,7 +56251,7 @@
         <v>3.25</v>
       </c>
       <c r="N1087">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56274,7 +56274,7 @@
         <v>378</v>
       </c>
       <c r="E1088">
-        <v>1.482684898285008</v>
+        <v>1.502684898285008</v>
       </c>
       <c r="F1088">
         <v>1</v>
@@ -56283,10 +56283,10 @@
         <v>0.006502865534362039</v>
       </c>
       <c r="H1088">
-        <v>0.006417315101714992</v>
+        <v>0.006437315101714993</v>
       </c>
       <c r="I1088">
-        <v>0.005550432647046133</v>
+        <v>0.02555043264704615</v>
       </c>
       <c r="J1088">
         <v>0.7591738774507669</v>
@@ -56301,7 +56301,7 @@
         <v>3.25</v>
       </c>
       <c r="N1088">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1088">
         <v>1</v>
@@ -56474,7 +56474,7 @@
         <v>378</v>
       </c>
       <c r="E1092">
-        <v>1.468537079911992</v>
+        <v>1.488537079911992</v>
       </c>
       <c r="F1092">
         <v>1</v>
@@ -56483,10 +56483,10 @@
         <v>0.006517274543228095</v>
       </c>
       <c r="H1092">
-        <v>0.006431462920088009</v>
+        <v>0.006451462920088009</v>
       </c>
       <c r="I1092">
-        <v>0.005811623140086208</v>
+        <v>0.02581162314008623</v>
       </c>
       <c r="J1092">
         <v>0.7635270523347718</v>
@@ -56501,7 +56501,7 @@
         <v>3.25</v>
       </c>
       <c r="N1092">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1092">
         <v>1</v>
@@ -56624,7 +56624,7 @@
         <v>231</v>
       </c>
       <c r="E1095">
-        <v>1.513174199563495</v>
+        <v>1.505515224715531</v>
       </c>
       <c r="F1095">
         <v>1</v>
@@ -56633,10 +56633,10 @@
         <v>0.006585756574068187</v>
       </c>
       <c r="H1095">
-        <v>0.006506825800436504</v>
+        <v>0.00651448477528447</v>
       </c>
       <c r="I1095">
-        <v>0.05893077363168286</v>
+        <v>0.05127179878371813</v>
       </c>
       <c r="J1095">
         <v>0.7658974847964738</v>
@@ -56648,7 +56648,7 @@
         <v>4.02</v>
       </c>
       <c r="M1095">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="N1095">
         <v>4.01</v>
@@ -56674,7 +56674,7 @@
         <v>378</v>
       </c>
       <c r="E1096">
-        <v>1.46083317441146</v>
+        <v>1.48083317441146</v>
       </c>
       <c r="F1096">
         <v>1</v>
@@ -56683,10 +56683,10 @@
         <v>0.006525120674676328</v>
       </c>
       <c r="H1096">
-        <v>0.00643916682558854</v>
+        <v>0.00645916682558854</v>
       </c>
       <c r="I1096">
-        <v>0.005953849087788399</v>
+        <v>0.02595384908778842</v>
       </c>
       <c r="J1096">
         <v>0.7658974847964738</v>
@@ -56701,7 +56701,7 @@
         <v>3.25</v>
       </c>
       <c r="N1096">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1096">
         <v>1</v>
@@ -56715,43 +56715,43 @@
         <v>0</v>
       </c>
       <c r="B1097" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C1097">
-        <v>1.54817973372066</v>
+        <v>1.533762485471971</v>
       </c>
       <c r="D1097" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E1097">
-        <v>1.501202619606667</v>
+        <v>1.469111076062641</v>
       </c>
       <c r="F1097">
         <v>-1</v>
       </c>
       <c r="G1097">
-        <v>0.00655182026627934</v>
+        <v>0.006706237514528029</v>
       </c>
       <c r="H1097">
-        <v>0.006458797380393334</v>
+        <v>0.006610888923937359</v>
       </c>
       <c r="I1097">
-        <v>0.04697711411399341</v>
+        <v>0.06465140940932956</v>
       </c>
       <c r="J1097">
         <v>0.7674295295335398</v>
       </c>
       <c r="K1097">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
       <c r="L1097">
-        <v>4.05</v>
+        <v>4.12</v>
       </c>
       <c r="M1097">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1097">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1097">
         <v>1</v>
@@ -56821,7 +56821,7 @@
         <v>1.449111076062641</v>
       </c>
       <c r="D1099" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E1099">
         <v>1.50817973372066</v>
@@ -56874,7 +56874,7 @@
         <v>378</v>
       </c>
       <c r="E1100">
-        <v>1.455854029015996</v>
+        <v>1.475854029015996</v>
       </c>
       <c r="F1100">
         <v>1</v>
@@ -56883,10 +56883,10 @@
         <v>0.006530191742756017</v>
       </c>
       <c r="H1100">
-        <v>0.006444145970984005</v>
+        <v>0.006464145970984004</v>
       </c>
       <c r="I1100">
-        <v>0.006045771772012376</v>
+        <v>0.02604577177201239</v>
       </c>
       <c r="J1100">
         <v>0.7674295295335398</v>
@@ -56901,7 +56901,7 @@
         <v>3.25</v>
       </c>
       <c r="N1100">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1100">
         <v>1</v>
@@ -56915,43 +56915,43 @@
         <v>0</v>
       </c>
       <c r="B1101" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C1101">
-        <v>1.544139279885719</v>
+        <v>1.543319483815254</v>
       </c>
       <c r="D1101" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E1101">
-        <v>1.49719934786223</v>
+        <v>1.464959075956183</v>
       </c>
       <c r="F1101">
         <v>-1</v>
       </c>
       <c r="G1101">
-        <v>0.006555860720114281</v>
+        <v>0.006416680516184746</v>
       </c>
       <c r="H1101">
-        <v>0.006462800652137769</v>
+        <v>0.006615040924043817</v>
       </c>
       <c r="I1101">
-        <v>0.04693993202348823</v>
+        <v>0.07836040785907095</v>
       </c>
       <c r="J1101">
         <v>0.7686689325503931</v>
       </c>
       <c r="K1101">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1101">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1101">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1101">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1101">
         <v>1</v>
@@ -56965,43 +56965,43 @@
         <v>1</v>
       </c>
       <c r="B1102" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C1102">
-        <v>1.543319483815254</v>
+        <v>1.444959075956183</v>
       </c>
       <c r="D1102" t="s">
-        <v>379</v>
+        <v>231</v>
       </c>
       <c r="E1102">
-        <v>1.464959075956183</v>
+        <v>1.496452590560214</v>
       </c>
       <c r="F1102">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1102">
-        <v>0.006416680516184746</v>
+        <v>0.006595040924043817</v>
       </c>
       <c r="H1102">
-        <v>0.006615040924043817</v>
+        <v>0.006523547409439786</v>
       </c>
       <c r="I1102">
-        <v>0.07836040785907095</v>
+        <v>0.05149351460403162</v>
       </c>
       <c r="J1102">
         <v>0.7686689325503931</v>
       </c>
       <c r="K1102">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1102">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1102">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="N1102">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="O1102">
         <v>1</v>
@@ -57015,43 +57015,43 @@
         <v>2</v>
       </c>
       <c r="B1103" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C1103">
-        <v>1.444959075956183</v>
+        <v>1.445705833258199</v>
       </c>
       <c r="D1103" t="s">
-        <v>231</v>
+        <v>378</v>
       </c>
       <c r="E1103">
-        <v>1.504139279885718</v>
+        <v>1.471825969211222</v>
       </c>
       <c r="F1103">
         <v>1</v>
       </c>
       <c r="G1103">
-        <v>0.006595040924043817</v>
+        <v>0.006534294166741802</v>
       </c>
       <c r="H1103">
-        <v>0.006515860720114282</v>
+        <v>0.006468174030788778</v>
       </c>
       <c r="I1103">
-        <v>0.05918020392953594</v>
+        <v>0.02612013595302365</v>
       </c>
       <c r="J1103">
         <v>0.7686689325503931</v>
       </c>
       <c r="K1103">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1103">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1103">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="N1103">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="O1103">
         <v>1</v>
@@ -57062,93 +57062,93 @@
     </row>
     <row r="1104" spans="1:16">
       <c r="A1104" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1104" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C1104">
-        <v>1.445705833258199</v>
+        <v>1.543648446795206</v>
       </c>
       <c r="D1104" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1104">
-        <v>1.451825969211222</v>
+        <v>1.465306718222064</v>
       </c>
       <c r="F1104">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1104">
-        <v>0.006534294166741802</v>
+        <v>0.006416351553204793</v>
       </c>
       <c r="H1104">
-        <v>0.006448174030788778</v>
+        <v>0.006614693281777937</v>
       </c>
       <c r="I1104">
-        <v>0.006120135953023631</v>
+        <v>0.0783417285731427</v>
       </c>
       <c r="J1104">
-        <v>0.7686689325503931</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1104">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="L1104">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1104">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N1104">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="O1104">
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
       <c r="A1105" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1105" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C1105">
-        <v>1.543648446795206</v>
+        <v>1.445306718222063</v>
       </c>
       <c r="D1105" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E1105">
-        <v>1.465306718222064</v>
+        <v>1.496049324571651</v>
       </c>
       <c r="F1105">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1105">
-        <v>0.006416351553204793</v>
+        <v>0.006594693281777936</v>
       </c>
       <c r="H1105">
-        <v>0.006614693281777937</v>
+        <v>0.006583950675428349</v>
       </c>
       <c r="I1105">
-        <v>0.0783417285731427</v>
+        <v>0.05074260634958749</v>
       </c>
       <c r="J1105">
         <v>0.7685651587396826</v>
       </c>
       <c r="K1105">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1105">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1105">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N1105">
         <v>4.04</v>
@@ -57162,46 +57162,46 @@
     </row>
     <row r="1106" spans="1:16">
       <c r="A1106" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1106" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C1106">
-        <v>1.445306718222063</v>
+        <v>1.446049324571651</v>
       </c>
       <c r="D1106" t="s">
-        <v>232</v>
+        <v>378</v>
       </c>
       <c r="E1106">
-        <v>1.496791930921238</v>
+        <v>1.472163234096032</v>
       </c>
       <c r="F1106">
         <v>1</v>
       </c>
       <c r="G1106">
-        <v>0.006594693281777936</v>
+        <v>0.00653395067542835</v>
       </c>
       <c r="H1106">
-        <v>0.006523208069078762</v>
+        <v>0.006467836765903968</v>
       </c>
       <c r="I1106">
-        <v>0.05148521269917472</v>
+        <v>0.0261139095243812</v>
       </c>
       <c r="J1106">
         <v>0.7685651587396826</v>
       </c>
       <c r="K1106">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1106">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1106">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="N1106">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="O1106">
         <v>1</v>
@@ -57212,93 +57212,93 @@
     </row>
     <row r="1107" spans="1:16">
       <c r="A1107" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1107" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C1107">
-        <v>1.446049324571651</v>
+        <v>1.547028640320606</v>
       </c>
       <c r="D1107" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1107">
-        <v>1.452163234096032</v>
+        <v>1.468878847026508</v>
       </c>
       <c r="F1107">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1107">
-        <v>0.00653395067542835</v>
+        <v>0.006412971359679395</v>
       </c>
       <c r="H1107">
-        <v>0.006447836765903969</v>
+        <v>0.006611121152973493</v>
       </c>
       <c r="I1107">
-        <v>0.006113909524381178</v>
+        <v>0.07814979329409821</v>
       </c>
       <c r="J1107">
-        <v>0.7685651587396826</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1107">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="L1107">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1107">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N1107">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="O1107">
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>222</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
       <c r="A1108" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1108" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C1108">
-        <v>1.547028640320606</v>
+        <v>1.448878847026507</v>
       </c>
       <c r="D1108" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E1108">
-        <v>1.468878847026508</v>
+        <v>1.499578801091863</v>
       </c>
       <c r="F1108">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1108">
-        <v>0.006412971359679395</v>
+        <v>0.006591121152973492</v>
       </c>
       <c r="H1108">
-        <v>0.006611121152973493</v>
+        <v>0.006580421198908138</v>
       </c>
       <c r="I1108">
-        <v>0.07814979329409821</v>
+        <v>0.05069995406535543</v>
       </c>
       <c r="J1108">
         <v>0.7674988516338783</v>
       </c>
       <c r="K1108">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1108">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1108">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N1108">
         <v>4.04</v>
@@ -57312,46 +57312,46 @@
     </row>
     <row r="1109" spans="1:16">
       <c r="A1109" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1109" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C1109">
-        <v>1.448878847026507</v>
+        <v>1.449578801091863</v>
       </c>
       <c r="D1109" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1109">
-        <v>1.499578801091863</v>
+        <v>1.475628732189896</v>
       </c>
       <c r="F1109">
         <v>1</v>
       </c>
       <c r="G1109">
-        <v>0.006591121152973492</v>
+        <v>0.006530421198908138</v>
       </c>
       <c r="H1109">
-        <v>0.006580421198908138</v>
+        <v>0.006464371267810105</v>
       </c>
       <c r="I1109">
-        <v>0.05069995406535543</v>
+        <v>0.02604993109803289</v>
       </c>
       <c r="J1109">
         <v>0.7674988516338783</v>
       </c>
       <c r="K1109">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1109">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1109">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N1109">
-        <v>4.04</v>
+        <v>3.97</v>
       </c>
       <c r="O1109">
         <v>1</v>
@@ -57362,93 +57362,93 @@
     </row>
     <row r="1110" spans="1:16">
       <c r="A1110" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1110" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C1110">
-        <v>1.449578801091863</v>
+        <v>1.54143940139528</v>
       </c>
       <c r="D1110" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1110">
-        <v>1.455628732189896</v>
+        <v>1.462972238067567</v>
       </c>
       <c r="F1110">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1110">
-        <v>0.006530421198908138</v>
+        <v>0.00641856059860472</v>
       </c>
       <c r="H1110">
-        <v>0.006444371267810105</v>
+        <v>0.006617027761932433</v>
       </c>
       <c r="I1110">
-        <v>0.006049931098032868</v>
+        <v>0.07846716332771297</v>
       </c>
       <c r="J1110">
-        <v>0.7674988516338783</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1110">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="L1110">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1110">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N1110">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="O1110">
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>507</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1111" spans="1:16">
       <c r="A1111" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1111" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C1111">
-        <v>1.54143940139528</v>
+        <v>1.442972238067567</v>
       </c>
       <c r="D1111" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E1111">
-        <v>1.462972238067567</v>
+        <v>1.493742718807059</v>
       </c>
       <c r="F1111">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1111">
-        <v>0.00641856059860472</v>
+        <v>0.006597027761932432</v>
       </c>
       <c r="H1111">
-        <v>0.006617027761932433</v>
+        <v>0.006586257281192941</v>
       </c>
       <c r="I1111">
-        <v>0.07846716332771297</v>
+        <v>0.0507704807394922</v>
       </c>
       <c r="J1111">
         <v>0.7692620184872934</v>
       </c>
       <c r="K1111">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1111">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1111">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N1111">
         <v>4.04</v>
@@ -57462,46 +57462,46 @@
     </row>
     <row r="1112" spans="1:16">
       <c r="A1112" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C1112">
-        <v>1.442972238067567</v>
+        <v>1.443742718807059</v>
       </c>
       <c r="D1112" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1112">
-        <v>1.493742718807059</v>
+        <v>1.469898439916297</v>
       </c>
       <c r="F1112">
         <v>1</v>
       </c>
       <c r="G1112">
-        <v>0.006597027761932432</v>
+        <v>0.006536257281192942</v>
       </c>
       <c r="H1112">
-        <v>0.006586257281192941</v>
+        <v>0.006470101560083704</v>
       </c>
       <c r="I1112">
-        <v>0.0507704807394922</v>
+        <v>0.02615572110923781</v>
       </c>
       <c r="J1112">
         <v>0.7692620184872934</v>
       </c>
       <c r="K1112">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1112">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1112">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N1112">
-        <v>4.04</v>
+        <v>3.97</v>
       </c>
       <c r="O1112">
         <v>1</v>
@@ -57512,93 +57512,93 @@
     </row>
     <row r="1113" spans="1:16">
       <c r="A1113" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1113" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C1113">
-        <v>1.443742718807059</v>
+        <v>1.541874717879155</v>
       </c>
       <c r="D1113" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1113">
-        <v>1.449898439916297</v>
+        <v>1.463432272837593</v>
       </c>
       <c r="F1113">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1113">
-        <v>0.006536257281192942</v>
+        <v>0.006418125282120845</v>
       </c>
       <c r="H1113">
-        <v>0.006450101560083704</v>
+        <v>0.006616567727162407</v>
       </c>
       <c r="I1113">
-        <v>0.006155721109237788</v>
+        <v>0.07844244504156217</v>
       </c>
       <c r="J1113">
-        <v>0.7692620184872934</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1113">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="L1113">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1113">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N1113">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="O1113">
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
       <c r="A1114" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1114" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C1114">
-        <v>1.541874717879155</v>
+        <v>1.443432272837593</v>
       </c>
       <c r="D1114" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E1114">
-        <v>1.463432272837593</v>
+        <v>1.494197260624607</v>
       </c>
       <c r="F1114">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1114">
-        <v>0.006418125282120845</v>
+        <v>0.006596567727162407</v>
       </c>
       <c r="H1114">
-        <v>0.006616567727162407</v>
+        <v>0.006585802739375394</v>
       </c>
       <c r="I1114">
-        <v>0.07844244504156217</v>
+        <v>0.05076498778701399</v>
       </c>
       <c r="J1114">
         <v>0.7691246946753454</v>
       </c>
       <c r="K1114">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1114">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1114">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N1114">
         <v>4.04</v>
@@ -57612,46 +57612,46 @@
     </row>
     <row r="1115" spans="1:16">
       <c r="A1115" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1115" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C1115">
-        <v>1.443432272837593</v>
+        <v>1.444197260624607</v>
       </c>
       <c r="D1115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1115">
-        <v>1.494197260624607</v>
+        <v>1.470344742305128</v>
       </c>
       <c r="F1115">
         <v>1</v>
       </c>
       <c r="G1115">
-        <v>0.006596567727162407</v>
+        <v>0.006535802739375394</v>
       </c>
       <c r="H1115">
-        <v>0.006585802739375394</v>
+        <v>0.006469655257694873</v>
       </c>
       <c r="I1115">
-        <v>0.05076498778701399</v>
+        <v>0.02614748168052117</v>
       </c>
       <c r="J1115">
         <v>0.7691246946753454</v>
       </c>
       <c r="K1115">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1115">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1115">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N1115">
-        <v>4.04</v>
+        <v>3.97</v>
       </c>
       <c r="O1115">
         <v>1</v>
@@ -57662,10 +57662,10 @@
     </row>
     <row r="1116" spans="1:16">
       <c r="A1116" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1116" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C1116">
         <v>1.444197260624607</v>
@@ -57674,7 +57674,7 @@
         <v>378</v>
       </c>
       <c r="E1116">
-        <v>1.450344742305128</v>
+        <v>1.470344742305128</v>
       </c>
       <c r="F1116">
         <v>1</v>
@@ -57683,10 +57683,10 @@
         <v>0.006535802739375394</v>
       </c>
       <c r="H1116">
-        <v>0.006449655257694873</v>
+        <v>0.006469655257694873</v>
       </c>
       <c r="I1116">
-        <v>0.00614748168052115</v>
+        <v>0.02614748168052117</v>
       </c>
       <c r="J1116">
         <v>0.7691246946753454</v>
@@ -57701,7 +57701,7 @@
         <v>3.25</v>
       </c>
       <c r="N1116">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1116">
         <v>1</v>
@@ -57824,7 +57824,7 @@
         <v>378</v>
       </c>
       <c r="E1119">
-        <v>1.439622909851884</v>
+        <v>1.459622909851884</v>
       </c>
       <c r="F1119">
         <v>1</v>
@@ -57833,10 +57833,10 @@
         <v>0.006546722513350851</v>
       </c>
       <c r="H1119">
-        <v>0.006460377090148116</v>
+        <v>0.006480377090148115</v>
       </c>
       <c r="I1119">
-        <v>0.006345423202734235</v>
+        <v>0.02634542320273425</v>
       </c>
       <c r="J1119">
         <v>0.772423720045574</v>
@@ -57851,7 +57851,7 @@
         <v>3.25</v>
       </c>
       <c r="N1119">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1119">
         <v>1</v>
@@ -57874,7 +57874,7 @@
         <v>378</v>
       </c>
       <c r="E1120">
-        <v>1.439622909851884</v>
+        <v>1.459622909851884</v>
       </c>
       <c r="F1120">
         <v>1</v>
@@ -57883,10 +57883,10 @@
         <v>0.006546722513350851</v>
       </c>
       <c r="H1120">
-        <v>0.006460377090148116</v>
+        <v>0.006480377090148115</v>
       </c>
       <c r="I1120">
-        <v>0.006345423202734235</v>
+        <v>0.02634542320273425</v>
       </c>
       <c r="J1120">
         <v>0.772423720045574</v>
@@ -57901,7 +57901,7 @@
         <v>3.25</v>
       </c>
       <c r="N1120">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1120">
         <v>1</v>
@@ -58024,7 +58024,7 @@
         <v>378</v>
       </c>
       <c r="E1123">
-        <v>1.438471730628844</v>
+        <v>1.458471730628844</v>
       </c>
       <c r="F1123">
         <v>1</v>
@@ -58033,10 +58033,10 @@
         <v>0.006547894945113393</v>
       </c>
       <c r="H1123">
-        <v>0.006461528269371156</v>
+        <v>0.006481528269371156</v>
       </c>
       <c r="I1123">
-        <v>0.006366675742236705</v>
+        <v>0.02636667574223672</v>
       </c>
       <c r="J1123">
         <v>0.7727779290372787</v>
@@ -58051,7 +58051,7 @@
         <v>3.25</v>
       </c>
       <c r="N1123">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1123">
         <v>1</v>
@@ -58074,7 +58074,7 @@
         <v>378</v>
       </c>
       <c r="E1124">
-        <v>1.438471730628844</v>
+        <v>1.458471730628844</v>
       </c>
       <c r="F1124">
         <v>1</v>
@@ -58083,10 +58083,10 @@
         <v>0.006547894945113393</v>
       </c>
       <c r="H1124">
-        <v>0.006461528269371156</v>
+        <v>0.006481528269371156</v>
       </c>
       <c r="I1124">
-        <v>0.006366675742236705</v>
+        <v>0.02636667574223672</v>
       </c>
       <c r="J1124">
         <v>0.7727779290372787</v>
@@ -58101,7 +58101,7 @@
         <v>3.25</v>
       </c>
       <c r="N1124">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1124">
         <v>1</v>
@@ -58174,7 +58174,7 @@
         <v>378</v>
       </c>
       <c r="E1126">
-        <v>1.439480223577778</v>
+        <v>1.459480223577778</v>
       </c>
       <c r="F1126">
         <v>1</v>
@@ -58183,10 +58183,10 @@
         <v>0.006546867833833094</v>
       </c>
       <c r="H1126">
-        <v>0.006460519776422222</v>
+        <v>0.006480519776422222</v>
       </c>
       <c r="I1126">
-        <v>0.006348057410872077</v>
+        <v>0.02634805741087209</v>
       </c>
       <c r="J1126">
         <v>0.7724676235145299</v>
@@ -58201,7 +58201,7 @@
         <v>3.25</v>
       </c>
       <c r="N1126">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1126">
         <v>1</v>
@@ -58224,7 +58224,7 @@
         <v>378</v>
       </c>
       <c r="E1127">
-        <v>1.439480223577778</v>
+        <v>1.459480223577778</v>
       </c>
       <c r="F1127">
         <v>1</v>
@@ -58233,10 +58233,10 @@
         <v>0.006546867833833094</v>
       </c>
       <c r="H1127">
-        <v>0.006460519776422222</v>
+        <v>0.006480519776422222</v>
       </c>
       <c r="I1127">
-        <v>0.006348057410872077</v>
+        <v>0.02634805741087209</v>
       </c>
       <c r="J1127">
         <v>0.7724676235145299</v>
@@ -58251,7 +58251,7 @@
         <v>3.25</v>
       </c>
       <c r="N1127">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1127">
         <v>1</v>
@@ -58374,7 +58374,7 @@
         <v>378</v>
       </c>
       <c r="E1130">
-        <v>1.445261339608558</v>
+        <v>1.465261339608558</v>
       </c>
       <c r="F1130">
         <v>1</v>
@@ -58383,10 +58383,10 @@
         <v>0.006540979989506361</v>
       </c>
       <c r="H1130">
-        <v>0.006454738660391443</v>
+        <v>0.006474738660391444</v>
       </c>
       <c r="I1130">
-        <v>0.006241329114919036</v>
+        <v>0.02624132911491905</v>
       </c>
       <c r="J1130">
         <v>0.7706888185819823</v>
@@ -58401,7 +58401,7 @@
         <v>3.25</v>
       </c>
       <c r="N1130">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1130">
         <v>1</v>
@@ -58468,7 +58468,7 @@
         <v>231</v>
       </c>
       <c r="C1132">
-        <v>1.501610911416412</v>
+        <v>1.493916466359406</v>
       </c>
       <c r="D1132" t="s">
         <v>225</v>
@@ -58480,19 +58480,19 @@
         <v>-1</v>
       </c>
       <c r="G1132">
-        <v>0.006518389088583588</v>
+        <v>0.006526083533640593</v>
       </c>
       <c r="H1132">
         <v>0.006536861313868613</v>
       </c>
       <c r="I1132">
-        <v>0.05847222528502449</v>
+        <v>0.05077778022801915</v>
       </c>
       <c r="J1132">
         <v>0.7694445057004873</v>
       </c>
       <c r="K1132">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="L1132">
         <v>4.01</v>
@@ -58524,7 +58524,7 @@
         <v>378</v>
       </c>
       <c r="E1133">
-        <v>1.449305356473416</v>
+        <v>1.469305356473416</v>
       </c>
       <c r="F1133">
         <v>1</v>
@@ -58533,10 +58533,10 @@
         <v>0.006536861313868613</v>
       </c>
       <c r="H1133">
-        <v>0.006450694643526583</v>
+        <v>0.006470694643526584</v>
       </c>
       <c r="I1133">
-        <v>0.006166670342029335</v>
+        <v>0.02616667034202935</v>
       </c>
       <c r="J1133">
         <v>0.7694445057004873</v>
@@ -58551,7 +58551,7 @@
         <v>3.25</v>
       </c>
       <c r="N1133">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1133">
         <v>1</v>
@@ -58624,7 +58624,7 @@
         <v>378</v>
       </c>
       <c r="E1135">
-        <v>1.449549738467668</v>
+        <v>1.469549738467668</v>
       </c>
       <c r="F1135">
         <v>1</v>
@@ -58633,10 +58633,10 @@
         <v>0.006536612420206776</v>
       </c>
       <c r="H1135">
-        <v>0.006450450261532333</v>
+        <v>0.006470450261532333</v>
       </c>
       <c r="I1135">
-        <v>0.006162158674443141</v>
+        <v>0.02616215867444316</v>
       </c>
       <c r="J1135">
         <v>0.7693693112407177</v>
@@ -58651,7 +58651,7 @@
         <v>3.25</v>
       </c>
       <c r="N1135">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1135">
         <v>1</v>
@@ -58665,43 +58665,43 @@
         <v>0</v>
       </c>
       <c r="B1136" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C1136">
-        <v>1.49166330670197</v>
+        <v>1.440857964887927</v>
       </c>
       <c r="D1136" t="s">
-        <v>225</v>
+        <v>378</v>
       </c>
       <c r="E1136">
-        <v>1.440857964887927</v>
+        <v>1.467065977608992</v>
       </c>
       <c r="F1136">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1136">
-        <v>0.00652833669329803</v>
+        <v>0.006539142035112073</v>
       </c>
       <c r="H1136">
-        <v>0.006539142035112073</v>
+        <v>0.006472934022391009</v>
       </c>
       <c r="I1136">
-        <v>0.05080534181404284</v>
+        <v>0.02620801272106466</v>
       </c>
       <c r="J1136">
         <v>0.7701335453510795</v>
       </c>
       <c r="K1136">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="L1136">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1136">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N1136">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="O1136">
         <v>1</v>
@@ -58712,96 +58712,96 @@
     </row>
     <row r="1137" spans="1:16">
       <c r="A1137" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1137" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C1137">
-        <v>1.440857964887927</v>
+        <v>1.490046937486885</v>
       </c>
       <c r="D1137" t="s">
-        <v>378</v>
+        <v>225</v>
       </c>
       <c r="E1137">
-        <v>1.447065977608992</v>
+        <v>1.439221823572351</v>
       </c>
       <c r="F1137">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1137">
-        <v>0.006539142035112073</v>
+        <v>0.006529953062513116</v>
       </c>
       <c r="H1137">
-        <v>0.006452934022391009</v>
+        <v>0.006540778176427649</v>
       </c>
       <c r="I1137">
-        <v>0.006208012721064637</v>
+        <v>0.05082511391453348</v>
       </c>
       <c r="J1137">
-        <v>0.7701335453510795</v>
+        <v>0.770627847863338</v>
       </c>
       <c r="K1137">
+        <v>3.27</v>
+      </c>
+      <c r="L1137">
+        <v>4.01</v>
+      </c>
+      <c r="M1137">
         <v>3.31</v>
       </c>
-      <c r="L1137">
+      <c r="N1137">
         <v>3.99</v>
       </c>
-      <c r="M1137">
-        <v>3.25</v>
-      </c>
-      <c r="N1137">
-        <v>3.95</v>
-      </c>
       <c r="O1137">
         <v>1</v>
       </c>
       <c r="P1137" t="s">
-        <v>224</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1138" spans="1:16">
       <c r="A1138" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1138" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1138">
-        <v>1.497753215965518</v>
+        <v>1.439221823572351</v>
       </c>
       <c r="D1138" t="s">
-        <v>225</v>
+        <v>378</v>
       </c>
       <c r="E1138">
-        <v>1.439221823572351</v>
+        <v>1.465459494444151</v>
       </c>
       <c r="F1138">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1138">
-        <v>0.006522246784034482</v>
+        <v>0.006540778176427649</v>
       </c>
       <c r="H1138">
-        <v>0.006540778176427649</v>
+        <v>0.006474540505555849</v>
       </c>
       <c r="I1138">
-        <v>0.05853139239316674</v>
+        <v>0.0262376708718004</v>
       </c>
       <c r="J1138">
         <v>0.770627847863338</v>
       </c>
       <c r="K1138">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1138">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1138">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N1138">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="O1138">
         <v>1</v>
@@ -58812,96 +58812,96 @@
     </row>
     <row r="1139" spans="1:16">
       <c r="A1139" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1139" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C1139">
-        <v>1.439221823572351</v>
+        <v>1.498375641177962</v>
       </c>
       <c r="D1139" t="s">
-        <v>378</v>
+        <v>225</v>
       </c>
       <c r="E1139">
-        <v>1.445459494444151</v>
+        <v>1.439853795183759</v>
       </c>
       <c r="F1139">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1139">
-        <v>0.006540778176427649</v>
+        <v>0.006521624358822038</v>
       </c>
       <c r="H1139">
-        <v>0.00645454050555585</v>
+        <v>0.006540146204816242</v>
       </c>
       <c r="I1139">
-        <v>0.006237670871800383</v>
+        <v>0.05852184599420296</v>
       </c>
       <c r="J1139">
-        <v>0.770627847863338</v>
+        <v>0.7704369198840608</v>
       </c>
       <c r="K1139">
+        <v>3.26</v>
+      </c>
+      <c r="L1139">
+        <v>4.01</v>
+      </c>
+      <c r="M1139">
         <v>3.31</v>
       </c>
-      <c r="L1139">
+      <c r="N1139">
         <v>3.99</v>
       </c>
-      <c r="M1139">
-        <v>3.25</v>
-      </c>
-      <c r="N1139">
-        <v>3.95</v>
-      </c>
       <c r="O1139">
         <v>1</v>
       </c>
       <c r="P1139" t="s">
-        <v>511</v>
+        <v>381</v>
       </c>
     </row>
     <row r="1140" spans="1:16">
       <c r="A1140" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1140" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1140">
-        <v>1.498375641177962</v>
+        <v>1.439853795183759</v>
       </c>
       <c r="D1140" t="s">
-        <v>225</v>
+        <v>378</v>
       </c>
       <c r="E1140">
-        <v>1.439853795183759</v>
+        <v>1.466080010376802</v>
       </c>
       <c r="F1140">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1140">
-        <v>0.006521624358822038</v>
+        <v>0.006540146204816242</v>
       </c>
       <c r="H1140">
-        <v>0.006540146204816242</v>
+        <v>0.006473919989623198</v>
       </c>
       <c r="I1140">
-        <v>0.05852184599420296</v>
+        <v>0.02622621519304369</v>
       </c>
       <c r="J1140">
         <v>0.7704369198840608</v>
       </c>
       <c r="K1140">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1140">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1140">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N1140">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="O1140">
         <v>1</v>
@@ -58912,96 +58912,96 @@
     </row>
     <row r="1141" spans="1:16">
       <c r="A1141" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1141" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C1141">
-        <v>1.439853795183759</v>
+        <v>1.500954835918747</v>
       </c>
       <c r="D1141" t="s">
-        <v>378</v>
+        <v>225</v>
       </c>
       <c r="E1141">
-        <v>1.446080010376802</v>
+        <v>1.44247254812609</v>
       </c>
       <c r="F1141">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1141">
-        <v>0.006540146204816242</v>
+        <v>0.006519045164081253</v>
       </c>
       <c r="H1141">
-        <v>0.006453919989623198</v>
+        <v>0.006537527451873911</v>
       </c>
       <c r="I1141">
-        <v>0.006226215193043672</v>
+        <v>0.05848228779265696</v>
       </c>
       <c r="J1141">
-        <v>0.7704369198840608</v>
+        <v>0.7696457558531451</v>
       </c>
       <c r="K1141">
+        <v>3.26</v>
+      </c>
+      <c r="L1141">
+        <v>4.01</v>
+      </c>
+      <c r="M1141">
         <v>3.31</v>
       </c>
-      <c r="L1141">
+      <c r="N1141">
         <v>3.99</v>
       </c>
-      <c r="M1141">
-        <v>3.25</v>
-      </c>
-      <c r="N1141">
-        <v>3.95</v>
-      </c>
       <c r="O1141">
         <v>1</v>
       </c>
       <c r="P1141" t="s">
-        <v>381</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1142" spans="1:16">
       <c r="A1142" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1142" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1142">
-        <v>1.500954835918747</v>
+        <v>1.44247254812609</v>
       </c>
       <c r="D1142" t="s">
-        <v>225</v>
+        <v>378</v>
       </c>
       <c r="E1142">
-        <v>1.44247254812609</v>
+        <v>1.468651293477279</v>
       </c>
       <c r="F1142">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1142">
-        <v>0.006519045164081253</v>
+        <v>0.006537527451873911</v>
       </c>
       <c r="H1142">
-        <v>0.006537527451873911</v>
+        <v>0.006471348706522722</v>
       </c>
       <c r="I1142">
-        <v>0.05848228779265696</v>
+        <v>0.02617874535118903</v>
       </c>
       <c r="J1142">
         <v>0.7696457558531451</v>
       </c>
       <c r="K1142">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1142">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1142">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N1142">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="O1142">
         <v>1</v>
@@ -59012,96 +59012,96 @@
     </row>
     <row r="1143" spans="1:16">
       <c r="A1143" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1143" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C1143">
-        <v>1.44247254812609</v>
+        <v>1.500696441772847</v>
       </c>
       <c r="D1143" t="s">
-        <v>378</v>
+        <v>225</v>
       </c>
       <c r="E1143">
-        <v>1.448651293477279</v>
+        <v>1.442210190879793</v>
       </c>
       <c r="F1143">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1143">
-        <v>0.006537527451873911</v>
+        <v>0.006519303558227153</v>
       </c>
       <c r="H1143">
-        <v>0.006451348706522721</v>
+        <v>0.006537789809120208</v>
       </c>
       <c r="I1143">
-        <v>0.006178745351189008</v>
+        <v>0.05848625089305415</v>
       </c>
       <c r="J1143">
-        <v>0.7696457558531451</v>
+        <v>0.7697250178610899</v>
       </c>
       <c r="K1143">
+        <v>3.26</v>
+      </c>
+      <c r="L1143">
+        <v>4.01</v>
+      </c>
+      <c r="M1143">
         <v>3.31</v>
       </c>
-      <c r="L1143">
+      <c r="N1143">
         <v>3.99</v>
       </c>
-      <c r="M1143">
-        <v>3.25</v>
-      </c>
-      <c r="N1143">
-        <v>3.95</v>
-      </c>
       <c r="O1143">
         <v>1</v>
       </c>
       <c r="P1143" t="s">
-        <v>512</v>
+        <v>377</v>
       </c>
     </row>
     <row r="1144" spans="1:16">
       <c r="A1144" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1144" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1144">
-        <v>1.500696441772847</v>
+        <v>1.442210190879793</v>
       </c>
       <c r="D1144" t="s">
-        <v>225</v>
+        <v>378</v>
       </c>
       <c r="E1144">
-        <v>1.442210190879793</v>
+        <v>1.468393691951458</v>
       </c>
       <c r="F1144">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1144">
-        <v>0.006519303558227153</v>
+        <v>0.006537789809120208</v>
       </c>
       <c r="H1144">
-        <v>0.006537789809120208</v>
+        <v>0.006471606308048543</v>
       </c>
       <c r="I1144">
-        <v>0.05848625089305415</v>
+        <v>0.02618350107166512</v>
       </c>
       <c r="J1144">
         <v>0.7697250178610899</v>
       </c>
       <c r="K1144">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1144">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1144">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N1144">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="O1144">
         <v>1</v>
@@ -59112,134 +59112,134 @@
     </row>
     <row r="1145" spans="1:16">
       <c r="A1145" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1145" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C1145">
-        <v>1.442210190879793</v>
+        <v>1.498025853638382</v>
       </c>
       <c r="D1145" t="s">
-        <v>378</v>
+        <v>225</v>
       </c>
       <c r="E1145">
-        <v>1.448393691951458</v>
+        <v>1.439498642804615</v>
       </c>
       <c r="F1145">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1145">
-        <v>0.006537789809120208</v>
+        <v>0.006521974146361618</v>
       </c>
       <c r="H1145">
-        <v>0.006451606308048544</v>
+        <v>0.006540501357195385</v>
       </c>
       <c r="I1145">
-        <v>0.006183501071665098</v>
+        <v>0.05852721083376711</v>
       </c>
       <c r="J1145">
-        <v>0.7697250178610899</v>
+        <v>0.770544216675343</v>
       </c>
       <c r="K1145">
+        <v>3.26</v>
+      </c>
+      <c r="L1145">
+        <v>4.01</v>
+      </c>
+      <c r="M1145">
         <v>3.31</v>
       </c>
-      <c r="L1145">
+      <c r="N1145">
         <v>3.99</v>
       </c>
-      <c r="M1145">
-        <v>3.25</v>
-      </c>
-      <c r="N1145">
-        <v>3.95</v>
-      </c>
       <c r="O1145">
         <v>1</v>
       </c>
       <c r="P1145" t="s">
-        <v>377</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1146" spans="1:16">
       <c r="A1146" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1146" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1146">
-        <v>1.498025853638382</v>
+        <v>1.439498642804615</v>
       </c>
       <c r="D1146" t="s">
-        <v>225</v>
+        <v>378</v>
       </c>
       <c r="E1146">
-        <v>1.439498642804615</v>
+        <v>1.465731295805135</v>
       </c>
       <c r="F1146">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1146">
-        <v>0.006521974146361618</v>
+        <v>0.006540501357195385</v>
       </c>
       <c r="H1146">
-        <v>0.006540501357195385</v>
+        <v>0.006474268704194865</v>
       </c>
       <c r="I1146">
-        <v>0.05852721083376711</v>
+        <v>0.02623265300052058</v>
       </c>
       <c r="J1146">
         <v>0.770544216675343</v>
       </c>
       <c r="K1146">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1146">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1146">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N1146">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="O1146">
         <v>1</v>
       </c>
       <c r="P1146" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1147" spans="1:16">
       <c r="A1147" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1147" t="s">
         <v>226</v>
       </c>
       <c r="C1147">
-        <v>1.439498642804615</v>
+        <v>1.439929878966419</v>
       </c>
       <c r="D1147" t="s">
         <v>378</v>
       </c>
       <c r="E1147">
-        <v>1.445731295805135</v>
+        <v>1.46615471499724</v>
       </c>
       <c r="F1147">
         <v>1</v>
       </c>
       <c r="G1147">
-        <v>0.006540501357195385</v>
+        <v>0.006540070121033582</v>
       </c>
       <c r="H1147">
-        <v>0.006454268704194865</v>
+        <v>0.006473845285002761</v>
       </c>
       <c r="I1147">
-        <v>0.00623265300052056</v>
+        <v>0.02622483603082015</v>
       </c>
       <c r="J1147">
-        <v>0.770544216675343</v>
+        <v>0.7704139338470033</v>
       </c>
       <c r="K1147">
         <v>3.31</v>
@@ -59251,7 +59251,7 @@
         <v>3.25</v>
       </c>
       <c r="N1147">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="O1147">
         <v>1</v>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3453" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3459" uniqueCount="514">
   <si>
     <t>trade_time</t>
   </si>
@@ -706,13 +706,10 @@
     <t>2021-08-06</t>
   </si>
   <si>
-    <t>2021-08-23</t>
+    <t>2021-08-20</t>
   </si>
   <si>
     <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>2021-08-20</t>
   </si>
   <si>
     <t>2016-07-22</t>
@@ -1150,7 +1147,7 @@
     <t>2021-08-18</t>
   </si>
   <si>
-    <t>2021-08-31</t>
+    <t>2021-09-01</t>
   </si>
   <si>
     <t>2021-08-11</t>
@@ -1160,6 +1157,9 @@
   </si>
   <si>
     <t>2021-08-16</t>
+  </si>
+  <si>
+    <t>2021-08-31</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1554,6 +1554,9 @@
   <si>
     <t>2021-08-17</t>
   </si>
+  <si>
+    <t>2021-08-26</t>
+  </si>
 </sst>
 </file>
 
@@ -1910,7 +1913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1147"/>
+  <dimension ref="A1:P1149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1971,7 +1974,7 @@
         <v>4.511229357554957</v>
       </c>
       <c r="D2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E2">
         <v>4.134562114333581</v>
@@ -2021,7 +2024,7 @@
         <v>4.54637358977963</v>
       </c>
       <c r="D3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E3">
         <v>4.134562114333581</v>
@@ -2071,7 +2074,7 @@
         <v>4.486167543744384</v>
       </c>
       <c r="D4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E4">
         <v>4.134562114333581</v>
@@ -2121,7 +2124,7 @@
         <v>4.514809369575879</v>
       </c>
       <c r="D5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E5">
         <v>4.134562114333581</v>
@@ -2171,7 +2174,7 @@
         <v>4.542134230445916</v>
       </c>
       <c r="D6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E6">
         <v>4.134562114333581</v>
@@ -2471,7 +2474,7 @@
         <v>3.284532976858507</v>
       </c>
       <c r="D12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E12">
         <v>2.677351292877795</v>
@@ -2521,7 +2524,7 @@
         <v>3.152631441452742</v>
       </c>
       <c r="D13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E13">
         <v>2.677351292877795</v>
@@ -2571,7 +2574,7 @@
         <v>3.063344517229904</v>
       </c>
       <c r="D14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E14">
         <v>2.677351292877795</v>
@@ -2621,7 +2624,7 @@
         <v>3.062156057601301</v>
       </c>
       <c r="D15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E15">
         <v>2.677351292877795</v>
@@ -2671,7 +2674,7 @@
         <v>3.143633135364715</v>
       </c>
       <c r="D16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E16">
         <v>2.677351292877795</v>
@@ -2721,7 +2724,7 @@
         <v>3.110016830269812</v>
       </c>
       <c r="D17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E17">
         <v>2.677351292877795</v>
@@ -2771,7 +2774,7 @@
         <v>2.366926835235442</v>
       </c>
       <c r="D18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E18">
         <v>2.179880990762272</v>
@@ -2821,7 +2824,7 @@
         <v>2.328641604924578</v>
       </c>
       <c r="D19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E19">
         <v>2.179880990762272</v>
@@ -2871,7 +2874,7 @@
         <v>3.263301236899546</v>
       </c>
       <c r="D20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E20">
         <v>2.652832252271777</v>
@@ -2921,7 +2924,7 @@
         <v>3.130193352632475</v>
       </c>
       <c r="D21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E21">
         <v>2.652832252271777</v>
@@ -2971,7 +2974,7 @@
         <v>3.041358809232626</v>
       </c>
       <c r="D22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E22">
         <v>2.652832252271777</v>
@@ -3021,7 +3024,7 @@
         <v>3.039416381565708</v>
       </c>
       <c r="D23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E23">
         <v>2.652832252271777</v>
@@ -3071,7 +3074,7 @@
         <v>3.085920011765251</v>
       </c>
       <c r="D24" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E24">
         <v>2.652832252271777</v>
@@ -3121,7 +3124,7 @@
         <v>2.240092728764494</v>
       </c>
       <c r="D25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E25">
         <v>2.153548849017755</v>
@@ -3171,7 +3174,7 @@
         <v>2.302403517191201</v>
       </c>
       <c r="D26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E26">
         <v>2.153548849017755</v>
@@ -3221,7 +3224,7 @@
         <v>3.266809754119012</v>
       </c>
       <c r="D27" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E27">
         <v>2.656883991617553</v>
@@ -3271,7 +3274,7 @@
         <v>3.133901217421229</v>
       </c>
       <c r="D28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E28">
         <v>2.656883991617553</v>
@@ -3321,7 +3324,7 @@
         <v>3.044991918682897</v>
       </c>
       <c r="D29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E29">
         <v>2.656883991617553</v>
@@ -3371,7 +3374,7 @@
         <v>3.043174083246784</v>
       </c>
       <c r="D30" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E30">
         <v>2.656883991617553</v>
@@ -3421,7 +3424,7 @@
         <v>3.089901979461776</v>
       </c>
       <c r="D31" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E31">
         <v>2.656883991617553</v>
@@ -3471,7 +3474,7 @@
         <v>2.244448473153433</v>
       </c>
       <c r="D32" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E32">
         <v>2.223248320745323</v>
@@ -3521,7 +3524,7 @@
         <v>2.306739326823212</v>
       </c>
       <c r="D33" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E33">
         <v>2.223248320745323</v>
@@ -3571,7 +3574,7 @@
         <v>3.150232952413131</v>
       </c>
       <c r="D34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E34">
         <v>2.674730363322413</v>
@@ -3621,7 +3624,7 @@
         <v>3.060994384824157</v>
       </c>
       <c r="D35" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E35">
         <v>2.674730363322413</v>
@@ -3671,7 +3674,7 @@
         <v>3.059725330805781</v>
       </c>
       <c r="D36" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E36">
         <v>2.674730363322413</v>
@@ -3721,7 +3724,7 @@
         <v>2.263633871517577</v>
       </c>
       <c r="D37" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E37">
         <v>2.243887682321252</v>
@@ -3771,7 +3774,7 @@
         <v>2.325836920160516</v>
       </c>
       <c r="D38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E38">
         <v>2.243887682321252</v>
@@ -3821,7 +3824,7 @@
         <v>3.082343576888696</v>
       </c>
       <c r="D39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E39">
         <v>2.60054479571305</v>
@@ -3871,7 +3874,7 @@
         <v>2.994473746709487</v>
       </c>
       <c r="D40" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E40">
         <v>2.60054479571305</v>
@@ -3921,7 +3924,7 @@
         <v>2.990923463674834</v>
       </c>
       <c r="D41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E41">
         <v>2.60054479571305</v>
@@ -4071,7 +4074,7 @@
         <v>3.040409741296517</v>
       </c>
       <c r="D44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E44">
         <v>2.508325187038523</v>
@@ -4121,7 +4124,7 @@
         <v>2.895004863307419</v>
       </c>
       <c r="D45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E45">
         <v>2.508325187038523</v>
@@ -4171,7 +4174,7 @@
         <v>2.948426001260181</v>
       </c>
       <c r="D46" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E46">
         <v>2.508325187038523</v>
@@ -4321,7 +4324,7 @@
         <v>3.031700902303593</v>
       </c>
       <c r="D49" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E49">
         <v>2.49878526260407</v>
@@ -4371,7 +4374,7 @@
         <v>2.878860584574042</v>
       </c>
       <c r="D50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E50">
         <v>2.49878526260407</v>
@@ -4521,7 +4524,7 @@
         <v>3.022635677892191</v>
       </c>
       <c r="D53" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E53">
         <v>2.464854567988125</v>
@@ -4571,7 +4574,7 @@
         <v>2.869746622396987</v>
       </c>
       <c r="D54" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E54">
         <v>2.464854567988125</v>
@@ -4721,7 +4724,7 @@
         <v>2.853132741882125</v>
       </c>
       <c r="D57" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E57">
         <v>2.446552646137529</v>
@@ -4771,7 +4774,7 @@
         <v>2.094328898937136</v>
       </c>
       <c r="D58" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E58">
         <v>1.842794376120828</v>
@@ -4821,7 +4824,7 @@
         <v>2.050128624441065</v>
       </c>
       <c r="D59" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E59">
         <v>1.842794376120828</v>
@@ -4921,7 +4924,7 @@
         <v>2.071512346378907</v>
       </c>
       <c r="D61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E61">
         <v>1.858583178679253</v>
@@ -4971,7 +4974,7 @@
         <v>2.027077118824455</v>
       </c>
       <c r="D62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E62">
         <v>1.858583178679253</v>
@@ -5071,7 +5074,7 @@
         <v>1.952441204043576</v>
       </c>
       <c r="D64" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E64">
         <v>1.768759504456596</v>
@@ -5121,7 +5124,7 @@
         <v>1.960665672922645</v>
       </c>
       <c r="D65" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E65">
         <v>1.768759504456596</v>
@@ -5171,7 +5174,7 @@
         <v>1.911863728646695</v>
       </c>
       <c r="D66" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E66">
         <v>1.759452065017152</v>
@@ -5221,7 +5224,7 @@
         <v>1.919858426996902</v>
       </c>
       <c r="D67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E67">
         <v>1.759452065017152</v>
@@ -5271,7 +5274,7 @@
         <v>1.905874331946279</v>
       </c>
       <c r="D68" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E68">
         <v>1.759452065017152</v>
@@ -5371,7 +5374,7 @@
         <v>2.136708142214575</v>
       </c>
       <c r="D70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E70">
         <v>2.108561718819574</v>
@@ -5421,7 +5424,7 @@
         <v>2.067829601844572</v>
       </c>
       <c r="D71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E71">
         <v>2.108561718819574</v>
@@ -5471,7 +5474,7 @@
         <v>2.12817237616458</v>
       </c>
       <c r="D72" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E72">
         <v>2.108561718819574</v>
@@ -5721,7 +5724,7 @@
         <v>2.142301413025561</v>
       </c>
       <c r="D77" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E77">
         <v>1.97780018839587</v>
@@ -5771,7 +5774,7 @@
         <v>2.110364066104271</v>
       </c>
       <c r="D78" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E78">
         <v>1.97780018839587</v>
@@ -5871,7 +5874,7 @@
         <v>2.09768233828219</v>
       </c>
       <c r="D80" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E80">
         <v>1.955795181546213</v>
@@ -5921,7 +5924,7 @@
         <v>2.065795181546212</v>
       </c>
       <c r="D81" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E81">
         <v>1.955795181546213</v>
@@ -5971,7 +5974,7 @@
         <v>2.020133711338287</v>
       </c>
       <c r="D82" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E82">
         <v>1.955795181546213</v>
@@ -6021,7 +6024,7 @@
         <v>2.685866995679533</v>
       </c>
       <c r="D83" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E83">
         <v>2.275991495057138</v>
@@ -6071,7 +6074,7 @@
         <v>1.920113324448644</v>
       </c>
       <c r="D84" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E84">
         <v>1.858301408508103</v>
@@ -6121,7 +6124,7 @@
         <v>1.888425907885709</v>
       </c>
       <c r="D85" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E85">
         <v>1.858301408508103</v>
@@ -6171,7 +6174,7 @@
         <v>1.843363658196906</v>
       </c>
       <c r="D86" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E86">
         <v>1.858301408508103</v>
@@ -6221,7 +6224,7 @@
         <v>2.660449968537363</v>
       </c>
       <c r="D87" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E87">
         <v>2.250393991982597</v>
@@ -6271,7 +6274,7 @@
         <v>1.893372807135757</v>
       </c>
       <c r="D88" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E88">
         <v>1.76840079541314</v>
@@ -6321,7 +6324,7 @@
         <v>1.861715469894883</v>
       </c>
       <c r="D89" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E89">
         <v>1.76840079541314</v>
@@ -6371,7 +6374,7 @@
         <v>1.816743458172266</v>
       </c>
       <c r="D90" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E90">
         <v>1.76840079541314</v>
@@ -6421,7 +6424,7 @@
         <v>2.753045004490679</v>
       </c>
       <c r="D91" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E91">
         <v>2.2971803418113</v>
@@ -6471,7 +6474,7 @@
         <v>1.990789359754097</v>
       </c>
       <c r="D92" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E92">
         <v>1.832556276919175</v>
@@ -6521,7 +6524,7 @@
         <v>1.959022442589019</v>
       </c>
       <c r="D93" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E93">
         <v>1.832556276919175</v>
@@ -6571,7 +6574,7 @@
         <v>1.913721691093786</v>
       </c>
       <c r="D94" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E94">
         <v>1.832556276919175</v>
@@ -6621,7 +6624,7 @@
         <v>2.92313924418029</v>
       </c>
       <c r="D95" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E95">
         <v>2.468884941166612</v>
@@ -6671,7 +6674,7 @@
         <v>2.153677001851642</v>
       </c>
       <c r="D96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E96">
         <v>1.949422698837964</v>
@@ -6721,7 +6724,7 @@
         <v>2.13777236548177</v>
       </c>
       <c r="D97" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E97">
         <v>1.949422698837964</v>
@@ -6771,7 +6774,7 @@
         <v>2.091867729111899</v>
       </c>
       <c r="D98" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E98">
         <v>1.949422698837964</v>
@@ -6821,7 +6824,7 @@
         <v>2.894427873207131</v>
       </c>
       <c r="D99" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E99">
         <v>2.439901746562937</v>
@@ -6871,7 +6874,7 @@
         <v>1.997271113341972</v>
       </c>
       <c r="D100" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E100">
         <v>2.044389132460881</v>
@@ -6921,7 +6924,7 @@
         <v>2.107599942494591</v>
       </c>
       <c r="D101" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E101">
         <v>2.044389132460881</v>
@@ -6971,7 +6974,7 @@
         <v>2.061797239986165</v>
       </c>
       <c r="D102" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E102">
         <v>2.044389132460881</v>
@@ -7021,7 +7024,7 @@
         <v>2.923596716153027</v>
       </c>
       <c r="D103" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E103">
         <v>2.407065525827111</v>
@@ -7071,7 +7074,7 @@
         <v>2.028096884644558</v>
       </c>
       <c r="D104" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E104">
         <v>2.036284363583118</v>
@@ -7121,7 +7124,7 @@
         <v>2.138253117093357</v>
       </c>
       <c r="D105" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E105">
         <v>2.036284363583118</v>
@@ -7171,7 +7174,7 @@
         <v>2.092346856562636</v>
       </c>
       <c r="D106" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E106">
         <v>2.036284363583118</v>
@@ -7221,7 +7224,7 @@
         <v>2.985463460161611</v>
       </c>
       <c r="D107" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E107">
         <v>2.470176926224034</v>
@@ -7271,7 +7274,7 @@
         <v>2.093477952573156</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E108">
         <v>2.244680549326919</v>
@@ -7321,7 +7324,7 @@
         <v>2.181435983981249</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E109">
         <v>2.244680549326919</v>
@@ -7371,7 +7374,7 @@
         <v>2.157142203837899</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E110">
         <v>2.244680549326919</v>
@@ -7421,7 +7424,7 @@
         <v>3.064233105493776</v>
       </c>
       <c r="D111" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E111">
         <v>2.550531286314361</v>
@@ -7471,7 +7474,7 @@
         <v>2.176722086634249</v>
       </c>
       <c r="D112" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E112">
         <v>2.41693684763564</v>
@@ -7521,7 +7524,7 @@
         <v>2.264586899527156</v>
       </c>
       <c r="D113" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E113">
         <v>2.41693684763564</v>
@@ -7571,7 +7574,7 @@
         <v>2.239640589777504</v>
       </c>
       <c r="D114" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E114">
         <v>2.41693684763564</v>
@@ -7621,7 +7624,7 @@
         <v>3.110186183160804</v>
       </c>
       <c r="D115" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E115">
         <v>2.597408863768773</v>
@@ -7671,7 +7674,7 @@
         <v>2.225285516642126</v>
       </c>
       <c r="D116" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E116">
         <v>2.368062836034158</v>
@@ -7721,7 +7724,7 @@
         <v>2.313095947194598</v>
       </c>
       <c r="D117" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E117">
         <v>2.368062836034158</v>
@@ -7771,7 +7774,7 @@
         <v>2.287768961061905</v>
       </c>
       <c r="D118" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E118">
         <v>2.368062836034158</v>
@@ -7821,7 +7824,7 @@
         <v>3.033340385849137</v>
       </c>
       <c r="D119" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E119">
         <v>2.719207193814303</v>
@@ -7871,7 +7874,7 @@
         <v>3.229582457973418</v>
       </c>
       <c r="D120" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E120">
         <v>2.719207193814303</v>
@@ -8221,7 +8224,7 @@
         <v>2.432163407485593</v>
       </c>
       <c r="D127" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E127">
         <v>2.56100240196795</v>
@@ -8271,7 +8274,7 @@
         <v>2.519742171866908</v>
       </c>
       <c r="D128" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E128">
         <v>2.56100240196795</v>
@@ -8321,7 +8324,7 @@
         <v>2.492793522536114</v>
       </c>
       <c r="D129" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E129">
         <v>2.56100240196795</v>
@@ -8371,7 +8374,7 @@
         <v>2.505529815680059</v>
       </c>
       <c r="D130" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E130">
         <v>2.56100240196795</v>
@@ -8621,7 +8624,7 @@
         <v>2.561090333833617</v>
       </c>
       <c r="D135" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E135">
         <v>2.754384456252795</v>
@@ -8671,7 +8674,7 @@
         <v>2.569312051271657</v>
       </c>
       <c r="D136" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E136">
         <v>2.754384456252795</v>
@@ -8721,7 +8724,7 @@
         <v>2.620565448424133</v>
       </c>
       <c r="D137" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E137">
         <v>2.754384456252795</v>
@@ -8771,7 +8774,7 @@
         <v>2.632868616395577</v>
       </c>
       <c r="D138" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E138">
         <v>2.754384456252795</v>
@@ -9021,7 +9024,7 @@
         <v>2.656093329609079</v>
       </c>
       <c r="D143" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E143">
         <v>2.992573434271657</v>
@@ -9071,7 +9074,7 @@
         <v>2.743421332599438</v>
       </c>
       <c r="D144" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E144">
         <v>2.992573434271657</v>
@@ -9121,7 +9124,7 @@
         <v>2.714717353531954</v>
       </c>
       <c r="D145" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E145">
         <v>2.992573434271657</v>
@@ -9171,7 +9174,7 @@
         <v>2.726701362503031</v>
       </c>
       <c r="D146" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E146">
         <v>2.992573434271657</v>
@@ -9471,7 +9474,7 @@
         <v>2.743265879725431</v>
       </c>
       <c r="D152" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E152">
         <v>3.076329367082216</v>
@@ -9521,7 +9524,7 @@
         <v>2.830496265078482</v>
       </c>
       <c r="D153" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E153">
         <v>3.076329367082216</v>
@@ -9571,7 +9574,7 @@
         <v>2.801108962549839</v>
       </c>
       <c r="D154" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E154">
         <v>3.076329367082216</v>
@@ -9621,7 +9624,7 @@
         <v>2.812800118608992</v>
       </c>
       <c r="D155" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E155">
         <v>3.076329367082216</v>
@@ -9671,7 +9674,7 @@
         <v>8.428041485362026</v>
       </c>
       <c r="D156" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E156">
         <v>7.860265385484505</v>
@@ -9721,7 +9724,7 @@
         <v>8.423754692426147</v>
       </c>
       <c r="D157" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E157">
         <v>7.860265385484505</v>
@@ -9771,7 +9774,7 @@
         <v>7.322493060882559</v>
       </c>
       <c r="D158" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E158">
         <v>7.276461614475858</v>
@@ -9821,7 +9824,7 @@
         <v>0.8245990177480174</v>
       </c>
       <c r="D159" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E159">
         <v>0.6142761207337122</v>
@@ -9871,7 +9874,7 @@
         <v>0.5627692680002871</v>
       </c>
       <c r="D160" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E160">
         <v>0.672123473971677</v>
@@ -9921,7 +9924,7 @@
         <v>0.5629845326764906</v>
       </c>
       <c r="D161" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E161">
         <v>0.7139532237194066</v>
@@ -9971,7 +9974,7 @@
         <v>0.5459982381433406</v>
       </c>
       <c r="D162" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E162">
         <v>0.7139532237194066</v>
@@ -10021,7 +10024,7 @@
         <v>0.5636303267051019</v>
       </c>
       <c r="D163" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E163">
         <v>0.8305089889001493</v>
@@ -10121,7 +10124,7 @@
         <v>0.8093250331810289</v>
       </c>
       <c r="D165" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E165">
         <v>0.8194326655191304</v>
@@ -10171,7 +10174,7 @@
         <v>0.8405770778352721</v>
       </c>
       <c r="D166" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E166">
         <v>0.6301931958588023</v>
@@ -10221,7 +10224,7 @@
         <v>0.5784017466352731</v>
       </c>
       <c r="D167" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E167">
         <v>0.7171221400470396</v>
@@ -10271,7 +10274,7 @@
         <v>0.5786576679529203</v>
       </c>
       <c r="D168" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E168">
         <v>0.7298093138823321</v>
@@ -10321,7 +10324,7 @@
         <v>0.5622405663999777</v>
       </c>
       <c r="D169" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E169">
         <v>0.7298093138823321</v>
@@ -10371,7 +10374,7 @@
         <v>0.5794254319058618</v>
       </c>
       <c r="D170" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E170">
         <v>0.84571457279998</v>
@@ -10421,7 +10424,7 @@
         <v>0.9516198317176272</v>
       </c>
       <c r="D171" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E171">
         <v>0.7660984547764507</v>
@@ -10471,7 +10474,7 @@
         <v>0.8243070055529209</v>
       </c>
       <c r="D172" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E172">
         <v>0.7660984547764507</v>
@@ -10521,7 +10524,7 @@
         <v>3.011517550684177</v>
       </c>
       <c r="D173" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E173">
         <v>3.259507704779772</v>
@@ -10571,7 +10574,7 @@
         <v>3.032305079205265</v>
       </c>
       <c r="D174" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E174">
         <v>3.259507704779772</v>
@@ -10621,7 +10624,7 @@
         <v>3.023912955928789</v>
       </c>
       <c r="D175" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E175">
         <v>3.259507704779772</v>
@@ -10671,7 +10674,7 @@
         <v>3.523510986747906</v>
       </c>
       <c r="D176" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E176">
         <v>3.205488012970963</v>
@@ -10721,7 +10724,7 @@
         <v>3.467481449034693</v>
       </c>
       <c r="D177" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E177">
         <v>3.205488012970963</v>
@@ -10771,7 +10774,7 @@
         <v>2.990019863222156</v>
       </c>
       <c r="D178" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E178">
         <v>3.2375712890022</v>
@@ -10821,7 +10824,7 @@
         <v>3.010251669210212</v>
       </c>
       <c r="D179" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E179">
         <v>3.2375712890022</v>
@@ -10871,7 +10874,7 @@
         <v>3.002210528586177</v>
       </c>
       <c r="D180" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E180">
         <v>3.2375712890022</v>
@@ -10921,7 +10924,7 @@
         <v>3.501720813742185</v>
       </c>
       <c r="D181" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E181">
         <v>3.182674140562288</v>
@@ -10971,7 +10974,7 @@
         <v>3.444375091082317</v>
       </c>
       <c r="D182" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E182">
         <v>3.182674140562288</v>
@@ -11021,7 +11024,7 @@
         <v>2.882489184657736</v>
       </c>
       <c r="D183" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E183">
         <v>3.127846106793607</v>
@@ -11071,7 +11074,7 @@
         <v>2.89994128602984</v>
       </c>
       <c r="D184" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E184">
         <v>3.127846106793607</v>
@@ -11121,7 +11124,7 @@
         <v>2.893655748321143</v>
       </c>
       <c r="D185" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E185">
         <v>3.127846106793607</v>
@@ -11171,7 +11174,7 @@
         <v>3.392727132748317</v>
       </c>
       <c r="D186" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E186">
         <v>3.602965080838898</v>
@@ -11221,7 +11224,7 @@
         <v>3.317869283583107</v>
       </c>
       <c r="D187" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E187">
         <v>3.602965080838898</v>
@@ -11271,7 +11274,7 @@
         <v>3.328797899155933</v>
       </c>
       <c r="D188" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E188">
         <v>3.602965080838898</v>
@@ -11321,7 +11324,7 @@
         <v>2.702672232723285</v>
       </c>
       <c r="D189" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E189">
         <v>2.944359421146208</v>
@@ -11371,7 +11374,7 @@
         <v>2.715476004725656</v>
       </c>
       <c r="D190" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E190">
         <v>2.944359421146208</v>
@@ -11421,7 +11424,7 @@
         <v>2.712126253987316</v>
       </c>
       <c r="D191" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E191">
         <v>2.944359421146208</v>
@@ -11471,7 +11474,7 @@
         <v>3.210463691671901</v>
       </c>
       <c r="D192" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E192">
         <v>3.418255150620516</v>
@@ -11521,7 +11524,7 @@
         <v>3.123862694625259</v>
       </c>
       <c r="D193" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E193">
         <v>3.418255150620516</v>
@@ -11571,7 +11574,7 @@
         <v>3.135525256940674</v>
       </c>
       <c r="D194" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E194">
         <v>3.418255150620516</v>
@@ -11621,7 +11624,7 @@
         <v>2.736071235676643</v>
       </c>
       <c r="D195" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E195">
         <v>2.942224758417352</v>
@@ -11671,7 +11674,7 @@
         <v>2.162283479363674</v>
       </c>
       <c r="D196" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E196">
         <v>2.372503094869548</v>
@@ -11707,7 +11710,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11721,7 +11724,7 @@
         <v>2.161118018285999</v>
       </c>
       <c r="D197" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E197">
         <v>2.372503094869548</v>
@@ -11757,7 +11760,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11771,7 +11774,7 @@
         <v>2.166590941071899</v>
       </c>
       <c r="D198" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E198">
         <v>2.372503094869548</v>
@@ -11807,7 +11810,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11821,7 +11824,7 @@
         <v>2.564986248982474</v>
       </c>
       <c r="D199" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E199">
         <v>2.863161941387174</v>
@@ -11857,7 +11860,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11871,7 +11874,7 @@
         <v>2.588567480624777</v>
       </c>
       <c r="D200" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E200">
         <v>2.863161941387174</v>
@@ -11907,7 +11910,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11921,7 +11924,7 @@
         <v>2.554699249928301</v>
       </c>
       <c r="D201" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E201">
         <v>2.863161941387174</v>
@@ -11957,7 +11960,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11971,7 +11974,7 @@
         <v>2.168347865118902</v>
       </c>
       <c r="D202" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E202">
         <v>2.433533788850627</v>
@@ -12007,7 +12010,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12021,7 +12024,7 @@
         <v>2.089009283775184</v>
       </c>
       <c r="D203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E203">
         <v>2.29873043536549</v>
@@ -12071,7 +12074,7 @@
         <v>2.085949659818351</v>
       </c>
       <c r="D204" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E204">
         <v>2.29873043536549</v>
@@ -12121,7 +12124,7 @@
         <v>2.092618896001614</v>
       </c>
       <c r="D205" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E205">
         <v>2.29873043536549</v>
@@ -12171,7 +12174,7 @@
         <v>2.490116968864166</v>
       </c>
       <c r="D206" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E206">
         <v>2.787893890136412</v>
@@ -12221,7 +12224,7 @@
         <v>2.51010926031438</v>
       </c>
       <c r="D207" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E207">
         <v>2.787893890136412</v>
@@ -12271,7 +12274,7 @@
         <v>2.475941951268564</v>
       </c>
       <c r="D208" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E208">
         <v>2.787893890136412</v>
@@ -12321,7 +12324,7 @@
         <v>2.090388108724073</v>
       </c>
       <c r="D209" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E209">
         <v>2.352882327311732</v>
@@ -12371,7 +12374,7 @@
         <v>2.192228120172728</v>
       </c>
       <c r="D210" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E210">
         <v>2.40265144071812</v>
@@ -12421,7 +12424,7 @@
         <v>2.19183673824522</v>
       </c>
       <c r="D211" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E211">
         <v>2.40265144071812</v>
@@ -12471,7 +12474,7 @@
         <v>2.196820768936278</v>
       </c>
       <c r="D212" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E212">
         <v>2.40265144071812</v>
@@ -12521,7 +12524,7 @@
         <v>2.595582745917984</v>
       </c>
       <c r="D213" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E213">
         <v>2.893921402354298</v>
@@ -12571,7 +12574,7 @@
         <v>2.620630653844811</v>
       </c>
       <c r="D214" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E214">
         <v>2.893921402354298</v>
@@ -12621,7 +12624,7 @@
         <v>2.586884646172047</v>
       </c>
       <c r="D215" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E215">
         <v>2.893921402354298</v>
@@ -12671,7 +12674,7 @@
         <v>2.20020733329942</v>
       </c>
       <c r="D216" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E216">
         <v>2.466493264244539</v>
@@ -12721,7 +12724,7 @@
         <v>2.278141334918415</v>
       </c>
       <c r="D217" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E217">
         <v>2.511164627467769</v>
@@ -12771,7 +12774,7 @@
         <v>2.279970838814265</v>
       </c>
       <c r="D218" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E218">
         <v>2.511164627467769</v>
@@ -12821,7 +12824,7 @@
         <v>2.283552204774781</v>
       </c>
       <c r="D219" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E219">
         <v>2.511164627467769</v>
@@ -12871,7 +12874,7 @@
         <v>2.683366180304393</v>
       </c>
       <c r="D220" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E220">
         <v>2.982172391650888</v>
@@ -12921,7 +12924,7 @@
         <v>2.712622082422847</v>
       </c>
       <c r="D221" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E221">
         <v>2.982172391650888</v>
@@ -12971,7 +12974,7 @@
         <v>2.679226740932718</v>
       </c>
       <c r="D222" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E222">
         <v>2.982172391650888</v>
@@ -13021,7 +13024,7 @@
         <v>2.291614318239729</v>
       </c>
       <c r="D223" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E223">
         <v>2.561056244828568</v>
@@ -13071,7 +13074,7 @@
         <v>2.24731466049155</v>
       </c>
       <c r="D224" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E224">
         <v>2.478681691470373</v>
@@ -13121,7 +13124,7 @@
         <v>2.251415753428024</v>
       </c>
       <c r="D225" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E225">
         <v>2.478681691470373</v>
@@ -13171,7 +13174,7 @@
         <v>2.650839933725667</v>
       </c>
       <c r="D226" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E226">
         <v>2.949472902746843</v>
@@ -13221,7 +13224,7 @@
         <v>2.678536654916245</v>
       </c>
       <c r="D227" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E227">
         <v>2.949472902746843</v>
@@ -13271,7 +13274,7 @@
         <v>2.645011381682127</v>
       </c>
       <c r="D228" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E228">
         <v>2.949472902746843</v>
@@ -13321,7 +13324,7 @@
         <v>2.257745443639777</v>
       </c>
       <c r="D229" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E229">
         <v>2.526017984532709</v>
@@ -13371,7 +13374,7 @@
         <v>2.655872947978581</v>
       </c>
       <c r="D230" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E230">
         <v>2.262418029764449</v>
@@ -13421,7 +13424,7 @@
         <v>2.172840353015851</v>
       </c>
       <c r="D231" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E231">
         <v>2.384007773516882</v>
@@ -13471,7 +13474,7 @@
         <v>2.178126713445307</v>
       </c>
       <c r="D232" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E232">
         <v>2.384007773516882</v>
@@ -13521,7 +13524,7 @@
         <v>2.576661943123215</v>
       </c>
       <c r="D233" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E233">
         <v>2.874899822980062</v>
@@ -13571,7 +13574,7 @@
         <v>2.600802861834847</v>
       </c>
       <c r="D234" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E234">
         <v>2.874899822980062</v>
@@ -13621,7 +13624,7 @@
         <v>2.780802861834847</v>
       </c>
       <c r="D235" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E235">
         <v>2.874899822980062</v>
@@ -13671,7 +13674,7 @@
         <v>2.180505512013787</v>
       </c>
       <c r="D236" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E236">
         <v>2.44611120104751</v>
@@ -13721,7 +13724,7 @@
         <v>3.16471395829044</v>
       </c>
       <c r="D237" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E237">
         <v>2.876141169417832</v>
@@ -13771,7 +13774,7 @@
         <v>3.118858906274599</v>
       </c>
       <c r="D238" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E238">
         <v>2.876141169417832</v>
@@ -13821,7 +13824,7 @@
         <v>3.298858906274599</v>
       </c>
       <c r="D239" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E239">
         <v>2.876141169417832</v>
@@ -13871,7 +13874,7 @@
         <v>3.129205380823773</v>
       </c>
       <c r="D240" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E240">
         <v>2.765963171089123</v>
@@ -13921,7 +13924,7 @@
         <v>2.558576013370311</v>
       </c>
       <c r="D241" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E241">
         <v>2.956487643967009</v>
@@ -13971,7 +13974,7 @@
         <v>2.955013317141319</v>
       </c>
       <c r="D242" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E242">
         <v>2.654899956071243</v>
@@ -14021,7 +14024,7 @@
         <v>2.897336215557339</v>
       </c>
       <c r="D243" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E243">
         <v>2.654899956071243</v>
@@ -14071,7 +14074,7 @@
         <v>3.077336215557339</v>
       </c>
       <c r="D244" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E244">
         <v>2.654899956071243</v>
@@ -14121,7 +14124,7 @@
         <v>2.891075525236986</v>
       </c>
       <c r="D245" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E245">
         <v>2.512633537486157</v>
@@ -14171,7 +14174,7 @@
         <v>2.301868651319306</v>
       </c>
       <c r="D246" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E246">
         <v>2.718639265750892</v>
@@ -14221,7 +14224,7 @@
         <v>1.005369382839041</v>
       </c>
       <c r="D247" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E247">
         <v>0.9358262153664816</v>
@@ -14271,7 +14274,7 @@
         <v>1.044536476187351</v>
       </c>
       <c r="D248" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E248">
         <v>1.246336640426168</v>
@@ -14321,7 +14324,7 @@
         <v>1.031411989433655</v>
       </c>
       <c r="D249" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E249">
         <v>1.246336640426168</v>
@@ -14371,7 +14374,7 @@
         <v>1.039611825194839</v>
       </c>
       <c r="D250" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E250">
         <v>1.246336640426168</v>
@@ -14421,7 +14424,7 @@
         <v>1.017811660956021</v>
       </c>
       <c r="D251" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E251">
         <v>1.246336640426168</v>
@@ -14471,7 +14474,7 @@
         <v>1.044036886784395</v>
       </c>
       <c r="D252" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E252">
         <v>1.246336640426168</v>
@@ -14521,7 +14524,7 @@
         <v>1.410611004000752</v>
       </c>
       <c r="D253" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E253">
         <v>1.196336640426169</v>
@@ -14571,7 +14574,7 @@
         <v>1.386986927844099</v>
       </c>
       <c r="D254" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E254">
         <v>1.320761702015725</v>
@@ -14621,7 +14624,7 @@
         <v>1.406011496717204</v>
       </c>
       <c r="D255" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E255">
         <v>1.320761702015725</v>
@@ -14671,7 +14674,7 @@
         <v>1.380936147709717</v>
       </c>
       <c r="D256" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E256">
         <v>1.320761702015725</v>
@@ -14721,7 +14724,7 @@
         <v>1.465686353008238</v>
       </c>
       <c r="D257" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E257">
         <v>1.320761702015725</v>
@@ -14771,7 +14774,7 @@
         <v>0.9661722288213106</v>
       </c>
       <c r="D258" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E258">
         <v>1.166850901147913</v>
@@ -14821,7 +14824,7 @@
         <v>0.9495430798419413</v>
       </c>
       <c r="D259" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E259">
         <v>1.166850901147913</v>
@@ -14871,7 +14874,7 @@
         <v>0.9588644075153399</v>
       </c>
       <c r="D260" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E260">
         <v>1.166850901147913</v>
@@ -14921,7 +14924,7 @@
         <v>0.9381857351887382</v>
       </c>
       <c r="D261" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E261">
         <v>1.166850901147913</v>
@@ -14971,7 +14974,7 @@
         <v>0.962868909637816</v>
       </c>
       <c r="D262" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E262">
         <v>1.166850901147913</v>
@@ -15021,7 +15024,7 @@
         <v>1.33547104588233</v>
       </c>
       <c r="D263" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E263">
         <v>1.116850901147913</v>
@@ -15071,7 +15074,7 @@
         <v>1.305538577719466</v>
       </c>
       <c r="D264" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E264">
         <v>1.19153407559699</v>
@@ -15121,7 +15124,7 @@
         <v>1.327507062862136</v>
       </c>
       <c r="D265" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E265">
         <v>1.19153407559699</v>
@@ -15171,7 +15174,7 @@
         <v>1.304814884168106</v>
       </c>
       <c r="D266" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E266">
         <v>1.19153407559699</v>
@@ -15221,7 +15224,7 @@
         <v>1.388163224576359</v>
       </c>
       <c r="D267" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E267">
         <v>1.19153407559699</v>
@@ -15271,7 +15274,7 @@
         <v>0.8431624363702266</v>
       </c>
       <c r="D268" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E268">
         <v>1.063566954489587</v>
@@ -15321,7 +15324,7 @@
         <v>0.8539410331322781</v>
       </c>
       <c r="D269" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E269">
         <v>1.063566954489587</v>
@@ -15371,7 +15374,7 @@
         <v>0.8347196298943302</v>
       </c>
       <c r="D270" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E270">
         <v>1.063566954489587</v>
@@ -15421,7 +15424,7 @@
         <v>0.8573990593465091</v>
       </c>
       <c r="D271" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E271">
         <v>1.063566954489587</v>
@@ -15471,7 +15474,7 @@
         <v>1.237834016942537</v>
       </c>
       <c r="D272" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E272">
         <v>1.013566954489587</v>
@@ -15521,7 +15524,7 @@
         <v>1.199704410155996</v>
       </c>
       <c r="D273" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E273">
         <v>1.035093708537022</v>
@@ -15571,7 +15574,7 @@
         <v>1.225498226656382</v>
       </c>
       <c r="D274" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E274">
         <v>1.035093708537022</v>
@@ -15621,7 +15624,7 @@
         <v>1.205902744775742</v>
       </c>
       <c r="D275" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E275">
         <v>1.035093708537022</v>
@@ -15671,7 +15674,7 @@
         <v>1.287429498823176</v>
       </c>
       <c r="D276" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E276">
         <v>1.035093708537022</v>
@@ -15721,7 +15724,7 @@
         <v>0.7929641978726467</v>
       </c>
       <c r="D277" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E277">
         <v>1.014829966085258</v>
@@ -15771,7 +15774,7 @@
         <v>0.8044304417374049</v>
       </c>
       <c r="D278" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E278">
         <v>1.014829966085258</v>
@@ -15821,7 +15824,7 @@
         <v>0.8309626123654903</v>
       </c>
       <c r="D279" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E279">
         <v>1.014829966085258</v>
@@ -15871,7 +15874,7 @@
         <v>0.7858966856021636</v>
       </c>
       <c r="D280" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E280">
         <v>1.014829966085258</v>
@@ -15921,7 +15924,7 @@
         <v>0.8076306002881211</v>
       </c>
       <c r="D281" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E281">
         <v>1.014829966085258</v>
@@ -15971,7 +15974,7 @@
         <v>1.191761661061197</v>
       </c>
       <c r="D282" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E282">
         <v>0.964829966085258</v>
@@ -16021,7 +16024,7 @@
         <v>1.177362929466922</v>
       </c>
       <c r="D283" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E283">
         <v>0.9893645149740777</v>
@@ -16071,7 +16074,7 @@
         <v>1.159228697679533</v>
       </c>
       <c r="D284" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E284">
         <v>0.9893645149740777</v>
@@ -16121,7 +16124,7 @@
         <v>1.239895892848584</v>
       </c>
       <c r="D285" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E285">
         <v>0.9893645149740777</v>
@@ -16171,7 +16174,7 @@
         <v>0.7494679440928866</v>
       </c>
       <c r="D286" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E286">
         <v>0.972599870377854</v>
@@ -16221,7 +16224,7 @@
         <v>0.7615300270505188</v>
       </c>
       <c r="D287" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E287">
         <v>0.972599870377854</v>
@@ -16271,7 +16274,7 @@
         <v>0.7897007551840058</v>
       </c>
       <c r="D288" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E288">
         <v>0.972599870377854</v>
@@ -16321,7 +16324,7 @@
         <v>0.7916076307475572</v>
       </c>
       <c r="D289" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E289">
         <v>0.972599870377854</v>
@@ -16371,7 +16374,7 @@
         <v>0.7645067459414072</v>
       </c>
       <c r="D290" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E290">
         <v>0.972599870377854</v>
@@ -16421,7 +16424,7 @@
         <v>1.151840441838677</v>
       </c>
       <c r="D291" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E291">
         <v>0.9225998703778542</v>
@@ -16471,7 +16474,7 @@
         <v>1.135654192965782</v>
       </c>
       <c r="D292" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E292">
         <v>0.9454213818746622</v>
@@ -16521,7 +16524,7 @@
         <v>1.118786119250749</v>
       </c>
       <c r="D293" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E293">
         <v>0.9454213818746622</v>
@@ -16571,7 +16574,7 @@
         <v>1.198708515553709</v>
       </c>
       <c r="D294" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E294">
         <v>0.9454213818746622</v>
@@ -16621,7 +16624,7 @@
         <v>0.707909471861206</v>
       </c>
       <c r="D295" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E295">
         <v>0.9322511481940143</v>
@@ -16671,7 +16674,7 @@
         <v>0.7205408489589988</v>
       </c>
       <c r="D296" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E296">
         <v>0.9322511481940143</v>
@@ -16721,7 +16724,7 @@
         <v>0.7586986932334456</v>
       </c>
       <c r="D297" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E297">
         <v>0.9322511481940143</v>
@@ -16771,7 +16774,7 @@
         <v>0.7502771359779254</v>
       </c>
       <c r="D298" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E298">
         <v>0.9322511481940143</v>
@@ -16821,7 +16824,7 @@
         <v>0.757645758880134</v>
       </c>
       <c r="D299" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E299">
         <v>0.9322511481940143</v>
@@ -16871,7 +16874,7 @@
         <v>0.7233040825473269</v>
       </c>
       <c r="D300" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E300">
         <v>0.9322511481940143</v>
@@ -16921,7 +16924,7 @@
         <v>1.113697734447957</v>
       </c>
       <c r="D301" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E301">
         <v>0.8822511481940145</v>
@@ -16971,7 +16974,7 @@
         <v>1.095803603154581</v>
       </c>
       <c r="D302" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E302">
         <v>0.9034359390378626</v>
@@ -17021,7 +17024,7 @@
         <v>1.080145279487389</v>
       </c>
       <c r="D303" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E303">
         <v>0.9034359390378626</v>
@@ -17071,7 +17074,7 @@
         <v>1.159356058115149</v>
       </c>
       <c r="D304" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E304">
         <v>0.9034359390378626</v>
@@ -17121,7 +17124,7 @@
         <v>0.6769872492951574</v>
       </c>
       <c r="D305" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E305">
         <v>0.9022290588191</v>
@@ -17171,7 +17174,7 @@
         <v>0.6900422184828958</v>
       </c>
       <c r="D306" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E306">
         <v>0.9022290588191</v>
@@ -17221,7 +17224,7 @@
         <v>0.7283059607798297</v>
       </c>
       <c r="D307" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E307">
         <v>0.9022290588191</v>
@@ -17271,7 +17274,7 @@
         <v>0.7209433837491739</v>
       </c>
       <c r="D308" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E308">
         <v>0.9022290588191</v>
@@ -17321,7 +17324,7 @@
         <v>0.7278884145614359</v>
       </c>
       <c r="D309" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E309">
         <v>0.9022290588191</v>
@@ -17371,7 +17374,7 @@
         <v>0.6926466050374938</v>
       </c>
       <c r="D310" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E310">
         <v>0.9022290588191</v>
@@ -17421,7 +17424,7 @@
         <v>1.085317064421583</v>
       </c>
       <c r="D311" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E311">
         <v>0.8522290588191002</v>
@@ -17471,7 +17474,7 @@
         <v>1.066152156858371</v>
       </c>
       <c r="D312" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E312">
         <v>0.8721960224043537</v>
@@ -17521,7 +17524,7 @@
         <v>1.051393966382313</v>
       </c>
       <c r="D313" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E313">
         <v>0.8721960224043537</v>
@@ -17571,7 +17574,7 @@
         <v>1.13007525489764</v>
       </c>
       <c r="D314" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E314">
         <v>0.8721960224043537</v>
@@ -17621,7 +17624,7 @@
         <v>0.6617004606469044</v>
       </c>
       <c r="D315" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E315">
         <v>0.8873872623061558</v>
@@ -17671,7 +17674,7 @@
         <v>0.6749648378983171</v>
       </c>
       <c r="D316" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E316">
         <v>0.8873872623061558</v>
@@ -17721,7 +17724,7 @@
         <v>0.7132809322111697</v>
       </c>
       <c r="D317" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E317">
         <v>0.8873872623061558</v>
@@ -17771,7 +17774,7 @@
         <v>0.706441875339701</v>
       </c>
       <c r="D318" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E318">
         <v>0.8873872623061558</v>
@@ -17821,7 +17824,7 @@
         <v>0.7131774980882888</v>
       </c>
       <c r="D319" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E319">
         <v>0.8873872623061558</v>
@@ -17871,7 +17874,7 @@
         <v>0.6774906964290377</v>
       </c>
       <c r="D320" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E320">
         <v>0.8873872623061558</v>
@@ -17921,7 +17924,7 @@
         <v>1.071286724155378</v>
       </c>
       <c r="D321" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E321">
         <v>0.837387262306156</v>
@@ -17971,7 +17974,7 @@
         <v>1.051493592401141</v>
       </c>
       <c r="D322" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E322">
         <v>0.8567521777083451</v>
@@ -18021,7 +18024,7 @@
         <v>1.037180394060393</v>
       </c>
       <c r="D323" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E323">
         <v>0.8567521777083451</v>
@@ -18071,7 +18074,7 @@
         <v>1.115599922496127</v>
       </c>
       <c r="D324" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E324">
         <v>0.8567521777083451</v>
@@ -18121,7 +18124,7 @@
         <v>0.6627117104425828</v>
       </c>
       <c r="D325" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E325">
         <v>0.8753255899669172</v>
@@ -18171,7 +18174,7 @@
         <v>0.7010703503368783</v>
       </c>
       <c r="D326" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E326">
         <v>0.8753255899669172</v>
@@ -18221,7 +18224,7 @@
         <v>0.6946567492798454</v>
       </c>
       <c r="D327" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E327">
         <v>0.8753255899669172</v>
@@ -18271,7 +18274,7 @@
         <v>0.7012221897026585</v>
       </c>
       <c r="D328" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E328">
         <v>0.8753255899669172</v>
@@ -18321,7 +18324,7 @@
         <v>0.6651737506011379</v>
       </c>
       <c r="D329" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E329">
         <v>0.8753255899669172</v>
@@ -18371,7 +18374,7 @@
         <v>1.059884508328515</v>
       </c>
       <c r="D330" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E330">
         <v>0.8253255899669174</v>
@@ -18421,7 +18424,7 @@
         <v>1.039580829596956</v>
       </c>
       <c r="D331" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E331">
         <v>0.844201231182506</v>
@@ -18471,7 +18474,7 @@
         <v>1.025629268698476</v>
       </c>
       <c r="D332" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E332">
         <v>0.844201231182506</v>
@@ -18521,7 +18524,7 @@
         <v>1.103836069226992</v>
       </c>
       <c r="D333" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E333">
         <v>0.844201231182506</v>
@@ -18571,7 +18574,7 @@
         <v>0.6443218537517277</v>
       </c>
       <c r="D334" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E334">
         <v>0.8572230747868561</v>
@@ -18621,7 +18624,7 @@
         <v>0.6827443473150883</v>
       </c>
       <c r="D335" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E335">
         <v>0.8572230747868561</v>
@@ -18671,7 +18674,7 @@
         <v>0.6769692829487095</v>
       </c>
       <c r="D336" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E336">
         <v>0.8572230747868561</v>
@@ -18721,7 +18724,7 @@
         <v>0.683279308695262</v>
       </c>
       <c r="D337" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E337">
         <v>0.8572230747868561</v>
@@ -18771,7 +18774,7 @@
         <v>0.6466881134066842</v>
       </c>
       <c r="D338" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E338">
         <v>0.8572230747868561</v>
@@ -18821,7 +18824,7 @@
         <v>1.042771725018969</v>
       </c>
       <c r="D339" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E339">
         <v>0.8072230747868563</v>
@@ -18871,7 +18874,7 @@
         <v>1.021701802258623</v>
       </c>
       <c r="D340" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E340">
         <v>0.8253643988081922</v>
@@ -18921,7 +18924,7 @@
         <v>1.008292997547201</v>
       </c>
       <c r="D341" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E341">
         <v>0.8253643988081922</v>
@@ -18971,7 +18974,7 @@
         <v>1.08618052973039</v>
       </c>
       <c r="D342" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E342">
         <v>0.8253643988081922</v>
@@ -19021,7 +19024,7 @@
         <v>0.626551025676668</v>
       </c>
       <c r="D343" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E343">
         <v>0.8397299159004703</v>
@@ -19071,7 +19074,7 @@
         <v>0.6650352235041792</v>
       </c>
       <c r="D344" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E344">
         <v>0.8397299159004703</v>
@@ -19121,7 +19124,7 @@
         <v>0.6598772017792953</v>
       </c>
       <c r="D345" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E345">
         <v>0.8397299159004703</v>
@@ -19171,7 +19174,7 @@
         <v>0.6659404104692488</v>
       </c>
       <c r="D346" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E346">
         <v>0.8397299159004703</v>
@@ -19221,7 +19224,7 @@
         <v>0.6288247289354008</v>
       </c>
       <c r="D347" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E347">
         <v>0.8397299159004703</v>
@@ -19271,7 +19274,7 @@
         <v>1.026234982226899</v>
       </c>
       <c r="D348" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E348">
         <v>0.7897299159004705</v>
@@ -19321,7 +19324,7 @@
         <v>1.004424608296761</v>
       </c>
       <c r="D349" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E349">
         <v>0.807161640884086</v>
@@ -19371,7 +19374,7 @@
         <v>0.9915402898306089</v>
       </c>
       <c r="D350" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E350">
         <v>0.807161640884086</v>
@@ -19421,7 +19424,7 @@
         <v>1.069119300693051</v>
       </c>
       <c r="D351" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E351">
         <v>0.807161640884086</v>
@@ -19471,7 +19474,7 @@
         <v>1.142735629781317</v>
       </c>
       <c r="D352" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E352">
         <v>1.359544955380558</v>
@@ -19521,7 +19524,7 @@
         <v>1.137455121112266</v>
       </c>
       <c r="D353" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E353">
         <v>1.359544955380558</v>
@@ -19571,7 +19574,7 @@
         <v>1.094341564253561</v>
       </c>
       <c r="D354" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E354">
         <v>1.359544955380558</v>
@@ -19821,7 +19824,7 @@
         <v>1.184551441658606</v>
       </c>
       <c r="D359" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E359">
         <v>1.405438550330987</v>
@@ -19871,7 +19874,7 @@
         <v>1.179048508458293</v>
       </c>
       <c r="D360" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E360">
         <v>1.405438550330987</v>
@@ -19921,7 +19924,7 @@
         <v>1.138752328995576</v>
       </c>
       <c r="D361" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E361">
         <v>1.405438550330987</v>
@@ -20221,7 +20224,7 @@
         <v>1.208450935989571</v>
       </c>
       <c r="D367" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E367">
         <v>1.43166866910912</v>
@@ -20271,7 +20274,7 @@
         <v>1.202820877819413</v>
       </c>
       <c r="D368" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E368">
         <v>1.43166866910912</v>
@@ -20321,7 +20324,7 @@
         <v>1.164134947974739</v>
       </c>
       <c r="D369" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E369">
         <v>1.43166866910912</v>
@@ -20371,7 +20374,7 @@
         <v>1.607271750371773</v>
       </c>
       <c r="D370" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E370">
         <v>1.654778494598649</v>
@@ -20421,7 +20424,7 @@
         <v>1.59290180854193</v>
       </c>
       <c r="D371" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E371">
         <v>1.654778494598649</v>
@@ -20471,7 +20474,7 @@
         <v>1.602847854726919</v>
       </c>
       <c r="D372" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E372">
         <v>1.654778494598649</v>
@@ -20521,7 +20524,7 @@
         <v>1.709711052329885</v>
       </c>
       <c r="D373" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E373">
         <v>1.654778494598649</v>
@@ -20571,7 +20574,7 @@
         <v>1.255887381215909</v>
       </c>
       <c r="D374" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E374">
         <v>1.479187680878161</v>
@@ -20621,7 +20624,7 @@
         <v>1.251747741543268</v>
       </c>
       <c r="D375" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E375">
         <v>1.479187680878161</v>
@@ -20671,7 +20674,7 @@
         <v>1.245887381215909</v>
       </c>
       <c r="D376" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E376">
         <v>1.479187680878161</v>
@@ -20721,7 +20724,7 @@
         <v>1.210118612029109</v>
       </c>
       <c r="D377" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E377">
         <v>1.479187680878161</v>
@@ -20771,7 +20774,7 @@
         <v>1.653792786126277</v>
       </c>
       <c r="D378" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E378">
         <v>1.675746239568729</v>
@@ -20821,7 +20824,7 @@
         <v>1.639653146453635</v>
       </c>
       <c r="D379" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E379">
         <v>1.675746239568729</v>
@@ -20871,7 +20874,7 @@
         <v>1.676211705144204</v>
       </c>
       <c r="D380" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E380">
         <v>1.675746239568729</v>
@@ -20921,7 +20924,7 @@
         <v>1.647142636295151</v>
       </c>
       <c r="D381" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E381">
         <v>1.675746239568729</v>
@@ -20971,7 +20974,7 @@
         <v>1.753468462197983</v>
       </c>
       <c r="D382" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E382">
         <v>1.675746239568729</v>
@@ -21021,7 +21024,7 @@
         <v>1.280568627878574</v>
       </c>
       <c r="D383" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E383">
         <v>1.506420642882063</v>
@@ -21071,7 +21074,7 @@
         <v>1.276560973482204</v>
       </c>
       <c r="D384" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E384">
         <v>1.506420642882063</v>
@@ -21121,7 +21124,7 @@
         <v>1.270568627878574</v>
       </c>
       <c r="D385" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E385">
         <v>1.506420642882063</v>
@@ -21171,7 +21174,7 @@
         <v>1.236471672191206</v>
       </c>
       <c r="D386" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E386">
         <v>1.506420642882063</v>
@@ -21471,7 +21474,7 @@
         <v>1.291319393306684</v>
       </c>
       <c r="D392" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E392">
         <v>1.518282895644987</v>
@@ -21521,7 +21524,7 @@
         <v>1.287369229634528</v>
       </c>
       <c r="D393" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E393">
         <v>1.518282895644987</v>
@@ -21571,7 +21574,7 @@
         <v>1.281319393306684</v>
       </c>
       <c r="D394" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E394">
         <v>1.518282895644987</v>
@@ -21621,7 +21624,7 @@
         <v>1.247950653459365</v>
       </c>
       <c r="D395" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E395">
         <v>1.518282895644987</v>
@@ -21671,7 +21674,7 @@
         <v>1.692066938224333</v>
       </c>
       <c r="D396" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E396">
         <v>1.787784532366555</v>
@@ -21721,7 +21724,7 @@
         <v>1.713917429240804</v>
       </c>
       <c r="D397" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E397">
         <v>1.787784532366555</v>
@@ -21771,7 +21774,7 @@
         <v>1.683585187055182</v>
       </c>
       <c r="D398" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E398">
         <v>1.787784532366555</v>
@@ -21821,7 +21824,7 @@
         <v>1.789468902290213</v>
       </c>
       <c r="D399" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E399">
         <v>1.787784532366555</v>
@@ -21871,7 +21874,7 @@
         <v>1.315907870194452</v>
       </c>
       <c r="D400" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E400">
         <v>1.545413496702969</v>
@@ -21921,7 +21924,7 @@
         <v>1.312089195703514</v>
       </c>
       <c r="D401" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E401">
         <v>1.545413496702969</v>
@@ -21971,7 +21974,7 @@
         <v>1.305907870194452</v>
       </c>
       <c r="D402" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E402">
         <v>1.545413496702969</v>
@@ -22021,7 +22024,7 @@
         <v>1.274204659975895</v>
       </c>
       <c r="D403" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E403">
         <v>1.545413496702969</v>
@@ -22071,7 +22074,7 @@
         <v>1.718627752830372</v>
       </c>
       <c r="D404" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E404">
         <v>1.809781567121418</v>
@@ -22121,7 +22124,7 @@
         <v>1.740083776303188</v>
       </c>
       <c r="D405" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E405">
         <v>1.809781567121418</v>
@@ -22171,7 +22174,7 @@
         <v>1.814451846721636</v>
       </c>
       <c r="D406" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E406">
         <v>1.809781567121418</v>
@@ -22221,7 +22224,7 @@
         <v>1.35168436621829</v>
       </c>
       <c r="D407" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E407">
         <v>1.584888810497543</v>
@@ -22271,7 +22274,7 @@
         <v>1.348057009887907</v>
       </c>
       <c r="D408" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E408">
         <v>1.584888810497543</v>
@@ -22321,7 +22324,7 @@
         <v>1.34168436621829</v>
       </c>
       <c r="D409" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E409">
         <v>1.584888810497543</v>
@@ -22371,7 +22374,7 @@
         <v>1.312404519366766</v>
       </c>
       <c r="D410" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E410">
         <v>1.584888810497543</v>
@@ -22421,7 +22424,7 @@
         <v>1.757274021262539</v>
       </c>
       <c r="D411" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E411">
         <v>1.821783446584072</v>
@@ -22471,7 +22474,7 @@
         <v>1.77815609025369</v>
       </c>
       <c r="D412" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E412">
         <v>1.821783446584072</v>
@@ -22521,7 +22524,7 @@
         <v>1.85080229722714</v>
       </c>
       <c r="D413" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E413">
         <v>1.821783446584072</v>
@@ -22571,7 +22574,7 @@
         <v>1.420621085395937</v>
       </c>
       <c r="D414" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E414">
         <v>1.660952677112452</v>
@@ -22621,7 +22624,7 @@
         <v>1.417362374622654</v>
       </c>
       <c r="D415" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E415">
         <v>1.660952677112452</v>
@@ -22671,7 +22674,7 @@
         <v>1.410621085395937</v>
       </c>
       <c r="D416" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E416">
         <v>1.660952677112452</v>
@@ -22721,7 +22724,7 @@
         <v>1.386010748934345</v>
       </c>
       <c r="D417" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E417">
         <v>1.660952677112452</v>
@@ -22771,7 +22774,7 @@
         <v>1.929717195067925</v>
       </c>
       <c r="D418" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E418">
         <v>1.895223002250114</v>
@@ -22821,7 +22824,7 @@
         <v>1.851516556116533</v>
       </c>
       <c r="D419" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E419">
         <v>1.895223002250114</v>
@@ -22871,7 +22874,7 @@
         <v>1.920844953076086</v>
       </c>
       <c r="D420" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E420">
         <v>1.895223002250114</v>
@@ -22921,7 +22924,7 @@
         <v>1.515514817968792</v>
       </c>
       <c r="D421" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E421">
         <v>1.765657169915654</v>
@@ -22971,7 +22974,7 @@
         <v>1.512763560310871</v>
       </c>
       <c r="D422" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E422">
         <v>1.765657169915654</v>
@@ -23021,7 +23024,7 @@
         <v>1.505514817968792</v>
       </c>
       <c r="D423" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E423">
         <v>1.765657169915654</v>
@@ -23071,7 +23074,7 @@
         <v>1.487332220968461</v>
       </c>
       <c r="D424" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E424">
         <v>1.765657169915654</v>
@@ -23121,7 +23124,7 @@
         <v>2.033575932678857</v>
       </c>
       <c r="D425" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E425">
         <v>2.006662200547338</v>
@@ -23171,7 +23174,7 @@
         <v>1.952499726073742</v>
       </c>
       <c r="D426" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E426">
         <v>2.006662200547338</v>
@@ -23221,7 +23224,7 @@
         <v>2.017261044995029</v>
       </c>
       <c r="D427" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E427">
         <v>2.006662200547338</v>
@@ -23271,7 +23274,7 @@
         <v>1.659769367802348</v>
       </c>
       <c r="D428" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E428">
         <v>1.924825737379062</v>
@@ -23321,7 +23324,7 @@
         <v>1.65778952484942</v>
       </c>
       <c r="D429" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E429">
         <v>1.924825737379062</v>
@@ -23371,7 +23374,7 @@
         <v>1.649769367802349</v>
       </c>
       <c r="D430" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E430">
         <v>1.924825737379062</v>
@@ -23421,7 +23424,7 @@
         <v>1.64135802373192</v>
       </c>
       <c r="D431" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E431">
         <v>1.924825737379062</v>
@@ -23471,7 +23474,7 @@
         <v>2.191458808967277</v>
       </c>
       <c r="D432" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E432">
         <v>2.110664481002491</v>
@@ -23521,7 +23524,7 @@
         <v>2.106011252367206</v>
       </c>
       <c r="D433" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E433">
         <v>2.110664481002491</v>
@@ -23571,7 +23574,7 @@
         <v>2.163829838943562</v>
       </c>
       <c r="D434" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E434">
         <v>2.110664481002491</v>
@@ -23621,7 +23624,7 @@
         <v>2.119970938273062</v>
       </c>
       <c r="D435" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E435">
         <v>2.110664481002491</v>
@@ -23671,7 +23674,7 @@
         <v>1.810285876772395</v>
       </c>
       <c r="D436" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E436">
         <v>2.090903667953855</v>
@@ -23721,7 +23724,7 @@
         <v>1.809110934936954</v>
       </c>
       <c r="D437" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E437">
         <v>2.090903667953855</v>
@@ -23771,7 +23774,7 @@
         <v>1.800285876772395</v>
       </c>
       <c r="D438" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E438">
         <v>2.090903667953855</v>
@@ -23821,7 +23824,7 @@
         <v>1.8020699468568</v>
       </c>
       <c r="D439" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E439">
         <v>2.090903667953855</v>
@@ -23871,7 +23874,7 @@
         <v>2.356195237679592</v>
       </c>
       <c r="D440" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E440">
         <v>2.212069946856801</v>
@@ -23921,7 +23924,7 @@
         <v>2.266186574747096</v>
       </c>
       <c r="D441" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E441">
         <v>2.212069946856801</v>
@@ -23971,7 +23974,7 @@
         <v>2.31676105126607</v>
       </c>
       <c r="D442" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E442">
         <v>2.212069946856801</v>
@@ -24021,7 +24024,7 @@
         <v>2.278536458417978</v>
       </c>
       <c r="D443" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E443">
         <v>2.212069946856801</v>
@@ -24071,7 +24074,7 @@
         <v>2.062986387766934</v>
       </c>
       <c r="D444" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E444">
         <v>2.369730078480806</v>
@@ -24121,7 +24124,7 @@
         <v>2.06316278556248</v>
       </c>
       <c r="D445" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E445">
         <v>2.369730078480806</v>
@@ -24171,7 +24174,7 @@
         <v>2.071887426510505</v>
       </c>
       <c r="D446" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E446">
         <v>2.369730078480806</v>
@@ -24221,7 +24224,7 @@
         <v>2.632769415488232</v>
       </c>
       <c r="D447" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E447">
         <v>2.50778970272981</v>
@@ -24271,7 +24274,7 @@
         <v>2.573515581153569</v>
       </c>
       <c r="D448" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E448">
         <v>2.50778970272981</v>
@@ -24321,7 +24324,7 @@
         <v>2.544750365722385</v>
       </c>
       <c r="D449" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E449">
         <v>2.50778970272981</v>
@@ -24371,7 +24374,7 @@
         <v>2.553999441272534</v>
       </c>
       <c r="D450" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E450">
         <v>2.813202993319117</v>
@@ -24421,7 +24424,7 @@
         <v>2.547533939997146</v>
       </c>
       <c r="D451" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E451">
         <v>2.813202993319117</v>
@@ -24471,7 +24474,7 @@
         <v>3.13326483080243</v>
       </c>
       <c r="D452" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E452">
         <v>2.87387576630591</v>
@@ -24521,7 +24524,7 @@
         <v>3.038144875500626</v>
       </c>
       <c r="D453" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E453">
         <v>2.87387576630591</v>
@@ -24571,7 +24574,7 @@
         <v>3.035948483419955</v>
       </c>
       <c r="D454" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E454">
         <v>2.87387576630591</v>
@@ -24621,7 +24624,7 @@
         <v>3.591660905082458</v>
       </c>
       <c r="D455" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E455">
         <v>3.945252973872349</v>
@@ -24771,7 +24774,7 @@
         <v>2.86820460595768</v>
       </c>
       <c r="D458" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E458">
         <v>3.138678397668333</v>
@@ -24821,7 +24824,7 @@
         <v>2.851519426722356</v>
       </c>
       <c r="D459" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E459">
         <v>3.138678397668333</v>
@@ -24871,7 +24874,7 @@
         <v>2.868149068251708</v>
       </c>
       <c r="D460" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E460">
         <v>3.138678397668333</v>
@@ -24921,7 +24924,7 @@
         <v>3.448970831229631</v>
       </c>
       <c r="D461" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E461">
         <v>3.183720050947811</v>
@@ -24971,7 +24974,7 @@
         <v>3.377034871712487</v>
       </c>
       <c r="D462" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E462">
         <v>3.183720050947811</v>
@@ -25021,7 +25024,7 @@
         <v>2.358110206260426</v>
       </c>
       <c r="D463" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E463">
         <v>2.638276257123781</v>
@@ -25071,7 +25074,7 @@
         <v>2.331756830399265</v>
       </c>
       <c r="D464" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E464">
         <v>2.638276257123781</v>
@@ -25121,7 +25124,7 @@
         <v>2.899146400442653</v>
       </c>
       <c r="D465" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E465">
         <v>2.658455604321169</v>
@@ -25171,7 +25174,7 @@
         <v>2.820803661648716</v>
       </c>
       <c r="D466" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E466">
         <v>2.658455604321169</v>
@@ -25221,7 +25224,7 @@
         <v>2.837060715744168</v>
       </c>
       <c r="D467" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E467">
         <v>2.658455604321169</v>
@@ -25271,7 +25274,7 @@
         <v>2.825582801735491</v>
       </c>
       <c r="D468" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E468">
         <v>2.658455604321169</v>
@@ -25321,7 +25324,7 @@
         <v>2.136909691166413</v>
       </c>
       <c r="D469" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E469">
         <v>2.404885634240017</v>
@@ -25371,7 +25374,7 @@
         <v>2.105907100015784</v>
       </c>
       <c r="D470" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E470">
         <v>2.404885634240017</v>
@@ -25421,7 +25424,7 @@
         <v>2.667641000683959</v>
       </c>
       <c r="D471" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E471">
         <v>2.457950031567318</v>
@@ -25471,7 +25474,7 @@
         <v>2.605888225390645</v>
       </c>
       <c r="D472" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E472">
         <v>2.457950031567318</v>
@@ -25521,7 +25524,7 @@
         <v>2.60970280686063</v>
       </c>
       <c r="D473" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E473">
         <v>2.457950031567318</v>
@@ -25571,7 +25574,7 @@
         <v>2.599356026726996</v>
       </c>
       <c r="D474" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E474">
         <v>2.457950031567318</v>
@@ -25621,7 +25624,7 @@
         <v>1.900611258233865</v>
       </c>
       <c r="D475" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E475">
         <v>2.138942488812295</v>
@@ -25671,7 +25674,7 @@
         <v>1.901190054137531</v>
       </c>
       <c r="D476" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E476">
         <v>2.138942488812295</v>
@@ -25721,7 +25724,7 @@
         <v>1.897421572498996</v>
       </c>
       <c r="D477" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E477">
         <v>2.138942488812295</v>
@@ -25771,7 +25774,7 @@
         <v>2.403846022828351</v>
       </c>
       <c r="D478" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E478">
         <v>2.266842776595331</v>
@@ -25821,7 +25824,7 @@
         <v>2.360997122169641</v>
       </c>
       <c r="D479" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E479">
         <v>2.266842776595331</v>
@@ -25871,7 +25874,7 @@
         <v>2.350633797663673</v>
       </c>
       <c r="D480" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E480">
         <v>2.266842776595331</v>
@@ -25921,7 +25924,7 @@
         <v>2.341575918073307</v>
       </c>
       <c r="D481" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E481">
         <v>2.266842776595331</v>
@@ -25971,7 +25974,7 @@
         <v>0.06833146887762798</v>
       </c>
       <c r="D482" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E482">
         <v>0.2515379924458756</v>
@@ -26021,7 +26024,7 @@
         <v>0.09559505684016401</v>
       </c>
       <c r="D483" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E483">
         <v>0.2515379924458756</v>
@@ -26071,7 +26074,7 @@
         <v>0.02229342594810202</v>
       </c>
       <c r="D484" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E484">
         <v>0.2515379924458756</v>
@@ -26121,7 +26124,7 @@
         <v>0.07493473066175138</v>
       </c>
       <c r="D485" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E485">
         <v>0.2515379924458756</v>
@@ -26171,7 +26174,7 @@
         <v>0.09682060187317454</v>
       </c>
       <c r="D486" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E486">
         <v>0.2921032113004749</v>
@@ -26221,7 +26224,7 @@
         <v>0.4058749537233215</v>
       </c>
       <c r="D487" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E487">
         <v>0.4152146275449082</v>
@@ -26271,7 +26274,7 @@
         <v>0.4038939751880841</v>
       </c>
       <c r="D488" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E488">
         <v>0.4152146275449082</v>
@@ -26321,7 +26324,7 @@
         <v>0.01461566789420843</v>
       </c>
       <c r="D489" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E489">
         <v>0.1862219618346161</v>
@@ -26371,7 +26374,7 @@
         <v>-0.05940006695681266</v>
       </c>
       <c r="D490" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E490">
         <v>0.1862219618346161</v>
@@ -26421,7 +26424,7 @@
         <v>-0.006187479075995483</v>
       </c>
       <c r="D491" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E491">
         <v>0.1862219618346161</v>
@@ -26471,7 +26474,7 @@
         <v>0.01826916638767973</v>
       </c>
       <c r="D492" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E492">
         <v>0.2146943421493139</v>
@@ -26521,7 +26524,7 @@
         <v>0.3336076330766655</v>
       </c>
       <c r="D493" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E493">
         <v>0.3744107800468699</v>
@@ -26571,7 +26574,7 @@
         <v>0.3311981921660534</v>
       </c>
       <c r="D494" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E494">
         <v>0.3744107800468699</v>
@@ -26621,7 +26624,7 @@
         <v>-0.03183657790337602</v>
       </c>
       <c r="D495" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E495">
         <v>0.1263451749282281</v>
@@ -26657,7 +26660,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26671,7 +26674,7 @@
         <v>-0.04547307224016794</v>
       </c>
       <c r="D496" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E496">
         <v>0.1263451749282281</v>
@@ -26707,7 +26710,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26721,7 +26724,7 @@
         <v>-0.06638219582436466</v>
       </c>
       <c r="D497" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E497">
         <v>0.1263451749282281</v>
@@ -26757,7 +26760,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26771,7 +26774,7 @@
         <v>-0.04001797130880469</v>
       </c>
       <c r="D498" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E498">
         <v>0.1572550173647782</v>
@@ -26807,7 +26810,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26821,7 +26824,7 @@
         <v>0.2799834663959002</v>
       </c>
       <c r="D499" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E499">
         <v>0.2990743428117018</v>
@@ -26857,7 +26860,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26871,7 +26874,7 @@
         <v>0.2927108371484932</v>
       </c>
       <c r="D500" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E500">
         <v>0.2990743428117018</v>
@@ -26907,7 +26910,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26921,7 +26924,7 @@
         <v>2.328573731313484</v>
       </c>
       <c r="D501" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E501">
         <v>2.38850098797026</v>
@@ -26971,7 +26974,7 @@
         <v>2.311727797453313</v>
       </c>
       <c r="D502" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E502">
         <v>2.38850098797026</v>
@@ -27021,7 +27024,7 @@
         <v>2.277498128152465</v>
       </c>
       <c r="D503" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E503">
         <v>2.38850098797026</v>
@@ -27071,7 +27074,7 @@
         <v>2.434271318669412</v>
       </c>
       <c r="D504" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E504">
         <v>2.368966046207545</v>
@@ -27121,7 +27124,7 @@
         <v>2.32366077374568</v>
       </c>
       <c r="D505" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E505">
         <v>2.390041649368564</v>
@@ -27171,7 +27174,7 @@
         <v>2.442730657271108</v>
       </c>
       <c r="D506" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E506">
         <v>2.371117252529581</v>
@@ -27221,7 +27224,7 @@
         <v>2.477425384809242</v>
       </c>
       <c r="D507" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E507">
         <v>2.518428244627036</v>
@@ -27271,7 +27274,7 @@
         <v>2.431582310766867</v>
       </c>
       <c r="D508" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E508">
         <v>2.369968906025341</v>
@@ -27571,7 +27574,7 @@
         <v>2.273423820568129</v>
       </c>
       <c r="D514" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E514">
         <v>2.348847751625323</v>
@@ -27621,7 +27624,7 @@
         <v>2.238819356972905</v>
       </c>
       <c r="D515" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E515">
         <v>2.348847751625323</v>
@@ -27671,7 +27674,7 @@
         <v>2.3942432880301</v>
       </c>
       <c r="D516" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E516">
         <v>2.328113468120607</v>
@@ -27721,7 +27724,7 @@
         <v>2.281983648211115</v>
       </c>
       <c r="D517" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E517">
         <v>2.349638824434876</v>
@@ -27771,7 +27774,7 @@
         <v>2.403452215220548</v>
       </c>
       <c r="D518" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E518">
         <v>2.331164180749144</v>
@@ -27821,7 +27824,7 @@
         <v>2.437322395311055</v>
       </c>
       <c r="D519" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E519">
         <v>2.477350789963473</v>
@@ -27871,7 +27874,7 @@
         <v>2.390429897244429</v>
       </c>
       <c r="D520" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E520">
         <v>2.328141862773026</v>
@@ -28171,7 +28174,7 @@
         <v>2.216097983185153</v>
       </c>
       <c r="D526" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E526">
         <v>2.278296441308225</v>
@@ -28221,7 +28224,7 @@
         <v>2.180932601415928</v>
       </c>
       <c r="D527" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E527">
         <v>2.289502608815942</v>
@@ -28271,7 +28274,7 @@
         <v>2.334337227046717</v>
       </c>
       <c r="D528" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E528">
         <v>2.26697338715442</v>
@@ -28321,7 +28324,7 @@
         <v>2.219609547262124</v>
       </c>
       <c r="D529" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E529">
         <v>2.289171845277491</v>
@@ -28371,7 +28374,7 @@
         <v>2.344667990585168</v>
       </c>
       <c r="D530" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E530">
         <v>2.271370303400561</v>
@@ -28421,7 +28424,7 @@
         <v>2.377304150692871</v>
       </c>
       <c r="D531" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E531">
         <v>2.415874158092884</v>
@@ -28471,7 +28474,7 @@
         <v>2.32884108173904</v>
       </c>
       <c r="D532" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E532">
         <v>2.265543394554435</v>
@@ -28771,7 +28774,7 @@
         <v>2.129304507872965</v>
       </c>
       <c r="D538" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E538">
         <v>2.23657380748992</v>
@@ -28821,7 +28824,7 @@
         <v>2.280908153496441</v>
       </c>
       <c r="D539" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E539">
         <v>2.212443714710786</v>
@@ -28871,7 +28874,7 @@
         <v>2.163979275925133</v>
       </c>
       <c r="D540" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E540">
         <v>2.235242499502962</v>
@@ -28921,7 +28924,7 @@
         <v>2.292239461483399</v>
       </c>
       <c r="D541" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E541">
         <v>2.218041284295136</v>
@@ -28971,7 +28974,7 @@
         <v>2.323775022697745</v>
       </c>
       <c r="D542" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E542">
         <v>2.361044322314699</v>
@@ -29021,7 +29024,7 @@
         <v>2.273911191516004</v>
       </c>
       <c r="D543" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E543">
         <v>2.209713014327742</v>
@@ -29371,7 +29374,7 @@
         <v>2.045412902019458</v>
       </c>
       <c r="D550" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E550">
         <v>2.135412902019459</v>
@@ -29421,7 +29424,7 @@
         <v>2.194090096275951</v>
       </c>
       <c r="D551" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E551">
         <v>2.123837270543807</v>
@@ -29471,7 +29474,7 @@
         <v>2.073584444811665</v>
       </c>
       <c r="D552" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E552">
         <v>2.147611539124977</v>
@@ -29521,7 +29524,7 @@
         <v>2.2070472105779</v>
       </c>
       <c r="D553" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E553">
         <v>2.131385807706146</v>
@@ -29571,7 +29574,7 @@
         <v>2.236794384845756</v>
       </c>
       <c r="D554" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E554">
         <v>2.271950136253223</v>
@@ -29621,7 +29624,7 @@
         <v>2.184654424823028</v>
       </c>
       <c r="D555" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E555">
         <v>2.118993021951275</v>
@@ -29971,7 +29974,7 @@
         <v>2.129009034907942</v>
       </c>
       <c r="D562" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E562">
         <v>2.057415588061476</v>
@@ -30021,7 +30024,7 @@
         <v>2.005822141215011</v>
       </c>
       <c r="D563" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E563">
         <v>2.081921104523186</v>
@@ -30071,7 +30074,7 @@
         <v>2.143184895677456</v>
       </c>
       <c r="D564" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E564">
         <v>2.205162829830622</v>
@@ -30121,7 +30124,7 @@
         <v>2.171591448830991</v>
       </c>
       <c r="D565" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E565">
         <v>2.205162829830622</v>
@@ -30171,7 +30174,7 @@
         <v>2.117745243753671</v>
       </c>
       <c r="D566" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E566">
         <v>2.050986969061109</v>
@@ -30471,7 +30474,7 @@
         <v>2.096029330113085</v>
       </c>
       <c r="D572" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E572">
         <v>2.023756526051743</v>
@@ -30507,7 +30510,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30521,7 +30524,7 @@
         <v>1.971483721990404</v>
       </c>
       <c r="D573" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E573">
         <v>2.048632600994294</v>
@@ -30557,7 +30560,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30571,7 +30574,7 @@
         <v>1.973756526051743</v>
       </c>
       <c r="D574" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E574">
         <v>2.048632600994294</v>
@@ -30607,7 +30610,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30621,7 +30624,7 @@
         <v>2.110822788350668</v>
       </c>
       <c r="D575" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E575">
         <v>2.171318488580469</v>
@@ -30657,7 +30660,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30671,7 +30674,7 @@
         <v>2.138549984289327</v>
       </c>
       <c r="D576" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E576">
         <v>2.171318488580469</v>
@@ -30707,7 +30710,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30721,7 +30724,7 @@
         <v>2.083839142756712</v>
       </c>
       <c r="D577" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E577">
         <v>2.016525030342887</v>
@@ -30757,7 +30760,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30807,7 +30810,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30857,7 +30860,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30907,7 +30910,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30921,7 +30924,7 @@
         <v>1.949210917929062</v>
       </c>
       <c r="D581" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E581">
         <v>1.907020730572688</v>
@@ -30957,7 +30960,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30971,7 +30974,7 @@
         <v>1.92954138474893</v>
       </c>
       <c r="D582" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E582">
         <v>1.907020730572688</v>
@@ -31007,7 +31010,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31021,7 +31024,7 @@
         <v>2.096163622975572</v>
       </c>
       <c r="D583" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E583">
         <v>2.023893585246604</v>
@@ -31057,7 +31060,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31071,7 +31074,7 @@
         <v>2.110954566365543</v>
       </c>
       <c r="D584" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E584">
         <v>2.171456302229613</v>
@@ -31107,7 +31110,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31121,7 +31124,7 @@
         <v>2.138684528636575</v>
       </c>
       <c r="D585" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E585">
         <v>2.171456302229613</v>
@@ -31157,7 +31160,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31207,7 +31210,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31257,7 +31260,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31307,7 +31310,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31357,7 +31360,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31407,7 +31410,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31421,7 +31424,7 @@
         <v>2.110759270205002</v>
       </c>
       <c r="D591" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E591">
         <v>2.038789891875891</v>
@@ -31457,7 +31460,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31471,7 +31474,7 @@
         <v>2.12527688686783</v>
       </c>
       <c r="D592" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E592">
         <v>2.013886368543326</v>
@@ -31507,7 +31510,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31521,7 +31524,7 @@
         <v>2.153307508538719</v>
       </c>
       <c r="D593" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E593">
         <v>2.013886368543326</v>
@@ -31557,7 +31560,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31607,7 +31610,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31657,7 +31660,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31707,7 +31710,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31757,7 +31760,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31807,7 +31810,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31871,7 +31874,7 @@
         <v>2.156860011399363</v>
       </c>
       <c r="D600" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E600">
         <v>2.046855775258495</v>
@@ -31921,7 +31924,7 @@
         <v>2.185553637592861</v>
       </c>
       <c r="D601" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E601">
         <v>2.046855775258495</v>
@@ -31971,7 +31974,7 @@
         <v>2.132072798202768</v>
       </c>
       <c r="D602" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E602">
         <v>2.065549401451994</v>
@@ -32321,7 +32324,7 @@
         <v>2.170392584088286</v>
       </c>
       <c r="D609" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E609">
         <v>2.060982334916589</v>
@@ -32371,7 +32374,7 @@
         <v>2.19937029100617</v>
       </c>
       <c r="D610" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E610">
         <v>2.060982334916589</v>
@@ -32421,7 +32424,7 @@
         <v>2.146251008901658</v>
       </c>
       <c r="D611" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E611">
         <v>2.079960041834473</v>
@@ -32757,7 +32760,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32771,7 +32774,7 @@
         <v>2.199468285459675</v>
       </c>
       <c r="D618" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E618">
         <v>2.091334259821454</v>
@@ -32807,7 +32810,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32821,7 +32824,7 @@
         <v>2.229056360154438</v>
       </c>
       <c r="D619" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E619">
         <v>2.091334259821454</v>
@@ -32857,7 +32860,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32871,7 +32874,7 @@
         <v>2.176713909765957</v>
       </c>
       <c r="D620" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E620">
         <v>2.110922334516219</v>
@@ -32907,7 +32910,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32957,7 +32960,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -33007,7 +33010,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -33057,7 +33060,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33107,7 +33110,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33157,7 +33160,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33171,7 +33174,7 @@
         <v>2.220298065961964</v>
       </c>
       <c r="D626" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E626">
         <v>2.113078324582432</v>
@@ -33207,7 +33210,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33221,7 +33224,7 @@
         <v>2.250323407041319</v>
       </c>
       <c r="D627" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E627">
         <v>2.113078324582432</v>
@@ -33257,7 +33260,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33271,7 +33274,7 @@
         <v>2.198537477505952</v>
       </c>
       <c r="D628" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E628">
         <v>2.133103665661787</v>
@@ -33307,7 +33310,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33357,7 +33360,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33407,7 +33410,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33457,7 +33460,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33507,7 +33510,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33571,7 +33574,7 @@
         <v>2.238063065063528</v>
       </c>
       <c r="D634" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E634">
         <v>2.131623085094942</v>
@@ -33621,7 +33624,7 @@
         <v>2.268461335513335</v>
       </c>
       <c r="D635" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E635">
         <v>2.131623085094942</v>
@@ -33671,7 +33674,7 @@
         <v>2.217150043358544</v>
       </c>
       <c r="D636" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E636">
         <v>2.15202135554475</v>
@@ -33971,7 +33974,7 @@
         <v>2.240855764159465</v>
       </c>
       <c r="D642" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E642">
         <v>2.134538364494709</v>
@@ -34021,7 +34024,7 @@
         <v>2.271312659971973</v>
       </c>
       <c r="D643" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E643">
         <v>2.134538364494709</v>
@@ -34071,7 +34074,7 @@
         <v>2.220075981915165</v>
       </c>
       <c r="D644" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E644">
         <v>2.154995260307217</v>
@@ -34321,7 +34324,7 @@
         <v>2.244303552497403</v>
       </c>
       <c r="D649" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E649">
         <v>2.138137487053587</v>
@@ -34371,7 +34374,7 @@
         <v>2.274832825546012</v>
       </c>
       <c r="D650" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E650">
         <v>2.138137487053587</v>
@@ -34421,7 +34424,7 @@
         <v>2.223688263971516</v>
       </c>
       <c r="D651" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E651">
         <v>2.149196033150806</v>
@@ -34721,7 +34724,7 @@
         <v>2.233337795982168</v>
       </c>
       <c r="D657" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E657">
         <v>2.126690409164592</v>
@@ -34757,7 +34760,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34771,7 +34774,7 @@
         <v>2.263636871852023</v>
       </c>
       <c r="D658" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E658">
         <v>2.126690409164592</v>
@@ -34807,7 +34810,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34821,7 +34824,7 @@
         <v>2.21219933205002</v>
       </c>
       <c r="D659" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E659">
         <v>2.137288560904301</v>
@@ -34857,7 +34860,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34907,7 +34910,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34957,7 +34960,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35007,7 +35010,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -35057,7 +35060,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35107,7 +35110,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35121,7 +35124,7 @@
         <v>2.221972886589618</v>
       </c>
       <c r="D665" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E665">
         <v>2.114826658329239</v>
@@ -35171,7 +35174,7 @@
         <v>2.252033386117262</v>
       </c>
       <c r="D666" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E666">
         <v>2.114826658329239</v>
@@ -35221,7 +35224,7 @@
         <v>2.200292203697901</v>
       </c>
       <c r="D667" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E667">
         <v>2.124947657384527</v>
@@ -35321,7 +35324,7 @@
         <v>2.06227538422784</v>
       </c>
       <c r="D669" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E669">
         <v>1.996930837914467</v>
@@ -35371,7 +35374,7 @@
         <v>2.053206474965166</v>
       </c>
       <c r="D670" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E670">
         <v>1.996930837914467</v>
@@ -35421,7 +35424,7 @@
         <v>2.020473702280834</v>
       </c>
       <c r="D671" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E671">
         <v>1.996930837914467</v>
@@ -35471,7 +35474,7 @@
         <v>2.029603111071154</v>
       </c>
       <c r="D672" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E672">
         <v>1.996930837914467</v>
@@ -35521,7 +35524,7 @@
         <v>2.207355417889053</v>
       </c>
       <c r="D673" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E673">
         <v>2.099567583178076</v>
@@ -35571,7 +35574,7 @@
         <v>2.237109062157716</v>
       </c>
       <c r="D674" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E674">
         <v>2.099567583178076</v>
@@ -35621,7 +35624,7 @@
         <v>2.184977336681469</v>
       </c>
       <c r="D675" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E675">
         <v>2.109074871715402</v>
@@ -35721,7 +35724,7 @@
         <v>2.036943146239156</v>
       </c>
       <c r="D677" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E677">
         <v>2.010221174266302</v>
@@ -35771,7 +35774,7 @@
         <v>2.004238269487459</v>
       </c>
       <c r="D678" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E678">
         <v>2.010221174266302</v>
@@ -35821,7 +35824,7 @@
         <v>2.013172406749336</v>
       </c>
       <c r="D679" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E679">
         <v>2.010221174266302</v>
@@ -35871,7 +35874,7 @@
         <v>2.197603098441371</v>
       </c>
       <c r="D680" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E680">
         <v>2.089387203907309</v>
@@ -35921,7 +35924,7 @@
         <v>2.22715201844682</v>
       </c>
       <c r="D681" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E681">
         <v>2.089387203907309</v>
@@ -35971,7 +35974,7 @@
         <v>2.174759734817391</v>
       </c>
       <c r="D682" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E682">
         <v>2.098485043918206</v>
@@ -36071,7 +36074,7 @@
         <v>2.184014672997228</v>
       </c>
       <c r="D684" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E684">
         <v>2.09430865482284</v>
@@ -36221,7 +36224,7 @@
         <v>2.195758520592005</v>
       </c>
       <c r="D687" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E687">
         <v>2.087461661763028</v>
@@ -36271,7 +36274,7 @@
         <v>2.225268718543363</v>
       </c>
       <c r="D688" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E688">
         <v>2.087461661763028</v>
@@ -36421,7 +36424,7 @@
         <v>2.182096171226417</v>
       </c>
       <c r="D691" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E691">
         <v>2.092337350250998</v>
@@ -36471,7 +36474,7 @@
         <v>1.991357746153715</v>
       </c>
       <c r="D692" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E692">
         <v>1.93891617990999</v>
@@ -36521,7 +36524,7 @@
         <v>2.000136963031852</v>
       </c>
       <c r="D693" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E693">
         <v>1.93891617990999</v>
@@ -36571,7 +36574,7 @@
         <v>2.189904250619724</v>
       </c>
       <c r="D694" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E694">
         <v>2.08135042955914</v>
@@ -36621,7 +36624,7 @@
         <v>2.219291553590749</v>
       </c>
       <c r="D695" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E695">
         <v>2.08135042955914</v>
@@ -36771,7 +36774,7 @@
         <v>2.176007283564408</v>
       </c>
       <c r="D698" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E698">
         <v>2.086080878524897</v>
@@ -36821,7 +36824,7 @@
         <v>1.984855484466945</v>
       </c>
       <c r="D699" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E699">
         <v>1.914929079427434</v>
@@ -36871,7 +36874,7 @@
         <v>1.993556495448507</v>
       </c>
       <c r="D700" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E700">
         <v>1.914929079427434</v>
@@ -36921,7 +36924,7 @@
         <v>2.193018564119005</v>
       </c>
       <c r="D701" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E701">
         <v>2.084601440024992</v>
@@ -36957,7 +36960,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36971,7 +36974,7 @@
         <v>2.222471243900129</v>
       </c>
       <c r="D702" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E702">
         <v>2.084601440024992</v>
@@ -37007,7 +37010,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37057,7 +37060,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37107,7 +37110,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37121,7 +37124,7 @@
         <v>2.179246407337514</v>
       </c>
       <c r="D705" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E705">
         <v>2.089409152493594</v>
@@ -37157,7 +37160,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37207,7 +37210,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37257,7 +37260,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37271,7 +37274,7 @@
         <v>2.19977860938273</v>
       </c>
       <c r="D708" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E708">
         <v>2.091658204832735</v>
@@ -37321,7 +37324,7 @@
         <v>2.229373198510994</v>
       </c>
       <c r="D709" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E709">
         <v>2.091658204832735</v>
@@ -37521,7 +37524,7 @@
         <v>1.995822806604482</v>
       </c>
       <c r="D713" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E713">
         <v>2.003132389411005</v>
@@ -37571,7 +37574,7 @@
         <v>2.004655726958832</v>
       </c>
       <c r="D714" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E714">
         <v>2.003132389411005</v>
@@ -37621,7 +37624,7 @@
         <v>2.193355078571245</v>
       </c>
       <c r="D715" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E715">
         <v>2.084952725149754</v>
@@ -37671,7 +37674,7 @@
         <v>2.222814822587054</v>
       </c>
       <c r="D716" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E716">
         <v>2.084952725149754</v>
@@ -39271,7 +39274,7 @@
         <v>2.337261384103764</v>
       </c>
       <c r="D748" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E748">
         <v>2.334684098776408</v>
@@ -40257,7 +40260,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40307,7 +40310,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40357,7 +40360,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40407,7 +40410,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40457,7 +40460,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40507,7 +40510,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40771,7 +40774,7 @@
         <v>2.194922646011972</v>
       </c>
       <c r="D778" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E778">
         <v>2.189382078142695</v>
@@ -40821,7 +40824,7 @@
         <v>2.206481859731435</v>
       </c>
       <c r="D779" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E779">
         <v>2.189382078142695</v>
@@ -41021,7 +41024,7 @@
         <v>2.131068921554799</v>
       </c>
       <c r="D783" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E783">
         <v>2.092957793173342</v>
@@ -41071,7 +41074,7 @@
         <v>2.132036227593599</v>
       </c>
       <c r="D784" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E784">
         <v>2.092957793173342</v>
@@ -41121,7 +41124,7 @@
         <v>2.146598315033257</v>
       </c>
       <c r="D785" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E785">
         <v>2.092957793173342</v>
@@ -41171,7 +41174,7 @@
         <v>2.102497010383471</v>
       </c>
       <c r="D786" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E786">
         <v>2.092957793173342</v>
@@ -41671,7 +41674,7 @@
         <v>2.073856432611444</v>
       </c>
       <c r="D796" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E796">
         <v>2.047486402626956</v>
@@ -41721,7 +41724,7 @@
         <v>2.077590491138006</v>
       </c>
       <c r="D797" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E797">
         <v>2.047486402626956</v>
@@ -41771,7 +41774,7 @@
         <v>2.08056732910815</v>
       </c>
       <c r="D798" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E798">
         <v>2.047486402626956</v>
@@ -41821,7 +41824,7 @@
         <v>2.048347711694423</v>
       </c>
       <c r="D799" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E799">
         <v>2.047486402626956</v>
@@ -41871,7 +41874,7 @@
         <v>2.04370029984487</v>
       </c>
       <c r="D800" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E800">
         <v>2.047486402626956</v>
@@ -42021,7 +42024,7 @@
         <v>2.024445400397088</v>
       </c>
       <c r="D803" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E803">
         <v>2.022683653209794</v>
@@ -42071,7 +42074,7 @@
         <v>2.030568938892565</v>
       </c>
       <c r="D804" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E804">
         <v>2.022683653209794</v>
@@ -42121,7 +42124,7 @@
         <v>2.034621883962056</v>
       </c>
       <c r="D805" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E805">
         <v>2.022683653209794</v>
@@ -42171,7 +42174,7 @@
         <v>2.001582175159937</v>
       </c>
       <c r="D806" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E806">
         <v>2.022683653209794</v>
@@ -42221,7 +42224,7 @@
         <v>1.997617471872931</v>
       </c>
       <c r="D807" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E807">
         <v>2.022683653209794</v>
@@ -43671,7 +43674,7 @@
         <v>1.759602623534774</v>
       </c>
       <c r="D836" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E836">
         <v>1.719390259748886</v>
@@ -43721,7 +43724,7 @@
         <v>1.825899932835016</v>
       </c>
       <c r="D837" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E837">
         <v>1.719390259748886</v>
@@ -43771,7 +43774,7 @@
         <v>1.830538284330232</v>
       </c>
       <c r="D838" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E838">
         <v>1.719390259748886</v>
@@ -43821,7 +43824,7 @@
         <v>1.836410866058698</v>
       </c>
       <c r="D839" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E839">
         <v>1.719390259748886</v>
@@ -43871,7 +43874,7 @@
         <v>1.829091690311091</v>
       </c>
       <c r="D840" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E840">
         <v>1.719390259748886</v>
@@ -43921,7 +43924,7 @@
         <v>1.827645096291951</v>
       </c>
       <c r="D841" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E841">
         <v>1.719390259748886</v>
@@ -43971,7 +43974,7 @@
         <v>1.815986138486923</v>
       </c>
       <c r="D842" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E842">
         <v>1.719390259748886</v>
@@ -44021,7 +44024,7 @@
         <v>2.078884835277132</v>
       </c>
       <c r="D843" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E843">
         <v>1.919229396577419</v>
@@ -44371,7 +44374,7 @@
         <v>2.058494156511253</v>
       </c>
       <c r="D850" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E850">
         <v>1.898167274316649</v>
@@ -44521,7 +44524,7 @@
         <v>2.05395617407601</v>
       </c>
       <c r="D853" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E853">
         <v>1.893479860917333</v>
@@ -44571,7 +44574,7 @@
         <v>1.719695780725853</v>
       </c>
       <c r="D854" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E854">
         <v>1.897089270892098</v>
@@ -44621,7 +44624,7 @@
         <v>1.731500485713235</v>
       </c>
       <c r="D855" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E855">
         <v>1.603580408564653</v>
@@ -44671,7 +44674,7 @@
         <v>2.009186193442025</v>
       </c>
       <c r="D856" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E856">
         <v>1.863835939658896</v>
@@ -44721,7 +44724,7 @@
         <v>2.007288122382748</v>
       </c>
       <c r="D857" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E857">
         <v>1.863835939658896</v>
@@ -44771,7 +44774,7 @@
         <v>1.708676548738404</v>
       </c>
       <c r="D858" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E858">
         <v>1.886090558889729</v>
@@ -44821,7 +44824,7 @@
         <v>1.721096853278158</v>
       </c>
       <c r="D859" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E859">
         <v>1.580396345711901</v>
@@ -44871,7 +44874,7 @@
         <v>1.963236498776014</v>
       </c>
       <c r="D860" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E860">
         <v>1.815877954142098</v>
@@ -44921,7 +44924,7 @@
         <v>1.960776106278517</v>
       </c>
       <c r="D861" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E861">
         <v>1.815877954142098</v>
@@ -44971,7 +44974,7 @@
         <v>1.665538461263496</v>
       </c>
       <c r="D862" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E862">
         <v>1.843032803048852</v>
@@ -45021,7 +45024,7 @@
         <v>1.680368714824194</v>
       </c>
       <c r="D863" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E863">
         <v>1.46569689127351</v>
@@ -45071,7 +45074,7 @@
         <v>1.897510677314785</v>
       </c>
       <c r="D864" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E864">
         <v>1.747279500623998</v>
@@ -45121,7 +45124,7 @@
         <v>1.894245947841364</v>
       </c>
       <c r="D865" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E865">
         <v>1.747279500623998</v>
@@ -45171,7 +45174,7 @@
         <v>1.603834324681888</v>
       </c>
       <c r="D866" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E866">
         <v>1.755351101073204</v>
@@ -45221,7 +45224,7 @@
         <v>1.536662065884782</v>
       </c>
       <c r="D867" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E867">
         <v>1.400775406788205</v>
@@ -45271,7 +45274,7 @@
         <v>1.895854864894484</v>
       </c>
       <c r="D868" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E868">
         <v>1.745551318779732</v>
@@ -45321,7 +45324,7 @@
         <v>1.892569871982353</v>
       </c>
       <c r="D869" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E869">
         <v>1.745551318779732</v>
@@ -45371,7 +45374,7 @@
         <v>1.602279829455136</v>
       </c>
       <c r="D870" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E870">
         <v>1.753770552853825</v>
@@ -45421,7 +45424,7 @@
         <v>1.535116254988906</v>
       </c>
       <c r="D871" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E871">
         <v>1.325406297516124</v>
@@ -45571,7 +45574,7 @@
         <v>1.521259989314879</v>
       </c>
       <c r="D874" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E874">
         <v>1.310460213193578</v>
@@ -45771,7 +45774,7 @@
         <v>1.513048711151803</v>
       </c>
       <c r="D878" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E878">
         <v>1.301603104163743</v>
@@ -45971,7 +45974,7 @@
         <v>1.507728180990036</v>
       </c>
       <c r="D882" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E882">
         <v>1.295864105337568</v>
@@ -46121,7 +46124,7 @@
         <v>1.483132200904999</v>
       </c>
       <c r="D885" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E885">
         <v>1.269333609964943</v>
@@ -46207,7 +46210,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46257,7 +46260,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46271,7 +46274,7 @@
         <v>1.477459737368338</v>
       </c>
       <c r="D888" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E888">
         <v>1.263214997610793</v>
@@ -46307,7 +46310,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46321,7 +46324,7 @@
         <v>1.484299398814228</v>
       </c>
       <c r="D889" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E889">
         <v>1.263214997610793</v>
@@ -46357,7 +46360,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -46421,7 +46424,7 @@
         <v>1.488270615876439</v>
       </c>
       <c r="D891" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E891">
         <v>1.274876169934136</v>
@@ -46471,7 +46474,7 @@
         <v>1.495171012594845</v>
       </c>
       <c r="D892" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E892">
         <v>1.274876169934136</v>
@@ -46571,7 +46574,7 @@
         <v>1.49050375652243</v>
       </c>
       <c r="D894" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E894">
         <v>1.277284950855655</v>
@@ -46621,7 +46624,7 @@
         <v>1.497416698974804</v>
       </c>
       <c r="D895" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E895">
         <v>1.277284950855655</v>
@@ -46721,7 +46724,7 @@
         <v>1.508128402761513</v>
       </c>
       <c r="D897" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E897">
         <v>1.296295805225902</v>
@@ -46771,7 +46774,7 @@
         <v>1.515140360080398</v>
       </c>
       <c r="D898" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E898">
         <v>1.296295805225902</v>
@@ -46871,7 +46874,7 @@
         <v>1.51528028529547</v>
       </c>
       <c r="D900" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E900">
         <v>1.304010195374889</v>
@@ -46921,7 +46924,7 @@
         <v>1.452891679611439</v>
       </c>
       <c r="D901" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E901">
         <v>1.304010195374889</v>
@@ -47207,7 +47210,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47221,7 +47224,7 @@
         <v>1.771438143096434</v>
       </c>
       <c r="D907" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E907">
         <v>1.769334769083512</v>
@@ -47257,7 +47260,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47271,7 +47274,7 @@
         <v>1.793666905958362</v>
       </c>
       <c r="D908" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E908">
         <v>1.769334769083512</v>
@@ -47307,7 +47310,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47371,7 +47374,7 @@
         <v>1.811874519598647</v>
       </c>
       <c r="D910" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E910">
         <v>1.900918826425524</v>
@@ -47421,7 +47424,7 @@
         <v>1.834912009990619</v>
       </c>
       <c r="D911" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E911">
         <v>1.900918826425524</v>
@@ -47521,7 +47524,7 @@
         <v>1.895528965493513</v>
       </c>
       <c r="D913" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E913">
         <v>1.932861573643335</v>
@@ -47571,7 +47574,7 @@
         <v>1.920239544803383</v>
       </c>
       <c r="D914" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E914">
         <v>1.932861573643335</v>
@@ -47657,7 +47660,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -47671,7 +47674,7 @@
         <v>2.14694519285309</v>
       </c>
       <c r="D916" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E916">
         <v>2.227783075723198</v>
@@ -47707,7 +47710,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -47721,7 +47724,7 @@
         <v>2.127521979580261</v>
       </c>
       <c r="D917" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E917">
         <v>2.227783075723198</v>
@@ -47757,7 +47760,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47771,7 +47774,7 @@
         <v>2.083648255813952</v>
       </c>
       <c r="D918" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E918">
         <v>2.227783075723198</v>
@@ -47807,7 +47810,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -47871,7 +47874,7 @@
         <v>2.161847691918457</v>
       </c>
       <c r="D920" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E920">
         <v>2.29633267654658</v>
@@ -47921,7 +47924,7 @@
         <v>2.142803814985473</v>
       </c>
       <c r="D921" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E921">
         <v>2.29633267654658</v>
@@ -47971,7 +47974,7 @@
         <v>2.099201045747626</v>
       </c>
       <c r="D922" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E922">
         <v>2.29633267654658</v>
@@ -48057,7 +48060,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48107,7 +48110,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48157,7 +48160,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48207,7 +48210,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48221,7 +48224,7 @@
         <v>2.281990200644458</v>
       </c>
       <c r="D927" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E927">
         <v>2.416557544639771</v>
@@ -48257,7 +48260,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48271,7 +48274,7 @@
         <v>2.266004496660863</v>
       </c>
       <c r="D928" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E928">
         <v>2.416557544639771</v>
@@ -48307,7 +48310,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48321,7 +48324,7 @@
         <v>2.22458613667258</v>
       </c>
       <c r="D929" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E929">
         <v>2.416557544639771</v>
@@ -48357,7 +48360,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48621,7 +48624,7 @@
         <v>2.294610334852642</v>
       </c>
       <c r="D935" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E935">
         <v>2.429085896053713</v>
@@ -48671,7 +48674,7 @@
         <v>2.278945870648891</v>
       </c>
       <c r="D936" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E936">
         <v>2.429085896053713</v>
@@ -48721,7 +48724,7 @@
         <v>2.237756967646212</v>
       </c>
       <c r="D937" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E937">
         <v>2.429085896053713</v>
@@ -48771,7 +48774,7 @@
         <v>1.478865024995372</v>
       </c>
       <c r="D938" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E938">
         <v>1.091736715423069</v>
@@ -48821,7 +48824,7 @@
         <v>1.38490187002407</v>
       </c>
       <c r="D939" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E939">
         <v>1.556095167561563</v>
@@ -48871,7 +48874,7 @@
         <v>1.411000217357541</v>
       </c>
       <c r="D940" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E940">
         <v>1.026647048618012</v>
@@ -48921,7 +48924,7 @@
         <v>1.329020625073216</v>
       </c>
       <c r="D941" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E941">
         <v>1.617052203789723</v>
@@ -48971,7 +48974,7 @@
         <v>1.335000528139656</v>
       </c>
       <c r="D942" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E942">
         <v>0.9537551533830149</v>
@@ -49021,7 +49024,7 @@
         <v>1.274396341734775</v>
       </c>
       <c r="D943" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E943">
         <v>1.498550586395873</v>
@@ -49071,7 +49074,7 @@
         <v>1.286901151623061</v>
       </c>
       <c r="D944" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E944">
         <v>0.9076226658689572</v>
@@ -49121,7 +49124,7 @@
         <v>1.247256712491893</v>
       </c>
       <c r="D945" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E945">
         <v>1.441230237098444</v>
@@ -49171,7 +49174,7 @@
         <v>1.233587671663713</v>
       </c>
       <c r="D946" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E946">
         <v>0.8564892910380584</v>
@@ -49221,7 +49224,7 @@
         <v>1.211322305183469</v>
       </c>
       <c r="D947" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E947">
         <v>1.391965348904197</v>
@@ -49271,7 +49274,7 @@
         <v>1.21037766405574</v>
       </c>
       <c r="D948" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E948">
         <v>0.8342283915478834</v>
@@ -49321,7 +49324,7 @@
         <v>1.192426425383669</v>
       </c>
       <c r="D949" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E949">
         <v>1.2587927643563</v>
@@ -49371,7 +49374,7 @@
         <v>1.194808180139088</v>
       </c>
       <c r="D950" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E950">
         <v>0.8192955779772646</v>
@@ -49421,7 +49424,7 @@
         <v>1.198498033457667</v>
       </c>
       <c r="D951" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E951">
         <v>1.158999179108742</v>
@@ -49471,7 +49474,7 @@
         <v>1.182088322901234</v>
       </c>
       <c r="D952" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E952">
         <v>0.8070958636004386</v>
@@ -49571,7 +49574,7 @@
         <v>1.320193729932789</v>
       </c>
       <c r="D954" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E954">
         <v>0.7970809127030485</v>
@@ -49621,7 +49624,7 @@
         <v>1.179856657365155</v>
       </c>
       <c r="D955" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E955">
         <v>1.189234093919208</v>
@@ -49671,7 +49674,7 @@
         <v>1.227366403581364</v>
       </c>
       <c r="D956" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E956">
         <v>1.189234093919208</v>
@@ -49721,7 +49724,7 @@
         <v>1.310478356163625</v>
       </c>
       <c r="D957" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E957">
         <v>0.7876399845205837</v>
@@ -49771,7 +49774,7 @@
         <v>0.6344231633251383</v>
       </c>
       <c r="D958" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E958">
         <v>0.9193140943676656</v>
@@ -49821,7 +49824,7 @@
         <v>1.171934328095761</v>
       </c>
       <c r="D959" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E959">
         <v>1.093069676752978</v>
@@ -49871,7 +49874,7 @@
         <v>1.219663630781329</v>
       </c>
       <c r="D960" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E960">
         <v>1.093069676752978</v>
@@ -49921,7 +49924,7 @@
         <v>1.353847387031876</v>
       </c>
       <c r="D961" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E961">
         <v>0.8297839015225001</v>
@@ -49971,7 +49974,7 @@
         <v>0.6751786179452095</v>
       </c>
       <c r="D962" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E962">
         <v>0.9775934449943753</v>
@@ -50021,7 +50024,7 @@
         <v>1.245944786534167</v>
       </c>
       <c r="D963" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E963">
         <v>1.097570180737918</v>
@@ -50071,7 +50074,7 @@
         <v>1.254048493296459</v>
       </c>
       <c r="D964" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E964">
         <v>1.097570180737918</v>
@@ -50121,7 +50124,7 @@
         <v>3.119396810901764</v>
       </c>
       <c r="D965" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E965">
         <v>2.981001707605099</v>
@@ -50171,7 +50174,7 @@
         <v>3.159377089407229</v>
       </c>
       <c r="D966" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E966">
         <v>2.981001707605099</v>
@@ -50221,7 +50224,7 @@
         <v>3.120981986110565</v>
       </c>
       <c r="D967" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E967">
         <v>2.981001707605099</v>
@@ -50321,7 +50324,7 @@
         <v>2.837870800176567</v>
       </c>
       <c r="D969" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E969">
         <v>2.894132615033631</v>
@@ -50371,7 +50374,7 @@
         <v>2.879396810901763</v>
       </c>
       <c r="D970" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E970">
         <v>2.894132615033631</v>
@@ -50421,7 +50424,7 @@
         <v>3.139316734249427</v>
       </c>
       <c r="D971" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E971">
         <v>2.958809334024729</v>
@@ -50471,7 +50474,7 @@
         <v>3.085357479560983</v>
       </c>
       <c r="D972" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E972">
         <v>2.958809334024729</v>
@@ -50571,7 +50574,7 @@
         <v>2.814418597528316</v>
       </c>
       <c r="D974" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E974">
         <v>2.897121366001221</v>
@@ -50621,7 +50624,7 @@
         <v>2.858415811425125</v>
       </c>
       <c r="D975" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E975">
         <v>2.897121366001221</v>
@@ -50671,7 +50674,7 @@
         <v>3.109459846308594</v>
       </c>
       <c r="D976" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E976">
         <v>2.925779250264097</v>
@@ -50721,7 +50724,7 @@
         <v>3.053481285189368</v>
       </c>
       <c r="D977" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E977">
         <v>2.925779250264097</v>
@@ -50821,7 +50824,7 @@
         <v>2.77951344351053</v>
       </c>
       <c r="D979" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E979">
         <v>2.852045057017663</v>
@@ -50871,7 +50874,7 @@
         <v>2.827188679834833</v>
       </c>
       <c r="D980" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E980">
         <v>2.852045057017663</v>
@@ -50921,7 +50924,7 @@
         <v>3.01635970015435</v>
       </c>
       <c r="D981" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E981">
         <v>2.903149755514105</v>
@@ -51021,7 +51024,7 @@
         <v>2.75559930495377</v>
       </c>
       <c r="D983" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E983">
         <v>2.855417565754478</v>
@@ -51071,7 +51074,7 @@
         <v>2.805794419514426</v>
       </c>
       <c r="D984" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E984">
         <v>2.855417565754478</v>
@@ -51321,7 +51324,7 @@
         <v>2.647424121190128</v>
       </c>
       <c r="D989" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E989">
         <v>2.713888571480405</v>
@@ -51371,7 +51374,7 @@
         <v>2.709017860486209</v>
       </c>
       <c r="D990" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E990">
         <v>2.713888571480405</v>
@@ -51421,7 +51424,7 @@
         <v>2.709276438497821</v>
       </c>
       <c r="D991" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E991">
         <v>2.713888571480405</v>
@@ -51821,7 +51824,7 @@
         <v>2.507960672292075</v>
       </c>
       <c r="D999" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E999">
         <v>2.634810324051362</v>
@@ -51871,7 +51874,7 @@
         <v>2.480590741940218</v>
       </c>
       <c r="D1000" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E1000">
         <v>2.521446129036562</v>
@@ -51921,7 +51924,7 @@
         <v>2.525024170825448</v>
       </c>
       <c r="D1001" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E1001">
         <v>2.521446129036562</v>
@@ -51971,7 +51974,7 @@
         <v>2.374355272751924</v>
       </c>
       <c r="D1002" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E1002">
         <v>2.508178066449632</v>
@@ -52121,7 +52124,7 @@
         <v>2.297264431187501</v>
       </c>
       <c r="D1005" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E1005">
         <v>2.435110755238258</v>
@@ -52171,7 +52174,7 @@
         <v>2.26769516637735</v>
       </c>
       <c r="D1006" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E1006">
         <v>2.422957079289015</v>
@@ -52321,7 +52324,7 @@
         <v>2.219172623318876</v>
       </c>
       <c r="D1009" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E1009">
         <v>2.361094720222901</v>
@@ -52371,7 +52374,7 @@
         <v>2.188788203938071</v>
       </c>
       <c r="D1010" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E1010">
         <v>2.345170584879249</v>
@@ -52421,7 +52424,7 @@
         <v>2.193248487975224</v>
       </c>
       <c r="D1011" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E1011">
         <v>2.145170584879249</v>
@@ -52471,7 +52474,7 @@
         <v>2.244786165498444</v>
       </c>
       <c r="D1012" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E1012">
         <v>2.145170584879249</v>
@@ -52521,7 +52524,7 @@
         <v>2.139178489138268</v>
       </c>
       <c r="D1013" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E1013">
         <v>2.285275645237524</v>
@@ -52571,7 +52574,7 @@
         <v>2.107959057918417</v>
       </c>
       <c r="D1014" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E1014">
         <v>2.27386057382472</v>
@@ -52621,7 +52624,7 @@
         <v>2.117763417725465</v>
       </c>
       <c r="D1015" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E1015">
         <v>2.06381166377648</v>
@@ -52671,7 +52674,7 @@
         <v>2.156397256360898</v>
       </c>
       <c r="D1016" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E1016">
         <v>2.06381166377648</v>
@@ -52721,7 +52724,7 @@
         <v>2.057977785544642</v>
       </c>
       <c r="D1017" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E1017">
         <v>2.208312974190537</v>
@@ -52771,7 +52774,7 @@
         <v>2.273206827011388</v>
       </c>
       <c r="D1018" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E1018">
         <v>2.138737562907135</v>
@@ -52821,7 +52824,7 @@
         <v>2.025910747815463</v>
       </c>
       <c r="D1019" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E1019">
         <v>2.201474977928105</v>
@@ -52871,7 +52874,7 @@
         <v>2.04113978928221</v>
       </c>
       <c r="D1020" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E1020">
         <v>2.069195645840627</v>
@@ -52921,7 +52924,7 @@
         <v>2.08299453265309</v>
       </c>
       <c r="D1021" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E1021">
         <v>2.069195645840627</v>
@@ -52971,7 +52974,7 @@
         <v>1.942015135643571</v>
       </c>
       <c r="D1022" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E1022">
         <v>2.098402654660086</v>
@@ -53021,7 +53024,7 @@
         <v>2.154957662266692</v>
       </c>
       <c r="D1023" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E1023">
         <v>2.02204863336159</v>
@@ -53071,7 +53074,7 @@
         <v>2.151713656181408</v>
       </c>
       <c r="D1024" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E1024">
         <v>2.02204863336159</v>
@@ -53121,7 +53124,7 @@
         <v>1.968838124994323</v>
       </c>
       <c r="D1025" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E1025">
         <v>2.061613163027353</v>
@@ -53171,7 +53174,7 @@
         <v>1.931713656181408</v>
       </c>
       <c r="D1026" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E1026">
         <v>2.044455196496419</v>
@@ -53221,7 +53224,7 @@
         <v>1.918201668351977</v>
       </c>
       <c r="D1027" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E1027">
         <v>2.044455196496419</v>
@@ -53271,7 +53274,7 @@
         <v>2.558838698778969</v>
       </c>
       <c r="D1028" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E1028">
         <v>2.418783335811877</v>
@@ -53321,7 +53324,7 @@
         <v>2.549888393340562</v>
       </c>
       <c r="D1029" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E1029">
         <v>2.418783335811877</v>
@@ -53371,7 +53374,7 @@
         <v>2.349004347317614</v>
       </c>
       <c r="D1030" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E1030">
         <v>2.458617687273231</v>
@@ -53421,7 +53424,7 @@
         <v>2.342871828486698</v>
       </c>
       <c r="D1031" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E1031">
         <v>2.213976886015383</v>
@@ -53471,7 +53474,7 @@
         <v>2.314805569071239</v>
       </c>
       <c r="D1032" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E1032">
         <v>2.213976886015383</v>
@@ -53521,7 +53524,7 @@
         <v>2.286739309655781</v>
       </c>
       <c r="D1033" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E1033">
         <v>2.213976886015383</v>
@@ -53621,7 +53624,7 @@
         <v>1.815102844953163</v>
       </c>
       <c r="D1035" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E1035">
         <v>1.753015209992995</v>
@@ -53671,7 +53674,7 @@
         <v>1.683711088313052</v>
       </c>
       <c r="D1036" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E1036">
         <v>1.760987732126702</v>
@@ -53721,7 +53724,7 @@
         <v>1.801047889220578</v>
       </c>
       <c r="D1037" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E1037">
         <v>1.751743767540634</v>
@@ -53771,7 +53774,7 @@
         <v>1.800034150287431</v>
       </c>
       <c r="D1038" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E1038">
         <v>1.751743767540634</v>
@@ -53821,7 +53824,7 @@
         <v>1.708960254260409</v>
       </c>
       <c r="D1039" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E1039">
         <v>1.756554758687151</v>
@@ -53871,10 +53874,10 @@
         <v>1.706554758687151</v>
       </c>
       <c r="D1040" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1040">
-        <v>1.727946515327263</v>
+        <v>1.74275750647378</v>
       </c>
       <c r="F1040">
         <v>1</v>
@@ -53883,10 +53886,10 @@
         <v>0.00627344524131285</v>
       </c>
       <c r="H1040">
-        <v>0.006212053484672737</v>
+        <v>0.006337242493526221</v>
       </c>
       <c r="I1040">
-        <v>0.02139175664011228</v>
+        <v>0.03620274778662891</v>
       </c>
       <c r="J1040">
         <v>0.6898626106685345</v>
@@ -53898,10 +53901,10 @@
         <v>3.99</v>
       </c>
       <c r="M1040">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1040">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1040">
         <v>1</v>
@@ -53921,10 +53924,10 @@
         <v>1.706554758687151</v>
       </c>
       <c r="D1041" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1041">
-        <v>1.727946515327263</v>
+        <v>1.74275750647378</v>
       </c>
       <c r="F1041">
         <v>1</v>
@@ -53933,10 +53936,10 @@
         <v>0.00627344524131285</v>
       </c>
       <c r="H1041">
-        <v>0.006212053484672737</v>
+        <v>0.006337242493526221</v>
       </c>
       <c r="I1041">
-        <v>0.02139175664011228</v>
+        <v>0.03620274778662891</v>
       </c>
       <c r="J1041">
         <v>0.6898626106685345</v>
@@ -53948,10 +53951,10 @@
         <v>3.99</v>
       </c>
       <c r="M1041">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1041">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1041">
         <v>1</v>
@@ -53971,7 +53974,7 @@
         <v>1.774652822327312</v>
       </c>
       <c r="D1042" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E1042">
         <v>1.711570514679623</v>
@@ -54021,7 +54024,7 @@
         <v>1.642597950562186</v>
       </c>
       <c r="D1043" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E1043">
         <v>1.721753420563377</v>
@@ -54071,7 +54074,7 @@
         <v>1.757918035858755</v>
       </c>
       <c r="D1044" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1044">
         <v>1.69193632644713</v>
@@ -54121,7 +54124,7 @@
         <v>1.760064360565757</v>
       </c>
       <c r="D1045" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1045">
         <v>1.69193632644713</v>
@@ -54171,7 +54174,7 @@
         <v>1.758100941742508</v>
       </c>
       <c r="D1046" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1046">
         <v>1.69193632644713</v>
@@ -54221,7 +54224,7 @@
         <v>1.671936326447129</v>
       </c>
       <c r="D1047" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E1047">
         <v>1.719972907623881</v>
@@ -54271,10 +54274,10 @@
         <v>1.669972907623881</v>
       </c>
       <c r="D1048" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1048">
-        <v>1.692027779389007</v>
+        <v>1.705954617035505</v>
       </c>
       <c r="F1048">
         <v>1</v>
@@ -54283,10 +54286,10 @@
         <v>0.006310027092376119</v>
       </c>
       <c r="H1048">
-        <v>0.006247972220610993</v>
+        <v>0.006374045382964494</v>
       </c>
       <c r="I1048">
-        <v>0.02205487176512566</v>
+        <v>0.03598170941162415</v>
       </c>
       <c r="J1048">
         <v>0.7009145294187672</v>
@@ -54298,10 +54301,10 @@
         <v>3.99</v>
       </c>
       <c r="M1048">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1048">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1048">
         <v>1</v>
@@ -54321,10 +54324,10 @@
         <v>1.669972907623881</v>
       </c>
       <c r="D1049" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1049">
-        <v>1.692027779389007</v>
+        <v>1.705954617035505</v>
       </c>
       <c r="F1049">
         <v>1</v>
@@ -54333,10 +54336,10 @@
         <v>0.006310027092376119</v>
       </c>
       <c r="H1049">
-        <v>0.006247972220610993</v>
+        <v>0.006374045382964494</v>
       </c>
       <c r="I1049">
-        <v>0.02205487176512566</v>
+        <v>0.03598170941162415</v>
       </c>
       <c r="J1049">
         <v>0.7009145294187672</v>
@@ -54348,10 +54351,10 @@
         <v>3.99</v>
       </c>
       <c r="M1049">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1049">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1049">
         <v>1</v>
@@ -54371,7 +54374,7 @@
         <v>1.745068418380975</v>
       </c>
       <c r="D1050" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E1050">
         <v>1.681258625390344</v>
@@ -54421,7 +54424,7 @@
         <v>1.612528556387221</v>
       </c>
       <c r="D1051" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E1051">
         <v>1.581258625390344</v>
@@ -54471,7 +54474,7 @@
         <v>1.730677751350789</v>
       </c>
       <c r="D1052" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1052">
         <v>1.664857705348707</v>
@@ -54521,7 +54524,7 @@
         <v>1.732477291329971</v>
       </c>
       <c r="D1053" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1053">
         <v>1.664857705348707</v>
@@ -54571,10 +54574,10 @@
         <v>1.643217613344544</v>
       </c>
       <c r="D1054" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1054">
-        <v>1.665757475338299</v>
+        <v>1.679037659346625</v>
       </c>
       <c r="F1054">
         <v>1</v>
@@ -54583,10 +54586,10 @@
         <v>0.006336782386655457</v>
       </c>
       <c r="H1054">
-        <v>0.006274242524661702</v>
+        <v>0.006400962340653375</v>
       </c>
       <c r="I1054">
-        <v>0.02253986199375468</v>
+        <v>0.03582004600208144</v>
       </c>
       <c r="J1054">
         <v>0.7089976998959082</v>
@@ -54598,10 +54601,10 @@
         <v>3.99</v>
       </c>
       <c r="M1054">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1054">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -54621,10 +54624,10 @@
         <v>1.643217613344544</v>
       </c>
       <c r="D1055" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1055">
-        <v>1.665757475338299</v>
+        <v>1.679037659346625</v>
       </c>
       <c r="F1055">
         <v>1</v>
@@ -54633,10 +54636,10 @@
         <v>0.006336782386655457</v>
       </c>
       <c r="H1055">
-        <v>0.006274242524661702</v>
+        <v>0.006400962340653375</v>
       </c>
       <c r="I1055">
-        <v>0.02253986199375468</v>
+        <v>0.03582004600208144</v>
       </c>
       <c r="J1055">
         <v>0.7089976998959082</v>
@@ -54648,10 +54651,10 @@
         <v>3.99</v>
       </c>
       <c r="M1055">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1055">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -54671,7 +54674,7 @@
         <v>1.725336643125503</v>
       </c>
       <c r="D1056" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E1056">
         <v>1.661041642546622</v>
@@ -54721,7 +54724,7 @@
         <v>1.592473309406249</v>
       </c>
       <c r="D1057" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E1057">
         <v>1.561041642546622</v>
@@ -54771,7 +54774,7 @@
         <v>1.712509422768564</v>
       </c>
       <c r="D1058" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1058">
         <v>1.646797200674982</v>
@@ -54821,7 +54824,7 @@
         <v>1.715387201832744</v>
       </c>
       <c r="D1059" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1059">
         <v>1.646797200674982</v>
@@ -54871,7 +54874,7 @@
         <v>1.706714139491356</v>
       </c>
       <c r="D1060" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E1060">
         <v>1.641961208495242</v>
@@ -54921,7 +54924,7 @@
         <v>1.57354551882728</v>
       </c>
       <c r="D1061" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E1061">
         <v>1.541961208495242</v>
@@ -54971,7 +54974,7 @@
         <v>1.695362472701057</v>
       </c>
       <c r="D1062" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1062">
         <v>1.629752012922416</v>
@@ -55021,7 +55024,7 @@
         <v>1.699257874914645</v>
       </c>
       <c r="D1063" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1063">
         <v>1.629752012922416</v>
@@ -55071,7 +55074,7 @@
         <v>1.687585123258323</v>
       </c>
       <c r="D1064" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E1064">
         <v>1.622361806617135</v>
@@ -55121,10 +55124,10 @@
         <v>1.554102912164197</v>
       </c>
       <c r="D1065" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E1065">
-        <v>1.637302510264221</v>
+        <v>1.522361806617135</v>
       </c>
       <c r="F1065">
         <v>1</v>
@@ -55133,10 +55136,10 @@
         <v>0.006945897087835803</v>
       </c>
       <c r="H1065">
-        <v>0.00678269748973578</v>
+        <v>0.006957638193382866</v>
       </c>
       <c r="I1065">
-        <v>0.08319959810002331</v>
+        <v>-0.03174110554706244</v>
       </c>
       <c r="J1065">
         <v>0.7247035182354308</v>
@@ -55148,10 +55151,10 @@
         <v>4.25</v>
       </c>
       <c r="M1065">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N1065">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="O1065">
         <v>1</v>
@@ -55171,7 +55174,7 @@
         <v>1.677749143546598</v>
       </c>
       <c r="D1066" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1066">
         <v>1.612243213911307</v>
@@ -55221,7 +55224,7 @@
         <v>1.682689847193684</v>
       </c>
       <c r="D1067" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1067">
         <v>1.612243213911307</v>
@@ -55271,7 +55274,7 @@
         <v>1.674071021437449</v>
       </c>
       <c r="D1068" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E1068">
         <v>1.608515390817058</v>
@@ -55321,7 +55324,7 @@
         <v>1.540367267690522</v>
       </c>
       <c r="D1069" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E1069">
         <v>1.624194569973482</v>
@@ -55371,7 +55374,7 @@
         <v>1.665305831214263</v>
       </c>
       <c r="D1070" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1070">
         <v>1.599873749129906</v>
@@ -55421,7 +55424,7 @@
         <v>1.670985010370687</v>
       </c>
       <c r="D1071" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1071">
         <v>1.599873749129906</v>
@@ -55471,7 +55474,7 @@
         <v>1.525149479713785</v>
       </c>
       <c r="D1072" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E1072">
         <v>1.609672218544069</v>
@@ -55521,7 +55524,7 @@
         <v>1.65151982436437</v>
       </c>
       <c r="D1073" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1073">
         <v>1.586169558344404</v>
@@ -55571,7 +55574,7 @@
         <v>1.658017164164704</v>
       </c>
       <c r="D1074" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1074">
         <v>1.586169558344404</v>
@@ -55621,7 +55624,7 @@
         <v>1.515332066574131</v>
       </c>
       <c r="D1075" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E1075">
         <v>1.600303450628539</v>
@@ -55657,7 +55660,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55671,7 +55674,7 @@
         <v>1.6426260925685</v>
       </c>
       <c r="D1076" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1076">
         <v>1.577328608339607</v>
@@ -55707,7 +55710,7 @@
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
@@ -55721,7 +55724,7 @@
         <v>1.649651250279569</v>
       </c>
       <c r="D1077" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1077">
         <v>1.577328608339607</v>
@@ -55757,7 +55760,7 @@
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1078" spans="1:16">
@@ -55771,7 +55774,7 @@
         <v>1.631729592152544</v>
       </c>
       <c r="D1078" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1078">
         <v>1.566496775581906</v>
@@ -55821,7 +55824,7 @@
         <v>1.639401426446162</v>
       </c>
       <c r="D1079" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1079">
         <v>1.566496775581906</v>
@@ -55871,7 +55874,7 @@
         <v>1.612906122499548</v>
       </c>
       <c r="D1080" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1080">
         <v>1.547785017914981</v>
@@ -55921,7 +55924,7 @@
         <v>1.621695076653878</v>
       </c>
       <c r="D1081" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1081">
         <v>1.547785017914981</v>
@@ -55971,7 +55974,7 @@
         <v>1.597836465352172</v>
       </c>
       <c r="D1082" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1082">
         <v>1.532804794934651</v>
@@ -56007,7 +56010,7 @@
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
@@ -56021,7 +56024,7 @@
         <v>1.607519761176969</v>
       </c>
       <c r="D1083" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1083">
         <v>1.532804794934651</v>
@@ -56057,7 +56060,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56071,7 +56074,7 @@
         <v>1.561584032990916</v>
       </c>
       <c r="D1084" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1084">
         <v>1.496767510539931</v>
@@ -56121,7 +56124,7 @@
         <v>1.573418808481069</v>
       </c>
       <c r="D1085" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1085">
         <v>1.496767510539931</v>
@@ -56171,7 +56174,7 @@
         <v>1.47676751053993</v>
       </c>
       <c r="D1086" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E1086">
         <v>1.527134465637961</v>
@@ -56221,10 +56224,10 @@
         <v>1.477134465637961</v>
       </c>
       <c r="D1087" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1087">
-        <v>1.502684898285008</v>
+        <v>1.511950988088946</v>
       </c>
       <c r="F1087">
         <v>1</v>
@@ -56233,10 +56236,10 @@
         <v>0.006502865534362039</v>
       </c>
       <c r="H1087">
-        <v>0.006437315101714993</v>
+        <v>0.006568049011911054</v>
       </c>
       <c r="I1087">
-        <v>0.02555043264704615</v>
+        <v>0.03481652245098488</v>
       </c>
       <c r="J1087">
         <v>0.7591738774507669</v>
@@ -56248,10 +56251,10 @@
         <v>3.99</v>
       </c>
       <c r="M1087">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1087">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56271,10 +56274,10 @@
         <v>1.477134465637961</v>
       </c>
       <c r="D1088" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1088">
-        <v>1.502684898285008</v>
+        <v>1.511950988088946</v>
       </c>
       <c r="F1088">
         <v>1</v>
@@ -56283,10 +56286,10 @@
         <v>0.006502865534362039</v>
       </c>
       <c r="H1088">
-        <v>0.006437315101714993</v>
+        <v>0.006568049011911054</v>
       </c>
       <c r="I1088">
-        <v>0.02555043264704615</v>
+        <v>0.03481652245098488</v>
       </c>
       <c r="J1088">
         <v>0.7591738774507669</v>
@@ -56298,10 +56301,10 @@
         <v>3.99</v>
       </c>
       <c r="M1088">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1088">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1088">
         <v>1</v>
@@ -56321,7 +56324,7 @@
         <v>1.546913833631819</v>
       </c>
       <c r="D1089" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1089">
         <v>1.482184374678515</v>
@@ -56371,7 +56374,7 @@
         <v>1.559619244098773</v>
       </c>
       <c r="D1090" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1090">
         <v>1.482184374678515</v>
@@ -56421,7 +56424,7 @@
         <v>1.462184374678514</v>
       </c>
       <c r="D1091" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E1091">
         <v>1.512725456771905</v>
@@ -56471,10 +56474,10 @@
         <v>1.462725456771905</v>
       </c>
       <c r="D1092" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1092">
-        <v>1.488537079911992</v>
+        <v>1.49745491572521</v>
       </c>
       <c r="F1092">
         <v>1</v>
@@ -56483,10 +56486,10 @@
         <v>0.006517274543228095</v>
       </c>
       <c r="H1092">
-        <v>0.006451462920088009</v>
+        <v>0.006582545084274791</v>
       </c>
       <c r="I1092">
-        <v>0.02581162314008623</v>
+        <v>0.03472945895330426</v>
       </c>
       <c r="J1092">
         <v>0.7635270523347718</v>
@@ -56498,10 +56501,10 @@
         <v>3.99</v>
       </c>
       <c r="M1092">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1092">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1092">
         <v>1</v>
@@ -56521,7 +56524,7 @@
         <v>1.538925476235883</v>
       </c>
       <c r="D1093" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1093">
         <v>1.474243425931813</v>
@@ -56557,7 +56560,7 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
@@ -56571,7 +56574,7 @@
         <v>1.552104973195178</v>
       </c>
       <c r="D1094" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1094">
         <v>1.474243425931813</v>
@@ -56607,7 +56610,7 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
@@ -56621,10 +56624,10 @@
         <v>1.454243425931812</v>
       </c>
       <c r="D1095" t="s">
-        <v>231</v>
+        <v>376</v>
       </c>
       <c r="E1095">
-        <v>1.505515224715531</v>
+        <v>1.504879325323672</v>
       </c>
       <c r="F1095">
         <v>1</v>
@@ -56633,10 +56636,10 @@
         <v>0.006585756574068187</v>
       </c>
       <c r="H1095">
-        <v>0.00651448477528447</v>
+        <v>0.006575120674676328</v>
       </c>
       <c r="I1095">
-        <v>0.05127179878371813</v>
+        <v>0.05063589939185942</v>
       </c>
       <c r="J1095">
         <v>0.7658974847964738</v>
@@ -56648,16 +56651,16 @@
         <v>4.02</v>
       </c>
       <c r="M1095">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="N1095">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="O1095">
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -56671,10 +56674,10 @@
         <v>1.454879325323672</v>
       </c>
       <c r="D1096" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1096">
-        <v>1.48083317441146</v>
+        <v>1.489561375627742</v>
       </c>
       <c r="F1096">
         <v>1</v>
@@ -56683,10 +56686,10 @@
         <v>0.006525120674676328</v>
       </c>
       <c r="H1096">
-        <v>0.00645916682558854</v>
+        <v>0.006590438624372258</v>
       </c>
       <c r="I1096">
-        <v>0.02595384908778842</v>
+        <v>0.03468205030407034</v>
       </c>
       <c r="J1096">
         <v>0.7658974847964738</v>
@@ -56698,16 +56701,16 @@
         <v>3.99</v>
       </c>
       <c r="M1096">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1096">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1096">
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
@@ -56721,7 +56724,7 @@
         <v>1.533762485471971</v>
       </c>
       <c r="D1097" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1097">
         <v>1.469111076062641</v>
@@ -56771,7 +56774,7 @@
         <v>1.547248391378679</v>
       </c>
       <c r="D1098" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1098">
         <v>1.469111076062641</v>
@@ -56821,10 +56824,10 @@
         <v>1.449111076062641</v>
       </c>
       <c r="D1099" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E1099">
-        <v>1.50817973372066</v>
+        <v>1.500505438425324</v>
       </c>
       <c r="F1099">
         <v>1</v>
@@ -56833,10 +56836,10 @@
         <v>0.006590888923937359</v>
       </c>
       <c r="H1099">
-        <v>0.00651182026627934</v>
+        <v>0.006519494561574675</v>
       </c>
       <c r="I1099">
-        <v>0.05906865765801905</v>
+        <v>0.05139436236268358</v>
       </c>
       <c r="J1099">
         <v>0.7674295295335398</v>
@@ -56848,7 +56851,7 @@
         <v>4.02</v>
       </c>
       <c r="M1099">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="N1099">
         <v>4.01</v>
@@ -56871,10 +56874,10 @@
         <v>1.449808257243983</v>
       </c>
       <c r="D1100" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1100">
-        <v>1.475854029015996</v>
+        <v>1.484459666653312</v>
       </c>
       <c r="F1100">
         <v>1</v>
@@ -56883,10 +56886,10 @@
         <v>0.006530191742756017</v>
       </c>
       <c r="H1100">
-        <v>0.006464145970984004</v>
+        <v>0.006595540333346687</v>
       </c>
       <c r="I1100">
-        <v>0.02604577177201239</v>
+        <v>0.03465140940932887</v>
       </c>
       <c r="J1100">
         <v>0.7674295295335398</v>
@@ -56898,10 +56901,10 @@
         <v>3.99</v>
       </c>
       <c r="M1100">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1100">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1100">
         <v>1</v>
@@ -56921,7 +56924,7 @@
         <v>1.543319483815254</v>
       </c>
       <c r="D1101" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1101">
         <v>1.464959075956183</v>
@@ -57021,10 +57024,10 @@
         <v>1.445705833258199</v>
       </c>
       <c r="D1103" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1103">
-        <v>1.471825969211222</v>
+        <v>1.480332454607191</v>
       </c>
       <c r="F1103">
         <v>1</v>
@@ -57033,10 +57036,10 @@
         <v>0.006534294166741802</v>
       </c>
       <c r="H1103">
-        <v>0.006468174030788778</v>
+        <v>0.006599667545392809</v>
       </c>
       <c r="I1103">
-        <v>0.02612013595302365</v>
+        <v>0.03462662134899208</v>
       </c>
       <c r="J1103">
         <v>0.7686689325503931</v>
@@ -57048,10 +57051,10 @@
         <v>3.99</v>
       </c>
       <c r="M1103">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1103">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1103">
         <v>1</v>
@@ -57071,7 +57074,7 @@
         <v>1.543648446795206</v>
       </c>
       <c r="D1104" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1104">
         <v>1.465306718222064</v>
@@ -57121,7 +57124,7 @@
         <v>1.445306718222063</v>
       </c>
       <c r="D1105" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E1105">
         <v>1.496049324571651</v>
@@ -57171,10 +57174,10 @@
         <v>1.446049324571651</v>
       </c>
       <c r="D1106" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1106">
-        <v>1.472163234096032</v>
+        <v>1.480678021396857</v>
       </c>
       <c r="F1106">
         <v>1</v>
@@ -57183,10 +57186,10 @@
         <v>0.00653395067542835</v>
       </c>
       <c r="H1106">
-        <v>0.006467836765903968</v>
+        <v>0.006599321978603143</v>
       </c>
       <c r="I1106">
-        <v>0.0261139095243812</v>
+        <v>0.03462869682520608</v>
       </c>
       <c r="J1106">
         <v>0.7685651587396826</v>
@@ -57198,10 +57201,10 @@
         <v>3.99</v>
       </c>
       <c r="M1106">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1106">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1106">
         <v>1</v>
@@ -57221,7 +57224,7 @@
         <v>1.547028640320606</v>
       </c>
       <c r="D1107" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1107">
         <v>1.468878847026508</v>
@@ -57271,7 +57274,7 @@
         <v>1.448878847026507</v>
       </c>
       <c r="D1108" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E1108">
         <v>1.499578801091863</v>
@@ -57321,10 +57324,10 @@
         <v>1.449578801091863</v>
       </c>
       <c r="D1109" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1109">
-        <v>1.475628732189896</v>
+        <v>1.484228824059185</v>
       </c>
       <c r="F1109">
         <v>1</v>
@@ -57333,10 +57336,10 @@
         <v>0.006530421198908138</v>
       </c>
       <c r="H1109">
-        <v>0.006464371267810105</v>
+        <v>0.006595771175940815</v>
       </c>
       <c r="I1109">
-        <v>0.02604993109803289</v>
+        <v>0.03465002296732234</v>
       </c>
       <c r="J1109">
         <v>0.7674988516338783</v>
@@ -57348,10 +57351,10 @@
         <v>3.99</v>
       </c>
       <c r="M1109">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1109">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1109">
         <v>1</v>
@@ -57371,7 +57374,7 @@
         <v>1.54143940139528</v>
       </c>
       <c r="D1110" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1110">
         <v>1.462972238067567</v>
@@ -57421,7 +57424,7 @@
         <v>1.442972238067567</v>
       </c>
       <c r="D1111" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E1111">
         <v>1.493742718807059</v>
@@ -57471,10 +57474,10 @@
         <v>1.443742718807059</v>
       </c>
       <c r="D1112" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1112">
-        <v>1.469898439916297</v>
+        <v>1.478357478437313</v>
       </c>
       <c r="F1112">
         <v>1</v>
@@ -57483,10 +57486,10 @@
         <v>0.006536257281192942</v>
       </c>
       <c r="H1112">
-        <v>0.006470101560083704</v>
+        <v>0.006601642521562687</v>
       </c>
       <c r="I1112">
-        <v>0.02615572110923781</v>
+        <v>0.03461475963025418</v>
       </c>
       <c r="J1112">
         <v>0.7692620184872934</v>
@@ -57498,10 +57501,10 @@
         <v>3.99</v>
       </c>
       <c r="M1112">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1112">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1112">
         <v>1</v>
@@ -57521,7 +57524,7 @@
         <v>1.541874717879155</v>
       </c>
       <c r="D1113" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1113">
         <v>1.463432272837593</v>
@@ -57571,7 +57574,7 @@
         <v>1.443432272837593</v>
       </c>
       <c r="D1114" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E1114">
         <v>1.494197260624607</v>
@@ -57621,10 +57624,10 @@
         <v>1.444197260624607</v>
       </c>
       <c r="D1115" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1115">
-        <v>1.470344742305128</v>
+        <v>1.4788147667311</v>
       </c>
       <c r="F1115">
         <v>1</v>
@@ -57633,10 +57636,10 @@
         <v>0.006535802739375394</v>
       </c>
       <c r="H1115">
-        <v>0.006469655257694873</v>
+        <v>0.006601185233268901</v>
       </c>
       <c r="I1115">
-        <v>0.02614748168052117</v>
+        <v>0.03461750610649306</v>
       </c>
       <c r="J1115">
         <v>0.7691246946753454</v>
@@ -57648,10 +57651,10 @@
         <v>3.99</v>
       </c>
       <c r="M1115">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1115">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1115">
         <v>1</v>
@@ -57671,10 +57674,10 @@
         <v>1.444197260624607</v>
       </c>
       <c r="D1116" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1116">
-        <v>1.470344742305128</v>
+        <v>1.4788147667311</v>
       </c>
       <c r="F1116">
         <v>1</v>
@@ -57683,10 +57686,10 @@
         <v>0.006535802739375394</v>
       </c>
       <c r="H1116">
-        <v>0.006469655257694873</v>
+        <v>0.006601185233268901</v>
       </c>
       <c r="I1116">
-        <v>0.02614748168052117</v>
+        <v>0.03461750610649306</v>
       </c>
       <c r="J1116">
         <v>0.7691246946753454</v>
@@ -57698,10 +57701,10 @@
         <v>3.99</v>
       </c>
       <c r="M1116">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1116">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1116">
         <v>1</v>
@@ -57721,7 +57724,7 @@
         <v>1.531416807455531</v>
       </c>
       <c r="D1117" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1117">
         <v>1.452380537847327</v>
@@ -57757,7 +57760,7 @@
         <v>1</v>
       </c>
       <c r="P1117" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1118" spans="1:16">
@@ -57771,7 +57774,7 @@
         <v>1.432380537847326</v>
       </c>
       <c r="D1118" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E1118">
         <v>1.47327748664915</v>
@@ -57807,7 +57810,7 @@
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
@@ -57821,10 +57824,10 @@
         <v>1.43327748664915</v>
       </c>
       <c r="D1119" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1119">
-        <v>1.459622909851884</v>
+        <v>1.467829012248238</v>
       </c>
       <c r="F1119">
         <v>1</v>
@@ -57833,10 +57836,10 @@
         <v>0.006546722513350851</v>
       </c>
       <c r="H1119">
-        <v>0.006480377090148115</v>
+        <v>0.006612170987751762</v>
       </c>
       <c r="I1119">
-        <v>0.02634542320273425</v>
+        <v>0.03455152559908825</v>
       </c>
       <c r="J1119">
         <v>0.772423720045574</v>
@@ -57848,16 +57851,16 @@
         <v>3.99</v>
       </c>
       <c r="M1119">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1119">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1119">
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
@@ -57871,10 +57874,10 @@
         <v>1.43327748664915</v>
       </c>
       <c r="D1120" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1120">
-        <v>1.459622909851884</v>
+        <v>1.467829012248238</v>
       </c>
       <c r="F1120">
         <v>1</v>
@@ -57883,10 +57886,10 @@
         <v>0.006546722513350851</v>
       </c>
       <c r="H1120">
-        <v>0.006480377090148115</v>
+        <v>0.006612170987751762</v>
       </c>
       <c r="I1120">
-        <v>0.02634542320273425</v>
+        <v>0.03455152559908825</v>
       </c>
       <c r="J1120">
         <v>0.772423720045574</v>
@@ -57898,16 +57901,16 @@
         <v>3.99</v>
       </c>
       <c r="M1120">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1120">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1120">
         <v>1</v>
       </c>
       <c r="P1120" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1121" spans="1:16">
@@ -57921,7 +57924,7 @@
         <v>1.530293964951826</v>
       </c>
       <c r="D1121" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1121">
         <v>1.451193937725116</v>
@@ -57971,7 +57974,7 @@
         <v>1.431193937725116</v>
       </c>
       <c r="D1122" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E1122">
         <v>1.472105054886608</v>
@@ -58021,10 +58024,10 @@
         <v>1.432105054886608</v>
       </c>
       <c r="D1123" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1123">
-        <v>1.458471730628844</v>
+        <v>1.466649496305862</v>
       </c>
       <c r="F1123">
         <v>1</v>
@@ -58033,10 +58036,10 @@
         <v>0.006547894945113393</v>
       </c>
       <c r="H1123">
-        <v>0.006481528269371156</v>
+        <v>0.006613350503694138</v>
       </c>
       <c r="I1123">
-        <v>0.02636667574223672</v>
+        <v>0.03454444141925439</v>
       </c>
       <c r="J1123">
         <v>0.7727779290372787</v>
@@ -58048,10 +58051,10 @@
         <v>3.99</v>
       </c>
       <c r="M1123">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1123">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1123">
         <v>1</v>
@@ -58071,10 +58074,10 @@
         <v>1.432105054886608</v>
       </c>
       <c r="D1124" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1124">
-        <v>1.458471730628844</v>
+        <v>1.466649496305862</v>
       </c>
       <c r="F1124">
         <v>1</v>
@@ -58083,10 +58086,10 @@
         <v>0.006547894945113393</v>
       </c>
       <c r="H1124">
-        <v>0.006481528269371156</v>
+        <v>0.006613350503694138</v>
       </c>
       <c r="I1124">
-        <v>0.02636667574223672</v>
+        <v>0.03454444141925439</v>
       </c>
       <c r="J1124">
         <v>0.7727779290372787</v>
@@ -58098,10 +58101,10 @@
         <v>3.99</v>
       </c>
       <c r="M1124">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1124">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1124">
         <v>1</v>
@@ -58121,7 +58124,7 @@
         <v>1.432233461226324</v>
       </c>
       <c r="D1125" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E1125">
         <v>1.473132166166906</v>
@@ -58171,10 +58174,10 @@
         <v>1.433132166166906</v>
       </c>
       <c r="D1126" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1126">
-        <v>1.459480223577778</v>
+        <v>1.467682813696615</v>
       </c>
       <c r="F1126">
         <v>1</v>
@@ -58183,10 +58186,10 @@
         <v>0.006546867833833094</v>
       </c>
       <c r="H1126">
-        <v>0.006480519776422222</v>
+        <v>0.006612317186303385</v>
       </c>
       <c r="I1126">
-        <v>0.02634805741087209</v>
+        <v>0.03455064752970927</v>
       </c>
       <c r="J1126">
         <v>0.7724676235145299</v>
@@ -58198,10 +58201,10 @@
         <v>3.99</v>
       </c>
       <c r="M1126">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1126">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1126">
         <v>1</v>
@@ -58221,10 +58224,10 @@
         <v>1.433132166166906</v>
       </c>
       <c r="D1127" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1127">
-        <v>1.459480223577778</v>
+        <v>1.467682813696615</v>
       </c>
       <c r="F1127">
         <v>1</v>
@@ -58233,10 +58236,10 @@
         <v>0.006546867833833094</v>
       </c>
       <c r="H1127">
-        <v>0.006480519776422222</v>
+        <v>0.006612317186303385</v>
       </c>
       <c r="I1127">
-        <v>0.02634805741087209</v>
+        <v>0.03455064752970927</v>
       </c>
       <c r="J1127">
         <v>0.7724676235145299</v>
@@ -58248,10 +58251,10 @@
         <v>3.99</v>
       </c>
       <c r="M1127">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1127">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1127">
         <v>1</v>
@@ -58271,7 +58274,7 @@
         <v>1.438192457750358</v>
       </c>
       <c r="D1128" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E1128">
         <v>1.479020010493639</v>
@@ -58318,7 +58321,7 @@
         <v>230</v>
       </c>
       <c r="C1129">
-        <v>1.502968227794377</v>
+        <v>1.497554451422737</v>
       </c>
       <c r="D1129" t="s">
         <v>225</v>
@@ -58330,22 +58333,22 @@
         <v>-1</v>
       </c>
       <c r="G1129">
-        <v>0.006497031772205623</v>
+        <v>0.006522445548577263</v>
       </c>
       <c r="H1129">
         <v>0.006540979989506361</v>
       </c>
       <c r="I1129">
-        <v>0.06394821730073863</v>
+        <v>0.05853444092909887</v>
       </c>
       <c r="J1129">
         <v>0.7706888185819823</v>
       </c>
       <c r="K1129">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="L1129">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="M1129">
         <v>3.31</v>
@@ -58371,10 +58374,10 @@
         <v>1.439020010493639</v>
       </c>
       <c r="D1130" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1130">
-        <v>1.465261339608558</v>
+        <v>1.473606234121999</v>
       </c>
       <c r="F1130">
         <v>1</v>
@@ -58383,10 +58386,10 @@
         <v>0.006540979989506361</v>
       </c>
       <c r="H1130">
-        <v>0.006474738660391444</v>
+        <v>0.006606393765878002</v>
       </c>
       <c r="I1130">
-        <v>0.02624132911491905</v>
+        <v>0.03458622362836028</v>
       </c>
       <c r="J1130">
         <v>0.7706888185819823</v>
@@ -58398,10 +58401,10 @@
         <v>3.99</v>
       </c>
       <c r="M1130">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1130">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1130">
         <v>1</v>
@@ -58421,7 +58424,7 @@
         <v>1.442360905903367</v>
       </c>
       <c r="D1131" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E1131">
         <v>1.483138686131387</v>
@@ -58521,10 +58524,10 @@
         <v>1.443138686131387</v>
       </c>
       <c r="D1133" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1133">
-        <v>1.469305356473416</v>
+        <v>1.477749796017378</v>
       </c>
       <c r="F1133">
         <v>1</v>
@@ -58533,10 +58536,10 @@
         <v>0.006536861313868613</v>
       </c>
       <c r="H1133">
-        <v>0.006470694643526584</v>
+        <v>0.006602250203982623</v>
       </c>
       <c r="I1133">
-        <v>0.02616667034202935</v>
+        <v>0.03461110988599048</v>
       </c>
       <c r="J1133">
         <v>0.7694445057004873</v>
@@ -58548,10 +58551,10 @@
         <v>3.99</v>
       </c>
       <c r="M1133">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1133">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1133">
         <v>1</v>
@@ -58571,7 +58574,7 @@
         <v>1.442612807343595</v>
       </c>
       <c r="D1134" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E1134">
         <v>1.483387579793225</v>
@@ -58607,7 +58610,7 @@
         <v>1</v>
       </c>
       <c r="P1134" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="1135" spans="1:16">
@@ -58621,10 +58624,10 @@
         <v>1.443387579793225</v>
       </c>
       <c r="D1135" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1135">
-        <v>1.469549738467668</v>
+        <v>1.47800019356841</v>
       </c>
       <c r="F1135">
         <v>1</v>
@@ -58633,10 +58636,10 @@
         <v>0.006536612420206776</v>
       </c>
       <c r="H1135">
-        <v>0.006470450261532333</v>
+        <v>0.006601999806431591</v>
       </c>
       <c r="I1135">
-        <v>0.02616215867444316</v>
+        <v>0.03461261377518543</v>
       </c>
       <c r="J1135">
         <v>0.7693693112407177</v>
@@ -58648,16 +58651,16 @@
         <v>3.99</v>
       </c>
       <c r="M1135">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1135">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1135">
         <v>1</v>
       </c>
       <c r="P1135" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="1136" spans="1:16">
@@ -58671,10 +58674,10 @@
         <v>1.440857964887927</v>
       </c>
       <c r="D1136" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1136">
-        <v>1.467065977608992</v>
+        <v>1.475455293980905</v>
       </c>
       <c r="F1136">
         <v>1</v>
@@ -58683,10 +58686,10 @@
         <v>0.006539142035112073</v>
       </c>
       <c r="H1136">
-        <v>0.006472934022391009</v>
+        <v>0.006604544706019094</v>
       </c>
       <c r="I1136">
-        <v>0.02620801272106466</v>
+        <v>0.03459732909297797</v>
       </c>
       <c r="J1136">
         <v>0.7701335453510795</v>
@@ -58698,10 +58701,10 @@
         <v>3.99</v>
       </c>
       <c r="M1136">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1136">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1136">
         <v>1</v>
@@ -58771,10 +58774,10 @@
         <v>1.439221823572351</v>
       </c>
       <c r="D1138" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1138">
-        <v>1.465459494444151</v>
+        <v>1.473809266615084</v>
       </c>
       <c r="F1138">
         <v>1</v>
@@ -58783,10 +58786,10 @@
         <v>0.006540778176427649</v>
       </c>
       <c r="H1138">
-        <v>0.006474540505555849</v>
+        <v>0.006606190733384916</v>
       </c>
       <c r="I1138">
-        <v>0.0262376708718004</v>
+        <v>0.03458744304273331</v>
       </c>
       <c r="J1138">
         <v>0.770627847863338</v>
@@ -58798,10 +58801,10 @@
         <v>3.99</v>
       </c>
       <c r="M1138">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1138">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1138">
         <v>1</v>
@@ -58815,7 +58818,7 @@
         <v>0</v>
       </c>
       <c r="B1139" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C1139">
         <v>1.498375641177962</v>
@@ -58857,7 +58860,7 @@
         <v>1</v>
       </c>
       <c r="P1139" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="1140" spans="1:16">
@@ -58871,10 +58874,10 @@
         <v>1.439853795183759</v>
       </c>
       <c r="D1140" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1140">
-        <v>1.466080010376802</v>
+        <v>1.474445056786077</v>
       </c>
       <c r="F1140">
         <v>1</v>
@@ -58883,10 +58886,10 @@
         <v>0.006540146204816242</v>
       </c>
       <c r="H1140">
-        <v>0.006473919989623198</v>
+        <v>0.006605554943213923</v>
       </c>
       <c r="I1140">
-        <v>0.02622621519304369</v>
+        <v>0.03459126160231873</v>
       </c>
       <c r="J1140">
         <v>0.7704369198840608</v>
@@ -58898,16 +58901,16 @@
         <v>3.99</v>
       </c>
       <c r="M1140">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1140">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1140">
         <v>1</v>
       </c>
       <c r="P1140" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="1141" spans="1:16">
@@ -58915,7 +58918,7 @@
         <v>0</v>
       </c>
       <c r="B1141" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C1141">
         <v>1.500954835918747</v>
@@ -58971,10 +58974,10 @@
         <v>1.44247254812609</v>
       </c>
       <c r="D1142" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1142">
-        <v>1.468651293477279</v>
+        <v>1.477079633009027</v>
       </c>
       <c r="F1142">
         <v>1</v>
@@ -58983,10 +58986,10 @@
         <v>0.006537527451873911</v>
       </c>
       <c r="H1142">
-        <v>0.006471348706522722</v>
+        <v>0.006602920366990974</v>
       </c>
       <c r="I1142">
-        <v>0.02617874535118903</v>
+        <v>0.03460708488293696</v>
       </c>
       <c r="J1142">
         <v>0.7696457558531451</v>
@@ -58998,10 +59001,10 @@
         <v>3.99</v>
       </c>
       <c r="M1142">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1142">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1142">
         <v>1</v>
@@ -59015,7 +59018,7 @@
         <v>0</v>
       </c>
       <c r="B1143" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C1143">
         <v>1.500696441772847</v>
@@ -59057,7 +59060,7 @@
         <v>1</v>
       </c>
       <c r="P1143" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="1144" spans="1:16">
@@ -59071,10 +59074,10 @@
         <v>1.442210190879793</v>
       </c>
       <c r="D1144" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1144">
-        <v>1.468393691951458</v>
+        <v>1.47681569052257</v>
       </c>
       <c r="F1144">
         <v>1</v>
@@ -59083,10 +59086,10 @@
         <v>0.006537789809120208</v>
       </c>
       <c r="H1144">
-        <v>0.006471606308048543</v>
+        <v>0.00660318430947743</v>
       </c>
       <c r="I1144">
-        <v>0.02618350107166512</v>
+        <v>0.03460549964277781</v>
       </c>
       <c r="J1144">
         <v>0.7697250178610899</v>
@@ -59098,16 +59101,16 @@
         <v>3.99</v>
       </c>
       <c r="M1144">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1144">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1144">
         <v>1</v>
       </c>
       <c r="P1144" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="1145" spans="1:16">
@@ -59115,7 +59118,7 @@
         <v>0</v>
       </c>
       <c r="B1145" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C1145">
         <v>1.498025853638382</v>
@@ -59171,10 +59174,10 @@
         <v>1.439498642804615</v>
       </c>
       <c r="D1146" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1146">
-        <v>1.465731295805135</v>
+        <v>1.474087758471108</v>
       </c>
       <c r="F1146">
         <v>1</v>
@@ -59183,10 +59186,10 @@
         <v>0.006540501357195385</v>
       </c>
       <c r="H1146">
-        <v>0.006474268704194865</v>
+        <v>0.006605912241528893</v>
       </c>
       <c r="I1146">
-        <v>0.02623265300052058</v>
+        <v>0.03458911566649281</v>
       </c>
       <c r="J1146">
         <v>0.770544216675343</v>
@@ -59198,10 +59201,10 @@
         <v>3.99</v>
       </c>
       <c r="M1146">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N1146">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O1146">
         <v>1</v>
@@ -59221,7 +59224,7 @@
         <v>1.439929878966419</v>
       </c>
       <c r="D1147" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E1147">
         <v>1.46615471499724</v>
@@ -59257,7 +59260,107 @@
         <v>1</v>
       </c>
       <c r="P1147" t="s">
-        <v>232</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:16">
+      <c r="A1148" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1148">
+        <v>1.443210680071608</v>
+      </c>
+      <c r="D1148" t="s">
+        <v>381</v>
+      </c>
+      <c r="E1148">
+        <v>1.469376045387531</v>
+      </c>
+      <c r="F1148">
+        <v>1</v>
+      </c>
+      <c r="G1148">
+        <v>0.006536789319928392</v>
+      </c>
+      <c r="H1148">
+        <v>0.00647062395461247</v>
+      </c>
+      <c r="I1148">
+        <v>0.02616536531592262</v>
+      </c>
+      <c r="J1148">
+        <v>0.7694227552653753</v>
+      </c>
+      <c r="K1148">
+        <v>3.31</v>
+      </c>
+      <c r="L1148">
+        <v>3.99</v>
+      </c>
+      <c r="M1148">
+        <v>3.25</v>
+      </c>
+      <c r="N1148">
+        <v>3.97</v>
+      </c>
+      <c r="O1148">
+        <v>1</v>
+      </c>
+      <c r="P1148" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:16">
+      <c r="A1149" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1149">
+        <v>1.442303822168713</v>
+      </c>
+      <c r="D1149" t="s">
+        <v>381</v>
+      </c>
+      <c r="E1149">
+        <v>1.46848562599647</v>
+      </c>
+      <c r="F1149">
+        <v>1</v>
+      </c>
+      <c r="G1149">
+        <v>0.006537696177831288</v>
+      </c>
+      <c r="H1149">
+        <v>0.00647151437400353</v>
+      </c>
+      <c r="I1149">
+        <v>0.02618180382775748</v>
+      </c>
+      <c r="J1149">
+        <v>0.7696967304626245</v>
+      </c>
+      <c r="K1149">
+        <v>3.31</v>
+      </c>
+      <c r="L1149">
+        <v>3.99</v>
+      </c>
+      <c r="M1149">
+        <v>3.25</v>
+      </c>
+      <c r="N1149">
+        <v>3.97</v>
+      </c>
+      <c r="O1149">
+        <v>1</v>
+      </c>
+      <c r="P1149" t="s">
+        <v>513</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3588" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3558" uniqueCount="515">
   <si>
     <t>trade_time</t>
   </si>
@@ -682,9 +682,6 @@
     <t>2021-07-12</t>
   </si>
   <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
     <t>2021-08-12</t>
   </si>
   <si>
@@ -694,13 +691,16 @@
     <t>2021-08-27</t>
   </si>
   <si>
-    <t>2021-07-29</t>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2021-09-03</t>
   </si>
   <si>
-    <t>2021-07-26</t>
+    <t>2021-07-29</t>
   </si>
   <si>
     <t>2021-08-06</t>
@@ -1129,13 +1129,13 @@
     <t>2021-05-10</t>
   </si>
   <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
     <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
   </si>
   <si>
     <t>2021-08-20</t>
@@ -1144,19 +1144,19 @@
     <t>2021-07-16</t>
   </si>
   <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
     <t>2021-08-18</t>
   </si>
   <si>
     <t>2021-09-02</t>
   </si>
   <si>
-    <t>2021-09-07</t>
+    <t>2021-09-08</t>
   </si>
   <si>
     <t>2021-08-11</t>
-  </si>
-  <si>
-    <t>2021-08-16</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1537,9 +1537,6 @@
     <t>2021-07-28</t>
   </si>
   <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
     <t>2021-08-05</t>
   </si>
   <si>
@@ -1550,6 +1547,9 @@
   </si>
   <si>
     <t>2021-08-13</t>
+  </si>
+  <si>
+    <t>2021-08-16</t>
   </si>
   <si>
     <t>2021-08-17</t>
@@ -1916,7 +1916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1192"/>
+  <dimension ref="A1:P1182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -53577,7 +53577,7 @@
         <v>1.710325886585777</v>
       </c>
       <c r="D1034" t="s">
-        <v>228</v>
+        <v>371</v>
       </c>
       <c r="E1034">
         <v>1.819273719837115</v>
@@ -53627,7 +53627,7 @@
         <v>1.815102844953163</v>
       </c>
       <c r="D1035" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E1035">
         <v>1.753015209992995</v>
@@ -53677,7 +53677,7 @@
         <v>1.683711088313052</v>
       </c>
       <c r="D1036" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E1036">
         <v>1.760987732126702</v>
@@ -53724,40 +53724,40 @@
         <v>222</v>
       </c>
       <c r="C1037">
-        <v>1.801047889220578</v>
+        <v>1.708960254260409</v>
       </c>
       <c r="D1037" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E1037">
-        <v>1.751743767540634</v>
+        <v>1.761047889220578</v>
       </c>
       <c r="F1037">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1037">
-        <v>0.006298952110779422</v>
+        <v>0.00633103974573959</v>
       </c>
       <c r="H1037">
-        <v>0.006208256232459367</v>
+        <v>0.006258952110779422</v>
       </c>
       <c r="I1037">
-        <v>0.04930412167994414</v>
+        <v>0.05208763496016866</v>
       </c>
       <c r="J1037">
         <v>0.6898626106685345</v>
       </c>
       <c r="K1037">
+        <v>3.35</v>
+      </c>
+      <c r="L1037">
+        <v>4.02</v>
+      </c>
+      <c r="M1037">
         <v>3.26</v>
       </c>
-      <c r="L1037">
-        <v>4.05</v>
-      </c>
-      <c r="M1037">
-        <v>3.23</v>
-      </c>
       <c r="N1037">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="O1037">
         <v>1</v>
@@ -53774,40 +53774,40 @@
         <v>223</v>
       </c>
       <c r="C1038">
-        <v>1.708960254260409</v>
+        <v>1.706554758687151</v>
       </c>
       <c r="D1038" t="s">
-        <v>374</v>
+        <v>227</v>
       </c>
       <c r="E1038">
-        <v>1.761047889220578</v>
+        <v>1.818960254260409</v>
       </c>
       <c r="F1038">
         <v>1</v>
       </c>
       <c r="G1038">
-        <v>0.00633103974573959</v>
+        <v>0.00627344524131285</v>
       </c>
       <c r="H1038">
-        <v>0.006258952110779422</v>
+        <v>0.006441039745739591</v>
       </c>
       <c r="I1038">
-        <v>0.05208763496016866</v>
+        <v>0.1124054955732583</v>
       </c>
       <c r="J1038">
         <v>0.6898626106685345</v>
       </c>
       <c r="K1038">
+        <v>3.31</v>
+      </c>
+      <c r="L1038">
+        <v>3.99</v>
+      </c>
+      <c r="M1038">
         <v>3.35</v>
       </c>
-      <c r="L1038">
-        <v>4.02</v>
-      </c>
-      <c r="M1038">
-        <v>3.26</v>
-      </c>
       <c r="N1038">
-        <v>4.01</v>
+        <v>4.13</v>
       </c>
       <c r="O1038">
         <v>1</v>
@@ -53868,96 +53868,96 @@
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1040" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C1040">
-        <v>1.706554758687151</v>
+        <v>1.774652822327312</v>
       </c>
       <c r="D1040" t="s">
-        <v>227</v>
+        <v>372</v>
       </c>
       <c r="E1040">
-        <v>1.818960254260409</v>
+        <v>1.711570514679623</v>
       </c>
       <c r="F1040">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1040">
-        <v>0.00627344524131285</v>
+        <v>0.006905347177672688</v>
       </c>
       <c r="H1040">
-        <v>0.006441039745739591</v>
+        <v>0.006968429485320377</v>
       </c>
       <c r="I1040">
-        <v>0.1124054955732583</v>
+        <v>0.06308230764768874</v>
       </c>
       <c r="J1040">
-        <v>0.6898626106685345</v>
+        <v>0.7009145294187672</v>
       </c>
       <c r="K1040">
-        <v>3.31</v>
+        <v>3.66</v>
       </c>
       <c r="L1040">
-        <v>3.99</v>
+        <v>4.34</v>
       </c>
       <c r="M1040">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N1040">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="O1040">
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1041" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1041">
-        <v>1.774652822327312</v>
+        <v>1.642597950562186</v>
       </c>
       <c r="D1041" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E1041">
-        <v>1.711570514679623</v>
+        <v>1.611570514679623</v>
       </c>
       <c r="F1041">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1041">
-        <v>0.006905347177672688</v>
+        <v>0.006857402049437814</v>
       </c>
       <c r="H1041">
-        <v>0.006968429485320377</v>
+        <v>0.006868429485320376</v>
       </c>
       <c r="I1041">
-        <v>0.06308230764768874</v>
+        <v>-0.0310274358825624</v>
       </c>
       <c r="J1041">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1041">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1041">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1041">
         <v>3.75</v>
       </c>
       <c r="N1041">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="O1041">
         <v>1</v>
@@ -53968,46 +53968,46 @@
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1042" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1042">
-        <v>1.642597950562186</v>
+        <v>1.765018634094819</v>
       </c>
       <c r="D1042" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E1042">
-        <v>1.611570514679623</v>
+        <v>1.716046069977382</v>
       </c>
       <c r="F1042">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1042">
-        <v>0.006857402049437814</v>
+        <v>0.006334981365905181</v>
       </c>
       <c r="H1042">
-        <v>0.006868429485320376</v>
+        <v>0.006243953930022619</v>
       </c>
       <c r="I1042">
-        <v>-0.0310274358825624</v>
+        <v>0.04897256411743678</v>
       </c>
       <c r="J1042">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1042">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1042">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1042">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N1042">
-        <v>4.24</v>
+        <v>3.98</v>
       </c>
       <c r="O1042">
         <v>1</v>
@@ -54018,16 +54018,16 @@
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1043" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C1043">
-        <v>1.765018634094819</v>
+        <v>1.765110087036696</v>
       </c>
       <c r="D1043" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E1043">
         <v>1.716046069977382</v>
@@ -54036,22 +54036,22 @@
         <v>-1</v>
       </c>
       <c r="G1043">
-        <v>0.006334981365905181</v>
+        <v>0.006194889912963305</v>
       </c>
       <c r="H1043">
         <v>0.006243953930022619</v>
       </c>
       <c r="I1043">
-        <v>0.04897256411743678</v>
+        <v>0.04906401705931351</v>
       </c>
       <c r="J1043">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1043">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="L1043">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1043">
         <v>3.23</v>
@@ -54068,46 +54068,46 @@
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1044" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C1044">
-        <v>1.760064360565757</v>
+        <v>1.671936326447129</v>
       </c>
       <c r="D1044" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E1044">
-        <v>1.716046069977382</v>
+        <v>1.719972907623881</v>
       </c>
       <c r="F1044">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1044">
-        <v>0.006259935639434243</v>
+        <v>0.00636806367355287</v>
       </c>
       <c r="H1044">
-        <v>0.006243953930022619</v>
+        <v>0.00636002709237612</v>
       </c>
       <c r="I1044">
-        <v>0.04401829058837503</v>
+        <v>0.04803658117675136</v>
       </c>
       <c r="J1044">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1044">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="L1044">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="M1044">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N1044">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1044">
         <v>1</v>
@@ -54118,46 +54118,46 @@
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1045" t="s">
         <v>223</v>
       </c>
       <c r="C1045">
-        <v>1.671936326447129</v>
+        <v>1.669972907623881</v>
       </c>
       <c r="D1045" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E1045">
-        <v>1.719972907623881</v>
+        <v>1.718945471741317</v>
       </c>
       <c r="F1045">
         <v>1</v>
       </c>
       <c r="G1045">
-        <v>0.00636806367355287</v>
+        <v>0.006310027092376119</v>
       </c>
       <c r="H1045">
-        <v>0.00636002709237612</v>
+        <v>0.006401054528258681</v>
       </c>
       <c r="I1045">
-        <v>0.04803658117675136</v>
+        <v>0.04897256411743633</v>
       </c>
       <c r="J1045">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1045">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1045">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1045">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="N1045">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="O1045">
         <v>1</v>
@@ -54168,7 +54168,7 @@
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1046" t="s">
         <v>224</v>
@@ -54177,7 +54177,7 @@
         <v>1.669972907623881</v>
       </c>
       <c r="D1046" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1046">
         <v>1.718945471741317</v>
@@ -54218,46 +54218,46 @@
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1047" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1047">
-        <v>1.669972907623881</v>
+        <v>1.78193632644713</v>
       </c>
       <c r="D1047" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E1047">
-        <v>1.718945471741317</v>
+        <v>1.770908890564566</v>
       </c>
       <c r="F1047">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1047">
-        <v>0.006310027092376119</v>
+        <v>0.00647806367355287</v>
       </c>
       <c r="H1047">
-        <v>0.006401054528258681</v>
+        <v>0.006509091109435433</v>
       </c>
       <c r="I1047">
-        <v>0.04897256411743633</v>
+        <v>0.01102743588256327</v>
       </c>
       <c r="J1047">
         <v>0.7009145294187672</v>
       </c>
       <c r="K1047">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1047">
-        <v>3.99</v>
+        <v>4.13</v>
       </c>
       <c r="M1047">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N1047">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="O1047">
         <v>1</v>
@@ -54268,96 +54268,96 @@
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1048" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C1048">
-        <v>1.78193632644713</v>
+        <v>1.745068418380975</v>
       </c>
       <c r="D1048" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E1048">
-        <v>1.760908890564567</v>
+        <v>1.681258625390344</v>
       </c>
       <c r="F1048">
         <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.00647806367355287</v>
+        <v>0.006934931581619024</v>
       </c>
       <c r="H1048">
-        <v>0.006499091109435433</v>
+        <v>0.006998741374609656</v>
       </c>
       <c r="I1048">
-        <v>0.02102743588256306</v>
+        <v>0.06380979299063139</v>
       </c>
       <c r="J1048">
-        <v>0.7009145294187672</v>
+        <v>0.7089976998959082</v>
       </c>
       <c r="K1048">
-        <v>3.35</v>
+        <v>3.66</v>
       </c>
       <c r="L1048">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="M1048">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="N1048">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="O1048">
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1049" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1049">
-        <v>1.745068418380975</v>
+        <v>1.612528556387221</v>
       </c>
       <c r="D1049" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E1049">
-        <v>1.681258625390344</v>
+        <v>1.581258625390344</v>
       </c>
       <c r="F1049">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1049">
-        <v>0.006934931581619024</v>
+        <v>0.006887471443612779</v>
       </c>
       <c r="H1049">
-        <v>0.006998741374609656</v>
+        <v>0.006898741374609657</v>
       </c>
       <c r="I1049">
-        <v>0.06380979299063139</v>
+        <v>-0.03126993099687692</v>
       </c>
       <c r="J1049">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1049">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1049">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1049">
         <v>3.75</v>
       </c>
       <c r="N1049">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="O1049">
         <v>1</v>
@@ -54368,46 +54368,46 @@
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1050" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1050">
-        <v>1.612528556387221</v>
+        <v>1.738667498339339</v>
       </c>
       <c r="D1050" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1050">
-        <v>1.581258625390344</v>
+        <v>1.664857705348707</v>
       </c>
       <c r="F1050">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.006887471443612779</v>
+        <v>0.006361332501660661</v>
       </c>
       <c r="H1050">
-        <v>0.006898741374609657</v>
+        <v>0.006415142294651293</v>
       </c>
       <c r="I1050">
-        <v>-0.03126993099687692</v>
+        <v>0.07380979299063162</v>
       </c>
       <c r="J1050">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1050">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1050">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1050">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1050">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="O1050">
         <v>1</v>
@@ -54418,16 +54418,16 @@
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1051" t="s">
         <v>228</v>
       </c>
       <c r="C1051">
-        <v>1.730677751350789</v>
+        <v>1.734117383334135</v>
       </c>
       <c r="D1051" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1051">
         <v>1.664857705348707</v>
@@ -54436,22 +54436,22 @@
         <v>-1</v>
       </c>
       <c r="G1051">
-        <v>0.006509322248649211</v>
+        <v>0.006285882616665866</v>
       </c>
       <c r="H1051">
         <v>0.006415142294651293</v>
       </c>
       <c r="I1051">
-        <v>0.06582004600208169</v>
+        <v>0.06925967798542709</v>
       </c>
       <c r="J1051">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1051">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="L1051">
-        <v>4.12</v>
+        <v>4.01</v>
       </c>
       <c r="M1051">
         <v>3.35</v>
@@ -54468,16 +54468,16 @@
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1052" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C1052">
-        <v>1.734117383334135</v>
+        <v>1.732477291329971</v>
       </c>
       <c r="D1052" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1052">
         <v>1.664857705348707</v>
@@ -54486,22 +54486,22 @@
         <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.006285882616665866</v>
+        <v>0.006227522708670029</v>
       </c>
       <c r="H1052">
         <v>0.006415142294651293</v>
       </c>
       <c r="I1052">
-        <v>0.06925967798542709</v>
+        <v>0.06761958598126361</v>
       </c>
       <c r="J1052">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1052">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1052">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1052">
         <v>3.35</v>
@@ -54518,43 +54518,43 @@
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1053" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C1053">
-        <v>1.732477291329971</v>
+        <v>1.644857705348707</v>
       </c>
       <c r="D1053" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E1053">
-        <v>1.664857705348707</v>
+        <v>1.693217613344544</v>
       </c>
       <c r="F1053">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.006227522708670029</v>
+        <v>0.006395142294651292</v>
       </c>
       <c r="H1053">
-        <v>0.006415142294651293</v>
+        <v>0.006386782386655456</v>
       </c>
       <c r="I1053">
-        <v>0.06761958598126361</v>
+        <v>0.04835990799583678</v>
       </c>
       <c r="J1053">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1053">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1053">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1053">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N1053">
         <v>4.04</v>
@@ -54568,46 +54568,46 @@
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1054" t="s">
         <v>223</v>
       </c>
       <c r="C1054">
-        <v>1.644857705348707</v>
+        <v>1.643217613344544</v>
       </c>
       <c r="D1054" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E1054">
-        <v>1.693217613344544</v>
+        <v>1.691947682347666</v>
       </c>
       <c r="F1054">
         <v>1</v>
       </c>
       <c r="G1054">
-        <v>0.006395142294651292</v>
+        <v>0.006336782386655457</v>
       </c>
       <c r="H1054">
-        <v>0.006386782386655456</v>
+        <v>0.006428052317652333</v>
       </c>
       <c r="I1054">
-        <v>0.04835990799583678</v>
+        <v>0.04873006900312227</v>
       </c>
       <c r="J1054">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1054">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1054">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1054">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="N1054">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -54618,7 +54618,7 @@
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1055" t="s">
         <v>224</v>
@@ -54627,7 +54627,7 @@
         <v>1.643217613344544</v>
       </c>
       <c r="D1055" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1055">
         <v>1.691947682347666</v>
@@ -54668,46 +54668,46 @@
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1056" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1056">
-        <v>1.643217613344544</v>
+        <v>1.754857705348707</v>
       </c>
       <c r="D1056" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E1056">
-        <v>1.691947682347666</v>
+        <v>1.74358777435183</v>
       </c>
       <c r="F1056">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.006336782386655457</v>
+        <v>0.006505142294651293</v>
       </c>
       <c r="H1056">
-        <v>0.006428052317652333</v>
+        <v>0.006536412225648169</v>
       </c>
       <c r="I1056">
-        <v>0.04873006900312227</v>
+        <v>0.01126993099687734</v>
       </c>
       <c r="J1056">
         <v>0.7089976998959082</v>
       </c>
       <c r="K1056">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1056">
-        <v>3.99</v>
+        <v>4.13</v>
       </c>
       <c r="M1056">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N1056">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="O1056">
         <v>1</v>
@@ -54718,96 +54718,96 @@
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1057" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C1057">
-        <v>1.754857705348707</v>
+        <v>1.725336643125503</v>
       </c>
       <c r="D1057" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E1057">
-        <v>1.73358777435183</v>
+        <v>1.661041642546622</v>
       </c>
       <c r="F1057">
         <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.006505142294651293</v>
+        <v>0.006954663356874498</v>
       </c>
       <c r="H1057">
-        <v>0.006526412225648169</v>
+        <v>0.007018958357453379</v>
       </c>
       <c r="I1057">
-        <v>0.02126993099687713</v>
+        <v>0.06429500057888093</v>
       </c>
       <c r="J1057">
-        <v>0.7089976998959082</v>
+        <v>0.7143888953209009</v>
       </c>
       <c r="K1057">
-        <v>3.35</v>
+        <v>3.66</v>
       </c>
       <c r="L1057">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="M1057">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="N1057">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="O1057">
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1058" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1058">
-        <v>1.725336643125503</v>
+        <v>1.592473309406249</v>
       </c>
       <c r="D1058" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E1058">
-        <v>1.661041642546622</v>
+        <v>1.561041642546622</v>
       </c>
       <c r="F1058">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.006954663356874498</v>
+        <v>0.006907526690593752</v>
       </c>
       <c r="H1058">
-        <v>0.007018958357453379</v>
+        <v>0.006918958357453379</v>
       </c>
       <c r="I1058">
-        <v>0.06429500057888093</v>
+        <v>-0.03143166685962662</v>
       </c>
       <c r="J1058">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1058">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1058">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1058">
         <v>3.75</v>
       </c>
       <c r="N1058">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="O1058">
         <v>1</v>
@@ -54818,46 +54818,46 @@
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1059" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1059">
-        <v>1.592473309406249</v>
+        <v>1.721092201253863</v>
       </c>
       <c r="D1059" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1059">
-        <v>1.561041642546622</v>
+        <v>1.646797200674982</v>
       </c>
       <c r="F1059">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1059">
-        <v>0.006907526690593752</v>
+        <v>0.006378907798746137</v>
       </c>
       <c r="H1059">
-        <v>0.006918958357453379</v>
+        <v>0.006433202799325018</v>
       </c>
       <c r="I1059">
-        <v>-0.03143166685962662</v>
+        <v>0.07429500057888117</v>
       </c>
       <c r="J1059">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1059">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1059">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1059">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1059">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="O1059">
         <v>1</v>
@@ -54868,16 +54868,16 @@
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1060" t="s">
         <v>228</v>
       </c>
       <c r="C1060">
-        <v>1.712509422768564</v>
+        <v>1.716811646019908</v>
       </c>
       <c r="D1060" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1060">
         <v>1.646797200674982</v>
@@ -54886,22 +54886,22 @@
         <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.006527490577231437</v>
+        <v>0.006303188353980092</v>
       </c>
       <c r="H1060">
         <v>0.006433202799325018</v>
       </c>
       <c r="I1060">
-        <v>0.06571222209358218</v>
+        <v>0.07001444534492629</v>
       </c>
       <c r="J1060">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1060">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="L1060">
-        <v>4.12</v>
+        <v>4.01</v>
       </c>
       <c r="M1060">
         <v>3.35</v>
@@ -54918,16 +54918,16 @@
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1061" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C1061">
-        <v>1.716811646019908</v>
+        <v>1.715387201832744</v>
       </c>
       <c r="D1061" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1061">
         <v>1.646797200674982</v>
@@ -54936,22 +54936,22 @@
         <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.006303188353980092</v>
+        <v>0.006244612798167256</v>
       </c>
       <c r="H1061">
         <v>0.006433202799325018</v>
       </c>
       <c r="I1061">
-        <v>0.07001444534492629</v>
+        <v>0.06859000115776226</v>
       </c>
       <c r="J1061">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1061">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1061">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1061">
         <v>3.35</v>
@@ -54968,43 +54968,43 @@
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1062" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C1062">
-        <v>1.715387201832744</v>
+        <v>1.626797200674981</v>
       </c>
       <c r="D1062" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E1062">
-        <v>1.646797200674982</v>
+        <v>1.675372756487818</v>
       </c>
       <c r="F1062">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.006244612798167256</v>
+        <v>0.006413202799325018</v>
       </c>
       <c r="H1062">
-        <v>0.006433202799325018</v>
+        <v>0.006404627243512183</v>
       </c>
       <c r="I1062">
-        <v>0.06859000115776226</v>
+        <v>0.04857555581283668</v>
       </c>
       <c r="J1062">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1062">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1062">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1062">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N1062">
         <v>4.04</v>
@@ -55018,46 +55018,46 @@
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1063" t="s">
         <v>223</v>
       </c>
       <c r="C1063">
-        <v>1.626797200674981</v>
+        <v>1.625372756487818</v>
       </c>
       <c r="D1063" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E1063">
-        <v>1.675372756487818</v>
+        <v>1.673941089628191</v>
       </c>
       <c r="F1063">
         <v>1</v>
       </c>
       <c r="G1063">
-        <v>0.006413202799325018</v>
+        <v>0.006354627243512182</v>
       </c>
       <c r="H1063">
-        <v>0.006404627243512183</v>
+        <v>0.006446058910371809</v>
       </c>
       <c r="I1063">
-        <v>0.04857555581283668</v>
+        <v>0.04856833314037257</v>
       </c>
       <c r="J1063">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1063">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1063">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1063">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="N1063">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="O1063">
         <v>1</v>
@@ -55068,7 +55068,7 @@
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1064" t="s">
         <v>224</v>
@@ -55077,7 +55077,7 @@
         <v>1.625372756487818</v>
       </c>
       <c r="D1064" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1064">
         <v>1.673941089628191</v>
@@ -55118,46 +55118,46 @@
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1065" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1065">
-        <v>1.625372756487818</v>
+        <v>1.736797200674982</v>
       </c>
       <c r="D1065" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E1065">
-        <v>1.673941089628191</v>
+        <v>1.725365533815355</v>
       </c>
       <c r="F1065">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1065">
-        <v>0.006354627243512182</v>
+        <v>0.006523202799325018</v>
       </c>
       <c r="H1065">
-        <v>0.006446058910371809</v>
+        <v>0.006554634466184645</v>
       </c>
       <c r="I1065">
-        <v>0.04856833314037257</v>
+        <v>0.01143166685962704</v>
       </c>
       <c r="J1065">
         <v>0.7143888953209009</v>
       </c>
       <c r="K1065">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1065">
-        <v>3.99</v>
+        <v>4.13</v>
       </c>
       <c r="M1065">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N1065">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="O1065">
         <v>1</v>
@@ -55168,96 +55168,96 @@
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1066" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C1066">
-        <v>1.736797200674982</v>
+        <v>1.706714139491356</v>
       </c>
       <c r="D1066" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E1066">
-        <v>1.715365533815355</v>
+        <v>1.641961208495242</v>
       </c>
       <c r="F1066">
         <v>-1</v>
       </c>
       <c r="G1066">
-        <v>0.006523202799325018</v>
+        <v>0.006973285860508644</v>
       </c>
       <c r="H1066">
-        <v>0.006544634466184645</v>
+        <v>0.007038038791504758</v>
       </c>
       <c r="I1066">
-        <v>0.02143166685962683</v>
+        <v>0.0647529309961139</v>
       </c>
       <c r="J1066">
-        <v>0.7143888953209009</v>
+        <v>0.7194770110679355</v>
       </c>
       <c r="K1066">
-        <v>3.35</v>
+        <v>3.66</v>
       </c>
       <c r="L1066">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="M1066">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="N1066">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="O1066">
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1067" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1067">
-        <v>1.706714139491356</v>
+        <v>1.57354551882728</v>
       </c>
       <c r="D1067" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E1067">
-        <v>1.641961208495242</v>
+        <v>1.541961208495242</v>
       </c>
       <c r="F1067">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1067">
-        <v>0.006973285860508644</v>
+        <v>0.00692645448117272</v>
       </c>
       <c r="H1067">
-        <v>0.007038038791504758</v>
+        <v>0.006938038791504758</v>
       </c>
       <c r="I1067">
-        <v>0.0647529309961139</v>
+        <v>-0.0315843103320379</v>
       </c>
       <c r="J1067">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1067">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1067">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1067">
         <v>3.75</v>
       </c>
       <c r="N1067">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="O1067">
         <v>1</v>
@@ -55268,46 +55268,46 @@
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1068" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1068">
-        <v>1.57354551882728</v>
+        <v>1.70450494391853</v>
       </c>
       <c r="D1068" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1068">
-        <v>1.541961208495242</v>
+        <v>1.629752012922416</v>
       </c>
       <c r="F1068">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1068">
-        <v>0.00692645448117272</v>
+        <v>0.006395495056081469</v>
       </c>
       <c r="H1068">
-        <v>0.006938038791504758</v>
+        <v>0.006450247987077585</v>
       </c>
       <c r="I1068">
-        <v>-0.0315843103320379</v>
+        <v>0.07475293099611457</v>
       </c>
       <c r="J1068">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1068">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1068">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1068">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1068">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="O1068">
         <v>1</v>
@@ -55318,16 +55318,16 @@
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1069" t="s">
         <v>228</v>
       </c>
       <c r="C1069">
-        <v>1.695362472701057</v>
+        <v>1.700478794471927</v>
       </c>
       <c r="D1069" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1069">
         <v>1.629752012922416</v>
@@ -55336,22 +55336,22 @@
         <v>-1</v>
       </c>
       <c r="G1069">
-        <v>0.006544637527298943</v>
+        <v>0.006319521205528073</v>
       </c>
       <c r="H1069">
         <v>0.006450247987077585</v>
       </c>
       <c r="I1069">
-        <v>0.06561045977864133</v>
+        <v>0.07072678154951095</v>
       </c>
       <c r="J1069">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1069">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="L1069">
-        <v>4.12</v>
+        <v>4.01</v>
       </c>
       <c r="M1069">
         <v>3.35</v>
@@ -55368,16 +55368,16 @@
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1070" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C1070">
-        <v>1.700478794471927</v>
+        <v>1.699257874914645</v>
       </c>
       <c r="D1070" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1070">
         <v>1.629752012922416</v>
@@ -55386,22 +55386,22 @@
         <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.006319521205528073</v>
+        <v>0.006260742125085356</v>
       </c>
       <c r="H1070">
         <v>0.006450247987077585</v>
       </c>
       <c r="I1070">
-        <v>0.07072678154951095</v>
+        <v>0.06950586199222863</v>
       </c>
       <c r="J1070">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1070">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1070">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1070">
         <v>3.35</v>
@@ -55418,46 +55418,46 @@
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1071" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C1071">
-        <v>1.699257874914645</v>
+        <v>1.608531093365134</v>
       </c>
       <c r="D1071" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1071">
-        <v>1.629752012922416</v>
+        <v>1.656946783033095</v>
       </c>
       <c r="F1071">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1071">
-        <v>0.006260742125085356</v>
+        <v>0.006371468906634867</v>
       </c>
       <c r="H1071">
-        <v>0.006450247987077585</v>
+        <v>0.006463053216966903</v>
       </c>
       <c r="I1071">
-        <v>0.06950586199222863</v>
+        <v>0.04841568966796173</v>
       </c>
       <c r="J1071">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1071">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1071">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1071">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N1071">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="O1071">
         <v>1</v>
@@ -55468,7 +55468,7 @@
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1072" t="s">
         <v>224</v>
@@ -55477,7 +55477,7 @@
         <v>1.608531093365134</v>
       </c>
       <c r="D1072" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1072">
         <v>1.656946783033095</v>
@@ -55518,46 +55518,46 @@
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1073" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1073">
-        <v>1.608531093365134</v>
+        <v>1.719752012922416</v>
       </c>
       <c r="D1073" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E1073">
-        <v>1.656946783033095</v>
+        <v>1.708167702590378</v>
       </c>
       <c r="F1073">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1073">
-        <v>0.006371468906634867</v>
+        <v>0.006540247987077585</v>
       </c>
       <c r="H1073">
-        <v>0.006463053216966903</v>
+        <v>0.006571832297409621</v>
       </c>
       <c r="I1073">
-        <v>0.04841568966796173</v>
+        <v>0.01158431033203788</v>
       </c>
       <c r="J1073">
         <v>0.7194770110679355</v>
       </c>
       <c r="K1073">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1073">
-        <v>3.99</v>
+        <v>4.13</v>
       </c>
       <c r="M1073">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N1073">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="O1073">
         <v>1</v>
@@ -55568,96 +55568,96 @@
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1074" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C1074">
-        <v>1.719752012922416</v>
+        <v>1.687585123258323</v>
       </c>
       <c r="D1074" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E1074">
-        <v>1.698167702590378</v>
+        <v>1.622361806617135</v>
       </c>
       <c r="F1074">
         <v>-1</v>
       </c>
       <c r="G1074">
-        <v>0.006540247987077585</v>
+        <v>0.006992414876741677</v>
       </c>
       <c r="H1074">
-        <v>0.006561832297409621</v>
+        <v>0.007057638193382865</v>
       </c>
       <c r="I1074">
-        <v>0.02158431033203767</v>
+        <v>0.06522331664118841</v>
       </c>
       <c r="J1074">
-        <v>0.7194770110679355</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1074">
-        <v>3.35</v>
+        <v>3.66</v>
       </c>
       <c r="L1074">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="M1074">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="N1074">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="O1074">
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
       <c r="A1075" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1075" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1075">
-        <v>1.687585123258323</v>
+        <v>1.554102912164197</v>
       </c>
       <c r="D1075" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E1075">
-        <v>1.622361806617135</v>
+        <v>1.522361806617135</v>
       </c>
       <c r="F1075">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1075">
-        <v>0.006992414876741677</v>
+        <v>0.006945897087835803</v>
       </c>
       <c r="H1075">
-        <v>0.007057638193382865</v>
+        <v>0.006957638193382866</v>
       </c>
       <c r="I1075">
-        <v>0.06522331664118841</v>
+        <v>-0.03174110554706244</v>
       </c>
       <c r="J1075">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1075">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1075">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1075">
         <v>3.75</v>
       </c>
       <c r="N1075">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="O1075">
         <v>1</v>
@@ -55668,46 +55668,46 @@
     </row>
     <row r="1076" spans="1:16">
       <c r="A1076" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1076" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1076">
-        <v>1.554102912164197</v>
+        <v>1.687466530552496</v>
       </c>
       <c r="D1076" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1076">
-        <v>1.522361806617135</v>
+        <v>1.612243213911307</v>
       </c>
       <c r="F1076">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1076">
-        <v>0.006945897087835803</v>
+        <v>0.006412533469447504</v>
       </c>
       <c r="H1076">
-        <v>0.006957638193382866</v>
+        <v>0.006467756786088693</v>
       </c>
       <c r="I1076">
-        <v>-0.03174110554706244</v>
+        <v>0.07522331664118909</v>
       </c>
       <c r="J1076">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1076">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1076">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1076">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1076">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="O1076">
         <v>1</v>
@@ -55718,16 +55718,16 @@
     </row>
     <row r="1077" spans="1:16">
       <c r="A1077" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1077" t="s">
         <v>228</v>
       </c>
       <c r="C1077">
-        <v>1.677749143546598</v>
+        <v>1.683701706464267</v>
       </c>
       <c r="D1077" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1077">
         <v>1.612243213911307</v>
@@ -55736,22 +55736,22 @@
         <v>-1</v>
       </c>
       <c r="G1077">
-        <v>0.006562250856453402</v>
+        <v>0.006336298293535732</v>
       </c>
       <c r="H1077">
         <v>0.006467756786088693</v>
       </c>
       <c r="I1077">
-        <v>0.06550592963529134</v>
+        <v>0.07145849255296044</v>
       </c>
       <c r="J1077">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1077">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="L1077">
-        <v>4.12</v>
+        <v>4.01</v>
       </c>
       <c r="M1077">
         <v>3.35</v>
@@ -55768,16 +55768,16 @@
     </row>
     <row r="1078" spans="1:16">
       <c r="A1078" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1078" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C1078">
-        <v>1.683701706464267</v>
+        <v>1.682689847193684</v>
       </c>
       <c r="D1078" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1078">
         <v>1.612243213911307</v>
@@ -55786,22 +55786,22 @@
         <v>-1</v>
       </c>
       <c r="G1078">
-        <v>0.006336298293535732</v>
+        <v>0.006277310152806315</v>
       </c>
       <c r="H1078">
         <v>0.006467756786088693</v>
       </c>
       <c r="I1078">
-        <v>0.07145849255296044</v>
+        <v>0.07044663328237766</v>
       </c>
       <c r="J1078">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1078">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1078">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1078">
         <v>3.35</v>
@@ -55818,46 +55818,46 @@
     </row>
     <row r="1079" spans="1:16">
       <c r="A1079" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1079" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C1079">
-        <v>1.682689847193684</v>
+        <v>1.702243213911307</v>
       </c>
       <c r="D1079" t="s">
         <v>379</v>
       </c>
       <c r="E1079">
-        <v>1.612243213911307</v>
+        <v>1.690502108364244</v>
       </c>
       <c r="F1079">
         <v>-1</v>
       </c>
       <c r="G1079">
-        <v>0.006277310152806315</v>
+        <v>0.006557756786088693</v>
       </c>
       <c r="H1079">
-        <v>0.006467756786088693</v>
+        <v>0.006589497891635755</v>
       </c>
       <c r="I1079">
-        <v>0.07044663328237766</v>
+        <v>0.01174110554706287</v>
       </c>
       <c r="J1079">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1079">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1079">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="M1079">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N1079">
-        <v>4.04</v>
+        <v>4.14</v>
       </c>
       <c r="O1079">
         <v>1</v>
@@ -55868,96 +55868,96 @@
     </row>
     <row r="1080" spans="1:16">
       <c r="A1080" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1080" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C1080">
-        <v>1.702243213911307</v>
+        <v>1.674071021437449</v>
       </c>
       <c r="D1080" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E1080">
-        <v>1.680502108364244</v>
+        <v>1.608515390817058</v>
       </c>
       <c r="F1080">
         <v>-1</v>
       </c>
       <c r="G1080">
-        <v>0.006557756786088693</v>
+        <v>0.007005928978562551</v>
       </c>
       <c r="H1080">
-        <v>0.006579497891635756</v>
+        <v>0.007071484609182941</v>
       </c>
       <c r="I1080">
-        <v>0.02174110554706266</v>
+        <v>0.06555563062039038</v>
       </c>
       <c r="J1080">
-        <v>0.7247035182354308</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1080">
-        <v>3.35</v>
+        <v>3.66</v>
       </c>
       <c r="L1080">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="M1080">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="N1080">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="O1080">
         <v>1</v>
       </c>
       <c r="P1080" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1081" spans="1:16">
       <c r="A1081" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1081" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1081">
-        <v>1.674071021437449</v>
+        <v>1.540367267690522</v>
       </c>
       <c r="D1081" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E1081">
-        <v>1.608515390817058</v>
+        <v>1.508515390817059</v>
       </c>
       <c r="F1081">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1081">
-        <v>0.007005928978562551</v>
+        <v>0.006959632732309478</v>
       </c>
       <c r="H1081">
-        <v>0.007071484609182941</v>
+        <v>0.006971484609182942</v>
       </c>
       <c r="I1081">
-        <v>0.06555563062039038</v>
+        <v>-0.03185187687346325</v>
       </c>
       <c r="J1081">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1081">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="L1081">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="M1081">
         <v>3.75</v>
       </c>
       <c r="N1081">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="O1081">
         <v>1</v>
@@ -55968,46 +55968,46 @@
     </row>
     <row r="1082" spans="1:16">
       <c r="A1082" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1082" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1082">
-        <v>1.540367267690522</v>
+        <v>1.675429379750296</v>
       </c>
       <c r="D1082" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1082">
-        <v>1.508515390817059</v>
+        <v>1.599873749129906</v>
       </c>
       <c r="F1082">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1082">
-        <v>0.006959632732309478</v>
+        <v>0.006424570620249703</v>
       </c>
       <c r="H1082">
-        <v>0.006971484609182942</v>
+        <v>0.006480126250870095</v>
       </c>
       <c r="I1082">
-        <v>-0.03185187687346325</v>
+        <v>0.07555563062039061</v>
       </c>
       <c r="J1082">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1082">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1082">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1082">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1082">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="O1082">
         <v>1</v>
@@ -56018,16 +56018,16 @@
     </row>
     <row r="1083" spans="1:16">
       <c r="A1083" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1083" t="s">
         <v>228</v>
       </c>
       <c r="C1083">
-        <v>1.665305831214263</v>
+        <v>1.671849174539402</v>
       </c>
       <c r="D1083" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1083">
         <v>1.599873749129906</v>
@@ -56036,22 +56036,22 @@
         <v>-1</v>
       </c>
       <c r="G1083">
-        <v>0.006574694168785737</v>
+        <v>0.006348150825460598</v>
       </c>
       <c r="H1083">
         <v>0.006480126250870095</v>
       </c>
       <c r="I1083">
-        <v>0.06543208208435747</v>
+        <v>0.0719754254094962</v>
       </c>
       <c r="J1083">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1083">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="L1083">
-        <v>4.12</v>
+        <v>4.01</v>
       </c>
       <c r="M1083">
         <v>3.35</v>
@@ -56068,16 +56068,16 @@
     </row>
     <row r="1084" spans="1:16">
       <c r="A1084" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1084" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C1084">
-        <v>1.671849174539402</v>
+        <v>1.670985010370687</v>
       </c>
       <c r="D1084" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1084">
         <v>1.599873749129906</v>
@@ -56086,22 +56086,22 @@
         <v>-1</v>
       </c>
       <c r="G1084">
-        <v>0.006348150825460598</v>
+        <v>0.006289014989629313</v>
       </c>
       <c r="H1084">
         <v>0.006480126250870095</v>
       </c>
       <c r="I1084">
-        <v>0.0719754254094962</v>
+        <v>0.07111126124078115</v>
       </c>
       <c r="J1084">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1084">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1084">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1084">
         <v>3.35</v>
@@ -56118,46 +56118,46 @@
     </row>
     <row r="1085" spans="1:16">
       <c r="A1085" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1085" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C1085">
-        <v>1.670985010370687</v>
+        <v>1.689873749129906</v>
       </c>
       <c r="D1085" t="s">
         <v>379</v>
       </c>
       <c r="E1085">
-        <v>1.599873749129906</v>
+        <v>1.678021872256442</v>
       </c>
       <c r="F1085">
         <v>-1</v>
       </c>
       <c r="G1085">
-        <v>0.006289014989629313</v>
+        <v>0.006570126250870095</v>
       </c>
       <c r="H1085">
-        <v>0.006480126250870095</v>
+        <v>0.006601978127743557</v>
       </c>
       <c r="I1085">
-        <v>0.07111126124078115</v>
+        <v>0.01185187687346367</v>
       </c>
       <c r="J1085">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1085">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1085">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="M1085">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N1085">
-        <v>4.04</v>
+        <v>4.14</v>
       </c>
       <c r="O1085">
         <v>1</v>
@@ -56168,96 +56168,96 @@
     </row>
     <row r="1086" spans="1:16">
       <c r="A1086" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1086" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C1086">
-        <v>1.689873749129906</v>
+        <v>1.525149479713785</v>
       </c>
       <c r="D1086" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E1086">
-        <v>1.668021872256442</v>
+        <v>1.493174878743735</v>
       </c>
       <c r="F1086">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1086">
-        <v>0.006570126250870095</v>
+        <v>0.006974850520286215</v>
       </c>
       <c r="H1086">
-        <v>0.006591978127743557</v>
+        <v>0.006986825121256265</v>
       </c>
       <c r="I1086">
-        <v>0.02185187687346346</v>
+        <v>-0.03197460097004967</v>
       </c>
       <c r="J1086">
-        <v>0.7283958957821177</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1086">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="L1086">
-        <v>4.13</v>
+        <v>4.25</v>
       </c>
       <c r="M1086">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="N1086">
-        <v>4.13</v>
+        <v>4.24</v>
       </c>
       <c r="O1086">
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>501</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
       <c r="A1087" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1087" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1087">
-        <v>1.525149479713785</v>
+        <v>1.662093361254554</v>
       </c>
       <c r="D1087" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1087">
-        <v>1.493174878743735</v>
+        <v>1.586169558344404</v>
       </c>
       <c r="F1087">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1087">
-        <v>0.006974850520286215</v>
+        <v>0.006437906638745446</v>
       </c>
       <c r="H1087">
-        <v>0.006986825121256265</v>
+        <v>0.006493830441655597</v>
       </c>
       <c r="I1087">
-        <v>-0.03197460097004967</v>
+        <v>0.07592380291015033</v>
       </c>
       <c r="J1087">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1087">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1087">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1087">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1087">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56268,16 +56268,16 @@
     </row>
     <row r="1088" spans="1:16">
       <c r="A1088" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1088" t="s">
         <v>228</v>
       </c>
       <c r="C1088">
-        <v>1.65151982436437</v>
+        <v>1.658717696204637</v>
       </c>
       <c r="D1088" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1088">
         <v>1.586169558344404</v>
@@ -56286,22 +56286,22 @@
         <v>-1</v>
       </c>
       <c r="G1088">
-        <v>0.00658848017563563</v>
+        <v>0.006361282303795362</v>
       </c>
       <c r="H1088">
         <v>0.006493830441655597</v>
       </c>
       <c r="I1088">
-        <v>0.06535026601996652</v>
+        <v>0.07254813786023373</v>
       </c>
       <c r="J1088">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1088">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="L1088">
-        <v>4.12</v>
+        <v>4.01</v>
       </c>
       <c r="M1088">
         <v>3.35</v>
@@ -56318,16 +56318,16 @@
     </row>
     <row r="1089" spans="1:16">
       <c r="A1089" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1089" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C1089">
-        <v>1.658717696204637</v>
+        <v>1.658017164164704</v>
       </c>
       <c r="D1089" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1089">
         <v>1.586169558344404</v>
@@ -56336,22 +56336,22 @@
         <v>-1</v>
       </c>
       <c r="G1089">
-        <v>0.006361282303795362</v>
+        <v>0.006301982835835296</v>
       </c>
       <c r="H1089">
         <v>0.006493830441655597</v>
       </c>
       <c r="I1089">
-        <v>0.07254813786023373</v>
+        <v>0.07184760582030059</v>
       </c>
       <c r="J1089">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1089">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1089">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1089">
         <v>3.35</v>
@@ -56368,46 +56368,46 @@
     </row>
     <row r="1090" spans="1:16">
       <c r="A1090" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1090" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C1090">
-        <v>1.658017164164704</v>
+        <v>1.676169558344403</v>
       </c>
       <c r="D1090" t="s">
         <v>379</v>
       </c>
       <c r="E1090">
-        <v>1.586169558344404</v>
+        <v>1.664194957374353</v>
       </c>
       <c r="F1090">
         <v>-1</v>
       </c>
       <c r="G1090">
-        <v>0.006301982835835296</v>
+        <v>0.006583830441655596</v>
       </c>
       <c r="H1090">
-        <v>0.006493830441655597</v>
+        <v>0.006615805042625647</v>
       </c>
       <c r="I1090">
-        <v>0.07184760582030059</v>
+        <v>0.01197460097005054</v>
       </c>
       <c r="J1090">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1090">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1090">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="M1090">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N1090">
-        <v>4.04</v>
+        <v>4.14</v>
       </c>
       <c r="O1090">
         <v>1</v>
@@ -56418,116 +56418,116 @@
     </row>
     <row r="1091" spans="1:16">
       <c r="A1091" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1091" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C1091">
-        <v>1.676169558344403</v>
+        <v>1.515332066574131</v>
       </c>
       <c r="D1091" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E1091">
-        <v>1.654194957374353</v>
+        <v>1.483278292917471</v>
       </c>
       <c r="F1091">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1091">
-        <v>0.006583830441655596</v>
+        <v>0.00698466793342587</v>
       </c>
       <c r="H1091">
-        <v>0.006605805042625647</v>
+        <v>0.00699672170708253</v>
       </c>
       <c r="I1091">
-        <v>0.02197460097005033</v>
+        <v>-0.03205377365665951</v>
       </c>
       <c r="J1091">
-        <v>0.7324866990016706</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1091">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="L1091">
-        <v>4.13</v>
+        <v>4.25</v>
       </c>
       <c r="M1091">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="N1091">
-        <v>4.13</v>
+        <v>4.24</v>
       </c>
       <c r="O1091">
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>221</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
       <c r="A1092" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1092" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1092">
-        <v>1.515332066574131</v>
+        <v>1.653489929309588</v>
       </c>
       <c r="D1092" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1092">
-        <v>1.483278292917471</v>
+        <v>1.577328608339607</v>
       </c>
       <c r="F1092">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1092">
-        <v>0.00698466793342587</v>
+        <v>0.006446510070690412</v>
       </c>
       <c r="H1092">
-        <v>0.00699672170708253</v>
+        <v>0.006502671391660392</v>
       </c>
       <c r="I1092">
-        <v>-0.03205377365665951</v>
+        <v>0.07616132096998074</v>
       </c>
       <c r="J1092">
         <v>0.7351257885553412</v>
       </c>
       <c r="K1092">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="L1092">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M1092">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N1092">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="O1092">
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1093" spans="1:16">
       <c r="A1093" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1093" t="s">
         <v>228</v>
       </c>
       <c r="C1093">
-        <v>1.6426260925685</v>
+        <v>1.650246218737355</v>
       </c>
       <c r="D1093" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1093">
         <v>1.577328608339607</v>
@@ -56536,22 +56536,22 @@
         <v>-1</v>
       </c>
       <c r="G1093">
-        <v>0.0065973739074315</v>
+        <v>0.006369753781262645</v>
       </c>
       <c r="H1093">
         <v>0.006502671391660392</v>
       </c>
       <c r="I1093">
-        <v>0.06529748422889314</v>
+        <v>0.07291761039774736</v>
       </c>
       <c r="J1093">
         <v>0.7351257885553412</v>
       </c>
       <c r="K1093">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="L1093">
-        <v>4.12</v>
+        <v>4.01</v>
       </c>
       <c r="M1093">
         <v>3.35</v>
@@ -56563,12 +56563,12 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
       <c r="A1094" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1094" t="s">
         <v>229</v>
@@ -56577,7 +56577,7 @@
         <v>1.649651250279569</v>
       </c>
       <c r="D1094" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1094">
         <v>1.577328608339607</v>
@@ -56613,12 +56613,12 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
       <c r="A1095" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1095" t="s">
         <v>227</v>
@@ -56627,10 +56627,10 @@
         <v>1.667328608339607</v>
       </c>
       <c r="D1095" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1095">
-        <v>1.645274834682947</v>
+        <v>1.655274834682947</v>
       </c>
       <c r="F1095">
         <v>-1</v>
@@ -56639,10 +56639,10 @@
         <v>0.006592671391660392</v>
       </c>
       <c r="H1095">
-        <v>0.006614725165317053</v>
+        <v>0.006624725165317052</v>
       </c>
       <c r="I1095">
-        <v>0.02205377365666017</v>
+        <v>0.01205377365666038</v>
       </c>
       <c r="J1095">
         <v>0.7351257885553412</v>
@@ -56657,13 +56657,13 @@
         <v>3.38</v>
       </c>
       <c r="N1095">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="O1095">
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -56671,13 +56671,13 @@
         <v>0</v>
       </c>
       <c r="B1096" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C1096">
-        <v>1.631729592152544</v>
+        <v>1.642949101014034</v>
       </c>
       <c r="D1096" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1096">
         <v>1.566496775581906</v>
@@ -56686,22 +56686,22 @@
         <v>-1</v>
       </c>
       <c r="G1096">
-        <v>0.006608270407847457</v>
+        <v>0.006457050898985965</v>
       </c>
       <c r="H1096">
         <v>0.006513503224418095</v>
       </c>
       <c r="I1096">
-        <v>0.06523281657063817</v>
+        <v>0.0764523254321281</v>
       </c>
       <c r="J1096">
         <v>0.7383591714680878</v>
       </c>
       <c r="K1096">
-        <v>3.37</v>
+        <v>3.26</v>
       </c>
       <c r="L1096">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="M1096">
         <v>3.35</v>
@@ -56721,13 +56721,13 @@
         <v>1</v>
       </c>
       <c r="B1097" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C1097">
         <v>1.639867059587438</v>
       </c>
       <c r="D1097" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1097">
         <v>1.566496775581906</v>
@@ -56777,7 +56777,7 @@
         <v>1.639401426446162</v>
       </c>
       <c r="D1098" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1098">
         <v>1.566496775581906</v>
@@ -56827,10 +56827,10 @@
         <v>1.656496775581906</v>
       </c>
       <c r="D1099" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1099">
-        <v>1.634346000437863</v>
+        <v>1.644346000437863</v>
       </c>
       <c r="F1099">
         <v>-1</v>
@@ -56839,10 +56839,10 @@
         <v>0.006603503224418095</v>
       </c>
       <c r="H1099">
-        <v>0.006625653999562137</v>
+        <v>0.006635653999562137</v>
       </c>
       <c r="I1099">
-        <v>0.02215077514404262</v>
+        <v>0.01215077514404284</v>
       </c>
       <c r="J1099">
         <v>0.7383591714680878</v>
@@ -56857,7 +56857,7 @@
         <v>3.38</v>
       </c>
       <c r="N1099">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="O1099">
         <v>1</v>
@@ -56871,13 +56871,13 @@
         <v>0</v>
       </c>
       <c r="B1100" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C1100">
         <v>1.624740047284429</v>
       </c>
       <c r="D1100" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1100">
         <v>1.547785017914981</v>
@@ -56921,13 +56921,13 @@
         <v>1</v>
       </c>
       <c r="B1101" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C1101">
         <v>1.621937285823011</v>
       </c>
       <c r="D1101" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1101">
         <v>1.547785017914981</v>
@@ -56977,7 +56977,7 @@
         <v>1.621695076653878</v>
       </c>
       <c r="D1102" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1102">
         <v>1.547785017914981</v>
@@ -57027,10 +57027,10 @@
         <v>1.637785017914981</v>
       </c>
       <c r="D1103" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1103">
-        <v>1.615466674791832</v>
+        <v>1.625466674791832</v>
       </c>
       <c r="F1103">
         <v>-1</v>
@@ -57039,10 +57039,10 @@
         <v>0.00662221498208502</v>
       </c>
       <c r="H1103">
-        <v>0.006644533325208168</v>
+        <v>0.006654533325208167</v>
       </c>
       <c r="I1103">
-        <v>0.02231834312314929</v>
+        <v>0.0123183431231495</v>
       </c>
       <c r="J1103">
         <v>0.7439447707716474</v>
@@ -57057,7 +57057,7 @@
         <v>3.38</v>
       </c>
       <c r="N1103">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="O1103">
         <v>1</v>
@@ -57071,13 +57071,13 @@
         <v>0</v>
       </c>
       <c r="B1104" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C1104">
         <v>1.61016227805581</v>
       </c>
       <c r="D1104" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1104">
         <v>1.532804794934651</v>
@@ -57121,13 +57121,13 @@
         <v>1</v>
       </c>
       <c r="B1105" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C1105">
         <v>1.607583102012009</v>
       </c>
       <c r="D1105" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1105">
         <v>1.532804794934651</v>
@@ -57177,7 +57177,7 @@
         <v>1.607519761176969</v>
       </c>
       <c r="D1106" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1106">
         <v>1.532804794934651</v>
@@ -57221,28 +57221,28 @@
         <v>3</v>
       </c>
       <c r="B1107" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C1107">
-        <v>1.622804794934651</v>
+        <v>1.512804794934651</v>
       </c>
       <c r="D1107" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1107">
-        <v>1.600352300560932</v>
+        <v>1.562741454099611</v>
       </c>
       <c r="F1107">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1107">
-        <v>0.006637195205065348</v>
+        <v>0.006527195205065349</v>
       </c>
       <c r="H1107">
-        <v>0.006659647699439069</v>
+        <v>0.006517258545900389</v>
       </c>
       <c r="I1107">
-        <v>0.02245249437371921</v>
+        <v>0.04993665916496015</v>
       </c>
       <c r="J1107">
         <v>0.7484164791239846</v>
@@ -57251,13 +57251,13 @@
         <v>3.35</v>
       </c>
       <c r="L1107">
-        <v>4.13</v>
+        <v>4.02</v>
       </c>
       <c r="M1107">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="N1107">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
       <c r="O1107">
         <v>1</v>
@@ -57268,196 +57268,196 @@
     </row>
     <row r="1108" spans="1:16">
       <c r="A1108" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1108" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1108">
-        <v>1.5750931595105</v>
+        <v>1.512741454099611</v>
       </c>
       <c r="D1108" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1108">
-        <v>1.496767510539931</v>
+        <v>1.560288959725891</v>
       </c>
       <c r="F1108">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1108">
-        <v>0.0065249068404895</v>
+        <v>0.006467258545900389</v>
       </c>
       <c r="H1108">
-        <v>0.006583232489460069</v>
+        <v>0.006559711040274108</v>
       </c>
       <c r="I1108">
-        <v>0.07832564897056882</v>
+        <v>0.04754750562627974</v>
       </c>
       <c r="J1108">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1108">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1108">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="M1108">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N1108">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="O1108">
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>503</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
       <c r="A1109" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B1109" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C1109">
-        <v>1.573051853383038</v>
+        <v>1.512741454099611</v>
       </c>
       <c r="D1109" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1109">
-        <v>1.496767510539931</v>
+        <v>1.560288959725891</v>
       </c>
       <c r="F1109">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1109">
-        <v>0.006446948146616961</v>
+        <v>0.006467258545900389</v>
       </c>
       <c r="H1109">
-        <v>0.006583232489460069</v>
+        <v>0.006559711040274108</v>
       </c>
       <c r="I1109">
-        <v>0.07628434284310703</v>
+        <v>0.04754750562627974</v>
       </c>
       <c r="J1109">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1109">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="L1109">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1109">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N1109">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="O1109">
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>503</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
       <c r="A1110" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B1110" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C1110">
-        <v>1.573418808481069</v>
+        <v>1.622804794934651</v>
       </c>
       <c r="D1110" t="s">
         <v>379</v>
       </c>
       <c r="E1110">
-        <v>1.496767510539931</v>
+        <v>1.610352300560932</v>
       </c>
       <c r="F1110">
         <v>-1</v>
       </c>
       <c r="G1110">
-        <v>0.006386581191518931</v>
+        <v>0.006637195205065348</v>
       </c>
       <c r="H1110">
-        <v>0.006583232489460069</v>
+        <v>0.006669647699439068</v>
       </c>
       <c r="I1110">
-        <v>0.07665129794113801</v>
+        <v>0.01245249437371942</v>
       </c>
       <c r="J1110">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1110">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="L1110">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="M1110">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N1110">
-        <v>4.04</v>
+        <v>4.14</v>
       </c>
       <c r="O1110">
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>503</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1111" spans="1:16">
       <c r="A1111" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1111" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C1111">
-        <v>1.47676751053993</v>
+        <v>1.5750931595105</v>
       </c>
       <c r="D1111" t="s">
         <v>376</v>
       </c>
       <c r="E1111">
-        <v>1.527134465637961</v>
+        <v>1.527868375834023</v>
       </c>
       <c r="F1111">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1111">
-        <v>0.006563232489460068</v>
+        <v>0.0065249068404895</v>
       </c>
       <c r="H1111">
-        <v>0.006552865534362039</v>
+        <v>0.006432131624165977</v>
       </c>
       <c r="I1111">
-        <v>0.0503669550980308</v>
+        <v>0.04722478367647698</v>
       </c>
       <c r="J1111">
         <v>0.7591738774507669</v>
       </c>
       <c r="K1111">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="L1111">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="M1111">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N1111">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="O1111">
         <v>1</v>
@@ -57468,46 +57468,46 @@
     </row>
     <row r="1112" spans="1:16">
       <c r="A1112" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1112" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C1112">
-        <v>1.477134465637961</v>
+        <v>1.573051853383038</v>
       </c>
       <c r="D1112" t="s">
-        <v>227</v>
+        <v>376</v>
       </c>
       <c r="E1112">
-        <v>1.586767510539931</v>
+        <v>1.527868375834023</v>
       </c>
       <c r="F1112">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1112">
-        <v>0.006502865534362039</v>
+        <v>0.006446948146616961</v>
       </c>
       <c r="H1112">
-        <v>0.006673232489460069</v>
+        <v>0.006432131624165977</v>
       </c>
       <c r="I1112">
-        <v>0.1096330449019693</v>
+        <v>0.04518347754901519</v>
       </c>
       <c r="J1112">
         <v>0.7591738774507669</v>
       </c>
       <c r="K1112">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1112">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="M1112">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N1112">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1112">
         <v>1</v>
@@ -57518,196 +57518,196 @@
     </row>
     <row r="1113" spans="1:16">
       <c r="A1113" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1113" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C1113">
-        <v>1.560901809388644</v>
+        <v>1.573418808481069</v>
       </c>
       <c r="D1113" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E1113">
-        <v>1.513807620958687</v>
+        <v>1.496767510539931</v>
       </c>
       <c r="F1113">
         <v>-1</v>
       </c>
       <c r="G1113">
-        <v>0.006539098190611355</v>
+        <v>0.006386581191518931</v>
       </c>
       <c r="H1113">
-        <v>0.006446192379041313</v>
+        <v>0.006583232489460069</v>
       </c>
       <c r="I1113">
-        <v>0.04709418842995694</v>
+        <v>0.07665129794113801</v>
       </c>
       <c r="J1113">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1113">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1113">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1113">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1113">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1113">
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
       <c r="A1114" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1114" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C1114">
-        <v>1.559078162005382</v>
+        <v>1.47676751053993</v>
       </c>
       <c r="D1114" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E1114">
-        <v>1.513807620958687</v>
+        <v>1.5350931595105</v>
       </c>
       <c r="F1114">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1114">
-        <v>0.006460921837994617</v>
+        <v>0.006563232489460068</v>
       </c>
       <c r="H1114">
-        <v>0.006446192379041313</v>
+        <v>0.0064849068404895</v>
       </c>
       <c r="I1114">
-        <v>0.04527054104669537</v>
+        <v>0.05832564897056924</v>
       </c>
       <c r="J1114">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1114">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="L1114">
+        <v>4.02</v>
+      </c>
+      <c r="M1114">
+        <v>3.26</v>
+      </c>
+      <c r="N1114">
         <v>4.01</v>
       </c>
-      <c r="M1114">
-        <v>3.23</v>
-      </c>
-      <c r="N1114">
-        <v>3.98</v>
-      </c>
       <c r="O1114">
         <v>1</v>
       </c>
       <c r="P1114" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1115" spans="1:16">
       <c r="A1115" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1115" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C1115">
-        <v>1.559619244098773</v>
+        <v>1.477134465637961</v>
       </c>
       <c r="D1115" t="s">
-        <v>379</v>
+        <v>227</v>
       </c>
       <c r="E1115">
-        <v>1.482184374678515</v>
+        <v>1.586767510539931</v>
       </c>
       <c r="F1115">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1115">
-        <v>0.006400380755901226</v>
+        <v>0.006502865534362039</v>
       </c>
       <c r="H1115">
-        <v>0.006597815625321486</v>
+        <v>0.006673232489460069</v>
       </c>
       <c r="I1115">
-        <v>0.07743486942025868</v>
+        <v>0.1096330449019693</v>
       </c>
       <c r="J1115">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1115">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1115">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1115">
         <v>3.35</v>
       </c>
       <c r="N1115">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="O1115">
         <v>1</v>
       </c>
       <c r="P1115" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1116" spans="1:16">
       <c r="A1116" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1116" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C1116">
-        <v>1.462184374678514</v>
+        <v>1.560901809388644</v>
       </c>
       <c r="D1116" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E1116">
-        <v>1.520901809388644</v>
+        <v>1.513807620958687</v>
       </c>
       <c r="F1116">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1116">
-        <v>0.006577815625321485</v>
+        <v>0.006539098190611355</v>
       </c>
       <c r="H1116">
-        <v>0.006499098190611357</v>
+        <v>0.006446192379041313</v>
       </c>
       <c r="I1116">
-        <v>0.0587174347101298</v>
+        <v>0.04709418842995694</v>
       </c>
       <c r="J1116">
         <v>0.7635270523347718</v>
       </c>
       <c r="K1116">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="L1116">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="M1116">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="N1116">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1116">
         <v>1</v>
@@ -57718,46 +57718,46 @@
     </row>
     <row r="1117" spans="1:16">
       <c r="A1117" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1117" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C1117">
-        <v>1.462725456771905</v>
+        <v>1.559078162005382</v>
       </c>
       <c r="D1117" t="s">
-        <v>227</v>
+        <v>376</v>
       </c>
       <c r="E1117">
-        <v>1.572184374678514</v>
+        <v>1.513807620958687</v>
       </c>
       <c r="F1117">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1117">
-        <v>0.006517274543228095</v>
+        <v>0.006460921837994617</v>
       </c>
       <c r="H1117">
-        <v>0.006687815625321486</v>
+        <v>0.006446192379041313</v>
       </c>
       <c r="I1117">
-        <v>0.109458917906609</v>
+        <v>0.04527054104669537</v>
       </c>
       <c r="J1117">
         <v>0.7635270523347718</v>
       </c>
       <c r="K1117">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1117">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="M1117">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N1117">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1117">
         <v>1</v>
@@ -57768,346 +57768,346 @@
     </row>
     <row r="1118" spans="1:16">
       <c r="A1118" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1118" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C1118">
-        <v>1.553174199563495</v>
+        <v>1.559619244098773</v>
       </c>
       <c r="D1118" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E1118">
-        <v>1.50615112410739</v>
+        <v>1.482184374678515</v>
       </c>
       <c r="F1118">
         <v>-1</v>
       </c>
       <c r="G1118">
-        <v>0.006546825800436505</v>
+        <v>0.006400380755901226</v>
       </c>
       <c r="H1118">
-        <v>0.006453848875892611</v>
+        <v>0.006597815625321486</v>
       </c>
       <c r="I1118">
-        <v>0.04702307545610562</v>
+        <v>0.07743486942025868</v>
       </c>
       <c r="J1118">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1118">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1118">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1118">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1118">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1118">
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>372</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
       <c r="A1119" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1119" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C1119">
-        <v>1.551469073803319</v>
+        <v>1.462725456771905</v>
       </c>
       <c r="D1119" t="s">
-        <v>373</v>
+        <v>227</v>
       </c>
       <c r="E1119">
-        <v>1.50615112410739</v>
+        <v>1.572184374678514</v>
       </c>
       <c r="F1119">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1119">
-        <v>0.006468530926196681</v>
+        <v>0.006517274543228095</v>
       </c>
       <c r="H1119">
-        <v>0.006453848875892611</v>
+        <v>0.006687815625321486</v>
       </c>
       <c r="I1119">
-        <v>0.04531794969592928</v>
+        <v>0.109458917906609</v>
       </c>
       <c r="J1119">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1119">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="L1119">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1119">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1119">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="O1119">
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>372</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
       <c r="A1120" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1120" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C1120">
-        <v>1.552104973195178</v>
+        <v>1.553174199563495</v>
       </c>
       <c r="D1120" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E1120">
-        <v>1.474243425931813</v>
+        <v>1.50615112410739</v>
       </c>
       <c r="F1120">
         <v>-1</v>
       </c>
       <c r="G1120">
-        <v>0.006407895026804822</v>
+        <v>0.006546825800436505</v>
       </c>
       <c r="H1120">
-        <v>0.006605756574068187</v>
+        <v>0.006453848875892611</v>
       </c>
       <c r="I1120">
-        <v>0.07786154726336525</v>
+        <v>0.04702307545610562</v>
       </c>
       <c r="J1120">
         <v>0.7658974847964738</v>
       </c>
       <c r="K1120">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L1120">
+        <v>4.05</v>
+      </c>
+      <c r="M1120">
+        <v>3.23</v>
+      </c>
+      <c r="N1120">
         <v>3.98</v>
       </c>
-      <c r="M1120">
-        <v>3.35</v>
-      </c>
-      <c r="N1120">
-        <v>4.04</v>
-      </c>
       <c r="O1120">
         <v>1</v>
       </c>
       <c r="P1120" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1121" spans="1:16">
       <c r="A1121" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1121" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C1121">
-        <v>1.454879325323672</v>
+        <v>1.551469073803319</v>
       </c>
       <c r="D1121" t="s">
-        <v>227</v>
+        <v>376</v>
       </c>
       <c r="E1121">
-        <v>1.564243425931813</v>
+        <v>1.50615112410739</v>
       </c>
       <c r="F1121">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1121">
-        <v>0.006525120674676328</v>
+        <v>0.006468530926196681</v>
       </c>
       <c r="H1121">
-        <v>0.006695756574068187</v>
+        <v>0.006453848875892611</v>
       </c>
       <c r="I1121">
-        <v>0.1093641006081407</v>
+        <v>0.04531794969592928</v>
       </c>
       <c r="J1121">
         <v>0.7658974847964738</v>
       </c>
       <c r="K1121">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1121">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="M1121">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N1121">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1121">
         <v>1</v>
       </c>
       <c r="P1121" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1122" spans="1:16">
       <c r="A1122" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1122" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C1122">
-        <v>1.54817973372066</v>
+        <v>1.552104973195178</v>
       </c>
       <c r="D1122" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E1122">
-        <v>1.501202619606667</v>
+        <v>1.474243425931813</v>
       </c>
       <c r="F1122">
         <v>-1</v>
       </c>
       <c r="G1122">
-        <v>0.00655182026627934</v>
+        <v>0.006407895026804822</v>
       </c>
       <c r="H1122">
-        <v>0.006458797380393334</v>
+        <v>0.006605756574068187</v>
       </c>
       <c r="I1122">
-        <v>0.04697711411399341</v>
+        <v>0.07786154726336525</v>
       </c>
       <c r="J1122">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1122">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1122">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1122">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1122">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1122">
         <v>1</v>
       </c>
       <c r="P1122" t="s">
-        <v>505</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1123" spans="1:16">
       <c r="A1123" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1123" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C1123">
-        <v>1.546551210197337</v>
+        <v>1.454879325323672</v>
       </c>
       <c r="D1123" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1123">
+        <v>1.564243425931813</v>
+      </c>
+      <c r="F1123">
+        <v>1</v>
+      </c>
+      <c r="G1123">
+        <v>0.006525120674676328</v>
+      </c>
+      <c r="H1123">
+        <v>0.006695756574068187</v>
+      </c>
+      <c r="I1123">
+        <v>0.1093641006081407</v>
+      </c>
+      <c r="J1123">
+        <v>0.7658974847964738</v>
+      </c>
+      <c r="K1123">
+        <v>3.31</v>
+      </c>
+      <c r="L1123">
+        <v>3.99</v>
+      </c>
+      <c r="M1123">
+        <v>3.35</v>
+      </c>
+      <c r="N1123">
+        <v>4.13</v>
+      </c>
+      <c r="O1123">
+        <v>1</v>
+      </c>
+      <c r="P1123" t="s">
         <v>373</v>
-      </c>
-      <c r="E1123">
-        <v>1.501202619606667</v>
-      </c>
-      <c r="F1123">
-        <v>-1</v>
-      </c>
-      <c r="G1123">
-        <v>0.006473448789802663</v>
-      </c>
-      <c r="H1123">
-        <v>0.006458797380393334</v>
-      </c>
-      <c r="I1123">
-        <v>0.04534859059067031</v>
-      </c>
-      <c r="J1123">
-        <v>0.7674295295335398</v>
-      </c>
-      <c r="K1123">
-        <v>3.21</v>
-      </c>
-      <c r="L1123">
-        <v>4.01</v>
-      </c>
-      <c r="M1123">
-        <v>3.23</v>
-      </c>
-      <c r="N1123">
-        <v>3.98</v>
-      </c>
-      <c r="O1123">
-        <v>1</v>
-      </c>
-      <c r="P1123" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="1124" spans="1:16">
       <c r="A1124" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1124" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C1124">
-        <v>1.547248391378679</v>
+        <v>1.54817973372066</v>
       </c>
       <c r="D1124" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E1124">
-        <v>1.469111076062641</v>
+        <v>1.501202619606667</v>
       </c>
       <c r="F1124">
         <v>-1</v>
       </c>
       <c r="G1124">
-        <v>0.00641275160862132</v>
+        <v>0.00655182026627934</v>
       </c>
       <c r="H1124">
-        <v>0.006610888923937359</v>
+        <v>0.006458797380393334</v>
       </c>
       <c r="I1124">
-        <v>0.07813731531603763</v>
+        <v>0.04697711411399341</v>
       </c>
       <c r="J1124">
         <v>0.7674295295335398</v>
       </c>
       <c r="K1124">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L1124">
+        <v>4.05</v>
+      </c>
+      <c r="M1124">
+        <v>3.23</v>
+      </c>
+      <c r="N1124">
         <v>3.98</v>
-      </c>
-      <c r="M1124">
-        <v>3.35</v>
-      </c>
-      <c r="N1124">
-        <v>4.04</v>
       </c>
       <c r="O1124">
         <v>1</v>
@@ -58118,46 +58118,46 @@
     </row>
     <row r="1125" spans="1:16">
       <c r="A1125" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1125" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C1125">
-        <v>1.449808257243983</v>
+        <v>1.546551210197337</v>
       </c>
       <c r="D1125" t="s">
-        <v>227</v>
+        <v>376</v>
       </c>
       <c r="E1125">
-        <v>1.559111076062641</v>
+        <v>1.501202619606667</v>
       </c>
       <c r="F1125">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1125">
-        <v>0.006530191742756017</v>
+        <v>0.006473448789802663</v>
       </c>
       <c r="H1125">
-        <v>0.006700888923937358</v>
+        <v>0.006458797380393334</v>
       </c>
       <c r="I1125">
-        <v>0.1093028188186578</v>
+        <v>0.04534859059067031</v>
       </c>
       <c r="J1125">
         <v>0.7674295295335398</v>
       </c>
       <c r="K1125">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1125">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="M1125">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N1125">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1125">
         <v>1</v>
@@ -58168,496 +58168,496 @@
     </row>
     <row r="1126" spans="1:16">
       <c r="A1126" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1126" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C1126">
-        <v>1.544139279885719</v>
+        <v>1.547248391378679</v>
       </c>
       <c r="D1126" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E1126">
-        <v>1.49719934786223</v>
+        <v>1.469111076062641</v>
       </c>
       <c r="F1126">
         <v>-1</v>
       </c>
       <c r="G1126">
-        <v>0.006555860720114281</v>
+        <v>0.00641275160862132</v>
       </c>
       <c r="H1126">
-        <v>0.006462800652137769</v>
+        <v>0.006610888923937359</v>
       </c>
       <c r="I1126">
-        <v>0.04693993202348823</v>
+        <v>0.07813731531603763</v>
       </c>
       <c r="J1126">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1126">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="L1126">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M1126">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1126">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1126">
         <v>1</v>
       </c>
       <c r="P1126" t="s">
-        <v>228</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1127" spans="1:16">
       <c r="A1127" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1127" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C1127">
-        <v>1.542572726513238</v>
+        <v>1.449808257243983</v>
       </c>
       <c r="D1127" t="s">
-        <v>373</v>
+        <v>227</v>
       </c>
       <c r="E1127">
-        <v>1.49719934786223</v>
+        <v>1.559111076062641</v>
       </c>
       <c r="F1127">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1127">
-        <v>0.006477427273486762</v>
+        <v>0.006530191742756017</v>
       </c>
       <c r="H1127">
-        <v>0.006462800652137769</v>
+        <v>0.006700888923937358</v>
       </c>
       <c r="I1127">
-        <v>0.04537337865100755</v>
+        <v>0.1093028188186578</v>
       </c>
       <c r="J1127">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1127">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="L1127">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M1127">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1127">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="O1127">
         <v>1</v>
       </c>
       <c r="P1127" t="s">
-        <v>228</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1128" spans="1:16">
       <c r="A1128" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1128" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C1128">
-        <v>1.543319483815254</v>
+        <v>1.544139279885719</v>
       </c>
       <c r="D1128" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E1128">
-        <v>1.464959075956183</v>
+        <v>1.49719934786223</v>
       </c>
       <c r="F1128">
         <v>-1</v>
       </c>
       <c r="G1128">
-        <v>0.006416680516184746</v>
+        <v>0.006555860720114281</v>
       </c>
       <c r="H1128">
-        <v>0.006615040924043817</v>
+        <v>0.006462800652137769</v>
       </c>
       <c r="I1128">
-        <v>0.07836040785907095</v>
+        <v>0.04693993202348823</v>
       </c>
       <c r="J1128">
         <v>0.7686689325503931</v>
       </c>
       <c r="K1128">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L1128">
+        <v>4.05</v>
+      </c>
+      <c r="M1128">
+        <v>3.23</v>
+      </c>
+      <c r="N1128">
         <v>3.98</v>
       </c>
-      <c r="M1128">
-        <v>3.35</v>
-      </c>
-      <c r="N1128">
-        <v>4.04</v>
-      </c>
       <c r="O1128">
         <v>1</v>
       </c>
       <c r="P1128" t="s">
-        <v>228</v>
+        <v>371</v>
       </c>
     </row>
     <row r="1129" spans="1:16">
       <c r="A1129" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1129" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C1129">
-        <v>1.445705833258199</v>
+        <v>1.542572726513238</v>
       </c>
       <c r="D1129" t="s">
-        <v>227</v>
+        <v>376</v>
       </c>
       <c r="E1129">
-        <v>1.554959075956183</v>
+        <v>1.49719934786223</v>
       </c>
       <c r="F1129">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1129">
-        <v>0.006534294166741802</v>
+        <v>0.006477427273486762</v>
       </c>
       <c r="H1129">
-        <v>0.006705040924043817</v>
+        <v>0.006462800652137769</v>
       </c>
       <c r="I1129">
-        <v>0.1092532426979842</v>
+        <v>0.04537337865100755</v>
       </c>
       <c r="J1129">
         <v>0.7686689325503931</v>
       </c>
       <c r="K1129">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1129">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="M1129">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N1129">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1129">
         <v>1</v>
       </c>
       <c r="P1129" t="s">
-        <v>228</v>
+        <v>371</v>
       </c>
     </row>
     <row r="1130" spans="1:16">
       <c r="A1130" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1130" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C1130">
-        <v>1.542905840445619</v>
+        <v>1.543319483815254</v>
       </c>
       <c r="D1130" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E1130">
-        <v>1.497534537270826</v>
+        <v>1.464959075956183</v>
       </c>
       <c r="F1130">
         <v>-1</v>
       </c>
       <c r="G1130">
-        <v>0.006477094159554382</v>
+        <v>0.006416680516184746</v>
       </c>
       <c r="H1130">
-        <v>0.006462465462729174</v>
+        <v>0.006615040924043817</v>
       </c>
       <c r="I1130">
-        <v>0.0453713031747931</v>
+        <v>0.07836040785907095</v>
       </c>
       <c r="J1130">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1130">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1130">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1130">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1130">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1130">
         <v>1</v>
       </c>
       <c r="P1130" t="s">
-        <v>222</v>
+        <v>371</v>
       </c>
     </row>
     <row r="1131" spans="1:16">
       <c r="A1131" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1131" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C1131">
-        <v>1.543648446795206</v>
+        <v>1.445705833258199</v>
       </c>
       <c r="D1131" t="s">
-        <v>379</v>
+        <v>227</v>
       </c>
       <c r="E1131">
-        <v>1.465306718222064</v>
+        <v>1.554959075956183</v>
       </c>
       <c r="F1131">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1131">
-        <v>0.006416351553204793</v>
+        <v>0.006534294166741802</v>
       </c>
       <c r="H1131">
-        <v>0.006614693281777937</v>
+        <v>0.006705040924043817</v>
       </c>
       <c r="I1131">
-        <v>0.0783417285731427</v>
+        <v>0.1092532426979842</v>
       </c>
       <c r="J1131">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1131">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1131">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1131">
         <v>3.35</v>
       </c>
       <c r="N1131">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="O1131">
         <v>1</v>
       </c>
       <c r="P1131" t="s">
-        <v>222</v>
+        <v>371</v>
       </c>
     </row>
     <row r="1132" spans="1:16">
       <c r="A1132" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1132" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C1132">
-        <v>1.446049324571651</v>
+        <v>1.542905840445619</v>
       </c>
       <c r="D1132" t="s">
-        <v>227</v>
+        <v>376</v>
       </c>
       <c r="E1132">
-        <v>1.555306718222063</v>
+        <v>1.497534537270826</v>
       </c>
       <c r="F1132">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1132">
-        <v>0.00653395067542835</v>
+        <v>0.006477094159554382</v>
       </c>
       <c r="H1132">
-        <v>0.006704693281777937</v>
+        <v>0.006462465462729174</v>
       </c>
       <c r="I1132">
-        <v>0.1092573936504126</v>
+        <v>0.0453713031747931</v>
       </c>
       <c r="J1132">
         <v>0.7685651587396826</v>
       </c>
       <c r="K1132">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1132">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="M1132">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N1132">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1132">
         <v>1</v>
       </c>
       <c r="P1132" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1133" spans="1:16">
       <c r="A1133" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1133" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C1133">
-        <v>1.54632868625525</v>
+        <v>1.543648446795206</v>
       </c>
       <c r="D1133" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E1133">
-        <v>1.500978709222573</v>
+        <v>1.465306718222064</v>
       </c>
       <c r="F1133">
         <v>-1</v>
       </c>
       <c r="G1133">
-        <v>0.006473671313744749</v>
+        <v>0.006416351553204793</v>
       </c>
       <c r="H1133">
-        <v>0.006459021290777427</v>
+        <v>0.006614693281777937</v>
       </c>
       <c r="I1133">
-        <v>0.04534997703267729</v>
+        <v>0.0783417285731427</v>
       </c>
       <c r="J1133">
-        <v>0.7674988516338783</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1133">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1133">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="M1133">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N1133">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="O1133">
         <v>1</v>
       </c>
       <c r="P1133" t="s">
-        <v>506</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1134" spans="1:16">
       <c r="A1134" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1134" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C1134">
-        <v>1.547028640320606</v>
+        <v>1.446049324571651</v>
       </c>
       <c r="D1134" t="s">
-        <v>379</v>
+        <v>227</v>
       </c>
       <c r="E1134">
-        <v>1.468878847026508</v>
+        <v>1.555306718222063</v>
       </c>
       <c r="F1134">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1134">
-        <v>0.006412971359679395</v>
+        <v>0.00653395067542835</v>
       </c>
       <c r="H1134">
-        <v>0.006611121152973493</v>
+        <v>0.006704693281777937</v>
       </c>
       <c r="I1134">
-        <v>0.07814979329409821</v>
+        <v>0.1092573936504126</v>
       </c>
       <c r="J1134">
-        <v>0.7674988516338783</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1134">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1134">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1134">
         <v>3.35</v>
       </c>
       <c r="N1134">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="O1134">
         <v>1</v>
       </c>
       <c r="P1134" t="s">
-        <v>506</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1135" spans="1:16">
       <c r="A1135" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1135" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C1135">
-        <v>1.448878847026507</v>
+        <v>1.54632868625525</v>
       </c>
       <c r="D1135" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E1135">
-        <v>1.507953743673557</v>
+        <v>1.500978709222573</v>
       </c>
       <c r="F1135">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1135">
-        <v>0.006591121152973492</v>
+        <v>0.006473671313744749</v>
       </c>
       <c r="H1135">
-        <v>0.006512046256326442</v>
+        <v>0.006459021290777427</v>
       </c>
       <c r="I1135">
-        <v>0.05907489664704935</v>
+        <v>0.04534997703267729</v>
       </c>
       <c r="J1135">
         <v>0.7674988516338783</v>
       </c>
       <c r="K1135">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="L1135">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="M1135">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="N1135">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="O1135">
         <v>1</v>
@@ -58668,46 +58668,46 @@
     </row>
     <row r="1136" spans="1:16">
       <c r="A1136" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1136" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C1136">
-        <v>1.449578801091863</v>
+        <v>1.547028640320606</v>
       </c>
       <c r="D1136" t="s">
-        <v>227</v>
+        <v>380</v>
       </c>
       <c r="E1136">
-        <v>1.558878847026508</v>
+        <v>1.468878847026508</v>
       </c>
       <c r="F1136">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1136">
-        <v>0.006530421198908138</v>
+        <v>0.006412971359679395</v>
       </c>
       <c r="H1136">
-        <v>0.006701121152973492</v>
+        <v>0.006611121152973493</v>
       </c>
       <c r="I1136">
-        <v>0.1093000459346447</v>
+        <v>0.07814979329409821</v>
       </c>
       <c r="J1136">
         <v>0.7674988516338783</v>
       </c>
       <c r="K1136">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="L1136">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1136">
         <v>3.35</v>
       </c>
       <c r="N1136">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
       <c r="O1136">
         <v>1</v>
@@ -58718,243 +58718,243 @@
     </row>
     <row r="1137" spans="1:16">
       <c r="A1137" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1137" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C1137">
-        <v>1.54143940139528</v>
+        <v>1.449578801091863</v>
       </c>
       <c r="D1137" t="s">
-        <v>379</v>
+        <v>227</v>
       </c>
       <c r="E1137">
-        <v>1.462972238067567</v>
+        <v>1.558878847026508</v>
       </c>
       <c r="F1137">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1137">
-        <v>0.00641856059860472</v>
+        <v>0.006530421198908138</v>
       </c>
       <c r="H1137">
-        <v>0.006617027761932433</v>
+        <v>0.006701121152973492</v>
       </c>
       <c r="I1137">
-        <v>0.07846716332771297</v>
+        <v>0.1093000459346447</v>
       </c>
       <c r="J1137">
-        <v>0.7692620184872934</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1137">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1137">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1137">
         <v>3.35</v>
       </c>
       <c r="N1137">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="O1137">
         <v>1</v>
       </c>
       <c r="P1137" t="s">
-        <v>226</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1138" spans="1:16">
       <c r="A1138" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1138" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C1138">
-        <v>1.442972238067567</v>
+        <v>1.54143940139528</v>
       </c>
       <c r="D1138" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E1138">
-        <v>1.502205819731424</v>
+        <v>1.462972238067567</v>
       </c>
       <c r="F1138">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1138">
-        <v>0.006597027761932432</v>
+        <v>0.00641856059860472</v>
       </c>
       <c r="H1138">
-        <v>0.006517794180268576</v>
+        <v>0.006617027761932433</v>
       </c>
       <c r="I1138">
-        <v>0.05923358166385695</v>
+        <v>0.07846716332771297</v>
       </c>
       <c r="J1138">
         <v>0.7692620184872934</v>
       </c>
       <c r="K1138">
+        <v>3.17</v>
+      </c>
+      <c r="L1138">
+        <v>3.98</v>
+      </c>
+      <c r="M1138">
         <v>3.35</v>
       </c>
-      <c r="L1138">
-        <v>4.02</v>
-      </c>
-      <c r="M1138">
-        <v>3.26</v>
-      </c>
       <c r="N1138">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="O1138">
         <v>1</v>
       </c>
       <c r="P1138" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1139" spans="1:16">
       <c r="A1139" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1139" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1139">
-        <v>1.443742718807059</v>
+        <v>1.442972238067567</v>
       </c>
       <c r="D1139" t="s">
-        <v>227</v>
+        <v>374</v>
       </c>
       <c r="E1139">
-        <v>1.552972238067567</v>
+        <v>1.502205819731424</v>
       </c>
       <c r="F1139">
         <v>1</v>
       </c>
       <c r="G1139">
-        <v>0.006536257281192942</v>
+        <v>0.006597027761932432</v>
       </c>
       <c r="H1139">
-        <v>0.006707027761932433</v>
+        <v>0.006517794180268576</v>
       </c>
       <c r="I1139">
-        <v>0.1092295192605079</v>
+        <v>0.05923358166385695</v>
       </c>
       <c r="J1139">
         <v>0.7692620184872934</v>
       </c>
       <c r="K1139">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1139">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1139">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1139">
-        <v>4.13</v>
+        <v>4.01</v>
       </c>
       <c r="O1139">
         <v>1</v>
       </c>
       <c r="P1139" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1140" spans="1:16">
       <c r="A1140" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1140" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C1140">
-        <v>1.541874717879155</v>
+        <v>1.443742718807059</v>
       </c>
       <c r="D1140" t="s">
-        <v>379</v>
+        <v>227</v>
       </c>
       <c r="E1140">
-        <v>1.463432272837593</v>
+        <v>1.552972238067567</v>
       </c>
       <c r="F1140">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1140">
-        <v>0.006418125282120845</v>
+        <v>0.006536257281192942</v>
       </c>
       <c r="H1140">
-        <v>0.006616567727162407</v>
+        <v>0.006707027761932433</v>
       </c>
       <c r="I1140">
-        <v>0.07844244504156217</v>
+        <v>0.1092295192605079</v>
       </c>
       <c r="J1140">
-        <v>0.7691246946753454</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1140">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1140">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1140">
         <v>3.35</v>
       </c>
       <c r="N1140">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="O1140">
         <v>1</v>
       </c>
       <c r="P1140" t="s">
-        <v>507</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1141" spans="1:16">
       <c r="A1141" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1141" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C1141">
-        <v>1.443432272837593</v>
+        <v>1.541874717879155</v>
       </c>
       <c r="D1141" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E1141">
-        <v>1.494197260624607</v>
+        <v>1.463432272837593</v>
       </c>
       <c r="F1141">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1141">
-        <v>0.006596567727162407</v>
+        <v>0.006418125282120845</v>
       </c>
       <c r="H1141">
-        <v>0.006585802739375394</v>
+        <v>0.006616567727162407</v>
       </c>
       <c r="I1141">
-        <v>0.05076498778701399</v>
+        <v>0.07844244504156217</v>
       </c>
       <c r="J1141">
         <v>0.7691246946753454</v>
       </c>
       <c r="K1141">
+        <v>3.17</v>
+      </c>
+      <c r="L1141">
+        <v>3.98</v>
+      </c>
+      <c r="M1141">
         <v>3.35</v>
-      </c>
-      <c r="L1141">
-        <v>4.02</v>
-      </c>
-      <c r="M1141">
-        <v>3.31</v>
       </c>
       <c r="N1141">
         <v>4.04</v>
@@ -58963,148 +58963,148 @@
         <v>1</v>
       </c>
       <c r="P1141" t="s">
-        <v>507</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1142" spans="1:16">
       <c r="A1142" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1142" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1142">
-        <v>1.444197260624607</v>
+        <v>1.443432272837593</v>
       </c>
       <c r="D1142" t="s">
-        <v>227</v>
+        <v>374</v>
       </c>
       <c r="E1142">
-        <v>1.553432272837593</v>
+        <v>1.502653495358374</v>
       </c>
       <c r="F1142">
         <v>1</v>
       </c>
       <c r="G1142">
-        <v>0.006535802739375394</v>
+        <v>0.006596567727162407</v>
       </c>
       <c r="H1142">
-        <v>0.006706567727162407</v>
+        <v>0.006517346504641626</v>
       </c>
       <c r="I1142">
-        <v>0.1092350122129861</v>
+        <v>0.05922122252078132</v>
       </c>
       <c r="J1142">
         <v>0.7691246946753454</v>
       </c>
       <c r="K1142">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1142">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1142">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1142">
-        <v>4.13</v>
+        <v>4.01</v>
       </c>
       <c r="O1142">
         <v>1</v>
       </c>
       <c r="P1142" t="s">
-        <v>507</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1143" spans="1:16">
       <c r="A1143" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1143" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C1143">
-        <v>1.531416807455531</v>
+        <v>1.444197260624607</v>
       </c>
       <c r="D1143" t="s">
-        <v>379</v>
+        <v>227</v>
       </c>
       <c r="E1143">
-        <v>1.452380537847327</v>
+        <v>1.553432272837593</v>
       </c>
       <c r="F1143">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1143">
-        <v>0.006428583192544469</v>
+        <v>0.006535802739375394</v>
       </c>
       <c r="H1143">
-        <v>0.006627619462152673</v>
+        <v>0.006706567727162407</v>
       </c>
       <c r="I1143">
-        <v>0.07903626960820365</v>
+        <v>0.1092350122129861</v>
       </c>
       <c r="J1143">
-        <v>0.772423720045574</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1143">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="L1143">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1143">
         <v>3.35</v>
       </c>
       <c r="N1143">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="O1143">
         <v>1</v>
       </c>
       <c r="P1143" t="s">
-        <v>373</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1144" spans="1:16">
       <c r="A1144" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1144" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C1144">
-        <v>1.432380537847326</v>
+        <v>1.531416807455531</v>
       </c>
       <c r="D1144" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E1144">
-        <v>1.48327748664915</v>
+        <v>1.452380537847327</v>
       </c>
       <c r="F1144">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1144">
-        <v>0.006607619462152673</v>
+        <v>0.006428583192544469</v>
       </c>
       <c r="H1144">
-        <v>0.00659672251335085</v>
+        <v>0.006627619462152673</v>
       </c>
       <c r="I1144">
-        <v>0.0508969488018236</v>
+        <v>0.07903626960820365</v>
       </c>
       <c r="J1144">
         <v>0.772423720045574</v>
       </c>
       <c r="K1144">
+        <v>3.17</v>
+      </c>
+      <c r="L1144">
+        <v>3.98</v>
+      </c>
+      <c r="M1144">
         <v>3.35</v>
-      </c>
-      <c r="L1144">
-        <v>4.02</v>
-      </c>
-      <c r="M1144">
-        <v>3.31</v>
       </c>
       <c r="N1144">
         <v>4.04</v>
@@ -59113,98 +59113,98 @@
         <v>1</v>
       </c>
       <c r="P1144" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="1145" spans="1:16">
       <c r="A1145" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1145" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1145">
-        <v>1.43327748664915</v>
+        <v>1.432380537847326</v>
       </c>
       <c r="D1145" t="s">
         <v>377</v>
       </c>
       <c r="E1145">
-        <v>1.480104775047782</v>
+        <v>1.48327748664915</v>
       </c>
       <c r="F1145">
         <v>1</v>
       </c>
       <c r="G1145">
-        <v>0.006546722513350851</v>
+        <v>0.006607619462152673</v>
       </c>
       <c r="H1145">
-        <v>0.006639895224952217</v>
+        <v>0.00659672251335085</v>
       </c>
       <c r="I1145">
-        <v>0.04682728839863204</v>
+        <v>0.0508969488018236</v>
       </c>
       <c r="J1145">
         <v>0.772423720045574</v>
       </c>
       <c r="K1145">
+        <v>3.35</v>
+      </c>
+      <c r="L1145">
+        <v>4.02</v>
+      </c>
+      <c r="M1145">
         <v>3.31</v>
       </c>
-      <c r="L1145">
-        <v>3.99</v>
-      </c>
-      <c r="M1145">
-        <v>3.34</v>
-      </c>
       <c r="N1145">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="O1145">
         <v>1</v>
       </c>
       <c r="P1145" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="1146" spans="1:16">
       <c r="A1146" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1146" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1146">
+        <v>1.43327748664915</v>
+      </c>
+      <c r="D1146" t="s">
         <v>227</v>
       </c>
-      <c r="C1146">
+      <c r="E1146">
         <v>1.542380537847327</v>
       </c>
-      <c r="D1146" t="s">
-        <v>378</v>
-      </c>
-      <c r="E1146">
-        <v>1.51920782624596</v>
-      </c>
       <c r="F1146">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1146">
+        <v>0.006546722513350851</v>
+      </c>
+      <c r="H1146">
         <v>0.006717619462152673</v>
       </c>
-      <c r="H1146">
-        <v>0.00674079217375404</v>
-      </c>
       <c r="I1146">
-        <v>0.02317271160136691</v>
+        <v>0.1091030511981765</v>
       </c>
       <c r="J1146">
         <v>0.772423720045574</v>
       </c>
       <c r="K1146">
+        <v>3.31</v>
+      </c>
+      <c r="L1146">
+        <v>3.99</v>
+      </c>
+      <c r="M1146">
         <v>3.35</v>
-      </c>
-      <c r="L1146">
-        <v>4.13</v>
-      </c>
-      <c r="M1146">
-        <v>3.38</v>
       </c>
       <c r="N1146">
         <v>4.13</v>
@@ -59213,7 +59213,7 @@
         <v>1</v>
       </c>
       <c r="P1146" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="1147" spans="1:16">
@@ -59227,7 +59227,7 @@
         <v>1.530293964951826</v>
       </c>
       <c r="D1147" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1147">
         <v>1.451193937725116</v>
@@ -59263,7 +59263,7 @@
         <v>1</v>
       </c>
       <c r="P1147" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1148" spans="1:16">
@@ -59271,13 +59271,13 @@
         <v>1</v>
       </c>
       <c r="B1148" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C1148">
         <v>1.431193937725116</v>
       </c>
       <c r="D1148" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E1148">
         <v>1.482105054886607</v>
@@ -59313,7 +59313,7 @@
         <v>1</v>
       </c>
       <c r="P1148" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1149" spans="1:16">
@@ -59321,16 +59321,16 @@
         <v>2</v>
       </c>
       <c r="B1149" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C1149">
         <v>1.432105054886608</v>
       </c>
       <c r="D1149" t="s">
-        <v>377</v>
+        <v>227</v>
       </c>
       <c r="E1149">
-        <v>1.478921717015489</v>
+        <v>1.541193937725116</v>
       </c>
       <c r="F1149">
         <v>1</v>
@@ -59339,10 +59339,10 @@
         <v>0.006547894945113393</v>
       </c>
       <c r="H1149">
-        <v>0.006641078282984511</v>
+        <v>0.006718806062274884</v>
       </c>
       <c r="I1149">
-        <v>0.04681666212888125</v>
+        <v>0.1090888828385084</v>
       </c>
       <c r="J1149">
         <v>0.7727779290372787</v>
@@ -59354,107 +59354,107 @@
         <v>3.99</v>
       </c>
       <c r="M1149">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N1149">
-        <v>4.06</v>
+        <v>4.13</v>
       </c>
       <c r="O1149">
         <v>1</v>
       </c>
       <c r="P1149" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1150" spans="1:16">
       <c r="A1150" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1150" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C1150">
-        <v>1.432105054886608</v>
+        <v>1.432233461226324</v>
       </c>
       <c r="D1150" t="s">
         <v>377</v>
       </c>
       <c r="E1150">
-        <v>1.478921717015489</v>
+        <v>1.483132166166906</v>
       </c>
       <c r="F1150">
         <v>1</v>
       </c>
       <c r="G1150">
-        <v>0.006547894945113393</v>
+        <v>0.006607766538773674</v>
       </c>
       <c r="H1150">
-        <v>0.006641078282984511</v>
+        <v>0.006596867833833095</v>
       </c>
       <c r="I1150">
-        <v>0.04681666212888125</v>
+        <v>0.05089870494058157</v>
       </c>
       <c r="J1150">
-        <v>0.7727779290372787</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1150">
+        <v>3.35</v>
+      </c>
+      <c r="L1150">
+        <v>4.02</v>
+      </c>
+      <c r="M1150">
         <v>3.31</v>
       </c>
-      <c r="L1150">
-        <v>3.99</v>
-      </c>
-      <c r="M1150">
-        <v>3.34</v>
-      </c>
       <c r="N1150">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="O1150">
         <v>1</v>
       </c>
       <c r="P1150" t="s">
-        <v>508</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1151" spans="1:16">
       <c r="A1151" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1151" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1151">
+        <v>1.433132166166906</v>
+      </c>
+      <c r="D1151" t="s">
         <v>227</v>
       </c>
-      <c r="C1151">
-        <v>1.541193937725116</v>
-      </c>
-      <c r="D1151" t="s">
-        <v>378</v>
-      </c>
       <c r="E1151">
-        <v>1.518010599853998</v>
+        <v>1.542233461226325</v>
       </c>
       <c r="F1151">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1151">
-        <v>0.006718806062274884</v>
+        <v>0.006546867833833094</v>
       </c>
       <c r="H1151">
-        <v>0.006741989400146002</v>
+        <v>0.006717766538773676</v>
       </c>
       <c r="I1151">
-        <v>0.02318333787111815</v>
+        <v>0.1091012950594186</v>
       </c>
       <c r="J1151">
-        <v>0.7727779290372787</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1151">
+        <v>3.31</v>
+      </c>
+      <c r="L1151">
+        <v>3.99</v>
+      </c>
+      <c r="M1151">
         <v>3.35</v>
-      </c>
-      <c r="L1151">
-        <v>4.13</v>
-      </c>
-      <c r="M1151">
-        <v>3.38</v>
       </c>
       <c r="N1151">
         <v>4.13</v>
@@ -59463,51 +59463,51 @@
         <v>1</v>
       </c>
       <c r="P1151" t="s">
-        <v>508</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1152" spans="1:16">
       <c r="A1152" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1152" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C1152">
-        <v>1.432233461226324</v>
+        <v>1.433132166166906</v>
       </c>
       <c r="D1152" t="s">
-        <v>376</v>
+        <v>227</v>
       </c>
       <c r="E1152">
-        <v>1.483132166166906</v>
+        <v>1.542233461226325</v>
       </c>
       <c r="F1152">
         <v>1</v>
       </c>
       <c r="G1152">
-        <v>0.006607766538773674</v>
+        <v>0.006546867833833094</v>
       </c>
       <c r="H1152">
-        <v>0.006596867833833095</v>
+        <v>0.006717766538773676</v>
       </c>
       <c r="I1152">
-        <v>0.05089870494058157</v>
+        <v>0.1091012950594186</v>
       </c>
       <c r="J1152">
         <v>0.7724676235145299</v>
       </c>
       <c r="K1152">
+        <v>3.31</v>
+      </c>
+      <c r="L1152">
+        <v>3.99</v>
+      </c>
+      <c r="M1152">
         <v>3.35</v>
       </c>
-      <c r="L1152">
-        <v>4.02</v>
-      </c>
-      <c r="M1152">
-        <v>3.31</v>
-      </c>
       <c r="N1152">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="O1152">
         <v>1</v>
@@ -59518,84 +59518,84 @@
     </row>
     <row r="1153" spans="1:16">
       <c r="A1153" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1153" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1153">
-        <v>1.433132166166906</v>
+        <v>1.438192457750358</v>
       </c>
       <c r="D1153" t="s">
         <v>377</v>
       </c>
       <c r="E1153">
-        <v>1.47995813746147</v>
+        <v>1.489020010493638</v>
       </c>
       <c r="F1153">
         <v>1</v>
       </c>
       <c r="G1153">
-        <v>0.006546867833833094</v>
+        <v>0.00660180754224964</v>
       </c>
       <c r="H1153">
-        <v>0.006640041862538529</v>
+        <v>0.006590979989506363</v>
       </c>
       <c r="I1153">
-        <v>0.04682597129456356</v>
+        <v>0.05082755274327999</v>
       </c>
       <c r="J1153">
-        <v>0.7724676235145299</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1153">
+        <v>3.35</v>
+      </c>
+      <c r="L1153">
+        <v>4.02</v>
+      </c>
+      <c r="M1153">
         <v>3.31</v>
       </c>
-      <c r="L1153">
-        <v>3.99</v>
-      </c>
-      <c r="M1153">
-        <v>3.34</v>
-      </c>
       <c r="N1153">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="O1153">
         <v>1</v>
       </c>
       <c r="P1153" t="s">
-        <v>229</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1154" spans="1:16">
       <c r="A1154" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1154" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C1154">
-        <v>1.433132166166906</v>
+        <v>1.439020010493639</v>
       </c>
       <c r="D1154" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1154">
-        <v>1.47995813746147</v>
+        <v>1.485899345936179</v>
       </c>
       <c r="F1154">
         <v>1</v>
       </c>
       <c r="G1154">
-        <v>0.006546867833833094</v>
+        <v>0.006540979989506361</v>
       </c>
       <c r="H1154">
-        <v>0.006640041862538529</v>
+        <v>0.00663410065406382</v>
       </c>
       <c r="I1154">
-        <v>0.04682597129456356</v>
+        <v>0.04687933544254008</v>
       </c>
       <c r="J1154">
-        <v>0.7724676235145299</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1154">
         <v>3.31</v>
@@ -59613,86 +59613,86 @@
         <v>1</v>
       </c>
       <c r="P1154" t="s">
-        <v>229</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1155" spans="1:16">
       <c r="A1155" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1155" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C1155">
-        <v>1.542233461226325</v>
+        <v>1.439020010493639</v>
       </c>
       <c r="D1155" t="s">
         <v>378</v>
       </c>
       <c r="E1155">
-        <v>1.519059432520889</v>
+        <v>1.485899345936179</v>
       </c>
       <c r="F1155">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1155">
-        <v>0.006717766538773676</v>
+        <v>0.006540979989506361</v>
       </c>
       <c r="H1155">
-        <v>0.006740940567479111</v>
+        <v>0.00663410065406382</v>
       </c>
       <c r="I1155">
-        <v>0.02317402870543583</v>
+        <v>0.04687933544254008</v>
       </c>
       <c r="J1155">
-        <v>0.7724676235145299</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1155">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1155">
-        <v>4.13</v>
+        <v>3.99</v>
       </c>
       <c r="M1155">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="N1155">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="O1155">
         <v>1</v>
       </c>
       <c r="P1155" t="s">
-        <v>229</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1156" spans="1:16">
       <c r="A1156" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1156" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C1156">
-        <v>1.438192457750358</v>
+        <v>1.548192457750359</v>
       </c>
       <c r="D1156" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E1156">
-        <v>1.489020010493638</v>
+        <v>1.535071793192899</v>
       </c>
       <c r="F1156">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1156">
-        <v>0.00660180754224964</v>
+        <v>0.006711807542249641</v>
       </c>
       <c r="H1156">
-        <v>0.006590979989506363</v>
+        <v>0.0067449282068071</v>
       </c>
       <c r="I1156">
-        <v>0.05082755274327999</v>
+        <v>0.01312066455745953</v>
       </c>
       <c r="J1156">
         <v>0.7706888185819823</v>
@@ -59701,63 +59701,63 @@
         <v>3.35</v>
       </c>
       <c r="L1156">
-        <v>4.02</v>
+        <v>4.13</v>
       </c>
       <c r="M1156">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="N1156">
-        <v>4.04</v>
+        <v>4.14</v>
       </c>
       <c r="O1156">
         <v>1</v>
       </c>
       <c r="P1156" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1157" spans="1:16">
       <c r="A1157" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1157" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1157">
-        <v>1.439020010493639</v>
+        <v>1.442360905903367</v>
       </c>
       <c r="D1157" t="s">
         <v>377</v>
       </c>
       <c r="E1157">
-        <v>1.485899345936179</v>
+        <v>1.493138686131387</v>
       </c>
       <c r="F1157">
         <v>1</v>
       </c>
       <c r="G1157">
-        <v>0.006540979989506361</v>
+        <v>0.006597639094096632</v>
       </c>
       <c r="H1157">
-        <v>0.00663410065406382</v>
+        <v>0.006586861313868614</v>
       </c>
       <c r="I1157">
-        <v>0.04687933544254008</v>
+        <v>0.0507777802280196</v>
       </c>
       <c r="J1157">
-        <v>0.7706888185819823</v>
+        <v>0.7694445057004873</v>
       </c>
       <c r="K1157">
+        <v>3.35</v>
+      </c>
+      <c r="L1157">
+        <v>4.02</v>
+      </c>
+      <c r="M1157">
         <v>3.31</v>
       </c>
-      <c r="L1157">
-        <v>3.99</v>
-      </c>
-      <c r="M1157">
-        <v>3.34</v>
-      </c>
       <c r="N1157">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="O1157">
         <v>1</v>
@@ -59768,34 +59768,34 @@
     </row>
     <row r="1158" spans="1:16">
       <c r="A1158" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1158" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C1158">
-        <v>1.439020010493639</v>
+        <v>1.443138686131387</v>
       </c>
       <c r="D1158" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1158">
-        <v>1.485899345936179</v>
+        <v>1.490055350960372</v>
       </c>
       <c r="F1158">
         <v>1</v>
       </c>
       <c r="G1158">
-        <v>0.006540979989506361</v>
+        <v>0.006536861313868613</v>
       </c>
       <c r="H1158">
-        <v>0.00663410065406382</v>
+        <v>0.006629944649039627</v>
       </c>
       <c r="I1158">
-        <v>0.04687933544254008</v>
+        <v>0.04691666482898516</v>
       </c>
       <c r="J1158">
-        <v>0.7706888185819823</v>
+        <v>0.7694445057004873</v>
       </c>
       <c r="K1158">
         <v>3.31</v>
@@ -59818,46 +59818,46 @@
     </row>
     <row r="1159" spans="1:16">
       <c r="A1159" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1159" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C1159">
-        <v>1.548192457750359</v>
+        <v>1.443138686131387</v>
       </c>
       <c r="D1159" t="s">
         <v>378</v>
       </c>
       <c r="E1159">
-        <v>1.525071793192899</v>
+        <v>1.490055350960372</v>
       </c>
       <c r="F1159">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1159">
-        <v>0.006711807542249641</v>
+        <v>0.006536861313868613</v>
       </c>
       <c r="H1159">
-        <v>0.0067349282068071</v>
+        <v>0.006629944649039627</v>
       </c>
       <c r="I1159">
-        <v>0.02312066455745931</v>
+        <v>0.04691666482898516</v>
       </c>
       <c r="J1159">
-        <v>0.7706888185819823</v>
+        <v>0.7694445057004873</v>
       </c>
       <c r="K1159">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1159">
-        <v>4.13</v>
+        <v>3.99</v>
       </c>
       <c r="M1159">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="N1159">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="O1159">
         <v>1</v>
@@ -59868,31 +59868,31 @@
     </row>
     <row r="1160" spans="1:16">
       <c r="A1160" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1160" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C1160">
-        <v>1.442360905903367</v>
+        <v>1.552360905903368</v>
       </c>
       <c r="D1160" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E1160">
-        <v>1.483138686131387</v>
+        <v>1.539277570732353</v>
       </c>
       <c r="F1160">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1160">
-        <v>0.006597639094096632</v>
+        <v>0.006707639094096632</v>
       </c>
       <c r="H1160">
-        <v>0.006576861313868614</v>
+        <v>0.006740722429267647</v>
       </c>
       <c r="I1160">
-        <v>0.04077778022801981</v>
+        <v>0.0130833351710149</v>
       </c>
       <c r="J1160">
         <v>0.7694445057004873</v>
@@ -59901,101 +59901,101 @@
         <v>3.35</v>
       </c>
       <c r="L1160">
-        <v>4.02</v>
+        <v>4.13</v>
       </c>
       <c r="M1160">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="N1160">
-        <v>4.03</v>
+        <v>4.14</v>
       </c>
       <c r="O1160">
         <v>1</v>
       </c>
       <c r="P1160" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1161" spans="1:16">
       <c r="A1161" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1161" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C1161">
-        <v>1.443138686131387</v>
+        <v>1.442612807343595</v>
       </c>
       <c r="D1161" t="s">
         <v>377</v>
       </c>
       <c r="E1161">
-        <v>1.490055350960372</v>
+        <v>1.493387579793224</v>
       </c>
       <c r="F1161">
         <v>1</v>
       </c>
       <c r="G1161">
-        <v>0.006536861313868613</v>
+        <v>0.006597387192656404</v>
       </c>
       <c r="H1161">
-        <v>0.006629944649039627</v>
+        <v>0.006586612420206776</v>
       </c>
       <c r="I1161">
-        <v>0.04691666482898516</v>
+        <v>0.05077477244962925</v>
       </c>
       <c r="J1161">
-        <v>0.7694445057004873</v>
+        <v>0.7693693112407177</v>
       </c>
       <c r="K1161">
+        <v>3.35</v>
+      </c>
+      <c r="L1161">
+        <v>4.02</v>
+      </c>
+      <c r="M1161">
         <v>3.31</v>
       </c>
-      <c r="L1161">
-        <v>3.99</v>
-      </c>
-      <c r="M1161">
-        <v>3.34</v>
-      </c>
       <c r="N1161">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="O1161">
         <v>1</v>
       </c>
       <c r="P1161" t="s">
-        <v>510</v>
+        <v>380</v>
       </c>
     </row>
     <row r="1162" spans="1:16">
       <c r="A1162" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1162" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C1162">
-        <v>1.443138686131387</v>
+        <v>1.443387579793225</v>
       </c>
       <c r="D1162" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1162">
-        <v>1.490055350960372</v>
+        <v>1.490306500456002</v>
       </c>
       <c r="F1162">
         <v>1</v>
       </c>
       <c r="G1162">
-        <v>0.006536861313868613</v>
+        <v>0.006536612420206776</v>
       </c>
       <c r="H1162">
-        <v>0.006629944649039627</v>
+        <v>0.006629693499543997</v>
       </c>
       <c r="I1162">
-        <v>0.04691666482898516</v>
+        <v>0.04691892066277781</v>
       </c>
       <c r="J1162">
-        <v>0.7694445057004873</v>
+        <v>0.7693693112407177</v>
       </c>
       <c r="K1162">
         <v>3.31</v>
@@ -60013,86 +60013,86 @@
         <v>1</v>
       </c>
       <c r="P1162" t="s">
-        <v>510</v>
+        <v>380</v>
       </c>
     </row>
     <row r="1163" spans="1:16">
       <c r="A1163" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1163" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C1163">
-        <v>1.552360905903368</v>
+        <v>1.443387579793225</v>
       </c>
       <c r="D1163" t="s">
         <v>378</v>
       </c>
       <c r="E1163">
-        <v>1.529277570732353</v>
+        <v>1.490306500456002</v>
       </c>
       <c r="F1163">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1163">
-        <v>0.006707639094096632</v>
+        <v>0.006536612420206776</v>
       </c>
       <c r="H1163">
-        <v>0.006730722429267647</v>
+        <v>0.006629693499543997</v>
       </c>
       <c r="I1163">
-        <v>0.02308333517101469</v>
+        <v>0.04691892066277781</v>
       </c>
       <c r="J1163">
-        <v>0.7694445057004873</v>
+        <v>0.7693693112407177</v>
       </c>
       <c r="K1163">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1163">
-        <v>4.13</v>
+        <v>3.99</v>
       </c>
       <c r="M1163">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="N1163">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="O1163">
         <v>1</v>
       </c>
       <c r="P1163" t="s">
-        <v>510</v>
+        <v>380</v>
       </c>
     </row>
     <row r="1164" spans="1:16">
       <c r="A1164" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1164" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C1164">
-        <v>1.442612807343595</v>
+        <v>1.552612807343595</v>
       </c>
       <c r="D1164" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E1164">
-        <v>1.483387579793225</v>
+        <v>1.539531728006374</v>
       </c>
       <c r="F1164">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1164">
-        <v>0.006597387192656404</v>
+        <v>0.006707387192656404</v>
       </c>
       <c r="H1164">
-        <v>0.006576612420206776</v>
+        <v>0.006740468271993626</v>
       </c>
       <c r="I1164">
-        <v>0.04077477244962946</v>
+        <v>0.01308107933722136</v>
       </c>
       <c r="J1164">
         <v>0.7693693112407177</v>
@@ -60101,51 +60101,51 @@
         <v>3.35</v>
       </c>
       <c r="L1164">
-        <v>4.02</v>
+        <v>4.13</v>
       </c>
       <c r="M1164">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="N1164">
-        <v>4.03</v>
+        <v>4.14</v>
       </c>
       <c r="O1164">
         <v>1</v>
       </c>
       <c r="P1164" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="1165" spans="1:16">
       <c r="A1165" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1165" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C1165">
-        <v>1.443387579793225</v>
+        <v>1.440857964887927</v>
       </c>
       <c r="D1165" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1165">
-        <v>1.490306500456002</v>
+        <v>1.487753958527394</v>
       </c>
       <c r="F1165">
         <v>1</v>
       </c>
       <c r="G1165">
-        <v>0.006536612420206776</v>
+        <v>0.006539142035112073</v>
       </c>
       <c r="H1165">
-        <v>0.006629693499543997</v>
+        <v>0.006632246041472605</v>
       </c>
       <c r="I1165">
-        <v>0.04691892066277781</v>
+        <v>0.04689599363946728</v>
       </c>
       <c r="J1165">
-        <v>0.7693693112407177</v>
+        <v>0.7701335453510795</v>
       </c>
       <c r="K1165">
         <v>3.31</v>
@@ -60163,39 +60163,39 @@
         <v>1</v>
       </c>
       <c r="P1165" t="s">
-        <v>379</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1166" spans="1:16">
       <c r="A1166" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1166" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C1166">
-        <v>1.443387579793225</v>
+        <v>1.440857964887927</v>
       </c>
       <c r="D1166" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1166">
-        <v>1.490306500456002</v>
+        <v>1.487753958527394</v>
       </c>
       <c r="F1166">
         <v>1</v>
       </c>
       <c r="G1166">
-        <v>0.006536612420206776</v>
+        <v>0.006539142035112073</v>
       </c>
       <c r="H1166">
-        <v>0.006629693499543997</v>
+        <v>0.006632246041472605</v>
       </c>
       <c r="I1166">
-        <v>0.04691892066277781</v>
+        <v>0.04689599363946728</v>
       </c>
       <c r="J1166">
-        <v>0.7693693112407177</v>
+        <v>0.7701335453510795</v>
       </c>
       <c r="K1166">
         <v>3.31</v>
@@ -60213,39 +60213,39 @@
         <v>1</v>
       </c>
       <c r="P1166" t="s">
-        <v>379</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1167" spans="1:16">
       <c r="A1167" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1167" t="s">
         <v>227</v>
       </c>
       <c r="C1167">
-        <v>1.552612807343595</v>
+        <v>1.550052623073884</v>
       </c>
       <c r="D1167" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1167">
-        <v>1.529531728006374</v>
+        <v>1.536948616713351</v>
       </c>
       <c r="F1167">
         <v>-1</v>
       </c>
       <c r="G1167">
-        <v>0.006707387192656404</v>
+        <v>0.006709947376926117</v>
       </c>
       <c r="H1167">
-        <v>0.006730468271993626</v>
+        <v>0.006743051383286648</v>
       </c>
       <c r="I1167">
-        <v>0.02308107933722114</v>
+        <v>0.01310400636053233</v>
       </c>
       <c r="J1167">
-        <v>0.7693693112407177</v>
+        <v>0.7701335453510795</v>
       </c>
       <c r="K1167">
         <v>3.35</v>
@@ -60257,13 +60257,13 @@
         <v>3.38</v>
       </c>
       <c r="N1167">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="O1167">
         <v>1</v>
       </c>
       <c r="P1167" t="s">
-        <v>379</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1168" spans="1:16">
@@ -60271,31 +60271,31 @@
         <v>0</v>
       </c>
       <c r="B1168" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C1168">
-        <v>1.440857964887927</v>
+        <v>1.439221823572351</v>
       </c>
       <c r="D1168" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1168">
-        <v>1.487753958527394</v>
+        <v>1.486102988136451</v>
       </c>
       <c r="F1168">
         <v>1</v>
       </c>
       <c r="G1168">
-        <v>0.006539142035112073</v>
+        <v>0.006540778176427649</v>
       </c>
       <c r="H1168">
-        <v>0.006632246041472605</v>
+        <v>0.006633897011863549</v>
       </c>
       <c r="I1168">
-        <v>0.04689599363946728</v>
+        <v>0.04688116456409963</v>
       </c>
       <c r="J1168">
-        <v>0.7701335453510795</v>
+        <v>0.770627847863338</v>
       </c>
       <c r="K1168">
         <v>3.31</v>
@@ -60313,7 +60313,7 @@
         <v>1</v>
       </c>
       <c r="P1168" t="s">
-        <v>223</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1169" spans="1:16">
@@ -60321,31 +60321,31 @@
         <v>1</v>
       </c>
       <c r="B1169" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C1169">
-        <v>1.440857964887927</v>
+        <v>1.439221823572351</v>
       </c>
       <c r="D1169" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1169">
-        <v>1.487753958527394</v>
+        <v>1.486102988136451</v>
       </c>
       <c r="F1169">
         <v>1</v>
       </c>
       <c r="G1169">
-        <v>0.006539142035112073</v>
+        <v>0.006540778176427649</v>
       </c>
       <c r="H1169">
-        <v>0.006632246041472605</v>
+        <v>0.006633897011863549</v>
       </c>
       <c r="I1169">
-        <v>0.04689599363946728</v>
+        <v>0.04688116456409963</v>
       </c>
       <c r="J1169">
-        <v>0.7701335453510795</v>
+        <v>0.770627847863338</v>
       </c>
       <c r="K1169">
         <v>3.31</v>
@@ -60363,7 +60363,7 @@
         <v>1</v>
       </c>
       <c r="P1169" t="s">
-        <v>223</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1170" spans="1:16">
@@ -60374,28 +60374,28 @@
         <v>227</v>
       </c>
       <c r="C1170">
-        <v>1.550052623073884</v>
+        <v>1.548396709657817</v>
       </c>
       <c r="D1170" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1170">
-        <v>1.526948616713351</v>
+        <v>1.535277874221917</v>
       </c>
       <c r="F1170">
         <v>-1</v>
       </c>
       <c r="G1170">
-        <v>0.006709947376926117</v>
+        <v>0.006711603290342183</v>
       </c>
       <c r="H1170">
-        <v>0.006733051383286648</v>
+        <v>0.006744722125778082</v>
       </c>
       <c r="I1170">
-        <v>0.02310400636053211</v>
+        <v>0.01311883543589998</v>
       </c>
       <c r="J1170">
-        <v>0.7701335453510795</v>
+        <v>0.770627847863338</v>
       </c>
       <c r="K1170">
         <v>3.35</v>
@@ -60407,13 +60407,13 @@
         <v>3.38</v>
       </c>
       <c r="N1170">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="O1170">
         <v>1</v>
       </c>
       <c r="P1170" t="s">
-        <v>223</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1171" spans="1:16">
@@ -60421,31 +60421,31 @@
         <v>0</v>
       </c>
       <c r="B1171" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C1171">
-        <v>1.439221823572351</v>
+        <v>1.439853795183759</v>
       </c>
       <c r="D1171" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1171">
-        <v>1.486102988136451</v>
+        <v>1.486740687587237</v>
       </c>
       <c r="F1171">
         <v>1</v>
       </c>
       <c r="G1171">
-        <v>0.006540778176427649</v>
+        <v>0.006540146204816242</v>
       </c>
       <c r="H1171">
-        <v>0.006633897011863549</v>
+        <v>0.006633259312412763</v>
       </c>
       <c r="I1171">
-        <v>0.04688116456409963</v>
+        <v>0.04688689240347799</v>
       </c>
       <c r="J1171">
-        <v>0.770627847863338</v>
+        <v>0.7704369198840608</v>
       </c>
       <c r="K1171">
         <v>3.31</v>
@@ -60471,43 +60471,43 @@
         <v>1</v>
       </c>
       <c r="B1172" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1172">
-        <v>1.439221823572351</v>
+        <v>1.549036318388396</v>
       </c>
       <c r="D1172" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E1172">
-        <v>1.486102988136451</v>
+        <v>1.535923210791874</v>
       </c>
       <c r="F1172">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1172">
-        <v>0.006540778176427649</v>
+        <v>0.006710963681611604</v>
       </c>
       <c r="H1172">
-        <v>0.006633897011863549</v>
+        <v>0.006744076789208126</v>
       </c>
       <c r="I1172">
-        <v>0.04688116456409963</v>
+        <v>0.01311310759652207</v>
       </c>
       <c r="J1172">
-        <v>0.770627847863338</v>
+        <v>0.7704369198840608</v>
       </c>
       <c r="K1172">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1172">
-        <v>3.99</v>
+        <v>4.13</v>
       </c>
       <c r="M1172">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N1172">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="O1172">
         <v>1</v>
@@ -60518,84 +60518,84 @@
     </row>
     <row r="1173" spans="1:16">
       <c r="A1173" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1173" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C1173">
-        <v>1.548396709657817</v>
+        <v>1.44247254812609</v>
       </c>
       <c r="D1173" t="s">
         <v>378</v>
       </c>
       <c r="E1173">
-        <v>1.525277874221918</v>
+        <v>1.489383175450495</v>
       </c>
       <c r="F1173">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1173">
-        <v>0.006711603290342183</v>
+        <v>0.006537527451873911</v>
       </c>
       <c r="H1173">
-        <v>0.006734722125778083</v>
+        <v>0.006630616824549504</v>
       </c>
       <c r="I1173">
-        <v>0.02311883543589976</v>
+        <v>0.04691062732440532</v>
       </c>
       <c r="J1173">
-        <v>0.770627847863338</v>
+        <v>0.7696457558531451</v>
       </c>
       <c r="K1173">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1173">
-        <v>4.13</v>
+        <v>3.99</v>
       </c>
       <c r="M1173">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="N1173">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="O1173">
         <v>1</v>
       </c>
       <c r="P1173" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1174" spans="1:16">
       <c r="A1174" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1174" t="s">
         <v>224</v>
       </c>
       <c r="C1174">
-        <v>1.439853795183759</v>
+        <v>1.44247254812609</v>
       </c>
       <c r="D1174" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1174">
-        <v>1.486740687587237</v>
+        <v>1.489383175450495</v>
       </c>
       <c r="F1174">
         <v>1</v>
       </c>
       <c r="G1174">
-        <v>0.006540146204816242</v>
+        <v>0.006537527451873911</v>
       </c>
       <c r="H1174">
-        <v>0.006633259312412763</v>
+        <v>0.006630616824549504</v>
       </c>
       <c r="I1174">
-        <v>0.04688689240347799</v>
+        <v>0.04691062732440532</v>
       </c>
       <c r="J1174">
-        <v>0.7704369198840608</v>
+        <v>0.7696457558531451</v>
       </c>
       <c r="K1174">
         <v>3.31</v>
@@ -60613,98 +60613,98 @@
         <v>1</v>
       </c>
       <c r="P1174" t="s">
-        <v>380</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1175" spans="1:16">
       <c r="A1175" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1175" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1175">
-        <v>1.439853795183759</v>
+        <v>1.551686717891964</v>
       </c>
       <c r="D1175" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E1175">
-        <v>1.486740687587237</v>
+        <v>1.538597345216369</v>
       </c>
       <c r="F1175">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1175">
-        <v>0.006540146204816242</v>
+        <v>0.006708313282108036</v>
       </c>
       <c r="H1175">
-        <v>0.006633259312412763</v>
+        <v>0.00674140265478363</v>
       </c>
       <c r="I1175">
-        <v>0.04688689240347799</v>
+        <v>0.01308937267559429</v>
       </c>
       <c r="J1175">
-        <v>0.7704369198840608</v>
+        <v>0.7696457558531451</v>
       </c>
       <c r="K1175">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1175">
-        <v>3.99</v>
+        <v>4.13</v>
       </c>
       <c r="M1175">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N1175">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="O1175">
         <v>1</v>
       </c>
       <c r="P1175" t="s">
-        <v>380</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1176" spans="1:16">
       <c r="A1176" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1176" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1176">
+        <v>1.442210190879793</v>
+      </c>
+      <c r="D1176" t="s">
         <v>227</v>
       </c>
-      <c r="C1176">
-        <v>1.549036318388396</v>
-      </c>
-      <c r="D1176" t="s">
-        <v>378</v>
-      </c>
       <c r="E1176">
-        <v>1.525923210791874</v>
+        <v>1.551421190165349</v>
       </c>
       <c r="F1176">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1176">
-        <v>0.006710963681611604</v>
+        <v>0.006537789809120208</v>
       </c>
       <c r="H1176">
-        <v>0.006734076789208125</v>
+        <v>0.006708578809834651</v>
       </c>
       <c r="I1176">
-        <v>0.02311310759652185</v>
+        <v>0.1092109992855561</v>
       </c>
       <c r="J1176">
-        <v>0.7704369198840608</v>
+        <v>0.7697250178610899</v>
       </c>
       <c r="K1176">
+        <v>3.31</v>
+      </c>
+      <c r="L1176">
+        <v>3.99</v>
+      </c>
+      <c r="M1176">
         <v>3.35</v>
-      </c>
-      <c r="L1176">
-        <v>4.13</v>
-      </c>
-      <c r="M1176">
-        <v>3.38</v>
       </c>
       <c r="N1176">
         <v>4.13</v>
@@ -60713,7 +60713,7 @@
         <v>1</v>
       </c>
       <c r="P1176" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="1177" spans="1:16">
@@ -60721,31 +60721,31 @@
         <v>0</v>
       </c>
       <c r="B1177" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C1177">
-        <v>1.44247254812609</v>
+        <v>1.439498642804615</v>
       </c>
       <c r="D1177" t="s">
-        <v>377</v>
+        <v>227</v>
       </c>
       <c r="E1177">
-        <v>1.489383175450495</v>
+        <v>1.548676874137601</v>
       </c>
       <c r="F1177">
         <v>1</v>
       </c>
       <c r="G1177">
-        <v>0.006537527451873911</v>
+        <v>0.006540501357195385</v>
       </c>
       <c r="H1177">
-        <v>0.006630616824549504</v>
+        <v>0.006711323125862399</v>
       </c>
       <c r="I1177">
-        <v>0.04691062732440532</v>
+        <v>0.1091782313329861</v>
       </c>
       <c r="J1177">
-        <v>0.7696457558531451</v>
+        <v>0.770544216675343</v>
       </c>
       <c r="K1177">
         <v>3.31</v>
@@ -60754,16 +60754,16 @@
         <v>3.99</v>
       </c>
       <c r="M1177">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N1177">
-        <v>4.06</v>
+        <v>4.13</v>
       </c>
       <c r="O1177">
         <v>1</v>
       </c>
       <c r="P1177" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1178" spans="1:16">
@@ -60771,31 +60771,31 @@
         <v>1</v>
       </c>
       <c r="B1178" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C1178">
-        <v>1.44247254812609</v>
+        <v>1.439498642804615</v>
       </c>
       <c r="D1178" t="s">
-        <v>377</v>
+        <v>227</v>
       </c>
       <c r="E1178">
-        <v>1.489383175450495</v>
+        <v>1.548676874137601</v>
       </c>
       <c r="F1178">
         <v>1</v>
       </c>
       <c r="G1178">
-        <v>0.006537527451873911</v>
+        <v>0.006540501357195385</v>
       </c>
       <c r="H1178">
-        <v>0.006630616824549504</v>
+        <v>0.006711323125862399</v>
       </c>
       <c r="I1178">
-        <v>0.04691062732440532</v>
+        <v>0.1091782313329861</v>
       </c>
       <c r="J1178">
-        <v>0.7696457558531451</v>
+        <v>0.770544216675343</v>
       </c>
       <c r="K1178">
         <v>3.31</v>
@@ -60804,57 +60804,57 @@
         <v>3.99</v>
       </c>
       <c r="M1178">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N1178">
-        <v>4.06</v>
+        <v>4.13</v>
       </c>
       <c r="O1178">
         <v>1</v>
       </c>
       <c r="P1178" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1179" spans="1:16">
       <c r="A1179" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1179" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1179">
+        <v>1.439929878966419</v>
+      </c>
+      <c r="D1179" t="s">
         <v>227</v>
       </c>
-      <c r="C1179">
-        <v>1.551686717891964</v>
-      </c>
-      <c r="D1179" t="s">
-        <v>378</v>
-      </c>
       <c r="E1179">
-        <v>1.52859734521637</v>
+        <v>1.549113321612539</v>
       </c>
       <c r="F1179">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1179">
-        <v>0.006708313282108036</v>
+        <v>0.006540070121033582</v>
       </c>
       <c r="H1179">
-        <v>0.00673140265478363</v>
+        <v>0.006710886678387462</v>
       </c>
       <c r="I1179">
-        <v>0.02308937267559408</v>
+        <v>0.1091834426461191</v>
       </c>
       <c r="J1179">
-        <v>0.7696457558531451</v>
+        <v>0.7704139338470033</v>
       </c>
       <c r="K1179">
+        <v>3.31</v>
+      </c>
+      <c r="L1179">
+        <v>3.99</v>
+      </c>
+      <c r="M1179">
         <v>3.35</v>
-      </c>
-      <c r="L1179">
-        <v>4.13</v>
-      </c>
-      <c r="M1179">
-        <v>3.38</v>
       </c>
       <c r="N1179">
         <v>4.13</v>
@@ -60863,39 +60863,39 @@
         <v>1</v>
       </c>
       <c r="P1179" t="s">
-        <v>512</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1180" spans="1:16">
       <c r="A1180" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1180" t="s">
         <v>224</v>
       </c>
       <c r="C1180">
-        <v>1.442210190879793</v>
+        <v>1.439929878966419</v>
       </c>
       <c r="D1180" t="s">
-        <v>377</v>
+        <v>227</v>
       </c>
       <c r="E1180">
-        <v>1.489118440343959</v>
+        <v>1.549113321612539</v>
       </c>
       <c r="F1180">
         <v>1</v>
       </c>
       <c r="G1180">
-        <v>0.006537789809120208</v>
+        <v>0.006540070121033582</v>
       </c>
       <c r="H1180">
-        <v>0.006630881559656039</v>
+        <v>0.006710886678387462</v>
       </c>
       <c r="I1180">
-        <v>0.04690824946416683</v>
+        <v>0.1091834426461191</v>
       </c>
       <c r="J1180">
-        <v>0.7697250178610899</v>
+        <v>0.7704139338470033</v>
       </c>
       <c r="K1180">
         <v>3.31</v>
@@ -60904,48 +60904,48 @@
         <v>3.99</v>
       </c>
       <c r="M1180">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N1180">
-        <v>4.06</v>
+        <v>4.13</v>
       </c>
       <c r="O1180">
         <v>1</v>
       </c>
       <c r="P1180" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1181" spans="1:16">
       <c r="A1181" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1181" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C1181">
-        <v>1.442210190879793</v>
+        <v>1.443210680071608</v>
       </c>
       <c r="D1181" t="s">
-        <v>377</v>
+        <v>227</v>
       </c>
       <c r="E1181">
-        <v>1.489118440343959</v>
+        <v>1.552433769860992</v>
       </c>
       <c r="F1181">
         <v>1</v>
       </c>
       <c r="G1181">
-        <v>0.006537789809120208</v>
+        <v>0.006536789319928392</v>
       </c>
       <c r="H1181">
-        <v>0.006630881559656039</v>
+        <v>0.006707566230139008</v>
       </c>
       <c r="I1181">
-        <v>0.04690824946416683</v>
+        <v>0.1092230897893844</v>
       </c>
       <c r="J1181">
-        <v>0.7697250178610899</v>
+        <v>0.7694227552653753</v>
       </c>
       <c r="K1181">
         <v>3.31</v>
@@ -60954,57 +60954,57 @@
         <v>3.99</v>
       </c>
       <c r="M1181">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N1181">
-        <v>4.06</v>
+        <v>4.13</v>
       </c>
       <c r="O1181">
         <v>1</v>
       </c>
       <c r="P1181" t="s">
-        <v>376</v>
+        <v>223</v>
       </c>
     </row>
     <row r="1182" spans="1:16">
       <c r="A1182" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1182" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1182">
+        <v>1.442303822168713</v>
+      </c>
+      <c r="D1182" t="s">
         <v>227</v>
       </c>
-      <c r="C1182">
-        <v>1.551421190165349</v>
-      </c>
-      <c r="D1182" t="s">
-        <v>378</v>
-      </c>
       <c r="E1182">
-        <v>1.528329439629516</v>
+        <v>1.551515952950207</v>
       </c>
       <c r="F1182">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1182">
-        <v>0.006708578809834651</v>
+        <v>0.006537696177831288</v>
       </c>
       <c r="H1182">
-        <v>0.006731670560370484</v>
+        <v>0.006708484047049792</v>
       </c>
       <c r="I1182">
-        <v>0.02309175053583257</v>
+        <v>0.1092121307814944</v>
       </c>
       <c r="J1182">
-        <v>0.7697250178610899</v>
+        <v>0.7696967304626245</v>
       </c>
       <c r="K1182">
+        <v>3.31</v>
+      </c>
+      <c r="L1182">
+        <v>3.99</v>
+      </c>
+      <c r="M1182">
         <v>3.35</v>
-      </c>
-      <c r="L1182">
-        <v>4.13</v>
-      </c>
-      <c r="M1182">
-        <v>3.38</v>
       </c>
       <c r="N1182">
         <v>4.13</v>
@@ -61013,506 +61013,6 @@
         <v>1</v>
       </c>
       <c r="P1182" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="1183" spans="1:16">
-      <c r="A1183" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1183" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1183">
-        <v>1.439498642804615</v>
-      </c>
-      <c r="D1183" t="s">
-        <v>377</v>
-      </c>
-      <c r="E1183">
-        <v>1.486382316304354</v>
-      </c>
-      <c r="F1183">
-        <v>1</v>
-      </c>
-      <c r="G1183">
-        <v>0.006540501357195385</v>
-      </c>
-      <c r="H1183">
-        <v>0.006633617683695645</v>
-      </c>
-      <c r="I1183">
-        <v>0.04688367349973932</v>
-      </c>
-      <c r="J1183">
-        <v>0.770544216675343</v>
-      </c>
-      <c r="K1183">
-        <v>3.31</v>
-      </c>
-      <c r="L1183">
-        <v>3.99</v>
-      </c>
-      <c r="M1183">
-        <v>3.34</v>
-      </c>
-      <c r="N1183">
-        <v>4.06</v>
-      </c>
-      <c r="O1183">
-        <v>1</v>
-      </c>
-      <c r="P1183" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="1184" spans="1:16">
-      <c r="A1184" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1184" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1184">
-        <v>1.439498642804615</v>
-      </c>
-      <c r="D1184" t="s">
-        <v>377</v>
-      </c>
-      <c r="E1184">
-        <v>1.486382316304354</v>
-      </c>
-      <c r="F1184">
-        <v>1</v>
-      </c>
-      <c r="G1184">
-        <v>0.006540501357195385</v>
-      </c>
-      <c r="H1184">
-        <v>0.006633617683695645</v>
-      </c>
-      <c r="I1184">
-        <v>0.04688367349973932</v>
-      </c>
-      <c r="J1184">
-        <v>0.770544216675343</v>
-      </c>
-      <c r="K1184">
-        <v>3.31</v>
-      </c>
-      <c r="L1184">
-        <v>3.99</v>
-      </c>
-      <c r="M1184">
-        <v>3.34</v>
-      </c>
-      <c r="N1184">
-        <v>4.06</v>
-      </c>
-      <c r="O1184">
-        <v>1</v>
-      </c>
-      <c r="P1184" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="1185" spans="1:16">
-      <c r="A1185" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1185" t="s">
-        <v>227</v>
-      </c>
-      <c r="C1185">
-        <v>1.548676874137601</v>
-      </c>
-      <c r="D1185" t="s">
-        <v>378</v>
-      </c>
-      <c r="E1185">
-        <v>1.52556054763734</v>
-      </c>
-      <c r="F1185">
-        <v>-1</v>
-      </c>
-      <c r="G1185">
-        <v>0.006711323125862399</v>
-      </c>
-      <c r="H1185">
-        <v>0.00673443945236266</v>
-      </c>
-      <c r="I1185">
-        <v>0.02311632650026052</v>
-      </c>
-      <c r="J1185">
-        <v>0.770544216675343</v>
-      </c>
-      <c r="K1185">
-        <v>3.35</v>
-      </c>
-      <c r="L1185">
-        <v>4.13</v>
-      </c>
-      <c r="M1185">
-        <v>3.38</v>
-      </c>
-      <c r="N1185">
-        <v>4.13</v>
-      </c>
-      <c r="O1185">
-        <v>1</v>
-      </c>
-      <c r="P1185" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="1186" spans="1:16">
-      <c r="A1186" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1186" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1186">
-        <v>1.439929878966419</v>
-      </c>
-      <c r="D1186" t="s">
-        <v>377</v>
-      </c>
-      <c r="E1186">
-        <v>1.486817460951009</v>
-      </c>
-      <c r="F1186">
-        <v>1</v>
-      </c>
-      <c r="G1186">
-        <v>0.006540070121033582</v>
-      </c>
-      <c r="H1186">
-        <v>0.00663318253904899</v>
-      </c>
-      <c r="I1186">
-        <v>0.04688758198458931</v>
-      </c>
-      <c r="J1186">
-        <v>0.7704139338470033</v>
-      </c>
-      <c r="K1186">
-        <v>3.31</v>
-      </c>
-      <c r="L1186">
-        <v>3.99</v>
-      </c>
-      <c r="M1186">
-        <v>3.34</v>
-      </c>
-      <c r="N1186">
-        <v>4.06</v>
-      </c>
-      <c r="O1186">
-        <v>1</v>
-      </c>
-      <c r="P1186" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="1187" spans="1:16">
-      <c r="A1187" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1187" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1187">
-        <v>1.439929878966419</v>
-      </c>
-      <c r="D1187" t="s">
-        <v>377</v>
-      </c>
-      <c r="E1187">
-        <v>1.486817460951009</v>
-      </c>
-      <c r="F1187">
-        <v>1</v>
-      </c>
-      <c r="G1187">
-        <v>0.006540070121033582</v>
-      </c>
-      <c r="H1187">
-        <v>0.00663318253904899</v>
-      </c>
-      <c r="I1187">
-        <v>0.04688758198458931</v>
-      </c>
-      <c r="J1187">
-        <v>0.7704139338470033</v>
-      </c>
-      <c r="K1187">
-        <v>3.31</v>
-      </c>
-      <c r="L1187">
-        <v>3.99</v>
-      </c>
-      <c r="M1187">
-        <v>3.34</v>
-      </c>
-      <c r="N1187">
-        <v>4.06</v>
-      </c>
-      <c r="O1187">
-        <v>1</v>
-      </c>
-      <c r="P1187" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="1188" spans="1:16">
-      <c r="A1188" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1188" t="s">
-        <v>227</v>
-      </c>
-      <c r="C1188">
-        <v>1.549113321612539</v>
-      </c>
-      <c r="D1188" t="s">
-        <v>378</v>
-      </c>
-      <c r="E1188">
-        <v>1.526000903597129</v>
-      </c>
-      <c r="F1188">
-        <v>-1</v>
-      </c>
-      <c r="G1188">
-        <v>0.006710886678387462</v>
-      </c>
-      <c r="H1188">
-        <v>0.006733999096402871</v>
-      </c>
-      <c r="I1188">
-        <v>0.02311241801540964</v>
-      </c>
-      <c r="J1188">
-        <v>0.7704139338470033</v>
-      </c>
-      <c r="K1188">
-        <v>3.35</v>
-      </c>
-      <c r="L1188">
-        <v>4.13</v>
-      </c>
-      <c r="M1188">
-        <v>3.38</v>
-      </c>
-      <c r="N1188">
-        <v>4.13</v>
-      </c>
-      <c r="O1188">
-        <v>1</v>
-      </c>
-      <c r="P1188" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="1189" spans="1:16">
-      <c r="A1189" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1189" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1189">
-        <v>1.443210680071608</v>
-      </c>
-      <c r="D1189" t="s">
-        <v>377</v>
-      </c>
-      <c r="E1189">
-        <v>1.490127997413646</v>
-      </c>
-      <c r="F1189">
-        <v>1</v>
-      </c>
-      <c r="G1189">
-        <v>0.006536789319928392</v>
-      </c>
-      <c r="H1189">
-        <v>0.006629872002586353</v>
-      </c>
-      <c r="I1189">
-        <v>0.04691731734203808</v>
-      </c>
-      <c r="J1189">
-        <v>0.7694227552653753</v>
-      </c>
-      <c r="K1189">
-        <v>3.31</v>
-      </c>
-      <c r="L1189">
-        <v>3.99</v>
-      </c>
-      <c r="M1189">
-        <v>3.34</v>
-      </c>
-      <c r="N1189">
-        <v>4.06</v>
-      </c>
-      <c r="O1189">
-        <v>1</v>
-      </c>
-      <c r="P1189" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="1190" spans="1:16">
-      <c r="A1190" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1190" t="s">
-        <v>227</v>
-      </c>
-      <c r="C1190">
-        <v>1.552433769860992</v>
-      </c>
-      <c r="D1190" t="s">
-        <v>378</v>
-      </c>
-      <c r="E1190">
-        <v>1.529351087203032</v>
-      </c>
-      <c r="F1190">
-        <v>-1</v>
-      </c>
-      <c r="G1190">
-        <v>0.006707566230139008</v>
-      </c>
-      <c r="H1190">
-        <v>0.006730648912796969</v>
-      </c>
-      <c r="I1190">
-        <v>0.02308268265796087</v>
-      </c>
-      <c r="J1190">
-        <v>0.7694227552653753</v>
-      </c>
-      <c r="K1190">
-        <v>3.35</v>
-      </c>
-      <c r="L1190">
-        <v>4.13</v>
-      </c>
-      <c r="M1190">
-        <v>3.38</v>
-      </c>
-      <c r="N1190">
-        <v>4.13</v>
-      </c>
-      <c r="O1190">
-        <v>1</v>
-      </c>
-      <c r="P1190" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="1191" spans="1:16">
-      <c r="A1191" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1191" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1191">
-        <v>1.442303822168713</v>
-      </c>
-      <c r="D1191" t="s">
-        <v>377</v>
-      </c>
-      <c r="E1191">
-        <v>1.489212920254834</v>
-      </c>
-      <c r="F1191">
-        <v>1</v>
-      </c>
-      <c r="G1191">
-        <v>0.006537696177831288</v>
-      </c>
-      <c r="H1191">
-        <v>0.006630787079745165</v>
-      </c>
-      <c r="I1191">
-        <v>0.04690909808612087</v>
-      </c>
-      <c r="J1191">
-        <v>0.7696967304626245</v>
-      </c>
-      <c r="K1191">
-        <v>3.31</v>
-      </c>
-      <c r="L1191">
-        <v>3.99</v>
-      </c>
-      <c r="M1191">
-        <v>3.34</v>
-      </c>
-      <c r="N1191">
-        <v>4.06</v>
-      </c>
-      <c r="O1191">
-        <v>1</v>
-      </c>
-      <c r="P1191" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="1192" spans="1:16">
-      <c r="A1192" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1192" t="s">
-        <v>227</v>
-      </c>
-      <c r="C1192">
-        <v>1.551515952950207</v>
-      </c>
-      <c r="D1192" t="s">
-        <v>378</v>
-      </c>
-      <c r="E1192">
-        <v>1.528425051036329</v>
-      </c>
-      <c r="F1192">
-        <v>-1</v>
-      </c>
-      <c r="G1192">
-        <v>0.006708484047049792</v>
-      </c>
-      <c r="H1192">
-        <v>0.00673157494896367</v>
-      </c>
-      <c r="I1192">
-        <v>0.02309090191387853</v>
-      </c>
-      <c r="J1192">
-        <v>0.7696967304626245</v>
-      </c>
-      <c r="K1192">
-        <v>3.35</v>
-      </c>
-      <c r="L1192">
-        <v>4.13</v>
-      </c>
-      <c r="M1192">
-        <v>3.38</v>
-      </c>
-      <c r="N1192">
-        <v>4.13</v>
-      </c>
-      <c r="O1192">
-        <v>1</v>
-      </c>
-      <c r="P1192" t="s">
         <v>514</v>
       </c>
     </row>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3522" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3525" uniqueCount="516">
   <si>
     <t>trade_time</t>
   </si>
@@ -1114,7 +1114,7 @@
     <t>2021-09-03</t>
   </si>
   <si>
-    <t>2021-09-28</t>
+    <t>2021-09-29</t>
   </si>
   <si>
     <t>2021-07-23</t>
@@ -1123,10 +1123,10 @@
     <t>2021-07-26</t>
   </si>
   <si>
-    <t>2021-09-24</t>
+    <t>2021-09-28</t>
   </si>
   <si>
-    <t>2021-09-23</t>
+    <t>2021-09-24</t>
   </si>
   <si>
     <t>2016-06-06</t>
@@ -1558,12 +1558,6 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
     <t>2021-09-08</t>
   </si>
   <si>
@@ -1925,7 +1919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1170"/>
+  <dimension ref="A1:P1171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -53289,7 +53283,7 @@
         <v>366</v>
       </c>
       <c r="E1028">
-        <v>1.827740310238339</v>
+        <v>1.799950743588071</v>
       </c>
       <c r="F1028">
         <v>-1</v>
@@ -53298,10 +53292,10 @@
         <v>0.005922545151710935</v>
       </c>
       <c r="H1028">
-        <v>0.005992259689761662</v>
+        <v>0.00606004925641193</v>
       </c>
       <c r="I1028">
-        <v>0.1897145380507266</v>
+        <v>0.2175041047009945</v>
       </c>
       <c r="J1028">
         <v>0.6827080950038233</v>
@@ -53313,10 +53307,10 @@
         <v>3.97</v>
       </c>
       <c r="M1028">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="N1028">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="O1028">
         <v>1</v>
@@ -54880,10 +54874,10 @@
         <v>1</v>
       </c>
       <c r="B1060" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C1060">
-        <v>1.591231354640724</v>
+        <v>1.592243213911306</v>
       </c>
       <c r="D1060" t="s">
         <v>365</v>
@@ -54895,22 +54889,22 @@
         <v>1</v>
       </c>
       <c r="G1060">
-        <v>0.006388768645359276</v>
+        <v>0.006447756786088693</v>
       </c>
       <c r="H1060">
         <v>0.006557756786088693</v>
       </c>
       <c r="I1060">
-        <v>0.1110118592705822</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1060">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1060">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1060">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1060">
         <v>3.35</v>
@@ -54930,7 +54924,7 @@
         <v>2</v>
       </c>
       <c r="B1061" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C1061">
         <v>1.591231354640724</v>
@@ -54980,28 +54974,28 @@
         <v>3</v>
       </c>
       <c r="B1062" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C1062">
-        <v>1.751231354640725</v>
+        <v>1.591231354640724</v>
       </c>
       <c r="D1062" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="E1062">
-        <v>1.897347937846668</v>
+        <v>1.702243213911307</v>
       </c>
       <c r="F1062">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.006548768645359276</v>
+        <v>0.006388768645359276</v>
       </c>
       <c r="H1062">
-        <v>0.006042652062153332</v>
+        <v>0.006557756786088693</v>
       </c>
       <c r="I1062">
-        <v>-0.1461165832059437</v>
+        <v>0.1110118592705822</v>
       </c>
       <c r="J1062">
         <v>0.7247035182354308</v>
@@ -55010,13 +55004,13 @@
         <v>3.31</v>
       </c>
       <c r="L1062">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1062">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1062">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1062">
         <v>1</v>
@@ -55030,10 +55024,10 @@
         <v>4</v>
       </c>
       <c r="B1063" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C1063">
-        <v>1.791395374928999</v>
+        <v>1.751231354640725</v>
       </c>
       <c r="D1063" t="s">
         <v>218</v>
@@ -55045,22 +55039,22 @@
         <v>-1</v>
       </c>
       <c r="G1063">
-        <v>0.006168604625071001</v>
+        <v>0.006548768645359276</v>
       </c>
       <c r="H1063">
         <v>0.006042652062153332</v>
       </c>
       <c r="I1063">
-        <v>-0.1059525629176692</v>
+        <v>-0.1461165832059437</v>
       </c>
       <c r="J1063">
         <v>0.7247035182354308</v>
       </c>
       <c r="K1063">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1063">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1063">
         <v>2.86</v>
@@ -55077,96 +55071,96 @@
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1064" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C1064">
-        <v>1.540367267690522</v>
+        <v>1.791395374928999</v>
       </c>
       <c r="D1064" t="s">
-        <v>368</v>
+        <v>218</v>
       </c>
       <c r="E1064">
-        <v>1.665305831214263</v>
+        <v>1.897347937846668</v>
       </c>
       <c r="F1064">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1064">
-        <v>0.006959632732309478</v>
+        <v>0.006168604625071001</v>
       </c>
       <c r="H1064">
-        <v>0.006574694168785737</v>
+        <v>0.006042652062153332</v>
       </c>
       <c r="I1064">
-        <v>0.1249385635237412</v>
+        <v>-0.1059525629176692</v>
       </c>
       <c r="J1064">
-        <v>0.7283958957821177</v>
+        <v>0.7247035182354308</v>
       </c>
       <c r="K1064">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="L1064">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1064">
-        <v>3.37</v>
+        <v>2.86</v>
       </c>
       <c r="N1064">
-        <v>4.12</v>
+        <v>3.97</v>
       </c>
       <c r="O1064">
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1065" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C1065">
-        <v>1.739009584961191</v>
+        <v>1.540367267690522</v>
       </c>
       <c r="D1065" t="s">
-        <v>218</v>
+        <v>368</v>
       </c>
       <c r="E1065">
-        <v>1.886787738063143</v>
+        <v>1.665305831214263</v>
       </c>
       <c r="F1065">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1065">
-        <v>0.00656099041503881</v>
+        <v>0.006959632732309478</v>
       </c>
       <c r="H1065">
-        <v>0.006053212261936856</v>
+        <v>0.006574694168785737</v>
       </c>
       <c r="I1065">
-        <v>-0.1477781531019526</v>
+        <v>0.1249385635237412</v>
       </c>
       <c r="J1065">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1065">
-        <v>3.31</v>
+        <v>3.72</v>
       </c>
       <c r="L1065">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="M1065">
-        <v>2.86</v>
+        <v>3.37</v>
       </c>
       <c r="N1065">
-        <v>3.97</v>
+        <v>4.12</v>
       </c>
       <c r="O1065">
         <v>1</v>
@@ -55177,46 +55171,46 @@
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1066" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C1066">
-        <v>1.780244394738005</v>
+        <v>1.579009584961191</v>
       </c>
       <c r="D1066" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="E1066">
-        <v>1.886787738063143</v>
+        <v>1.689873749129906</v>
       </c>
       <c r="F1066">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1066">
-        <v>0.006179755605261995</v>
+        <v>0.00640099041503881</v>
       </c>
       <c r="H1066">
-        <v>0.006053212261936856</v>
+        <v>0.006570126250870095</v>
       </c>
       <c r="I1066">
-        <v>-0.1065433433251388</v>
+        <v>0.1108641641687149</v>
       </c>
       <c r="J1066">
         <v>0.7283958957821177</v>
       </c>
       <c r="K1066">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1066">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1066">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1066">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1066">
         <v>1</v>
@@ -55227,84 +55221,84 @@
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1067" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C1067">
-        <v>1.525149479713785</v>
+        <v>1.579009584961191</v>
       </c>
       <c r="D1067" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E1067">
-        <v>1.65151982436437</v>
+        <v>1.689873749129906</v>
       </c>
       <c r="F1067">
         <v>1</v>
       </c>
       <c r="G1067">
-        <v>0.006974850520286215</v>
+        <v>0.00640099041503881</v>
       </c>
       <c r="H1067">
-        <v>0.00658848017563563</v>
+        <v>0.006570126250870095</v>
       </c>
       <c r="I1067">
-        <v>0.1263703446505851</v>
+        <v>0.1108641641687149</v>
       </c>
       <c r="J1067">
-        <v>0.7324866990016706</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1067">
-        <v>3.72</v>
+        <v>3.31</v>
       </c>
       <c r="L1067">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="M1067">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N1067">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
       <c r="O1067">
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1068" t="s">
         <v>219</v>
       </c>
       <c r="C1068">
-        <v>1.725469026304471</v>
+        <v>1.739009584961191</v>
       </c>
       <c r="D1068" t="s">
         <v>218</v>
       </c>
       <c r="E1068">
-        <v>1.875088040855222</v>
+        <v>1.886787738063143</v>
       </c>
       <c r="F1068">
         <v>-1</v>
       </c>
       <c r="G1068">
-        <v>0.006574530973695531</v>
+        <v>0.00656099041503881</v>
       </c>
       <c r="H1068">
-        <v>0.006064911959144778</v>
+        <v>0.006053212261936856</v>
       </c>
       <c r="I1068">
-        <v>-0.1496190145507517</v>
+        <v>-0.1477781531019526</v>
       </c>
       <c r="J1068">
-        <v>0.7324866990016706</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1068">
         <v>3.31</v>
@@ -55322,39 +55316,39 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1069" t="s">
         <v>220</v>
       </c>
       <c r="C1069">
-        <v>1.767890169014955</v>
+        <v>1.780244394738005</v>
       </c>
       <c r="D1069" t="s">
         <v>218</v>
       </c>
       <c r="E1069">
-        <v>1.875088040855222</v>
+        <v>1.886787738063143</v>
       </c>
       <c r="F1069">
         <v>-1</v>
       </c>
       <c r="G1069">
-        <v>0.006192109830985045</v>
+        <v>0.006179755605261995</v>
       </c>
       <c r="H1069">
-        <v>0.006064911959144778</v>
+        <v>0.006053212261936856</v>
       </c>
       <c r="I1069">
-        <v>-0.1071978718402673</v>
+        <v>-0.1065433433251388</v>
       </c>
       <c r="J1069">
-        <v>0.7324866990016706</v>
+        <v>0.7283958957821177</v>
       </c>
       <c r="K1069">
         <v>3.02</v>
@@ -55372,7 +55366,7 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
@@ -55383,28 +55377,28 @@
         <v>214</v>
       </c>
       <c r="C1070">
-        <v>1.515332066574131</v>
+        <v>1.525149479713785</v>
       </c>
       <c r="D1070" t="s">
         <v>368</v>
       </c>
       <c r="E1070">
-        <v>1.6426260925685</v>
+        <v>1.65151982436437</v>
       </c>
       <c r="F1070">
         <v>1</v>
       </c>
       <c r="G1070">
-        <v>0.00698466793342587</v>
+        <v>0.006974850520286215</v>
       </c>
       <c r="H1070">
-        <v>0.0065973739074315</v>
+        <v>0.00658848017563563</v>
       </c>
       <c r="I1070">
-        <v>0.1272940259943698</v>
+        <v>0.1263703446505851</v>
       </c>
       <c r="J1070">
-        <v>0.7351257885553412</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1070">
         <v>3.72</v>
@@ -55422,7 +55416,7 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
@@ -55433,28 +55427,28 @@
         <v>219</v>
       </c>
       <c r="C1071">
-        <v>1.716733639881821</v>
+        <v>1.725469026304471</v>
       </c>
       <c r="D1071" t="s">
         <v>218</v>
       </c>
       <c r="E1071">
-        <v>1.867540244731725</v>
+        <v>1.875088040855222</v>
       </c>
       <c r="F1071">
         <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.00658326636011818</v>
+        <v>0.006574530973695531</v>
       </c>
       <c r="H1071">
-        <v>0.006072459755268276</v>
+        <v>0.006064911959144778</v>
       </c>
       <c r="I1071">
-        <v>-0.1508066048499037</v>
+        <v>-0.1496190145507517</v>
       </c>
       <c r="J1071">
-        <v>0.7351257885553412</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1071">
         <v>3.31</v>
@@ -55472,7 +55466,7 @@
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -55483,28 +55477,28 @@
         <v>220</v>
       </c>
       <c r="C1072">
-        <v>1.759920118562869</v>
+        <v>1.767890169014955</v>
       </c>
       <c r="D1072" t="s">
         <v>218</v>
       </c>
       <c r="E1072">
-        <v>1.867540244731725</v>
+        <v>1.875088040855222</v>
       </c>
       <c r="F1072">
         <v>-1</v>
       </c>
       <c r="G1072">
-        <v>0.006200079881437131</v>
+        <v>0.006192109830985045</v>
       </c>
       <c r="H1072">
-        <v>0.006072459755268276</v>
+        <v>0.006064911959144778</v>
       </c>
       <c r="I1072">
-        <v>-0.1076201261688552</v>
+        <v>-0.1071978718402673</v>
       </c>
       <c r="J1072">
-        <v>0.7351257885553412</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1072">
         <v>3.02</v>
@@ -55522,7 +55516,7 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -55530,49 +55524,49 @@
         <v>0</v>
       </c>
       <c r="B1073" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C1073">
-        <v>1.70603114244063</v>
+        <v>1.515332066574131</v>
       </c>
       <c r="D1073" t="s">
-        <v>218</v>
+        <v>368</v>
       </c>
       <c r="E1073">
-        <v>1.858292769601269</v>
+        <v>1.6426260925685</v>
       </c>
       <c r="F1073">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1073">
-        <v>0.006593968857559371</v>
+        <v>0.00698466793342587</v>
       </c>
       <c r="H1073">
-        <v>0.006081707230398731</v>
+        <v>0.0065973739074315</v>
       </c>
       <c r="I1073">
-        <v>-0.1522616271606392</v>
+        <v>0.1272940259943698</v>
       </c>
       <c r="J1073">
-        <v>0.7383591714680878</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1073">
-        <v>3.31</v>
+        <v>3.72</v>
       </c>
       <c r="L1073">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="M1073">
-        <v>2.86</v>
+        <v>3.37</v>
       </c>
       <c r="N1073">
-        <v>3.97</v>
+        <v>4.12</v>
       </c>
       <c r="O1073">
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>214</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -55580,37 +55574,37 @@
         <v>1</v>
       </c>
       <c r="B1074" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C1074">
-        <v>1.750155302166375</v>
+        <v>1.716733639881821</v>
       </c>
       <c r="D1074" t="s">
         <v>218</v>
       </c>
       <c r="E1074">
-        <v>1.858292769601269</v>
+        <v>1.867540244731725</v>
       </c>
       <c r="F1074">
         <v>-1</v>
       </c>
       <c r="G1074">
-        <v>0.006209844697833625</v>
+        <v>0.00658326636011818</v>
       </c>
       <c r="H1074">
-        <v>0.006081707230398731</v>
+        <v>0.006072459755268276</v>
       </c>
       <c r="I1074">
-        <v>-0.1081374674348941</v>
+        <v>-0.1508066048499037</v>
       </c>
       <c r="J1074">
-        <v>0.7383591714680878</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1074">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1074">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1074">
         <v>2.86</v>
@@ -55622,45 +55616,45 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>214</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
       <c r="A1075" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1075" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1075">
-        <v>1.687542808745847</v>
+        <v>1.759920118562869</v>
       </c>
       <c r="D1075" t="s">
         <v>218</v>
       </c>
       <c r="E1075">
-        <v>1.842317955593089</v>
+        <v>1.867540244731725</v>
       </c>
       <c r="F1075">
         <v>-1</v>
       </c>
       <c r="G1075">
-        <v>0.006612457191254154</v>
+        <v>0.006200079881437131</v>
       </c>
       <c r="H1075">
-        <v>0.006097682044406912</v>
+        <v>0.006072459755268276</v>
       </c>
       <c r="I1075">
-        <v>-0.1547751468472414</v>
+        <v>-0.1076201261688552</v>
       </c>
       <c r="J1075">
-        <v>0.7439447707716474</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1075">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1075">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1075">
         <v>2.86</v>
@@ -55672,45 +55666,45 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
       <c r="A1076" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1076" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C1076">
-        <v>1.733286792269625</v>
+        <v>1.70603114244063</v>
       </c>
       <c r="D1076" t="s">
         <v>218</v>
       </c>
       <c r="E1076">
-        <v>1.842317955593089</v>
+        <v>1.858292769601269</v>
       </c>
       <c r="F1076">
         <v>-1</v>
       </c>
       <c r="G1076">
-        <v>0.006226713207730375</v>
+        <v>0.006593968857559371</v>
       </c>
       <c r="H1076">
-        <v>0.006097682044406912</v>
+        <v>0.006081707230398731</v>
       </c>
       <c r="I1076">
-        <v>-0.109031163323464</v>
+        <v>-0.1522616271606392</v>
       </c>
       <c r="J1076">
-        <v>0.7439447707716474</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1076">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1076">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1076">
         <v>2.86</v>
@@ -55722,89 +55716,89 @@
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>493</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
       <c r="A1077" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1077" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C1077">
-        <v>1.512804794934651</v>
+        <v>1.750155302166375</v>
       </c>
       <c r="D1077" t="s">
-        <v>365</v>
+        <v>218</v>
       </c>
       <c r="E1077">
-        <v>1.622804794934651</v>
+        <v>1.858292769601269</v>
       </c>
       <c r="F1077">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1077">
-        <v>0.006527195205065349</v>
+        <v>0.006209844697833625</v>
       </c>
       <c r="H1077">
-        <v>0.006637195205065348</v>
+        <v>0.006081707230398731</v>
       </c>
       <c r="I1077">
-        <v>0.1100000000000003</v>
+        <v>-0.1081374674348941</v>
       </c>
       <c r="J1077">
-        <v>0.7484164791239846</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1077">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1077">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1077">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1077">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1077">
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>494</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1078" spans="1:16">
       <c r="A1078" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1078" t="s">
         <v>216</v>
       </c>
       <c r="C1078">
-        <v>1.512741454099611</v>
+        <v>1.527542808745847</v>
       </c>
       <c r="D1078" t="s">
         <v>365</v>
       </c>
       <c r="E1078">
-        <v>1.622804794934651</v>
+        <v>1.637785017914981</v>
       </c>
       <c r="F1078">
         <v>1</v>
       </c>
       <c r="G1078">
-        <v>0.006467258545900389</v>
+        <v>0.006452457191254153</v>
       </c>
       <c r="H1078">
-        <v>0.006637195205065348</v>
+        <v>0.00662221498208502</v>
       </c>
       <c r="I1078">
-        <v>0.11006334083504</v>
+        <v>0.110242209169134</v>
       </c>
       <c r="J1078">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1078">
         <v>3.31</v>
@@ -55822,39 +55816,39 @@
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
       <c r="A1079" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1079" t="s">
         <v>217</v>
       </c>
       <c r="C1079">
-        <v>1.512741454099611</v>
+        <v>1.527542808745847</v>
       </c>
       <c r="D1079" t="s">
         <v>365</v>
       </c>
       <c r="E1079">
-        <v>1.622804794934651</v>
+        <v>1.637785017914981</v>
       </c>
       <c r="F1079">
         <v>1</v>
       </c>
       <c r="G1079">
-        <v>0.006467258545900389</v>
+        <v>0.006452457191254153</v>
       </c>
       <c r="H1079">
-        <v>0.006637195205065348</v>
+        <v>0.00662221498208502</v>
       </c>
       <c r="I1079">
-        <v>0.11006334083504</v>
+        <v>0.110242209169134</v>
       </c>
       <c r="J1079">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1079">
         <v>3.31</v>
@@ -55872,39 +55866,39 @@
         <v>1</v>
       </c>
       <c r="P1079" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1080" spans="1:16">
       <c r="A1080" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1080" t="s">
         <v>219</v>
       </c>
       <c r="C1080">
-        <v>1.672741454099612</v>
+        <v>1.687542808745847</v>
       </c>
       <c r="D1080" t="s">
         <v>218</v>
       </c>
       <c r="E1080">
-        <v>1.829528869705404</v>
+        <v>1.842317955593089</v>
       </c>
       <c r="F1080">
         <v>-1</v>
       </c>
       <c r="G1080">
-        <v>0.00662725854590039</v>
+        <v>0.006612457191254154</v>
       </c>
       <c r="H1080">
-        <v>0.006110471130294596</v>
+        <v>0.006097682044406912</v>
       </c>
       <c r="I1080">
-        <v>-0.1567874156057929</v>
+        <v>-0.1547751468472414</v>
       </c>
       <c r="J1080">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1080">
         <v>3.31</v>
@@ -55922,39 +55916,39 @@
         <v>1</v>
       </c>
       <c r="P1080" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1081" spans="1:16">
       <c r="A1081" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1081" t="s">
         <v>220</v>
       </c>
       <c r="C1081">
-        <v>1.719782233045567</v>
+        <v>1.733286792269625</v>
       </c>
       <c r="D1081" t="s">
         <v>218</v>
       </c>
       <c r="E1081">
-        <v>1.829528869705404</v>
+        <v>1.842317955593089</v>
       </c>
       <c r="F1081">
         <v>-1</v>
       </c>
       <c r="G1081">
-        <v>0.006240217766954434</v>
+        <v>0.006226713207730375</v>
       </c>
       <c r="H1081">
-        <v>0.006110471130294596</v>
+        <v>0.006097682044406912</v>
       </c>
       <c r="I1081">
-        <v>-0.1097466366598376</v>
+        <v>-0.109031163323464</v>
       </c>
       <c r="J1081">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1081">
         <v>3.02</v>
@@ -55972,7 +55966,7 @@
         <v>1</v>
       </c>
       <c r="P1081" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1082" spans="1:16">
@@ -55983,28 +55977,28 @@
         <v>215</v>
       </c>
       <c r="C1082">
-        <v>1.47676751053993</v>
+        <v>1.512804794934651</v>
       </c>
       <c r="D1082" t="s">
         <v>365</v>
       </c>
       <c r="E1082">
-        <v>1.586767510539931</v>
+        <v>1.622804794934651</v>
       </c>
       <c r="F1082">
         <v>1</v>
       </c>
       <c r="G1082">
-        <v>0.006563232489460068</v>
+        <v>0.006527195205065349</v>
       </c>
       <c r="H1082">
-        <v>0.006673232489460069</v>
+        <v>0.006637195205065348</v>
       </c>
       <c r="I1082">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1082">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1082">
         <v>3.35</v>
@@ -56022,7 +56016,7 @@
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
@@ -56033,28 +56027,28 @@
         <v>216</v>
       </c>
       <c r="C1083">
-        <v>1.477134465637961</v>
+        <v>1.512741454099611</v>
       </c>
       <c r="D1083" t="s">
         <v>365</v>
       </c>
       <c r="E1083">
-        <v>1.586767510539931</v>
+        <v>1.622804794934651</v>
       </c>
       <c r="F1083">
         <v>1</v>
       </c>
       <c r="G1083">
-        <v>0.006502865534362039</v>
+        <v>0.006467258545900389</v>
       </c>
       <c r="H1083">
-        <v>0.006673232489460069</v>
+        <v>0.006637195205065348</v>
       </c>
       <c r="I1083">
-        <v>0.1096330449019693</v>
+        <v>0.11006334083504</v>
       </c>
       <c r="J1083">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1083">
         <v>3.31</v>
@@ -56072,7 +56066,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56083,28 +56077,28 @@
         <v>217</v>
       </c>
       <c r="C1084">
-        <v>1.477134465637961</v>
+        <v>1.512741454099611</v>
       </c>
       <c r="D1084" t="s">
         <v>365</v>
       </c>
       <c r="E1084">
-        <v>1.586767510539931</v>
+        <v>1.622804794934651</v>
       </c>
       <c r="F1084">
         <v>1</v>
       </c>
       <c r="G1084">
-        <v>0.006502865534362039</v>
+        <v>0.006467258545900389</v>
       </c>
       <c r="H1084">
-        <v>0.006673232489460069</v>
+        <v>0.006637195205065348</v>
       </c>
       <c r="I1084">
-        <v>0.1096330449019693</v>
+        <v>0.11006334083504</v>
       </c>
       <c r="J1084">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1084">
         <v>3.31</v>
@@ -56122,7 +56116,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56133,28 +56127,28 @@
         <v>219</v>
       </c>
       <c r="C1085">
-        <v>1.637134465637962</v>
+        <v>1.672741454099612</v>
       </c>
       <c r="D1085" t="s">
         <v>218</v>
       </c>
       <c r="E1085">
-        <v>1.798762710490807</v>
+        <v>1.829528869705404</v>
       </c>
       <c r="F1085">
         <v>-1</v>
       </c>
       <c r="G1085">
-        <v>0.006662865534362039</v>
+        <v>0.00662725854590039</v>
       </c>
       <c r="H1085">
-        <v>0.006141237289509194</v>
+        <v>0.006110471130294596</v>
       </c>
       <c r="I1085">
-        <v>-0.1616282448528454</v>
+        <v>-0.1567874156057929</v>
       </c>
       <c r="J1085">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1085">
         <v>3.31</v>
@@ -56172,7 +56166,7 @@
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56183,28 +56177,28 @@
         <v>220</v>
       </c>
       <c r="C1086">
-        <v>1.687294890098684</v>
+        <v>1.719782233045567</v>
       </c>
       <c r="D1086" t="s">
         <v>218</v>
       </c>
       <c r="E1086">
-        <v>1.798762710490807</v>
+        <v>1.829528869705404</v>
       </c>
       <c r="F1086">
         <v>-1</v>
       </c>
       <c r="G1086">
-        <v>0.006272705109901317</v>
+        <v>0.006240217766954434</v>
       </c>
       <c r="H1086">
-        <v>0.006141237289509194</v>
+        <v>0.006110471130294596</v>
       </c>
       <c r="I1086">
-        <v>-0.1114678203921233</v>
+        <v>-0.1097466366598376</v>
       </c>
       <c r="J1086">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1086">
         <v>3.02</v>
@@ -56222,7 +56216,7 @@
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
@@ -56233,28 +56227,28 @@
         <v>215</v>
       </c>
       <c r="C1087">
-        <v>1.462184374678514</v>
+        <v>1.47676751053993</v>
       </c>
       <c r="D1087" t="s">
         <v>365</v>
       </c>
       <c r="E1087">
-        <v>1.572184374678514</v>
+        <v>1.586767510539931</v>
       </c>
       <c r="F1087">
         <v>1</v>
       </c>
       <c r="G1087">
-        <v>0.006577815625321485</v>
+        <v>0.006563232489460068</v>
       </c>
       <c r="H1087">
-        <v>0.006687815625321486</v>
+        <v>0.006673232489460069</v>
       </c>
       <c r="I1087">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1087">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1087">
         <v>3.35</v>
@@ -56272,7 +56266,7 @@
         <v>1</v>
       </c>
       <c r="P1087" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1088" spans="1:16">
@@ -56283,28 +56277,28 @@
         <v>216</v>
       </c>
       <c r="C1088">
-        <v>1.462725456771905</v>
+        <v>1.477134465637961</v>
       </c>
       <c r="D1088" t="s">
         <v>365</v>
       </c>
       <c r="E1088">
-        <v>1.572184374678514</v>
+        <v>1.586767510539931</v>
       </c>
       <c r="F1088">
         <v>1</v>
       </c>
       <c r="G1088">
-        <v>0.006517274543228095</v>
+        <v>0.006502865534362039</v>
       </c>
       <c r="H1088">
-        <v>0.006687815625321486</v>
+        <v>0.006673232489460069</v>
       </c>
       <c r="I1088">
-        <v>0.109458917906609</v>
+        <v>0.1096330449019693</v>
       </c>
       <c r="J1088">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1088">
         <v>3.31</v>
@@ -56322,7 +56316,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56333,28 +56327,28 @@
         <v>219</v>
       </c>
       <c r="C1089">
-        <v>1.622725456771906</v>
+        <v>1.637134465637962</v>
       </c>
       <c r="D1089" t="s">
         <v>218</v>
       </c>
       <c r="E1089">
-        <v>1.786312630322553</v>
+        <v>1.798762710490807</v>
       </c>
       <c r="F1089">
         <v>-1</v>
       </c>
       <c r="G1089">
-        <v>0.006677274543228095</v>
+        <v>0.006662865534362039</v>
       </c>
       <c r="H1089">
-        <v>0.006153687369677447</v>
+        <v>0.006141237289509194</v>
       </c>
       <c r="I1089">
-        <v>-0.1635871735506473</v>
+        <v>-0.1616282448528454</v>
       </c>
       <c r="J1089">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1089">
         <v>3.31</v>
@@ -56372,7 +56366,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -56383,28 +56377,28 @@
         <v>220</v>
       </c>
       <c r="C1090">
-        <v>1.674148301948989</v>
+        <v>1.687294890098684</v>
       </c>
       <c r="D1090" t="s">
         <v>218</v>
       </c>
       <c r="E1090">
-        <v>1.786312630322553</v>
+        <v>1.798762710490807</v>
       </c>
       <c r="F1090">
         <v>-1</v>
       </c>
       <c r="G1090">
-        <v>0.006285851698051011</v>
+        <v>0.006272705109901317</v>
       </c>
       <c r="H1090">
-        <v>0.006153687369677447</v>
+        <v>0.006141237289509194</v>
       </c>
       <c r="I1090">
-        <v>-0.1121643283735638</v>
+        <v>-0.1114678203921233</v>
       </c>
       <c r="J1090">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1090">
         <v>3.02</v>
@@ -56422,7 +56416,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -56433,28 +56427,28 @@
         <v>215</v>
       </c>
       <c r="C1091">
-        <v>1.454243425931812</v>
+        <v>1.462184374678514</v>
       </c>
       <c r="D1091" t="s">
         <v>365</v>
       </c>
       <c r="E1091">
-        <v>1.564243425931813</v>
+        <v>1.572184374678514</v>
       </c>
       <c r="F1091">
         <v>1</v>
       </c>
       <c r="G1091">
-        <v>0.006585756574068187</v>
+        <v>0.006577815625321485</v>
       </c>
       <c r="H1091">
-        <v>0.006695756574068187</v>
+        <v>0.006687815625321486</v>
       </c>
       <c r="I1091">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1091">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1091">
         <v>3.35</v>
@@ -56472,7 +56466,7 @@
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
@@ -56483,28 +56477,28 @@
         <v>216</v>
       </c>
       <c r="C1092">
-        <v>1.454879325323672</v>
+        <v>1.462725456771905</v>
       </c>
       <c r="D1092" t="s">
         <v>365</v>
       </c>
       <c r="E1092">
-        <v>1.564243425931813</v>
+        <v>1.572184374678514</v>
       </c>
       <c r="F1092">
         <v>1</v>
       </c>
       <c r="G1092">
-        <v>0.006525120674676328</v>
+        <v>0.006517274543228095</v>
       </c>
       <c r="H1092">
-        <v>0.006695756574068187</v>
+        <v>0.006687815625321486</v>
       </c>
       <c r="I1092">
-        <v>0.1093641006081407</v>
+        <v>0.109458917906609</v>
       </c>
       <c r="J1092">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1092">
         <v>3.31</v>
@@ -56522,7 +56516,7 @@
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1093" spans="1:16">
@@ -56533,28 +56527,28 @@
         <v>219</v>
       </c>
       <c r="C1093">
-        <v>1.614879325323672</v>
+        <v>1.622725456771906</v>
       </c>
       <c r="D1093" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E1093">
-        <v>1.533174199563496</v>
+        <v>1.786312630322553</v>
       </c>
       <c r="F1093">
         <v>-1</v>
       </c>
       <c r="G1093">
-        <v>0.006685120674676329</v>
+        <v>0.006677274543228095</v>
       </c>
       <c r="H1093">
-        <v>0.006526825800436505</v>
+        <v>0.006153687369677447</v>
       </c>
       <c r="I1093">
-        <v>0.08170512576017641</v>
+        <v>-0.1635871735506473</v>
       </c>
       <c r="J1093">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1093">
         <v>3.31</v>
@@ -56563,16 +56557,16 @@
         <v>4.15</v>
       </c>
       <c r="M1093">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1093">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1093">
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
@@ -56583,28 +56577,28 @@
         <v>220</v>
       </c>
       <c r="C1094">
-        <v>1.666989595914649</v>
+        <v>1.674148301948989</v>
       </c>
       <c r="D1094" t="s">
         <v>218</v>
       </c>
       <c r="E1094">
-        <v>1.779533193482085</v>
+        <v>1.786312630322553</v>
       </c>
       <c r="F1094">
         <v>-1</v>
       </c>
       <c r="G1094">
-        <v>0.006293010404085351</v>
+        <v>0.006285851698051011</v>
       </c>
       <c r="H1094">
-        <v>0.006160466806517915</v>
+        <v>0.006153687369677447</v>
       </c>
       <c r="I1094">
-        <v>-0.112543597567436</v>
+        <v>-0.1121643283735638</v>
       </c>
       <c r="J1094">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1094">
         <v>3.02</v>
@@ -56622,7 +56616,7 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
@@ -56633,28 +56627,28 @@
         <v>215</v>
       </c>
       <c r="C1095">
-        <v>1.449111076062641</v>
+        <v>1.454243425931812</v>
       </c>
       <c r="D1095" t="s">
         <v>365</v>
       </c>
       <c r="E1095">
-        <v>1.559111076062641</v>
+        <v>1.564243425931813</v>
       </c>
       <c r="F1095">
         <v>1</v>
       </c>
       <c r="G1095">
-        <v>0.006590888923937359</v>
+        <v>0.006585756574068187</v>
       </c>
       <c r="H1095">
-        <v>0.006700888923937358</v>
+        <v>0.006695756574068187</v>
       </c>
       <c r="I1095">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1095">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1095">
         <v>3.35</v>
@@ -56672,7 +56666,7 @@
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>367</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -56683,28 +56677,28 @@
         <v>216</v>
       </c>
       <c r="C1096">
-        <v>1.449808257243983</v>
+        <v>1.454879325323672</v>
       </c>
       <c r="D1096" t="s">
         <v>365</v>
       </c>
       <c r="E1096">
-        <v>1.559111076062641</v>
+        <v>1.564243425931813</v>
       </c>
       <c r="F1096">
         <v>1</v>
       </c>
       <c r="G1096">
-        <v>0.006530191742756017</v>
+        <v>0.006525120674676328</v>
       </c>
       <c r="H1096">
-        <v>0.006700888923937358</v>
+        <v>0.006695756574068187</v>
       </c>
       <c r="I1096">
-        <v>0.1093028188186578</v>
+        <v>0.1093641006081407</v>
       </c>
       <c r="J1096">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1096">
         <v>3.31</v>
@@ -56722,7 +56716,7 @@
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>367</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
@@ -56733,28 +56727,28 @@
         <v>219</v>
       </c>
       <c r="C1097">
-        <v>1.609808257243984</v>
+        <v>1.614879325323672</v>
       </c>
       <c r="D1097" t="s">
         <v>221</v>
       </c>
       <c r="E1097">
-        <v>1.52817973372066</v>
+        <v>1.533174199563496</v>
       </c>
       <c r="F1097">
         <v>-1</v>
       </c>
       <c r="G1097">
-        <v>0.006690191742756017</v>
+        <v>0.006685120674676329</v>
       </c>
       <c r="H1097">
-        <v>0.00653182026627934</v>
+        <v>0.006526825800436505</v>
       </c>
       <c r="I1097">
-        <v>0.08162852352332317</v>
+        <v>0.08170512576017641</v>
       </c>
       <c r="J1097">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1097">
         <v>3.31</v>
@@ -56772,7 +56766,7 @@
         <v>1</v>
       </c>
       <c r="P1097" t="s">
-        <v>367</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1098" spans="1:16">
@@ -56783,28 +56777,28 @@
         <v>220</v>
       </c>
       <c r="C1098">
-        <v>1.66236282080871</v>
+        <v>1.666989595914649</v>
       </c>
       <c r="D1098" t="s">
         <v>218</v>
       </c>
       <c r="E1098">
-        <v>1.775151545534076</v>
+        <v>1.779533193482085</v>
       </c>
       <c r="F1098">
         <v>-1</v>
       </c>
       <c r="G1098">
-        <v>0.00629763717919129</v>
+        <v>0.006293010404085351</v>
       </c>
       <c r="H1098">
-        <v>0.006164848454465924</v>
+        <v>0.006160466806517915</v>
       </c>
       <c r="I1098">
-        <v>-0.1127887247253665</v>
+        <v>-0.112543597567436</v>
       </c>
       <c r="J1098">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1098">
         <v>3.02</v>
@@ -56822,7 +56816,7 @@
         <v>1</v>
       </c>
       <c r="P1098" t="s">
-        <v>367</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1099" spans="1:16">
@@ -56833,28 +56827,28 @@
         <v>215</v>
       </c>
       <c r="C1099">
-        <v>1.444959075956183</v>
+        <v>1.449111076062641</v>
       </c>
       <c r="D1099" t="s">
         <v>365</v>
       </c>
       <c r="E1099">
-        <v>1.554959075956183</v>
+        <v>1.559111076062641</v>
       </c>
       <c r="F1099">
         <v>1</v>
       </c>
       <c r="G1099">
-        <v>0.006595040924043817</v>
+        <v>0.006590888923937359</v>
       </c>
       <c r="H1099">
-        <v>0.006705040924043817</v>
+        <v>0.006700888923937358</v>
       </c>
       <c r="I1099">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1099">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1099">
         <v>3.35</v>
@@ -56872,7 +56866,7 @@
         <v>1</v>
       </c>
       <c r="P1099" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="1100" spans="1:16">
@@ -56883,28 +56877,28 @@
         <v>216</v>
       </c>
       <c r="C1100">
-        <v>1.445705833258199</v>
+        <v>1.449808257243983</v>
       </c>
       <c r="D1100" t="s">
         <v>365</v>
       </c>
       <c r="E1100">
-        <v>1.554959075956183</v>
+        <v>1.559111076062641</v>
       </c>
       <c r="F1100">
         <v>1</v>
       </c>
       <c r="G1100">
-        <v>0.006534294166741802</v>
+        <v>0.006530191742756017</v>
       </c>
       <c r="H1100">
-        <v>0.006705040924043817</v>
+        <v>0.006700888923937358</v>
       </c>
       <c r="I1100">
-        <v>0.1092532426979842</v>
+        <v>0.1093028188186578</v>
       </c>
       <c r="J1100">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1100">
         <v>3.31</v>
@@ -56922,7 +56916,7 @@
         <v>1</v>
       </c>
       <c r="P1100" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="1101" spans="1:16">
@@ -56933,28 +56927,28 @@
         <v>219</v>
       </c>
       <c r="C1101">
-        <v>1.605705833258199</v>
+        <v>1.609808257243984</v>
       </c>
       <c r="D1101" t="s">
         <v>221</v>
       </c>
       <c r="E1101">
-        <v>1.524139279885719</v>
+        <v>1.52817973372066</v>
       </c>
       <c r="F1101">
         <v>-1</v>
       </c>
       <c r="G1101">
-        <v>0.006694294166741802</v>
+        <v>0.006690191742756017</v>
       </c>
       <c r="H1101">
-        <v>0.006535860720114282</v>
+        <v>0.00653182026627934</v>
       </c>
       <c r="I1101">
-        <v>0.08156655337247987</v>
+        <v>0.08162852352332317</v>
       </c>
       <c r="J1101">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1101">
         <v>3.31</v>
@@ -56972,7 +56966,7 @@
         <v>1</v>
       </c>
       <c r="P1101" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="1102" spans="1:16">
@@ -56983,28 +56977,28 @@
         <v>220</v>
       </c>
       <c r="C1102">
-        <v>1.658619823697812</v>
+        <v>1.66236282080871</v>
       </c>
       <c r="D1102" t="s">
         <v>218</v>
       </c>
       <c r="E1102">
-        <v>1.771606852905876</v>
+        <v>1.775151545534076</v>
       </c>
       <c r="F1102">
         <v>-1</v>
       </c>
       <c r="G1102">
-        <v>0.006301380176302187</v>
+        <v>0.00629763717919129</v>
       </c>
       <c r="H1102">
-        <v>0.006168393147094125</v>
+        <v>0.006164848454465924</v>
       </c>
       <c r="I1102">
-        <v>-0.1129870292080635</v>
+        <v>-0.1127887247253665</v>
       </c>
       <c r="J1102">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1102">
         <v>3.02</v>
@@ -57022,7 +57016,7 @@
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
@@ -57033,28 +57027,28 @@
         <v>215</v>
       </c>
       <c r="C1103">
-        <v>1.445306718222063</v>
+        <v>1.444959075956183</v>
       </c>
       <c r="D1103" t="s">
         <v>365</v>
       </c>
       <c r="E1103">
-        <v>1.555306718222063</v>
+        <v>1.554959075956183</v>
       </c>
       <c r="F1103">
         <v>1</v>
       </c>
       <c r="G1103">
-        <v>0.006594693281777936</v>
+        <v>0.006595040924043817</v>
       </c>
       <c r="H1103">
-        <v>0.006704693281777937</v>
+        <v>0.006705040924043817</v>
       </c>
       <c r="I1103">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1103">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1103">
         <v>3.35</v>
@@ -57072,7 +57066,7 @@
         <v>1</v>
       </c>
       <c r="P1103" t="s">
-        <v>498</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1104" spans="1:16">
@@ -57083,28 +57077,28 @@
         <v>216</v>
       </c>
       <c r="C1104">
-        <v>1.446049324571651</v>
+        <v>1.445705833258199</v>
       </c>
       <c r="D1104" t="s">
         <v>365</v>
       </c>
       <c r="E1104">
-        <v>1.555306718222063</v>
+        <v>1.554959075956183</v>
       </c>
       <c r="F1104">
         <v>1</v>
       </c>
       <c r="G1104">
-        <v>0.00653395067542835</v>
+        <v>0.006534294166741802</v>
       </c>
       <c r="H1104">
-        <v>0.006704693281777937</v>
+        <v>0.006705040924043817</v>
       </c>
       <c r="I1104">
-        <v>0.1092573936504126</v>
+        <v>0.1092532426979842</v>
       </c>
       <c r="J1104">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1104">
         <v>3.31</v>
@@ -57122,7 +57116,7 @@
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>498</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
@@ -57133,28 +57127,28 @@
         <v>219</v>
       </c>
       <c r="C1105">
-        <v>1.606049324571651</v>
+        <v>1.605705833258199</v>
       </c>
       <c r="D1105" t="s">
         <v>221</v>
       </c>
       <c r="E1105">
-        <v>1.524477582508635</v>
+        <v>1.524139279885719</v>
       </c>
       <c r="F1105">
         <v>-1</v>
       </c>
       <c r="G1105">
-        <v>0.00669395067542835</v>
+        <v>0.006694294166741802</v>
       </c>
       <c r="H1105">
-        <v>0.006535522417491365</v>
+        <v>0.006535860720114282</v>
       </c>
       <c r="I1105">
-        <v>0.08157174206301576</v>
+        <v>0.08156655337247987</v>
       </c>
       <c r="J1105">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1105">
         <v>3.31</v>
@@ -57172,7 +57166,7 @@
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>498</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
@@ -57183,28 +57177,28 @@
         <v>220</v>
       </c>
       <c r="C1106">
-        <v>1.658933220606158</v>
+        <v>1.658619823697812</v>
       </c>
       <c r="D1106" t="s">
         <v>218</v>
       </c>
       <c r="E1106">
-        <v>1.771903646004508</v>
+        <v>1.771606852905876</v>
       </c>
       <c r="F1106">
         <v>-1</v>
       </c>
       <c r="G1106">
-        <v>0.006301066779393841</v>
+        <v>0.006301380176302187</v>
       </c>
       <c r="H1106">
-        <v>0.006168096353995493</v>
+        <v>0.006168393147094125</v>
       </c>
       <c r="I1106">
-        <v>-0.1129704253983497</v>
+        <v>-0.1129870292080635</v>
       </c>
       <c r="J1106">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1106">
         <v>3.02</v>
@@ -57222,7 +57216,7 @@
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>498</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
@@ -57233,28 +57227,28 @@
         <v>215</v>
       </c>
       <c r="C1107">
-        <v>1.448878847026507</v>
+        <v>1.445306718222063</v>
       </c>
       <c r="D1107" t="s">
         <v>365</v>
       </c>
       <c r="E1107">
-        <v>1.558878847026508</v>
+        <v>1.555306718222063</v>
       </c>
       <c r="F1107">
         <v>1</v>
       </c>
       <c r="G1107">
-        <v>0.006591121152973492</v>
+        <v>0.006594693281777936</v>
       </c>
       <c r="H1107">
-        <v>0.006701121152973492</v>
+        <v>0.006704693281777937</v>
       </c>
       <c r="I1107">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1107">
-        <v>0.7674988516338783</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1107">
         <v>3.35</v>
@@ -57272,7 +57266,7 @@
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
@@ -57283,28 +57277,28 @@
         <v>216</v>
       </c>
       <c r="C1108">
-        <v>1.449578801091863</v>
+        <v>1.446049324571651</v>
       </c>
       <c r="D1108" t="s">
         <v>365</v>
       </c>
       <c r="E1108">
-        <v>1.558878847026508</v>
+        <v>1.555306718222063</v>
       </c>
       <c r="F1108">
         <v>1</v>
       </c>
       <c r="G1108">
-        <v>0.006530421198908138</v>
+        <v>0.00653395067542835</v>
       </c>
       <c r="H1108">
-        <v>0.006701121152973492</v>
+        <v>0.006704693281777937</v>
       </c>
       <c r="I1108">
-        <v>0.1093000459346447</v>
+        <v>0.1092573936504126</v>
       </c>
       <c r="J1108">
-        <v>0.7674988516338783</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1108">
         <v>3.31</v>
@@ -57322,7 +57316,7 @@
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
@@ -57333,28 +57327,28 @@
         <v>219</v>
       </c>
       <c r="C1109">
-        <v>1.609578801091863</v>
+        <v>1.606049324571651</v>
       </c>
       <c r="D1109" t="s">
         <v>221</v>
       </c>
       <c r="E1109">
-        <v>1.527953743673557</v>
+        <v>1.524477582508635</v>
       </c>
       <c r="F1109">
         <v>-1</v>
       </c>
       <c r="G1109">
-        <v>0.006690421198908138</v>
+        <v>0.00669395067542835</v>
       </c>
       <c r="H1109">
-        <v>0.006532046256326444</v>
+        <v>0.006535522417491365</v>
       </c>
       <c r="I1109">
-        <v>0.08162505741830595</v>
+        <v>0.08157174206301576</v>
       </c>
       <c r="J1109">
-        <v>0.7674988516338783</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1109">
         <v>3.31</v>
@@ -57372,7 +57366,7 @@
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
@@ -57383,28 +57377,28 @@
         <v>220</v>
       </c>
       <c r="C1110">
-        <v>1.662153468065688</v>
+        <v>1.658933220606158</v>
       </c>
       <c r="D1110" t="s">
         <v>218</v>
       </c>
       <c r="E1110">
-        <v>1.774953284327108</v>
+        <v>1.771903646004508</v>
       </c>
       <c r="F1110">
         <v>-1</v>
       </c>
       <c r="G1110">
-        <v>0.006297846531934313</v>
+        <v>0.006301066779393841</v>
       </c>
       <c r="H1110">
-        <v>0.006165046715672892</v>
+        <v>0.006168096353995493</v>
       </c>
       <c r="I1110">
-        <v>-0.1127998162614205</v>
+        <v>-0.1129704253983497</v>
       </c>
       <c r="J1110">
-        <v>0.7674988516338783</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1110">
         <v>3.02</v>
@@ -57422,7 +57416,7 @@
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1111" spans="1:16">
@@ -57433,28 +57427,28 @@
         <v>215</v>
       </c>
       <c r="C1111">
-        <v>1.442972238067567</v>
+        <v>1.448878847026507</v>
       </c>
       <c r="D1111" t="s">
         <v>365</v>
       </c>
       <c r="E1111">
-        <v>1.552972238067567</v>
+        <v>1.558878847026508</v>
       </c>
       <c r="F1111">
         <v>1</v>
       </c>
       <c r="G1111">
-        <v>0.006597027761932432</v>
+        <v>0.006591121152973492</v>
       </c>
       <c r="H1111">
-        <v>0.006707027761932433</v>
+        <v>0.006701121152973492</v>
       </c>
       <c r="I1111">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1111">
-        <v>0.7692620184872934</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1111">
         <v>3.35</v>
@@ -57472,7 +57466,7 @@
         <v>1</v>
       </c>
       <c r="P1111" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1112" spans="1:16">
@@ -57483,28 +57477,28 @@
         <v>216</v>
       </c>
       <c r="C1112">
-        <v>1.443742718807059</v>
+        <v>1.449578801091863</v>
       </c>
       <c r="D1112" t="s">
         <v>365</v>
       </c>
       <c r="E1112">
-        <v>1.552972238067567</v>
+        <v>1.558878847026508</v>
       </c>
       <c r="F1112">
         <v>1</v>
       </c>
       <c r="G1112">
-        <v>0.006536257281192942</v>
+        <v>0.006530421198908138</v>
       </c>
       <c r="H1112">
-        <v>0.006707027761932433</v>
+        <v>0.006701121152973492</v>
       </c>
       <c r="I1112">
-        <v>0.1092295192605079</v>
+        <v>0.1093000459346447</v>
       </c>
       <c r="J1112">
-        <v>0.7692620184872934</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1112">
         <v>3.31</v>
@@ -57522,7 +57516,7 @@
         <v>1</v>
       </c>
       <c r="P1112" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1113" spans="1:16">
@@ -57533,28 +57527,28 @@
         <v>219</v>
       </c>
       <c r="C1113">
-        <v>1.603742718807059</v>
+        <v>1.609578801091863</v>
       </c>
       <c r="D1113" t="s">
         <v>221</v>
       </c>
       <c r="E1113">
-        <v>1.522205819731424</v>
+        <v>1.527953743673557</v>
       </c>
       <c r="F1113">
         <v>-1</v>
       </c>
       <c r="G1113">
-        <v>0.006696257281192942</v>
+        <v>0.006690421198908138</v>
       </c>
       <c r="H1113">
-        <v>0.006537794180268577</v>
+        <v>0.006532046256326444</v>
       </c>
       <c r="I1113">
-        <v>0.08153689907563511</v>
+        <v>0.08162505741830595</v>
       </c>
       <c r="J1113">
-        <v>0.7692620184872934</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1113">
         <v>3.31</v>
@@ -57572,7 +57566,7 @@
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
@@ -57583,28 +57577,28 @@
         <v>220</v>
       </c>
       <c r="C1114">
-        <v>1.656828704168374</v>
+        <v>1.662153468065688</v>
       </c>
       <c r="D1114" t="s">
         <v>218</v>
       </c>
       <c r="E1114">
-        <v>1.769910627126341</v>
+        <v>1.774953284327108</v>
       </c>
       <c r="F1114">
         <v>-1</v>
       </c>
       <c r="G1114">
-        <v>0.006303171295831626</v>
+        <v>0.006297846531934313</v>
       </c>
       <c r="H1114">
-        <v>0.006170089372873659</v>
+        <v>0.006165046715672892</v>
       </c>
       <c r="I1114">
-        <v>-0.1130819229579676</v>
+        <v>-0.1127998162614205</v>
       </c>
       <c r="J1114">
-        <v>0.7692620184872934</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1114">
         <v>3.02</v>
@@ -57622,7 +57616,7 @@
         <v>1</v>
       </c>
       <c r="P1114" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1115" spans="1:16">
@@ -57633,28 +57627,28 @@
         <v>215</v>
       </c>
       <c r="C1115">
-        <v>1.443432272837593</v>
+        <v>1.442972238067567</v>
       </c>
       <c r="D1115" t="s">
         <v>365</v>
       </c>
       <c r="E1115">
-        <v>1.553432272837593</v>
+        <v>1.552972238067567</v>
       </c>
       <c r="F1115">
         <v>1</v>
       </c>
       <c r="G1115">
-        <v>0.006596567727162407</v>
+        <v>0.006597027761932432</v>
       </c>
       <c r="H1115">
-        <v>0.006706567727162407</v>
+        <v>0.006707027761932433</v>
       </c>
       <c r="I1115">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1115">
-        <v>0.7691246946753454</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1115">
         <v>3.35</v>
@@ -57672,7 +57666,7 @@
         <v>1</v>
       </c>
       <c r="P1115" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1116" spans="1:16">
@@ -57683,28 +57677,28 @@
         <v>216</v>
       </c>
       <c r="C1116">
-        <v>1.444197260624607</v>
+        <v>1.443742718807059</v>
       </c>
       <c r="D1116" t="s">
         <v>365</v>
       </c>
       <c r="E1116">
-        <v>1.553432272837593</v>
+        <v>1.552972238067567</v>
       </c>
       <c r="F1116">
         <v>1</v>
       </c>
       <c r="G1116">
-        <v>0.006535802739375394</v>
+        <v>0.006536257281192942</v>
       </c>
       <c r="H1116">
-        <v>0.006706567727162407</v>
+        <v>0.006707027761932433</v>
       </c>
       <c r="I1116">
-        <v>0.1092350122129861</v>
+        <v>0.1092295192605079</v>
       </c>
       <c r="J1116">
-        <v>0.7691246946753454</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1116">
         <v>3.31</v>
@@ -57722,7 +57716,7 @@
         <v>1</v>
       </c>
       <c r="P1116" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1117" spans="1:16">
@@ -57733,28 +57727,28 @@
         <v>219</v>
       </c>
       <c r="C1117">
-        <v>1.604197260624607</v>
+        <v>1.603742718807059</v>
       </c>
       <c r="D1117" t="s">
         <v>221</v>
       </c>
       <c r="E1117">
-        <v>1.522653495358374</v>
+        <v>1.522205819731424</v>
       </c>
       <c r="F1117">
         <v>-1</v>
       </c>
       <c r="G1117">
-        <v>0.006695802739375393</v>
+        <v>0.006696257281192942</v>
       </c>
       <c r="H1117">
-        <v>0.006537346504641626</v>
+        <v>0.006537794180268577</v>
       </c>
       <c r="I1117">
-        <v>0.08154376526623253</v>
+        <v>0.08153689907563511</v>
       </c>
       <c r="J1117">
-        <v>0.7691246946753454</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1117">
         <v>3.31</v>
@@ -57772,7 +57766,7 @@
         <v>1</v>
       </c>
       <c r="P1117" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1118" spans="1:16">
@@ -57783,28 +57777,28 @@
         <v>220</v>
       </c>
       <c r="C1118">
-        <v>1.657243422080457</v>
+        <v>1.656828704168374</v>
       </c>
       <c r="D1118" t="s">
         <v>218</v>
       </c>
       <c r="E1118">
-        <v>1.770303373228512</v>
+        <v>1.769910627126341</v>
       </c>
       <c r="F1118">
         <v>-1</v>
       </c>
       <c r="G1118">
-        <v>0.006302756577919543</v>
+        <v>0.006303171295831626</v>
       </c>
       <c r="H1118">
-        <v>0.006169696626771489</v>
+        <v>0.006170089372873659</v>
       </c>
       <c r="I1118">
-        <v>-0.1130599511480552</v>
+        <v>-0.1130819229579676</v>
       </c>
       <c r="J1118">
-        <v>0.7691246946753454</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1118">
         <v>3.02</v>
@@ -57822,7 +57816,7 @@
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
@@ -57833,28 +57827,28 @@
         <v>215</v>
       </c>
       <c r="C1119">
-        <v>1.432380537847326</v>
+        <v>1.443432272837593</v>
       </c>
       <c r="D1119" t="s">
         <v>365</v>
       </c>
       <c r="E1119">
-        <v>1.542380537847327</v>
+        <v>1.553432272837593</v>
       </c>
       <c r="F1119">
         <v>1</v>
       </c>
       <c r="G1119">
-        <v>0.006607619462152673</v>
+        <v>0.006596567727162407</v>
       </c>
       <c r="H1119">
-        <v>0.006717619462152673</v>
+        <v>0.006706567727162407</v>
       </c>
       <c r="I1119">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1119">
-        <v>0.772423720045574</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1119">
         <v>3.35</v>
@@ -57872,7 +57866,7 @@
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
@@ -57883,28 +57877,28 @@
         <v>216</v>
       </c>
       <c r="C1120">
-        <v>1.43327748664915</v>
+        <v>1.444197260624607</v>
       </c>
       <c r="D1120" t="s">
         <v>365</v>
       </c>
       <c r="E1120">
-        <v>1.542380537847327</v>
+        <v>1.553432272837593</v>
       </c>
       <c r="F1120">
         <v>1</v>
       </c>
       <c r="G1120">
-        <v>0.006546722513350851</v>
+        <v>0.006535802739375394</v>
       </c>
       <c r="H1120">
-        <v>0.006717619462152673</v>
+        <v>0.006706567727162407</v>
       </c>
       <c r="I1120">
-        <v>0.1091030511981765</v>
+        <v>0.1092350122129861</v>
       </c>
       <c r="J1120">
-        <v>0.772423720045574</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1120">
         <v>3.31</v>
@@ -57922,7 +57916,7 @@
         <v>1</v>
       </c>
       <c r="P1120" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1121" spans="1:16">
@@ -57930,49 +57924,49 @@
         <v>2</v>
       </c>
       <c r="B1121" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C1121">
-        <v>1.43327748664915</v>
+        <v>1.604197260624607</v>
       </c>
       <c r="D1121" t="s">
-        <v>365</v>
+        <v>221</v>
       </c>
       <c r="E1121">
-        <v>1.542380537847327</v>
+        <v>1.522653495358374</v>
       </c>
       <c r="F1121">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1121">
-        <v>0.006546722513350851</v>
+        <v>0.006695802739375393</v>
       </c>
       <c r="H1121">
-        <v>0.006717619462152673</v>
+        <v>0.006537346504641626</v>
       </c>
       <c r="I1121">
-        <v>0.1091030511981765</v>
+        <v>0.08154376526623253</v>
       </c>
       <c r="J1121">
-        <v>0.772423720045574</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1121">
         <v>3.31</v>
       </c>
       <c r="L1121">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1121">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1121">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1121">
         <v>1</v>
       </c>
       <c r="P1121" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1122" spans="1:16">
@@ -57980,93 +57974,93 @@
         <v>3</v>
       </c>
       <c r="B1122" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1122">
-        <v>1.59327748664915</v>
+        <v>1.657243422080457</v>
       </c>
       <c r="D1122" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E1122">
-        <v>1.511898672651429</v>
+        <v>1.770303373228512</v>
       </c>
       <c r="F1122">
         <v>-1</v>
       </c>
       <c r="G1122">
-        <v>0.006706722513350851</v>
+        <v>0.006302756577919543</v>
       </c>
       <c r="H1122">
-        <v>0.006548101327348572</v>
+        <v>0.006169696626771489</v>
       </c>
       <c r="I1122">
-        <v>0.08137881399772118</v>
+        <v>-0.1130599511480552</v>
       </c>
       <c r="J1122">
-        <v>0.772423720045574</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1122">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1122">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1122">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1122">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1122">
         <v>1</v>
       </c>
       <c r="P1122" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1123" spans="1:16">
       <c r="A1123" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1123" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C1123">
-        <v>1.647280365462366</v>
+        <v>1.432380537847326</v>
       </c>
       <c r="D1123" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="E1123">
-        <v>1.760868160669659</v>
+        <v>1.542380537847327</v>
       </c>
       <c r="F1123">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1123">
-        <v>0.006312719634537634</v>
+        <v>0.006607619462152673</v>
       </c>
       <c r="H1123">
-        <v>0.006179131839330342</v>
+        <v>0.006717619462152673</v>
       </c>
       <c r="I1123">
-        <v>-0.1135877952072923</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1123">
         <v>0.772423720045574</v>
       </c>
       <c r="K1123">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="L1123">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1123">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1123">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1123">
         <v>1</v>
@@ -58077,40 +58071,40 @@
     </row>
     <row r="1124" spans="1:16">
       <c r="A1124" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1124" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C1124">
-        <v>1.431193937725116</v>
+        <v>1.43327748664915</v>
       </c>
       <c r="D1124" t="s">
         <v>365</v>
       </c>
       <c r="E1124">
-        <v>1.541193937725116</v>
+        <v>1.542380537847327</v>
       </c>
       <c r="F1124">
         <v>1</v>
       </c>
       <c r="G1124">
-        <v>0.006608806062274883</v>
+        <v>0.006546722513350851</v>
       </c>
       <c r="H1124">
-        <v>0.006718806062274884</v>
+        <v>0.006717619462152673</v>
       </c>
       <c r="I1124">
-        <v>0.1100000000000003</v>
+        <v>0.1091030511981765</v>
       </c>
       <c r="J1124">
-        <v>0.7727779290372787</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1124">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1124">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1124">
         <v>3.35</v>
@@ -58122,39 +58116,39 @@
         <v>1</v>
       </c>
       <c r="P1124" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1125" spans="1:16">
       <c r="A1125" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C1125">
-        <v>1.432105054886608</v>
+        <v>1.43327748664915</v>
       </c>
       <c r="D1125" t="s">
         <v>365</v>
       </c>
       <c r="E1125">
-        <v>1.541193937725116</v>
+        <v>1.542380537847327</v>
       </c>
       <c r="F1125">
         <v>1</v>
       </c>
       <c r="G1125">
-        <v>0.006547894945113393</v>
+        <v>0.006546722513350851</v>
       </c>
       <c r="H1125">
-        <v>0.006718806062274884</v>
+        <v>0.006717619462152673</v>
       </c>
       <c r="I1125">
-        <v>0.1090888828385084</v>
+        <v>0.1091030511981765</v>
       </c>
       <c r="J1125">
-        <v>0.7727779290372787</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1125">
         <v>3.31</v>
@@ -58172,151 +58166,151 @@
         <v>1</v>
       </c>
       <c r="P1125" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1126" spans="1:16">
       <c r="A1126" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1126" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C1126">
-        <v>1.432105054886608</v>
+        <v>1.59327748664915</v>
       </c>
       <c r="D1126" t="s">
-        <v>365</v>
+        <v>221</v>
       </c>
       <c r="E1126">
-        <v>1.541193937725116</v>
+        <v>1.511898672651429</v>
       </c>
       <c r="F1126">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1126">
-        <v>0.006547894945113393</v>
+        <v>0.006706722513350851</v>
       </c>
       <c r="H1126">
-        <v>0.006718806062274884</v>
+        <v>0.006548101327348572</v>
       </c>
       <c r="I1126">
-        <v>0.1090888828385084</v>
+        <v>0.08137881399772118</v>
       </c>
       <c r="J1126">
-        <v>0.7727779290372787</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1126">
         <v>3.31</v>
       </c>
       <c r="L1126">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1126">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1126">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1126">
         <v>1</v>
       </c>
       <c r="P1126" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1127" spans="1:16">
       <c r="A1127" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1127">
-        <v>1.592105054886608</v>
+        <v>1.647280365462366</v>
       </c>
       <c r="D1127" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E1127">
-        <v>1.510743951338472</v>
+        <v>1.760868160669659</v>
       </c>
       <c r="F1127">
         <v>-1</v>
       </c>
       <c r="G1127">
-        <v>0.006707894945113394</v>
+        <v>0.006312719634537634</v>
       </c>
       <c r="H1127">
-        <v>0.006549256048661529</v>
+        <v>0.006179131839330342</v>
       </c>
       <c r="I1127">
-        <v>0.08136110354813608</v>
+        <v>-0.1135877952072923</v>
       </c>
       <c r="J1127">
-        <v>0.7727779290372787</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1127">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1127">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1127">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1127">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1127">
         <v>1</v>
       </c>
       <c r="P1127" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1128" spans="1:16">
       <c r="A1128" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1128" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C1128">
-        <v>1.646210654307418</v>
+        <v>1.431193937725116</v>
       </c>
       <c r="D1128" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="E1128">
-        <v>1.759855122953383</v>
+        <v>1.541193937725116</v>
       </c>
       <c r="F1128">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1128">
-        <v>0.006313789345692582</v>
+        <v>0.006608806062274883</v>
       </c>
       <c r="H1128">
-        <v>0.006180144877046617</v>
+        <v>0.006718806062274884</v>
       </c>
       <c r="I1128">
-        <v>-0.1136444686459646</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1128">
         <v>0.7727779290372787</v>
       </c>
       <c r="K1128">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="L1128">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1128">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1128">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1128">
         <v>1</v>
@@ -58327,40 +58321,40 @@
     </row>
     <row r="1129" spans="1:16">
       <c r="A1129" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1129" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C1129">
-        <v>1.432233461226324</v>
+        <v>1.432105054886608</v>
       </c>
       <c r="D1129" t="s">
         <v>365</v>
       </c>
       <c r="E1129">
-        <v>1.542233461226325</v>
+        <v>1.541193937725116</v>
       </c>
       <c r="F1129">
         <v>1</v>
       </c>
       <c r="G1129">
-        <v>0.006607766538773674</v>
+        <v>0.006547894945113393</v>
       </c>
       <c r="H1129">
-        <v>0.006717766538773676</v>
+        <v>0.006718806062274884</v>
       </c>
       <c r="I1129">
-        <v>0.1100000000000003</v>
+        <v>0.1090888828385084</v>
       </c>
       <c r="J1129">
-        <v>0.7724676235145299</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1129">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1129">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1129">
         <v>3.35</v>
@@ -58372,39 +58366,39 @@
         <v>1</v>
       </c>
       <c r="P1129" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1130" spans="1:16">
       <c r="A1130" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1130" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C1130">
-        <v>1.433132166166906</v>
+        <v>1.432105054886608</v>
       </c>
       <c r="D1130" t="s">
         <v>365</v>
       </c>
       <c r="E1130">
-        <v>1.542233461226325</v>
+        <v>1.541193937725116</v>
       </c>
       <c r="F1130">
         <v>1</v>
       </c>
       <c r="G1130">
-        <v>0.006546867833833094</v>
+        <v>0.006547894945113393</v>
       </c>
       <c r="H1130">
-        <v>0.006717766538773676</v>
+        <v>0.006718806062274884</v>
       </c>
       <c r="I1130">
-        <v>0.1091012950594186</v>
+        <v>0.1090888828385084</v>
       </c>
       <c r="J1130">
-        <v>0.7724676235145299</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1130">
         <v>3.31</v>
@@ -58422,151 +58416,151 @@
         <v>1</v>
       </c>
       <c r="P1130" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1131" spans="1:16">
       <c r="A1131" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1131" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C1131">
-        <v>1.433132166166906</v>
+        <v>1.592105054886608</v>
       </c>
       <c r="D1131" t="s">
-        <v>365</v>
+        <v>221</v>
       </c>
       <c r="E1131">
-        <v>1.542233461226325</v>
+        <v>1.510743951338472</v>
       </c>
       <c r="F1131">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1131">
-        <v>0.006546867833833094</v>
+        <v>0.006707894945113394</v>
       </c>
       <c r="H1131">
-        <v>0.006717766538773676</v>
+        <v>0.006549256048661529</v>
       </c>
       <c r="I1131">
-        <v>0.1091012950594186</v>
+        <v>0.08136110354813608</v>
       </c>
       <c r="J1131">
-        <v>0.7724676235145299</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1131">
         <v>3.31</v>
       </c>
       <c r="L1131">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1131">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1131">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1131">
         <v>1</v>
       </c>
       <c r="P1131" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1132" spans="1:16">
       <c r="A1132" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1132" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1132">
-        <v>1.593132166166906</v>
+        <v>1.646210654307418</v>
       </c>
       <c r="D1132" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E1132">
-        <v>1.511755547342633</v>
+        <v>1.759855122953383</v>
       </c>
       <c r="F1132">
         <v>-1</v>
       </c>
       <c r="G1132">
-        <v>0.006706867833833094</v>
+        <v>0.006313789345692582</v>
       </c>
       <c r="H1132">
-        <v>0.006548244452657368</v>
+        <v>0.006180144877046617</v>
       </c>
       <c r="I1132">
-        <v>0.08137661882427327</v>
+        <v>-0.1136444686459646</v>
       </c>
       <c r="J1132">
-        <v>0.7724676235145299</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1132">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1132">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1132">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1132">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1132">
         <v>1</v>
       </c>
       <c r="P1132" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1133" spans="1:16">
       <c r="A1133" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1133" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C1133">
-        <v>1.64714777698612</v>
+        <v>1.432233461226324</v>
       </c>
       <c r="D1133" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="E1133">
-        <v>1.760742596748445</v>
+        <v>1.542233461226325</v>
       </c>
       <c r="F1133">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1133">
-        <v>0.006312852223013881</v>
+        <v>0.006607766538773674</v>
       </c>
       <c r="H1133">
-        <v>0.006179257403251556</v>
+        <v>0.006717766538773676</v>
       </c>
       <c r="I1133">
-        <v>-0.1135948197623251</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1133">
         <v>0.7724676235145299</v>
       </c>
       <c r="K1133">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="L1133">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1133">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1133">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1133">
         <v>1</v>
@@ -58577,40 +58571,40 @@
     </row>
     <row r="1134" spans="1:16">
       <c r="A1134" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1134" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C1134">
-        <v>1.438192457750358</v>
+        <v>1.433132166166906</v>
       </c>
       <c r="D1134" t="s">
         <v>365</v>
       </c>
       <c r="E1134">
-        <v>1.548192457750359</v>
+        <v>1.542233461226325</v>
       </c>
       <c r="F1134">
         <v>1</v>
       </c>
       <c r="G1134">
-        <v>0.00660180754224964</v>
+        <v>0.006546867833833094</v>
       </c>
       <c r="H1134">
-        <v>0.006711807542249641</v>
+        <v>0.006717766538773676</v>
       </c>
       <c r="I1134">
-        <v>0.1100000000000003</v>
+        <v>0.1091012950594186</v>
       </c>
       <c r="J1134">
-        <v>0.7706888185819823</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1134">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1134">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1134">
         <v>3.35</v>
@@ -58622,39 +58616,39 @@
         <v>1</v>
       </c>
       <c r="P1134" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1135" spans="1:16">
       <c r="A1135" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1135" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C1135">
-        <v>1.439020010493639</v>
+        <v>1.433132166166906</v>
       </c>
       <c r="D1135" t="s">
         <v>365</v>
       </c>
       <c r="E1135">
-        <v>1.548192457750359</v>
+        <v>1.542233461226325</v>
       </c>
       <c r="F1135">
         <v>1</v>
       </c>
       <c r="G1135">
-        <v>0.006540979989506361</v>
+        <v>0.006546867833833094</v>
       </c>
       <c r="H1135">
-        <v>0.006711807542249641</v>
+        <v>0.006717766538773676</v>
       </c>
       <c r="I1135">
-        <v>0.1091724472567202</v>
+        <v>0.1091012950594186</v>
       </c>
       <c r="J1135">
-        <v>0.7706888185819823</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1135">
         <v>3.31</v>
@@ -58672,151 +58666,151 @@
         <v>1</v>
       </c>
       <c r="P1135" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1136" spans="1:16">
       <c r="A1136" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1136" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C1136">
-        <v>1.439020010493639</v>
+        <v>1.593132166166906</v>
       </c>
       <c r="D1136" t="s">
-        <v>365</v>
+        <v>221</v>
       </c>
       <c r="E1136">
-        <v>1.548192457750359</v>
+        <v>1.511755547342633</v>
       </c>
       <c r="F1136">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1136">
-        <v>0.006540979989506361</v>
+        <v>0.006706867833833094</v>
       </c>
       <c r="H1136">
-        <v>0.006711807542249641</v>
+        <v>0.006548244452657368</v>
       </c>
       <c r="I1136">
-        <v>0.1091724472567202</v>
+        <v>0.08137661882427327</v>
       </c>
       <c r="J1136">
-        <v>0.7706888185819823</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1136">
         <v>3.31</v>
       </c>
       <c r="L1136">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1136">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1136">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1136">
         <v>1</v>
       </c>
       <c r="P1136" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1137" spans="1:16">
       <c r="A1137" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1137" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1137">
-        <v>1.599020010493639</v>
+        <v>1.64714777698612</v>
       </c>
       <c r="D1137" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E1137">
-        <v>1.517554451422738</v>
+        <v>1.760742596748445</v>
       </c>
       <c r="F1137">
         <v>-1</v>
       </c>
       <c r="G1137">
-        <v>0.006700979989506362</v>
+        <v>0.006312852223013881</v>
       </c>
       <c r="H1137">
-        <v>0.006542445548577263</v>
+        <v>0.006179257403251556</v>
       </c>
       <c r="I1137">
-        <v>0.08146555907090081</v>
+        <v>-0.1135948197623251</v>
       </c>
       <c r="J1137">
-        <v>0.7706888185819823</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1137">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1137">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1137">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1137">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1137">
         <v>1</v>
       </c>
       <c r="P1137" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1138" spans="1:16">
       <c r="A1138" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1138" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C1138">
-        <v>1.652519767882413</v>
+        <v>1.438192457750358</v>
       </c>
       <c r="D1138" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="E1138">
-        <v>1.765829978855531</v>
+        <v>1.548192457750359</v>
       </c>
       <c r="F1138">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1138">
-        <v>0.006307480232117587</v>
+        <v>0.00660180754224964</v>
       </c>
       <c r="H1138">
-        <v>0.00617417002114447</v>
+        <v>0.006711807542249641</v>
       </c>
       <c r="I1138">
-        <v>-0.1133102109731179</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1138">
         <v>0.7706888185819823</v>
       </c>
       <c r="K1138">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="L1138">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1138">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1138">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1138">
         <v>1</v>
@@ -58827,40 +58821,40 @@
     </row>
     <row r="1139" spans="1:16">
       <c r="A1139" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1139" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C1139">
-        <v>1.442360905903367</v>
+        <v>1.439020010493639</v>
       </c>
       <c r="D1139" t="s">
         <v>365</v>
       </c>
       <c r="E1139">
-        <v>1.552360905903368</v>
+        <v>1.548192457750359</v>
       </c>
       <c r="F1139">
         <v>1</v>
       </c>
       <c r="G1139">
-        <v>0.006597639094096632</v>
+        <v>0.006540979989506361</v>
       </c>
       <c r="H1139">
-        <v>0.006707639094096632</v>
+        <v>0.006711807542249641</v>
       </c>
       <c r="I1139">
-        <v>0.1100000000000003</v>
+        <v>0.1091724472567202</v>
       </c>
       <c r="J1139">
-        <v>0.7694445057004873</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1139">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1139">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1139">
         <v>3.35</v>
@@ -58872,39 +58866,39 @@
         <v>1</v>
       </c>
       <c r="P1139" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1140" spans="1:16">
       <c r="A1140" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1140" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C1140">
-        <v>1.443138686131387</v>
+        <v>1.439020010493639</v>
       </c>
       <c r="D1140" t="s">
         <v>365</v>
       </c>
       <c r="E1140">
-        <v>1.552360905903368</v>
+        <v>1.548192457750359</v>
       </c>
       <c r="F1140">
         <v>1</v>
       </c>
       <c r="G1140">
-        <v>0.006536861313868613</v>
+        <v>0.006540979989506361</v>
       </c>
       <c r="H1140">
-        <v>0.006707639094096632</v>
+        <v>0.006711807542249641</v>
       </c>
       <c r="I1140">
-        <v>0.1092222197719805</v>
+        <v>0.1091724472567202</v>
       </c>
       <c r="J1140">
-        <v>0.7694445057004873</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1140">
         <v>3.31</v>
@@ -58922,151 +58916,151 @@
         <v>1</v>
       </c>
       <c r="P1140" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1141" spans="1:16">
       <c r="A1141" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1141" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C1141">
-        <v>1.443138686131387</v>
+        <v>1.599020010493639</v>
       </c>
       <c r="D1141" t="s">
-        <v>365</v>
+        <v>221</v>
       </c>
       <c r="E1141">
-        <v>1.552360905903368</v>
+        <v>1.517554451422738</v>
       </c>
       <c r="F1141">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1141">
-        <v>0.006536861313868613</v>
+        <v>0.006700979989506362</v>
       </c>
       <c r="H1141">
-        <v>0.006707639094096632</v>
+        <v>0.006542445548577263</v>
       </c>
       <c r="I1141">
-        <v>0.1092222197719805</v>
+        <v>0.08146555907090081</v>
       </c>
       <c r="J1141">
-        <v>0.7694445057004873</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1141">
         <v>3.31</v>
       </c>
       <c r="L1141">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1141">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1141">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1141">
         <v>1</v>
       </c>
       <c r="P1141" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1142" spans="1:16">
       <c r="A1142" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1142" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1142">
-        <v>1.603138686131387</v>
+        <v>1.652519767882413</v>
       </c>
       <c r="D1142" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E1142">
-        <v>1.521610911416412</v>
+        <v>1.765829978855531</v>
       </c>
       <c r="F1142">
         <v>-1</v>
       </c>
       <c r="G1142">
-        <v>0.006696861313868614</v>
+        <v>0.006307480232117587</v>
       </c>
       <c r="H1142">
-        <v>0.006538389088583589</v>
+        <v>0.00617417002114447</v>
       </c>
       <c r="I1142">
-        <v>0.08152777471497519</v>
+        <v>-0.1133102109731179</v>
       </c>
       <c r="J1142">
-        <v>0.7694445057004873</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1142">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1142">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1142">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1142">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1142">
         <v>1</v>
       </c>
       <c r="P1142" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1143" spans="1:16">
       <c r="A1143" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1143" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C1143">
-        <v>1.656277592784528</v>
+        <v>1.442360905903367</v>
       </c>
       <c r="D1143" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="E1143">
-        <v>1.769388713696607</v>
+        <v>1.552360905903368</v>
       </c>
       <c r="F1143">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1143">
-        <v>0.006303722407215472</v>
+        <v>0.006597639094096632</v>
       </c>
       <c r="H1143">
-        <v>0.006170611286303394</v>
+        <v>0.006707639094096632</v>
       </c>
       <c r="I1143">
-        <v>-0.1131111209120785</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1143">
         <v>0.7694445057004873</v>
       </c>
       <c r="K1143">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="L1143">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1143">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1143">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1143">
         <v>1</v>
@@ -59077,40 +59071,40 @@
     </row>
     <row r="1144" spans="1:16">
       <c r="A1144" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1144" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C1144">
-        <v>1.442612807343595</v>
+        <v>1.443138686131387</v>
       </c>
       <c r="D1144" t="s">
         <v>365</v>
       </c>
       <c r="E1144">
-        <v>1.552612807343595</v>
+        <v>1.552360905903368</v>
       </c>
       <c r="F1144">
         <v>1</v>
       </c>
       <c r="G1144">
-        <v>0.006597387192656404</v>
+        <v>0.006536861313868613</v>
       </c>
       <c r="H1144">
-        <v>0.006707387192656404</v>
+        <v>0.006707639094096632</v>
       </c>
       <c r="I1144">
-        <v>0.1100000000000003</v>
+        <v>0.1092222197719805</v>
       </c>
       <c r="J1144">
-        <v>0.7693693112407177</v>
+        <v>0.7694445057004873</v>
       </c>
       <c r="K1144">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1144">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1144">
         <v>3.35</v>
@@ -59122,39 +59116,39 @@
         <v>1</v>
       </c>
       <c r="P1144" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1145" spans="1:16">
       <c r="A1145" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1145" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C1145">
-        <v>1.443387579793225</v>
+        <v>1.443138686131387</v>
       </c>
       <c r="D1145" t="s">
         <v>365</v>
       </c>
       <c r="E1145">
-        <v>1.552612807343595</v>
+        <v>1.552360905903368</v>
       </c>
       <c r="F1145">
         <v>1</v>
       </c>
       <c r="G1145">
-        <v>0.006536612420206776</v>
+        <v>0.006536861313868613</v>
       </c>
       <c r="H1145">
-        <v>0.006707387192656404</v>
+        <v>0.006707639094096632</v>
       </c>
       <c r="I1145">
-        <v>0.1092252275503709</v>
+        <v>0.1092222197719805</v>
       </c>
       <c r="J1145">
-        <v>0.7693693112407177</v>
+        <v>0.7694445057004873</v>
       </c>
       <c r="K1145">
         <v>3.31</v>
@@ -59172,151 +59166,151 @@
         <v>1</v>
       </c>
       <c r="P1145" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1146" spans="1:16">
       <c r="A1146" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1146" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C1146">
-        <v>1.443387579793225</v>
+        <v>1.603138686131387</v>
       </c>
       <c r="D1146" t="s">
-        <v>365</v>
+        <v>221</v>
       </c>
       <c r="E1146">
-        <v>1.552612807343595</v>
+        <v>1.521610911416412</v>
       </c>
       <c r="F1146">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1146">
-        <v>0.006536612420206776</v>
+        <v>0.006696861313868614</v>
       </c>
       <c r="H1146">
-        <v>0.006707387192656404</v>
+        <v>0.006538389088583589</v>
       </c>
       <c r="I1146">
-        <v>0.1092252275503709</v>
+        <v>0.08152777471497519</v>
       </c>
       <c r="J1146">
-        <v>0.7693693112407177</v>
+        <v>0.7694445057004873</v>
       </c>
       <c r="K1146">
         <v>3.31</v>
       </c>
       <c r="L1146">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1146">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1146">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1146">
         <v>1</v>
       </c>
       <c r="P1146" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1147" spans="1:16">
       <c r="A1147" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1147" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1147">
-        <v>1.603387579793225</v>
+        <v>1.656277592784528</v>
       </c>
       <c r="D1147" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E1147">
-        <v>1.521856045355261</v>
+        <v>1.769388713696607</v>
       </c>
       <c r="F1147">
         <v>-1</v>
       </c>
       <c r="G1147">
-        <v>0.006696612420206776</v>
+        <v>0.006303722407215472</v>
       </c>
       <c r="H1147">
-        <v>0.00653814395464474</v>
+        <v>0.006170611286303394</v>
       </c>
       <c r="I1147">
-        <v>0.08153153443796413</v>
+        <v>-0.1131111209120785</v>
       </c>
       <c r="J1147">
-        <v>0.7693693112407177</v>
+        <v>0.7694445057004873</v>
       </c>
       <c r="K1147">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1147">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1147">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1147">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1147">
         <v>1</v>
       </c>
       <c r="P1147" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1148" spans="1:16">
       <c r="A1148" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1148" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C1148">
-        <v>1.656504680053033</v>
+        <v>1.442612807343595</v>
       </c>
       <c r="D1148" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="E1148">
-        <v>1.769603769851547</v>
+        <v>1.552612807343595</v>
       </c>
       <c r="F1148">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1148">
-        <v>0.006303495319946967</v>
+        <v>0.006597387192656404</v>
       </c>
       <c r="H1148">
-        <v>0.006170396230148453</v>
+        <v>0.006707387192656404</v>
       </c>
       <c r="I1148">
-        <v>-0.1130990897985149</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1148">
         <v>0.7693693112407177</v>
       </c>
       <c r="K1148">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="L1148">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1148">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1148">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1148">
         <v>1</v>
@@ -59327,34 +59321,34 @@
     </row>
     <row r="1149" spans="1:16">
       <c r="A1149" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1149" t="s">
         <v>216</v>
       </c>
       <c r="C1149">
-        <v>1.440857964887927</v>
+        <v>1.443387579793225</v>
       </c>
       <c r="D1149" t="s">
         <v>365</v>
       </c>
       <c r="E1149">
-        <v>1.550052623073884</v>
+        <v>1.552612807343595</v>
       </c>
       <c r="F1149">
         <v>1</v>
       </c>
       <c r="G1149">
-        <v>0.006539142035112073</v>
+        <v>0.006536612420206776</v>
       </c>
       <c r="H1149">
-        <v>0.006709947376926117</v>
+        <v>0.006707387192656404</v>
       </c>
       <c r="I1149">
-        <v>0.1091946581859564</v>
+        <v>0.1092252275503709</v>
       </c>
       <c r="J1149">
-        <v>0.7701335453510795</v>
+        <v>0.7693693112407177</v>
       </c>
       <c r="K1149">
         <v>3.31</v>
@@ -59372,39 +59366,39 @@
         <v>1</v>
       </c>
       <c r="P1149" t="s">
-        <v>215</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1150" spans="1:16">
       <c r="A1150" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1150" t="s">
         <v>217</v>
       </c>
       <c r="C1150">
-        <v>1.440857964887927</v>
+        <v>1.443387579793225</v>
       </c>
       <c r="D1150" t="s">
         <v>365</v>
       </c>
       <c r="E1150">
-        <v>1.550052623073884</v>
+        <v>1.552612807343595</v>
       </c>
       <c r="F1150">
         <v>1</v>
       </c>
       <c r="G1150">
-        <v>0.006539142035112073</v>
+        <v>0.006536612420206776</v>
       </c>
       <c r="H1150">
-        <v>0.006709947376926117</v>
+        <v>0.006707387192656404</v>
       </c>
       <c r="I1150">
-        <v>0.1091946581859564</v>
+        <v>0.1092252275503709</v>
       </c>
       <c r="J1150">
-        <v>0.7701335453510795</v>
+        <v>0.7693693112407177</v>
       </c>
       <c r="K1150">
         <v>3.31</v>
@@ -59422,39 +59416,39 @@
         <v>1</v>
       </c>
       <c r="P1150" t="s">
-        <v>215</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1151" spans="1:16">
       <c r="A1151" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1151" t="s">
         <v>219</v>
       </c>
       <c r="C1151">
-        <v>1.600857964887927</v>
+        <v>1.603387579793225</v>
       </c>
       <c r="D1151" t="s">
         <v>221</v>
       </c>
       <c r="E1151">
-        <v>1.519364642155481</v>
+        <v>1.521856045355261</v>
       </c>
       <c r="F1151">
         <v>-1</v>
       </c>
       <c r="G1151">
-        <v>0.006699142035112074</v>
+        <v>0.006696612420206776</v>
       </c>
       <c r="H1151">
-        <v>0.006540635357844519</v>
+        <v>0.00653814395464474</v>
       </c>
       <c r="I1151">
-        <v>0.08149332273244614</v>
+        <v>0.08153153443796413</v>
       </c>
       <c r="J1151">
-        <v>0.7701335453510795</v>
+        <v>0.7693693112407177</v>
       </c>
       <c r="K1151">
         <v>3.31</v>
@@ -59472,39 +59466,39 @@
         <v>1</v>
       </c>
       <c r="P1151" t="s">
-        <v>215</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1152" spans="1:16">
       <c r="A1152" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1152" t="s">
         <v>220</v>
       </c>
       <c r="C1152">
-        <v>1.65419669303974</v>
+        <v>1.656504680053033</v>
       </c>
       <c r="D1152" t="s">
         <v>218</v>
       </c>
       <c r="E1152">
-        <v>1.767418060295913</v>
+        <v>1.769603769851547</v>
       </c>
       <c r="F1152">
         <v>-1</v>
       </c>
       <c r="G1152">
-        <v>0.00630580330696026</v>
+        <v>0.006303495319946967</v>
       </c>
       <c r="H1152">
-        <v>0.006172581939704088</v>
+        <v>0.006170396230148453</v>
       </c>
       <c r="I1152">
-        <v>-0.1132213672561728</v>
+        <v>-0.1130990897985149</v>
       </c>
       <c r="J1152">
-        <v>0.7701335453510795</v>
+        <v>0.7693693112407177</v>
       </c>
       <c r="K1152">
         <v>3.02</v>
@@ -59522,7 +59516,7 @@
         <v>1</v>
       </c>
       <c r="P1152" t="s">
-        <v>215</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1153" spans="1:16">
@@ -59533,28 +59527,28 @@
         <v>216</v>
       </c>
       <c r="C1153">
-        <v>1.439221823572351</v>
+        <v>1.440857964887927</v>
       </c>
       <c r="D1153" t="s">
         <v>365</v>
       </c>
       <c r="E1153">
-        <v>1.548396709657817</v>
+        <v>1.550052623073884</v>
       </c>
       <c r="F1153">
         <v>1</v>
       </c>
       <c r="G1153">
-        <v>0.006540778176427649</v>
+        <v>0.006539142035112073</v>
       </c>
       <c r="H1153">
-        <v>0.006711603290342183</v>
+        <v>0.006709947376926117</v>
       </c>
       <c r="I1153">
-        <v>0.1091748860854662</v>
+        <v>0.1091946581859564</v>
       </c>
       <c r="J1153">
-        <v>0.770627847863338</v>
+        <v>0.7701335453510795</v>
       </c>
       <c r="K1153">
         <v>3.31</v>
@@ -59572,7 +59566,7 @@
         <v>1</v>
       </c>
       <c r="P1153" t="s">
-        <v>508</v>
+        <v>215</v>
       </c>
     </row>
     <row r="1154" spans="1:16">
@@ -59580,49 +59574,49 @@
         <v>1</v>
       </c>
       <c r="B1154" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C1154">
-        <v>1.599221823572351</v>
+        <v>1.440857964887927</v>
       </c>
       <c r="D1154" t="s">
-        <v>221</v>
+        <v>365</v>
       </c>
       <c r="E1154">
-        <v>1.517753215965518</v>
+        <v>1.550052623073884</v>
       </c>
       <c r="F1154">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1154">
-        <v>0.00670077817642765</v>
+        <v>0.006539142035112073</v>
       </c>
       <c r="H1154">
-        <v>0.006542246784034482</v>
+        <v>0.006709947376926117</v>
       </c>
       <c r="I1154">
-        <v>0.08146860760683294</v>
+        <v>0.1091946581859564</v>
       </c>
       <c r="J1154">
-        <v>0.770627847863338</v>
+        <v>0.7701335453510795</v>
       </c>
       <c r="K1154">
         <v>3.31</v>
       </c>
       <c r="L1154">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1154">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1154">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1154">
         <v>1</v>
       </c>
       <c r="P1154" t="s">
-        <v>508</v>
+        <v>215</v>
       </c>
     </row>
     <row r="1155" spans="1:16">
@@ -59630,231 +59624,231 @@
         <v>2</v>
       </c>
       <c r="B1155" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C1155">
-        <v>1.652703899452719</v>
+        <v>1.600857964887927</v>
       </c>
       <c r="D1155" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E1155">
-        <v>1.766004355110853</v>
+        <v>1.519364642155481</v>
       </c>
       <c r="F1155">
         <v>-1</v>
       </c>
       <c r="G1155">
-        <v>0.006307296100547281</v>
+        <v>0.006699142035112074</v>
       </c>
       <c r="H1155">
-        <v>0.006173995644889147</v>
+        <v>0.006540635357844519</v>
       </c>
       <c r="I1155">
-        <v>-0.1133004556581341</v>
+        <v>0.08149332273244614</v>
       </c>
       <c r="J1155">
-        <v>0.770627847863338</v>
+        <v>0.7701335453510795</v>
       </c>
       <c r="K1155">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1155">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1155">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="N1155">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="O1155">
         <v>1</v>
       </c>
       <c r="P1155" t="s">
-        <v>508</v>
+        <v>215</v>
       </c>
     </row>
     <row r="1156" spans="1:16">
       <c r="A1156" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1156" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C1156">
-        <v>1.439853795183759</v>
+        <v>1.65419669303974</v>
       </c>
       <c r="D1156" t="s">
-        <v>365</v>
+        <v>218</v>
       </c>
       <c r="E1156">
-        <v>1.549036318388396</v>
+        <v>1.767418060295913</v>
       </c>
       <c r="F1156">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1156">
-        <v>0.006540146204816242</v>
+        <v>0.00630580330696026</v>
       </c>
       <c r="H1156">
-        <v>0.006710963681611604</v>
+        <v>0.006172581939704088</v>
       </c>
       <c r="I1156">
-        <v>0.1091825232046375</v>
+        <v>-0.1132213672561728</v>
       </c>
       <c r="J1156">
-        <v>0.7704369198840608</v>
+        <v>0.7701335453510795</v>
       </c>
       <c r="K1156">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1156">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1156">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1156">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1156">
         <v>1</v>
       </c>
       <c r="P1156" t="s">
-        <v>509</v>
+        <v>215</v>
       </c>
     </row>
     <row r="1157" spans="1:16">
       <c r="A1157" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1157" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C1157">
-        <v>1.653280501950136</v>
+        <v>1.439221823572351</v>
       </c>
       <c r="D1157" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="E1157">
-        <v>1.766550409131586</v>
+        <v>1.548396709657817</v>
       </c>
       <c r="F1157">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1157">
-        <v>0.006306719498049864</v>
+        <v>0.006540778176427649</v>
       </c>
       <c r="H1157">
-        <v>0.006173449590868413</v>
+        <v>0.006711603290342183</v>
       </c>
       <c r="I1157">
-        <v>-0.1132699071814502</v>
+        <v>0.1091748860854662</v>
       </c>
       <c r="J1157">
-        <v>0.7704369198840608</v>
+        <v>0.770627847863338</v>
       </c>
       <c r="K1157">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1157">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1157">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1157">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1157">
         <v>1</v>
       </c>
       <c r="P1157" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1158" spans="1:16">
       <c r="A1158" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1158" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C1158">
-        <v>1.44247254812609</v>
+        <v>1.599221823572351</v>
       </c>
       <c r="D1158" t="s">
-        <v>365</v>
+        <v>221</v>
       </c>
       <c r="E1158">
-        <v>1.551686717891964</v>
+        <v>1.517753215965518</v>
       </c>
       <c r="F1158">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1158">
-        <v>0.006537527451873911</v>
+        <v>0.00670077817642765</v>
       </c>
       <c r="H1158">
-        <v>0.006708313282108036</v>
+        <v>0.006542246784034482</v>
       </c>
       <c r="I1158">
-        <v>0.1092141697658739</v>
+        <v>0.08146860760683294</v>
       </c>
       <c r="J1158">
-        <v>0.7696457558531451</v>
+        <v>0.770627847863338</v>
       </c>
       <c r="K1158">
         <v>3.31</v>
       </c>
       <c r="L1158">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1158">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1158">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1158">
         <v>1</v>
       </c>
       <c r="P1158" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1159" spans="1:16">
       <c r="A1159" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1159" t="s">
         <v>220</v>
       </c>
       <c r="C1159">
-        <v>1.655669817323502</v>
+        <v>1.652703899452719</v>
       </c>
       <c r="D1159" t="s">
         <v>218</v>
       </c>
       <c r="E1159">
-        <v>1.768813138260005</v>
+        <v>1.766004355110853</v>
       </c>
       <c r="F1159">
         <v>-1</v>
       </c>
       <c r="G1159">
-        <v>0.006304330182676498</v>
+        <v>0.006307296100547281</v>
       </c>
       <c r="H1159">
-        <v>0.006171186861739996</v>
+        <v>0.006173995644889147</v>
       </c>
       <c r="I1159">
-        <v>-0.1131433209365036</v>
+        <v>-0.1133004556581341</v>
       </c>
       <c r="J1159">
-        <v>0.7696457558531451</v>
+        <v>0.770627847863338</v>
       </c>
       <c r="K1159">
         <v>3.02</v>
@@ -59872,7 +59866,7 @@
         <v>1</v>
       </c>
       <c r="P1159" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1160" spans="1:16">
@@ -59883,28 +59877,28 @@
         <v>216</v>
       </c>
       <c r="C1160">
-        <v>1.442210190879793</v>
+        <v>1.439853795183759</v>
       </c>
       <c r="D1160" t="s">
         <v>365</v>
       </c>
       <c r="E1160">
-        <v>1.551421190165349</v>
+        <v>1.549036318388396</v>
       </c>
       <c r="F1160">
         <v>1</v>
       </c>
       <c r="G1160">
-        <v>0.006537789809120208</v>
+        <v>0.006540146204816242</v>
       </c>
       <c r="H1160">
-        <v>0.006708578809834651</v>
+        <v>0.006710963681611604</v>
       </c>
       <c r="I1160">
-        <v>0.1092109992855561</v>
+        <v>0.1091825232046375</v>
       </c>
       <c r="J1160">
-        <v>0.7697250178610899</v>
+        <v>0.7704369198840608</v>
       </c>
       <c r="K1160">
         <v>3.31</v>
@@ -59922,57 +59916,57 @@
         <v>1</v>
       </c>
       <c r="P1160" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1161" spans="1:16">
       <c r="A1161" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1161" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C1161">
-        <v>1.439498642804615</v>
+        <v>1.653280501950136</v>
       </c>
       <c r="D1161" t="s">
-        <v>365</v>
+        <v>218</v>
       </c>
       <c r="E1161">
-        <v>1.548676874137601</v>
+        <v>1.766550409131586</v>
       </c>
       <c r="F1161">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1161">
-        <v>0.006540501357195385</v>
+        <v>0.006306719498049864</v>
       </c>
       <c r="H1161">
-        <v>0.006711323125862399</v>
+        <v>0.006173449590868413</v>
       </c>
       <c r="I1161">
-        <v>0.1091782313329861</v>
+        <v>-0.1132699071814502</v>
       </c>
       <c r="J1161">
-        <v>0.770544216675343</v>
+        <v>0.7704369198840608</v>
       </c>
       <c r="K1161">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1161">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1161">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1161">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1161">
         <v>1</v>
       </c>
       <c r="P1161" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1162" spans="1:16">
@@ -59983,28 +59977,28 @@
         <v>216</v>
       </c>
       <c r="C1162">
-        <v>1.439929878966419</v>
+        <v>1.44247254812609</v>
       </c>
       <c r="D1162" t="s">
         <v>365</v>
       </c>
       <c r="E1162">
-        <v>1.549113321612539</v>
+        <v>1.551686717891964</v>
       </c>
       <c r="F1162">
         <v>1</v>
       </c>
       <c r="G1162">
-        <v>0.006540070121033582</v>
+        <v>0.006537527451873911</v>
       </c>
       <c r="H1162">
-        <v>0.006710886678387462</v>
+        <v>0.006708313282108036</v>
       </c>
       <c r="I1162">
-        <v>0.1091834426461191</v>
+        <v>0.1092141697658739</v>
       </c>
       <c r="J1162">
-        <v>0.7704139338470033</v>
+        <v>0.7696457558531451</v>
       </c>
       <c r="K1162">
         <v>3.31</v>
@@ -60022,57 +60016,57 @@
         <v>1</v>
       </c>
       <c r="P1162" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1163" spans="1:16">
       <c r="A1163" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1163" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1163">
-        <v>1.535830209806174</v>
+        <v>1.655669817323502</v>
       </c>
       <c r="D1163" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E1163">
-        <v>1.669450071660934</v>
+        <v>1.768813138260005</v>
       </c>
       <c r="F1163">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1163">
-        <v>0.006524169790193828</v>
+        <v>0.006304330182676498</v>
       </c>
       <c r="H1163">
-        <v>0.006290549928339067</v>
+        <v>0.006171186861739996</v>
       </c>
       <c r="I1163">
-        <v>0.1336198618547599</v>
+        <v>-0.1131433209365036</v>
       </c>
       <c r="J1163">
-        <v>0.7650827577281677</v>
+        <v>0.7696457558531451</v>
       </c>
       <c r="K1163">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="L1163">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="M1163">
-        <v>3.02</v>
+        <v>2.86</v>
       </c>
       <c r="N1163">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="O1163">
         <v>1</v>
       </c>
       <c r="P1163" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1164" spans="1:16">
@@ -60080,49 +60074,49 @@
         <v>0</v>
       </c>
       <c r="B1164" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C1164">
-        <v>1.542834743861608</v>
+        <v>1.442210190879793</v>
       </c>
       <c r="D1164" t="s">
-        <v>220</v>
+        <v>365</v>
       </c>
       <c r="E1164">
-        <v>1.675938934497562</v>
+        <v>1.551421190165349</v>
       </c>
       <c r="F1164">
         <v>1</v>
       </c>
       <c r="G1164">
-        <v>0.006517165256138393</v>
+        <v>0.006537789809120208</v>
       </c>
       <c r="H1164">
-        <v>0.006284061065502437</v>
+        <v>0.006708578809834651</v>
       </c>
       <c r="I1164">
-        <v>0.1331041906359545</v>
+        <v>0.1092109992855561</v>
       </c>
       <c r="J1164">
-        <v>0.7629341276498137</v>
+        <v>0.7697250178610899</v>
       </c>
       <c r="K1164">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1164">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="M1164">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="N1164">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="O1164">
         <v>1</v>
       </c>
       <c r="P1164" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1165" spans="1:16">
@@ -60130,49 +60124,49 @@
         <v>0</v>
       </c>
       <c r="B1165" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C1165">
-        <v>1.548510552889843</v>
+        <v>1.439498642804615</v>
       </c>
       <c r="D1165" t="s">
-        <v>220</v>
+        <v>365</v>
       </c>
       <c r="E1165">
-        <v>1.681196892554393</v>
+        <v>1.548676874137601</v>
       </c>
       <c r="F1165">
         <v>1</v>
       </c>
       <c r="G1165">
-        <v>0.006511489447110158</v>
+        <v>0.006540501357195385</v>
       </c>
       <c r="H1165">
-        <v>0.006278803107445607</v>
+        <v>0.006711323125862399</v>
       </c>
       <c r="I1165">
-        <v>0.1326863396645508</v>
+        <v>0.1091782313329861</v>
       </c>
       <c r="J1165">
-        <v>0.7611930819356313</v>
+        <v>0.770544216675343</v>
       </c>
       <c r="K1165">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1165">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="M1165">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="N1165">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="O1165">
         <v>1</v>
       </c>
       <c r="P1165" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1166" spans="1:16">
@@ -60180,99 +60174,99 @@
         <v>0</v>
       </c>
       <c r="B1166" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C1166">
-        <v>1.554315618478226</v>
+        <v>1.439929878966419</v>
       </c>
       <c r="D1166" t="s">
-        <v>220</v>
+        <v>365</v>
       </c>
       <c r="E1166">
-        <v>1.686574591350994</v>
+        <v>1.549113321612539</v>
       </c>
       <c r="F1166">
         <v>1</v>
       </c>
       <c r="G1166">
-        <v>0.006505684381521775</v>
+        <v>0.006540070121033582</v>
       </c>
       <c r="H1166">
-        <v>0.006273425408649006</v>
+        <v>0.006710886678387462</v>
       </c>
       <c r="I1166">
-        <v>0.1322589728727683</v>
+        <v>0.1091834426461191</v>
       </c>
       <c r="J1166">
-        <v>0.7594123869698695</v>
+        <v>0.7704139338470033</v>
       </c>
       <c r="K1166">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="L1166">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="M1166">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="N1166">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="O1166">
         <v>1</v>
       </c>
       <c r="P1166" t="s">
-        <v>219</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1167" spans="1:16">
       <c r="A1167" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1167" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C1167">
-        <v>1.798080573266174</v>
+        <v>1.548510552889843</v>
       </c>
       <c r="D1167" t="s">
-        <v>366</v>
+        <v>220</v>
       </c>
       <c r="E1167">
-        <v>1.593792219741899</v>
+        <v>1.681196892554393</v>
       </c>
       <c r="F1167">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1167">
-        <v>0.006141919426733827</v>
+        <v>0.006511489447110158</v>
       </c>
       <c r="H1167">
-        <v>0.006226207780258102</v>
+        <v>0.006278803107445607</v>
       </c>
       <c r="I1167">
-        <v>0.2042883535242752</v>
+        <v>0.1326863396645508</v>
       </c>
       <c r="J1167">
-        <v>0.7594123869698695</v>
+        <v>0.7611930819356313</v>
       </c>
       <c r="K1167">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="L1167">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="M1167">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="N1167">
-        <v>3.91</v>
+        <v>3.98</v>
       </c>
       <c r="O1167">
         <v>1</v>
       </c>
       <c r="P1167" t="s">
-        <v>219</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1168" spans="1:16">
@@ -60280,49 +60274,49 @@
         <v>0</v>
       </c>
       <c r="B1168" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C1168">
-        <v>1.818831234438868</v>
+        <v>1.554315618478226</v>
       </c>
       <c r="D1168" t="s">
-        <v>369</v>
+        <v>220</v>
       </c>
       <c r="E1168">
-        <v>1.661050836004271</v>
+        <v>1.686574591350994</v>
       </c>
       <c r="F1168">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1168">
-        <v>0.006121168765561132</v>
+        <v>0.006505684381521775</v>
       </c>
       <c r="H1168">
-        <v>0.00615894916399573</v>
+        <v>0.006273425408649006</v>
       </c>
       <c r="I1168">
-        <v>0.1577803984345971</v>
+        <v>0.1322589728727683</v>
       </c>
       <c r="J1168">
-        <v>0.752156911035361</v>
+        <v>0.7594123869698695</v>
       </c>
       <c r="K1168">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="L1168">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="M1168">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="N1168">
-        <v>3.91</v>
+        <v>3.98</v>
       </c>
       <c r="O1168">
         <v>1</v>
       </c>
       <c r="P1168" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="1169" spans="1:16">
@@ -60333,28 +60327,28 @@
         <v>218</v>
       </c>
       <c r="C1169">
-        <v>1.815398126910906</v>
+        <v>1.818831234438868</v>
       </c>
       <c r="D1169" t="s">
         <v>369</v>
       </c>
       <c r="E1169">
-        <v>1.657461678134128</v>
+        <v>1.615921421342149</v>
       </c>
       <c r="F1169">
         <v>-1</v>
       </c>
       <c r="G1169">
-        <v>0.006124601873089094</v>
+        <v>0.006121168765561132</v>
       </c>
       <c r="H1169">
-        <v>0.006162538321865872</v>
+        <v>0.006204078578657852</v>
       </c>
       <c r="I1169">
-        <v>0.1579364487767774</v>
+        <v>0.2029098130967184</v>
       </c>
       <c r="J1169">
-        <v>0.7533572982829001</v>
+        <v>0.752156911035361</v>
       </c>
       <c r="K1169">
         <v>2.86</v>
@@ -60363,7 +60357,7 @@
         <v>3.97</v>
       </c>
       <c r="M1169">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="N1169">
         <v>3.91</v>
@@ -60372,7 +60366,7 @@
         <v>1</v>
       </c>
       <c r="P1169" t="s">
-        <v>517</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1170" spans="1:16">
@@ -60383,28 +60377,28 @@
         <v>218</v>
       </c>
       <c r="C1170">
-        <v>1.811875464143863</v>
+        <v>1.815398126910906</v>
       </c>
       <c r="D1170" t="s">
         <v>370</v>
       </c>
       <c r="E1170">
-        <v>1.68377889433222</v>
+        <v>1.657461678134128</v>
       </c>
       <c r="F1170">
         <v>-1</v>
       </c>
       <c r="G1170">
-        <v>0.006128124535856137</v>
+        <v>0.006124601873089094</v>
       </c>
       <c r="H1170">
-        <v>0.00619622110566778</v>
+        <v>0.006162538321865872</v>
       </c>
       <c r="I1170">
-        <v>0.1280965698116434</v>
+        <v>0.1579364487767774</v>
       </c>
       <c r="J1170">
-        <v>0.7545889985510968</v>
+        <v>0.7533572982829001</v>
       </c>
       <c r="K1170">
         <v>2.86</v>
@@ -60416,12 +60410,62 @@
         <v>2.99</v>
       </c>
       <c r="N1170">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="O1170">
         <v>1</v>
       </c>
       <c r="P1170" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:16">
+      <c r="A1171" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1171">
+        <v>1.811875464143863</v>
+      </c>
+      <c r="D1171" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1171">
+        <v>1.65377889433222</v>
+      </c>
+      <c r="F1171">
+        <v>-1</v>
+      </c>
+      <c r="G1171">
+        <v>0.006128124535856137</v>
+      </c>
+      <c r="H1171">
+        <v>0.00616622110566778</v>
+      </c>
+      <c r="I1171">
+        <v>0.1580965698116432</v>
+      </c>
+      <c r="J1171">
+        <v>0.7545889985510968</v>
+      </c>
+      <c r="K1171">
+        <v>2.86</v>
+      </c>
+      <c r="L1171">
+        <v>3.97</v>
+      </c>
+      <c r="M1171">
+        <v>2.99</v>
+      </c>
+      <c r="N1171">
+        <v>3.91</v>
+      </c>
+      <c r="O1171">
+        <v>1</v>
+      </c>
+      <c r="P1171" t="s">
         <v>220</v>
       </c>
     </row>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3567" uniqueCount="521">
   <si>
     <t>trade_time</t>
   </si>
@@ -1126,7 +1126,7 @@
     <t>2021-09-14</t>
   </si>
   <si>
-    <t>2021-10-11</t>
+    <t>2021-10-12</t>
   </si>
   <si>
     <t>2021-09-28</t>
@@ -1558,6 +1558,9 @@
     <t>2021-08-20</t>
   </si>
   <si>
+    <t>2021-09-02</t>
+  </si>
+  <si>
     <t>2021-09-06</t>
   </si>
   <si>
@@ -1571,6 +1574,9 @@
   </si>
   <si>
     <t>2021-09-24</t>
+  </si>
+  <si>
+    <t>2021-09-27</t>
   </si>
 </sst>
 </file>
@@ -1928,7 +1934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1180"/>
+  <dimension ref="A1:P1185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -54739,10 +54745,10 @@
         <v>1.554102912164197</v>
       </c>
       <c r="D1057" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E1057">
-        <v>1.656290650993638</v>
+        <v>1.677749143546598</v>
       </c>
       <c r="F1057">
         <v>1</v>
@@ -54751,10 +54757,10 @@
         <v>0.006945897087835803</v>
       </c>
       <c r="H1057">
-        <v>0.006743709349006363</v>
+        <v>0.006562250856453402</v>
       </c>
       <c r="I1057">
-        <v>0.102187738829441</v>
+        <v>0.1236462313824007</v>
       </c>
       <c r="J1057">
         <v>0.7247035182354308</v>
@@ -54766,10 +54772,10 @@
         <v>4.25</v>
       </c>
       <c r="M1057">
-        <v>3.51</v>
+        <v>3.37</v>
       </c>
       <c r="N1057">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -55383,10 +55389,10 @@
         <v>1</v>
       </c>
       <c r="B1070" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C1070">
-        <v>1.56546902630447</v>
+        <v>1.566169558344403</v>
       </c>
       <c r="D1070" t="s">
         <v>366</v>
@@ -55398,22 +55404,22 @@
         <v>1</v>
       </c>
       <c r="G1070">
-        <v>0.00641453097369553</v>
+        <v>0.006473830441655597</v>
       </c>
       <c r="H1070">
         <v>0.006583830441655596</v>
       </c>
       <c r="I1070">
-        <v>0.110700532039933</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1070">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1070">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1070">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1070">
         <v>3.35</v>
@@ -55433,7 +55439,7 @@
         <v>2</v>
       </c>
       <c r="B1071" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C1071">
         <v>1.56546902630447</v>
@@ -55483,28 +55489,28 @@
         <v>3</v>
       </c>
       <c r="B1072" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C1072">
-        <v>1.725469026304471</v>
+        <v>1.56546902630447</v>
       </c>
       <c r="D1072" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1072">
-        <v>1.875088040855222</v>
+        <v>1.676169558344403</v>
       </c>
       <c r="F1072">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1072">
-        <v>0.006574530973695531</v>
+        <v>0.00641453097369553</v>
       </c>
       <c r="H1072">
-        <v>0.006064911959144778</v>
+        <v>0.006583830441655596</v>
       </c>
       <c r="I1072">
-        <v>-0.1496190145507517</v>
+        <v>0.110700532039933</v>
       </c>
       <c r="J1072">
         <v>0.7324866990016706</v>
@@ -55513,13 +55519,13 @@
         <v>3.31</v>
       </c>
       <c r="L1072">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1072">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1072">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1072">
         <v>1</v>
@@ -55533,10 +55539,10 @@
         <v>4</v>
       </c>
       <c r="B1073" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1073">
-        <v>1.767890169014955</v>
+        <v>1.725469026304471</v>
       </c>
       <c r="D1073" t="s">
         <v>222</v>
@@ -55548,22 +55554,22 @@
         <v>-1</v>
       </c>
       <c r="G1073">
-        <v>0.006192109830985045</v>
+        <v>0.006574530973695531</v>
       </c>
       <c r="H1073">
         <v>0.006064911959144778</v>
       </c>
       <c r="I1073">
-        <v>-0.1071978718402673</v>
+        <v>-0.1496190145507517</v>
       </c>
       <c r="J1073">
         <v>0.7324866990016706</v>
       </c>
       <c r="K1073">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1073">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1073">
         <v>2.86</v>
@@ -55580,96 +55586,96 @@
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1074" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C1074">
-        <v>1.515332066574131</v>
+        <v>1.767890169014955</v>
       </c>
       <c r="D1074" t="s">
-        <v>368</v>
+        <v>222</v>
       </c>
       <c r="E1074">
-        <v>1.6426260925685</v>
+        <v>1.875088040855222</v>
       </c>
       <c r="F1074">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1074">
-        <v>0.00698466793342587</v>
+        <v>0.006192109830985045</v>
       </c>
       <c r="H1074">
-        <v>0.0065973739074315</v>
+        <v>0.006064911959144778</v>
       </c>
       <c r="I1074">
-        <v>0.1272940259943698</v>
+        <v>-0.1071978718402673</v>
       </c>
       <c r="J1074">
-        <v>0.7351257885553412</v>
+        <v>0.7324866990016706</v>
       </c>
       <c r="K1074">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="L1074">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="M1074">
-        <v>3.37</v>
+        <v>2.86</v>
       </c>
       <c r="N1074">
-        <v>4.12</v>
+        <v>3.97</v>
       </c>
       <c r="O1074">
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
       <c r="A1075" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1075" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C1075">
-        <v>1.716733639881821</v>
+        <v>1.515332066574131</v>
       </c>
       <c r="D1075" t="s">
-        <v>222</v>
+        <v>368</v>
       </c>
       <c r="E1075">
-        <v>1.867540244731725</v>
+        <v>1.6426260925685</v>
       </c>
       <c r="F1075">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1075">
-        <v>0.00658326636011818</v>
+        <v>0.00698466793342587</v>
       </c>
       <c r="H1075">
-        <v>0.006072459755268276</v>
+        <v>0.0065973739074315</v>
       </c>
       <c r="I1075">
-        <v>-0.1508066048499037</v>
+        <v>0.1272940259943698</v>
       </c>
       <c r="J1075">
         <v>0.7351257885553412</v>
       </c>
       <c r="K1075">
-        <v>3.31</v>
+        <v>3.72</v>
       </c>
       <c r="L1075">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="M1075">
-        <v>2.86</v>
+        <v>3.37</v>
       </c>
       <c r="N1075">
-        <v>3.97</v>
+        <v>4.12</v>
       </c>
       <c r="O1075">
         <v>1</v>
@@ -55680,46 +55686,46 @@
     </row>
     <row r="1076" spans="1:16">
       <c r="A1076" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1076" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C1076">
-        <v>1.759920118562869</v>
+        <v>1.556733639881821</v>
       </c>
       <c r="D1076" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1076">
-        <v>1.867540244731725</v>
+        <v>1.667328608339607</v>
       </c>
       <c r="F1076">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1076">
-        <v>0.006200079881437131</v>
+        <v>0.00642326636011818</v>
       </c>
       <c r="H1076">
-        <v>0.006072459755268276</v>
+        <v>0.006592671391660392</v>
       </c>
       <c r="I1076">
-        <v>-0.1076201261688552</v>
+        <v>0.1105949684577863</v>
       </c>
       <c r="J1076">
         <v>0.7351257885553412</v>
       </c>
       <c r="K1076">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1076">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1076">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1076">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1076">
         <v>1</v>
@@ -55730,90 +55736,90 @@
     </row>
     <row r="1077" spans="1:16">
       <c r="A1077" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1077" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C1077">
-        <v>1.70603114244063</v>
+        <v>1.556733639881821</v>
       </c>
       <c r="D1077" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1077">
-        <v>1.858292769601269</v>
+        <v>1.667328608339607</v>
       </c>
       <c r="F1077">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1077">
-        <v>0.006593968857559371</v>
+        <v>0.00642326636011818</v>
       </c>
       <c r="H1077">
-        <v>0.006081707230398731</v>
+        <v>0.006592671391660392</v>
       </c>
       <c r="I1077">
-        <v>-0.1522616271606392</v>
+        <v>0.1105949684577863</v>
       </c>
       <c r="J1077">
-        <v>0.7383591714680878</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1077">
         <v>3.31</v>
       </c>
       <c r="L1077">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1077">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1077">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1077">
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>214</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1078" spans="1:16">
       <c r="A1078" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1078" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1078">
-        <v>1.750155302166375</v>
+        <v>1.716733639881821</v>
       </c>
       <c r="D1078" t="s">
         <v>222</v>
       </c>
       <c r="E1078">
-        <v>1.858292769601269</v>
+        <v>1.867540244731725</v>
       </c>
       <c r="F1078">
         <v>-1</v>
       </c>
       <c r="G1078">
-        <v>0.006209844697833625</v>
+        <v>0.00658326636011818</v>
       </c>
       <c r="H1078">
-        <v>0.006081707230398731</v>
+        <v>0.006072459755268276</v>
       </c>
       <c r="I1078">
-        <v>-0.1081374674348941</v>
+        <v>-0.1508066048499037</v>
       </c>
       <c r="J1078">
-        <v>0.7383591714680878</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1078">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1078">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1078">
         <v>2.86</v>
@@ -55825,89 +55831,89 @@
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>214</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
       <c r="A1079" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1079" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1079">
-        <v>1.527785017914981</v>
+        <v>1.759920118562869</v>
       </c>
       <c r="D1079" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1079">
-        <v>1.637785017914981</v>
+        <v>1.867540244731725</v>
       </c>
       <c r="F1079">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1079">
-        <v>0.006512214982085018</v>
+        <v>0.006200079881437131</v>
       </c>
       <c r="H1079">
-        <v>0.00662221498208502</v>
+        <v>0.006072459755268276</v>
       </c>
       <c r="I1079">
-        <v>0.1100000000000003</v>
+        <v>-0.1076201261688552</v>
       </c>
       <c r="J1079">
-        <v>0.7439447707716474</v>
+        <v>0.7351257885553412</v>
       </c>
       <c r="K1079">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1079">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1079">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1079">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1079">
         <v>1</v>
       </c>
       <c r="P1079" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1080" spans="1:16">
       <c r="A1080" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1080" t="s">
         <v>216</v>
       </c>
       <c r="C1080">
-        <v>1.527542808745847</v>
+        <v>1.54603114244063</v>
       </c>
       <c r="D1080" t="s">
         <v>366</v>
       </c>
       <c r="E1080">
-        <v>1.637785017914981</v>
+        <v>1.656496775581906</v>
       </c>
       <c r="F1080">
         <v>1</v>
       </c>
       <c r="G1080">
-        <v>0.006452457191254153</v>
+        <v>0.006433968857559372</v>
       </c>
       <c r="H1080">
-        <v>0.00662221498208502</v>
+        <v>0.006603503224418095</v>
       </c>
       <c r="I1080">
-        <v>0.110242209169134</v>
+        <v>0.1104656331412759</v>
       </c>
       <c r="J1080">
-        <v>0.7439447707716474</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1080">
         <v>3.31</v>
@@ -55925,39 +55931,39 @@
         <v>1</v>
       </c>
       <c r="P1080" t="s">
-        <v>494</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1081" spans="1:16">
       <c r="A1081" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1081" t="s">
         <v>217</v>
       </c>
       <c r="C1081">
-        <v>1.527542808745847</v>
+        <v>1.54603114244063</v>
       </c>
       <c r="D1081" t="s">
         <v>366</v>
       </c>
       <c r="E1081">
-        <v>1.637785017914981</v>
+        <v>1.656496775581906</v>
       </c>
       <c r="F1081">
         <v>1</v>
       </c>
       <c r="G1081">
-        <v>0.006452457191254153</v>
+        <v>0.006433968857559372</v>
       </c>
       <c r="H1081">
-        <v>0.00662221498208502</v>
+        <v>0.006603503224418095</v>
       </c>
       <c r="I1081">
-        <v>0.110242209169134</v>
+        <v>0.1104656331412759</v>
       </c>
       <c r="J1081">
-        <v>0.7439447707716474</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1081">
         <v>3.31</v>
@@ -55975,39 +55981,39 @@
         <v>1</v>
       </c>
       <c r="P1081" t="s">
-        <v>494</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1082" spans="1:16">
       <c r="A1082" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1082" t="s">
         <v>218</v>
       </c>
       <c r="C1082">
-        <v>1.687542808745847</v>
+        <v>1.70603114244063</v>
       </c>
       <c r="D1082" t="s">
         <v>222</v>
       </c>
       <c r="E1082">
-        <v>1.842317955593089</v>
+        <v>1.858292769601269</v>
       </c>
       <c r="F1082">
         <v>-1</v>
       </c>
       <c r="G1082">
-        <v>0.006612457191254154</v>
+        <v>0.006593968857559371</v>
       </c>
       <c r="H1082">
-        <v>0.006097682044406912</v>
+        <v>0.006081707230398731</v>
       </c>
       <c r="I1082">
-        <v>-0.1547751468472414</v>
+        <v>-0.1522616271606392</v>
       </c>
       <c r="J1082">
-        <v>0.7439447707716474</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1082">
         <v>3.31</v>
@@ -56025,39 +56031,39 @@
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>494</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
       <c r="A1083" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1083" t="s">
         <v>219</v>
       </c>
       <c r="C1083">
-        <v>1.733286792269625</v>
+        <v>1.750155302166375</v>
       </c>
       <c r="D1083" t="s">
         <v>222</v>
       </c>
       <c r="E1083">
-        <v>1.842317955593089</v>
+        <v>1.858292769601269</v>
       </c>
       <c r="F1083">
         <v>-1</v>
       </c>
       <c r="G1083">
-        <v>0.006226713207730375</v>
+        <v>0.006209844697833625</v>
       </c>
       <c r="H1083">
-        <v>0.006097682044406912</v>
+        <v>0.006081707230398731</v>
       </c>
       <c r="I1083">
-        <v>-0.109031163323464</v>
+        <v>-0.1081374674348941</v>
       </c>
       <c r="J1083">
-        <v>0.7439447707716474</v>
+        <v>0.7383591714680878</v>
       </c>
       <c r="K1083">
         <v>3.02</v>
@@ -56075,7 +56081,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>494</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56086,28 +56092,28 @@
         <v>215</v>
       </c>
       <c r="C1084">
-        <v>1.512804794934651</v>
+        <v>1.527785017914981</v>
       </c>
       <c r="D1084" t="s">
         <v>366</v>
       </c>
       <c r="E1084">
-        <v>1.622804794934651</v>
+        <v>1.637785017914981</v>
       </c>
       <c r="F1084">
         <v>1</v>
       </c>
       <c r="G1084">
-        <v>0.006527195205065349</v>
+        <v>0.006512214982085018</v>
       </c>
       <c r="H1084">
-        <v>0.006637195205065348</v>
+        <v>0.00662221498208502</v>
       </c>
       <c r="I1084">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1084">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1084">
         <v>3.35</v>
@@ -56125,7 +56131,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56136,28 +56142,28 @@
         <v>216</v>
       </c>
       <c r="C1085">
-        <v>1.512741454099611</v>
+        <v>1.527542808745847</v>
       </c>
       <c r="D1085" t="s">
         <v>366</v>
       </c>
       <c r="E1085">
-        <v>1.622804794934651</v>
+        <v>1.637785017914981</v>
       </c>
       <c r="F1085">
         <v>1</v>
       </c>
       <c r="G1085">
-        <v>0.006467258545900389</v>
+        <v>0.006452457191254153</v>
       </c>
       <c r="H1085">
-        <v>0.006637195205065348</v>
+        <v>0.00662221498208502</v>
       </c>
       <c r="I1085">
-        <v>0.11006334083504</v>
+        <v>0.110242209169134</v>
       </c>
       <c r="J1085">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1085">
         <v>3.31</v>
@@ -56175,7 +56181,7 @@
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56186,28 +56192,28 @@
         <v>217</v>
       </c>
       <c r="C1086">
-        <v>1.512741454099611</v>
+        <v>1.527542808745847</v>
       </c>
       <c r="D1086" t="s">
         <v>366</v>
       </c>
       <c r="E1086">
-        <v>1.622804794934651</v>
+        <v>1.637785017914981</v>
       </c>
       <c r="F1086">
         <v>1</v>
       </c>
       <c r="G1086">
-        <v>0.006467258545900389</v>
+        <v>0.006452457191254153</v>
       </c>
       <c r="H1086">
-        <v>0.006637195205065348</v>
+        <v>0.00662221498208502</v>
       </c>
       <c r="I1086">
-        <v>0.11006334083504</v>
+        <v>0.110242209169134</v>
       </c>
       <c r="J1086">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1086">
         <v>3.31</v>
@@ -56225,7 +56231,7 @@
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
@@ -56236,28 +56242,28 @@
         <v>218</v>
       </c>
       <c r="C1087">
-        <v>1.672741454099612</v>
+        <v>1.687542808745847</v>
       </c>
       <c r="D1087" t="s">
         <v>222</v>
       </c>
       <c r="E1087">
-        <v>1.829528869705404</v>
+        <v>1.842317955593089</v>
       </c>
       <c r="F1087">
         <v>-1</v>
       </c>
       <c r="G1087">
-        <v>0.00662725854590039</v>
+        <v>0.006612457191254154</v>
       </c>
       <c r="H1087">
-        <v>0.006110471130294596</v>
+        <v>0.006097682044406912</v>
       </c>
       <c r="I1087">
-        <v>-0.1567874156057929</v>
+        <v>-0.1547751468472414</v>
       </c>
       <c r="J1087">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1087">
         <v>3.31</v>
@@ -56275,7 +56281,7 @@
         <v>1</v>
       </c>
       <c r="P1087" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1088" spans="1:16">
@@ -56286,28 +56292,28 @@
         <v>219</v>
       </c>
       <c r="C1088">
-        <v>1.719782233045567</v>
+        <v>1.733286792269625</v>
       </c>
       <c r="D1088" t="s">
         <v>222</v>
       </c>
       <c r="E1088">
-        <v>1.829528869705404</v>
+        <v>1.842317955593089</v>
       </c>
       <c r="F1088">
         <v>-1</v>
       </c>
       <c r="G1088">
-        <v>0.006240217766954434</v>
+        <v>0.006226713207730375</v>
       </c>
       <c r="H1088">
-        <v>0.006110471130294596</v>
+        <v>0.006097682044406912</v>
       </c>
       <c r="I1088">
-        <v>-0.1097466366598376</v>
+        <v>-0.109031163323464</v>
       </c>
       <c r="J1088">
-        <v>0.7484164791239846</v>
+        <v>0.7439447707716474</v>
       </c>
       <c r="K1088">
         <v>3.02</v>
@@ -56325,7 +56331,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56336,28 +56342,28 @@
         <v>215</v>
       </c>
       <c r="C1089">
-        <v>1.47676751053993</v>
+        <v>1.512804794934651</v>
       </c>
       <c r="D1089" t="s">
         <v>366</v>
       </c>
       <c r="E1089">
-        <v>1.586767510539931</v>
+        <v>1.622804794934651</v>
       </c>
       <c r="F1089">
         <v>1</v>
       </c>
       <c r="G1089">
-        <v>0.006563232489460068</v>
+        <v>0.006527195205065349</v>
       </c>
       <c r="H1089">
-        <v>0.006673232489460069</v>
+        <v>0.006637195205065348</v>
       </c>
       <c r="I1089">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1089">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1089">
         <v>3.35</v>
@@ -56375,7 +56381,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -56386,28 +56392,28 @@
         <v>216</v>
       </c>
       <c r="C1090">
-        <v>1.477134465637961</v>
+        <v>1.512741454099611</v>
       </c>
       <c r="D1090" t="s">
         <v>366</v>
       </c>
       <c r="E1090">
-        <v>1.586767510539931</v>
+        <v>1.622804794934651</v>
       </c>
       <c r="F1090">
         <v>1</v>
       </c>
       <c r="G1090">
-        <v>0.006502865534362039</v>
+        <v>0.006467258545900389</v>
       </c>
       <c r="H1090">
-        <v>0.006673232489460069</v>
+        <v>0.006637195205065348</v>
       </c>
       <c r="I1090">
-        <v>0.1096330449019693</v>
+        <v>0.11006334083504</v>
       </c>
       <c r="J1090">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1090">
         <v>3.31</v>
@@ -56425,7 +56431,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -56433,49 +56439,49 @@
         <v>2</v>
       </c>
       <c r="B1091" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C1091">
-        <v>1.637134465637962</v>
+        <v>1.512741454099611</v>
       </c>
       <c r="D1091" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1091">
-        <v>1.798762710490807</v>
+        <v>1.622804794934651</v>
       </c>
       <c r="F1091">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1091">
-        <v>0.006662865534362039</v>
+        <v>0.006467258545900389</v>
       </c>
       <c r="H1091">
-        <v>0.006141237289509194</v>
+        <v>0.006637195205065348</v>
       </c>
       <c r="I1091">
-        <v>-0.1616282448528454</v>
+        <v>0.11006334083504</v>
       </c>
       <c r="J1091">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1091">
         <v>3.31</v>
       </c>
       <c r="L1091">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1091">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1091">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1091">
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
@@ -56483,37 +56489,37 @@
         <v>3</v>
       </c>
       <c r="B1092" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1092">
-        <v>1.687294890098684</v>
+        <v>1.672741454099612</v>
       </c>
       <c r="D1092" t="s">
         <v>222</v>
       </c>
       <c r="E1092">
-        <v>1.798762710490807</v>
+        <v>1.829528869705404</v>
       </c>
       <c r="F1092">
         <v>-1</v>
       </c>
       <c r="G1092">
-        <v>0.006272705109901317</v>
+        <v>0.00662725854590039</v>
       </c>
       <c r="H1092">
-        <v>0.006141237289509194</v>
+        <v>0.006110471130294596</v>
       </c>
       <c r="I1092">
-        <v>-0.1114678203921233</v>
+        <v>-0.1567874156057929</v>
       </c>
       <c r="J1092">
-        <v>0.7591738774507669</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1092">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1092">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1092">
         <v>2.86</v>
@@ -56525,95 +56531,95 @@
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1093" spans="1:16">
       <c r="A1093" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1093" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1093">
-        <v>1.462184374678514</v>
+        <v>1.719782233045567</v>
       </c>
       <c r="D1093" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1093">
-        <v>1.572184374678514</v>
+        <v>1.829528869705404</v>
       </c>
       <c r="F1093">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1093">
-        <v>0.006577815625321485</v>
+        <v>0.006240217766954434</v>
       </c>
       <c r="H1093">
-        <v>0.006687815625321486</v>
+        <v>0.006110471130294596</v>
       </c>
       <c r="I1093">
-        <v>0.1100000000000003</v>
+        <v>-0.1097466366598376</v>
       </c>
       <c r="J1093">
-        <v>0.7635270523347718</v>
+        <v>0.7484164791239846</v>
       </c>
       <c r="K1093">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1093">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1093">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1093">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1093">
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
       <c r="A1094" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1094" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C1094">
-        <v>1.462725456771905</v>
+        <v>1.47676751053993</v>
       </c>
       <c r="D1094" t="s">
         <v>366</v>
       </c>
       <c r="E1094">
-        <v>1.572184374678514</v>
+        <v>1.586767510539931</v>
       </c>
       <c r="F1094">
         <v>1</v>
       </c>
       <c r="G1094">
-        <v>0.006517274543228095</v>
+        <v>0.006563232489460068</v>
       </c>
       <c r="H1094">
-        <v>0.006687815625321486</v>
+        <v>0.006673232489460069</v>
       </c>
       <c r="I1094">
-        <v>0.109458917906609</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1094">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1094">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1094">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1094">
         <v>3.35</v>
@@ -56625,95 +56631,95 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
       <c r="A1095" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1095" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1095">
-        <v>1.622725456771906</v>
+        <v>1.477134465637961</v>
       </c>
       <c r="D1095" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1095">
-        <v>1.786312630322553</v>
+        <v>1.586767510539931</v>
       </c>
       <c r="F1095">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1095">
-        <v>0.006677274543228095</v>
+        <v>0.006502865534362039</v>
       </c>
       <c r="H1095">
-        <v>0.006153687369677447</v>
+        <v>0.006673232489460069</v>
       </c>
       <c r="I1095">
-        <v>-0.1635871735506473</v>
+        <v>0.1096330449019693</v>
       </c>
       <c r="J1095">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1095">
         <v>3.31</v>
       </c>
       <c r="L1095">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1095">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1095">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1095">
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
       <c r="A1096" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1096" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1096">
-        <v>1.674148301948989</v>
+        <v>1.637134465637962</v>
       </c>
       <c r="D1096" t="s">
         <v>222</v>
       </c>
       <c r="E1096">
-        <v>1.786312630322553</v>
+        <v>1.798762710490807</v>
       </c>
       <c r="F1096">
         <v>-1</v>
       </c>
       <c r="G1096">
-        <v>0.006285851698051011</v>
+        <v>0.006662865534362039</v>
       </c>
       <c r="H1096">
-        <v>0.006153687369677447</v>
+        <v>0.006141237289509194</v>
       </c>
       <c r="I1096">
-        <v>-0.1121643283735638</v>
+        <v>-0.1616282448528454</v>
       </c>
       <c r="J1096">
-        <v>0.7635270523347718</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1096">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1096">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1096">
         <v>2.86</v>
@@ -56725,95 +56731,95 @@
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
       <c r="A1097" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1097" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C1097">
-        <v>1.474243425931813</v>
+        <v>1.687294890098684</v>
       </c>
       <c r="D1097" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1097">
-        <v>1.564243425931813</v>
+        <v>1.798762710490807</v>
       </c>
       <c r="F1097">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1097">
-        <v>0.006605756574068187</v>
+        <v>0.006272705109901317</v>
       </c>
       <c r="H1097">
-        <v>0.006695756574068187</v>
+        <v>0.006141237289509194</v>
       </c>
       <c r="I1097">
-        <v>0.08999999999999986</v>
+        <v>-0.1114678203921233</v>
       </c>
       <c r="J1097">
-        <v>0.7658974847964738</v>
+        <v>0.7591738774507669</v>
       </c>
       <c r="K1097">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1097">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="M1097">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1097">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1097">
         <v>1</v>
       </c>
       <c r="P1097" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1098" spans="1:16">
       <c r="A1098" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1098" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C1098">
-        <v>1.454879325323672</v>
+        <v>1.462184374678514</v>
       </c>
       <c r="D1098" t="s">
         <v>366</v>
       </c>
       <c r="E1098">
-        <v>1.564243425931813</v>
+        <v>1.572184374678514</v>
       </c>
       <c r="F1098">
         <v>1</v>
       </c>
       <c r="G1098">
-        <v>0.006525120674676328</v>
+        <v>0.006577815625321485</v>
       </c>
       <c r="H1098">
-        <v>0.006695756574068187</v>
+        <v>0.006687815625321486</v>
       </c>
       <c r="I1098">
-        <v>0.1093641006081407</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1098">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1098">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1098">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1098">
         <v>3.35</v>
@@ -56825,95 +56831,95 @@
         <v>1</v>
       </c>
       <c r="P1098" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1099" spans="1:16">
       <c r="A1099" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1099" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1099">
-        <v>1.614879325323672</v>
+        <v>1.462725456771905</v>
       </c>
       <c r="D1099" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1099">
-        <v>1.533174199563496</v>
+        <v>1.572184374678514</v>
       </c>
       <c r="F1099">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1099">
-        <v>0.006685120674676329</v>
+        <v>0.006517274543228095</v>
       </c>
       <c r="H1099">
-        <v>0.006526825800436505</v>
+        <v>0.006687815625321486</v>
       </c>
       <c r="I1099">
-        <v>0.08170512576017641</v>
+        <v>0.109458917906609</v>
       </c>
       <c r="J1099">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1099">
         <v>3.31</v>
       </c>
       <c r="L1099">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1099">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1099">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1099">
         <v>1</v>
       </c>
       <c r="P1099" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1100" spans="1:16">
       <c r="A1100" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1100" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1100">
-        <v>1.666989595914649</v>
+        <v>1.622725456771906</v>
       </c>
       <c r="D1100" t="s">
         <v>222</v>
       </c>
       <c r="E1100">
-        <v>1.779533193482085</v>
+        <v>1.786312630322553</v>
       </c>
       <c r="F1100">
         <v>-1</v>
       </c>
       <c r="G1100">
-        <v>0.006293010404085351</v>
+        <v>0.006677274543228095</v>
       </c>
       <c r="H1100">
-        <v>0.006160466806517915</v>
+        <v>0.006153687369677447</v>
       </c>
       <c r="I1100">
-        <v>-0.112543597567436</v>
+        <v>-0.1635871735506473</v>
       </c>
       <c r="J1100">
-        <v>0.7658974847964738</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1100">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1100">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1100">
         <v>2.86</v>
@@ -56925,95 +56931,95 @@
         <v>1</v>
       </c>
       <c r="P1100" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1101" spans="1:16">
       <c r="A1101" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1101" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C1101">
-        <v>1.469111076062641</v>
+        <v>1.674148301948989</v>
       </c>
       <c r="D1101" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1101">
-        <v>1.559111076062641</v>
+        <v>1.786312630322553</v>
       </c>
       <c r="F1101">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1101">
-        <v>0.006610888923937359</v>
+        <v>0.006285851698051011</v>
       </c>
       <c r="H1101">
-        <v>0.006700888923937358</v>
+        <v>0.006153687369677447</v>
       </c>
       <c r="I1101">
-        <v>0.08999999999999986</v>
+        <v>-0.1121643283735638</v>
       </c>
       <c r="J1101">
-        <v>0.7674295295335398</v>
+        <v>0.7635270523347718</v>
       </c>
       <c r="K1101">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1101">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="M1101">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1101">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1101">
         <v>1</v>
       </c>
       <c r="P1101" t="s">
-        <v>367</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1102" spans="1:16">
       <c r="A1102" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1102" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C1102">
-        <v>1.449808257243983</v>
+        <v>1.474243425931813</v>
       </c>
       <c r="D1102" t="s">
         <v>366</v>
       </c>
       <c r="E1102">
-        <v>1.559111076062641</v>
+        <v>1.564243425931813</v>
       </c>
       <c r="F1102">
         <v>1</v>
       </c>
       <c r="G1102">
-        <v>0.006530191742756017</v>
+        <v>0.006605756574068187</v>
       </c>
       <c r="H1102">
-        <v>0.006700888923937358</v>
+        <v>0.006695756574068187</v>
       </c>
       <c r="I1102">
-        <v>0.1093028188186578</v>
+        <v>0.08999999999999986</v>
       </c>
       <c r="J1102">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1102">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1102">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="M1102">
         <v>3.35</v>
@@ -57025,195 +57031,195 @@
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>367</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
       <c r="A1103" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1103" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1103">
-        <v>1.609808257243984</v>
+        <v>1.454879325323672</v>
       </c>
       <c r="D1103" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1103">
-        <v>1.52817973372066</v>
+        <v>1.564243425931813</v>
       </c>
       <c r="F1103">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1103">
-        <v>0.006690191742756017</v>
+        <v>0.006525120674676328</v>
       </c>
       <c r="H1103">
-        <v>0.00653182026627934</v>
+        <v>0.006695756574068187</v>
       </c>
       <c r="I1103">
-        <v>0.08162852352332317</v>
+        <v>0.1093641006081407</v>
       </c>
       <c r="J1103">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1103">
         <v>3.31</v>
       </c>
       <c r="L1103">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1103">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1103">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1103">
         <v>1</v>
       </c>
       <c r="P1103" t="s">
-        <v>367</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1104" spans="1:16">
       <c r="A1104" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1104" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1104">
-        <v>1.66236282080871</v>
+        <v>1.614879325323672</v>
       </c>
       <c r="D1104" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="E1104">
-        <v>1.775151545534076</v>
+        <v>1.533174199563496</v>
       </c>
       <c r="F1104">
         <v>-1</v>
       </c>
       <c r="G1104">
-        <v>0.00629763717919129</v>
+        <v>0.006685120674676329</v>
       </c>
       <c r="H1104">
-        <v>0.006164848454465924</v>
+        <v>0.006526825800436505</v>
       </c>
       <c r="I1104">
-        <v>-0.1127887247253665</v>
+        <v>0.08170512576017641</v>
       </c>
       <c r="J1104">
-        <v>0.7674295295335398</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1104">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1104">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1104">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="N1104">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="O1104">
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>367</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
       <c r="A1105" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1105" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C1105">
-        <v>1.464959075956183</v>
+        <v>1.666989595914649</v>
       </c>
       <c r="D1105" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1105">
-        <v>1.554959075956183</v>
+        <v>1.779533193482085</v>
       </c>
       <c r="F1105">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1105">
-        <v>0.006615040924043817</v>
+        <v>0.006293010404085351</v>
       </c>
       <c r="H1105">
-        <v>0.006705040924043817</v>
+        <v>0.006160466806517915</v>
       </c>
       <c r="I1105">
-        <v>0.08999999999999986</v>
+        <v>-0.112543597567436</v>
       </c>
       <c r="J1105">
-        <v>0.7686689325503931</v>
+        <v>0.7658974847964738</v>
       </c>
       <c r="K1105">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1105">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="M1105">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1105">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1105">
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>368</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
       <c r="A1106" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1106" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C1106">
-        <v>1.445705833258199</v>
+        <v>1.469111076062641</v>
       </c>
       <c r="D1106" t="s">
         <v>366</v>
       </c>
       <c r="E1106">
-        <v>1.554959075956183</v>
+        <v>1.559111076062641</v>
       </c>
       <c r="F1106">
         <v>1</v>
       </c>
       <c r="G1106">
-        <v>0.006534294166741802</v>
+        <v>0.006610888923937359</v>
       </c>
       <c r="H1106">
-        <v>0.006705040924043817</v>
+        <v>0.006700888923937358</v>
       </c>
       <c r="I1106">
-        <v>0.1092532426979842</v>
+        <v>0.08999999999999986</v>
       </c>
       <c r="J1106">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1106">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1106">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="M1106">
         <v>3.35</v>
@@ -57225,195 +57231,195 @@
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
       <c r="A1107" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1107" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1107">
-        <v>1.605705833258199</v>
+        <v>1.449808257243983</v>
       </c>
       <c r="D1107" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1107">
-        <v>1.524139279885719</v>
+        <v>1.559111076062641</v>
       </c>
       <c r="F1107">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1107">
-        <v>0.006694294166741802</v>
+        <v>0.006530191742756017</v>
       </c>
       <c r="H1107">
-        <v>0.006535860720114282</v>
+        <v>0.006700888923937358</v>
       </c>
       <c r="I1107">
-        <v>0.08156655337247987</v>
+        <v>0.1093028188186578</v>
       </c>
       <c r="J1107">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1107">
         <v>3.31</v>
       </c>
       <c r="L1107">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1107">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1107">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1107">
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
       <c r="A1108" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1108" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1108">
-        <v>1.658619823697812</v>
+        <v>1.609808257243984</v>
       </c>
       <c r="D1108" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="E1108">
-        <v>1.771606852905876</v>
+        <v>1.52817973372066</v>
       </c>
       <c r="F1108">
         <v>-1</v>
       </c>
       <c r="G1108">
-        <v>0.006301380176302187</v>
+        <v>0.006690191742756017</v>
       </c>
       <c r="H1108">
-        <v>0.006168393147094125</v>
+        <v>0.00653182026627934</v>
       </c>
       <c r="I1108">
-        <v>-0.1129870292080635</v>
+        <v>0.08162852352332317</v>
       </c>
       <c r="J1108">
-        <v>0.7686689325503931</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1108">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1108">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1108">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="N1108">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="O1108">
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
       <c r="A1109" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1109" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1109">
-        <v>1.445306718222063</v>
+        <v>1.66236282080871</v>
       </c>
       <c r="D1109" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1109">
-        <v>1.555306718222063</v>
+        <v>1.775151545534076</v>
       </c>
       <c r="F1109">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1109">
-        <v>0.006594693281777936</v>
+        <v>0.00629763717919129</v>
       </c>
       <c r="H1109">
-        <v>0.006704693281777937</v>
+        <v>0.006164848454465924</v>
       </c>
       <c r="I1109">
-        <v>0.1100000000000003</v>
+        <v>-0.1127887247253665</v>
       </c>
       <c r="J1109">
-        <v>0.7685651587396826</v>
+        <v>0.7674295295335398</v>
       </c>
       <c r="K1109">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1109">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1109">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1109">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1109">
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>499</v>
+        <v>367</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
       <c r="A1110" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1110" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C1110">
-        <v>1.446049324571651</v>
+        <v>1.464959075956183</v>
       </c>
       <c r="D1110" t="s">
         <v>366</v>
       </c>
       <c r="E1110">
-        <v>1.555306718222063</v>
+        <v>1.554959075956183</v>
       </c>
       <c r="F1110">
         <v>1</v>
       </c>
       <c r="G1110">
-        <v>0.00653395067542835</v>
+        <v>0.006615040924043817</v>
       </c>
       <c r="H1110">
-        <v>0.006704693281777937</v>
+        <v>0.006705040924043817</v>
       </c>
       <c r="I1110">
-        <v>0.1092573936504126</v>
+        <v>0.08999999999999986</v>
       </c>
       <c r="J1110">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1110">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1110">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="M1110">
         <v>3.35</v>
@@ -57425,195 +57431,195 @@
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>499</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1111" spans="1:16">
       <c r="A1111" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1111" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1111">
-        <v>1.606049324571651</v>
+        <v>1.445705833258199</v>
       </c>
       <c r="D1111" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1111">
-        <v>1.524477582508635</v>
+        <v>1.554959075956183</v>
       </c>
       <c r="F1111">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1111">
-        <v>0.00669395067542835</v>
+        <v>0.006534294166741802</v>
       </c>
       <c r="H1111">
-        <v>0.006535522417491365</v>
+        <v>0.006705040924043817</v>
       </c>
       <c r="I1111">
-        <v>0.08157174206301576</v>
+        <v>0.1092532426979842</v>
       </c>
       <c r="J1111">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1111">
         <v>3.31</v>
       </c>
       <c r="L1111">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1111">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1111">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1111">
         <v>1</v>
       </c>
       <c r="P1111" t="s">
-        <v>499</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1112" spans="1:16">
       <c r="A1112" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1112" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1112">
-        <v>1.658933220606158</v>
+        <v>1.605705833258199</v>
       </c>
       <c r="D1112" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="E1112">
-        <v>1.771903646004508</v>
+        <v>1.524139279885719</v>
       </c>
       <c r="F1112">
         <v>-1</v>
       </c>
       <c r="G1112">
-        <v>0.006301066779393841</v>
+        <v>0.006694294166741802</v>
       </c>
       <c r="H1112">
-        <v>0.006168096353995493</v>
+        <v>0.006535860720114282</v>
       </c>
       <c r="I1112">
-        <v>-0.1129704253983497</v>
+        <v>0.08156655337247987</v>
       </c>
       <c r="J1112">
-        <v>0.7685651587396826</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1112">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1112">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1112">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="N1112">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="O1112">
         <v>1</v>
       </c>
       <c r="P1112" t="s">
-        <v>499</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1113" spans="1:16">
       <c r="A1113" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1113" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1113">
-        <v>1.448878847026507</v>
+        <v>1.658619823697812</v>
       </c>
       <c r="D1113" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1113">
-        <v>1.558878847026508</v>
+        <v>1.771606852905876</v>
       </c>
       <c r="F1113">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1113">
-        <v>0.006591121152973492</v>
+        <v>0.006301380176302187</v>
       </c>
       <c r="H1113">
-        <v>0.006701121152973492</v>
+        <v>0.006168393147094125</v>
       </c>
       <c r="I1113">
-        <v>0.1100000000000003</v>
+        <v>-0.1129870292080635</v>
       </c>
       <c r="J1113">
-        <v>0.7674988516338783</v>
+        <v>0.7686689325503931</v>
       </c>
       <c r="K1113">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1113">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1113">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1113">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1113">
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>500</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
       <c r="A1114" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1114" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C1114">
-        <v>1.449578801091863</v>
+        <v>1.465306718222064</v>
       </c>
       <c r="D1114" t="s">
         <v>366</v>
       </c>
       <c r="E1114">
-        <v>1.558878847026508</v>
+        <v>1.555306718222063</v>
       </c>
       <c r="F1114">
         <v>1</v>
       </c>
       <c r="G1114">
-        <v>0.006530421198908138</v>
+        <v>0.006614693281777937</v>
       </c>
       <c r="H1114">
-        <v>0.006701121152973492</v>
+        <v>0.006704693281777937</v>
       </c>
       <c r="I1114">
-        <v>0.1093000459346447</v>
+        <v>0.08999999999999986</v>
       </c>
       <c r="J1114">
-        <v>0.7674988516338783</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1114">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1114">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="M1114">
         <v>3.35</v>
@@ -57625,195 +57631,195 @@
         <v>1</v>
       </c>
       <c r="P1114" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1115" spans="1:16">
       <c r="A1115" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1115" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1115">
-        <v>1.609578801091863</v>
+        <v>1.446049324571651</v>
       </c>
       <c r="D1115" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1115">
-        <v>1.527953743673557</v>
+        <v>1.555306718222063</v>
       </c>
       <c r="F1115">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1115">
-        <v>0.006690421198908138</v>
+        <v>0.00653395067542835</v>
       </c>
       <c r="H1115">
-        <v>0.006532046256326444</v>
+        <v>0.006704693281777937</v>
       </c>
       <c r="I1115">
-        <v>0.08162505741830595</v>
+        <v>0.1092573936504126</v>
       </c>
       <c r="J1115">
-        <v>0.7674988516338783</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1115">
         <v>3.31</v>
       </c>
       <c r="L1115">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1115">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1115">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1115">
         <v>1</v>
       </c>
       <c r="P1115" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1116" spans="1:16">
       <c r="A1116" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1116" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1116">
-        <v>1.662153468065688</v>
+        <v>1.606049324571651</v>
       </c>
       <c r="D1116" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="E1116">
-        <v>1.774953284327108</v>
+        <v>1.524477582508635</v>
       </c>
       <c r="F1116">
         <v>-1</v>
       </c>
       <c r="G1116">
-        <v>0.006297846531934313</v>
+        <v>0.00669395067542835</v>
       </c>
       <c r="H1116">
-        <v>0.006165046715672892</v>
+        <v>0.006535522417491365</v>
       </c>
       <c r="I1116">
-        <v>-0.1127998162614205</v>
+        <v>0.08157174206301576</v>
       </c>
       <c r="J1116">
-        <v>0.7674988516338783</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1116">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1116">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1116">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="N1116">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="O1116">
         <v>1</v>
       </c>
       <c r="P1116" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1117" spans="1:16">
       <c r="A1117" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1117" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1117">
-        <v>1.442972238067567</v>
+        <v>1.658933220606158</v>
       </c>
       <c r="D1117" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1117">
-        <v>1.552972238067567</v>
+        <v>1.771903646004508</v>
       </c>
       <c r="F1117">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1117">
-        <v>0.006597027761932432</v>
+        <v>0.006301066779393841</v>
       </c>
       <c r="H1117">
-        <v>0.006707027761932433</v>
+        <v>0.006168096353995493</v>
       </c>
       <c r="I1117">
-        <v>0.1100000000000003</v>
+        <v>-0.1129704253983497</v>
       </c>
       <c r="J1117">
-        <v>0.7692620184872934</v>
+        <v>0.7685651587396826</v>
       </c>
       <c r="K1117">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1117">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1117">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1117">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1117">
         <v>1</v>
       </c>
       <c r="P1117" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1118" spans="1:16">
       <c r="A1118" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1118" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C1118">
-        <v>1.443742718807059</v>
+        <v>1.468878847026508</v>
       </c>
       <c r="D1118" t="s">
         <v>366</v>
       </c>
       <c r="E1118">
-        <v>1.552972238067567</v>
+        <v>1.558878847026508</v>
       </c>
       <c r="F1118">
         <v>1</v>
       </c>
       <c r="G1118">
-        <v>0.006536257281192942</v>
+        <v>0.006611121152973493</v>
       </c>
       <c r="H1118">
-        <v>0.006707027761932433</v>
+        <v>0.006701121152973492</v>
       </c>
       <c r="I1118">
-        <v>0.1092295192605079</v>
+        <v>0.08999999999999986</v>
       </c>
       <c r="J1118">
-        <v>0.7692620184872934</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1118">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1118">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="M1118">
         <v>3.35</v>
@@ -57825,195 +57831,195 @@
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
       <c r="A1119" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1119" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1119">
-        <v>1.603742718807059</v>
+        <v>1.449578801091863</v>
       </c>
       <c r="D1119" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1119">
-        <v>1.522205819731424</v>
+        <v>1.558878847026508</v>
       </c>
       <c r="F1119">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1119">
-        <v>0.006696257281192942</v>
+        <v>0.006530421198908138</v>
       </c>
       <c r="H1119">
-        <v>0.006537794180268577</v>
+        <v>0.006701121152973492</v>
       </c>
       <c r="I1119">
-        <v>0.08153689907563511</v>
+        <v>0.1093000459346447</v>
       </c>
       <c r="J1119">
-        <v>0.7692620184872934</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1119">
         <v>3.31</v>
       </c>
       <c r="L1119">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1119">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1119">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1119">
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
       <c r="A1120" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1120" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1120">
-        <v>1.656828704168374</v>
+        <v>1.609578801091863</v>
       </c>
       <c r="D1120" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="E1120">
-        <v>1.769910627126341</v>
+        <v>1.527953743673557</v>
       </c>
       <c r="F1120">
         <v>-1</v>
       </c>
       <c r="G1120">
-        <v>0.006303171295831626</v>
+        <v>0.006690421198908138</v>
       </c>
       <c r="H1120">
-        <v>0.006170089372873659</v>
+        <v>0.006532046256326444</v>
       </c>
       <c r="I1120">
-        <v>-0.1130819229579676</v>
+        <v>0.08162505741830595</v>
       </c>
       <c r="J1120">
-        <v>0.7692620184872934</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1120">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1120">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1120">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="N1120">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="O1120">
         <v>1</v>
       </c>
       <c r="P1120" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1121" spans="1:16">
       <c r="A1121" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1121" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1121">
-        <v>1.443432272837593</v>
+        <v>1.662153468065688</v>
       </c>
       <c r="D1121" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1121">
-        <v>1.553432272837593</v>
+        <v>1.774953284327108</v>
       </c>
       <c r="F1121">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1121">
-        <v>0.006596567727162407</v>
+        <v>0.006297846531934313</v>
       </c>
       <c r="H1121">
-        <v>0.006706567727162407</v>
+        <v>0.006165046715672892</v>
       </c>
       <c r="I1121">
-        <v>0.1100000000000003</v>
+        <v>-0.1127998162614205</v>
       </c>
       <c r="J1121">
-        <v>0.7691246946753454</v>
+        <v>0.7674988516338783</v>
       </c>
       <c r="K1121">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1121">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1121">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1121">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1121">
         <v>1</v>
       </c>
       <c r="P1121" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1122" spans="1:16">
       <c r="A1122" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1122" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C1122">
-        <v>1.444197260624607</v>
+        <v>1.442972238067567</v>
       </c>
       <c r="D1122" t="s">
         <v>366</v>
       </c>
       <c r="E1122">
-        <v>1.553432272837593</v>
+        <v>1.552972238067567</v>
       </c>
       <c r="F1122">
         <v>1</v>
       </c>
       <c r="G1122">
-        <v>0.006535802739375394</v>
+        <v>0.006597027761932432</v>
       </c>
       <c r="H1122">
-        <v>0.006706567727162407</v>
+        <v>0.006707027761932433</v>
       </c>
       <c r="I1122">
-        <v>0.1092350122129861</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1122">
-        <v>0.7691246946753454</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1122">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1122">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1122">
         <v>3.35</v>
@@ -58025,195 +58031,195 @@
         <v>1</v>
       </c>
       <c r="P1122" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1123" spans="1:16">
       <c r="A1123" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1123" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1123">
-        <v>1.604197260624607</v>
+        <v>1.443742718807059</v>
       </c>
       <c r="D1123" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1123">
-        <v>1.522653495358374</v>
+        <v>1.552972238067567</v>
       </c>
       <c r="F1123">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1123">
-        <v>0.006695802739375393</v>
+        <v>0.006536257281192942</v>
       </c>
       <c r="H1123">
-        <v>0.006537346504641626</v>
+        <v>0.006707027761932433</v>
       </c>
       <c r="I1123">
-        <v>0.08154376526623253</v>
+        <v>0.1092295192605079</v>
       </c>
       <c r="J1123">
-        <v>0.7691246946753454</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1123">
         <v>3.31</v>
       </c>
       <c r="L1123">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1123">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1123">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1123">
         <v>1</v>
       </c>
       <c r="P1123" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1124" spans="1:16">
       <c r="A1124" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1124" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1124">
-        <v>1.657243422080457</v>
+        <v>1.603742718807059</v>
       </c>
       <c r="D1124" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="E1124">
-        <v>1.770303373228512</v>
+        <v>1.522205819731424</v>
       </c>
       <c r="F1124">
         <v>-1</v>
       </c>
       <c r="G1124">
-        <v>0.006302756577919543</v>
+        <v>0.006696257281192942</v>
       </c>
       <c r="H1124">
-        <v>0.006169696626771489</v>
+        <v>0.006537794180268577</v>
       </c>
       <c r="I1124">
-        <v>-0.1130599511480552</v>
+        <v>0.08153689907563511</v>
       </c>
       <c r="J1124">
-        <v>0.7691246946753454</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1124">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1124">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1124">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="N1124">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="O1124">
         <v>1</v>
       </c>
       <c r="P1124" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1125" spans="1:16">
       <c r="A1125" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1125" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1125">
-        <v>1.432380537847326</v>
+        <v>1.656828704168374</v>
       </c>
       <c r="D1125" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1125">
-        <v>1.542380537847327</v>
+        <v>1.769910627126341</v>
       </c>
       <c r="F1125">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1125">
-        <v>0.006607619462152673</v>
+        <v>0.006303171295831626</v>
       </c>
       <c r="H1125">
-        <v>0.006717619462152673</v>
+        <v>0.006170089372873659</v>
       </c>
       <c r="I1125">
-        <v>0.1100000000000003</v>
+        <v>-0.1130819229579676</v>
       </c>
       <c r="J1125">
-        <v>0.772423720045574</v>
+        <v>0.7692620184872934</v>
       </c>
       <c r="K1125">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1125">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1125">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1125">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1125">
         <v>1</v>
       </c>
       <c r="P1125" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1126" spans="1:16">
       <c r="A1126" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1126" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C1126">
-        <v>1.43327748664915</v>
+        <v>1.443432272837593</v>
       </c>
       <c r="D1126" t="s">
         <v>366</v>
       </c>
       <c r="E1126">
-        <v>1.542380537847327</v>
+        <v>1.553432272837593</v>
       </c>
       <c r="F1126">
         <v>1</v>
       </c>
       <c r="G1126">
-        <v>0.006546722513350851</v>
+        <v>0.006596567727162407</v>
       </c>
       <c r="H1126">
-        <v>0.006717619462152673</v>
+        <v>0.006706567727162407</v>
       </c>
       <c r="I1126">
-        <v>0.1091030511981765</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1126">
-        <v>0.772423720045574</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1126">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1126">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1126">
         <v>3.35</v>
@@ -58225,195 +58231,195 @@
         <v>1</v>
       </c>
       <c r="P1126" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1127" spans="1:16">
       <c r="A1127" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1127" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1127">
-        <v>1.59327748664915</v>
+        <v>1.444197260624607</v>
       </c>
       <c r="D1127" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1127">
-        <v>1.511898672651429</v>
+        <v>1.553432272837593</v>
       </c>
       <c r="F1127">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1127">
-        <v>0.006706722513350851</v>
+        <v>0.006535802739375394</v>
       </c>
       <c r="H1127">
-        <v>0.006548101327348572</v>
+        <v>0.006706567727162407</v>
       </c>
       <c r="I1127">
-        <v>0.08137881399772118</v>
+        <v>0.1092350122129861</v>
       </c>
       <c r="J1127">
-        <v>0.772423720045574</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1127">
         <v>3.31</v>
       </c>
       <c r="L1127">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1127">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1127">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1127">
         <v>1</v>
       </c>
       <c r="P1127" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1128" spans="1:16">
       <c r="A1128" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1128" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1128">
-        <v>1.647280365462366</v>
+        <v>1.604197260624607</v>
       </c>
       <c r="D1128" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="E1128">
-        <v>1.760868160669659</v>
+        <v>1.522653495358374</v>
       </c>
       <c r="F1128">
         <v>-1</v>
       </c>
       <c r="G1128">
-        <v>0.006312719634537634</v>
+        <v>0.006695802739375393</v>
       </c>
       <c r="H1128">
-        <v>0.006179131839330342</v>
+        <v>0.006537346504641626</v>
       </c>
       <c r="I1128">
-        <v>-0.1135877952072923</v>
+        <v>0.08154376526623253</v>
       </c>
       <c r="J1128">
-        <v>0.772423720045574</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1128">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1128">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1128">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="N1128">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="O1128">
         <v>1</v>
       </c>
       <c r="P1128" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1129" spans="1:16">
       <c r="A1129" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1129" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1129">
-        <v>1.431193937725116</v>
+        <v>1.657243422080457</v>
       </c>
       <c r="D1129" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1129">
-        <v>1.541193937725116</v>
+        <v>1.770303373228512</v>
       </c>
       <c r="F1129">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1129">
-        <v>0.006608806062274883</v>
+        <v>0.006302756577919543</v>
       </c>
       <c r="H1129">
-        <v>0.006718806062274884</v>
+        <v>0.006169696626771489</v>
       </c>
       <c r="I1129">
-        <v>0.1100000000000003</v>
+        <v>-0.1130599511480552</v>
       </c>
       <c r="J1129">
-        <v>0.7727779290372787</v>
+        <v>0.7691246946753454</v>
       </c>
       <c r="K1129">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1129">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1129">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1129">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1129">
         <v>1</v>
       </c>
       <c r="P1129" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1130" spans="1:16">
       <c r="A1130" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1130" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C1130">
-        <v>1.432105054886608</v>
+        <v>1.432380537847326</v>
       </c>
       <c r="D1130" t="s">
         <v>366</v>
       </c>
       <c r="E1130">
-        <v>1.541193937725116</v>
+        <v>1.542380537847327</v>
       </c>
       <c r="F1130">
         <v>1</v>
       </c>
       <c r="G1130">
-        <v>0.006547894945113393</v>
+        <v>0.006607619462152673</v>
       </c>
       <c r="H1130">
-        <v>0.006718806062274884</v>
+        <v>0.006717619462152673</v>
       </c>
       <c r="I1130">
-        <v>0.1090888828385084</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1130">
-        <v>0.7727779290372787</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1130">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1130">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1130">
         <v>3.35</v>
@@ -58425,195 +58431,195 @@
         <v>1</v>
       </c>
       <c r="P1130" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1131" spans="1:16">
       <c r="A1131" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1131" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1131">
-        <v>1.592105054886608</v>
+        <v>1.43327748664915</v>
       </c>
       <c r="D1131" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1131">
-        <v>1.510743951338472</v>
+        <v>1.542380537847327</v>
       </c>
       <c r="F1131">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1131">
-        <v>0.006707894945113394</v>
+        <v>0.006546722513350851</v>
       </c>
       <c r="H1131">
-        <v>0.006549256048661529</v>
+        <v>0.006717619462152673</v>
       </c>
       <c r="I1131">
-        <v>0.08136110354813608</v>
+        <v>0.1091030511981765</v>
       </c>
       <c r="J1131">
-        <v>0.7727779290372787</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1131">
         <v>3.31</v>
       </c>
       <c r="L1131">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1131">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1131">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1131">
         <v>1</v>
       </c>
       <c r="P1131" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1132" spans="1:16">
       <c r="A1132" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1132" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1132">
-        <v>1.646210654307418</v>
+        <v>1.59327748664915</v>
       </c>
       <c r="D1132" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="E1132">
-        <v>1.759855122953383</v>
+        <v>1.511898672651429</v>
       </c>
       <c r="F1132">
         <v>-1</v>
       </c>
       <c r="G1132">
-        <v>0.006313789345692582</v>
+        <v>0.006706722513350851</v>
       </c>
       <c r="H1132">
-        <v>0.006180144877046617</v>
+        <v>0.006548101327348572</v>
       </c>
       <c r="I1132">
-        <v>-0.1136444686459646</v>
+        <v>0.08137881399772118</v>
       </c>
       <c r="J1132">
-        <v>0.7727779290372787</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1132">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1132">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1132">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="N1132">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="O1132">
         <v>1</v>
       </c>
       <c r="P1132" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1133" spans="1:16">
       <c r="A1133" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1133" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1133">
-        <v>1.432233461226324</v>
+        <v>1.647280365462366</v>
       </c>
       <c r="D1133" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1133">
-        <v>1.542233461226325</v>
+        <v>1.760868160669659</v>
       </c>
       <c r="F1133">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1133">
-        <v>0.006607766538773674</v>
+        <v>0.006312719634537634</v>
       </c>
       <c r="H1133">
-        <v>0.006717766538773676</v>
+        <v>0.006179131839330342</v>
       </c>
       <c r="I1133">
-        <v>0.1100000000000003</v>
+        <v>-0.1135877952072923</v>
       </c>
       <c r="J1133">
-        <v>0.7724676235145299</v>
+        <v>0.772423720045574</v>
       </c>
       <c r="K1133">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1133">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1133">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1133">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1133">
         <v>1</v>
       </c>
       <c r="P1133" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1134" spans="1:16">
       <c r="A1134" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1134" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C1134">
-        <v>1.433132166166906</v>
+        <v>1.431193937725116</v>
       </c>
       <c r="D1134" t="s">
         <v>366</v>
       </c>
       <c r="E1134">
-        <v>1.542233461226325</v>
+        <v>1.541193937725116</v>
       </c>
       <c r="F1134">
         <v>1</v>
       </c>
       <c r="G1134">
-        <v>0.006546867833833094</v>
+        <v>0.006608806062274883</v>
       </c>
       <c r="H1134">
-        <v>0.006717766538773676</v>
+        <v>0.006718806062274884</v>
       </c>
       <c r="I1134">
-        <v>0.1091012950594186</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1134">
-        <v>0.7724676235145299</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1134">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1134">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1134">
         <v>3.35</v>
@@ -58625,195 +58631,195 @@
         <v>1</v>
       </c>
       <c r="P1134" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1135" spans="1:16">
       <c r="A1135" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1135" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C1135">
-        <v>1.593132166166906</v>
+        <v>1.432105054886608</v>
       </c>
       <c r="D1135" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1135">
-        <v>1.511755547342633</v>
+        <v>1.541193937725116</v>
       </c>
       <c r="F1135">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1135">
-        <v>0.006706867833833094</v>
+        <v>0.006547894945113393</v>
       </c>
       <c r="H1135">
-        <v>0.006548244452657368</v>
+        <v>0.006718806062274884</v>
       </c>
       <c r="I1135">
-        <v>0.08137661882427327</v>
+        <v>0.1090888828385084</v>
       </c>
       <c r="J1135">
-        <v>0.7724676235145299</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1135">
         <v>3.31</v>
       </c>
       <c r="L1135">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="M1135">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1135">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1135">
         <v>1</v>
       </c>
       <c r="P1135" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1136" spans="1:16">
       <c r="A1136" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1136" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C1136">
-        <v>1.64714777698612</v>
+        <v>1.592105054886608</v>
       </c>
       <c r="D1136" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="E1136">
-        <v>1.760742596748445</v>
+        <v>1.510743951338472</v>
       </c>
       <c r="F1136">
         <v>-1</v>
       </c>
       <c r="G1136">
-        <v>0.006312852223013881</v>
+        <v>0.006707894945113394</v>
       </c>
       <c r="H1136">
-        <v>0.006179257403251556</v>
+        <v>0.006549256048661529</v>
       </c>
       <c r="I1136">
-        <v>-0.1135948197623251</v>
+        <v>0.08136110354813608</v>
       </c>
       <c r="J1136">
-        <v>0.7724676235145299</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1136">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1136">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="M1136">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="N1136">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="O1136">
         <v>1</v>
       </c>
       <c r="P1136" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1137" spans="1:16">
       <c r="A1137" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1137" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1137">
-        <v>1.438192457750358</v>
+        <v>1.646210654307418</v>
       </c>
       <c r="D1137" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1137">
-        <v>1.548192457750359</v>
+        <v>1.759855122953383</v>
       </c>
       <c r="F1137">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1137">
-        <v>0.00660180754224964</v>
+        <v>0.006313789345692582</v>
       </c>
       <c r="H1137">
-        <v>0.006711807542249641</v>
+        <v>0.006180144877046617</v>
       </c>
       <c r="I1137">
-        <v>0.1100000000000003</v>
+        <v>-0.1136444686459646</v>
       </c>
       <c r="J1137">
-        <v>0.7706888185819823</v>
+        <v>0.7727779290372787</v>
       </c>
       <c r="K1137">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="L1137">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="M1137">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1137">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1137">
         <v>1</v>
       </c>
       <c r="P1137" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1138" spans="1:16">
       <c r="A1138" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1138" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C1138">
-        <v>1.439020010493639</v>
+        <v>1.432233461226324</v>
       </c>
       <c r="D1138" t="s">
         <v>366</v>
       </c>
       <c r="E1138">
-        <v>1.548192457750359</v>
+        <v>1.542233461226325</v>
       </c>
       <c r="F1138">
         <v>1</v>
       </c>
       <c r="G1138">
-        <v>0.006540979989506361</v>
+        <v>0.006607766538773674</v>
       </c>
       <c r="H1138">
-        <v>0.006711807542249641</v>
+        <v>0.006717766538773676</v>
       </c>
       <c r="I1138">
-        <v>0.1091724472567202</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1138">
-        <v>0.7706888185819823</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1138">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1138">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="M1138">
         <v>3.35</v>
@@ -58825,39 +58831,39 @@
         <v>1</v>
       </c>
       <c r="P1138" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1139" spans="1:16">
       <c r="A1139" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1139" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C1139">
-        <v>1.439020010493639</v>
+        <v>1.433132166166906</v>
       </c>
       <c r="D1139" t="s">
         <v>366</v>
       </c>
       <c r="E1139">
-        <v>1.548192457750359</v>
+        <v>1.542233461226325</v>
       </c>
       <c r="F1139">
         <v>1</v>
       </c>
       <c r="G1139">
-        <v>0.006540979989506361</v>
+        <v>0.006546867833833094</v>
       </c>
       <c r="H1139">
-        <v>0.006711807542249641</v>
+        <v>0.006717766538773676</v>
       </c>
       <c r="I1139">
-        <v>0.1091724472567202</v>
+        <v>0.1091012950594186</v>
       </c>
       <c r="J1139">
-        <v>0.7706888185819823</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1139">
         <v>3.31</v>
@@ -58875,39 +58881,39 @@
         <v>1</v>
       </c>
       <c r="P1139" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1140" spans="1:16">
       <c r="A1140" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1140" t="s">
         <v>218</v>
       </c>
       <c r="C1140">
-        <v>1.599020010493639</v>
+        <v>1.593132166166906</v>
       </c>
       <c r="D1140" t="s">
         <v>369</v>
       </c>
       <c r="E1140">
-        <v>1.517554451422738</v>
+        <v>1.511755547342633</v>
       </c>
       <c r="F1140">
         <v>-1</v>
       </c>
       <c r="G1140">
-        <v>0.006700979989506362</v>
+        <v>0.006706867833833094</v>
       </c>
       <c r="H1140">
-        <v>0.006542445548577263</v>
+        <v>0.006548244452657368</v>
       </c>
       <c r="I1140">
-        <v>0.08146555907090081</v>
+        <v>0.08137661882427327</v>
       </c>
       <c r="J1140">
-        <v>0.7706888185819823</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1140">
         <v>3.31</v>
@@ -58925,39 +58931,39 @@
         <v>1</v>
       </c>
       <c r="P1140" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1141" spans="1:16">
       <c r="A1141" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1141" t="s">
         <v>219</v>
       </c>
       <c r="C1141">
-        <v>1.652519767882413</v>
+        <v>1.64714777698612</v>
       </c>
       <c r="D1141" t="s">
         <v>222</v>
       </c>
       <c r="E1141">
-        <v>1.765829978855531</v>
+        <v>1.760742596748445</v>
       </c>
       <c r="F1141">
         <v>-1</v>
       </c>
       <c r="G1141">
-        <v>0.006307480232117587</v>
+        <v>0.006312852223013881</v>
       </c>
       <c r="H1141">
-        <v>0.00617417002114447</v>
+        <v>0.006179257403251556</v>
       </c>
       <c r="I1141">
-        <v>-0.1133102109731179</v>
+        <v>-0.1135948197623251</v>
       </c>
       <c r="J1141">
-        <v>0.7706888185819823</v>
+        <v>0.7724676235145299</v>
       </c>
       <c r="K1141">
         <v>3.02</v>
@@ -58975,7 +58981,7 @@
         <v>1</v>
       </c>
       <c r="P1141" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1142" spans="1:16">
@@ -58986,28 +58992,28 @@
         <v>215</v>
       </c>
       <c r="C1142">
-        <v>1.442360905903367</v>
+        <v>1.438192457750358</v>
       </c>
       <c r="D1142" t="s">
         <v>366</v>
       </c>
       <c r="E1142">
-        <v>1.552360905903368</v>
+        <v>1.548192457750359</v>
       </c>
       <c r="F1142">
         <v>1</v>
       </c>
       <c r="G1142">
-        <v>0.006597639094096632</v>
+        <v>0.00660180754224964</v>
       </c>
       <c r="H1142">
-        <v>0.006707639094096632</v>
+        <v>0.006711807542249641</v>
       </c>
       <c r="I1142">
         <v>0.1100000000000003</v>
       </c>
       <c r="J1142">
-        <v>0.7694445057004873</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1142">
         <v>3.35</v>
@@ -59025,7 +59031,7 @@
         <v>1</v>
       </c>
       <c r="P1142" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1143" spans="1:16">
@@ -59036,28 +59042,28 @@
         <v>216</v>
       </c>
       <c r="C1143">
-        <v>1.443138686131387</v>
+        <v>1.439020010493639</v>
       </c>
       <c r="D1143" t="s">
         <v>366</v>
       </c>
       <c r="E1143">
-        <v>1.552360905903368</v>
+        <v>1.548192457750359</v>
       </c>
       <c r="F1143">
         <v>1</v>
       </c>
       <c r="G1143">
-        <v>0.006536861313868613</v>
+        <v>0.006540979989506361</v>
       </c>
       <c r="H1143">
-        <v>0.006707639094096632</v>
+        <v>0.006711807542249641</v>
       </c>
       <c r="I1143">
-        <v>0.1092222197719805</v>
+        <v>0.1091724472567202</v>
       </c>
       <c r="J1143">
-        <v>0.7694445057004873</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1143">
         <v>3.31</v>
@@ -59075,7 +59081,7 @@
         <v>1</v>
       </c>
       <c r="P1143" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1144" spans="1:16">
@@ -59083,49 +59089,49 @@
         <v>2</v>
       </c>
       <c r="B1144" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C1144">
-        <v>1.443138686131387</v>
+        <v>1.599020010493639</v>
       </c>
       <c r="D1144" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1144">
-        <v>1.552360905903368</v>
+        <v>1.517554451422738</v>
       </c>
       <c r="F1144">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1144">
-        <v>0.006536861313868613</v>
+        <v>0.006700979989506362</v>
       </c>
       <c r="H1144">
-        <v>0.006707639094096632</v>
+        <v>0.006542445548577263</v>
       </c>
       <c r="I1144">
-        <v>0.1092222197719805</v>
+        <v>0.08146555907090081</v>
       </c>
       <c r="J1144">
-        <v>0.7694445057004873</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1144">
         <v>3.31</v>
       </c>
       <c r="L1144">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1144">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1144">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1144">
         <v>1</v>
       </c>
       <c r="P1144" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1145" spans="1:16">
@@ -59133,93 +59139,93 @@
         <v>3</v>
       </c>
       <c r="B1145" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C1145">
-        <v>1.603138686131387</v>
+        <v>1.652519767882413</v>
       </c>
       <c r="D1145" t="s">
-        <v>369</v>
+        <v>222</v>
       </c>
       <c r="E1145">
-        <v>1.521610911416412</v>
+        <v>1.765829978855531</v>
       </c>
       <c r="F1145">
         <v>-1</v>
       </c>
       <c r="G1145">
-        <v>0.006696861313868614</v>
+        <v>0.006307480232117587</v>
       </c>
       <c r="H1145">
-        <v>0.006538389088583589</v>
+        <v>0.00617417002114447</v>
       </c>
       <c r="I1145">
-        <v>0.08152777471497519</v>
+        <v>-0.1133102109731179</v>
       </c>
       <c r="J1145">
-        <v>0.7694445057004873</v>
+        <v>0.7706888185819823</v>
       </c>
       <c r="K1145">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1145">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1145">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1145">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1145">
         <v>1</v>
       </c>
       <c r="P1145" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1146" spans="1:16">
       <c r="A1146" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1146" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C1146">
-        <v>1.656277592784528</v>
+        <v>1.442360905903367</v>
       </c>
       <c r="D1146" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1146">
-        <v>1.769388713696607</v>
+        <v>1.552360905903368</v>
       </c>
       <c r="F1146">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1146">
-        <v>0.006303722407215472</v>
+        <v>0.006597639094096632</v>
       </c>
       <c r="H1146">
-        <v>0.006170611286303394</v>
+        <v>0.006707639094096632</v>
       </c>
       <c r="I1146">
-        <v>-0.1131111209120785</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1146">
         <v>0.7694445057004873</v>
       </c>
       <c r="K1146">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="L1146">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="M1146">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1146">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1146">
         <v>1</v>
@@ -59230,40 +59236,40 @@
     </row>
     <row r="1147" spans="1:16">
       <c r="A1147" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1147" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C1147">
-        <v>1.442612807343595</v>
+        <v>1.443138686131387</v>
       </c>
       <c r="D1147" t="s">
         <v>366</v>
       </c>
       <c r="E1147">
-        <v>1.552612807343595</v>
+        <v>1.552360905903368</v>
       </c>
       <c r="F1147">
         <v>1</v>
       </c>
       <c r="G1147">
-        <v>0.006597387192656404</v>
+        <v>0.006536861313868613</v>
       </c>
       <c r="H1147">
-        <v>0.006707387192656404</v>
+        <v>0.006707639094096632</v>
       </c>
       <c r="I1147">
-        <v>0.1100000000000003</v>
+        <v>0.1092222197719805</v>
       </c>
       <c r="J1147">
-        <v>0.7693693112407177</v>
+        <v>0.7694445057004873</v>
       </c>
       <c r="K1147">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1147">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1147">
         <v>3.35</v>
@@ -59275,151 +59281,151 @@
         <v>1</v>
       </c>
       <c r="P1147" t="s">
-        <v>220</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1148" spans="1:16">
       <c r="A1148" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1148" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C1148">
-        <v>1.443387579793225</v>
+        <v>1.603138686131387</v>
       </c>
       <c r="D1148" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1148">
-        <v>1.552612807343595</v>
+        <v>1.521610911416412</v>
       </c>
       <c r="F1148">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1148">
-        <v>0.006536612420206776</v>
+        <v>0.006696861313868614</v>
       </c>
       <c r="H1148">
-        <v>0.006707387192656404</v>
+        <v>0.006538389088583589</v>
       </c>
       <c r="I1148">
-        <v>0.1092252275503709</v>
+        <v>0.08152777471497519</v>
       </c>
       <c r="J1148">
-        <v>0.7693693112407177</v>
+        <v>0.7694445057004873</v>
       </c>
       <c r="K1148">
         <v>3.31</v>
       </c>
       <c r="L1148">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1148">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1148">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1148">
         <v>1</v>
       </c>
       <c r="P1148" t="s">
-        <v>220</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1149" spans="1:16">
       <c r="A1149" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1149" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C1149">
-        <v>1.443387579793225</v>
+        <v>1.656277592784528</v>
       </c>
       <c r="D1149" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1149">
-        <v>1.552612807343595</v>
+        <v>1.769388713696607</v>
       </c>
       <c r="F1149">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1149">
-        <v>0.006536612420206776</v>
+        <v>0.006303722407215472</v>
       </c>
       <c r="H1149">
-        <v>0.006707387192656404</v>
+        <v>0.006170611286303394</v>
       </c>
       <c r="I1149">
-        <v>0.1092252275503709</v>
+        <v>-0.1131111209120785</v>
       </c>
       <c r="J1149">
-        <v>0.7693693112407177</v>
+        <v>0.7694445057004873</v>
       </c>
       <c r="K1149">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1149">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1149">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1149">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1149">
         <v>1</v>
       </c>
       <c r="P1149" t="s">
-        <v>220</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1150" spans="1:16">
       <c r="A1150" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1150" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C1150">
-        <v>1.603387579793225</v>
+        <v>1.442612807343595</v>
       </c>
       <c r="D1150" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E1150">
-        <v>1.521856045355261</v>
+        <v>1.552612807343595</v>
       </c>
       <c r="F1150">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1150">
-        <v>0.006696612420206776</v>
+        <v>0.006597387192656404</v>
       </c>
       <c r="H1150">
-        <v>0.00653814395464474</v>
+        <v>0.006707387192656404</v>
       </c>
       <c r="I1150">
-        <v>0.08153153443796413</v>
+        <v>0.1100000000000003</v>
       </c>
       <c r="J1150">
         <v>0.7693693112407177</v>
       </c>
       <c r="K1150">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="L1150">
-        <v>4.15</v>
+        <v>4.02</v>
       </c>
       <c r="M1150">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N1150">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="O1150">
         <v>1</v>
@@ -59430,46 +59436,46 @@
     </row>
     <row r="1151" spans="1:16">
       <c r="A1151" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1151" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C1151">
-        <v>1.656504680053033</v>
+        <v>1.443387579793225</v>
       </c>
       <c r="D1151" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1151">
-        <v>1.769603769851547</v>
+        <v>1.552612807343595</v>
       </c>
       <c r="F1151">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1151">
-        <v>0.006303495319946967</v>
+        <v>0.006536612420206776</v>
       </c>
       <c r="H1151">
-        <v>0.006170396230148453</v>
+        <v>0.006707387192656404</v>
       </c>
       <c r="I1151">
-        <v>-0.1130990897985149</v>
+        <v>0.1092252275503709</v>
       </c>
       <c r="J1151">
         <v>0.7693693112407177</v>
       </c>
       <c r="K1151">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1151">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1151">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1151">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1151">
         <v>1</v>
@@ -59480,34 +59486,34 @@
     </row>
     <row r="1152" spans="1:16">
       <c r="A1152" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1152" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C1152">
-        <v>1.440857964887927</v>
+        <v>1.443387579793225</v>
       </c>
       <c r="D1152" t="s">
         <v>366</v>
       </c>
       <c r="E1152">
-        <v>1.550052623073884</v>
+        <v>1.552612807343595</v>
       </c>
       <c r="F1152">
         <v>1</v>
       </c>
       <c r="G1152">
-        <v>0.006539142035112073</v>
+        <v>0.006536612420206776</v>
       </c>
       <c r="H1152">
-        <v>0.006709947376926117</v>
+        <v>0.006707387192656404</v>
       </c>
       <c r="I1152">
-        <v>0.1091946581859564</v>
+        <v>0.1092252275503709</v>
       </c>
       <c r="J1152">
-        <v>0.7701335453510795</v>
+        <v>0.7693693112407177</v>
       </c>
       <c r="K1152">
         <v>3.31</v>
@@ -59525,151 +59531,151 @@
         <v>1</v>
       </c>
       <c r="P1152" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1153" spans="1:16">
       <c r="A1153" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1153" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C1153">
-        <v>1.440857964887927</v>
+        <v>1.603387579793225</v>
       </c>
       <c r="D1153" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1153">
-        <v>1.550052623073884</v>
+        <v>1.521856045355261</v>
       </c>
       <c r="F1153">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1153">
-        <v>0.006539142035112073</v>
+        <v>0.006696612420206776</v>
       </c>
       <c r="H1153">
-        <v>0.006709947376926117</v>
+        <v>0.00653814395464474</v>
       </c>
       <c r="I1153">
-        <v>0.1091946581859564</v>
+        <v>0.08153153443796413</v>
       </c>
       <c r="J1153">
-        <v>0.7701335453510795</v>
+        <v>0.7693693112407177</v>
       </c>
       <c r="K1153">
         <v>3.31</v>
       </c>
       <c r="L1153">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1153">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1153">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1153">
         <v>1</v>
       </c>
       <c r="P1153" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1154" spans="1:16">
       <c r="A1154" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1154" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C1154">
-        <v>1.600857964887927</v>
+        <v>1.656504680053033</v>
       </c>
       <c r="D1154" t="s">
-        <v>369</v>
+        <v>222</v>
       </c>
       <c r="E1154">
-        <v>1.519364642155481</v>
+        <v>1.769603769851547</v>
       </c>
       <c r="F1154">
         <v>-1</v>
       </c>
       <c r="G1154">
-        <v>0.006699142035112074</v>
+        <v>0.006303495319946967</v>
       </c>
       <c r="H1154">
-        <v>0.006540635357844519</v>
+        <v>0.006170396230148453</v>
       </c>
       <c r="I1154">
-        <v>0.08149332273244614</v>
+        <v>-0.1130990897985149</v>
       </c>
       <c r="J1154">
-        <v>0.7701335453510795</v>
+        <v>0.7693693112407177</v>
       </c>
       <c r="K1154">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1154">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1154">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1154">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1154">
         <v>1</v>
       </c>
       <c r="P1154" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1155" spans="1:16">
       <c r="A1155" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1155" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C1155">
-        <v>1.65419669303974</v>
+        <v>1.440857964887927</v>
       </c>
       <c r="D1155" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1155">
-        <v>1.767418060295913</v>
+        <v>1.550052623073884</v>
       </c>
       <c r="F1155">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1155">
-        <v>0.00630580330696026</v>
+        <v>0.006539142035112073</v>
       </c>
       <c r="H1155">
-        <v>0.006172581939704088</v>
+        <v>0.006709947376926117</v>
       </c>
       <c r="I1155">
-        <v>-0.1132213672561728</v>
+        <v>0.1091946581859564</v>
       </c>
       <c r="J1155">
         <v>0.7701335453510795</v>
       </c>
       <c r="K1155">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1155">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1155">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1155">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1155">
         <v>1</v>
@@ -59680,146 +59686,146 @@
     </row>
     <row r="1156" spans="1:16">
       <c r="A1156" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1156" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C1156">
-        <v>1.439221823572351</v>
+        <v>1.600857964887927</v>
       </c>
       <c r="D1156" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1156">
-        <v>1.548396709657817</v>
+        <v>1.519364642155481</v>
       </c>
       <c r="F1156">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1156">
-        <v>0.006540778176427649</v>
+        <v>0.006699142035112074</v>
       </c>
       <c r="H1156">
-        <v>0.006711603290342183</v>
+        <v>0.006540635357844519</v>
       </c>
       <c r="I1156">
-        <v>0.1091748860854662</v>
+        <v>0.08149332273244614</v>
       </c>
       <c r="J1156">
-        <v>0.770627847863338</v>
+        <v>0.7701335453510795</v>
       </c>
       <c r="K1156">
         <v>3.31</v>
       </c>
       <c r="L1156">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1156">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1156">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1156">
         <v>1</v>
       </c>
       <c r="P1156" t="s">
-        <v>508</v>
+        <v>215</v>
       </c>
     </row>
     <row r="1157" spans="1:16">
       <c r="A1157" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1157" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C1157">
-        <v>1.599221823572351</v>
+        <v>1.65419669303974</v>
       </c>
       <c r="D1157" t="s">
-        <v>369</v>
+        <v>222</v>
       </c>
       <c r="E1157">
-        <v>1.517753215965518</v>
+        <v>1.767418060295913</v>
       </c>
       <c r="F1157">
         <v>-1</v>
       </c>
       <c r="G1157">
-        <v>0.00670077817642765</v>
+        <v>0.00630580330696026</v>
       </c>
       <c r="H1157">
-        <v>0.006542246784034482</v>
+        <v>0.006172581939704088</v>
       </c>
       <c r="I1157">
-        <v>0.08146860760683294</v>
+        <v>-0.1132213672561728</v>
       </c>
       <c r="J1157">
-        <v>0.770627847863338</v>
+        <v>0.7701335453510795</v>
       </c>
       <c r="K1157">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1157">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1157">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1157">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1157">
         <v>1</v>
       </c>
       <c r="P1157" t="s">
-        <v>508</v>
+        <v>215</v>
       </c>
     </row>
     <row r="1158" spans="1:16">
       <c r="A1158" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1158" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C1158">
-        <v>1.652703899452719</v>
+        <v>1.439221823572351</v>
       </c>
       <c r="D1158" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1158">
-        <v>1.766004355110853</v>
+        <v>1.548396709657817</v>
       </c>
       <c r="F1158">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1158">
-        <v>0.006307296100547281</v>
+        <v>0.006540778176427649</v>
       </c>
       <c r="H1158">
-        <v>0.006173995644889147</v>
+        <v>0.006711603290342183</v>
       </c>
       <c r="I1158">
-        <v>-0.1133004556581341</v>
+        <v>0.1091748860854662</v>
       </c>
       <c r="J1158">
         <v>0.770627847863338</v>
       </c>
       <c r="K1158">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1158">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1158">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1158">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1158">
         <v>1</v>
@@ -59830,146 +59836,146 @@
     </row>
     <row r="1159" spans="1:16">
       <c r="A1159" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1159" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C1159">
-        <v>1.439853795183759</v>
+        <v>1.599221823572351</v>
       </c>
       <c r="D1159" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1159">
-        <v>1.549036318388396</v>
+        <v>1.517753215965518</v>
       </c>
       <c r="F1159">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1159">
-        <v>0.006540146204816242</v>
+        <v>0.00670077817642765</v>
       </c>
       <c r="H1159">
-        <v>0.006710963681611604</v>
+        <v>0.006542246784034482</v>
       </c>
       <c r="I1159">
-        <v>0.1091825232046375</v>
+        <v>0.08146860760683294</v>
       </c>
       <c r="J1159">
-        <v>0.7704369198840608</v>
+        <v>0.770627847863338</v>
       </c>
       <c r="K1159">
         <v>3.31</v>
       </c>
       <c r="L1159">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1159">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1159">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1159">
         <v>1</v>
       </c>
       <c r="P1159" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1160" spans="1:16">
       <c r="A1160" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1160" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C1160">
-        <v>1.599853795183759</v>
+        <v>1.652703899452719</v>
       </c>
       <c r="D1160" t="s">
-        <v>369</v>
+        <v>222</v>
       </c>
       <c r="E1160">
-        <v>1.518375641177962</v>
+        <v>1.766004355110853</v>
       </c>
       <c r="F1160">
         <v>-1</v>
       </c>
       <c r="G1160">
-        <v>0.006700146204816243</v>
+        <v>0.006307296100547281</v>
       </c>
       <c r="H1160">
-        <v>0.006541624358822038</v>
+        <v>0.006173995644889147</v>
       </c>
       <c r="I1160">
-        <v>0.08147815400579672</v>
+        <v>-0.1133004556581341</v>
       </c>
       <c r="J1160">
-        <v>0.7704369198840608</v>
+        <v>0.770627847863338</v>
       </c>
       <c r="K1160">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1160">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1160">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1160">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1160">
         <v>1</v>
       </c>
       <c r="P1160" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1161" spans="1:16">
       <c r="A1161" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1161" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C1161">
-        <v>1.653280501950136</v>
+        <v>1.439853795183759</v>
       </c>
       <c r="D1161" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1161">
-        <v>1.766550409131586</v>
+        <v>1.549036318388396</v>
       </c>
       <c r="F1161">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1161">
-        <v>0.006306719498049864</v>
+        <v>0.006540146204816242</v>
       </c>
       <c r="H1161">
-        <v>0.006173449590868413</v>
+        <v>0.006710963681611604</v>
       </c>
       <c r="I1161">
-        <v>-0.1132699071814502</v>
+        <v>0.1091825232046375</v>
       </c>
       <c r="J1161">
         <v>0.7704369198840608</v>
       </c>
       <c r="K1161">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1161">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1161">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1161">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1161">
         <v>1</v>
@@ -59980,146 +59986,146 @@
     </row>
     <row r="1162" spans="1:16">
       <c r="A1162" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1162" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C1162">
-        <v>1.44247254812609</v>
+        <v>1.599853795183759</v>
       </c>
       <c r="D1162" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1162">
-        <v>1.551686717891964</v>
+        <v>1.518375641177962</v>
       </c>
       <c r="F1162">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1162">
-        <v>0.006537527451873911</v>
+        <v>0.006700146204816243</v>
       </c>
       <c r="H1162">
-        <v>0.006708313282108036</v>
+        <v>0.006541624358822038</v>
       </c>
       <c r="I1162">
-        <v>0.1092141697658739</v>
+        <v>0.08147815400579672</v>
       </c>
       <c r="J1162">
-        <v>0.7696457558531451</v>
+        <v>0.7704369198840608</v>
       </c>
       <c r="K1162">
         <v>3.31</v>
       </c>
       <c r="L1162">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1162">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1162">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1162">
         <v>1</v>
       </c>
       <c r="P1162" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1163" spans="1:16">
       <c r="A1163" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1163" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C1163">
-        <v>1.60247254812609</v>
+        <v>1.653280501950136</v>
       </c>
       <c r="D1163" t="s">
-        <v>369</v>
+        <v>222</v>
       </c>
       <c r="E1163">
-        <v>1.520954835918747</v>
+        <v>1.766550409131586</v>
       </c>
       <c r="F1163">
         <v>-1</v>
       </c>
       <c r="G1163">
-        <v>0.006697527451873911</v>
+        <v>0.006306719498049864</v>
       </c>
       <c r="H1163">
-        <v>0.006539045164081253</v>
+        <v>0.006173449590868413</v>
       </c>
       <c r="I1163">
-        <v>0.08151771220734272</v>
+        <v>-0.1132699071814502</v>
       </c>
       <c r="J1163">
-        <v>0.7696457558531451</v>
+        <v>0.7704369198840608</v>
       </c>
       <c r="K1163">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1163">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1163">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1163">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1163">
         <v>1</v>
       </c>
       <c r="P1163" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1164" spans="1:16">
       <c r="A1164" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1164" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C1164">
-        <v>1.655669817323502</v>
+        <v>1.44247254812609</v>
       </c>
       <c r="D1164" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1164">
-        <v>1.768813138260005</v>
+        <v>1.551686717891964</v>
       </c>
       <c r="F1164">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1164">
-        <v>0.006304330182676498</v>
+        <v>0.006537527451873911</v>
       </c>
       <c r="H1164">
-        <v>0.006171186861739996</v>
+        <v>0.006708313282108036</v>
       </c>
       <c r="I1164">
-        <v>-0.1131433209365036</v>
+        <v>0.1092141697658739</v>
       </c>
       <c r="J1164">
         <v>0.7696457558531451</v>
       </c>
       <c r="K1164">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1164">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1164">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1164">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1164">
         <v>1</v>
@@ -60130,146 +60136,146 @@
     </row>
     <row r="1165" spans="1:16">
       <c r="A1165" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1165" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C1165">
-        <v>1.442210190879793</v>
+        <v>1.60247254812609</v>
       </c>
       <c r="D1165" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1165">
-        <v>1.551421190165349</v>
+        <v>1.520954835918747</v>
       </c>
       <c r="F1165">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1165">
-        <v>0.006537789809120208</v>
+        <v>0.006697527451873911</v>
       </c>
       <c r="H1165">
-        <v>0.006708578809834651</v>
+        <v>0.006539045164081253</v>
       </c>
       <c r="I1165">
-        <v>0.1092109992855561</v>
+        <v>0.08151771220734272</v>
       </c>
       <c r="J1165">
-        <v>0.7697250178610899</v>
+        <v>0.7696457558531451</v>
       </c>
       <c r="K1165">
         <v>3.31</v>
       </c>
       <c r="L1165">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1165">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1165">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1165">
         <v>1</v>
       </c>
       <c r="P1165" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1166" spans="1:16">
       <c r="A1166" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1166" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C1166">
-        <v>1.602210190879793</v>
+        <v>1.655669817323502</v>
       </c>
       <c r="D1166" t="s">
-        <v>369</v>
+        <v>222</v>
       </c>
       <c r="E1166">
-        <v>1.520696441772847</v>
+        <v>1.768813138260005</v>
       </c>
       <c r="F1166">
         <v>-1</v>
       </c>
       <c r="G1166">
-        <v>0.006697789809120207</v>
+        <v>0.006304330182676498</v>
       </c>
       <c r="H1166">
-        <v>0.006539303558227154</v>
+        <v>0.006171186861739996</v>
       </c>
       <c r="I1166">
-        <v>0.08151374910694553</v>
+        <v>-0.1131433209365036</v>
       </c>
       <c r="J1166">
-        <v>0.7697250178610899</v>
+        <v>0.7696457558531451</v>
       </c>
       <c r="K1166">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1166">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="M1166">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="N1166">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="O1166">
         <v>1</v>
       </c>
       <c r="P1166" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1167" spans="1:16">
       <c r="A1167" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1167" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C1167">
-        <v>1.655430446059508</v>
+        <v>1.442210190879793</v>
       </c>
       <c r="D1167" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="E1167">
-        <v>1.768586448917283</v>
+        <v>1.551421190165349</v>
       </c>
       <c r="F1167">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1167">
-        <v>0.006304569553940492</v>
+        <v>0.006537789809120208</v>
       </c>
       <c r="H1167">
-        <v>0.006171413551082717</v>
+        <v>0.006708578809834651</v>
       </c>
       <c r="I1167">
-        <v>-0.1131560028577745</v>
+        <v>0.1092109992855561</v>
       </c>
       <c r="J1167">
         <v>0.7697250178610899</v>
       </c>
       <c r="K1167">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="L1167">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="M1167">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="N1167">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="O1167">
         <v>1</v>
@@ -60280,102 +60286,102 @@
     </row>
     <row r="1168" spans="1:16">
       <c r="A1168" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1168" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C1168">
-        <v>1.439498642804615</v>
+        <v>1.602210190879793</v>
       </c>
       <c r="D1168" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1168">
-        <v>1.548676874137601</v>
+        <v>1.520696441772847</v>
       </c>
       <c r="F1168">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1168">
-        <v>0.006540501357195385</v>
+        <v>0.006697789809120207</v>
       </c>
       <c r="H1168">
-        <v>0.006711323125862399</v>
+        <v>0.006539303558227154</v>
       </c>
       <c r="I1168">
-        <v>0.1091782313329861</v>
+        <v>0.08151374910694553</v>
       </c>
       <c r="J1168">
-        <v>0.770544216675343</v>
+        <v>0.7697250178610899</v>
       </c>
       <c r="K1168">
         <v>3.31</v>
       </c>
       <c r="L1168">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1168">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N1168">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="O1168">
         <v>1</v>
       </c>
       <c r="P1168" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1169" spans="1:16">
       <c r="A1169" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1169" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C1169">
-        <v>1.439929878966419</v>
+        <v>1.655430446059508</v>
       </c>
       <c r="D1169" t="s">
-        <v>366</v>
+        <v>222</v>
       </c>
       <c r="E1169">
-        <v>1.549113321612539</v>
+        <v>1.768586448917283</v>
       </c>
       <c r="F1169">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1169">
-        <v>0.006540070121033582</v>
+        <v>0.006304569553940492</v>
       </c>
       <c r="H1169">
-        <v>0.006710886678387462</v>
+        <v>0.006171413551082717</v>
       </c>
       <c r="I1169">
-        <v>0.1091834426461191</v>
+        <v>-0.1131560028577745</v>
       </c>
       <c r="J1169">
-        <v>0.7704139338470033</v>
+        <v>0.7697250178610899</v>
       </c>
       <c r="K1169">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1169">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1169">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1169">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1169">
         <v>1</v>
       </c>
       <c r="P1169" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1170" spans="1:16">
@@ -60383,49 +60389,49 @@
         <v>0</v>
       </c>
       <c r="B1170" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C1170">
-        <v>1.515290968310835</v>
+        <v>1.439498642804615</v>
       </c>
       <c r="D1170" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E1170">
-        <v>1.531735175269863</v>
+        <v>1.548676874137601</v>
       </c>
       <c r="F1170">
         <v>1</v>
       </c>
       <c r="G1170">
-        <v>0.006304709031689165</v>
+        <v>0.006540501357195385</v>
       </c>
       <c r="H1170">
-        <v>0.006428264824730137</v>
+        <v>0.006711323125862399</v>
       </c>
       <c r="I1170">
-        <v>0.01644420695902804</v>
+        <v>0.1091782313329861</v>
       </c>
       <c r="J1170">
-        <v>0.7650827577281677</v>
+        <v>0.770544216675343</v>
       </c>
       <c r="K1170">
-        <v>3.13</v>
+        <v>3.31</v>
       </c>
       <c r="L1170">
-        <v>3.91</v>
+        <v>3.99</v>
       </c>
       <c r="M1170">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N1170">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="O1170">
         <v>1</v>
       </c>
       <c r="P1170" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1171" spans="1:16">
@@ -60433,49 +60439,49 @@
         <v>0</v>
       </c>
       <c r="B1171" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C1171">
-        <v>1.522016180456083</v>
+        <v>1.439929878966419</v>
       </c>
       <c r="D1171" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E1171">
-        <v>1.538610791520596</v>
+        <v>1.549113321612539</v>
       </c>
       <c r="F1171">
         <v>1</v>
       </c>
       <c r="G1171">
-        <v>0.006297983819543918</v>
+        <v>0.006540070121033582</v>
       </c>
       <c r="H1171">
-        <v>0.006421389208479404</v>
+        <v>0.006710886678387462</v>
       </c>
       <c r="I1171">
-        <v>0.01659461106451277</v>
+        <v>0.1091834426461191</v>
       </c>
       <c r="J1171">
-        <v>0.7629341276498137</v>
+        <v>0.7704139338470033</v>
       </c>
       <c r="K1171">
-        <v>3.13</v>
+        <v>3.31</v>
       </c>
       <c r="L1171">
-        <v>3.91</v>
+        <v>3.99</v>
       </c>
       <c r="M1171">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N1171">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="O1171">
         <v>1</v>
       </c>
       <c r="P1171" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1172" spans="1:16">
@@ -60486,28 +60492,28 @@
         <v>221</v>
       </c>
       <c r="C1172">
-        <v>1.527465653541474</v>
+        <v>1.504166281567789</v>
       </c>
       <c r="D1172" t="s">
         <v>370</v>
       </c>
       <c r="E1172">
-        <v>1.54418213780598</v>
+        <v>1.56185265127524</v>
       </c>
       <c r="F1172">
         <v>1</v>
       </c>
       <c r="G1172">
-        <v>0.006292534346458526</v>
+        <v>0.006315833718432211</v>
       </c>
       <c r="H1172">
-        <v>0.00641581786219402</v>
+        <v>0.00635814734872476</v>
       </c>
       <c r="I1172">
-        <v>0.01671648426450556</v>
+        <v>0.05768636970745078</v>
       </c>
       <c r="J1172">
-        <v>0.7611930819356313</v>
+        <v>0.7686369707451154</v>
       </c>
       <c r="K1172">
         <v>3.13</v>
@@ -60516,16 +60522,16 @@
         <v>3.91</v>
       </c>
       <c r="M1172">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="N1172">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="O1172">
         <v>1</v>
       </c>
       <c r="P1172" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1173" spans="1:16">
@@ -60536,28 +60542,28 @@
         <v>221</v>
       </c>
       <c r="C1173">
-        <v>1.533039228784309</v>
+        <v>1.515290968310835</v>
       </c>
       <c r="D1173" t="s">
         <v>370</v>
       </c>
       <c r="E1173">
-        <v>1.549880361696418</v>
+        <v>1.572941795888117</v>
       </c>
       <c r="F1173">
         <v>1</v>
       </c>
       <c r="G1173">
-        <v>0.006286960771215691</v>
+        <v>0.006304709031689165</v>
       </c>
       <c r="H1173">
-        <v>0.006410119638303582</v>
+        <v>0.006347058204111884</v>
       </c>
       <c r="I1173">
-        <v>0.01684113291210876</v>
+        <v>0.05765082757728157</v>
       </c>
       <c r="J1173">
-        <v>0.7594123869698695</v>
+        <v>0.7650827577281677</v>
       </c>
       <c r="K1173">
         <v>3.13</v>
@@ -60566,16 +60572,16 @@
         <v>3.91</v>
       </c>
       <c r="M1173">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="N1173">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="O1173">
         <v>1</v>
       </c>
       <c r="P1173" t="s">
-        <v>218</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1174" spans="1:16">
@@ -60586,28 +60592,28 @@
         <v>221</v>
       </c>
       <c r="C1174">
-        <v>1.55574886845932</v>
+        <v>1.522016180456083</v>
       </c>
       <c r="D1174" t="s">
         <v>370</v>
       </c>
       <c r="E1174">
-        <v>1.573097884686845</v>
+        <v>1.579645521732581</v>
       </c>
       <c r="F1174">
         <v>1</v>
       </c>
       <c r="G1174">
-        <v>0.00626425113154068</v>
+        <v>0.006297983819543918</v>
       </c>
       <c r="H1174">
-        <v>0.006386902115313156</v>
+        <v>0.006340354478267419</v>
       </c>
       <c r="I1174">
-        <v>0.01734901622752449</v>
+        <v>0.05762934127649766</v>
       </c>
       <c r="J1174">
-        <v>0.752156911035361</v>
+        <v>0.7629341276498137</v>
       </c>
       <c r="K1174">
         <v>3.13</v>
@@ -60616,16 +60622,16 @@
         <v>3.91</v>
       </c>
       <c r="M1174">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="N1174">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="O1174">
         <v>1</v>
       </c>
       <c r="P1174" t="s">
-        <v>369</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1175" spans="1:16">
@@ -60633,43 +60639,43 @@
         <v>0</v>
       </c>
       <c r="B1175" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1175">
-        <v>1.815398126910906</v>
+        <v>1.527465653541474</v>
       </c>
       <c r="D1175" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E1175">
-        <v>1.612260240237155</v>
+        <v>1.58507758436083</v>
       </c>
       <c r="F1175">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1175">
-        <v>0.006124601873089094</v>
+        <v>0.006292534346458526</v>
       </c>
       <c r="H1175">
-        <v>0.006207739759762845</v>
+        <v>0.00633492241563917</v>
       </c>
       <c r="I1175">
-        <v>0.2031378866737508</v>
+        <v>0.05761193081935634</v>
       </c>
       <c r="J1175">
-        <v>0.7533572982829001</v>
+        <v>0.7611930819356313</v>
       </c>
       <c r="K1175">
-        <v>2.86</v>
+        <v>3.13</v>
       </c>
       <c r="L1175">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="M1175">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="N1175">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="O1175">
         <v>1</v>
@@ -60680,34 +60686,34 @@
     </row>
     <row r="1176" spans="1:16">
       <c r="A1176" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1176" t="s">
         <v>221</v>
       </c>
       <c r="C1176">
-        <v>1.551991656374523</v>
+        <v>1.533039228784309</v>
       </c>
       <c r="D1176" t="s">
         <v>370</v>
       </c>
       <c r="E1176">
-        <v>1.56925664549472</v>
+        <v>1.590633352654007</v>
       </c>
       <c r="F1176">
         <v>1</v>
       </c>
       <c r="G1176">
-        <v>0.006268008343625477</v>
+        <v>0.006286960771215691</v>
       </c>
       <c r="H1176">
-        <v>0.006390743354505281</v>
+        <v>0.006329366647345992</v>
       </c>
       <c r="I1176">
-        <v>0.01726498912019681</v>
+        <v>0.05759412386969842</v>
       </c>
       <c r="J1176">
-        <v>0.7533572982829001</v>
+        <v>0.7594123869698695</v>
       </c>
       <c r="K1176">
         <v>3.13</v>
@@ -60716,16 +60722,16 @@
         <v>3.91</v>
       </c>
       <c r="M1176">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="N1176">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="O1176">
         <v>1</v>
       </c>
       <c r="P1176" t="s">
-        <v>517</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1177" spans="1:16">
@@ -60733,131 +60739,131 @@
         <v>0</v>
       </c>
       <c r="B1177" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1177">
-        <v>1.811875464143863</v>
+        <v>1.55574886845932</v>
       </c>
       <c r="D1177" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E1177">
-        <v>1.608503554419155</v>
+        <v>1.613270437569674</v>
       </c>
       <c r="F1177">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1177">
-        <v>0.006128124535856137</v>
+        <v>0.00626425113154068</v>
       </c>
       <c r="H1177">
-        <v>0.006211496445580845</v>
+        <v>0.006306729562430326</v>
       </c>
       <c r="I1177">
-        <v>0.2033719097247086</v>
+        <v>0.05752156911035344</v>
       </c>
       <c r="J1177">
-        <v>0.7545889985510968</v>
+        <v>0.752156911035361</v>
       </c>
       <c r="K1177">
-        <v>2.86</v>
+        <v>3.13</v>
       </c>
       <c r="L1177">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="M1177">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="N1177">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="O1177">
         <v>1</v>
       </c>
       <c r="P1177" t="s">
-        <v>219</v>
+        <v>369</v>
       </c>
     </row>
     <row r="1178" spans="1:16">
       <c r="A1178" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1178" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1178">
-        <v>1.548136434535067</v>
+        <v>1.815398126910906</v>
       </c>
       <c r="D1178" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1178">
-        <v>1.56531520463649</v>
+        <v>1.612260240237155</v>
       </c>
       <c r="F1178">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1178">
-        <v>0.006271863565464933</v>
+        <v>0.006124601873089094</v>
       </c>
       <c r="H1178">
-        <v>0.00639468479536351</v>
+        <v>0.006207739759762845</v>
       </c>
       <c r="I1178">
-        <v>0.01717877010142299</v>
+        <v>0.2031378866737508</v>
       </c>
       <c r="J1178">
-        <v>0.7545889985510968</v>
+        <v>0.7533572982829001</v>
       </c>
       <c r="K1178">
-        <v>3.13</v>
+        <v>2.86</v>
       </c>
       <c r="L1178">
+        <v>3.97</v>
+      </c>
+      <c r="M1178">
+        <v>3.05</v>
+      </c>
+      <c r="N1178">
         <v>3.91</v>
       </c>
-      <c r="M1178">
-        <v>3.2</v>
-      </c>
-      <c r="N1178">
-        <v>3.98</v>
-      </c>
       <c r="O1178">
         <v>1</v>
       </c>
       <c r="P1178" t="s">
-        <v>219</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1179" spans="1:16">
       <c r="A1179" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1179" t="s">
         <v>221</v>
       </c>
       <c r="C1179">
-        <v>1.54953959092474</v>
+        <v>1.551991656374523</v>
       </c>
       <c r="D1179" t="s">
         <v>370</v>
       </c>
       <c r="E1179">
-        <v>1.5667497415205</v>
+        <v>1.609525229357351</v>
       </c>
       <c r="F1179">
         <v>1</v>
       </c>
       <c r="G1179">
-        <v>0.006270460409075261</v>
+        <v>0.006268008343625477</v>
       </c>
       <c r="H1179">
-        <v>0.0063932502584795</v>
+        <v>0.006310474770642649</v>
       </c>
       <c r="I1179">
-        <v>0.0172101505957607</v>
+        <v>0.05753357298282857</v>
       </c>
       <c r="J1179">
-        <v>0.7541407057748436</v>
+        <v>0.7533572982829001</v>
       </c>
       <c r="K1179">
         <v>3.13</v>
@@ -60866,16 +60872,16 @@
         <v>3.91</v>
       </c>
       <c r="M1179">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="N1179">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="O1179">
         <v>1</v>
       </c>
       <c r="P1179" t="s">
-        <v>222</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1180" spans="1:16">
@@ -60883,49 +60889,299 @@
         <v>0</v>
       </c>
       <c r="B1180" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1180">
+        <v>1.811875464143863</v>
+      </c>
+      <c r="D1180" t="s">
+        <v>371</v>
+      </c>
+      <c r="E1180">
+        <v>1.608503554419155</v>
+      </c>
+      <c r="F1180">
+        <v>-1</v>
+      </c>
+      <c r="G1180">
+        <v>0.006128124535856137</v>
+      </c>
+      <c r="H1180">
+        <v>0.006211496445580845</v>
+      </c>
+      <c r="I1180">
+        <v>0.2033719097247086</v>
+      </c>
+      <c r="J1180">
+        <v>0.7545889985510968</v>
+      </c>
+      <c r="K1180">
+        <v>2.86</v>
+      </c>
+      <c r="L1180">
+        <v>3.97</v>
+      </c>
+      <c r="M1180">
+        <v>3.05</v>
+      </c>
+      <c r="N1180">
+        <v>3.91</v>
+      </c>
+      <c r="O1180">
+        <v>1</v>
+      </c>
+      <c r="P1180" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:16">
+      <c r="A1181" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1181" t="s">
         <v>221</v>
       </c>
-      <c r="C1180">
+      <c r="C1181">
+        <v>1.548136434535067</v>
+      </c>
+      <c r="D1181" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1181">
+        <v>1.605682324520578</v>
+      </c>
+      <c r="F1181">
+        <v>1</v>
+      </c>
+      <c r="G1181">
+        <v>0.006271863565464933</v>
+      </c>
+      <c r="H1181">
+        <v>0.006314317675479423</v>
+      </c>
+      <c r="I1181">
+        <v>0.0575458899855108</v>
+      </c>
+      <c r="J1181">
+        <v>0.7545889985510968</v>
+      </c>
+      <c r="K1181">
+        <v>3.13</v>
+      </c>
+      <c r="L1181">
+        <v>3.91</v>
+      </c>
+      <c r="M1181">
+        <v>3.12</v>
+      </c>
+      <c r="N1181">
+        <v>3.96</v>
+      </c>
+      <c r="O1181">
+        <v>1</v>
+      </c>
+      <c r="P1181" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:16">
+      <c r="A1182" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1182">
+        <v>1.54953959092474</v>
+      </c>
+      <c r="D1182" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1182">
+        <v>1.607080997982488</v>
+      </c>
+      <c r="F1182">
+        <v>1</v>
+      </c>
+      <c r="G1182">
+        <v>0.006270460409075261</v>
+      </c>
+      <c r="H1182">
+        <v>0.006312919002017512</v>
+      </c>
+      <c r="I1182">
+        <v>0.05754140705774846</v>
+      </c>
+      <c r="J1182">
+        <v>0.7541407057748436</v>
+      </c>
+      <c r="K1182">
+        <v>3.13</v>
+      </c>
+      <c r="L1182">
+        <v>3.91</v>
+      </c>
+      <c r="M1182">
+        <v>3.12</v>
+      </c>
+      <c r="N1182">
+        <v>3.96</v>
+      </c>
+      <c r="O1182">
+        <v>1</v>
+      </c>
+      <c r="P1182" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:16">
+      <c r="A1183" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1183">
         <v>1.562550231027863</v>
       </c>
-      <c r="D1180" t="s">
+      <c r="D1183" t="s">
         <v>370</v>
       </c>
-      <c r="E1180">
-        <v>1.580051354405483</v>
-      </c>
-      <c r="F1180">
-        <v>1</v>
-      </c>
-      <c r="G1180">
+      <c r="E1183">
+        <v>1.620050070545346</v>
+      </c>
+      <c r="F1183">
+        <v>1</v>
+      </c>
+      <c r="G1183">
         <v>0.006257449768972137</v>
       </c>
-      <c r="H1180">
-        <v>0.006379948645594517</v>
-      </c>
-      <c r="I1180">
-        <v>0.01750112337761989</v>
-      </c>
-      <c r="J1180">
+      <c r="H1183">
+        <v>0.006299949929454654</v>
+      </c>
+      <c r="I1183">
+        <v>0.05749983951748261</v>
+      </c>
+      <c r="J1183">
         <v>0.7499839517482865</v>
       </c>
-      <c r="K1180">
+      <c r="K1183">
         <v>3.13</v>
       </c>
-      <c r="L1180">
+      <c r="L1183">
         <v>3.91</v>
       </c>
-      <c r="M1180">
-        <v>3.2</v>
-      </c>
-      <c r="N1180">
-        <v>3.98</v>
-      </c>
-      <c r="O1180">
-        <v>1</v>
-      </c>
-      <c r="P1180" t="s">
-        <v>518</v>
+      <c r="M1183">
+        <v>3.12</v>
+      </c>
+      <c r="N1183">
+        <v>3.96</v>
+      </c>
+      <c r="O1183">
+        <v>1</v>
+      </c>
+      <c r="P1183" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:16">
+      <c r="A1184" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1184">
+        <v>1.558416625529189</v>
+      </c>
+      <c r="D1184" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1184">
+        <v>1.615929671454015</v>
+      </c>
+      <c r="F1184">
+        <v>1</v>
+      </c>
+      <c r="G1184">
+        <v>0.006261583374470811</v>
+      </c>
+      <c r="H1184">
+        <v>0.006304070328545985</v>
+      </c>
+      <c r="I1184">
+        <v>0.05751304592482631</v>
+      </c>
+      <c r="J1184">
+        <v>0.7513045924826874</v>
+      </c>
+      <c r="K1184">
+        <v>3.13</v>
+      </c>
+      <c r="L1184">
+        <v>3.91</v>
+      </c>
+      <c r="M1184">
+        <v>3.12</v>
+      </c>
+      <c r="N1184">
+        <v>3.96</v>
+      </c>
+      <c r="O1184">
+        <v>1</v>
+      </c>
+      <c r="P1184" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:16">
+      <c r="A1185" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1185">
+        <v>1.553167810108476</v>
+      </c>
+      <c r="D1185" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1185">
+        <v>1.610697625411644</v>
+      </c>
+      <c r="F1185">
+        <v>1</v>
+      </c>
+      <c r="G1185">
+        <v>0.006266832189891524</v>
+      </c>
+      <c r="H1185">
+        <v>0.006309302374588356</v>
+      </c>
+      <c r="I1185">
+        <v>0.05752981530316781</v>
+      </c>
+      <c r="J1185">
+        <v>0.7529815303167808</v>
+      </c>
+      <c r="K1185">
+        <v>3.13</v>
+      </c>
+      <c r="L1185">
+        <v>3.91</v>
+      </c>
+      <c r="M1185">
+        <v>3.12</v>
+      </c>
+      <c r="N1185">
+        <v>3.96</v>
+      </c>
+      <c r="O1185">
+        <v>1</v>
+      </c>
+      <c r="P1185" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3555" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3555" uniqueCount="520">
   <si>
     <t>trade_time</t>
   </si>
@@ -1132,7 +1132,7 @@
     <t>2021-09-13</t>
   </si>
   <si>
-    <t>2021-10-18</t>
+    <t>2021-10-19</t>
   </si>
   <si>
     <t>2021-10-12</t>
@@ -1570,9 +1570,6 @@
     <t>2021-09-08</t>
   </si>
   <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
     <t>2021-09-24</t>
   </si>
   <si>
@@ -58289,10 +58286,10 @@
         <v>0</v>
       </c>
       <c r="B1128" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C1128">
-        <v>1.443432272837593</v>
+        <v>1.463432272837593</v>
       </c>
       <c r="D1128" t="s">
         <v>366</v>
@@ -58304,13 +58301,13 @@
         <v>1</v>
       </c>
       <c r="G1128">
-        <v>0.006596567727162407</v>
+        <v>0.006616567727162407</v>
       </c>
       <c r="H1128">
         <v>0.006706567727162407</v>
       </c>
       <c r="I1128">
-        <v>0.1100000000000003</v>
+        <v>0.08999999999999986</v>
       </c>
       <c r="J1128">
         <v>0.7691246946753454</v>
@@ -58319,7 +58316,7 @@
         <v>3.35</v>
       </c>
       <c r="L1128">
-        <v>4.02</v>
+        <v>4.04</v>
       </c>
       <c r="M1128">
         <v>3.35</v>
@@ -60536,52 +60533,52 @@
     </row>
     <row r="1173" spans="1:16">
       <c r="A1173" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1173" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C1173">
-        <v>1.439929878966419</v>
+        <v>1.652956465640464</v>
       </c>
       <c r="D1173" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E1173">
-        <v>1.549113321612539</v>
+        <v>1.766243540308519</v>
       </c>
       <c r="F1173">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1173">
-        <v>0.006540070121033582</v>
+        <v>0.006307043534359537</v>
       </c>
       <c r="H1173">
-        <v>0.006710886678387462</v>
+        <v>0.006173756459691481</v>
       </c>
       <c r="I1173">
-        <v>0.1091834426461191</v>
+        <v>-0.1132870746680554</v>
       </c>
       <c r="J1173">
-        <v>0.7704139338470033</v>
+        <v>0.770544216675343</v>
       </c>
       <c r="K1173">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="L1173">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="M1173">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="N1173">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="O1173">
         <v>1</v>
       </c>
       <c r="P1173" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1174" spans="1:16">
@@ -60589,99 +60586,99 @@
         <v>0</v>
       </c>
       <c r="B1174" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C1174">
-        <v>1.515290968310835</v>
+        <v>1.439929878966419</v>
       </c>
       <c r="D1174" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="E1174">
-        <v>1.555894278619962</v>
+        <v>1.549113321612539</v>
       </c>
       <c r="F1174">
         <v>1</v>
       </c>
       <c r="G1174">
-        <v>0.006304709031689165</v>
+        <v>0.006540070121033582</v>
       </c>
       <c r="H1174">
-        <v>0.006284105721380039</v>
+        <v>0.006710886678387462</v>
       </c>
       <c r="I1174">
-        <v>0.04060331030912634</v>
+        <v>0.1091834426461191</v>
       </c>
       <c r="J1174">
-        <v>0.7650827577281677</v>
+        <v>0.7704139338470033</v>
       </c>
       <c r="K1174">
-        <v>3.13</v>
+        <v>3.31</v>
       </c>
       <c r="L1174">
-        <v>3.91</v>
+        <v>3.99</v>
       </c>
       <c r="M1174">
-        <v>3.09</v>
+        <v>3.35</v>
       </c>
       <c r="N1174">
-        <v>3.92</v>
+        <v>4.13</v>
       </c>
       <c r="O1174">
         <v>1</v>
       </c>
       <c r="P1174" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1175" spans="1:16">
       <c r="A1175" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1175" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C1175">
-        <v>1.522016180456083</v>
+        <v>1.59992987896642</v>
       </c>
       <c r="D1175" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E1175">
-        <v>1.562533545562076</v>
+        <v>1.531409182274069</v>
       </c>
       <c r="F1175">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1175">
-        <v>0.006297983819543918</v>
+        <v>0.006700070121033581</v>
       </c>
       <c r="H1175">
-        <v>0.006277466454437925</v>
+        <v>0.006708590817725931</v>
       </c>
       <c r="I1175">
-        <v>0.04051736510599246</v>
+        <v>0.06852069669235039</v>
       </c>
       <c r="J1175">
-        <v>0.7629341276498137</v>
+        <v>0.7704139338470033</v>
       </c>
       <c r="K1175">
-        <v>3.13</v>
+        <v>3.31</v>
       </c>
       <c r="L1175">
-        <v>3.91</v>
+        <v>4.15</v>
       </c>
       <c r="M1175">
-        <v>3.09</v>
+        <v>3.36</v>
       </c>
       <c r="N1175">
-        <v>3.92</v>
+        <v>4.12</v>
       </c>
       <c r="O1175">
         <v>1</v>
       </c>
       <c r="P1175" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1176" spans="1:16">
@@ -60692,28 +60689,28 @@
         <v>221</v>
       </c>
       <c r="C1176">
-        <v>1.527465653541474</v>
+        <v>1.515290968310835</v>
       </c>
       <c r="D1176" t="s">
         <v>372</v>
       </c>
       <c r="E1176">
-        <v>1.5679133768189</v>
+        <v>1.532941795888117</v>
       </c>
       <c r="F1176">
         <v>1</v>
       </c>
       <c r="G1176">
-        <v>0.006292534346458526</v>
+        <v>0.006304709031689165</v>
       </c>
       <c r="H1176">
-        <v>0.0062720866231811</v>
+        <v>0.006307058204111883</v>
       </c>
       <c r="I1176">
-        <v>0.04044772327742541</v>
+        <v>0.01765082757728154</v>
       </c>
       <c r="J1176">
-        <v>0.7611930819356313</v>
+        <v>0.7650827577281677</v>
       </c>
       <c r="K1176">
         <v>3.13</v>
@@ -60722,7 +60719,7 @@
         <v>3.91</v>
       </c>
       <c r="M1176">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="N1176">
         <v>3.92</v>
@@ -60731,7 +60728,7 @@
         <v>1</v>
       </c>
       <c r="P1176" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1177" spans="1:16">
@@ -60742,28 +60739,28 @@
         <v>221</v>
       </c>
       <c r="C1177">
-        <v>1.533039228784309</v>
+        <v>1.522016180456083</v>
       </c>
       <c r="D1177" t="s">
         <v>372</v>
       </c>
       <c r="E1177">
-        <v>1.573415724263103</v>
+        <v>1.539645521732581</v>
       </c>
       <c r="F1177">
         <v>1</v>
       </c>
       <c r="G1177">
-        <v>0.006286960771215691</v>
+        <v>0.006297983819543918</v>
       </c>
       <c r="H1177">
-        <v>0.006266584275736896</v>
+        <v>0.006300354478267419</v>
       </c>
       <c r="I1177">
-        <v>0.04037649547879463</v>
+        <v>0.01762934127649762</v>
       </c>
       <c r="J1177">
-        <v>0.7594123869698695</v>
+        <v>0.7629341276498137</v>
       </c>
       <c r="K1177">
         <v>3.13</v>
@@ -60772,7 +60769,7 @@
         <v>3.91</v>
       </c>
       <c r="M1177">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="N1177">
         <v>3.92</v>
@@ -60781,7 +60778,7 @@
         <v>1</v>
       </c>
       <c r="P1177" t="s">
-        <v>218</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1178" spans="1:16">
@@ -60792,28 +60789,28 @@
         <v>221</v>
       </c>
       <c r="C1178">
-        <v>1.551991656374523</v>
+        <v>1.527465653541474</v>
       </c>
       <c r="D1178" t="s">
         <v>372</v>
       </c>
       <c r="E1178">
-        <v>1.592125948305839</v>
+        <v>1.54507758436083</v>
       </c>
       <c r="F1178">
         <v>1</v>
       </c>
       <c r="G1178">
-        <v>0.006268008343625477</v>
+        <v>0.006292534346458526</v>
       </c>
       <c r="H1178">
-        <v>0.006247874051694162</v>
+        <v>0.006294922415639169</v>
       </c>
       <c r="I1178">
-        <v>0.04013429193131568</v>
+        <v>0.0176119308193563</v>
       </c>
       <c r="J1178">
-        <v>0.7533572982829001</v>
+        <v>0.7611930819356313</v>
       </c>
       <c r="K1178">
         <v>3.13</v>
@@ -60822,7 +60819,7 @@
         <v>3.91</v>
       </c>
       <c r="M1178">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="N1178">
         <v>3.92</v>
@@ -60831,7 +60828,7 @@
         <v>1</v>
       </c>
       <c r="P1178" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1179" spans="1:16">
@@ -60842,28 +60839,28 @@
         <v>221</v>
       </c>
       <c r="C1179">
-        <v>1.548136434535067</v>
+        <v>1.533039228784309</v>
       </c>
       <c r="D1179" t="s">
         <v>372</v>
       </c>
       <c r="E1179">
-        <v>1.588319994477111</v>
+        <v>1.550633352654007</v>
       </c>
       <c r="F1179">
         <v>1</v>
       </c>
       <c r="G1179">
-        <v>0.006271863565464933</v>
+        <v>0.006286960771215691</v>
       </c>
       <c r="H1179">
-        <v>0.006251680005522889</v>
+        <v>0.006289366647345993</v>
       </c>
       <c r="I1179">
-        <v>0.0401835599420437</v>
+        <v>0.01759412386969839</v>
       </c>
       <c r="J1179">
-        <v>0.7545889985510968</v>
+        <v>0.7594123869698695</v>
       </c>
       <c r="K1179">
         <v>3.13</v>
@@ -60872,7 +60869,7 @@
         <v>3.91</v>
       </c>
       <c r="M1179">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="N1179">
         <v>3.92</v>
@@ -60881,7 +60878,7 @@
         <v>1</v>
       </c>
       <c r="P1179" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1180" spans="1:16">
@@ -60931,7 +60928,7 @@
         <v>1</v>
       </c>
       <c r="P1180" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1181" spans="1:16">
@@ -60981,7 +60978,7 @@
         <v>1</v>
       </c>
       <c r="P1181" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3546" uniqueCount="516">
   <si>
     <t>trade_time</t>
   </si>
@@ -1135,9 +1135,6 @@
     <t>2021-09-13</t>
   </si>
   <si>
-    <t>2021-10-20</t>
-  </si>
-  <si>
     <t>2021-10-12</t>
   </si>
   <si>
@@ -1561,9 +1558,6 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
     <t>2021-09-24</t>
   </si>
   <si>
@@ -1925,7 +1919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1180"/>
+  <dimension ref="A1:P1178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2022,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2072,7 +2066,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2122,7 +2116,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2172,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2222,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2272,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2322,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2372,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2422,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2472,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2522,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2572,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2622,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2672,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2722,7 +2716,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2772,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2822,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2872,7 +2866,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2922,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2972,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3022,7 +3016,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3072,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3372,7 +3366,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3422,7 +3416,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3472,7 +3466,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3522,7 +3516,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3572,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3622,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3672,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3722,7 +3716,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3772,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3822,7 +3816,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3872,7 +3866,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3922,7 +3916,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3972,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4022,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4072,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4122,7 +4116,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4172,7 +4166,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4222,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4272,7 +4266,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4322,7 +4316,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4372,7 +4366,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4422,7 +4416,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4472,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4522,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4572,7 +4566,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4622,7 +4616,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4672,7 +4666,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4722,7 +4716,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4772,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4822,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4872,7 +4866,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4922,7 +4916,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4972,7 +4966,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5022,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5072,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5122,7 +5116,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5172,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5222,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5272,7 +5266,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5322,7 +5316,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5572,7 +5566,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5622,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5672,7 +5666,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5722,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6372,7 +6366,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6422,7 +6416,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6472,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6522,7 +6516,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6572,7 +6566,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6622,7 +6616,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6672,7 +6666,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6722,7 +6716,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6772,7 +6766,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6822,7 +6816,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6872,7 +6866,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6922,7 +6916,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -7172,7 +7166,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7222,7 +7216,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7272,7 +7266,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7322,7 +7316,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7622,7 +7616,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7672,7 +7666,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7722,7 +7716,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7772,7 +7766,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7822,7 +7816,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7872,7 +7866,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7922,7 +7916,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8372,7 +8366,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8422,7 +8416,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8472,7 +8466,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8522,7 +8516,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8572,7 +8566,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8622,7 +8616,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8672,7 +8666,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8722,7 +8716,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8772,7 +8766,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8822,7 +8816,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8872,7 +8866,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8922,7 +8916,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8972,7 +8966,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9022,7 +9016,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9072,7 +9066,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9122,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9172,7 +9166,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9222,7 +9216,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9272,7 +9266,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9322,7 +9316,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9372,7 +9366,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9422,7 +9416,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9472,7 +9466,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9522,7 +9516,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9572,7 +9566,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9622,7 +9616,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9672,7 +9666,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9722,7 +9716,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9772,7 +9766,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9822,7 +9816,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9872,7 +9866,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9922,7 +9916,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9972,7 +9966,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10022,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10072,7 +10066,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10122,7 +10116,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10172,7 +10166,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10222,7 +10216,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10272,7 +10266,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10322,7 +10316,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10372,7 +10366,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10422,7 +10416,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10472,7 +10466,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10522,7 +10516,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10872,7 +10866,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10922,7 +10916,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10972,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -11022,7 +11016,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11072,7 +11066,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11122,7 +11116,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11172,7 +11166,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11572,7 +11566,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11622,7 +11616,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11672,7 +11666,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11722,7 +11716,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11772,7 +11766,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11822,7 +11816,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11872,7 +11866,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11922,7 +11916,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11972,7 +11966,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -12022,7 +12016,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12072,7 +12066,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12122,7 +12116,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12172,7 +12166,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12222,7 +12216,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12272,7 +12266,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12322,7 +12316,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12372,7 +12366,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12422,7 +12416,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12472,7 +12466,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12522,7 +12516,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12572,7 +12566,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -13522,7 +13516,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13572,7 +13566,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13622,7 +13616,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13672,7 +13666,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13722,7 +13716,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13772,7 +13766,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13822,7 +13816,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13872,7 +13866,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13922,7 +13916,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13972,7 +13966,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -14022,7 +14016,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14072,7 +14066,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14122,7 +14116,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14172,7 +14166,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14222,7 +14216,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14272,7 +14266,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14322,7 +14316,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14372,7 +14366,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14422,7 +14416,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14472,7 +14466,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14522,7 +14516,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14572,7 +14566,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14622,7 +14616,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14672,7 +14666,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14722,7 +14716,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14772,7 +14766,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14822,7 +14816,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14872,7 +14866,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14922,7 +14916,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14972,7 +14966,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -15022,7 +15016,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15072,7 +15066,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15122,7 +15116,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15172,7 +15166,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15222,7 +15216,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15272,7 +15266,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15322,7 +15316,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15372,7 +15366,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15422,7 +15416,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15472,7 +15466,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15522,7 +15516,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15572,7 +15566,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15622,7 +15616,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15672,7 +15666,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15722,7 +15716,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15772,7 +15766,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15822,7 +15816,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15872,7 +15866,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15922,7 +15916,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15972,7 +15966,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -16022,7 +16016,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -16072,7 +16066,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -16122,7 +16116,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16172,7 +16166,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16222,7 +16216,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16272,7 +16266,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16322,7 +16316,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16372,7 +16366,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16422,7 +16416,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16472,7 +16466,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16522,7 +16516,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16572,7 +16566,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16622,7 +16616,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16672,7 +16666,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16722,7 +16716,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16772,7 +16766,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16822,7 +16816,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16872,7 +16866,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16922,7 +16916,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16972,7 +16966,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17022,7 +17016,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17072,7 +17066,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17122,7 +17116,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17172,7 +17166,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17222,7 +17216,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17272,7 +17266,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17322,7 +17316,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17372,7 +17366,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17422,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17472,7 +17466,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17522,7 +17516,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17572,7 +17566,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17622,7 +17616,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -18122,7 +18116,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18172,7 +18166,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18222,7 +18216,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18272,7 +18266,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18322,7 +18316,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18372,7 +18366,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18422,7 +18416,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18472,7 +18466,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18522,7 +18516,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18572,7 +18566,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18622,7 +18616,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18672,7 +18666,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18722,7 +18716,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18772,7 +18766,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18822,7 +18816,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18872,7 +18866,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18922,7 +18916,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18972,7 +18966,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19022,7 +19016,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19072,7 +19066,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19122,7 +19116,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19172,7 +19166,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19222,7 +19216,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19272,7 +19266,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19322,7 +19316,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19372,7 +19366,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19422,7 +19416,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19472,7 +19466,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19522,7 +19516,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19572,7 +19566,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19622,7 +19616,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19672,7 +19666,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19722,7 +19716,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19772,7 +19766,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19822,7 +19816,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19872,7 +19866,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19922,7 +19916,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19972,7 +19966,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20022,7 +20016,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20072,7 +20066,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20122,7 +20116,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20172,7 +20166,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20222,7 +20216,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20272,7 +20266,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20322,7 +20316,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20372,7 +20366,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20422,7 +20416,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20472,7 +20466,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20522,7 +20516,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20572,7 +20566,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20622,7 +20616,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20672,7 +20666,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20722,7 +20716,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20772,7 +20766,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20822,7 +20816,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20872,7 +20866,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20922,7 +20916,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20972,7 +20966,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21022,7 +21016,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21072,7 +21066,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21122,7 +21116,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21172,7 +21166,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21222,7 +21216,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21272,7 +21266,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21322,7 +21316,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21372,7 +21366,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21422,7 +21416,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21472,7 +21466,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21522,7 +21516,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21572,7 +21566,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21622,7 +21616,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21672,7 +21666,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21722,7 +21716,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21772,7 +21766,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21822,7 +21816,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21872,7 +21866,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21922,7 +21916,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21972,7 +21966,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22022,7 +22016,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22072,7 +22066,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22122,7 +22116,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22172,7 +22166,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22222,7 +22216,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22272,7 +22266,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22322,7 +22316,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22372,7 +22366,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22422,7 +22416,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22472,7 +22466,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22522,7 +22516,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22572,7 +22566,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22622,7 +22616,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22672,7 +22666,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22722,7 +22716,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22772,7 +22766,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22822,7 +22816,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22872,7 +22866,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22922,7 +22916,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22972,7 +22966,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23022,7 +23016,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23072,7 +23066,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23122,7 +23116,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23172,7 +23166,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23222,7 +23216,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23272,7 +23266,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23322,7 +23316,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23372,7 +23366,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23422,7 +23416,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23472,7 +23466,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23522,7 +23516,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23572,7 +23566,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23622,7 +23616,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23672,7 +23666,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23722,7 +23716,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23772,7 +23766,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23822,7 +23816,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23872,7 +23866,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23922,7 +23916,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23972,7 +23966,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24022,7 +24016,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24072,7 +24066,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24122,7 +24116,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24172,7 +24166,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24222,7 +24216,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24272,7 +24266,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24322,7 +24316,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24372,7 +24366,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24422,7 +24416,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24472,7 +24466,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24522,7 +24516,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24872,7 +24866,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24922,7 +24916,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24972,7 +24966,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25022,7 +25016,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25072,7 +25066,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25122,7 +25116,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25172,7 +25166,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25222,7 +25216,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25272,7 +25266,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25322,7 +25316,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25372,7 +25366,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25422,7 +25416,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25472,7 +25466,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25522,7 +25516,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25572,7 +25566,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25622,7 +25616,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25672,7 +25666,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25722,7 +25716,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25772,7 +25766,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25822,7 +25816,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26472,7 +26466,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26522,7 +26516,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26572,7 +26566,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26622,7 +26616,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26672,7 +26666,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26722,7 +26716,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26772,7 +26766,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26822,7 +26816,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26872,7 +26866,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26922,7 +26916,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26972,7 +26966,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27022,7 +27016,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27072,7 +27066,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27722,7 +27716,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27772,7 +27766,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27822,7 +27816,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27872,7 +27866,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27922,7 +27916,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27972,7 +27966,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28022,7 +28016,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28072,7 +28066,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28122,7 +28116,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28172,7 +28166,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28222,7 +28216,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28272,7 +28266,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -31822,7 +31816,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31872,7 +31866,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31922,7 +31916,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31972,7 +31966,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32022,7 +32016,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32072,7 +32066,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32122,7 +32116,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32172,7 +32166,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32222,7 +32216,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -33072,7 +33066,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33122,7 +33116,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33172,7 +33166,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33222,7 +33216,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33272,7 +33266,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33322,7 +33316,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33372,7 +33366,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33422,7 +33416,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33472,7 +33466,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33522,7 +33516,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33572,7 +33566,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33622,7 +33616,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33672,7 +33666,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33722,7 +33716,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33772,7 +33766,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33822,7 +33816,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34672,7 +34666,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34722,7 +34716,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34772,7 +34766,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34822,7 +34816,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34872,7 +34866,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34922,7 +34916,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34972,7 +34966,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35022,7 +35016,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -35072,7 +35066,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35122,7 +35116,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35172,7 +35166,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35222,7 +35216,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35272,7 +35266,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35322,7 +35316,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35372,7 +35366,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35772,7 +35766,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35822,7 +35816,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35872,7 +35866,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35922,7 +35916,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35972,7 +35966,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36022,7 +36016,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36072,7 +36066,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36822,7 +36816,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36872,7 +36866,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36922,7 +36916,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36972,7 +36966,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -37022,7 +37016,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37072,7 +37066,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37122,7 +37116,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37172,7 +37166,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37222,7 +37216,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37272,7 +37266,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37322,7 +37316,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37372,7 +37366,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37422,7 +37416,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37472,7 +37466,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37522,7 +37516,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37572,7 +37566,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37622,7 +37616,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37672,7 +37666,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37722,7 +37716,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37772,7 +37766,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38222,7 +38216,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38272,7 +38266,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38322,7 +38316,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38372,7 +38366,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38422,7 +38416,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38472,7 +38466,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38522,7 +38516,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38872,7 +38866,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38922,7 +38916,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38972,7 +38966,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39022,7 +39016,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39072,7 +39066,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39122,7 +39116,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39172,7 +39166,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39222,7 +39216,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39272,7 +39266,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39322,7 +39316,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39372,7 +39366,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -41472,7 +41466,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41522,7 +41516,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41572,7 +41566,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41622,7 +41616,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41672,7 +41666,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41722,7 +41716,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41772,7 +41766,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41822,7 +41816,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -41872,7 +41866,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41922,7 +41916,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41972,7 +41966,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42022,7 +42016,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42072,7 +42066,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42122,7 +42116,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42172,7 +42166,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42222,7 +42216,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42272,7 +42266,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42322,7 +42316,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42372,7 +42366,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42422,7 +42416,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42472,7 +42466,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42522,7 +42516,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42572,7 +42566,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -44222,7 +44216,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44272,7 +44266,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44322,7 +44316,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44372,7 +44366,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44422,7 +44416,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44472,7 +44466,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44522,7 +44516,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44572,7 +44566,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44622,7 +44616,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44672,7 +44666,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44722,7 +44716,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44772,7 +44766,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -45022,7 +45016,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45072,7 +45066,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45122,7 +45116,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45172,7 +45166,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45222,7 +45216,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45272,7 +45266,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45322,7 +45316,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45372,7 +45366,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45422,7 +45416,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45472,7 +45466,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45522,7 +45516,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45572,7 +45566,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45622,7 +45616,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45672,7 +45666,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -46072,7 +46066,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46122,7 +46116,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46172,7 +46166,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -48322,7 +48316,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48372,7 +48366,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48422,7 +48416,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48472,7 +48466,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48522,7 +48516,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48572,7 +48566,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48622,7 +48616,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48672,7 +48666,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48722,7 +48716,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -48772,7 +48766,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -48822,7 +48816,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -48872,7 +48866,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -48922,7 +48916,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -48972,7 +48966,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -49022,7 +49016,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49072,7 +49066,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49122,7 +49116,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49172,7 +49166,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49222,7 +49216,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49272,7 +49266,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49322,7 +49316,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49372,7 +49366,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49422,7 +49416,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49472,7 +49466,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49522,7 +49516,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49572,7 +49566,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49622,7 +49616,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49672,7 +49666,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49722,7 +49716,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49772,7 +49766,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -49822,7 +49816,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -49872,7 +49866,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -49922,7 +49916,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -49972,7 +49966,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -50022,7 +50016,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -50072,7 +50066,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50122,7 +50116,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50172,7 +50166,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50222,7 +50216,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50272,7 +50266,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50322,7 +50316,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -50372,7 +50366,7 @@
         <v>1</v>
       </c>
       <c r="P969" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="970" spans="1:16">
@@ -50422,7 +50416,7 @@
         <v>1</v>
       </c>
       <c r="P970" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="971" spans="1:16">
@@ -50472,7 +50466,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -50522,7 +50516,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -50572,7 +50566,7 @@
         <v>1</v>
       </c>
       <c r="P973" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="974" spans="1:16">
@@ -50622,7 +50616,7 @@
         <v>1</v>
       </c>
       <c r="P974" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="975" spans="1:16">
@@ -50672,7 +50666,7 @@
         <v>1</v>
       </c>
       <c r="P975" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="976" spans="1:16">
@@ -50722,7 +50716,7 @@
         <v>1</v>
       </c>
       <c r="P976" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="977" spans="1:16">
@@ -50772,7 +50766,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50822,7 +50816,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50872,7 +50866,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50922,7 +50916,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50972,7 +50966,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -51022,7 +51016,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51072,7 +51066,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51122,7 +51116,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51172,7 +51166,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51222,7 +51216,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51272,7 +51266,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51322,7 +51316,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51372,7 +51366,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51422,7 +51416,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51472,7 +51466,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51672,7 +51666,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51722,7 +51716,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51772,7 +51766,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51822,7 +51816,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -52072,7 +52066,7 @@
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -52122,7 +52116,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -52172,7 +52166,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52222,7 +52216,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52272,7 +52266,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52322,7 +52316,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52372,7 +52366,7 @@
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
@@ -52422,7 +52416,7 @@
         <v>1</v>
       </c>
       <c r="P1010" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1011" spans="1:16">
@@ -52472,7 +52466,7 @@
         <v>1</v>
       </c>
       <c r="P1011" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1012" spans="1:16">
@@ -52522,7 +52516,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52572,7 +52566,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52622,7 +52616,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -52672,7 +52666,7 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -52722,7 +52716,7 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -52772,7 +52766,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52822,7 +52816,7 @@
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
@@ -52872,7 +52866,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52922,7 +52916,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52972,7 +52966,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -53022,7 +53016,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -53072,7 +53066,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -53122,7 +53116,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53172,7 +53166,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53222,7 +53216,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53272,7 +53266,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53322,7 +53316,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53372,7 +53366,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53422,7 +53416,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53472,7 +53466,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53522,7 +53516,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53572,7 +53566,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53622,7 +53616,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53672,7 +53666,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -53722,7 +53716,7 @@
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
@@ -53772,7 +53766,7 @@
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
@@ -53822,7 +53816,7 @@
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
@@ -53872,7 +53866,7 @@
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
@@ -53922,7 +53916,7 @@
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
@@ -53972,7 +53966,7 @@
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
@@ -54022,7 +54016,7 @@
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
@@ -54072,7 +54066,7 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
@@ -54122,7 +54116,7 @@
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
@@ -54172,7 +54166,7 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
@@ -54222,7 +54216,7 @@
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54272,7 +54266,7 @@
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54322,7 +54316,7 @@
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
@@ -54372,7 +54366,7 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -54422,7 +54416,7 @@
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
@@ -54472,7 +54466,7 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -54522,7 +54516,7 @@
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -54572,7 +54566,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -54622,7 +54616,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -54672,7 +54666,7 @@
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
@@ -54722,7 +54716,7 @@
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
@@ -54772,7 +54766,7 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
@@ -54822,7 +54816,7 @@
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -54872,7 +54866,7 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
@@ -54922,7 +54916,7 @@
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
@@ -54972,7 +54966,7 @@
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
@@ -55022,7 +55016,7 @@
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
@@ -55072,7 +55066,7 @@
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
@@ -55122,7 +55116,7 @@
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
@@ -55172,7 +55166,7 @@
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55222,7 +55216,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55272,7 +55266,7 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
@@ -55322,7 +55316,7 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55372,7 +55366,7 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
@@ -55422,7 +55416,7 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
@@ -55472,7 +55466,7 @@
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -55522,7 +55516,7 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -55572,7 +55566,7 @@
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -55622,7 +55616,7 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
@@ -55672,7 +55666,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55722,7 +55716,7 @@
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
@@ -55772,7 +55766,7 @@
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1078" spans="1:16">
@@ -55822,7 +55816,7 @@
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
@@ -55872,7 +55866,7 @@
         <v>1</v>
       </c>
       <c r="P1079" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1080" spans="1:16">
@@ -56172,7 +56166,7 @@
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56222,7 +56216,7 @@
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
@@ -56272,7 +56266,7 @@
         <v>1</v>
       </c>
       <c r="P1087" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1088" spans="1:16">
@@ -56322,7 +56316,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56372,7 +56366,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -56422,7 +56416,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -56472,7 +56466,7 @@
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
@@ -56522,7 +56516,7 @@
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1093" spans="1:16">
@@ -56572,7 +56566,7 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
@@ -56622,7 +56616,7 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
@@ -56672,7 +56666,7 @@
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -56722,7 +56716,7 @@
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
@@ -56772,7 +56766,7 @@
         <v>1</v>
       </c>
       <c r="P1097" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1098" spans="1:16">
@@ -56822,7 +56816,7 @@
         <v>1</v>
       </c>
       <c r="P1098" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1099" spans="1:16">
@@ -56872,7 +56866,7 @@
         <v>1</v>
       </c>
       <c r="P1099" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1100" spans="1:16">
@@ -56922,7 +56916,7 @@
         <v>1</v>
       </c>
       <c r="P1100" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1101" spans="1:16">
@@ -56972,7 +56966,7 @@
         <v>1</v>
       </c>
       <c r="P1101" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1102" spans="1:16">
@@ -57022,7 +57016,7 @@
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
@@ -57072,7 +57066,7 @@
         <v>1</v>
       </c>
       <c r="P1103" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1104" spans="1:16">
@@ -57122,7 +57116,7 @@
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
@@ -57172,7 +57166,7 @@
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
@@ -57222,7 +57216,7 @@
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
@@ -57972,7 +57966,7 @@
         <v>1</v>
       </c>
       <c r="P1121" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1122" spans="1:16">
@@ -58022,7 +58016,7 @@
         <v>1</v>
       </c>
       <c r="P1122" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1123" spans="1:16">
@@ -58072,7 +58066,7 @@
         <v>1</v>
       </c>
       <c r="P1123" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1124" spans="1:16">
@@ -58122,7 +58116,7 @@
         <v>1</v>
       </c>
       <c r="P1124" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1125" spans="1:16">
@@ -58172,7 +58166,7 @@
         <v>1</v>
       </c>
       <c r="P1125" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1126" spans="1:16">
@@ -58222,7 +58216,7 @@
         <v>1</v>
       </c>
       <c r="P1126" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1127" spans="1:16">
@@ -58272,7 +58266,7 @@
         <v>1</v>
       </c>
       <c r="P1127" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1128" spans="1:16">
@@ -58322,7 +58316,7 @@
         <v>1</v>
       </c>
       <c r="P1128" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1129" spans="1:16">
@@ -58372,7 +58366,7 @@
         <v>1</v>
       </c>
       <c r="P1129" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1130" spans="1:16">
@@ -58422,7 +58416,7 @@
         <v>1</v>
       </c>
       <c r="P1130" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1131" spans="1:16">
@@ -58472,7 +58466,7 @@
         <v>1</v>
       </c>
       <c r="P1131" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1132" spans="1:16">
@@ -58522,7 +58516,7 @@
         <v>1</v>
       </c>
       <c r="P1132" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1133" spans="1:16">
@@ -58572,7 +58566,7 @@
         <v>1</v>
       </c>
       <c r="P1133" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1134" spans="1:16">
@@ -58622,7 +58616,7 @@
         <v>1</v>
       </c>
       <c r="P1134" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1135" spans="1:16">
@@ -58672,7 +58666,7 @@
         <v>1</v>
       </c>
       <c r="P1135" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1136" spans="1:16">
@@ -58722,7 +58716,7 @@
         <v>1</v>
       </c>
       <c r="P1136" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1137" spans="1:16">
@@ -58772,7 +58766,7 @@
         <v>1</v>
       </c>
       <c r="P1137" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1138" spans="1:16">
@@ -58822,7 +58816,7 @@
         <v>1</v>
       </c>
       <c r="P1138" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1139" spans="1:16">
@@ -58872,7 +58866,7 @@
         <v>1</v>
       </c>
       <c r="P1139" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1140" spans="1:16">
@@ -58922,7 +58916,7 @@
         <v>1</v>
       </c>
       <c r="P1140" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1141" spans="1:16">
@@ -58972,7 +58966,7 @@
         <v>1</v>
       </c>
       <c r="P1141" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1142" spans="1:16">
@@ -59022,7 +59016,7 @@
         <v>1</v>
       </c>
       <c r="P1142" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1143" spans="1:16">
@@ -59072,7 +59066,7 @@
         <v>1</v>
       </c>
       <c r="P1143" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1144" spans="1:16">
@@ -59122,7 +59116,7 @@
         <v>1</v>
       </c>
       <c r="P1144" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1145" spans="1:16">
@@ -59172,7 +59166,7 @@
         <v>1</v>
       </c>
       <c r="P1145" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1146" spans="1:16">
@@ -59222,7 +59216,7 @@
         <v>1</v>
       </c>
       <c r="P1146" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1147" spans="1:16">
@@ -59272,7 +59266,7 @@
         <v>1</v>
       </c>
       <c r="P1147" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1148" spans="1:16">
@@ -59322,7 +59316,7 @@
         <v>1</v>
       </c>
       <c r="P1148" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1149" spans="1:16">
@@ -59372,7 +59366,7 @@
         <v>1</v>
       </c>
       <c r="P1149" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1150" spans="1:16">
@@ -59422,7 +59416,7 @@
         <v>1</v>
       </c>
       <c r="P1150" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1151" spans="1:16">
@@ -59472,7 +59466,7 @@
         <v>1</v>
       </c>
       <c r="P1151" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1152" spans="1:16">
@@ -59522,7 +59516,7 @@
         <v>1</v>
       </c>
       <c r="P1152" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1153" spans="1:16">
@@ -59922,7 +59916,7 @@
         <v>1</v>
       </c>
       <c r="P1160" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1161" spans="1:16">
@@ -59972,7 +59966,7 @@
         <v>1</v>
       </c>
       <c r="P1161" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1162" spans="1:16">
@@ -60022,7 +60016,7 @@
         <v>1</v>
       </c>
       <c r="P1162" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1163" spans="1:16">
@@ -60072,7 +60066,7 @@
         <v>1</v>
       </c>
       <c r="P1163" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1164" spans="1:16">
@@ -60122,7 +60116,7 @@
         <v>1</v>
       </c>
       <c r="P1164" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1165" spans="1:16">
@@ -60172,7 +60166,7 @@
         <v>1</v>
       </c>
       <c r="P1165" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1166" spans="1:16">
@@ -60372,7 +60366,7 @@
         <v>1</v>
       </c>
       <c r="P1169" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1170" spans="1:16">
@@ -60422,7 +60416,7 @@
         <v>1</v>
       </c>
       <c r="P1170" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1171" spans="1:16">
@@ -60472,7 +60466,7 @@
         <v>1</v>
       </c>
       <c r="P1171" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1172" spans="1:16">
@@ -60522,7 +60516,7 @@
         <v>1</v>
       </c>
       <c r="P1172" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1173" spans="1:16">
@@ -60572,7 +60566,7 @@
         <v>1</v>
       </c>
       <c r="P1173" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1174" spans="1:16">
@@ -60622,7 +60616,7 @@
         <v>1</v>
       </c>
       <c r="P1174" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1175" spans="1:16">
@@ -60672,7 +60666,7 @@
         <v>1</v>
       </c>
       <c r="P1175" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1176" spans="1:16">
@@ -60722,7 +60716,7 @@
         <v>1</v>
       </c>
       <c r="P1176" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1177" spans="1:16">
@@ -60733,28 +60727,28 @@
         <v>222</v>
       </c>
       <c r="C1177">
-        <v>1.527465653541474</v>
+        <v>1.562550231027863</v>
       </c>
       <c r="D1177" t="s">
         <v>373</v>
       </c>
       <c r="E1177">
-        <v>1.542689515180187</v>
+        <v>1.620050070545346</v>
       </c>
       <c r="F1177">
         <v>1</v>
       </c>
       <c r="G1177">
-        <v>0.006292534346458526</v>
+        <v>0.006257449768972137</v>
       </c>
       <c r="H1177">
-        <v>0.006277310484819814</v>
+        <v>0.006299949929454654</v>
       </c>
       <c r="I1177">
-        <v>0.01522386163871259</v>
+        <v>0.05749983951748261</v>
       </c>
       <c r="J1177">
-        <v>0.7611930819356313</v>
+        <v>0.7499839517482865</v>
       </c>
       <c r="K1177">
         <v>3.13</v>
@@ -60763,16 +60757,16 @@
         <v>3.91</v>
       </c>
       <c r="M1177">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="N1177">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="O1177">
         <v>1</v>
       </c>
       <c r="P1177" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1178" spans="1:16">
@@ -60783,28 +60777,28 @@
         <v>222</v>
       </c>
       <c r="C1178">
-        <v>1.533039228784309</v>
+        <v>1.558416625529189</v>
       </c>
       <c r="D1178" t="s">
         <v>373</v>
       </c>
       <c r="E1178">
-        <v>1.548227476523706</v>
+        <v>1.615929671454015</v>
       </c>
       <c r="F1178">
         <v>1</v>
       </c>
       <c r="G1178">
-        <v>0.006286960771215691</v>
+        <v>0.006261583374470811</v>
       </c>
       <c r="H1178">
-        <v>0.006271772523476294</v>
+        <v>0.006304070328545985</v>
       </c>
       <c r="I1178">
-        <v>0.0151882477393972</v>
+        <v>0.05751304592482631</v>
       </c>
       <c r="J1178">
-        <v>0.7594123869698695</v>
+        <v>0.7513045924826874</v>
       </c>
       <c r="K1178">
         <v>3.13</v>
@@ -60813,116 +60807,16 @@
         <v>3.91</v>
       </c>
       <c r="M1178">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="N1178">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="O1178">
         <v>1</v>
       </c>
       <c r="P1178" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="1179" spans="1:16">
-      <c r="A1179" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1179" t="s">
-        <v>222</v>
-      </c>
-      <c r="C1179">
-        <v>1.562550231027863</v>
-      </c>
-      <c r="D1179" t="s">
-        <v>374</v>
-      </c>
-      <c r="E1179">
-        <v>1.620050070545346</v>
-      </c>
-      <c r="F1179">
-        <v>1</v>
-      </c>
-      <c r="G1179">
-        <v>0.006257449768972137</v>
-      </c>
-      <c r="H1179">
-        <v>0.006299949929454654</v>
-      </c>
-      <c r="I1179">
-        <v>0.05749983951748261</v>
-      </c>
-      <c r="J1179">
-        <v>0.7499839517482865</v>
-      </c>
-      <c r="K1179">
-        <v>3.13</v>
-      </c>
-      <c r="L1179">
-        <v>3.91</v>
-      </c>
-      <c r="M1179">
-        <v>3.12</v>
-      </c>
-      <c r="N1179">
-        <v>3.96</v>
-      </c>
-      <c r="O1179">
-        <v>1</v>
-      </c>
-      <c r="P1179" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="1180" spans="1:16">
-      <c r="A1180" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1180" t="s">
-        <v>222</v>
-      </c>
-      <c r="C1180">
-        <v>1.558416625529189</v>
-      </c>
-      <c r="D1180" t="s">
-        <v>374</v>
-      </c>
-      <c r="E1180">
-        <v>1.615929671454015</v>
-      </c>
-      <c r="F1180">
-        <v>1</v>
-      </c>
-      <c r="G1180">
-        <v>0.006261583374470811</v>
-      </c>
-      <c r="H1180">
-        <v>0.006304070328545985</v>
-      </c>
-      <c r="I1180">
-        <v>0.05751304592482631</v>
-      </c>
-      <c r="J1180">
-        <v>0.7513045924826874</v>
-      </c>
-      <c r="K1180">
-        <v>3.13</v>
-      </c>
-      <c r="L1180">
-        <v>3.91</v>
-      </c>
-      <c r="M1180">
-        <v>3.12</v>
-      </c>
-      <c r="N1180">
-        <v>3.96</v>
-      </c>
-      <c r="O1180">
-        <v>1</v>
-      </c>
-      <c r="P1180" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01988-600016.xlsx
+++ b/s60_signal/position-01988-600016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3774" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3747" uniqueCount="527">
   <si>
     <t>trade_time</t>
   </si>
@@ -649,10 +649,10 @@
     <t>2021-10-22</t>
   </si>
   <si>
-    <t>2021-11-12</t>
+    <t>2021-11-03</t>
   </si>
   <si>
-    <t>2021-11-03</t>
+    <t>2021-11-12</t>
   </si>
   <si>
     <t>2021-11-11</t>
@@ -1952,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1254"/>
+  <dimension ref="A1:P1245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -55457,10 +55457,10 @@
         <v>0</v>
       </c>
       <c r="B1071" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C1071">
-        <v>1.442360905903367</v>
+        <v>1.462360905903368</v>
       </c>
       <c r="D1071" t="s">
         <v>348</v>
@@ -55472,13 +55472,13 @@
         <v>1</v>
       </c>
       <c r="G1071">
-        <v>0.006597639094096632</v>
+        <v>0.006617639094096632</v>
       </c>
       <c r="H1071">
         <v>0.006707639094096632</v>
       </c>
       <c r="I1071">
-        <v>0.1100000000000003</v>
+        <v>0.08999999999999986</v>
       </c>
       <c r="J1071">
         <v>0.7694445057004873</v>
@@ -55487,7 +55487,7 @@
         <v>3.35</v>
       </c>
       <c r="L1071">
-        <v>4.02</v>
+        <v>4.04</v>
       </c>
       <c r="M1071">
         <v>3.35</v>
@@ -55707,10 +55707,10 @@
         <v>0</v>
       </c>
       <c r="B1076" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C1076">
-        <v>1.442612807343595</v>
+        <v>1.443387579793225</v>
       </c>
       <c r="D1076" t="s">
         <v>348</v>
@@ -55722,22 +55722,22 @@
         <v>1</v>
       </c>
       <c r="G1076">
-        <v>0.006597387192656404</v>
+        <v>0.006536612420206776</v>
       </c>
       <c r="H1076">
         <v>0.006707387192656404</v>
       </c>
       <c r="I1076">
-        <v>0.1100000000000003</v>
+        <v>0.1092252275503709</v>
       </c>
       <c r="J1076">
         <v>0.7693693112407177</v>
       </c>
       <c r="K1076">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="L1076">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="M1076">
         <v>3.35</v>
@@ -55757,28 +55757,28 @@
         <v>1</v>
       </c>
       <c r="B1077" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1077">
-        <v>1.443387579793225</v>
+        <v>1.603387579793225</v>
       </c>
       <c r="D1077" t="s">
-        <v>348</v>
+        <v>204</v>
       </c>
       <c r="E1077">
-        <v>1.552612807343595</v>
+        <v>1.656504680053033</v>
       </c>
       <c r="F1077">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1077">
-        <v>0.006536612420206776</v>
+        <v>0.006696612420206776</v>
       </c>
       <c r="H1077">
-        <v>0.006707387192656404</v>
+        <v>0.006303495319946967</v>
       </c>
       <c r="I1077">
-        <v>0.1092252275503709</v>
+        <v>-0.05311710025980787</v>
       </c>
       <c r="J1077">
         <v>0.7693693112407177</v>
@@ -55787,13 +55787,13 @@
         <v>3.31</v>
       </c>
       <c r="L1077">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1077">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="N1077">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1077">
         <v>1</v>
@@ -55807,43 +55807,43 @@
         <v>2</v>
       </c>
       <c r="B1078" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C1078">
-        <v>1.603387579793225</v>
+        <v>1.445711897142111</v>
       </c>
       <c r="D1078" t="s">
-        <v>204</v>
+        <v>354</v>
       </c>
       <c r="E1078">
-        <v>1.656504680053033</v>
+        <v>1.517261442041368</v>
       </c>
       <c r="F1078">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1078">
-        <v>0.006696612420206776</v>
+        <v>0.00635428810285789</v>
       </c>
       <c r="H1078">
-        <v>0.006303495319946967</v>
+        <v>0.006302738557958632</v>
       </c>
       <c r="I1078">
-        <v>-0.05311710025980787</v>
+        <v>0.07154954489925736</v>
       </c>
       <c r="J1078">
         <v>0.7693693112407177</v>
       </c>
       <c r="K1078">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="L1078">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="M1078">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="N1078">
-        <v>3.98</v>
+        <v>3.91</v>
       </c>
       <c r="O1078">
         <v>1</v>
@@ -55857,43 +55857,43 @@
         <v>3</v>
       </c>
       <c r="B1079" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C1079">
-        <v>1.445711897142111</v>
+        <v>1.581892066277847</v>
       </c>
       <c r="D1079" t="s">
-        <v>354</v>
+        <v>217</v>
       </c>
       <c r="E1079">
-        <v>1.517261442041368</v>
+        <v>1.504180362704146</v>
       </c>
       <c r="F1079">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1079">
-        <v>0.00635428810285789</v>
+        <v>0.006198107933722153</v>
       </c>
       <c r="H1079">
-        <v>0.006302738557958632</v>
+        <v>0.006335819637295854</v>
       </c>
       <c r="I1079">
-        <v>0.07154954489925736</v>
+        <v>0.07771170357370094</v>
       </c>
       <c r="J1079">
         <v>0.7693693112407177</v>
       </c>
       <c r="K1079">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="L1079">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="M1079">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="N1079">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="O1079">
         <v>1</v>
@@ -55904,81 +55904,81 @@
     </row>
     <row r="1080" spans="1:16">
       <c r="A1080" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1080" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C1080">
-        <v>1.581892066277847</v>
+        <v>1.440857964887927</v>
       </c>
       <c r="D1080" t="s">
-        <v>217</v>
+        <v>348</v>
       </c>
       <c r="E1080">
-        <v>1.504180362704146</v>
+        <v>1.550052623073884</v>
       </c>
       <c r="F1080">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1080">
-        <v>0.006198107933722153</v>
+        <v>0.006539142035112073</v>
       </c>
       <c r="H1080">
-        <v>0.006335819637295854</v>
+        <v>0.006709947376926117</v>
       </c>
       <c r="I1080">
-        <v>0.07771170357370094</v>
+        <v>0.1091946581859564</v>
       </c>
       <c r="J1080">
-        <v>0.7693693112407177</v>
+        <v>0.7701335453510795</v>
       </c>
       <c r="K1080">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="L1080">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="M1080">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="N1080">
-        <v>3.92</v>
+        <v>4.13</v>
       </c>
       <c r="O1080">
         <v>1</v>
       </c>
       <c r="P1080" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1081" spans="1:16">
       <c r="A1081" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1081" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1081">
-        <v>1.440857964887927</v>
+        <v>1.600857964887927</v>
       </c>
       <c r="D1081" t="s">
-        <v>348</v>
+        <v>204</v>
       </c>
       <c r="E1081">
-        <v>1.550052623073884</v>
+        <v>1.65419669303974</v>
       </c>
       <c r="F1081">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1081">
-        <v>0.006539142035112073</v>
+        <v>0.006699142035112074</v>
       </c>
       <c r="H1081">
-        <v>0.006709947376926117</v>
+        <v>0.00630580330696026</v>
       </c>
       <c r="I1081">
-        <v>0.1091946581859564</v>
+        <v>-0.05333872815181273</v>
       </c>
       <c r="J1081">
         <v>0.7701335453510795</v>
@@ -55987,13 +55987,13 @@
         <v>3.31</v>
       </c>
       <c r="L1081">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1081">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="N1081">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1081">
         <v>1</v>
@@ -56004,46 +56004,46 @@
     </row>
     <row r="1082" spans="1:16">
       <c r="A1082" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1082" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C1082">
-        <v>1.600857964887927</v>
+        <v>1.443273990330056</v>
       </c>
       <c r="D1082" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E1082">
-        <v>1.65419669303974</v>
+        <v>1.556495357586229</v>
       </c>
       <c r="F1082">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1082">
-        <v>0.006699142035112074</v>
+        <v>0.006356726009669944</v>
       </c>
       <c r="H1082">
-        <v>0.00630580330696026</v>
+        <v>0.00622350464241377</v>
       </c>
       <c r="I1082">
-        <v>-0.05333872815181273</v>
+        <v>0.1132213672561733</v>
       </c>
       <c r="J1082">
         <v>0.7701335453510795</v>
       </c>
       <c r="K1082">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="L1082">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="M1082">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="N1082">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="O1082">
         <v>1</v>
@@ -56054,40 +56054,40 @@
     </row>
     <row r="1083" spans="1:16">
       <c r="A1083" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1083" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C1083">
-        <v>1.443273990330056</v>
+        <v>1.579599363946762</v>
       </c>
       <c r="D1083" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E1083">
         <v>1.514884673958143</v>
       </c>
       <c r="F1083">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1083">
-        <v>0.006356726009669944</v>
+        <v>0.006200400636053239</v>
       </c>
       <c r="H1083">
         <v>0.006305115326041858</v>
       </c>
       <c r="I1083">
-        <v>0.07161068362808676</v>
+        <v>0.06471468998861862</v>
       </c>
       <c r="J1083">
         <v>0.7701335453510795</v>
       </c>
       <c r="K1083">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="L1083">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="M1083">
         <v>3.11</v>
@@ -56104,81 +56104,81 @@
     </row>
     <row r="1084" spans="1:16">
       <c r="A1084" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1084" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C1084">
-        <v>1.579599363946762</v>
+        <v>1.439221823572351</v>
       </c>
       <c r="D1084" t="s">
-        <v>217</v>
+        <v>348</v>
       </c>
       <c r="E1084">
-        <v>1.50178066759761</v>
+        <v>1.548396709657817</v>
       </c>
       <c r="F1084">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1084">
-        <v>0.006200400636053239</v>
+        <v>0.006540778176427649</v>
       </c>
       <c r="H1084">
-        <v>0.006338219332402389</v>
+        <v>0.006711603290342183</v>
       </c>
       <c r="I1084">
-        <v>0.07781869634915139</v>
+        <v>0.1091748860854662</v>
       </c>
       <c r="J1084">
-        <v>0.7701335453510795</v>
+        <v>0.770627847863338</v>
       </c>
       <c r="K1084">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="L1084">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="M1084">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="N1084">
-        <v>3.92</v>
+        <v>4.13</v>
       </c>
       <c r="O1084">
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>200</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
       <c r="A1085" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1085" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1085">
-        <v>1.439221823572351</v>
+        <v>1.599221823572351</v>
       </c>
       <c r="D1085" t="s">
-        <v>348</v>
+        <v>204</v>
       </c>
       <c r="E1085">
-        <v>1.548396709657817</v>
+        <v>1.652703899452719</v>
       </c>
       <c r="F1085">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1085">
-        <v>0.006540778176427649</v>
+        <v>0.00670077817642765</v>
       </c>
       <c r="H1085">
-        <v>0.006711603290342183</v>
+        <v>0.006307296100547281</v>
       </c>
       <c r="I1085">
-        <v>0.1091748860854662</v>
+        <v>-0.05348207588036802</v>
       </c>
       <c r="J1085">
         <v>0.770627847863338</v>
@@ -56187,13 +56187,13 @@
         <v>3.31</v>
       </c>
       <c r="L1085">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1085">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="N1085">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1085">
         <v>1</v>
@@ -56204,46 +56204,46 @@
     </row>
     <row r="1086" spans="1:16">
       <c r="A1086" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1086" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C1086">
-        <v>1.599221823572351</v>
+        <v>1.441697165315952</v>
       </c>
       <c r="D1086" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E1086">
-        <v>1.652703899452719</v>
+        <v>1.554997620974086</v>
       </c>
       <c r="F1086">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1086">
-        <v>0.00670077817642765</v>
+        <v>0.006358302834684048</v>
       </c>
       <c r="H1086">
-        <v>0.006307296100547281</v>
+        <v>0.006225002379025915</v>
       </c>
       <c r="I1086">
-        <v>-0.05348207588036802</v>
+        <v>0.1133004556581345</v>
       </c>
       <c r="J1086">
         <v>0.770627847863338</v>
       </c>
       <c r="K1086">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="L1086">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="M1086">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="N1086">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="O1086">
         <v>1</v>
@@ -56254,46 +56254,46 @@
     </row>
     <row r="1087" spans="1:16">
       <c r="A1087" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1087" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C1087">
-        <v>1.441697165315952</v>
+        <v>1.578116456409986</v>
       </c>
       <c r="D1087" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
       <c r="E1087">
-        <v>1.554997620974086</v>
+        <v>1.513347393145019</v>
       </c>
       <c r="F1087">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1087">
-        <v>0.006358302834684048</v>
+        <v>0.006201883543590014</v>
       </c>
       <c r="H1087">
-        <v>0.006225002379025915</v>
+        <v>0.006306652606854982</v>
       </c>
       <c r="I1087">
-        <v>0.1133004556581345</v>
+        <v>0.06476906326496712</v>
       </c>
       <c r="J1087">
         <v>0.770627847863338</v>
       </c>
       <c r="K1087">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="L1087">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="M1087">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="N1087">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56304,81 +56304,81 @@
     </row>
     <row r="1088" spans="1:16">
       <c r="A1088" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1088" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C1088">
-        <v>1.578116456409986</v>
+        <v>1.439853795183759</v>
       </c>
       <c r="D1088" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E1088">
-        <v>1.513347393145019</v>
+        <v>1.549036318388396</v>
       </c>
       <c r="F1088">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1088">
-        <v>0.006201883543590014</v>
+        <v>0.006540146204816242</v>
       </c>
       <c r="H1088">
-        <v>0.006306652606854982</v>
+        <v>0.006710963681611604</v>
       </c>
       <c r="I1088">
-        <v>0.06476906326496712</v>
+        <v>0.1091825232046375</v>
       </c>
       <c r="J1088">
-        <v>0.770627847863338</v>
+        <v>0.7704369198840608</v>
       </c>
       <c r="K1088">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="L1088">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="M1088">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="N1088">
-        <v>3.91</v>
+        <v>4.13</v>
       </c>
       <c r="O1088">
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
       <c r="A1089" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1089" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1089">
-        <v>1.439853795183759</v>
+        <v>1.599853795183759</v>
       </c>
       <c r="D1089" t="s">
-        <v>348</v>
+        <v>204</v>
       </c>
       <c r="E1089">
-        <v>1.549036318388396</v>
+        <v>1.653280501950136</v>
       </c>
       <c r="F1089">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1089">
-        <v>0.006540146204816242</v>
+        <v>0.006700146204816243</v>
       </c>
       <c r="H1089">
-        <v>0.006710963681611604</v>
+        <v>0.006306719498049864</v>
       </c>
       <c r="I1089">
-        <v>0.1091825232046375</v>
+        <v>-0.0534267067663774</v>
       </c>
       <c r="J1089">
         <v>0.7704369198840608</v>
@@ -56387,13 +56387,13 @@
         <v>3.31</v>
       </c>
       <c r="L1089">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1089">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="N1089">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1089">
         <v>1</v>
@@ -56404,46 +56404,46 @@
     </row>
     <row r="1090" spans="1:16">
       <c r="A1090" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1090" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C1090">
-        <v>1.599853795183759</v>
+        <v>1.462306225569846</v>
       </c>
       <c r="D1090" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E1090">
-        <v>1.653280501950136</v>
+        <v>1.555576132751296</v>
       </c>
       <c r="F1090">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1090">
-        <v>0.006700146204816243</v>
+        <v>0.006377693774430155</v>
       </c>
       <c r="H1090">
-        <v>0.006306719498049864</v>
+        <v>0.006224423867248705</v>
       </c>
       <c r="I1090">
-        <v>-0.0534267067663774</v>
+        <v>0.09326990718145023</v>
       </c>
       <c r="J1090">
         <v>0.7704369198840608</v>
       </c>
       <c r="K1090">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="L1090">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="M1090">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="N1090">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="O1090">
         <v>1</v>
@@ -56454,46 +56454,46 @@
     </row>
     <row r="1091" spans="1:16">
       <c r="A1091" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1091" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C1091">
-        <v>1.442306225569846</v>
+        <v>1.578689240347817</v>
       </c>
       <c r="D1091" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
       <c r="E1091">
-        <v>1.555576132751296</v>
+        <v>1.513941179160571</v>
       </c>
       <c r="F1091">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1091">
-        <v>0.006357693774430154</v>
+        <v>0.006201310759652182</v>
       </c>
       <c r="H1091">
-        <v>0.006224423867248705</v>
+        <v>0.006306058820839428</v>
       </c>
       <c r="I1091">
-        <v>0.1132699071814502</v>
+        <v>0.06474806118724619</v>
       </c>
       <c r="J1091">
         <v>0.7704369198840608</v>
       </c>
       <c r="K1091">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="L1091">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="M1091">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="N1091">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="O1091">
         <v>1</v>
@@ -56504,81 +56504,81 @@
     </row>
     <row r="1092" spans="1:16">
       <c r="A1092" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1092" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C1092">
-        <v>1.578689240347817</v>
+        <v>1.44247254812609</v>
       </c>
       <c r="D1092" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E1092">
-        <v>1.513941179160571</v>
+        <v>1.551686717891964</v>
       </c>
       <c r="F1092">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1092">
-        <v>0.006201310759652182</v>
+        <v>0.006537527451873911</v>
       </c>
       <c r="H1092">
-        <v>0.006306058820839428</v>
+        <v>0.006708313282108036</v>
       </c>
       <c r="I1092">
-        <v>0.06474806118724619</v>
+        <v>0.1092141697658739</v>
       </c>
       <c r="J1092">
-        <v>0.7704369198840608</v>
+        <v>0.7696457558531451</v>
       </c>
       <c r="K1092">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="L1092">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="M1092">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="N1092">
-        <v>3.91</v>
+        <v>4.13</v>
       </c>
       <c r="O1092">
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1093" spans="1:16">
       <c r="A1093" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1093" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1093">
-        <v>1.44247254812609</v>
+        <v>1.60247254812609</v>
       </c>
       <c r="D1093" t="s">
-        <v>348</v>
+        <v>204</v>
       </c>
       <c r="E1093">
-        <v>1.551686717891964</v>
+        <v>1.655669817323502</v>
       </c>
       <c r="F1093">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1093">
-        <v>0.006537527451873911</v>
+        <v>0.006697527451873911</v>
       </c>
       <c r="H1093">
-        <v>0.006708313282108036</v>
+        <v>0.006304330182676498</v>
       </c>
       <c r="I1093">
-        <v>0.1092141697658739</v>
+        <v>-0.05319726919741186</v>
       </c>
       <c r="J1093">
         <v>0.7696457558531451</v>
@@ -56587,13 +56587,13 @@
         <v>3.31</v>
       </c>
       <c r="L1093">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1093">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="N1093">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1093">
         <v>1</v>
@@ -56604,46 +56604,46 @@
     </row>
     <row r="1094" spans="1:16">
       <c r="A1094" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1094" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C1094">
-        <v>1.60247254812609</v>
+        <v>1.464830038828467</v>
       </c>
       <c r="D1094" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E1094">
-        <v>1.655669817323502</v>
+        <v>1.557973359764971</v>
       </c>
       <c r="F1094">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1094">
-        <v>0.006697527451873911</v>
+        <v>0.006375169961171533</v>
       </c>
       <c r="H1094">
-        <v>0.006304330182676498</v>
+        <v>0.006222026640235029</v>
       </c>
       <c r="I1094">
-        <v>-0.05319726919741186</v>
+        <v>0.09314332093650357</v>
       </c>
       <c r="J1094">
         <v>0.7696457558531451</v>
       </c>
       <c r="K1094">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="L1094">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="M1094">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="N1094">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="O1094">
         <v>1</v>
@@ -56654,46 +56654,46 @@
     </row>
     <row r="1095" spans="1:16">
       <c r="A1095" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1095" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C1095">
-        <v>1.444830038828467</v>
+        <v>1.581062732440565</v>
       </c>
       <c r="D1095" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
       <c r="E1095">
-        <v>1.557973359764971</v>
+        <v>1.516401699296719</v>
       </c>
       <c r="F1095">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1095">
-        <v>0.006355169961171533</v>
+        <v>0.006198937267559435</v>
       </c>
       <c r="H1095">
-        <v>0.006222026640235029</v>
+        <v>0.006303598300703282</v>
       </c>
       <c r="I1095">
-        <v>0.1131433209365036</v>
+        <v>0.06466103314384597</v>
       </c>
       <c r="J1095">
         <v>0.7696457558531451</v>
       </c>
       <c r="K1095">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="L1095">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="M1095">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="N1095">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="O1095">
         <v>1</v>
@@ -56704,81 +56704,81 @@
     </row>
     <row r="1096" spans="1:16">
       <c r="A1096" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1096" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C1096">
-        <v>1.581062732440565</v>
+        <v>1.442210190879793</v>
       </c>
       <c r="D1096" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E1096">
-        <v>1.516401699296719</v>
+        <v>1.551421190165349</v>
       </c>
       <c r="F1096">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1096">
-        <v>0.006198937267559435</v>
+        <v>0.006537789809120208</v>
       </c>
       <c r="H1096">
-        <v>0.006303598300703282</v>
+        <v>0.006708578809834651</v>
       </c>
       <c r="I1096">
-        <v>0.06466103314384597</v>
+        <v>0.1092109992855561</v>
       </c>
       <c r="J1096">
-        <v>0.7696457558531451</v>
+        <v>0.7697250178610899</v>
       </c>
       <c r="K1096">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="L1096">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="M1096">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="N1096">
-        <v>3.91</v>
+        <v>4.13</v>
       </c>
       <c r="O1096">
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
       <c r="A1097" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1097" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1097">
-        <v>1.442210190879793</v>
+        <v>1.602210190879793</v>
       </c>
       <c r="D1097" t="s">
-        <v>348</v>
+        <v>204</v>
       </c>
       <c r="E1097">
-        <v>1.551421190165349</v>
+        <v>1.655430446059508</v>
       </c>
       <c r="F1097">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1097">
-        <v>0.006537789809120208</v>
+        <v>0.006697789809120207</v>
       </c>
       <c r="H1097">
-        <v>0.006708578809834651</v>
+        <v>0.006304569553940492</v>
       </c>
       <c r="I1097">
-        <v>0.1092109992855561</v>
+        <v>-0.05322025517971563</v>
       </c>
       <c r="J1097">
         <v>0.7697250178610899</v>
@@ -56787,13 +56787,13 @@
         <v>3.31</v>
       </c>
       <c r="L1097">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1097">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="N1097">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1097">
         <v>1</v>
@@ -56804,46 +56804,46 @@
     </row>
     <row r="1098" spans="1:16">
       <c r="A1098" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1098" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C1098">
-        <v>1.602210190879793</v>
+        <v>1.464577193023123</v>
       </c>
       <c r="D1098" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E1098">
-        <v>1.655430446059508</v>
+        <v>1.557733195880898</v>
       </c>
       <c r="F1098">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1098">
-        <v>0.006697789809120207</v>
+        <v>0.006375422806976877</v>
       </c>
       <c r="H1098">
-        <v>0.006304569553940492</v>
+        <v>0.006222266804119103</v>
       </c>
       <c r="I1098">
-        <v>-0.05322025517971563</v>
+        <v>0.09315600285777492</v>
       </c>
       <c r="J1098">
         <v>0.7697250178610899</v>
       </c>
       <c r="K1098">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="L1098">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="M1098">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="N1098">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="O1098">
         <v>1</v>
@@ -56854,46 +56854,46 @@
     </row>
     <row r="1099" spans="1:16">
       <c r="A1099" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1099" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C1099">
-        <v>1.464577193023123</v>
+        <v>1.58082494641673</v>
       </c>
       <c r="D1099" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
       <c r="E1099">
-        <v>1.557733195880898</v>
+        <v>1.51615519445201</v>
       </c>
       <c r="F1099">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1099">
-        <v>0.006375422806976877</v>
+        <v>0.00619917505358327</v>
       </c>
       <c r="H1099">
-        <v>0.006222266804119103</v>
+        <v>0.00630384480554799</v>
       </c>
       <c r="I1099">
-        <v>0.09315600285777492</v>
+        <v>0.06466975196471969</v>
       </c>
       <c r="J1099">
         <v>0.7697250178610899</v>
       </c>
       <c r="K1099">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="L1099">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="M1099">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="N1099">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="O1099">
         <v>1</v>
@@ -56904,81 +56904,81 @@
     </row>
     <row r="1100" spans="1:16">
       <c r="A1100" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1100" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C1100">
-        <v>1.58082494641673</v>
+        <v>1.439498642804615</v>
       </c>
       <c r="D1100" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E1100">
-        <v>1.51615519445201</v>
+        <v>1.548676874137601</v>
       </c>
       <c r="F1100">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1100">
-        <v>0.00619917505358327</v>
+        <v>0.006540501357195385</v>
       </c>
       <c r="H1100">
-        <v>0.00630384480554799</v>
+        <v>0.006711323125862399</v>
       </c>
       <c r="I1100">
-        <v>0.06466975196471969</v>
+        <v>0.1091782313329861</v>
       </c>
       <c r="J1100">
-        <v>0.7697250178610899</v>
+        <v>0.770544216675343</v>
       </c>
       <c r="K1100">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="L1100">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="M1100">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="N1100">
-        <v>3.91</v>
+        <v>4.13</v>
       </c>
       <c r="O1100">
         <v>1</v>
       </c>
       <c r="P1100" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1101" spans="1:16">
       <c r="A1101" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1101" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1101">
-        <v>1.439498642804615</v>
+        <v>1.599498642804615</v>
       </c>
       <c r="D1101" t="s">
-        <v>348</v>
+        <v>204</v>
       </c>
       <c r="E1101">
-        <v>1.548676874137601</v>
+        <v>1.652956465640464</v>
       </c>
       <c r="F1101">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1101">
-        <v>0.006540501357195385</v>
+        <v>0.006700501357195385</v>
       </c>
       <c r="H1101">
-        <v>0.006711323125862399</v>
+        <v>0.006307043534359537</v>
       </c>
       <c r="I1101">
-        <v>0.1091782313329861</v>
+        <v>-0.0534578228358491</v>
       </c>
       <c r="J1101">
         <v>0.770544216675343</v>
@@ -56987,13 +56987,13 @@
         <v>3.31</v>
       </c>
       <c r="L1101">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1101">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="N1101">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1101">
         <v>1</v>
@@ -57004,46 +57004,46 @@
     </row>
     <row r="1102" spans="1:16">
       <c r="A1102" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1102" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C1102">
-        <v>1.599498642804615</v>
+        <v>1.461963948805656</v>
       </c>
       <c r="D1102" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E1102">
-        <v>1.652956465640464</v>
+        <v>1.555251023473711</v>
       </c>
       <c r="F1102">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1102">
-        <v>0.006700501357195385</v>
+        <v>0.006378036051194345</v>
       </c>
       <c r="H1102">
-        <v>0.006307043534359537</v>
+        <v>0.006224748976526289</v>
       </c>
       <c r="I1102">
-        <v>-0.0534578228358491</v>
+        <v>0.09328707466805541</v>
       </c>
       <c r="J1102">
         <v>0.770544216675343</v>
       </c>
       <c r="K1102">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="L1102">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="M1102">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="N1102">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="O1102">
         <v>1</v>
@@ -57054,46 +57054,46 @@
     </row>
     <row r="1103" spans="1:16">
       <c r="A1103" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1103" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C1103">
-        <v>1.461963948805656</v>
+        <v>1.578367349973971</v>
       </c>
       <c r="D1103" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
       <c r="E1103">
-        <v>1.555251023473711</v>
+        <v>1.513607486139684</v>
       </c>
       <c r="F1103">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1103">
-        <v>0.006378036051194345</v>
+        <v>0.00620163265002603</v>
       </c>
       <c r="H1103">
-        <v>0.006224748976526289</v>
+        <v>0.006306392513860317</v>
       </c>
       <c r="I1103">
-        <v>0.09328707466805541</v>
+        <v>0.06475986383428767</v>
       </c>
       <c r="J1103">
         <v>0.770544216675343</v>
       </c>
       <c r="K1103">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="L1103">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="M1103">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="N1103">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="O1103">
         <v>1</v>
@@ -57104,81 +57104,81 @@
     </row>
     <row r="1104" spans="1:16">
       <c r="A1104" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1104" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C1104">
-        <v>1.578367349973971</v>
+        <v>1.439929878966419</v>
       </c>
       <c r="D1104" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E1104">
-        <v>1.513607486139684</v>
+        <v>1.549113321612539</v>
       </c>
       <c r="F1104">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1104">
-        <v>0.00620163265002603</v>
+        <v>0.006540070121033582</v>
       </c>
       <c r="H1104">
-        <v>0.006306392513860317</v>
+        <v>0.006710886678387462</v>
       </c>
       <c r="I1104">
-        <v>0.06475986383428767</v>
+        <v>0.1091834426461191</v>
       </c>
       <c r="J1104">
-        <v>0.770544216675343</v>
+        <v>0.7704139338470033</v>
       </c>
       <c r="K1104">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="L1104">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="M1104">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="N1104">
-        <v>3.91</v>
+        <v>4.13</v>
       </c>
       <c r="O1104">
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
       <c r="A1105" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1105" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1105">
-        <v>1.439929878966419</v>
+        <v>1.59992987896642</v>
       </c>
       <c r="D1105" t="s">
-        <v>348</v>
+        <v>204</v>
       </c>
       <c r="E1105">
-        <v>1.549113321612539</v>
+        <v>1.65334991978205</v>
       </c>
       <c r="F1105">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1105">
-        <v>0.006540070121033582</v>
+        <v>0.006700070121033581</v>
       </c>
       <c r="H1105">
-        <v>0.006710886678387462</v>
+        <v>0.00630665008021795</v>
       </c>
       <c r="I1105">
-        <v>0.1091834426461191</v>
+        <v>-0.05342004081563045</v>
       </c>
       <c r="J1105">
         <v>0.7704139338470033</v>
@@ -57187,13 +57187,13 @@
         <v>3.31</v>
       </c>
       <c r="L1105">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="M1105">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="N1105">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="O1105">
         <v>1</v>
@@ -57204,46 +57204,46 @@
     </row>
     <row r="1106" spans="1:16">
       <c r="A1106" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1106" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C1106">
-        <v>1.59992987896642</v>
+        <v>1.462379551028059</v>
       </c>
       <c r="D1106" t="s">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="E1106">
-        <v>1.766616149197571</v>
+        <v>1.55564578044358</v>
       </c>
       <c r="F1106">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1106">
-        <v>0.006700070121033581</v>
+        <v>0.006377620448971941</v>
       </c>
       <c r="H1106">
-        <v>0.00617338385080243</v>
+        <v>0.00622435421955642</v>
       </c>
       <c r="I1106">
-        <v>-0.1666862702311511</v>
+        <v>0.09326622941552065</v>
       </c>
       <c r="J1106">
         <v>0.7704139338470033</v>
       </c>
       <c r="K1106">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="L1106">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="M1106">
-        <v>2.86</v>
+        <v>3.03</v>
       </c>
       <c r="N1106">
-        <v>3.97</v>
+        <v>3.89</v>
       </c>
       <c r="O1106">
         <v>1</v>
@@ -57254,46 +57254,46 @@
     </row>
     <row r="1107" spans="1:16">
       <c r="A1107" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1107" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C1107">
-        <v>1.65334991978205</v>
+        <v>1.57875819845899</v>
       </c>
       <c r="D1107" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E1107">
-        <v>1.766616149197571</v>
+        <v>1.51401266573582</v>
       </c>
       <c r="F1107">
         <v>-1</v>
       </c>
       <c r="G1107">
-        <v>0.00630665008021795</v>
+        <v>0.00620124180154101</v>
       </c>
       <c r="H1107">
-        <v>0.00617338385080243</v>
+        <v>0.006305987334264181</v>
       </c>
       <c r="I1107">
-        <v>-0.1132662294155207</v>
+        <v>0.0647455327231703</v>
       </c>
       <c r="J1107">
         <v>0.7704139338470033</v>
       </c>
       <c r="K1107">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="L1107">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="M1107">
-        <v>2.86</v>
+        <v>3.11</v>
       </c>
       <c r="N1107">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="O1107">
         <v>1</v>
@@ -57304,146 +57304,146 @@
     </row>
     <row r="1108" spans="1:16">
       <c r="A1108" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1108" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C1108">
-        <v>1.462379551028059</v>
+        <v>1.603210680071608</v>
       </c>
       <c r="D1108" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="E1108">
-        <v>1.55564578044358</v>
+        <v>1.521681817834877</v>
       </c>
       <c r="F1108">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1108">
-        <v>0.006377620448971941</v>
+        <v>0.006696789319928393</v>
       </c>
       <c r="H1108">
-        <v>0.00622435421955642</v>
+        <v>0.006538318182165125</v>
       </c>
       <c r="I1108">
-        <v>0.09326622941552065</v>
+        <v>0.08152886223673139</v>
       </c>
       <c r="J1108">
-        <v>0.7704139338470033</v>
+        <v>0.7694227552653753</v>
       </c>
       <c r="K1108">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="L1108">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="M1108">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="N1108">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="O1108">
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>493</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
       <c r="A1109" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1109" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1109">
-        <v>1.57875819845899</v>
+        <v>1.656343279098567</v>
       </c>
       <c r="D1109" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E1109">
-        <v>1.51401266573582</v>
+        <v>1.769450919941027</v>
       </c>
       <c r="F1109">
         <v>-1</v>
       </c>
       <c r="G1109">
-        <v>0.00620124180154101</v>
+        <v>0.006303656720901433</v>
       </c>
       <c r="H1109">
-        <v>0.006305987334264181</v>
+        <v>0.006170549080058974</v>
       </c>
       <c r="I1109">
-        <v>0.0647455327231703</v>
+        <v>-0.1131076408424603</v>
       </c>
       <c r="J1109">
-        <v>0.7704139338470033</v>
+        <v>0.7694227552653753</v>
       </c>
       <c r="K1109">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="L1109">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
       <c r="M1109">
-        <v>3.11</v>
+        <v>2.86</v>
       </c>
       <c r="N1109">
-        <v>3.91</v>
+        <v>3.97</v>
       </c>
       <c r="O1109">
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>493</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
       <c r="A1110" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1110" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C1110">
-        <v>1.603210680071608</v>
+        <v>1.465541410703453</v>
       </c>
       <c r="D1110" t="s">
-        <v>357</v>
+        <v>216</v>
       </c>
       <c r="E1110">
-        <v>1.521681817834877</v>
+        <v>1.558649051545913</v>
       </c>
       <c r="F1110">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1110">
-        <v>0.006696789319928393</v>
+        <v>0.006374458589296547</v>
       </c>
       <c r="H1110">
-        <v>0.006538318182165125</v>
+        <v>0.006221350948454087</v>
       </c>
       <c r="I1110">
-        <v>0.08152886223673139</v>
+        <v>0.09310764084246026</v>
       </c>
       <c r="J1110">
         <v>0.7694227552653753</v>
       </c>
       <c r="K1110">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="L1110">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="M1110">
-        <v>3.26</v>
+        <v>3.03</v>
       </c>
       <c r="N1110">
-        <v>4.03</v>
+        <v>3.89</v>
       </c>
       <c r="O1110">
         <v>1</v>
@@ -57454,46 +57454,46 @@
     </row>
     <row r="1111" spans="1:16">
       <c r="A1111" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1111" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C1111">
-        <v>1.656343279098567</v>
+        <v>1.581731734203874</v>
       </c>
       <c r="D1111" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E1111">
-        <v>1.769450919941027</v>
+        <v>1.517095231124683</v>
       </c>
       <c r="F1111">
         <v>-1</v>
       </c>
       <c r="G1111">
-        <v>0.006303656720901433</v>
+        <v>0.006198268265796126</v>
       </c>
       <c r="H1111">
-        <v>0.006170549080058974</v>
+        <v>0.006302904768875317</v>
       </c>
       <c r="I1111">
-        <v>-0.1131076408424603</v>
+        <v>0.06463650307919089</v>
       </c>
       <c r="J1111">
         <v>0.7694227552653753</v>
       </c>
       <c r="K1111">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="L1111">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="M1111">
-        <v>2.86</v>
+        <v>3.11</v>
       </c>
       <c r="N1111">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="O1111">
         <v>1</v>
@@ -57504,146 +57504,146 @@
     </row>
     <row r="1112" spans="1:16">
       <c r="A1112" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1112" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C1112">
-        <v>1.465541410703453</v>
+        <v>1.602303822168713</v>
       </c>
       <c r="D1112" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="E1112">
-        <v>1.558649051545913</v>
+        <v>1.520788658691844</v>
       </c>
       <c r="F1112">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1112">
-        <v>0.006374458589296547</v>
+        <v>0.006697696177831288</v>
       </c>
       <c r="H1112">
-        <v>0.006221350948454087</v>
+        <v>0.006539211341308157</v>
       </c>
       <c r="I1112">
-        <v>0.09310764084246026</v>
+        <v>0.08151516347686893</v>
       </c>
       <c r="J1112">
-        <v>0.7694227552653753</v>
+        <v>0.7696967304626245</v>
       </c>
       <c r="K1112">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="L1112">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="M1112">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="N1112">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="O1112">
         <v>1</v>
       </c>
       <c r="P1112" t="s">
-        <v>201</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1113" spans="1:16">
       <c r="A1113" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1113" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1113">
-        <v>1.581731734203874</v>
+        <v>1.655515874002874</v>
       </c>
       <c r="D1113" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E1113">
-        <v>1.517095231124683</v>
+        <v>1.768667350876894</v>
       </c>
       <c r="F1113">
         <v>-1</v>
       </c>
       <c r="G1113">
-        <v>0.006198268265796126</v>
+        <v>0.006304484125997126</v>
       </c>
       <c r="H1113">
-        <v>0.006302904768875317</v>
+        <v>0.006171332649123107</v>
       </c>
       <c r="I1113">
-        <v>0.06463650307919089</v>
+        <v>-0.1131514768740201</v>
       </c>
       <c r="J1113">
-        <v>0.7694227552653753</v>
+        <v>0.7696967304626245</v>
       </c>
       <c r="K1113">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="L1113">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
       <c r="M1113">
-        <v>3.11</v>
+        <v>2.86</v>
       </c>
       <c r="N1113">
-        <v>3.91</v>
+        <v>3.97</v>
       </c>
       <c r="O1113">
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>201</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
       <c r="A1114" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1114" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C1114">
-        <v>1.602303822168713</v>
+        <v>1.464667429824228</v>
       </c>
       <c r="D1114" t="s">
-        <v>357</v>
+        <v>216</v>
       </c>
       <c r="E1114">
-        <v>1.520788658691844</v>
+        <v>1.557818906698248</v>
       </c>
       <c r="F1114">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1114">
-        <v>0.006697696177831288</v>
+        <v>0.006375332570175772</v>
       </c>
       <c r="H1114">
-        <v>0.006539211341308157</v>
+        <v>0.006222181093301753</v>
       </c>
       <c r="I1114">
-        <v>0.08151516347686893</v>
+        <v>0.09315147687402003</v>
       </c>
       <c r="J1114">
         <v>0.7696967304626245</v>
       </c>
       <c r="K1114">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="L1114">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="M1114">
-        <v>3.26</v>
+        <v>3.03</v>
       </c>
       <c r="N1114">
-        <v>4.03</v>
+        <v>3.89</v>
       </c>
       <c r="O1114">
         <v>1</v>
@@ -57654,46 +57654,46 @@
     </row>
     <row r="1115" spans="1:16">
       <c r="A1115" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1115" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C1115">
-        <v>1.655515874002874</v>
+        <v>1.580909808612126</v>
       </c>
       <c r="D1115" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E1115">
-        <v>1.768667350876894</v>
+        <v>1.516243168261238</v>
       </c>
       <c r="F1115">
         <v>-1</v>
       </c>
       <c r="G1115">
-        <v>0.006304484125997126</v>
+        <v>0.006199090191387874</v>
       </c>
       <c r="H1115">
-        <v>0.006171332649123107</v>
+        <v>0.006303756831738763</v>
       </c>
       <c r="I1115">
-        <v>-0.1131514768740201</v>
+        <v>0.0646666403508882</v>
       </c>
       <c r="J1115">
         <v>0.7696967304626245</v>
       </c>
       <c r="K1115">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="L1115">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="M1115">
-        <v>2.86</v>
+        <v>3.11</v>
       </c>
       <c r="N1115">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="O1115">
         <v>1</v>
@@ -57704,146 +57704,146 @@
     </row>
     <row r="1116" spans="1:16">
       <c r="A1116" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1116" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C1116">
-        <v>1.464667429824228</v>
+        <v>1.603418306336815</v>
       </c>
       <c r="D1116" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="E1116">
-        <v>1.557818906698248</v>
+        <v>1.521886307751668</v>
       </c>
       <c r="F1116">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1116">
-        <v>0.006375332570175772</v>
+        <v>0.006696581693663186</v>
       </c>
       <c r="H1116">
-        <v>0.006222181093301753</v>
+        <v>0.006538113692248332</v>
       </c>
       <c r="I1116">
-        <v>0.09315147687402003</v>
+        <v>0.08153199858514792</v>
       </c>
       <c r="J1116">
-        <v>0.7696967304626245</v>
+        <v>0.7693600282970346</v>
       </c>
       <c r="K1116">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="L1116">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="M1116">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="N1116">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="O1116">
         <v>1</v>
       </c>
       <c r="P1116" t="s">
-        <v>494</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1117" spans="1:16">
       <c r="A1117" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1117" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1117">
-        <v>1.580909808612126</v>
+        <v>1.656532714542955</v>
       </c>
       <c r="D1117" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E1117">
-        <v>1.516243168261238</v>
+        <v>1.769630319070481</v>
       </c>
       <c r="F1117">
         <v>-1</v>
       </c>
       <c r="G1117">
-        <v>0.006199090191387874</v>
+        <v>0.006303467285457044</v>
       </c>
       <c r="H1117">
-        <v>0.006303756831738763</v>
+        <v>0.006170369680929519</v>
       </c>
       <c r="I1117">
-        <v>0.0646666403508882</v>
+        <v>-0.113097604527526</v>
       </c>
       <c r="J1117">
-        <v>0.7696967304626245</v>
+        <v>0.7693600282970346</v>
       </c>
       <c r="K1117">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="L1117">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
       <c r="M1117">
-        <v>3.11</v>
+        <v>2.86</v>
       </c>
       <c r="N1117">
-        <v>3.91</v>
+        <v>3.97</v>
       </c>
       <c r="O1117">
         <v>1</v>
       </c>
       <c r="P1117" t="s">
-        <v>494</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1118" spans="1:16">
       <c r="A1118" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1118" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C1118">
-        <v>1.603418306336815</v>
+        <v>1.469596711713252</v>
       </c>
       <c r="D1118" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1118">
-        <v>1.521886307751668</v>
+        <v>1.531145513977015</v>
       </c>
       <c r="F1118">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1118">
-        <v>0.006696581693663186</v>
+        <v>0.006270403288286749</v>
       </c>
       <c r="H1118">
-        <v>0.006538113692248332</v>
+        <v>0.006208854486022986</v>
       </c>
       <c r="I1118">
-        <v>0.08153199858514792</v>
+        <v>0.06154880226376269</v>
       </c>
       <c r="J1118">
         <v>0.7693600282970346</v>
       </c>
       <c r="K1118">
-        <v>3.31</v>
+        <v>3.12</v>
       </c>
       <c r="L1118">
-        <v>4.15</v>
+        <v>3.87</v>
       </c>
       <c r="M1118">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="N1118">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="O1118">
         <v>1</v>
@@ -57854,46 +57854,46 @@
     </row>
     <row r="1119" spans="1:16">
       <c r="A1119" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1119" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C1119">
-        <v>1.656532714542955</v>
+        <v>1.465741509732459</v>
       </c>
       <c r="D1119" t="s">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="E1119">
-        <v>1.769630319070481</v>
+        <v>1.558839114259985</v>
       </c>
       <c r="F1119">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1119">
-        <v>0.006303467285457044</v>
+        <v>0.006374258490267541</v>
       </c>
       <c r="H1119">
-        <v>0.006170369680929519</v>
+        <v>0.006221160885740015</v>
       </c>
       <c r="I1119">
-        <v>-0.113097604527526</v>
+        <v>0.09309760452752602</v>
       </c>
       <c r="J1119">
         <v>0.7693600282970346</v>
       </c>
       <c r="K1119">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="L1119">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="M1119">
-        <v>2.86</v>
+        <v>3.03</v>
       </c>
       <c r="N1119">
-        <v>3.97</v>
+        <v>3.89</v>
       </c>
       <c r="O1119">
         <v>1</v>
@@ -57904,46 +57904,46 @@
     </row>
     <row r="1120" spans="1:16">
       <c r="A1120" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1120" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C1120">
-        <v>1.469596711713252</v>
+        <v>1.581919915108896</v>
       </c>
       <c r="D1120" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E1120">
-        <v>1.531145513977015</v>
+        <v>1.517290311996223</v>
       </c>
       <c r="F1120">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1120">
-        <v>0.006270403288286749</v>
+        <v>0.006198080084891104</v>
       </c>
       <c r="H1120">
-        <v>0.006208854486022986</v>
+        <v>0.006302709688003778</v>
       </c>
       <c r="I1120">
-        <v>0.06154880226376269</v>
+        <v>0.06462960311267363</v>
       </c>
       <c r="J1120">
         <v>0.7693600282970346</v>
       </c>
       <c r="K1120">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="L1120">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="M1120">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="N1120">
-        <v>3.87</v>
+        <v>3.91</v>
       </c>
       <c r="O1120">
         <v>1</v>
@@ -57954,146 +57954,146 @@
     </row>
     <row r="1121" spans="1:16">
       <c r="A1121" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1121" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C1121">
-        <v>1.465741509732459</v>
+        <v>1.603914205797025</v>
       </c>
       <c r="D1121" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="E1121">
-        <v>1.558839114259985</v>
+        <v>1.522374716283474</v>
       </c>
       <c r="F1121">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1121">
-        <v>0.006374258490267541</v>
+        <v>0.006696085794202976</v>
       </c>
       <c r="H1121">
-        <v>0.006221160885740015</v>
+        <v>0.006537625283716526</v>
       </c>
       <c r="I1121">
-        <v>0.09309760452752602</v>
+        <v>0.08153948951355039</v>
       </c>
       <c r="J1121">
-        <v>0.7693600282970346</v>
+        <v>0.7692102097289957</v>
       </c>
       <c r="K1121">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="L1121">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="M1121">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="N1121">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="O1121">
         <v>1</v>
       </c>
       <c r="P1121" t="s">
-        <v>202</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1122" spans="1:16">
       <c r="A1122" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1122" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1122">
-        <v>1.581919915108896</v>
+        <v>1.656985166618433</v>
       </c>
       <c r="D1122" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E1122">
-        <v>1.517290311996223</v>
+        <v>1.770058800175073</v>
       </c>
       <c r="F1122">
         <v>-1</v>
       </c>
       <c r="G1122">
-        <v>0.006198080084891104</v>
+        <v>0.006303014833381568</v>
       </c>
       <c r="H1122">
-        <v>0.006302709688003778</v>
+        <v>0.006169941199824928</v>
       </c>
       <c r="I1122">
-        <v>0.06462960311267363</v>
+        <v>-0.1130736335566396</v>
       </c>
       <c r="J1122">
-        <v>0.7693600282970346</v>
+        <v>0.7692102097289957</v>
       </c>
       <c r="K1122">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="L1122">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
       <c r="M1122">
-        <v>3.11</v>
+        <v>2.86</v>
       </c>
       <c r="N1122">
-        <v>3.91</v>
+        <v>3.97</v>
       </c>
       <c r="O1122">
         <v>1</v>
       </c>
       <c r="P1122" t="s">
-        <v>202</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1123" spans="1:16">
       <c r="A1123" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1123" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C1123">
-        <v>1.603914205797025</v>
+        <v>1.470835226769924</v>
       </c>
       <c r="D1123" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1123">
-        <v>1.522374716283474</v>
+        <v>1.531600962423853</v>
       </c>
       <c r="F1123">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1123">
-        <v>0.006696085794202976</v>
+        <v>0.006409164773230077</v>
       </c>
       <c r="H1123">
-        <v>0.006537625283716526</v>
+        <v>0.006208399037576147</v>
       </c>
       <c r="I1123">
-        <v>0.08153948951355039</v>
+        <v>0.06076573565392929</v>
       </c>
       <c r="J1123">
         <v>0.7692102097289957</v>
       </c>
       <c r="K1123">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1123">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="M1123">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="N1123">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="O1123">
         <v>1</v>
@@ -58104,46 +58104,46 @@
     </row>
     <row r="1124" spans="1:16">
       <c r="A1124" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1124" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C1124">
-        <v>1.656985166618433</v>
+        <v>1.472372043548244</v>
       </c>
       <c r="D1124" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E1124">
-        <v>1.770058800175073</v>
+        <v>1.531600962423853</v>
       </c>
       <c r="F1124">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1124">
-        <v>0.006303014833381568</v>
+        <v>0.006287627956451756</v>
       </c>
       <c r="H1124">
-        <v>0.006169941199824928</v>
+        <v>0.006208399037576147</v>
       </c>
       <c r="I1124">
-        <v>-0.1130736335566396</v>
+        <v>0.05922891887560944</v>
       </c>
       <c r="J1124">
         <v>0.7692102097289957</v>
       </c>
       <c r="K1124">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="L1124">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="M1124">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="N1124">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
       <c r="O1124">
         <v>1</v>
@@ -58154,46 +58154,46 @@
     </row>
     <row r="1125" spans="1:16">
       <c r="A1125" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1125" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1125">
-        <v>1.470835226769924</v>
+        <v>1.471603635159084</v>
       </c>
       <c r="D1125" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1125">
-        <v>1.531600962423853</v>
+        <v>1.559293064521143</v>
       </c>
       <c r="F1125">
         <v>1</v>
       </c>
       <c r="G1125">
-        <v>0.006409164773230077</v>
+        <v>0.006348396364840916</v>
       </c>
       <c r="H1125">
-        <v>0.006208399037576147</v>
+        <v>0.006220706935478857</v>
       </c>
       <c r="I1125">
-        <v>0.06076573565392929</v>
+        <v>0.08768942936205937</v>
       </c>
       <c r="J1125">
         <v>0.7692102097289957</v>
       </c>
       <c r="K1125">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1125">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="M1125">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1125">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1125">
         <v>1</v>
@@ -58204,46 +58204,46 @@
     </row>
     <row r="1126" spans="1:16">
       <c r="A1126" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1126" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C1126">
-        <v>1.470064145645534</v>
+        <v>1.466219430964504</v>
       </c>
       <c r="D1126" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1126">
-        <v>1.531600962423853</v>
+        <v>1.559293064521143</v>
       </c>
       <c r="F1126">
         <v>1</v>
       </c>
       <c r="G1126">
-        <v>0.006269935854354466</v>
+        <v>0.006373780569035497</v>
       </c>
       <c r="H1126">
-        <v>0.006208399037576147</v>
+        <v>0.006220706935478857</v>
       </c>
       <c r="I1126">
-        <v>0.06153681677831946</v>
+        <v>0.09307363355663956</v>
       </c>
       <c r="J1126">
         <v>0.7692102097289957</v>
       </c>
       <c r="K1126">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="L1126">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="M1126">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1126">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1126">
         <v>1</v>
@@ -58254,46 +58254,46 @@
     </row>
     <row r="1127" spans="1:16">
       <c r="A1127" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1127" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C1127">
-        <v>1.471603635159084</v>
+        <v>1.582369370813013</v>
       </c>
       <c r="D1127" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
       <c r="E1127">
-        <v>1.559293064521143</v>
+        <v>1.517756247742823</v>
       </c>
       <c r="F1127">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1127">
-        <v>0.006348396364840916</v>
+        <v>0.006197630629186987</v>
       </c>
       <c r="H1127">
-        <v>0.006220706935478857</v>
+        <v>0.006302243752257177</v>
       </c>
       <c r="I1127">
-        <v>0.08768942936205937</v>
+        <v>0.06461312307018963</v>
       </c>
       <c r="J1127">
         <v>0.7692102097289957</v>
       </c>
       <c r="K1127">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="L1127">
+        <v>3.89</v>
+      </c>
+      <c r="M1127">
+        <v>3.11</v>
+      </c>
+      <c r="N1127">
         <v>3.91</v>
-      </c>
-      <c r="M1127">
-        <v>3.03</v>
-      </c>
-      <c r="N1127">
-        <v>3.89</v>
       </c>
       <c r="O1127">
         <v>1</v>
@@ -58304,146 +58304,146 @@
     </row>
     <row r="1128" spans="1:16">
       <c r="A1128" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1128" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C1128">
-        <v>1.466219430964504</v>
+        <v>1.602907629898571</v>
       </c>
       <c r="D1128" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="E1128">
-        <v>1.559293064521143</v>
+        <v>1.521383345459015</v>
       </c>
       <c r="F1128">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1128">
-        <v>0.006373780569035497</v>
+        <v>0.00669709237010143</v>
       </c>
       <c r="H1128">
-        <v>0.006220706935478857</v>
+        <v>0.006538616654540985</v>
       </c>
       <c r="I1128">
-        <v>0.09307363355663956</v>
+        <v>0.08152428443955539</v>
       </c>
       <c r="J1128">
-        <v>0.7692102097289957</v>
+        <v>0.7695143112088911</v>
       </c>
       <c r="K1128">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="L1128">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="M1128">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="N1128">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="O1128">
         <v>1</v>
       </c>
       <c r="P1128" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1129" spans="1:16">
       <c r="A1129" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B1129" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1129">
-        <v>1.582369370813013</v>
+        <v>1.656066780149149</v>
       </c>
       <c r="D1129" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E1129">
-        <v>1.517756247742823</v>
+        <v>1.769189069942572</v>
       </c>
       <c r="F1129">
         <v>-1</v>
       </c>
       <c r="G1129">
-        <v>0.006197630629186987</v>
+        <v>0.006303933219850851</v>
       </c>
       <c r="H1129">
-        <v>0.006302243752257177</v>
+        <v>0.006170810930057429</v>
       </c>
       <c r="I1129">
-        <v>0.06461312307018963</v>
+        <v>-0.1131222897934228</v>
       </c>
       <c r="J1129">
-        <v>0.7692102097289957</v>
+        <v>0.7695143112088911</v>
       </c>
       <c r="K1129">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="L1129">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
       <c r="M1129">
-        <v>3.11</v>
+        <v>2.86</v>
       </c>
       <c r="N1129">
-        <v>3.91</v>
+        <v>3.97</v>
       </c>
       <c r="O1129">
         <v>1</v>
       </c>
       <c r="P1129" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1130" spans="1:16">
       <c r="A1130" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1130" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C1130">
-        <v>1.602907629898571</v>
+        <v>1.469859061019459</v>
       </c>
       <c r="D1130" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1130">
-        <v>1.521383345459015</v>
+        <v>1.530676493924971</v>
       </c>
       <c r="F1130">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1130">
-        <v>0.00669709237010143</v>
+        <v>0.006410140938980541</v>
       </c>
       <c r="H1130">
-        <v>0.006538616654540985</v>
+        <v>0.006209323506075029</v>
       </c>
       <c r="I1130">
-        <v>0.08152428443955539</v>
+        <v>0.06081743290551156</v>
       </c>
       <c r="J1130">
         <v>0.7695143112088911</v>
       </c>
       <c r="K1130">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1130">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="M1130">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="N1130">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="O1130">
         <v>1</v>
@@ -58454,46 +58454,46 @@
     </row>
     <row r="1131" spans="1:16">
       <c r="A1131" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1131" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C1131">
-        <v>1.656066780149149</v>
+        <v>1.471420205916171</v>
       </c>
       <c r="D1131" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E1131">
-        <v>1.769189069942572</v>
+        <v>1.530676493924971</v>
       </c>
       <c r="F1131">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1131">
-        <v>0.006303933219850851</v>
+        <v>0.00628857979408383</v>
       </c>
       <c r="H1131">
-        <v>0.006170810930057429</v>
+        <v>0.006209323506075029</v>
       </c>
       <c r="I1131">
-        <v>-0.1131222897934228</v>
+        <v>0.05925628800880034</v>
       </c>
       <c r="J1131">
         <v>0.7695143112088911</v>
       </c>
       <c r="K1131">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="L1131">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="M1131">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="N1131">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
       <c r="O1131">
         <v>1</v>
@@ -58504,46 +58504,46 @@
     </row>
     <row r="1132" spans="1:16">
       <c r="A1132" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1132" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C1132">
-        <v>1.469859061019459</v>
+        <v>1.472944490355726</v>
       </c>
       <c r="D1132" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1132">
-        <v>1.530676493924971</v>
+        <v>1.55837163703706</v>
       </c>
       <c r="F1132">
         <v>1</v>
       </c>
       <c r="G1132">
-        <v>0.006410140938980541</v>
+        <v>0.006367055509644274</v>
       </c>
       <c r="H1132">
-        <v>0.006209323506075029</v>
+        <v>0.006221628362962941</v>
       </c>
       <c r="I1132">
-        <v>0.06081743290551156</v>
+        <v>0.08542714668133433</v>
       </c>
       <c r="J1132">
         <v>0.7695143112088911</v>
       </c>
       <c r="K1132">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="L1132">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="M1132">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1132">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1132">
         <v>1</v>
@@ -58554,46 +58554,46 @@
     </row>
     <row r="1133" spans="1:16">
       <c r="A1133" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1133" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C1133">
-        <v>1.471420205916171</v>
+        <v>1.465249347243637</v>
       </c>
       <c r="D1133" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1133">
-        <v>1.530676493924971</v>
+        <v>1.55837163703706</v>
       </c>
       <c r="F1133">
         <v>1</v>
       </c>
       <c r="G1133">
-        <v>0.00628857979408383</v>
+        <v>0.006374750652756362</v>
       </c>
       <c r="H1133">
-        <v>0.006209323506075029</v>
+        <v>0.006221628362962941</v>
       </c>
       <c r="I1133">
-        <v>0.05925628800880034</v>
+        <v>0.09312228979342274</v>
       </c>
       <c r="J1133">
         <v>0.7695143112088911</v>
       </c>
       <c r="K1133">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="L1133">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="M1133">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1133">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1133">
         <v>1</v>
@@ -58604,46 +58604,46 @@
     </row>
     <row r="1134" spans="1:16">
       <c r="A1134" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1134" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C1134">
-        <v>1.472944490355726</v>
+        <v>1.581457066373327</v>
       </c>
       <c r="D1134" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
       <c r="E1134">
-        <v>1.55837163703706</v>
+        <v>1.516810492140349</v>
       </c>
       <c r="F1134">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1134">
-        <v>0.006367055509644274</v>
+        <v>0.006198542933626674</v>
       </c>
       <c r="H1134">
-        <v>0.006221628362962941</v>
+        <v>0.006303189507859651</v>
       </c>
       <c r="I1134">
-        <v>0.08542714668133433</v>
+        <v>0.06464657423297782</v>
       </c>
       <c r="J1134">
         <v>0.7695143112088911</v>
       </c>
       <c r="K1134">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="L1134">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="M1134">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="N1134">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="O1134">
         <v>1</v>
@@ -58654,146 +58654,146 @@
     </row>
     <row r="1135" spans="1:16">
       <c r="A1135" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1135" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C1135">
-        <v>1.465249347243637</v>
+        <v>1.605811626833668</v>
       </c>
       <c r="D1135" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="E1135">
-        <v>1.55837163703706</v>
+        <v>1.524243475370924</v>
       </c>
       <c r="F1135">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1135">
-        <v>0.006374750652756362</v>
+        <v>0.006694188373166332</v>
       </c>
       <c r="H1135">
-        <v>0.006221628362962941</v>
+        <v>0.006535756524629076</v>
       </c>
       <c r="I1135">
-        <v>0.09312228979342274</v>
+        <v>0.08156815146274399</v>
       </c>
       <c r="J1135">
-        <v>0.7695143112088911</v>
+        <v>0.7686369707451154</v>
       </c>
       <c r="K1135">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="L1135">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="M1135">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="N1135">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="O1135">
         <v>1</v>
       </c>
       <c r="P1135" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1136" spans="1:16">
       <c r="A1136" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B1136" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1136">
-        <v>1.581457066373327</v>
+        <v>1.658716348349751</v>
       </c>
       <c r="D1136" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E1136">
-        <v>1.516810492140349</v>
+        <v>1.77169826366897</v>
       </c>
       <c r="F1136">
         <v>-1</v>
       </c>
       <c r="G1136">
-        <v>0.006198542933626674</v>
+        <v>0.006301283651650248</v>
       </c>
       <c r="H1136">
-        <v>0.006303189507859651</v>
+        <v>0.006168301736331029</v>
       </c>
       <c r="I1136">
-        <v>0.06464657423297782</v>
+        <v>-0.1129819153192191</v>
       </c>
       <c r="J1136">
-        <v>0.7695143112088911</v>
+        <v>0.7686369707451154</v>
       </c>
       <c r="K1136">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="L1136">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
       <c r="M1136">
-        <v>3.11</v>
+        <v>2.86</v>
       </c>
       <c r="N1136">
-        <v>3.91</v>
+        <v>3.97</v>
       </c>
       <c r="O1136">
         <v>1</v>
       </c>
       <c r="P1136" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1137" spans="1:16">
       <c r="A1137" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1137" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C1137">
-        <v>1.605811626833668</v>
+        <v>1.47267532390818</v>
       </c>
       <c r="D1137" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1137">
-        <v>1.524243475370924</v>
+        <v>1.533343608934849</v>
       </c>
       <c r="F1137">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1137">
-        <v>0.006694188373166332</v>
+        <v>0.00640732467609182</v>
       </c>
       <c r="H1137">
-        <v>0.006535756524629076</v>
+        <v>0.00620665639106515</v>
       </c>
       <c r="I1137">
-        <v>0.08156815146274399</v>
+        <v>0.06066828502666954</v>
       </c>
       <c r="J1137">
         <v>0.7686369707451154</v>
       </c>
       <c r="K1137">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1137">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="M1137">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="N1137">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="O1137">
         <v>1</v>
@@ -58804,46 +58804,46 @@
     </row>
     <row r="1138" spans="1:16">
       <c r="A1138" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1138" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C1138">
-        <v>1.658716348349751</v>
+        <v>1.474166281567789</v>
       </c>
       <c r="D1138" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E1138">
-        <v>1.77169826366897</v>
+        <v>1.533343608934849</v>
       </c>
       <c r="F1138">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1138">
-        <v>0.006301283651650248</v>
+        <v>0.006285833718432211</v>
       </c>
       <c r="H1138">
-        <v>0.006168301736331029</v>
+        <v>0.00620665639106515</v>
       </c>
       <c r="I1138">
-        <v>-0.1129819153192191</v>
+        <v>0.05917732736706016</v>
       </c>
       <c r="J1138">
         <v>0.7686369707451154</v>
       </c>
       <c r="K1138">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="L1138">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="M1138">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="N1138">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
       <c r="O1138">
         <v>1</v>
@@ -58854,46 +58854,46 @@
     </row>
     <row r="1139" spans="1:16">
       <c r="A1139" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1139" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C1139">
-        <v>1.47267532390818</v>
+        <v>1.475734433030533</v>
       </c>
       <c r="D1139" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1139">
-        <v>1.533343608934849</v>
+        <v>1.561029978642301</v>
       </c>
       <c r="F1139">
         <v>1</v>
       </c>
       <c r="G1139">
-        <v>0.00640732467609182</v>
+        <v>0.006364265566969467</v>
       </c>
       <c r="H1139">
-        <v>0.00620665639106515</v>
+        <v>0.0062189700213577</v>
       </c>
       <c r="I1139">
-        <v>0.06066828502666954</v>
+        <v>0.08529554561176766</v>
       </c>
       <c r="J1139">
         <v>0.7686369707451154</v>
       </c>
       <c r="K1139">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="L1139">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="M1139">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1139">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1139">
         <v>1</v>
@@ -58904,46 +58904,46 @@
     </row>
     <row r="1140" spans="1:16">
       <c r="A1140" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1140" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C1140">
-        <v>1.474166281567789</v>
+        <v>1.468048063323082</v>
       </c>
       <c r="D1140" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1140">
-        <v>1.533343608934849</v>
+        <v>1.561029978642301</v>
       </c>
       <c r="F1140">
         <v>1</v>
       </c>
       <c r="G1140">
-        <v>0.006285833718432211</v>
+        <v>0.006371951936676918</v>
       </c>
       <c r="H1140">
-        <v>0.00620665639106515</v>
+        <v>0.0062189700213577</v>
       </c>
       <c r="I1140">
-        <v>0.05917732736706016</v>
+        <v>0.09298191531921862</v>
       </c>
       <c r="J1140">
         <v>0.7686369707451154</v>
       </c>
       <c r="K1140">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="L1140">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="M1140">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1140">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1140">
         <v>1</v>
@@ -58954,146 +58954,146 @@
     </row>
     <row r="1141" spans="1:16">
       <c r="A1141" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1141" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C1141">
-        <v>1.475734433030533</v>
+        <v>1.617576071919765</v>
       </c>
       <c r="D1141" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="E1141">
-        <v>1.561029978642301</v>
+        <v>1.535830209806174</v>
       </c>
       <c r="F1141">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1141">
-        <v>0.006364265566969467</v>
+        <v>0.006682423928080235</v>
       </c>
       <c r="H1141">
-        <v>0.0062189700213577</v>
+        <v>0.006524169790193828</v>
       </c>
       <c r="I1141">
-        <v>0.08529554561176766</v>
+        <v>0.08174586211359181</v>
       </c>
       <c r="J1141">
-        <v>0.7686369707451154</v>
+        <v>0.7650827577281677</v>
       </c>
       <c r="K1141">
-        <v>3.18</v>
+        <v>3.31</v>
       </c>
       <c r="L1141">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="M1141">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="N1141">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="O1141">
         <v>1</v>
       </c>
       <c r="P1141" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1142" spans="1:16">
       <c r="A1142" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1142" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C1142">
-        <v>1.468048063323082</v>
+        <v>1.669450071660934</v>
       </c>
       <c r="D1142" t="s">
-        <v>216</v>
+        <v>350</v>
       </c>
       <c r="E1142">
-        <v>1.561029978642301</v>
+        <v>1.781863312897441</v>
       </c>
       <c r="F1142">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1142">
-        <v>0.006371951936676918</v>
+        <v>0.006290549928339067</v>
       </c>
       <c r="H1142">
-        <v>0.0062189700213577</v>
+        <v>0.00615813668710256</v>
       </c>
       <c r="I1142">
-        <v>0.09298191531921862</v>
+        <v>-0.1124132412365073</v>
       </c>
       <c r="J1142">
-        <v>0.7686369707451154</v>
+        <v>0.7650827577281677</v>
       </c>
       <c r="K1142">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="L1142">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="M1142">
-        <v>3.03</v>
+        <v>2.86</v>
       </c>
       <c r="N1142">
-        <v>3.89</v>
+        <v>3.97</v>
       </c>
       <c r="O1142">
         <v>1</v>
       </c>
       <c r="P1142" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1143" spans="1:16">
       <c r="A1143" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1143" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C1143">
-        <v>1.617576071919765</v>
+        <v>1.484084347692582</v>
       </c>
       <c r="D1143" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1143">
-        <v>1.535830209806174</v>
+        <v>1.54414841650637</v>
       </c>
       <c r="F1143">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1143">
-        <v>0.006682423928080235</v>
+        <v>0.006395915652307418</v>
       </c>
       <c r="H1143">
-        <v>0.006524169790193828</v>
+        <v>0.00619585158349363</v>
       </c>
       <c r="I1143">
-        <v>0.08174586211359181</v>
+        <v>0.06006406881378856</v>
       </c>
       <c r="J1143">
         <v>0.7650827577281677</v>
       </c>
       <c r="K1143">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1143">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="M1143">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="N1143">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="O1143">
         <v>1</v>
@@ -59104,46 +59104,46 @@
     </row>
     <row r="1144" spans="1:16">
       <c r="A1144" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1144" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C1144">
-        <v>1.669450071660934</v>
+        <v>1.485290968310835</v>
       </c>
       <c r="D1144" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E1144">
-        <v>1.781863312897441</v>
+        <v>1.54414841650637</v>
       </c>
       <c r="F1144">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1144">
-        <v>0.006290549928339067</v>
+        <v>0.006274709031689165</v>
       </c>
       <c r="H1144">
-        <v>0.00615813668710256</v>
+        <v>0.00619585158349363</v>
       </c>
       <c r="I1144">
-        <v>-0.1124132412365073</v>
+        <v>0.05885744819553507</v>
       </c>
       <c r="J1144">
         <v>0.7650827577281677</v>
       </c>
       <c r="K1144">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="L1144">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="M1144">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="N1144">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
       <c r="O1144">
         <v>1</v>
@@ -59154,46 +59154,46 @@
     </row>
     <row r="1145" spans="1:16">
       <c r="A1145" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1145" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C1145">
-        <v>1.484084347692582</v>
+        <v>1.487036830424426</v>
       </c>
       <c r="D1145" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1145">
-        <v>1.54414841650637</v>
+        <v>1.571799244083652</v>
       </c>
       <c r="F1145">
         <v>1</v>
       </c>
       <c r="G1145">
-        <v>0.006395915652307418</v>
+        <v>0.006352963169575574</v>
       </c>
       <c r="H1145">
-        <v>0.00619585158349363</v>
+        <v>0.006208200755916348</v>
       </c>
       <c r="I1145">
-        <v>0.06006406881378856</v>
+        <v>0.08476241365922599</v>
       </c>
       <c r="J1145">
         <v>0.7650827577281677</v>
       </c>
       <c r="K1145">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="L1145">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="M1145">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1145">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1145">
         <v>1</v>
@@ -59204,46 +59204,46 @@
     </row>
     <row r="1146" spans="1:16">
       <c r="A1146" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1146" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C1146">
-        <v>1.485290968310835</v>
+        <v>1.479386002847145</v>
       </c>
       <c r="D1146" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1146">
-        <v>1.54414841650637</v>
+        <v>1.571799244083652</v>
       </c>
       <c r="F1146">
         <v>1</v>
       </c>
       <c r="G1146">
-        <v>0.006274709031689165</v>
+        <v>0.006360613997152855</v>
       </c>
       <c r="H1146">
-        <v>0.00619585158349363</v>
+        <v>0.006208200755916348</v>
       </c>
       <c r="I1146">
-        <v>0.05885744819553507</v>
+        <v>0.09241324123650729</v>
       </c>
       <c r="J1146">
         <v>0.7650827577281677</v>
       </c>
       <c r="K1146">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="L1146">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="M1146">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1146">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1146">
         <v>1</v>
@@ -59254,146 +59254,146 @@
     </row>
     <row r="1147" spans="1:16">
       <c r="A1147" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1147" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C1147">
-        <v>1.487036830424426</v>
+        <v>1.624688037479117</v>
       </c>
       <c r="D1147" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="E1147">
-        <v>1.571799244083652</v>
+        <v>1.542834743861608</v>
       </c>
       <c r="F1147">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1147">
-        <v>0.006352963169575574</v>
+        <v>0.006675311962520883</v>
       </c>
       <c r="H1147">
-        <v>0.006208200755916348</v>
+        <v>0.006517165256138393</v>
       </c>
       <c r="I1147">
-        <v>0.08476241365922599</v>
+        <v>0.08185329361750915</v>
       </c>
       <c r="J1147">
-        <v>0.7650827577281677</v>
+        <v>0.7629341276498137</v>
       </c>
       <c r="K1147">
-        <v>3.18</v>
+        <v>3.31</v>
       </c>
       <c r="L1147">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="M1147">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="N1147">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="O1147">
         <v>1</v>
       </c>
       <c r="P1147" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1148" spans="1:16">
       <c r="A1148" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1148" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C1148">
-        <v>1.479386002847145</v>
+        <v>1.675938934497562</v>
       </c>
       <c r="D1148" t="s">
-        <v>216</v>
+        <v>350</v>
       </c>
       <c r="E1148">
-        <v>1.571799244083652</v>
+        <v>1.788008394921533</v>
       </c>
       <c r="F1148">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1148">
-        <v>0.006360613997152855</v>
+        <v>0.006284061065502437</v>
       </c>
       <c r="H1148">
-        <v>0.006208200755916348</v>
+        <v>0.006151991605078468</v>
       </c>
       <c r="I1148">
-        <v>0.09241324123650729</v>
+        <v>-0.1120694604239705</v>
       </c>
       <c r="J1148">
-        <v>0.7650827577281677</v>
+        <v>0.7629341276498137</v>
       </c>
       <c r="K1148">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="L1148">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="M1148">
-        <v>3.03</v>
+        <v>2.86</v>
       </c>
       <c r="N1148">
-        <v>3.89</v>
+        <v>3.97</v>
       </c>
       <c r="O1148">
         <v>1</v>
       </c>
       <c r="P1148" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1149" spans="1:16">
       <c r="A1149" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1149" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C1149">
-        <v>1.624688037479117</v>
+        <v>1.490981450244098</v>
       </c>
       <c r="D1149" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1149">
-        <v>1.542834743861608</v>
+        <v>1.550680251944566</v>
       </c>
       <c r="F1149">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1149">
-        <v>0.006675311962520883</v>
+        <v>0.006389018549755901</v>
       </c>
       <c r="H1149">
-        <v>0.006517165256138393</v>
+        <v>0.006189319748055434</v>
       </c>
       <c r="I1149">
-        <v>0.08185329361750915</v>
+        <v>0.05969880170046826</v>
       </c>
       <c r="J1149">
         <v>0.7629341276498137</v>
       </c>
       <c r="K1149">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1149">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="M1149">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="N1149">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="O1149">
         <v>1</v>
@@ -59404,46 +59404,46 @@
     </row>
     <row r="1150" spans="1:16">
       <c r="A1150" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1150" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C1150">
-        <v>1.675938934497562</v>
+        <v>1.492016180456083</v>
       </c>
       <c r="D1150" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E1150">
-        <v>1.788008394921533</v>
+        <v>1.550680251944566</v>
       </c>
       <c r="F1150">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1150">
-        <v>0.006284061065502437</v>
+        <v>0.006267983819543917</v>
       </c>
       <c r="H1150">
-        <v>0.006151991605078468</v>
+        <v>0.006189319748055434</v>
       </c>
       <c r="I1150">
-        <v>-0.1120694604239705</v>
+        <v>0.0586640714884834</v>
       </c>
       <c r="J1150">
         <v>0.7629341276498137</v>
       </c>
       <c r="K1150">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="L1150">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="M1150">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="N1150">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
       <c r="O1150">
         <v>1</v>
@@ -59454,46 +59454,46 @@
     </row>
     <row r="1151" spans="1:16">
       <c r="A1151" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1151" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C1151">
-        <v>1.490981450244098</v>
+        <v>1.493869474073592</v>
       </c>
       <c r="D1151" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1151">
-        <v>1.550680251944566</v>
+        <v>1.578309593221065</v>
       </c>
       <c r="F1151">
         <v>1</v>
       </c>
       <c r="G1151">
-        <v>0.006389018549755901</v>
+        <v>0.006346130525926408</v>
       </c>
       <c r="H1151">
-        <v>0.006189319748055434</v>
+        <v>0.006201690406778935</v>
       </c>
       <c r="I1151">
-        <v>0.05969880170046826</v>
+        <v>0.08444011914747263</v>
       </c>
       <c r="J1151">
         <v>0.7629341276498137</v>
       </c>
       <c r="K1151">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="L1151">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="M1151">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1151">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1151">
         <v>1</v>
@@ -59504,46 +59504,46 @@
     </row>
     <row r="1152" spans="1:16">
       <c r="A1152" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1152" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C1152">
-        <v>1.492016180456083</v>
+        <v>1.486240132797094</v>
       </c>
       <c r="D1152" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1152">
-        <v>1.550680251944566</v>
+        <v>1.578309593221065</v>
       </c>
       <c r="F1152">
         <v>1</v>
       </c>
       <c r="G1152">
-        <v>0.006267983819543917</v>
+        <v>0.006353759867202905</v>
       </c>
       <c r="H1152">
-        <v>0.006189319748055434</v>
+        <v>0.006201690406778935</v>
       </c>
       <c r="I1152">
-        <v>0.0586640714884834</v>
+        <v>0.09206946042397046</v>
       </c>
       <c r="J1152">
         <v>0.7629341276498137</v>
       </c>
       <c r="K1152">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="L1152">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="M1152">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1152">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1152">
         <v>1</v>
@@ -59554,146 +59554,146 @@
     </row>
     <row r="1153" spans="1:16">
       <c r="A1153" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1153" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C1153">
-        <v>1.493869474073592</v>
+        <v>1.630450898793061</v>
       </c>
       <c r="D1153" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="E1153">
-        <v>1.578309593221065</v>
+        <v>1.548510552889843</v>
       </c>
       <c r="F1153">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1153">
-        <v>0.006346130525926408</v>
+        <v>0.00666954910120694</v>
       </c>
       <c r="H1153">
-        <v>0.006201690406778935</v>
+        <v>0.006511489447110158</v>
       </c>
       <c r="I1153">
-        <v>0.08444011914747263</v>
+        <v>0.08194034590321797</v>
       </c>
       <c r="J1153">
-        <v>0.7629341276498137</v>
+        <v>0.7611930819356313</v>
       </c>
       <c r="K1153">
-        <v>3.18</v>
+        <v>3.31</v>
       </c>
       <c r="L1153">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="M1153">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="N1153">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="O1153">
         <v>1</v>
       </c>
       <c r="P1153" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1154" spans="1:16">
       <c r="A1154" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1154" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C1154">
-        <v>1.486240132797094</v>
+        <v>1.681196892554393</v>
       </c>
       <c r="D1154" t="s">
-        <v>216</v>
+        <v>350</v>
       </c>
       <c r="E1154">
-        <v>1.578309593221065</v>
+        <v>1.792987785664095</v>
       </c>
       <c r="F1154">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1154">
-        <v>0.006353759867202905</v>
+        <v>0.006278803107445607</v>
       </c>
       <c r="H1154">
-        <v>0.006201690406778935</v>
+        <v>0.006147012214335906</v>
       </c>
       <c r="I1154">
-        <v>0.09206946042397046</v>
+        <v>-0.1117908931097014</v>
       </c>
       <c r="J1154">
-        <v>0.7629341276498137</v>
+        <v>0.7611930819356313</v>
       </c>
       <c r="K1154">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="L1154">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="M1154">
-        <v>3.03</v>
+        <v>2.86</v>
       </c>
       <c r="N1154">
-        <v>3.89</v>
+        <v>3.97</v>
       </c>
       <c r="O1154">
         <v>1</v>
       </c>
       <c r="P1154" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1155" spans="1:16">
       <c r="A1155" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1155" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C1155">
-        <v>1.630450898793061</v>
+        <v>1.496570206986624</v>
       </c>
       <c r="D1155" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1155">
-        <v>1.548510552889843</v>
+        <v>1.555973030915681</v>
       </c>
       <c r="F1155">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1155">
-        <v>0.00666954910120694</v>
+        <v>0.006383429793013377</v>
       </c>
       <c r="H1155">
-        <v>0.006511489447110158</v>
+        <v>0.00618402696908432</v>
       </c>
       <c r="I1155">
-        <v>0.08194034590321797</v>
+        <v>0.05940282392905738</v>
       </c>
       <c r="J1155">
         <v>0.7611930819356313</v>
       </c>
       <c r="K1155">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="L1155">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="M1155">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="N1155">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="O1155">
         <v>1</v>
@@ -59704,46 +59704,46 @@
     </row>
     <row r="1156" spans="1:16">
       <c r="A1156" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1156" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C1156">
-        <v>1.681196892554393</v>
+        <v>1.497465653541474</v>
       </c>
       <c r="D1156" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E1156">
-        <v>1.792987785664095</v>
+        <v>1.555973030915681</v>
       </c>
       <c r="F1156">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1156">
-        <v>0.006278803107445607</v>
+        <v>0.006262534346458526</v>
       </c>
       <c r="H1156">
-        <v>0.006147012214335906</v>
+        <v>0.00618402696908432</v>
       </c>
       <c r="I1156">
-        <v>-0.1117908931097014</v>
+        <v>0.05850737737420708</v>
       </c>
       <c r="J1156">
         <v>0.7611930819356313</v>
       </c>
       <c r="K1156">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="L1156">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="M1156">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="N1156">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
       <c r="O1156">
         <v>1</v>
@@ -59754,46 +59754,46 @@
     </row>
     <row r="1157" spans="1:16">
       <c r="A1157" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1157" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C1157">
-        <v>1.496570206986624</v>
+        <v>1.499405999444692</v>
       </c>
       <c r="D1157" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1157">
-        <v>1.555973030915681</v>
+        <v>1.583584961735037</v>
       </c>
       <c r="F1157">
         <v>1</v>
       </c>
       <c r="G1157">
-        <v>0.006383429793013377</v>
+        <v>0.006340594000555308</v>
       </c>
       <c r="H1157">
-        <v>0.00618402696908432</v>
+        <v>0.006196415038264963</v>
       </c>
       <c r="I1157">
-        <v>0.05940282392905738</v>
+        <v>0.08417896229034527</v>
       </c>
       <c r="J1157">
         <v>0.7611930819356313</v>
       </c>
       <c r="K1157">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="L1157">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="M1157">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1157">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1157">
         <v>1</v>
@@ -59804,46 +59804,46 @@
     </row>
     <row r="1158" spans="1:16">
       <c r="A1158" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1158" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C1158">
-        <v>1.497465653541474</v>
+        <v>1.491794068625336</v>
       </c>
       <c r="D1158" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1158">
-        <v>1.555973030915681</v>
+        <v>1.583584961735037</v>
       </c>
       <c r="F1158">
         <v>1</v>
       </c>
       <c r="G1158">
-        <v>0.006262534346458526</v>
+        <v>0.006348205931374664</v>
       </c>
       <c r="H1158">
-        <v>0.00618402696908432</v>
+        <v>0.006196415038264963</v>
       </c>
       <c r="I1158">
-        <v>0.05850737737420708</v>
+        <v>0.09179089310970134</v>
       </c>
       <c r="J1158">
         <v>0.7611930819356313</v>
       </c>
       <c r="K1158">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="L1158">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="M1158">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1158">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1158">
         <v>1</v>
@@ -59854,146 +59854,146 @@
     </row>
     <row r="1159" spans="1:16">
       <c r="A1159" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1159" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C1159">
-        <v>1.497017930264049</v>
+        <v>1.686574591350994</v>
       </c>
       <c r="D1159" t="s">
-        <v>216</v>
+        <v>350</v>
       </c>
       <c r="E1159">
-        <v>1.583584961735037</v>
+        <v>1.798080573266174</v>
       </c>
       <c r="F1159">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1159">
-        <v>0.006322982069735952</v>
+        <v>0.006273425408649006</v>
       </c>
       <c r="H1159">
-        <v>0.006196415038264963</v>
+        <v>0.006141919426733827</v>
       </c>
       <c r="I1159">
-        <v>0.08656703147098854</v>
+        <v>-0.1115059819151796</v>
       </c>
       <c r="J1159">
-        <v>0.7611930819356313</v>
+        <v>0.7594123869698695</v>
       </c>
       <c r="K1159">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="L1159">
-        <v>3.91</v>
+        <v>3.98</v>
       </c>
       <c r="M1159">
-        <v>3.03</v>
+        <v>2.86</v>
       </c>
       <c r="N1159">
-        <v>3.89</v>
+        <v>3.97</v>
       </c>
       <c r="O1159">
         <v>1</v>
       </c>
       <c r="P1159" t="s">
-        <v>500</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1160" spans="1:16">
       <c r="A1160" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1160" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C1160">
-        <v>1.491794068625336</v>
+        <v>1.502286237826719</v>
       </c>
       <c r="D1160" t="s">
-        <v>216</v>
+        <v>358</v>
       </c>
       <c r="E1160">
-        <v>1.583584961735037</v>
+        <v>1.561386343611597</v>
       </c>
       <c r="F1160">
         <v>1</v>
       </c>
       <c r="G1160">
-        <v>0.006348205931374664</v>
+        <v>0.006377713762173281</v>
       </c>
       <c r="H1160">
-        <v>0.006196415038264963</v>
+        <v>0.006178613656388404</v>
       </c>
       <c r="I1160">
-        <v>0.09179089310970134</v>
+        <v>0.05910010578487812</v>
       </c>
       <c r="J1160">
-        <v>0.7611930819356313</v>
+        <v>0.7594123869698695</v>
       </c>
       <c r="K1160">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="L1160">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="M1160">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="N1160">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="O1160">
         <v>1</v>
       </c>
       <c r="P1160" t="s">
-        <v>500</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1161" spans="1:16">
       <c r="A1161" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1161" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C1161">
-        <v>1.686574591350994</v>
+        <v>1.503039228784309</v>
       </c>
       <c r="D1161" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E1161">
-        <v>1.798080573266174</v>
+        <v>1.561386343611597</v>
       </c>
       <c r="F1161">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1161">
-        <v>0.006273425408649006</v>
+        <v>0.006256960771215692</v>
       </c>
       <c r="H1161">
-        <v>0.006141919426733827</v>
+        <v>0.006178613656388404</v>
       </c>
       <c r="I1161">
-        <v>-0.1115059819151796</v>
+        <v>0.05834711482728849</v>
       </c>
       <c r="J1161">
         <v>0.7594123869698695</v>
       </c>
       <c r="K1161">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="L1161">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="M1161">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="N1161">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
       <c r="O1161">
         <v>1</v>
@@ -60004,46 +60004,46 @@
     </row>
     <row r="1162" spans="1:16">
       <c r="A1162" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1162" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1162">
-        <v>1.502286237826719</v>
+        <v>1.502662733305514</v>
       </c>
       <c r="D1162" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1162">
-        <v>1.561386343611597</v>
+        <v>1.588980467481296</v>
       </c>
       <c r="F1162">
         <v>1</v>
       </c>
       <c r="G1162">
-        <v>0.006377713762173281</v>
+        <v>0.006317337266694486</v>
       </c>
       <c r="H1162">
-        <v>0.006178613656388404</v>
+        <v>0.006191019532518704</v>
       </c>
       <c r="I1162">
-        <v>0.05910010578487812</v>
+        <v>0.0863177341757817</v>
       </c>
       <c r="J1162">
         <v>0.7594123869698695</v>
       </c>
       <c r="K1162">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="L1162">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="M1162">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1162">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1162">
         <v>1</v>
@@ -60054,46 +60054,46 @@
     </row>
     <row r="1163" spans="1:16">
       <c r="A1163" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1163" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C1163">
-        <v>1.503039228784309</v>
+        <v>1.497474485566117</v>
       </c>
       <c r="D1163" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="E1163">
-        <v>1.561386343611597</v>
+        <v>1.588980467481296</v>
       </c>
       <c r="F1163">
         <v>1</v>
       </c>
       <c r="G1163">
-        <v>0.006256960771215692</v>
+        <v>0.006342525514433883</v>
       </c>
       <c r="H1163">
-        <v>0.006178613656388404</v>
+        <v>0.006191019532518704</v>
       </c>
       <c r="I1163">
-        <v>0.05834711482728849</v>
+        <v>0.09150598191517911</v>
       </c>
       <c r="J1163">
         <v>0.7594123869698695</v>
       </c>
       <c r="K1163">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="L1163">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="M1163">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N1163">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="O1163">
         <v>1</v>
@@ -60104,146 +60104,146 @@
     </row>
     <row r="1164" spans="1:16">
       <c r="A1164" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1164" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C1164">
-        <v>1.502662733305514</v>
+        <v>1.70848612867321</v>
       </c>
       <c r="D1164" t="s">
-        <v>216</v>
+        <v>350</v>
       </c>
       <c r="E1164">
-        <v>1.588980467481296</v>
+        <v>1.818831234438868</v>
       </c>
       <c r="F1164">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1164">
-        <v>0.006317337266694486</v>
+        <v>0.00625151387132679</v>
       </c>
       <c r="H1164">
-        <v>0.006191019532518704</v>
+        <v>0.006121168765561132</v>
       </c>
       <c r="I1164">
-        <v>0.0863177341757817</v>
+        <v>-0.1103451057656577</v>
       </c>
       <c r="J1164">
-        <v>0.7594123869698695</v>
+        <v>0.752156911035361</v>
       </c>
       <c r="K1164">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="L1164">
-        <v>3.91</v>
+        <v>3.98</v>
       </c>
       <c r="M1164">
-        <v>3.03</v>
+        <v>2.86</v>
       </c>
       <c r="N1164">
-        <v>3.89</v>
+        <v>3.97</v>
       </c>
       <c r="O1164">
         <v>1</v>
       </c>
       <c r="P1164" t="s">
-        <v>203</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1165" spans="1:16">
       <c r="A1165" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1165" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C1165">
-        <v>1.497474485566117</v>
+        <v>1.523270437569674</v>
       </c>
       <c r="D1165" t="s">
-        <v>216</v>
+        <v>358</v>
       </c>
       <c r="E1165">
-        <v>1.588980467481296</v>
+        <v>1.583442990452503</v>
       </c>
       <c r="F1165">
         <v>1</v>
       </c>
       <c r="G1165">
-        <v>0.006342525514433883</v>
+        <v>0.006216729562430326</v>
       </c>
       <c r="H1165">
-        <v>0.006191019532518704</v>
+        <v>0.006156557009547497</v>
       </c>
       <c r="I1165">
-        <v>0.09150598191517911</v>
+        <v>0.06017255288282897</v>
       </c>
       <c r="J1165">
-        <v>0.7594123869698695</v>
+        <v>0.752156911035361</v>
       </c>
       <c r="K1165">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="L1165">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="M1165">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="N1165">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="O1165">
         <v>1</v>
       </c>
       <c r="P1165" t="s">
-        <v>203</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1166" spans="1:16">
       <c r="A1166" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1166" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C1166">
-        <v>1.70848612867321</v>
+        <v>1.520619453797198</v>
       </c>
       <c r="D1166" t="s">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="E1166">
-        <v>1.818831234438868</v>
+        <v>1.610964559562857</v>
       </c>
       <c r="F1166">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1166">
-        <v>0.00625151387132679</v>
+        <v>0.006319380546202801</v>
       </c>
       <c r="H1166">
-        <v>0.006121168765561132</v>
+        <v>0.006169035440437144</v>
       </c>
       <c r="I1166">
-        <v>-0.1103451057656577</v>
+        <v>0.09034510576565813</v>
       </c>
       <c r="J1166">
         <v>0.752156911035361</v>
       </c>
       <c r="K1166">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="L1166">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="M1166">
-        <v>2.86</v>
+        <v>3.03</v>
       </c>
       <c r="N1166">
-        <v>3.97</v>
+        <v>3.89</v>
       </c>
       <c r="O1166">
         <v>1</v>
@@ -60254,146 +60254,146 @@
     </row>
     <row r="1167" spans="1:16">
       <c r="A1167" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1167" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C1167">
-        <v>1.523270437569674</v>
+        <v>1.704860959185642</v>
       </c>
       <c r="D1167" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="E1167">
-        <v>1.583442990452503</v>
+        <v>1.815398126910906</v>
       </c>
       <c r="F1167">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1167">
-        <v>0.006216729562430326</v>
+        <v>0.006255139040814358</v>
       </c>
       <c r="H1167">
-        <v>0.006156557009547497</v>
+        <v>0.006124601873089094</v>
       </c>
       <c r="I1167">
-        <v>0.06017255288282897</v>
+        <v>-0.1105371677252642</v>
       </c>
       <c r="J1167">
-        <v>0.752156911035361</v>
+        <v>0.7533572982829001</v>
       </c>
       <c r="K1167">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="L1167">
-        <v>3.87</v>
+        <v>3.98</v>
       </c>
       <c r="M1167">
-        <v>3.04</v>
+        <v>2.86</v>
       </c>
       <c r="N1167">
-        <v>3.87</v>
+        <v>3.97</v>
       </c>
       <c r="O1167">
         <v>1</v>
       </c>
       <c r="P1167" t="s">
-        <v>357</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1168" spans="1:16">
       <c r="A1168" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1168" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C1168">
-        <v>1.520619453797198</v>
+        <v>1.519525229357352</v>
       </c>
       <c r="D1168" t="s">
-        <v>216</v>
+        <v>358</v>
       </c>
       <c r="E1168">
-        <v>1.610964559562857</v>
+        <v>1.579793813219984</v>
       </c>
       <c r="F1168">
         <v>1</v>
       </c>
       <c r="G1168">
-        <v>0.006319380546202801</v>
+        <v>0.006220474770642649</v>
       </c>
       <c r="H1168">
-        <v>0.006169035440437144</v>
+        <v>0.006160206186780016</v>
       </c>
       <c r="I1168">
-        <v>0.09034510576565813</v>
+        <v>0.06026858386263223</v>
       </c>
       <c r="J1168">
-        <v>0.752156911035361</v>
+        <v>0.7533572982829001</v>
       </c>
       <c r="K1168">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="L1168">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="M1168">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="N1168">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="O1168">
         <v>1</v>
       </c>
       <c r="P1168" t="s">
-        <v>357</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1169" spans="1:16">
       <c r="A1169" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1169" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C1169">
-        <v>1.704860959185642</v>
+        <v>1.516790218477549</v>
       </c>
       <c r="D1169" t="s">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="E1169">
-        <v>1.815398126910906</v>
+        <v>1.607327386202813</v>
       </c>
       <c r="F1169">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1169">
-        <v>0.006255139040814358</v>
+        <v>0.006323209781522451</v>
       </c>
       <c r="H1169">
-        <v>0.006124601873089094</v>
+        <v>0.006172672613797188</v>
       </c>
       <c r="I1169">
-        <v>-0.1105371677252642</v>
+        <v>0.09053716772526421</v>
       </c>
       <c r="J1169">
         <v>0.7533572982829001</v>
       </c>
       <c r="K1169">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="L1169">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="M1169">
-        <v>2.86</v>
+        <v>3.03</v>
       </c>
       <c r="N1169">
-        <v>3.97</v>
+        <v>3.89</v>
       </c>
       <c r="O1169">
         <v>1</v>
@@ -60404,34 +60404,34 @@
     </row>
     <row r="1170" spans="1:16">
       <c r="A1170" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1170" t="s">
         <v>209</v>
       </c>
       <c r="C1170">
-        <v>1.519525229357352</v>
+        <v>1.515682324520578</v>
       </c>
       <c r="D1170" t="s">
         <v>358</v>
       </c>
       <c r="E1170">
-        <v>1.579793813219984</v>
+        <v>1.576049444404666</v>
       </c>
       <c r="F1170">
         <v>1</v>
       </c>
       <c r="G1170">
-        <v>0.006220474770642649</v>
+        <v>0.006224317675479422</v>
       </c>
       <c r="H1170">
-        <v>0.006160206186780016</v>
+        <v>0.006163950555595335</v>
       </c>
       <c r="I1170">
-        <v>0.06026858386263223</v>
+        <v>0.06036711988408783</v>
       </c>
       <c r="J1170">
-        <v>0.7533572982829001</v>
+        <v>0.7545889985510968</v>
       </c>
       <c r="K1170">
         <v>3.12</v>
@@ -60449,39 +60449,39 @@
         <v>1</v>
       </c>
       <c r="P1170" t="s">
-        <v>501</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1171" spans="1:16">
       <c r="A1171" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1171" t="s">
         <v>208</v>
       </c>
       <c r="C1171">
-        <v>1.516790218477549</v>
+        <v>1.512861094622001</v>
       </c>
       <c r="D1171" t="s">
         <v>216</v>
       </c>
       <c r="E1171">
-        <v>1.607327386202813</v>
+        <v>1.603595334390177</v>
       </c>
       <c r="F1171">
         <v>1</v>
       </c>
       <c r="G1171">
-        <v>0.006323209781522451</v>
+        <v>0.006327138905377999</v>
       </c>
       <c r="H1171">
-        <v>0.006172672613797188</v>
+        <v>0.006176404665609823</v>
       </c>
       <c r="I1171">
-        <v>0.09053716772526421</v>
+        <v>0.09073423976817585</v>
       </c>
       <c r="J1171">
-        <v>0.7533572982829001</v>
+        <v>0.7545889985510968</v>
       </c>
       <c r="K1171">
         <v>3.19</v>
@@ -60499,7 +60499,7 @@
         <v>1</v>
       </c>
       <c r="P1171" t="s">
-        <v>501</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1172" spans="1:16">
@@ -60507,54 +60507,54 @@
         <v>0</v>
       </c>
       <c r="B1172" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C1172">
-        <v>1.512861094622001</v>
+        <v>1.517080997982488</v>
       </c>
       <c r="D1172" t="s">
-        <v>216</v>
+        <v>358</v>
       </c>
       <c r="E1172">
-        <v>1.603595334390177</v>
+        <v>1.577412254444476</v>
       </c>
       <c r="F1172">
         <v>1</v>
       </c>
       <c r="G1172">
-        <v>0.006327138905377999</v>
+        <v>0.006222919002017512</v>
       </c>
       <c r="H1172">
-        <v>0.006176404665609823</v>
+        <v>0.006162587745555525</v>
       </c>
       <c r="I1172">
-        <v>0.09073423976817585</v>
+        <v>0.06033125646198734</v>
       </c>
       <c r="J1172">
-        <v>0.7545889985510968</v>
+        <v>0.7541407057748436</v>
       </c>
       <c r="K1172">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="L1172">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="M1172">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="N1172">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="O1172">
         <v>1</v>
       </c>
       <c r="P1172" t="s">
-        <v>204</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1173" spans="1:16">
       <c r="A1173" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1173" t="s">
         <v>208</v>
@@ -60604,7 +60604,7 @@
     </row>
     <row r="1174" spans="1:16">
       <c r="A1174" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1174" t="s">
         <v>207</v>
@@ -61307,43 +61307,43 @@
         <v>1</v>
       </c>
       <c r="B1188" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C1188">
-        <v>1.556299298461621</v>
+        <v>1.479804130127046</v>
       </c>
       <c r="D1188" t="s">
-        <v>210</v>
+        <v>354</v>
       </c>
       <c r="E1188">
-        <v>1.484505096460131</v>
+        <v>1.531000264794707</v>
       </c>
       <c r="F1188">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1188">
-        <v>0.006283700701538379</v>
+        <v>0.006360195869872953</v>
       </c>
       <c r="H1188">
-        <v>0.006395494903539869</v>
+        <v>0.006288999735205293</v>
       </c>
       <c r="I1188">
-        <v>0.07179420200149034</v>
+        <v>0.0511961346676606</v>
       </c>
       <c r="J1188">
         <v>0.7649516833457536</v>
       </c>
       <c r="K1188">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="L1188">
         <v>3.92</v>
       </c>
       <c r="M1188">
-        <v>3.21</v>
+        <v>3.11</v>
       </c>
       <c r="N1188">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="O1188">
         <v>1</v>
@@ -61354,96 +61354,96 @@
     </row>
     <row r="1189" spans="1:16">
       <c r="A1189" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1189" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C1189">
-        <v>1.479804130127046</v>
+        <v>1.577585951951323</v>
       </c>
       <c r="D1189" t="s">
-        <v>354</v>
+        <v>210</v>
       </c>
       <c r="E1189">
-        <v>1.531000264794707</v>
+        <v>1.488862469796072</v>
       </c>
       <c r="F1189">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1189">
-        <v>0.006360195869872953</v>
+        <v>0.006342414048048678</v>
       </c>
       <c r="H1189">
-        <v>0.006288999735205293</v>
+        <v>0.006391137530203927</v>
       </c>
       <c r="I1189">
-        <v>0.0511961346676606</v>
+        <v>0.08872348215525028</v>
       </c>
       <c r="J1189">
-        <v>0.7649516833457536</v>
+        <v>0.7635942461694478</v>
       </c>
       <c r="K1189">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="L1189">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="M1189">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="N1189">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="O1189">
         <v>1</v>
       </c>
       <c r="P1189" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1190" spans="1:16">
       <c r="A1190" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1190" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C1190">
-        <v>1.577585951951323</v>
+        <v>1.484134354719461</v>
       </c>
       <c r="D1190" t="s">
-        <v>210</v>
+        <v>354</v>
       </c>
       <c r="E1190">
-        <v>1.488862469796072</v>
+        <v>1.535221894413017</v>
       </c>
       <c r="F1190">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1190">
-        <v>0.006342414048048678</v>
+        <v>0.006355865645280538</v>
       </c>
       <c r="H1190">
-        <v>0.006391137530203927</v>
+        <v>0.006284778105586983</v>
       </c>
       <c r="I1190">
-        <v>0.08872348215525028</v>
+        <v>0.05108753969355595</v>
       </c>
       <c r="J1190">
         <v>0.7635942461694478</v>
       </c>
       <c r="K1190">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="L1190">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="M1190">
-        <v>3.21</v>
+        <v>3.11</v>
       </c>
       <c r="N1190">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="O1190">
         <v>1</v>
@@ -61454,34 +61454,34 @@
     </row>
     <row r="1191" spans="1:16">
       <c r="A1191" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1191" t="s">
         <v>208</v>
       </c>
       <c r="C1191">
-        <v>1.484134354719461</v>
+        <v>1.491154685192168</v>
       </c>
       <c r="D1191" t="s">
         <v>354</v>
       </c>
       <c r="E1191">
-        <v>1.535221894413017</v>
+        <v>1.542066166441268</v>
       </c>
       <c r="F1191">
         <v>1</v>
       </c>
       <c r="G1191">
-        <v>0.006355865645280538</v>
+        <v>0.006348845314807832</v>
       </c>
       <c r="H1191">
-        <v>0.006284778105586983</v>
+        <v>0.006277933833558733</v>
       </c>
       <c r="I1191">
-        <v>0.05108753969355595</v>
+        <v>0.05091148124909983</v>
       </c>
       <c r="J1191">
-        <v>0.7635942461694478</v>
+        <v>0.7613935156137405</v>
       </c>
       <c r="K1191">
         <v>3.19</v>
@@ -61499,7 +61499,7 @@
         <v>1</v>
       </c>
       <c r="P1191" t="s">
-        <v>508</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1192" spans="1:16">
@@ -61507,93 +61507,93 @@
         <v>0</v>
       </c>
       <c r="B1192" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C1192">
-        <v>1.491154685192168</v>
+        <v>1.57604516738898</v>
       </c>
       <c r="D1192" t="s">
-        <v>354</v>
+        <v>210</v>
       </c>
       <c r="E1192">
-        <v>1.542066166441268</v>
+        <v>1.505017795248746</v>
       </c>
       <c r="F1192">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1192">
-        <v>0.006348845314807832</v>
+        <v>0.00626395483261102</v>
       </c>
       <c r="H1192">
-        <v>0.006277933833558733</v>
+        <v>0.006374982204751255</v>
       </c>
       <c r="I1192">
-        <v>0.05091148124909983</v>
+        <v>0.07102737214023414</v>
       </c>
       <c r="J1192">
-        <v>0.7613935156137405</v>
+        <v>0.7585614345019484</v>
       </c>
       <c r="K1192">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
       <c r="L1192">
         <v>3.92</v>
       </c>
       <c r="M1192">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="N1192">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="O1192">
         <v>1</v>
       </c>
       <c r="P1192" t="s">
-        <v>214</v>
+        <v>359</v>
       </c>
     </row>
     <row r="1193" spans="1:16">
       <c r="A1193" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1193" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C1193">
-        <v>1.57604516738898</v>
+        <v>1.500189023938785</v>
       </c>
       <c r="D1193" t="s">
-        <v>210</v>
+        <v>354</v>
       </c>
       <c r="E1193">
-        <v>1.505017795248746</v>
+        <v>1.550873938698941</v>
       </c>
       <c r="F1193">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1193">
-        <v>0.00626395483261102</v>
+        <v>0.006339810976061215</v>
       </c>
       <c r="H1193">
-        <v>0.006374982204751255</v>
+        <v>0.00626912606130106</v>
       </c>
       <c r="I1193">
-        <v>0.07102737214023414</v>
+        <v>0.05068491476015602</v>
       </c>
       <c r="J1193">
         <v>0.7585614345019484</v>
       </c>
       <c r="K1193">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="L1193">
         <v>3.92</v>
       </c>
       <c r="M1193">
-        <v>3.21</v>
+        <v>3.11</v>
       </c>
       <c r="N1193">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="O1193">
         <v>1</v>
@@ -61604,34 +61604,34 @@
     </row>
     <row r="1194" spans="1:16">
       <c r="A1194" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1194" t="s">
         <v>208</v>
       </c>
       <c r="C1194">
-        <v>1.500189023938785</v>
+        <v>1.5071415834207</v>
       </c>
       <c r="D1194" t="s">
         <v>354</v>
       </c>
       <c r="E1194">
-        <v>1.550873938698941</v>
+        <v>1.557652139322375</v>
       </c>
       <c r="F1194">
         <v>1</v>
       </c>
       <c r="G1194">
-        <v>0.006339810976061215</v>
+        <v>0.0063328584165793</v>
       </c>
       <c r="H1194">
-        <v>0.00626912606130106</v>
+        <v>0.006262347860677625</v>
       </c>
       <c r="I1194">
-        <v>0.05068491476015602</v>
+        <v>0.05051055590167541</v>
       </c>
       <c r="J1194">
-        <v>0.7585614345019484</v>
+        <v>0.7563819487709404</v>
       </c>
       <c r="K1194">
         <v>3.19</v>
@@ -61649,7 +61649,7 @@
         <v>1</v>
       </c>
       <c r="P1194" t="s">
-        <v>359</v>
+        <v>215</v>
       </c>
     </row>
     <row r="1195" spans="1:16">
@@ -61660,28 +61660,28 @@
         <v>208</v>
       </c>
       <c r="C1195">
-        <v>1.5071415834207</v>
+        <v>1.519176243368408</v>
       </c>
       <c r="D1195" t="s">
         <v>354</v>
       </c>
       <c r="E1195">
-        <v>1.557652139322375</v>
+        <v>1.569384989616222</v>
       </c>
       <c r="F1195">
         <v>1</v>
       </c>
       <c r="G1195">
-        <v>0.0063328584165793</v>
+        <v>0.006320823756631592</v>
       </c>
       <c r="H1195">
-        <v>0.006262347860677625</v>
+        <v>0.006250615010383778</v>
       </c>
       <c r="I1195">
-        <v>0.05051055590167541</v>
+        <v>0.05020874624781424</v>
       </c>
       <c r="J1195">
-        <v>0.7563819487709404</v>
+        <v>0.7526093280976778</v>
       </c>
       <c r="K1195">
         <v>3.19</v>
@@ -61699,7 +61699,7 @@
         <v>1</v>
       </c>
       <c r="P1195" t="s">
-        <v>215</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1196" spans="1:16">
@@ -61710,28 +61710,28 @@
         <v>208</v>
       </c>
       <c r="C1196">
-        <v>1.519176243368408</v>
+        <v>1.528360032203719</v>
       </c>
       <c r="D1196" t="s">
         <v>354</v>
       </c>
       <c r="E1196">
-        <v>1.569384989616222</v>
+        <v>1.578338463997983</v>
       </c>
       <c r="F1196">
         <v>1</v>
       </c>
       <c r="G1196">
-        <v>0.006320823756631592</v>
+        <v>0.006311639967796282</v>
       </c>
       <c r="H1196">
-        <v>0.006250615010383778</v>
+        <v>0.006241661536002018</v>
       </c>
       <c r="I1196">
-        <v>0.05020874624781424</v>
+        <v>0.0499784317942642</v>
       </c>
       <c r="J1196">
-        <v>0.7526093280976778</v>
+        <v>0.7497303974283014</v>
       </c>
       <c r="K1196">
         <v>3.19</v>
@@ -61749,7 +61749,7 @@
         <v>1</v>
       </c>
       <c r="P1196" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1197" spans="1:16">
@@ -61757,31 +61757,31 @@
         <v>0</v>
       </c>
       <c r="B1197" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1197">
-        <v>1.533354640152285</v>
+        <v>1.545059323053998</v>
       </c>
       <c r="D1197" t="s">
         <v>354</v>
       </c>
       <c r="E1197">
-        <v>1.578338463997983</v>
+        <v>1.589821607160231</v>
       </c>
       <c r="F1197">
         <v>1</v>
       </c>
       <c r="G1197">
-        <v>0.006286645359847716</v>
+        <v>0.006274940676946002</v>
       </c>
       <c r="H1197">
-        <v>0.006241661536002018</v>
+        <v>0.006230178392839771</v>
       </c>
       <c r="I1197">
-        <v>0.0449838238456981</v>
+        <v>0.04476228410623317</v>
       </c>
       <c r="J1197">
-        <v>0.7497303974283014</v>
+        <v>0.7460380684372249</v>
       </c>
       <c r="K1197">
         <v>3.17</v>
@@ -61799,7 +61799,7 @@
         <v>1</v>
       </c>
       <c r="P1197" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1198" spans="1:16">
@@ -61810,28 +61810,28 @@
         <v>208</v>
       </c>
       <c r="C1198">
-        <v>1.528360032203719</v>
+        <v>1.540138561685253</v>
       </c>
       <c r="D1198" t="s">
         <v>354</v>
       </c>
       <c r="E1198">
-        <v>1.578338463997983</v>
+        <v>1.589821607160231</v>
       </c>
       <c r="F1198">
         <v>1</v>
       </c>
       <c r="G1198">
-        <v>0.006311639967796282</v>
+        <v>0.006299861438314747</v>
       </c>
       <c r="H1198">
-        <v>0.006241661536002018</v>
+        <v>0.006230178392839771</v>
       </c>
       <c r="I1198">
-        <v>0.0499784317942642</v>
+        <v>0.04968304547497793</v>
       </c>
       <c r="J1198">
-        <v>0.7497303974283014</v>
+        <v>0.7460380684372249</v>
       </c>
       <c r="K1198">
         <v>3.19</v>
@@ -61849,95 +61849,95 @@
         <v>1</v>
       </c>
       <c r="P1198" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1199" spans="1:16">
       <c r="A1199" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1199" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C1199">
-        <v>1.618316895792247</v>
+        <v>1.554351261278527</v>
       </c>
       <c r="D1199" t="s">
-        <v>217</v>
+        <v>354</v>
       </c>
       <c r="E1199">
-        <v>1.565846552075134</v>
+        <v>1.598937672736978</v>
       </c>
       <c r="F1199">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1199">
-        <v>0.006161683104207754</v>
+        <v>0.006265648738721473</v>
       </c>
       <c r="H1199">
-        <v>0.006274153447924867</v>
+        <v>0.006221062327263022</v>
       </c>
       <c r="I1199">
-        <v>0.05247034371711345</v>
+        <v>0.04458641145845066</v>
       </c>
       <c r="J1199">
-        <v>0.7497303974283014</v>
+        <v>0.7431068576408432</v>
       </c>
       <c r="K1199">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
       <c r="L1199">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="M1199">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="N1199">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="O1199">
         <v>1</v>
       </c>
       <c r="P1199" t="s">
-        <v>510</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1200" spans="1:16">
       <c r="A1200" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1200" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C1200">
-        <v>1.545059323053998</v>
+        <v>1.54948912412571</v>
       </c>
       <c r="D1200" t="s">
         <v>354</v>
       </c>
       <c r="E1200">
-        <v>1.589821607160231</v>
+        <v>1.598937672736978</v>
       </c>
       <c r="F1200">
         <v>1</v>
       </c>
       <c r="G1200">
-        <v>0.006274940676946002</v>
+        <v>0.00629051087587429</v>
       </c>
       <c r="H1200">
-        <v>0.006230178392839771</v>
+        <v>0.006221062327263022</v>
       </c>
       <c r="I1200">
-        <v>0.04476228410623317</v>
+        <v>0.04944854861126791</v>
       </c>
       <c r="J1200">
-        <v>0.7460380684372249</v>
+        <v>0.7431068576408432</v>
       </c>
       <c r="K1200">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="L1200">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="M1200">
         <v>3.11</v>
@@ -61949,145 +61949,145 @@
         <v>1</v>
       </c>
       <c r="P1200" t="s">
-        <v>511</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1201" spans="1:16">
       <c r="A1201" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1201" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C1201">
-        <v>1.540138561685253</v>
+        <v>1.638386221348246</v>
       </c>
       <c r="D1201" t="s">
-        <v>354</v>
+        <v>217</v>
       </c>
       <c r="E1201">
-        <v>1.589821607160231</v>
+        <v>1.586644467007752</v>
       </c>
       <c r="F1201">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1201">
-        <v>0.006299861438314747</v>
+        <v>0.006141613778651754</v>
       </c>
       <c r="H1201">
-        <v>0.006230178392839771</v>
+        <v>0.006253355532992248</v>
       </c>
       <c r="I1201">
-        <v>0.04968304547497793</v>
+        <v>0.05174175434049344</v>
       </c>
       <c r="J1201">
-        <v>0.7460380684372249</v>
+        <v>0.7431068576408432</v>
       </c>
       <c r="K1201">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="L1201">
+        <v>3.89</v>
+      </c>
+      <c r="M1201">
+        <v>3.14</v>
+      </c>
+      <c r="N1201">
         <v>3.92</v>
       </c>
-      <c r="M1201">
-        <v>3.11</v>
-      </c>
-      <c r="N1201">
-        <v>3.91</v>
-      </c>
       <c r="O1201">
         <v>1</v>
       </c>
       <c r="P1201" t="s">
-        <v>511</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1202" spans="1:16">
       <c r="A1202" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1202" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C1202">
-        <v>1.629504652635209</v>
+        <v>1.560077217882976</v>
       </c>
       <c r="D1202" t="s">
-        <v>217</v>
+        <v>354</v>
       </c>
       <c r="E1202">
-        <v>1.577440465107114</v>
+        <v>1.604555251613898</v>
       </c>
       <c r="F1202">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1202">
-        <v>0.006150495347364791</v>
+        <v>0.006259922782117025</v>
       </c>
       <c r="H1202">
-        <v>0.006262559534892886</v>
+        <v>0.006215444748386104</v>
       </c>
       <c r="I1202">
-        <v>0.05206418752809494</v>
+        <v>0.04447803373092185</v>
       </c>
       <c r="J1202">
-        <v>0.7460380684372249</v>
+        <v>0.7413005621820266</v>
       </c>
       <c r="K1202">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
       <c r="L1202">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="M1202">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="N1202">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="O1202">
         <v>1</v>
       </c>
       <c r="P1202" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1203" spans="1:16">
       <c r="A1203" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1203" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C1203">
-        <v>1.554351261278527</v>
+        <v>1.555251206639335</v>
       </c>
       <c r="D1203" t="s">
         <v>354</v>
       </c>
       <c r="E1203">
-        <v>1.598937672736978</v>
+        <v>1.604555251613898</v>
       </c>
       <c r="F1203">
         <v>1</v>
       </c>
       <c r="G1203">
-        <v>0.006265648738721473</v>
+        <v>0.006284748793360665</v>
       </c>
       <c r="H1203">
-        <v>0.006221062327263022</v>
+        <v>0.006215444748386104</v>
       </c>
       <c r="I1203">
-        <v>0.04458641145845066</v>
+        <v>0.04930404497456253</v>
       </c>
       <c r="J1203">
-        <v>0.7431068576408432</v>
+        <v>0.7413005621820266</v>
       </c>
       <c r="K1203">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="L1203">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="M1203">
         <v>3.11</v>
@@ -62099,45 +62099,45 @@
         <v>1</v>
       </c>
       <c r="P1203" t="s">
-        <v>210</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1204" spans="1:16">
       <c r="A1204" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1204" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C1204">
-        <v>1.54948912412571</v>
+        <v>1.568848653254727</v>
       </c>
       <c r="D1204" t="s">
         <v>354</v>
       </c>
       <c r="E1204">
-        <v>1.598937672736978</v>
+        <v>1.613160666126877</v>
       </c>
       <c r="F1204">
         <v>1</v>
       </c>
       <c r="G1204">
-        <v>0.00629051087587429</v>
+        <v>0.006251151346745274</v>
       </c>
       <c r="H1204">
-        <v>0.006221062327263022</v>
+        <v>0.006206839333873123</v>
       </c>
       <c r="I1204">
-        <v>0.04944854861126791</v>
+        <v>0.04431201287215059</v>
       </c>
       <c r="J1204">
-        <v>0.7431068576408432</v>
+        <v>0.7385335478691714</v>
       </c>
       <c r="K1204">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="L1204">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="M1204">
         <v>3.11</v>
@@ -62149,57 +62149,57 @@
         <v>1</v>
       </c>
       <c r="P1204" t="s">
-        <v>210</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1205" spans="1:16">
       <c r="A1205" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1205" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C1205">
-        <v>1.638386221348246</v>
+        <v>1.564077982297343</v>
       </c>
       <c r="D1205" t="s">
-        <v>217</v>
+        <v>354</v>
       </c>
       <c r="E1205">
-        <v>1.586644467007752</v>
+        <v>1.613160666126877</v>
       </c>
       <c r="F1205">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1205">
-        <v>0.006141613778651754</v>
+        <v>0.006275922017702657</v>
       </c>
       <c r="H1205">
-        <v>0.006253355532992248</v>
+        <v>0.006206839333873123</v>
       </c>
       <c r="I1205">
-        <v>0.05174175434049344</v>
+        <v>0.04908268382953418</v>
       </c>
       <c r="J1205">
-        <v>0.7431068576408432</v>
+        <v>0.7385335478691714</v>
       </c>
       <c r="K1205">
-        <v>3.03</v>
+        <v>3.19</v>
       </c>
       <c r="L1205">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="M1205">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="N1205">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="O1205">
         <v>1</v>
       </c>
       <c r="P1205" t="s">
-        <v>210</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1206" spans="1:16">
@@ -62207,31 +62207,31 @@
         <v>0</v>
       </c>
       <c r="B1206" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1206">
-        <v>1.560077217882976</v>
+        <v>1.573316459270653</v>
       </c>
       <c r="D1206" t="s">
         <v>354</v>
       </c>
       <c r="E1206">
-        <v>1.604555251613898</v>
+        <v>1.617543907991082</v>
       </c>
       <c r="F1206">
         <v>1</v>
       </c>
       <c r="G1206">
-        <v>0.006259922782117025</v>
+        <v>0.006246683540729348</v>
       </c>
       <c r="H1206">
-        <v>0.006215444748386104</v>
+        <v>0.006202456092008919</v>
       </c>
       <c r="I1206">
-        <v>0.04447803373092185</v>
+        <v>0.04422744872042905</v>
       </c>
       <c r="J1206">
-        <v>0.7413005621820266</v>
+        <v>0.7371241453404882</v>
       </c>
       <c r="K1206">
         <v>3.17</v>
@@ -62249,7 +62249,7 @@
         <v>1</v>
       </c>
       <c r="P1206" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1207" spans="1:16">
@@ -62260,28 +62260,28 @@
         <v>208</v>
       </c>
       <c r="C1207">
-        <v>1.555251206639335</v>
+        <v>1.568573976363842</v>
       </c>
       <c r="D1207" t="s">
         <v>354</v>
       </c>
       <c r="E1207">
-        <v>1.604555251613898</v>
+        <v>1.617543907991082</v>
       </c>
       <c r="F1207">
         <v>1</v>
       </c>
       <c r="G1207">
-        <v>0.006284748793360665</v>
+        <v>0.006271426023636158</v>
       </c>
       <c r="H1207">
-        <v>0.006215444748386104</v>
+        <v>0.006202456092008919</v>
       </c>
       <c r="I1207">
-        <v>0.04930404497456253</v>
+        <v>0.04896993162723939</v>
       </c>
       <c r="J1207">
-        <v>0.7413005621820266</v>
+        <v>0.7371241453404882</v>
       </c>
       <c r="K1207">
         <v>3.19</v>
@@ -62299,7 +62299,7 @@
         <v>1</v>
       </c>
       <c r="P1207" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1208" spans="1:16">
@@ -62307,31 +62307,31 @@
         <v>0</v>
       </c>
       <c r="B1208" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1208">
-        <v>1.568848653254727</v>
+        <v>1.567016297975903</v>
       </c>
       <c r="D1208" t="s">
         <v>354</v>
       </c>
       <c r="E1208">
-        <v>1.613160666126877</v>
+        <v>1.611362992651438</v>
       </c>
       <c r="F1208">
         <v>1</v>
       </c>
       <c r="G1208">
-        <v>0.006251151346745274</v>
+        <v>0.006252983702024098</v>
       </c>
       <c r="H1208">
-        <v>0.006206839333873123</v>
+        <v>0.006208637007348562</v>
       </c>
       <c r="I1208">
-        <v>0.04431201287215059</v>
+        <v>0.04434669467553487</v>
       </c>
       <c r="J1208">
-        <v>0.7385335478691714</v>
+        <v>0.7391115779255828</v>
       </c>
       <c r="K1208">
         <v>3.17</v>
@@ -62349,7 +62349,7 @@
         <v>1</v>
       </c>
       <c r="P1208" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1209" spans="1:16">
@@ -62360,28 +62360,28 @@
         <v>208</v>
       </c>
       <c r="C1209">
-        <v>1.564077982297343</v>
+        <v>1.562234066417391</v>
       </c>
       <c r="D1209" t="s">
         <v>354</v>
       </c>
       <c r="E1209">
-        <v>1.613160666126877</v>
+        <v>1.611362992651438</v>
       </c>
       <c r="F1209">
         <v>1</v>
       </c>
       <c r="G1209">
-        <v>0.006275922017702657</v>
+        <v>0.006277765933582609</v>
       </c>
       <c r="H1209">
-        <v>0.006206839333873123</v>
+        <v>0.006208637007348562</v>
       </c>
       <c r="I1209">
-        <v>0.04908268382953418</v>
+        <v>0.04912892623404685</v>
       </c>
       <c r="J1209">
-        <v>0.7385335478691714</v>
+        <v>0.7391115779255828</v>
       </c>
       <c r="K1209">
         <v>3.19</v>
@@ -62399,57 +62399,57 @@
         <v>1</v>
       </c>
       <c r="P1209" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1210" spans="1:16">
       <c r="A1210" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1210" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C1210">
-        <v>1.652243349956411</v>
+        <v>1.566363106476563</v>
       </c>
       <c r="D1210" t="s">
-        <v>217</v>
+        <v>354</v>
       </c>
       <c r="E1210">
-        <v>1.601004659690802</v>
+        <v>1.61538848311665</v>
       </c>
       <c r="F1210">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1210">
-        <v>0.006127756650043589</v>
+        <v>0.006273636893523437</v>
       </c>
       <c r="H1210">
-        <v>0.006238995340309199</v>
+        <v>0.00620461151688335</v>
       </c>
       <c r="I1210">
-        <v>0.05123869026560923</v>
+        <v>0.04902537664008655</v>
       </c>
       <c r="J1210">
-        <v>0.7385335478691714</v>
+        <v>0.7378172080010774</v>
       </c>
       <c r="K1210">
-        <v>3.03</v>
+        <v>3.19</v>
       </c>
       <c r="L1210">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="M1210">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="N1210">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="O1210">
         <v>1</v>
       </c>
       <c r="P1210" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1211" spans="1:16">
@@ -62457,49 +62457,49 @@
         <v>0</v>
       </c>
       <c r="B1211" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C1211">
-        <v>1.568573976363842</v>
+        <v>1.571925651019426</v>
       </c>
       <c r="D1211" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E1211">
-        <v>1.617543907991082</v>
+        <v>1.63085063432662</v>
       </c>
       <c r="F1211">
         <v>1</v>
       </c>
       <c r="G1211">
-        <v>0.006271426023636158</v>
+        <v>0.006168074348980575</v>
       </c>
       <c r="H1211">
-        <v>0.006202456092008919</v>
+        <v>0.00610914936567338</v>
       </c>
       <c r="I1211">
-        <v>0.04896993162723939</v>
+        <v>0.05892498330719409</v>
       </c>
       <c r="J1211">
-        <v>0.7371241453404882</v>
+        <v>0.7365622913399277</v>
       </c>
       <c r="K1211">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="L1211">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="M1211">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="N1211">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="O1211">
         <v>1</v>
       </c>
       <c r="P1211" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1212" spans="1:16">
@@ -62507,49 +62507,49 @@
         <v>1</v>
       </c>
       <c r="B1212" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C1212">
-        <v>1.656513839618321</v>
+        <v>1.570366290625631</v>
       </c>
       <c r="D1212" t="s">
-        <v>217</v>
+        <v>354</v>
       </c>
       <c r="E1212">
-        <v>1.605430183630867</v>
+        <v>1.619291273932825</v>
       </c>
       <c r="F1212">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1212">
-        <v>0.006123486160381679</v>
+        <v>0.00626963370937437</v>
       </c>
       <c r="H1212">
-        <v>0.006234569816369133</v>
+        <v>0.006200708726067175</v>
       </c>
       <c r="I1212">
-        <v>0.0510836559874539</v>
+        <v>0.04892498330719475</v>
       </c>
       <c r="J1212">
-        <v>0.7371241453404882</v>
+        <v>0.7365622913399277</v>
       </c>
       <c r="K1212">
-        <v>3.03</v>
+        <v>3.19</v>
       </c>
       <c r="L1212">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="M1212">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="N1212">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="O1212">
         <v>1</v>
       </c>
       <c r="P1212" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1213" spans="1:16">
@@ -62560,28 +62560,28 @@
         <v>209</v>
       </c>
       <c r="C1213">
-        <v>1.563971876872182</v>
+        <v>1.573531281390085</v>
       </c>
       <c r="D1213" t="s">
         <v>358</v>
       </c>
 